--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69893410-B92B-4A9C-B93E-599EF283EF23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E65165-62A4-4188-BB7C-56029849ADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
+    <sheet name="Transcripts" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$G$37</definedName>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="184">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -467,6 +468,5606 @@
   </si>
   <si>
     <t>youtube_link</t>
+  </si>
+  <si>
+    <t>transcript</t>
+  </si>
+  <si>
+    <t>Jordan: How'd you um break up your axe?
+Darius: Which one?
+Jordan: Oh, I thought you said break up with my ex... I think I've had one ex-girlfriend. I'm fucking 37 years old.
+Darius: So when you were shotting at Anthony, what happened?
+Jordan: Hey everybody, welcome to Out the Trunk with Jordan and Darius. My name is Jordan. Jordybe riding on all socials.
+Darius: And I'm Darius, that's D's all up in your area on all socials.
+Jordan: And today we're going to be reviewing 12 Angry Men. This movie came out in 1957. This is actually the oldest movie we've reviewed so far, so it is black and white, literally a classic movie.
+Darius: Might be the oldest by like 30 years.
+Jordan: Yeah, no, definitely. We haven't done any 70s movies yet. Yeah, definitely. Good 30 years. Maybe 40, shit. Did a lot of 90s movies. Um, it's starring legendary Henry Fonda, that's Jane Fonda's dad for those who don't know, Lee J. Cobb, Ed Begley, E.G. Marshall, Jack Warden, Martin Balsam, John Fiedler, Jack Klugman, Edward Binns, Joseph Sweeney, George Voskovec, and Robert Webber. 12 Angry Men follows a seemingly open and shut murder trial where 12 jurors retreat to a sweltering room to debate. While 11 are ready to convict a teenager for killing his father, one lone dissenter forces the group to reexamine the evidence. Tensions boil as personal prejudices collide with the pursuit of justice. So I'll toss it to you for Act 1.
+Darius: Act 1, The Lone Voice. The jury enters a deliberation room and takes an initial vote, resulting in an 11-1 for guilty. Juror 8 stands alone, arguing that they owe the defendant a serious discussion before sending him to his death. Off the rip, let me just say to the people out there listening, never ever ever skip jury duty. Um, never ever ever skip jury duty. I know it's annoying. I know you don't want to do it, but it is your civic duty, unless you or your spouse are 9 months pregnant, take your ass down to the courthouse and sign up for jury duty. It is the only way this thing works. So, um, what you got for Act 1, man?
+Jordan: Um, so I love this movie. This is one of my favorite movies of all time. I think it's literally a perfect movie. Um, it's less than 100 minutes and you have 12 fully fleshed out characters, excellent dialogue, excellent exposition, and there's like literally not a line wasted. Um, this movie does require multiple rewatches because that way you can kind of catch everything the plot is setting up in the first act all the way through the third, and everything literally comes full circle. Um, so I did want to say that. And, uh, it's also crazy that, uh, Henry Fonda didn't win an Oscar for this movie. Took him like 50 years to get his first Oscar. Um, I don't see how he didn't win one for this role.
+Darius: This movie didn't win any Oscars, it went 0 for 3.
+Jordan: Yeah, it's fucking nuts.
+Darius: I don't know what beat it, I guess we could Google it, but um...
+Jordan: Yeah.
+Darius: Yeah, I agree. One of my favorite movies of all time. Um, I just love how it just it's so, it kind of exemplifies why our system, our legal system, is so much better than other countries, other peer countries, because you just have 12 regular people who are just... you're not... the state doesn't throw you away in theory. Um, 12 regular people have to think about it, and the evidentiary burden is high, it's beyond a reasonable doubt because it should be hard. It should be incredibly difficult for the state to deprive you of your freedom. And your life.
+Jordan: You know, you know, it's not a bunch of scientists in there, it's not the state, it's just 12 regular people looking at the facts. The state gets to state their case, the defense gets to state their case. And, um, is it perfect? No, but I wouldn't have it any other way. So, I love this movie because it just, it shows the system working as it should.
+Darius: Yes.
+Jordan: And it shows people, one person with a healthy skepticism of the state, uh, just asking questions. And the more he asks questions, the more you see other people start to ask questions. And we should always be asking questions when the state wants to remove someone's freedom.
+Darius: Correct.
+Jordan: And so I just love it. I just, I just love how they set all that up and how they showed that. So. Um, what else you got for Act 1?
+Darius: Um, act one. Um, so one thing I wish, I mean obviously it's 50s, that there wasn't really a lot of color at that time. Uh, no pun intended, color in the art of filmmaking, not the actors at the time. So, uh, I just wish uh there was a little more uh clarity on what the ethnicity of the kid was, because I couldn't tell if he was supposed to be Hispanic or Italian. Um...
+Jordan: I think that was do you think that was intentional though?
+Darius: It's possible. It's possible.
+Jordan: Uh, I mean, I could just be imparting my 2026 sensibilities on a 1957.
+Darius: 'Cause neither, yes I was going to say, 'cause neither nationality or ethnicity was considered white at that time period. Like even Italians at that time period were not considered white. Um, so it does make sense.
+Jordan: And also, um, yeah, that's true. I don't... I lost my train of thought, but...
+Darius: Yeah.
+Jordan: Yeah, I think, well they didn't name the jurors and that felt intentional.
+Darius: Yeah for sure, that was definitely intentional.
+Jordan: And so I think they kept... I like to think that they kept the immutable characteristics of the people in the movie out of the movie because in theory justice is supposed to be colorblind. Uh, and that might be me putting 2026 onto 1957 sensibilities. It's hard to do that 'cause, again, this movie came out before our parents were born. So, I, you know, I literally can't... if a movie comes out 10 years ago, I can tell you what the world was like then and think about it, but I like to think that that was an intentional thing by the director. Is that justice is colorblind and we never got to know, you know, the names of the people in the room, it's just the facts are the facts and let's talk about the facts. And so...
+Darius: I agree. That's a good point. I actually have something a topic about that I'm gonna bring up in Act 3. Um...
+Jordan: Yeah, actually let me lead right into my next point about, uh, there's no character names.
+Darius: Yep.
+Jordan: At all. They're just literally the whole cast is Juror Number 1 through Juror Number 12. Um, I really love that because the only thing that this movie is truly about and the only thing that really matters, aside from obviously the the trial, is everyone's stories. Yep. 'Cause, you know, you go in there with your whole, you have your whole life that you've lived and you go into this room and you're supposed to throw away everything that you've thought prior to the trial starting about your inherent biases and um, you know, your triggers, things of that nature, but you know, we're human beings. And so we're flawed, therefore our decisions, our decision-making and our judgment and our system is going to be flawed, and I love the way that this uh, the movie illustrated that phenomenon.
+Darius: Yeah, it's just supposed to be 12 ordinary people, you know, um, which can be a bit tricky. Uh, there's a uh, there's a viral Sebastian Maniscalco bit and um, it's hard to make me laugh with stand up, I'm not crazy about it, but he has this bit, he's like, I got called down to jury duty and I'm in the line and um, you know, these people like are just the craziest people, he's like, ladies get the sheet and she's like, "Name?" and they're looking like, "Huh?" and they're just like, one lady's like, "I have a condition" and like this one guy is just looking at the thing like it's in a different language and he says, "I think to myself, this... you guys are going to decide who goes to prison?"
+Jordan: Right!
+Darius: "And the fucking sign-up sheet confuses you?"
+Jordan: Yeah!
+Darius: It's so real, like 12 ordinary people can be 12 ordinary people.
+Jordan: No, uh, so there's actually this really dope show that came out during the pandemic, I think it's called Jury Duty. I can't remember. It's got James Marsden in it. Where it's a the whole show is a prank. Where there's a fake trial and and there are 12 people on a jury. Only one guy there all... everybody's an actor except for this one guy, and just the most crazy shit happens. And so, um, there's this guy he was like trying to get out of jury duty 'cause you know nobody wants to do jury duty, and someone was like, "Just tell them you're racist. Just tell the judge you're racist and that you hate Black people."
+Darius: And so, but that's the problem though, right? Like, the only people on juries are people who couldn't get out of jury duty. And the kind of people who couldn't get out of jury duty are the people who aren't smart enough to know how, or who don't have a job that they can go to, that that can get out of... And so that's why I say everyone should accept and enthusiastically do jury duty, because again, the only people on juries are people who don't who aren't smart enough to figure out how to get out of it. That's how it is right now. And so that's why it's your civic duty to get on there because right now, basically the only people who can get stuck doing jury duty are like 12 unemployed people who who can't Google "how do I get out of jury duty".
+Jordan: So. That's why you should do it. Um, move want to head on to Act 2?
+Darius: Uh... yeah, yeah.
+Jordan: Alright. Act 2. We're going to call this Shifting the Tide. As the jurors meticulously break down the testimony of the witnesses, doubt begins to creep into the room. Heated arguments break out as more jurors change their votes, exposing deep-seated biases and personal flaws. Um... my note is redundant right there, so I'm gonna hand it to you. What you got for Act 2?
+Darius: Okay, uh, so Act 2. Uh, I have... I love the point that they, the... I forget what his number is, but Henry Fonda, he brings up the point about basically having a public defender. And the strain that they're under, you know, like they're they're not getting paid very well, they may not have had the resources or the time to really put together a compelling case. Um, at this time period, again it's before CCTV, it's before you know, DNA and all that stuff, so you it really looks like an open and shut case. And you're, and you know, I think some member you mentioned it's this young defender, so it may have been the guy's first case and it's it's a death, you know, death penalty murder murder. Um, you know, um... I don't envy the people who do that work, and they get a lot of they get a lot of shit. But I mean they are just as underserved in certain respects as the people that they they represent, you know?
+Jordan: The thing about um public defenders is, by and large, they're the best option available to you, they just don't have the time. And I say that to say that criminal defense in and of itself is not a lucrative practice. And so what happens when you like every so often you get like a famous one, like you know the one who does for all the rappers and like back then Johnnie Cochran. Right. By and large, if you are a person of means and you're hiring a firm to defend you in a criminal case, you're getting someone who doesn't practice criminal defense. They just, they practice other things and they're they're mapping over... they're good, they're probably, you know, fancy, have you know some white shoe law firm, but this is not their expertise. Public defenders, it is their expertise. Um, and so often they're better options, um, the caveat is if they have the time, and often they just don't. Um. And so the state gets unlimited resources to staff the prosecutor's office, and the defense just doesn't. Um, and so... I mean if you look at the average workload of a public defender, there's just no way they can zealously defend all their clients, and that's why you get so many plea deals. Um, and plea deals, I I don't even think should be constitutional. And so it gets... you get people pleeing out because they see their lawyers overwhelmed, and the state's throwing 10 years at them and saying, "Hey, you can take it to trial... you do two... and sometimes not even that, it'll be like, "Well, you can do a year plus time served and you'll be out in six weeks." And often these people can't post bail so they're already in jail. Right. And so someone saying you sign this piece of paper and plea, you get to go home today... what are you gonna do, you know? Right. You gonna sit in jail and try to fight this with your attorney who you see once a week who's dropping papers as they walk in 'cause they're so busy? Mm-hmm. Or you gonna sign that paper and go home? You know? Like it it's now what you don't know is that paper locks you in as a felon forever, and you're on, you know, probation and is, you know, you know what that is.
+Darius: Right. But, again, you're poor, so you're in jail, you can't make bail, if you get a bond at all, and someone's saying you sign this you get to go home. Most people are gonna go home. You know, like most... it's like uh the scene from a line from Training Day, "You wanna go to jail, or you wanna go home?"
+Jordan: Right, it's just, um, it's unfortunate. Um, it really is. But, what can you do? Do you think the kid was actually innocent, or did the jury just realize the prosecution didn't prove the case?
+Darius: Mm... Um... I think... I think the kid was innocent. Yeah. I think the kid was innocent. Um, maybe it's just the casting, he just didn't look like a killer to me. Yeah. Um, you know, and, um, even just like the way like the way they broke it down, you know, there was this the part about the the el train where someone said, "I heard them arguing. I couldn't tell what they were arguing about, but I heard him strike him." It's like, so you didn't hear the words they were screaming but you heard a punch? Like that just doesn't that doesn't make sense.
+Jordan: Eyewitnesses are just...
+Darius: Yeah. You saw you saw through an el train at night, a guy getting stabbed and you like, you know, and the point with the knife about, you know... I was a big uh, I was a big like greaser fan, like the novels and stuff like that, that S.E. Hinton novels when I was a kid, so I loved like switchblades and shit like that. And the point about the knife is just dead accurate. No even if you use a switchblade, even if you hadn't killed someone before, you were never going to use it like this. Right. 'Cause that's just not the style that you use. Um, and again, even the point that the fact that the the juror was able to find an exact copy pretty much of the the knife at a pawn shop. Those things are obviously popular, everybody probably had one in that area of the city, so I mean it really could have been anybody.
+Jordan: Um, I my thing is it just doesn't matter. It doesn't matter if he did it or not. True, that's true. The defense's job to prove if he did it, he didn't do it. Exactly. It's the prosecution's job to prove beyond a reasonable doubt that he did do it. A lot of people think the defense has to put up an alternative explanation, and they don't. Right. They just have to poke holes in the the prosecution's story. And so, I don't know whether he did it or not, (laughs) you know, sometimes the truth is stranger than fiction. Um, is it unusual to hold a knife that way? Yes, but stranger things have happened. I mean, yeah, spot on. Yeah. You know, um, but the point of the movie I think is that it just doesn't matter. You know, right. I mean I agree, I think the same thing. Um, and...
+Darius: We have to make it really hard to take someone's freedom, and part of that is the prosecution has to do their, they have a hard job, and they didn't do their job. So.
+Jordan: Right. Um, yeah I agree. And then also even, you know, with the like the the knife thing, it's like okay so he was dumb enough to leave the knife but smart enough to wipe it off? Like it just some of the the the it just there were a lot of fallacies there um in the the execution of the crime if you will, no pun intended. Um.
+Darius: Though you'd be surprised how dumb criminals are man. Like I I've heard of stories where um a home invasion one of the person people left their ID. Like...
+Jordan: Literally, um, like I don't know how why they took their ID out, but they literally left their ID at the crime scene. And if I told you that, you'd be like, "Who what kind of person..." I've literally heard of that story, where like, I don't know if it fell out their wallet, but like the cops showed up to the crime scene and like, the criminal's ID was there.
+Darius: Imagine they have you in the in the uh interrogation room, you're like, "No, I what, I didn't do it. I was at a restaurant." And they're like, "Sir, here's your ID." Just slap it on the table.
+Jordan: I would I would be like, "Hey, okay, I'll admit to it, but can y'all like lie and say y'all had something else, so my mom and them don't..." Can we just come up with something a bit more clever. I'm a criminal either way, but please don't let them know I'm stupid.
+Darius: And imagine you go to jail and that word spreads around, and they're like, "Yeah this nigga left his ID at the scene of the crime." "Left his ID!" Name, picture, height, eye color, weight, address... address... license number.
+Jordan: You might as well just leave and go to the police station.
+Darius: Yeah.
+Jordan: Say, "Hey I committed a crime today. Hey Brenda, is dispatch 'cause I did it."
+Darius: Yeah.
+Jordan: You might as well leave the crime and go straight to the police station and turn yourself in. Um. What else you got for Act 2, man?
+Darius: Um, oh yeah, so I love the scene where uh they were talking about like he screamed, "I want to kill him", and he's like, you know, he obviously meant it. No one says that without meaning it, and then he baited him into screaming, "I'm gonna kill you!" Yeah. And then at the end he's like, "You didn't really mean that." Uh this movie has some of the best one-liners ever.
+Jordan: Yeah, I mean, you have to be tricky with that because, you know, I'm so mad I could kill him, like okay, but like...
+Darius: Right.
+Jordan: That's why I'm always skeptical of like screenshots out of context as some sort of evidence of wrongdoing, um, because... you'd be surprised how crazy you look screenshot out of context. Um, and you might have nine months of a conversation where you've set the tone and and so on and so forth and like this is how y'all talk, but someone's looking at six messages in the middle of that... Yeah. With no other context. And it looks like you're begging or something like that. Yeah it's just you I'm show the whole like I'm, you know, I never trust out of context screenshots like that. So.
+Darius: That's true.
+Jordan: Um, anything else for Act 2?
+Darius: Um, no that was all I had for Act 2.
+Jordan: Well moving into Act 3, we're gonna call this The Final Verdict. The remaining holdouts face intense pressure as the logic of the prosecution's case crumbles. A final confrontation forces the last guilty voter to face his internal demons before the group reaches a unanimous decision. I loved the scene of them breaking down how hard it is to remember details. Um...
+Darius: Yes.
+Jordan: It's so much harder than people think. Um, and that's why, you know, defense attorneys say do not talk to the police. Even if you're innocent. Because um, you think it's easy to remember what you had for lunch last Tuesday, and I promise you it's not. Right. You know, it's like you know someone says asks me you know, "Where were you at 4 o'clock last Thursday?" I might say the gym 'cause I go to the gym every afternoon, but was that 4:15? Or okay let's say I say that, but I went to the gym at 4:15, and someone says, "Well no I heard him in his apartment at 4 o'clock." He said he was at the gym. But like my mind just thinks 4 o'clock is gym, but I might have left at 4:15. You know, like you it's just...
+Darius: And I think you lied about everything.
+Jordan: And now it sounds like you're lying, but no that's just not how the like I just told you a stock answer and I didn't time it to the minute, but for whatever reason I was 10 minutes behind and I went to the gym at 4:15 and now a neighbor's like, "Well I heard him in his room at 4 o'clock, he said he was..." And now you're like, that's why you just don't talk. You know, so... What you got for Act 3, man?
+Darius: Yeah, uh, that's one of my favorite scenes in the movie. Um, I also, uh, so I love this love this movie. For several reasons, one of the things I love about this movie is everyone in the cast is you can tell they're all at their core good hum- most of them are good human beings. Yeah. And they just have their shit that they just their baggage and shit that they have to deal with. Um, and I feel like there's I don't know if it's just 'cause it was the 50s and there's like the nostalgia of, you know, a certain kind of manners and things of that nature, but like the fact that that guy went on a racist rant and they all just stood up and literally turned their back.
+Jordan: And this is in the 50s. And it's like, man, maybe it wasn't that bad, but you know it was that bad. But you know it was that bad, but it was just kind of interesting to see that 'cause today that's just that's so okay now it feels like, and I know it was okay then too 'cause it was the 50s and we know what the sort of rights looked like back then. But it's just it's just interesting to to see that.
+Darius: Color in the film. It's a movie. So...
+Jordan: Oh for sure, yeah, yeah, it's a movie.
+Darius: Two, I'm guessing the just the characters in the movies, I don't think they stated their occupations, but like these looked like came off as just like well to do, high society people. Um, I'm I'm thinking it was in I believe it was in New York. New York which is, you know, progressive. These weren't 12 jurors in rural Mississippi. We'll put it like that.
+Jordan: Yeah, yeah, yeah, true. Just to set say it like that. Um... you know, so. Um, yeah, I just... I don't really have anything other than as the kids say "glazing" for Act 3 'cause it's just perfect when it's just asking him, "What movie did you go see?" and like he gets shakier and shakier...
+Darius: Who was in it? Who was in the movie? What was the what was the second feature?
+Jordan: And people watching today who might go to three movies a year don't understand that going to the movies is just it was like picking up takeout. You know, like it was just what you did, and so this idea that like you would remember the specific movie you saw and who was in it and that's it was a different time. Going to the movie is is what you did you know on your way home from work. And as a matter of fact type thing, and so I just it's just one of my favorite things about um, one of my pet, one of my hobby horses is just how inaccurate people's memories are actually are... especially like long-term things are are different, but like the minor details like what specifically you ate, what you ordered, um you know, where your location was, it's harder than you think. Yes. And especially when you're in an interrogation room and you think you're you're these you're untrained, they're trained. They do 10 of these a day, you don't. This is the first time you've ever been in that box. I promise you won't hold up as well as you think.
+Darius: Yeah, no, even if like I I got mugged when I was like 18, and they brought me in to you know give a statement and shit whatever, and I've been in the the room with the two-way mirrors and shit, and I didn't do anything wrong! Yeah. But I'm in that room and I'm just like a little nervous and you're like, you know what I mean, it's...
+Jordan: Your heart's like right here. Yeah.
+Darius: Yeah, and it's like they were showing me looking having me look through photos of people that I thought did it, and one of the guys I'm pretty sure was the guy, but I was like, well, if I'm wrong this person goes to jail... yeah, I could be ruining somebody's life. So I really wasn't sure. He's like scale 1 to 10. I was like, I think I said maybe like a 7 or some shit like that, but you know, it could have been. It could have been anybody. And so yeah that it's a really uh a really tricky system and a really tricky craft, you know solving crimes and things of that nature that people don't really... it's not it's not like the movies, you know what I'm saying.
+Jordan: No, it's not at all. Um, yeah, and and the thing is people who never who don't know anything about it would just say like, well why'd you lie? If you weren't if you weren't at the gym at 4 o'clock and you went at 4:15, why did you just say you went at 4:15? And it's like it's not how the brain works.
+Darius: No. Yeah, yeah. But it's easy I mean, it's intuitive to wonder like I know when I went to work, if it was 7:15 or 7 o'clock. You do until you don't, you know? Like...
+Jordan: Right. Yeah it's it's very easy to get that shit twisted. Like think about it like say like we work, we both work remote. So we can say certain time of day during the work day, we were at home. Right. But if they were to ask you what you were doing at 4:35 p.m.? Or 7:37 p.m.? What room in your house were you at? You might have went to the bathroom for a second and you thought you were at your at your monitor typing a prompt for the pod. Is is that easy. It is, and one inconsistency and now you're a liar.
+Darius: Yeah, you're fine.
+Jordan: And now everything you say is in question. And so. And then the juror jury sees that and then that again, similar to this movie, they're like, "Well, that's a hole." Yeah. And that's why defend a lot of defendants just don't take the stand. Um, 'cause if you take the stand, you got to do the the prosecution gets to question you as well, and it's hard to look good, especially when you're not ready for it, so. Right. Um, what else you got for Act 3, man?
+Darius: Um, so I was gonna say, so yeah, so I think one thing that makes this movie difficult to judge in terms of the characters is all of the jurors are white men. Yeah. And so they were more respectful, they were talking crazy to each other, but they were probably more respectful than they would have been in that time period to other genders and races. And it kind of makes it almost a little harder 'cause you almost wonder, I think back now I'm like if there was if it was a mixed jury, or if that movie was made today with a with a truly diverse uh set of jurors, would they have been as open to each other's opinions? Would would they have been able to even conceive of the possibility of coming to the same conclusion, like in this movie.
+Jordan: I just I mean, it depends on the case. Um... I like to think so. I do. Um, people obviously have their prejudices and their priors and their, you know, preconceived notions, I just said the same thing three times. But, um... you know, you get in that box and you're tasked with taking someone's freedom, I like to think that most people, if they've gotten that far in the situation, would take it seriously. Um... yeah. Um... you know, like I said, it's a big responsibility and obviously it's 12 random people. This is random and it isn't like you're jury is selected, um, and both sides get strikes, and um, so I don't know. Obviously it would be different 'cause you're bringing in any dynamic to a situation, especially one as potent as race, it changes things, but I like to think that most people in that situation would take the job seriously. So.
+Darius: I feel you.
+Jordan: It's rare that I see a high profile case that I think was just like outright wrong. Like I think the OJ trial was just... I don't know how nine people could listen to that evidence and say innocent, but um, like Casey Anthony, I don't think the prosecutors proved that case. I think she did it, but I don't think they proved their case. Oh yeah, she definitely did it, for sure. And so the jury is not tasked with uh anything but determining if the prosecution proved their case. And um, Casey Anthony was not a a lovable, you know, defendant, and and so, but the facts were the facts and the prosecution didn't prove their case. And so... yeah. You have to do what you have to do as a jury. You have to take your job seriously and you have to acquit. Even though I think she did it, I would have voted to acquit, given that's the evidence that they had, so.
+Darius: And and the thing too is that's also kind of a Catch-22 with the death penalty is most people are not prepared to send someone off to die. Yeah. Especially if there's like a if there's a a speck of doubt, that's some shit that you keep would keep you up at night for the rest of your life, you know?
+Jordan: That's why I don't believe in the death penalty. It's not 'cause I don't believe some crimes are are heinous enough to kill people over, I just don't trust the state to pick and choose. Um, and yeah. Life without parole is fine. I don't like why do we need to, you know, you're gonna sit in a room the sizes of a closet with another man and a bathroom for the rest of your life, like I don't need that's fine. We're good with that. Like you know. So, and you know, that's why when people, whenever there's a death penalty case and death penalty advocates and and abolitionists is, you know, at the last minute it's about time to execute, and they there's always someone on the internet who like looks at the crime and they go, "Um, you know this is I'm I'm out on this one. This one's terrible." And it's like, the problem with uh death penalty advo- advocates and and abolition is that there are no good cases. No one goes on death row for traffic tickets. And so if you're waiting around for a sympathetic victim, you'll never do any work. You know, like it's what do you think people go on death row for? They're all heinous crimes. And so you have to have a principled objection to it, otherwise you'll never do any active advocacy 'cause there's never going to be any good cases that are like there maybe in a blue moon you'll find one where it's obvious, but for the most part you're advocating for true people who've done terrible things. Um, and so you either you're in or you're out, 'cause if you're waiting around for a good one, you'll never do any work. You know?
+Darius: Facts. Um... did you have a favorite juror?
+Jordan: Nah, really. Um... I guess the guy um who who the short guy with the knife and he stood up and he's like showing how the angles wouldn't have worked. I thought that was pretty cool, um, bringing physical evidence, but nah man, it's hard to pick a favorite when I just everything was so well acted and so professional and and it did it felt like I was watching documentary footage. It didn't feel like a movie.
+Darius: No, you kind of forget.
+Jordan: Yeah, and so uh, I guess that's my question to you. You know, this is obviously considered one of the greatest films of all time, and why do you think it it resonated so well and why do you think it held up so well?
+Darius: Um... because it showed it's probably one of the best examples I've seen in a in a movie of literally just people. Yes. Like the complexities, the the beauty, the ugliness, the the judgment, the redemption, the love, the hate, the bigotry, the the grace, you know, it just it showed literally every spectrum of human emotion, of human behavior. Um, there was a point where you could look at every just about everybody in the movie and say like they were they were in the wrong. And then that same person, you could say here's where they did the right thing. And I think that's that's probably what I think is so so poignant about the movie. It also just it aged really well. Like it doesn't it doesn't feel like 50s. You know it doesn't feel like "Right here, Shay!", you know like it doesn't feel like that.
+Jordan: It feels it wasn't in black and white I it like, I mean the suits are a bit are fancy for the time, but like other than everybody being suited and booted, nothing feels like 1957 in it. Um...
+Darius: Exactly. And uh, I don't know if you did you know that there's a there's a remake that came out in 97. uh and that cast is loaded too and it's it's really, really good, it pretty much holds up. Um, yeah I think that it's just one of those stories where it's just a story about the human experience. And I think there's there's very there's very few things more dramatic than that, you know? Like it's it's basically I view it almost as like a sociology exp</t>
+  </si>
+  <si>
+    <t>Darius: He was mad because he felt like he had to give a ****.
+Jordan: He's like, I'm so hurt.
+Darius: Oh my God, how could you do this to me?
+Jordan: Hey everybody, welcome to Out of the Trunk Pile with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's these all up in your area on all socials.
+Jordan: And today we're going to be reviewing American Beauty. This movie came out in 1999, starring Kevin Spacey, Annette Bening, Dora Burch, Wes Bentley, Amanda Suvari, Chris Cooper, Allison Janney, and Peter Gallagher. This movie is about a guy named Lester Burnham, who's a suburban father suffering through a midlife crisis and a loveless marriage. After becoming infatuated with his daughter's teenage friend, he rebels against his mundane existence, seeking personal liberation. However, his radical transformation triggers a chain reaction of obsessions and secrets within his neighborhood. Someone tells us to you to set up act one.
+Darius: Act one, the wake up call. Lester lives a numb, numb, repetitive life until a high school basketball game changes his perspective and begins to reject his corporate job and his wife's perfectionism, seeking a new identity. Add this to the list of 90s movies that are about bored suburban nights way too comfortable. Yes. So that one's up there also. Very 90s in the sense that the cast looks like regular people. now every movie has, every movie has a bunch of extras that everyone in the movie looks like models. So it was a nice little touch. I was like, this feels very 90s and that the people look normal.
+Jordan: Yeah, I was watching it and I thought too, I was like, I feel like half of the cast would be considered ugly by today's standards. Not that any of them are actually ugly, but just like, it feels like Hollywood's very anti-normal looking people.
+Darius: Yeah, I mean, it just looked. Like a normal suburban area. And if it was casted today, like the everyday woman would be like Margot Roby. It was like, okay. Right.
+Jordan: Correct.
+Darius: I'm supposed to believe this woman is just normal. Everyone looking at her and no one's like crashing their cars as she walks by. Right. What do you have for act one, man?
+Jordan: I was going to say, just ask you whether is this your first time seeing it?
+Darius: Yes. Okay, which I know is weird because it was on my hard drive, but I just be downloading stuff. Like I just, it's the first, I don't even remember what prompted me to download it. I think Alice and Janie, I was watching West Wing.
+Jordan: Yeah, I love her.
+Darius: And I think I looked up like some movie she was in and they just got you.
+Jordan: Okay. Yeah. I think she didn't resume her for a minute. I didn't Google it because I was like, she looked because, you know, they aged her up. And I was like, wait, is that her?
+Darius: Yeah, this is before the West Wing and Yeah. man, I just, I got like 500 movies on a hard drive. I ain't watched them all, but this is my very first time seeing it. And it's a little weird, not gonna lie.
+Jordan: It is weird. It didn't quite age great.
+Darius: No, it did not.
+Jordan: Like it did not age great. Cause I mean, I didn't see it when it first came out cause I was 7. But I remember seeing this for the first time. I was like 18 or 19. We have, we have had it on DVD or whatever. And I watched it and I thought it was like incredible. And looking back, I was, you know, a teenager looking back now watching as a girl, I'm like, this is some sick ****.
+Darius: Yeah. Honestly, there's some things I had to just fast forward through because I felt weird.
+Jordan: No, I feel. Yeah, I feel.
+Darius: There's one at the end where I'm like, yeah, I'm not watching this. No. Oh, God, no. And then they. Yeah, there's a lot of stuff in this movie where I'm just like. How did it get made? Well, it got made even for the 90s. This is creepy, man. Like, I don't know how this would. This one's best picture. I don't think Oscars.
+Jordan: Yeah, and this got Kevin Spacey, his Oscar too.
+Darius: You know, I have later in my notes how did this win best picture, but.
+Jordan: Yeah, even so the window scene with his daughter. The girl who played his daughter was 17. She was not a, she was a minor when they shot this movie. They had to have her parents like on set. That's ******* crazy.
+Darius: This won an Oscar in 1999, right? Yeah. Best picture nominees. Let's see what it was up against. Cause I need to know.
+Jordan: Oh yeah, we need to know.
+Darius: This can't, well, it had to have been 2000 because it came out in 99.
+Jordan: Yeah.
+Darius: This beat the green mile. ****. That's crazy.
+Jordan: What else would it be?
+Darius: The Cider House Rules. Never seen that. The Insider.
+Jordan: Oh, that's really good. The Cider House Rules has Tobey Maguire, Delray Lindo, and Charlize Theron.
+Darius: I've never seen it.
+Jordan: It's really good. And Erykah Badu.
+Darius: Look at that. But no, I mean, this was worse than the Insider, the Green Mile, and the Sixth Sense to me. when you know the twist, it's kind of over.
+Jordan: that's nuts. Yeah, also, I think this is one of the movies you do have to watch multiple times because of the twist at the end. It makes everything make sense once you go back and watch it for sure. Did you kind of catch on? Not going to lie.
+Darius: This is the one and done for me.
+Jordan: I feel you. I get you. I get you. Because this whole movie, so you haven't seen the show Euphoria, but watching this as an adult, I feel like this movie walked so Euphoria could run from a standpoint of 1, pretty much every character in this movie is horrible. And the ones who aren't horrible are just really weird. And then of course, there's the underlying theme of predatory behavior and grooming and so on and so forth as well.
+Darius: I know I'm just becoming a middle-aged man because I would, I mean, Kevin Spacey's character in his movies, what, in his early 40s? Something like that, yeah. I'm 37 and I just, it's all gross. Like I, you know. Yeah, it's really gross. It's just, I'm just, he's too close to making
+Jordan: sure I have a daughter be like in college or something. I don't know. Yeah.
+Darius: You know, let's just move on. You got anything else for act one?
+Jordan: so I did like I did really like the scene of the wife who's a real estate agent she's like does all the work to clean the house up and get it ready for the sale open house or whatever and she's you know trying her best to sell it and like nobody buys it and she's just like completely devastated and like just has to crash out in silence in private you know as someone who has done like creative endeavors and just you know you put you put your all into it and you don't get the result And then that reality of it hitting, I can definitely relate to that. So I did like that they showed that aspect of the American dream in a sense, this movie is a lot about that. And I like that they showed that, she put her best foot forward. She, again, this whole movie is about like everything looking perfect on the surface and on the inside, it's a mess. And I felt like that scene really did a great job of illustrating that.
+Darius: It's the, what is it? The, I forget the word, but Yeah, man, when you pour yourself all into something, especially a creative endeavor, I'm reminded of the lady who wrote a book and it was like, it was like a PhD thesis and it was a, I wish I knew more specifics about it, but she was on tour for the book and a host asked her a very straightforward question and it like undermined the thesis of her entire book. Oh man. And she, let me see if I can find that. And host asked question that undermines thesis of entire book.
+Jordan: It was.
+Darius: It was. Yeah, it was Naomi Wolf. Hold on.
+Jordan: Okay.
+Darius: Naomi Wolf, American author journalist. It's really good.
+Jordan: Disproved. Apparently she sought to delay the release of her thesis.
+Darius: Yeah, so it was like she was on, she wrote a book about 150,000 women dying every year from anorexia. But the data she was pulling was from like a different, like I want to say it was like an English journal. And there was like, you know, there's like a language barrier there, even though it's in the same language. And like the word meant something totally different. And it just undermined her whole thesis. And it was like,
+Jordan: Yikes.
+Darius: It was just, I forget what it was, but he was like, you do realize that word means something different here. And she was like, what? He's like, what? It's like her whole book just fell apart. And it was like, caught live on camera. This is bad radio. So I'll stop like looking it up. But it's, it's, it's one of the funniest ones of all time where he's just like, oh man. You know, it's like there was like, It was a Supreme Court case. This is an example. It doesn't work, but it works in a sense that like, yeah. The dude in, this just speaks to like vernacular differences. And he was being interrogated by the cops. And he said, I want a lawyer, dog. And she had ruled that you asked for a lawyer dog. And it was something like that, but for like a PhD thesis that she had spent. And she just didn't know that word meant something else somewhere else.
+Jordan: And that's unfortunate.
+Darius: Yeah. So way off topic.
+Jordan: That's so precious, dude. You saw her die on TV.
+Darius: But he's like, yeah. It was rough.
+Jordan: Oh, man. So I will say this movie is really did a great job of like dark humor. in the spots that were supposed to be funny. one of my favorite scenes in the movies when the gay neighbors come up to the military guy and they're like, Hey, we want to work in the neighborhood. He's like, What are you selling? He's like, Oh no, we're not selling anything. We just want to look into the neighborhood. He's like, But you said you have a partner, so what are y'all in business together for? He said, Well, I'm a tax attorney, and he does, was it like engineering or some ****?
+Darius: Anesthesiologist.
+Jordan: Anesthesiologist. And he's like, What the ****?
+Darius: Oh, now that was very nineties, because you can't keep in mind or back or Bergefell was a Supreme Court ruling in 2011 making gay marriage legal. So they even 20 years. So in 1999, they would be like husbands was just. Yeah, he thought they were business partners. Yeah, I think so. That was actually a funny way to I mean, the movie wasn't trying to, but kind of reveals the era of the movie.
+Jordan: Yeah, it does. It does.
+Darius: We get it to act two, breaking the mold. Lester starts working out and smoking with his neighbor, Ricky, while Caroline pursues her own professional validation in the by way of an affair. Tensions about as their daughter goes further away from her parents chaos. I do love that they shoot a scene where the two teenagers are in the car listening to Bill Weathers.
+Jordan: Oh, yeah, that's right. I forgot about that. Yeah. Even by the- That's some super 90s ****.
+Darius: You know, back then we did have to listen to our parents' music.
+Jordan: Yeah.
+Darius: But I don't know, man. Like when I was a teenager, I wasn't rolling around bumping Al Green. No, I like Al Green, but nah. Me too, me too.
+Jordan: Correct.
+Darius: Like no Eminem, no NSYNC, no Brittany Spears.
+Jordan: Yeah, no Nirvana.
+Darius: I'm like, these two white teenagers are not listening to no ******* and no sunshine when she's gone.
+Jordan: They don't know the Kirkland soundtrack.
+Darius: Not only is it an age gap, it's a racial gap. Yeah, racial *******.
+Jordan: Yeah, cultural gap, everything socioeconomic.
+Darius: But you can't brag too bad.
+Jordan: What was I going to say? Yeah, so I. So this movie does. I mean, obviously we see there in like the loveless marriage. I do wish they had kind of shown a little or talked about like how it got to that point. But it's almost, it's crazy because it's like you almost don't know which parent is worse because you have one that's like having a midlife crisis, midlife crisis and is like grooming basically. And then you have the other who's a perfectionist and a cheater and all that. So you almost don't know which one to root against or which one to root for, which is a weird conundrum.
+Darius: I think they kind of showed it in the sense that like, I think The marriage fell apart and became loveless because they were bored. Suburban nights, like everything was going too well. He had a good job. She had a good job.
+Jordan: She had a good job.
+Darius: Kids are being raised, right? Daughters are cheerleader.
+Jordan: Come home, eat dinner, you go to bed. And that's kind of that. Do it all again.
+Darius: It's a plot of Fight Club, right? He just got bored of. He just too comfortable. And so.
+Jordan: Yeah.
+Darius: This is a weird.
+Jordan: I feel like this movie.
+Darius: Go ahead. Sorry.
+Jordan: I feel like this movie accomplished everything that American fiction failed to do. I'm sorry, not American fiction. What did we just do? What did we just watch? Stranger than fiction. Stranger than fiction.
+Darius: Yes, I agree. But this is random. I didn't even have this written down, but you just mentioned the loveless marriage. Thoughts on sticking into the loveless marriage for the kids.
+Jordan: No, do not do it for the kids. Kids don't need it. Kids don't want to see it. Kids don't deserve it. I think kids should be in, kids should be raised by people, two people, even if they're in different homes who are mentally stable and happy and mentally healthy and have a life of wellness. I don't think teaching, I don't think there's any value in teaching children to be miserable and to suffer. I mean, you can't do it in every situation, but it's just like, I don't wanna say too much, but it's just people, they're like, I'm staying for the kids. Like, that's actually who you're hurting.
+Darius: I'll grab the baton. Loveless is not toxic. Those are two different things. Okay, fair, fair, fair. So to me, it just depends on how much it bleeds into, you know, outside of your bedroom, for lack of a better word. Right. And I do think once you get married and have children, you can't prioritize your well-being over everything. And like anything, marriages, they ebb and flow. Um, you know, so like I've known people, coworkers actually, who, who have told me, you know, like for two years there, we just passing by each other. But like now it's great. And like, that's kind of, I do think when you, when you take an oath for, for life, you do owe it some effort. Now that's a, that's definitely not unconditional. You know, some things are beyond the pale and some things are just irreparable. But I do think we lose something when we tell people to just bounce when it gets uncomfortable or when it gets a little boring. And so I just think that it's a delicate balance to to do. I myself have never been married, so I'm speaking. I'm not from any sort of experience, but, you know, obviously to death do us part is a little extreme. Oh, and by a little, I mean a lot. But, you know, I can see why people do it, though. If the kids like 16 and they're going to be off of college in two years, that's a lot of disruption to throw on them their last two years of high school, you know, and it is logistically harder to do it with when there's two different houses. I just I mean, I'll never forget little real. He was at a radio show and he just like it was just hard for me. He was like, because he went through a divorce and they stare at custody. He's like, I'm sitting in my living room watching TV and why aren't my kids with me? You know, they've been in my house for 10 years.
+Jordan: Every day.
+Darius: And now they're not, you know, like you don't realize how much you will miss the noise. The, you know. Yeah, it's a big adjustment for sure. I think people play hard and fast with the rules when in real life it's just a little more complicated than that. So a little went off to a little aside there.
+Jordan: Mostly because I don't really have anything else as far as notes for this movie. So. I think, I can't remember which movie it was, but we talked before about cheating and what would you forgive and the different situations and stuff like that. In this situation where like she's having a full on affair with this other guy who she's like literally thrown in your face. Are you, sticking, are you sticking around and making that work?
+Darius: No, I'm talking about pre the like. My question was spawned of you saying they were kind of like bored. The marriage is falling apart because they were bored. But nah, man, if I'm at work slinging burgers and I open the drive through window and you,
+Jordan: he would just step on his
+Darius: And you, what do you call him? Mistress? I don't know what you call him.
+Jordan: Mister.
+Darius: You're Mister.
+Jordan: I don't know.
+Darius: The other man in the drive through, you got a handful of ***** and you Nah, we can't look past that. That's doing too much.
+Jordan: Yeah.
+Darius: The way he found out was crazy, bro, was slanging burgers. That was right to the drive-through. But she didn't even know she worked there, but still.
+Jordan: Right.
+Darius: That's a rough one, man. That's a rough one.
+Jordan: Yeah, it's also a testament to like just how lovely the second marriage was because it never even occurred to him to care or think about whether or not she was ******* some other guy. He truly just didn't give a ****.
+Darius: They were just totally checked out on each other. Yeah. He didn't care about this. He was mad because he felt like he had to be. We didn't give a **** about that.
+Jordan: He's like, I'm so hurt.
+Darius: Oh my God. How could you do this to me?
+Jordan: Oh, no, I can divorce you and get half of your ****.
+Darius: I got the papers in my pocket. Here. Stay right there.
+Jordan: Stay right there. Hold on. Here.
+Darius: Hold on. Let me go to my locker. Don't drive off.
+Jordan: I've already signed my portion for the document.
+Darius: It's signed right there. Put it in the mail. We're good to go. Got a new lease.
+Jordan: It's over. It's done. It's over and done. I'll get an apartment by tomorrow.
+Darius: What was my pops used to say 1 foot in the grave, the other on a banana peel. Like it was all the way out there. You got anything else for that too?
+Jordan: Yeah. And by the way, banana peels actually are slick. I almost busted my *** in the parking lot on one of those one time. Granted, it was raining. It was raining. I didn't see it. But it is real. I thought it was a joke this whole time. But yeah, so one of my favorite scenes is the family dinner where he's like, he just loses his ****. And he's like, I'm sick of y'all treating me like I don't mean **** to y'all. And he just throws the plate at the wall. And he's like, by the way, I'm sick of this ******* music.
+Darius: What would you say this movie is about?
+Jordan: I'd say it's about One, appreciating the small things. I'd say it's also about the insignificance of classism. Well, okay, I'd say that the consequences of classism, and I'd say it's about people's desire to be young, like just anti-aging, basically. I think he was quote unquote, attracted to his daughter's friend, but he was more such attracted to the fact that someone younger. I know, I couldn't not. I couldn't not. I don't even think it was so much about the girl. It was about what she represented. You know what I mean? It was youth, you know, temptation. It was virality, if you will. It's disgusting, obviously, and predatory. But, you know, it wasn't even like, remember at the end of the movie, fast forward a little bit, he turns back into a father. That moment turned it back into a father, which he shouldn't have taken that, obviously. But I think it's about people not wanting to age. I think it's about people trying to have it all. And I think it's about people trying so much to have it all that they can't recognize, again, the beauty around them.
+Darius: Not wanting to age. That's a good one, man. This is totally off topic, but I was when we were watching the, we were watching them together, but we were watching the Oscars at the same time. And I just was like, I remember when all of the Oscar Best Picture nominees were old and stuffy and boring movies that I thought only old people liked. And I was like, I like all these movies. It must not be because I'm old and stuffy now. And why does the grocery store play good music now? What's going on? I heard a Nelly song at the grocery store and I was like, oh no, not my music at the grocery store.
+Jordan: That's crazy. Oh my god. Imagine that they play like the college dropout at the grocery store, dog. I probably shoot myself.
+Darius: Yeah, man. They play music we like in Target now.
+Jordan: That's unfortunate.
+Darius: You know, it just, it's little reminders that you're getting old, man. It's just like, man, I liked it. Damn near every movie nominated for Best Picture. Some more than others. Me too.
+Jordan: Yeah, some more than others.
+Darius: But when they were all just like movies I had never seen, old stuffy.
+Jordan: Yeah.
+Darius: Like who, which old 90 year old white man voting for these and now?
+Jordan: Yeah. I love them. I think, was it, what year was it where it was the Moonlight La La Fiasco? Was that 2016? I think it was. And I remember being like, I've never heard any of these movies.
+Darius: Yeah. Now, I saw half of them in the theater. Like, I didn't know they were gonna be nominated. I just saw, this looks good. We go see Begonia.
+Jordan: I thought they look cool. Right.
+Darius: Man, 20, you would have told 22 year old me that I would go see Begonia like on my own accord. Like with just, It's just like, oh, movie. We're about some crazy lady. No, man. Just three people acting in a basement for an hour and a half. I actually enjoyed it. You know? Yeah. Act three beautiful and multiple character arcs converge on a rainy night as secrets are exposed. Lester finds a moment of true clarity and peace just as the consequences of his environment finally catch up. I have here that this movie is gross. You could tell what scene happened when I wrote that down. I can't even, even for 1999, I can't believe no one on set was like, hey, do we need to?
+Jordan: Put this in here.
+Darius: Cause 1999 is not 1959. You know, like they should have known.
+Jordan: No, I don't understand. Yeah. And again, this is another movie where Kevin's basically played a creep, like a super dupe creep. Yeah, no, it's like we really should have known. This is craziness. It reminds me of like that somebody posted the album cover for that Aaliyah album, AJ and the Cover. And you know who's in the background on the cover. And it's just like, how did y'all let this happen?
+Darius: That's like, I listen to a lot of problematic people. I'm not gonna act like I'm holier than thou. For sure. Marvin Gaye's jacket is crazy. James Brown beat every woman he ever dated.
+Jordan: Everybody tried to kill Otis Redding.
+Darius: Right. But the R. Kelly thing for me is like, the music is literally about his crimes. And I'm just not going to listen to, I just, I can't. I got literally, it's not about, you know, and no one's going to know what's in my headphones at home on my Spotify. It's like I'm doing this to be a performer. I literally can't listen to it.
+Jordan: No, yeah, no, yeah, for real. Like it's, you know, right. Like, you know, Chris Brown doesn't make music about, Abuse, right?
+Darius: It's particularly pernicious when the song is describing crimes.
+Jordan: Yeah, it just gives you an icky feeling.
+Darius: Correct. I'll spare the people the details. Y'all got Google, but the crimes aren't. Yeah. I do love how the pivoting. I do love how the weird kid next door was actually the only normal person in the movie.
+Jordan: He was the only normal person in this whole movie.
+Darius: You got the dad across the street looking out the window. So let's just assume he believed everything. That was what he thought. Right. So when the kid was rolling up a blunt for Kevin Spacey, but the angle looked like.
+Jordan: He was giving ********.
+Darius: Correct. As a father. You're just watching.
+Jordan: Let's and let's don't like the fact that it's not like your child within a grown man. Let's just feel like that's not the issue here. You're watching it.
+Darius: One, you're watching it. Two, you believe that this is your child within a grown man.
+Jordan: Yeah.
+Darius: Whole lot weird. Again, the kid was the only normal person in this ******* movie.
+Jordan: Yeah. And then remember when he was watching the videos back and he saw the video of Kevin Spacey working out in the garage and he just sat in like that. This is, yeah.
+Darius: And then he, I think he just, I made a pass at Kevin Spacey at the end, right?
+Jordan: Yeah, he made a pass. That's why he killed him.
+Darius: I was wondering if I read that right.
+Jordan: Oh yeah, he, oh yeah, so he, comes to the garage. I think he, I think he was, I think he thought he was going to try to confront him or I think that's what the father planned to do. And then he was shaken by his, I guess, revelation about himself. I don't know. And then if Spacey's like, yo, you good, bro? Like he gives him a hug. Dude starts like caressing his back and then he goes in for a kiss. Spacey goes like, no, oh, sorry, dude, you got the wrong idea. He walks away and then we know what happens at the end. Well, he blows his brains out at the end.
+Darius: Yeah, we could put this one in the archives. I'll never watch this movie. So much weird **** man.
+Jordan: It is. I just wish they had shown the father getting retribution, though, like him getting arrested or killing himself or something like that. Because just kill a dude because you mad that you gay is crazy.
+Darius: Well, I mean, with that. Well, yeah, I was going to say he thought that that's what happened to his child, but he didn't clearly didn't care if he made a pass at him afterwards. Right. Yeah, man. And the fact that Like you said, they didn't even show him like getting arrested or anything, because I guess in 1999, that wasn't a bad thing to do, to just break out a hate crime. Right.
+Jordan: Even like the Nazi plate, remember that.
+Darius: Yeah. Weird movie. Got anything else for act three?
+Jordan: Oh yeah, so I did want to ask you, so the the wife in her affair. Do you think she actually loved him or do you think it was just like the first ounce of excitement and youth she got to feel in however many years?
+Darius: 100% the first ounce of excitement in youth and probably first time she's had an orgasm in half a decade. And yeah, I mean, she's not going to run off with that man. She just it's fun, you know?
+Jordan: Yeah.
+Darius: Forbidden fruit is always sweeter as the old people used to say.
+Jordan: True. Did you think when she had the gun, did you think she was going to kill her herself or kill him?
+Darius: Herself. I don't really have a logic, but I just had to pick one. So herself. How about you, man?
+Jordan: I got the feeling she. I think she probably would have killed him. I think she would have rather killed him than kill herself because she was pretty vain. That's really the only reason I feel like that, though.
+Darius: You don't really have anything else. I guess I'll close it with you said this movie is about getting old. You are what, 33?
+Jordan: Yeah.
+Darius: What is your what is the first I'm getting old moment that comes to mind.
+Jordan: It's a good one. I think just when I see like, oh, I know it is. I was driving the other day. I was going to, going somewhere and I saw a little kid, my neighbor, two doors down, his dad was helping with a pitcher and some water and **** whatever. And they were setting up like a lemonade stand on the corner. I thought to myself, well, when it's really early in the year to be selling lemonade, it's not summertime. Also, lik</t>
+  </si>
+  <si>
+    <t>Jordan: And for the listeners, you have to watch this and pay attention. Do not be scrolling on your phone because you won't know what the hell's happening. No.
+Darius: This is, you know, one thing we should try to do is figure out when the cutoff was from like when they started making movies assuming you're not paying attention. Yeah, I agree.
+Jordan: Hey everybody, welcome to the Out the Trunk Pod with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Steve's. I love me area on all socials.
+Jordan: And today we're going to be reviewing Arrival. This movie came out in 2016, starring Amy Adams, Jeremy Renner, Forest Whitaker, Michael Stahlberg, and Zi Ma. This movie is about when 12 mysterious spacecraft land around the world. Linguistics professor Louise Banks is recruited by the military to communicate with the visitors. As she begins to decode their complex circular language, she experiences vivid flashbacks that hold the key to understanding the alien's true purpose and the nature of time itself. I'm going to toss it to you for act one.
+Darius: Act one is the first encounter. The world goes into a collective panic as the shells hover over random locations. Louise and physicist Ian Donnelly are brought to the Montana site to answer the ultimate question. What is your purpose on Earth? Ian Donnelly played by Jeremy Renner, Jeremy Renner, Jeremy, what's his name? Yeah, Renner, yeah. I thought that was one of the Kardashian people. And then Louise played by Amy Adams. Let me just say, I remember seeing this in the theater in 2016, but I just don't, I remember seeing it, but this is probably the best movie I've watched like on my soundbar. Like the just the noise that the aliens made when they tap the glass. I felt that in my living room. And I normally don't give my soundbar a good workout. Just like this was like, it's a good home viewing movie as far if your sound system is right. So that's off the rip. What you got for act one?
+Jordan: It's funny, talk about the sound. That's one of the first things I wrote is the score of this movie is incredible. Like it just hits you emotionally. Even like this is my first time seeing this movie. And literally when I heard the score, like I felt something I had no idea what the movie was about at the time, you know? So actually it was used in a few previous movies. But I'd heard it, I feel like I'd heard it somewhere, maybe like some sort of YouTube video or some compilation or some **** like that, whatever. But I mean, it's not that the score was incredible. It's interesting that you touched on the sound because it does feel like you're right there. Like when the aliens like touch the wall and **** you're like, oh ****.
+Darius: And like the visuals of it, how they're like, you can, it's hard to make out what they are. Like I have no idea. They could have been 5 feet tall, they could have been 50 feet tall, and you just really couldn't tell. And I just thought that was like, they did that really, really well. As far as just making you feel like you were in that heptapod with them, Yeah,
+Jordan: because you almost were like backing away from the screen because you didn't want to be too close to some random foreign object.
+Darius: Yeah, it's, you know, I'm not a score person in general, but like this one stood out to me as a non-score person. So absolutely. Well, what else you got for Act 1?
+Jordan: I like that the aliens look like whatever you may think aliens look like, I don't know if they're really not. I mean, I think there's probably some other life form out there. I mean, it's plausible. And I saw this quote once. They said someone said like, everyone's afraid of like what's up there in space. But to me, like the **** that's in the deep of the sea looks like aliens to me, And I kind of think that like, if you looked at an, if you saw an octopus in space, you would call that an alien. And these look kind of like octopuses, which I thought was octopi octopuses. I don't know. And I thought that was kind of cool.
+Darius: Oh, you say plausible. I'd say it's likely. I would.
+Jordan: Yeah, for sure.
+Darius: I would be more surprised if we were the only intelligent life in the universe. Like that strikes me as statistically impossible. I, it's just to be fair, the set of conditions that made life on Earth possible are pretty unique. But the fact that it's never been replicated anywhere or the fact that life needs the things that we need to, like the atmospheric conditions, the level of water required, it just strikes me as, and also just like the amount of alien appearances in our fiction and our writing and how that's continuous across millions of years of human evolution. It's like, you know, the AI thing, right? How many movies have we seen about like AI robots taking over the world? Right. And like, we're seeing that technology.
+Jordan: And we have robot vacuum cleaners.
+Darius: Correct. And it's like, Correct. And the odds that we're just wrong on this one, that we've been creating, we as a species have been creating alien fiction for millions of years. You know, it just strikes me as impossible.
+Jordan: I agree. Yeah, I think there's, I don't even know if you call them aliens, but I guess that just means a foreign life form. So I do believe they exist. I don't know what they look like, obviously. Who knows, maybe they all just look like mammals that are just in, on whatever perspective planet or orbit or star, whatever is out there.
+Darius: Or maybe it's something we, I forget, I remember which friend told me, he was like, explain our existence to a rabbit and see how much he comprehends it. You know, maybe it's something we don't even understand. You know, like it's just maybe they're around us and we just don't get it because again, How much do rabbits know about our life? Our intelligence and how we study them.
+Jordan: They know when they see them to run away.
+Darius: Study them. They know like how do they know any of that? So it's like maybe it's beyond our comprehension. So that's true. If alien pods hit Earth, would you want to be privy to the government negotiations or would you want to just ignorance is bliss it? But you get what I mean.
+Jordan: Yeah, I want to know. I'm a curious person. Yeah, I want to know for sure. I want to see what they look like. You know, what have we had any communication with them? Are they what are they? I mean, like the move. What are they here for? You know, are they lost? Do they want to get back home? You know? Yeah, I want to know for sure. Why not?
+Darius: I mean, sure, I'd want to know. I thought we would be privy to. I mean, you'd be privy to it.
+Jordan: Yeah, I don't think they tell us.
+Darius: No, I mean, with good reason, though, like the average People don't, I mean, you know how people handle complex things. Right. And just like, if it's at any degree of complexity, they just chalk it up to a conspiracy theory. And so, you know, I would want to know, but I would understand why they would keep it under wraps if they're not already doing so.
+Jordan: it makes me, ironically, this movie made me think of that, the one scene from Men in Black where the first one where they're on the park bench and he first learned about aliens and ****. And he's like, well, I think people can handle it and know that they're aliens, whatever, you know. And he's like, no, they can't. He's like, a person is smart. People are dumb, stupid, and scary. And you know it. Yeah. And this movie just did an excellent job of illustrating that.
+Darius: I mean, just imagine if CNN tonight just broke the news that like we have linguists talking to hepatods and They're communicating in a non-linear language format that might be, you know, they're communicating whole stories in a circle. And like you think.
+Jordan: And you know, can see the future.
+Darius: It's still people who don't who think the 2020 election was rigged and they've seen every piece of evidence, you know, right? Yeah, that's true. Vaccines cause, you know, autism, all kinds of ****. So like, no, I don't. I don't. A person is smart, but people are stupid. I would not argue in the contrary. Yeah, that's valid.
+Jordan: We saw, we reacted to the, actually no, yeah, they wouldn't tell us because the way people reacted over things like the pandemic when they just bought all the toilet paper for no reason, or the way they acted over the Popeyes chicken sandwich, we could never, they'd never tell us about aliens.
+Darius: That OG chicken sandwich was the truth though.
+Jordan: Oh, it was. Oh, I still get it all the time.
+Darius: Well, it ain't like it. It was like the OG run. But no, I mean, listen, yeah, the Cleveland collective action, you know, it's doesn't really work that well. So I, I would understand why, especially when you have to coordinate with all of the world's governments like, you know. Right. I have a call back to something later that I want to spoil, but like. Yeah, it's hard. So you got anything else for that one?
+Jordan: Yeah, I got two more observations. Well, actually, I guess three more. So one, the idea of Jeremy Renner playing a theoretical physicist is hilarious because he don't even know what to do. He just, I'm sure he's a smart guy, but he just doesn't look like he's smart enough to play. theoretical physicist.
+Darius: Well, to be fair, in the movie, he was just kind of like guy, guy #2.
+Jordan: Yeah, that's true.
+Darius: He was just kind of standing next to her doing nothing. They didn't really give him a lot to work with.
+Jordan: That's true.
+Darius: They just needed to stand in for the big reveal later.
+Jordan: Right.
+Darius: So, you know, he got a good check out of it, but. I think he was just tired of being a Hawkeye for a little bit. This was peak MCU. So he's like, hey, man, I get to be a, I get to just talk to Amy Adams for, that's all he did was just talk to Amy Adams.
+Jordan: Just talk to Amy Adams, which is not a bad way to make a living.
+Darius: No, man, you know, Amy Adams wasn't, was she even, I don't think she was even nominated for it.
+Jordan: She wasn't nominated. That's the crazy part.
+Darius: She was incredible in this movie.
+Jordan: No, she did. Her and them CGI aliens.
+Darius: Forest Whitaker held it down.
+Jordan: Forest Whitaker was good too. He's always great.
+Darius: One of the great character actors of our time.
+Jordan: Correct. He's kind of like the black Walter Goggins. What else was I going to say? Yeah, so shout out to Dennis Villeneuve, I believe is how you say his name. He's French-Canadian director. He directed this movie. He also directed the Dune series. I'm excited for what's called Doomsday, December 18th, where Doomsday Avengers movie and then Dune 3 come out the same day. I think I'm just going to spend 8 hours on a movie. It's going to be the best day ever.
+Darius: There's no chance those two movies come out on the same weekend.
+Jordan: No, they are. Yeah, that's it. It's like Barmenheimer 2.0.
+Darius: I will believe it when I see it. There's not enough IMAX theaters to go around.
+Jordan: The release dates are set.
+Darius: I'll believe it when I see it. Before the more the reason then like, why would you step on the dope like that? Like you need that. It's just like those. Well, first of all, like, I don't know which theater you go to, but mine has one IMAX theater. So like, what are they going to do, like, fighting theater? Like, you know, like, who's going to go to? It's just, I'll believe it when I see it. I know this is what they say. I'll believe it when I see it.
+Jordan: I hear you. If they do go through with it, I will be there. And then I also wanted to say, like, I love the We talk a lot about storytelling when we do our movie reviews. And this movie is, first of all, a masterclass in storytelling. The epitome of like excellent nonlinear storytelling as well. But also, I love the way they showed like the loss of her child without making it Yeah, it's presented as flashbacks. They don't make it a gimmick. They don't make it, you know, her whole personality, but they show just the way that grief, quote unquote, as what we know in act one to be what it is. I thought that was really awesome. I thought it was like super intelligent.
+Darius: And they, you know, they didn't, there was no narrator to tell you, like, it just happened. You didn't really know You had to watch the movie. This is a reoccurring theme on the spot, but like movies, you can tell when a movie was made before ubiquitous smartphones, because they don't, there's no unnecessary exposition. She's not coming to work and being like, I'm sad because I can't work today. That's what would happen. I promise you, once you see it, you can't unsee it. When you watch a movie today, people walk in a room and just explain the plot to you. They do. They're like, we don't get this object, the whole world's gonna fall apart. It's like, my God, I'm so tired because I didn't get any sleep because my daughter died. Okay. Endless exorcist.
+Jordan: I'm in grief.
+Darius: We're going to go get a grief. Then they'll do **** like, let's go get a grief tattoo. Like it was sitting
+Jordan: on the whole scene where she gets a tattoo
+Darius: that says I'm grieving. It's like, oh my God. You could find a more subtle way to do this. Right.
+Jordan: Yeah. Or they're in like an Alcoholics Anonymous for grieving people. I don't know what you're called. Like group therapy, I guess.
+Darius: Yeah, And they use that scene for the character to get up and tell the story. I, what's your name? Hi, I'm so. And then this is why I'm grieving. And it's like, yeah, just such lazy storytelling.
+Jordan: Correct.
+Darius: Anything else for act one?
+Jordan: No, that was all I had for act one.
+Darius: Moving into act two, Luis makes a breakthrough with the heptopods, realizing that their language isn't linear like ours. It's circular. As she immerses herself in their symbols, her perception of her own life begins to fracture and shift. Was I the one who thought that was Joaquin Phoenix for a minute?
+Jordan: Where?
+Darius: The white guy in the I forget his name, but like, I was a soldier. No, no, it's like. Maybe it was just me, but there's one guy in the movie. I was like, did they give Joaquin Phoenix for a non-name random character actor role? But baby is just.
+Jordan: I think I know what you're talking about. I didn't think that was him though. If that's, if I'm thinking of who I think you're thinking of.
+Darius: It was like, I thought it was him for like a half a second before I thought. No, he's just like, he's on the base and he's talking to him and he's got, he's like the straight guy. He's not a military person. He's just a white guy
+Jordan: in a bloody shirt. And I was just, I know what you're talking about. Yeah, with the long hair.
+Darius: Yeah. And I'm just like, Joaquin Phoenix would be on the ******* poster if he was in this movie. So no, but I thought it was for a second.
+Jordan: That's funny. But yeah, that was, that's, I can see that's what you got back to. Yes, I wanted to ask you, they have the bird in the cage and they're talking to the aliens.
+Darius: Yeah.
+Jordan: What did you think was the purpose of that?
+Darius: I don't know. I had nothing. I mean, like the second that got a little dry.
+Jordan: It did.
+Darius: You could tell. So this was based off of a short story. And you could just tell it kind of stretched. It was under two hours, but they needed, you know, you can't have a 90 minute movie, but this was based off.
+Jordan: I think the novella was like 70, 80 pages, something like that.
+Darius: Yeah, it's like a novel's like 300 pages. And this is the part where you could tell they were kind of like, all right, let's get to the, because the ending's so great. We just got to put some steps.
+Jordan: Yeah, the ending is the payoff is huge and it is worth it. But yeah, I agree. Because I was like, is the bird, is that supposed to be some sort of like, comparative metric to the to the to the way they communicate almost like a metronome or something like that. I didn't really understand what that what that was.
+Darius: Yeah, they kind of lost me for a little bit that way. But I will say it does illustrate, though, how an underrated technological invention and the reason why we're ahead of the food chain is just language. You know, we Being able to communicate to your fellow caveman, hey, around that corner is a giant bear, don't do that, is an advantage that we have over other species who just can't communicate as effectively. They have communication, right? But we can, the dexterity and the level of nuance within our conversation is just so beyond, you know, our main predators, you know, wolves or whatever, like they can't coordinate the same way we can coordinate. And you combine that with tools and fire and eventually guns. We dominate, we wreck ****. So I do love how the film emphasizes just how you take it for granted, especially, you know, being an English speaking person, because even when we travel places, outside of the country. Most of those countries have English in their curriculum and it's, it makes it things easier.
+Jordan: But forget that that's not normal.
+Darius: But if you've ever been to a place where everyone spoke a language and you didn't, you realize quickly just how alienating and how frustrating that can be. So yeah, I do love how they, you know, use basic things like human food, dog love and just trying to decode it that way. I thought that was brilliant how they handled me too. So
+Jordan: Yeah, I really like the way that scene where she broke down the sentence of, what is your purpose here on Earth? And she kind of was like, well, they have to know what Earth is. They have to know what Y is, so on and so forth. And then also, we communicate in linear, in one sentence, the beginning, middle, end. Whereas again, like I said, it's a circle. They're communicating. She said it was like two ends who know where each other's, you have to know where the beginning and the middle end. beginning and the end are so they can meet in the middle. But to know that you have to know what the middle is, right? I thought that was a really cool way of breaking that down. It almost that scene kind of reminded me of like it's almost like that's why that movie Memento didn't work. Yeah, because it didn't properly illustrate that the beginning and the middle and the end were all the same.
+Darius: Yeah, I yeah, Memento was yeah, Mento didn't give you enough and it was. Yeah. Like you said, it was nonlinear and you can do that, but you have to, it was disorienting and it can't be disorienting. You can be nonlinear, but you can't be like confusing. And like, you know, Pulp Fiction, one of the greatest movies of all time is nonlinear, but you don't feel completely lost. You like when you're in a scene. That scene makes sense. It's just out of order with what else is going on. But like I was watching Memento and I'm like, I just can't follow this. I don't know where this person, like it's just confused. I was not a fan of that movie. I think it got a two star for me.
+Jordan: So yeah, it outsmarted itself. What was I going to say? I did love the the chess metaphor that she used when she was talking to, I think, for when there was a character where she was saying that the other country, I think it was maybe Venezuela or China, was they were playing games to communicate with the aliens. And she was like, that's not good because that's a that's a binary result, win or lose competition, life, death. And you don't want that because If they miss, if they accept a loss as defeat, they're going to want to, dominate you. And we're already at a loss because you got these 12 pods around the world. These 2 aliens are ******* 50 feet tall. What are you going to do when they send the rest of them?
+Darius: When you don't have a shared mode of communication, you just no way to understand how they're going to take disappointment. Like, you know, you beat a toddler at chess and they think literally the world might end. You know, it's like, how do you know that they understand? that it's a ******* board game. It doesn't really matter that you lose. We can just put the pieces back on the board and do it again. Yeah. So yeah, I agree. You know, language is the tie that binds. And until you. They have to, now they've fixed it. Like my boy just was in South Korea and he's just like, I just use AI translators and I just talk in English and they just talk back in their language or in Korean and it just instantly translates. Like you don't even have to type it anymore.
+Jordan: That's cool.
+Darius: You know, I was like, that's pretty dope. Which, you know, it's, you know, as someone who aspires to do some international travel, that would make things a lot easier. So, yeah. Anything else for I too?
+Jordan: No, that's all I got for act two.
+Darius: All right, act two, the dry middle. We're gonna call that three. Now, the non-zero sum game, global tensions reach a breaking point as nations prepare to attack the ships. Louise must take a massive leap of faith using her new understanding of time to prevent a global war and fulfill a destiny she's only just beginning to understand. So hear me out. It almost felt a little like Game of Thrones where like the Heptapods were the White Walkers and all of the politics of Earth was just kind of like the biggest thing in the world to them. But like there's this existential threat that if you don't coordinate and deal with, doesn't matter who's on the throne. It doesn't matter if it's Daenerys or Cersei or whatever.
+Jordan: Right.
+Darius: You know, it's so like the third act when we're beefing with China, we're beefing with this. And I just kept thinking the White Walkers are here. Y'all need to figure this **** out because winter is coming. And you know, that was a great parallel. Yeah, like that was the core premise of George R. Martin's whole book was like the White Walkers represented like was meant, but he didn't finish it, but it was meant to make all the politics of Westeros feel so small. when they finally, and then the TV show botched it, but that was the point.
+Jordan: Right.
+Darius: So yeah, I was like, this is really, this feels like White Walkers. So, yeah, that's my, it's my corollary, whatever you want to call it. So, what did you got for act three?
+Jordan: That's a great point. I like that. I agree. I think that's a great point. I also think that the, to me, well, there's several messages of the film. One of the films is that we're trying to communicate with these aliens, but the truth is, we can't communicate with the aliens because we can't communicate with each other. We are foreign life forms to each other. Different races, different countries, different genders, different sexualities, all that come into play. I mean, we're supposed to be correlating with each other. We don't know what the hell the aliens are saying. And then they're like, oh, let's just stop talking to each other. What the **** does that make?
+Darius: And then you find out, like you said, Venezuela's communicating in a way that you disagree with because. Right. Whatever. And I'm sure they would disagree with the way she's doing it or, you know, yeah, it's hard. You know, this planet is big and people have entrenched beliefs and tribalism and, you know, these things are hard. It's hard to coordinate. It's hard to collaborate. And you have to do it at such a scale at global scale. the only thing humans have been good at is war, And so, we've been fighting over pieces of land for affinity. So the idea that you would think that an alien invasion would tighten us up and get us to a coordinate, but you saw in this movie, like when the damn things are on the ground, we're still bickering. So.
+Jordan: Correct. Yep. It's almost like, you know, if there's a Deadly virus is going on. It's killing lots of people that we don't know what it is. And four other governments couldn't coordinate and, you know, get themselves together. Sounds like 2020 to me.
+Darius: Yeah. I mean, the thing is, that if another one hits, God only knows how less cooperative people will be then. And, you know, and I get it in the sense that like I was sick of being in the house too. I'm not going to act like I strictly adhere to all COVID policies during that summer. But, you know, these things are hard and everyone has their own interests and everyone wants to do what's best for them and you want to do what's best for you without being taken advantage of and if you are the you feel like if you're sacrificing and the other side isn't or your country is doing this and that country is doing it the wrong way it's just then you're like what's the point what's the point we might as well just do it for ourselves and you know it just becomes you know it's just easier to look out for your own so I correct.
+Jordan: Yeah What else? just the scene where they kind of cracked the code of basically the purpose of the, not purpose, but just the communication style of the aliens where he had that like that simulator show like the distance between the languages or sentences, if you will. Where it's like, you know, it's one, it was some crazy number of things like the fraction is 1 out of 12, you know, meaning that they all need to communicate, they're all communicating with each other. So we need to communicate with each other so we can figure out what these each individual pod is doing and what they what they want from us. I thought that was really cool. And it showed like, you know, it's always easier to it's just easier to go, you know what they say, further together, faster by yourself, further together. And you know, it's easy for them aliens to coordinate because they were on one chord. If they were going to destroy us, they would have won because they were working together. We weren't and we were already at war with ourselves, with each other rather. And you know, the fact that they were gonna kill her for trying to crack the code. Yeah, that's the problem.
+Darius: Yeah, I mean, well, for all we know that the aliens were a monoculture, though, like it's easier to coordinate when it's just you and your people versus, you know, 10 countries with, you know, different cultures and different motivations and different languages and different da da da da. So I mean, it really was a testament to like one side was On one accord and one side was abandoned on every and all every member was on a different key. So yeah. we should tell the people the big reveal or you about say yes. So then we can actually talk to you. Big reveal is that the flashbacks were not flashbacks. They were flash forwards and she ended up marrying and having a child in Jeremy Renner's character and the child ended up dying of I don't know what specific cancer but young childhood cancer. And Jeremy Renner ends up leaving her because she knew it was going to happen and she went forward with it, and so it's like a and told him, told him that she knew it was going to happen. And it's just one of those things like having the love was worth it, even if it was only for a short period of time. And so she knew telling it, I mean, she knew everything. She knew the kid was going to die. She knew he was going to leave her because he knew or he was going to leave her because she knew and she knew. She wrote a book about it. Probably made some M's. So I'm sure the book sold a lot of copies, right?
+Jordan: Yeah. I talked to aliens and.
+Darius: Yeah, you know, I'd buy the book. **** it.
+Jordan: Hell, yeah.
+Darius: Great book. Not even science fiction. Just science. Real science fact. Yeah, big facts. Star Wars, but real.
+Jordan: Hashtag really do. Yeah. Yeah, I love the. That's my favorite part of thing about the movie is the message at the end where basically it's not just choose love, but choose love over fear, you know, because she could have she could have just not gotten together with him and lived the rest of her life without her soulmate. But she chose to go into it knowing she was had to gain everything to basically lose everything. because, you know, that's ultimately what life is at the end of the day. And I thought that was really beautiful message. I guess you could you could perceive it as being selfish because they both lost. But I think at the end of the day, as sad as he was about losing the child, I think he'd rather have grieved her than never had her.
+Darius: Yeah, I mean, selfish is strong, but I see I see how that goes. But like, you know, what was she supposed to do? Not marry the love of her life and not have a child and, not experience that joy. And, however short-lived it was, I'm sure, it was worth it. I mean, clearly it was worth a pretty shot to go through with it.
+Jordan: Right. Darius [0</t>
+  </si>
+  <si>
+    <t>Darius: Sexy Red got a new one.
+Jordan: He wouldn't hang with it.
+Darius: I must admit.
+Jordan: And guess what? I do.
+Darius: I do. I mean, it is. I feel that song in my soul, man.
+Jordan: I do. I felt it right here.
+Darius: She just knows exactly what I had on my heart when she made that song.
+Jordan: That's my goal every weekend. Hey everybody, welcome to Out the Trunk Pod with Jordan and Darius. I'm Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Deez. I love the area on all socials.
+Jordan: And this is our movie review segment. Today we're going to be reviewing Baby Driver. This movie came out in 2017, starring Ansel Elgort, Kevin Spacey, Lily James, John Barenthal, Asa Gomez, sorry, Asa or Liza? Asa Gomez, oh wow, Gonzalez, whew, long day, John Hammond, Jamie Fox. Baby Driver is about Gannon Baby, a talented young getaway driver with a constant soundtrack playing in his ears to drag out the tenitis, seeks a way out of his life of crime. After meeting a charming waitress, he hopes to complete one final job for a ruthless crime boss to gain his freedom. So I'm going to tell Steve to set the table for Act 1.
+Darius: Act 1, the beat of the streets. The baby serves as a getaway driver for a revolving door of heist crews to pay off a debt. He meets Deborah at a diner, sparking a desire to leave the criminal world behind forever. For the audience who has not or have not watched it yet, it's basically a two hour music video. You can, you know, put your brain in the box next to you, get you some popcorn and watch a two hour music video.
+Jordan: Yeah, it's very much a popcorn movie, but it's fun. I **** with it.
+Darius: Popcorn, junior mints, mug soda. If you can, if it's on a repeat, check in in a movie theater. I didn't watch it in a movie theater, but I imagine that it is, you know, a lot like Top Gun Maverick. A lot of, you know, you lose a lot when you leave the theater. So what you got for act one, man?
+Jordan: Yeah, I definitely wouldn't move. You should check out enthused if possible. I love this movie. It's a lot of fun. I remember seeing enthused. I thought it was like dope as ****. The attention to detail is so like incredible in this movie. In that first sequence after the first robbery scene where he's walking down the street and like there's some music playing and you see the ad-libs in the graffiti behind him.
+Darius: I don't know.
+Jordan: Did you notice that? Oh, you didn't know. Oh, man. See, that's why you got, yeah, that's why this movie was meant to like be watched in theaters because like there's, it's, you know, everything's done to the rhythm of the songs. Obviously, we'll talk about that later in the movie, but so there's literally when he's walking down the street, there's there's that first song playing as he's singing or there's the ad-libs from the background vocalist there. It's literally like, you know, you have the read along in those old musicals. It's like that. Like if you go back and watch it, there's literally graffiti all around every scene in the movie that is illustrating like the song lyrics, which is pretty dope.
+Darius: That's pretty dope, man. So it was, it's wild, you know, how technology can like instantly date a movie. What was the last time you've seen some wired headphones in the wild?
+Jordan: It's probably me. And I haven't done that in like 6 months. What were you doing with wired headphones? I was a holdover. I really was trying not to do the Bluetooth thing, but it's just so much more convenient. I can charge my phone and listen to music at the same time, you know, especially when I work at the office. That's a super clutch feature because I listen to YouTube and audio books and stuff like that all day. Yeah. And plus, I think I got to I didn't want to get the AirPods because there's the whole thing about the radiation and stuff people were saying. So I kind of wanted to abstain from that for a little bit. But these are phones I love. No, I don't use AirPods. I use these.
+Darius: I use Bose. I have them over the ears.
+Jordan: Yeah. I'm also just always worried about them falling out and losing them or breaking them and stuff like that. So It's just easy for me to have something that I can just like, okay, it's right here. I got it. Okay, cool.
+Darius: The audience should know that I do appreciate the irony in me having a wired headset right here. But for content creation, I like to keep it hardwired to the system. I do notice that you are, you know, I mean breaking cords. Yeah, who's still using cords? There's a cord hanging from me right here. So I do appreciate that. But no, outside of Right, The gym work. I don't like having giant over the ears for work. So I have like a pair of earbuds for that. I hate them, but whatever. But everything else around the crib, it's just, you know, a pair of both headphones. So what else you got, right?
+Jordan: It's funny. My whole family, we use Bluetooth, but most of us don't use the air. My dad does. My sister has a pair, but she don't really use it that much.
+Darius: They also just seem like Unsanitary. Like, wouldn't you have relax issues with the AirPods? Like, I mean, I don't know. I guess that's not really a podcast conversation, but yeah. What else you got?
+Jordan: Yeah, so speaking of technology, Swoop came out in 2017, but the character is obviously very young in the movie. And so like the fact that there's a flashback with even like the old color grading and all that, and then like he's getting an iPod, like it's a rate, like it's like, you know, Walkman or something back in the day, it was kind of a funny like time capsule moment.
+Darius: And the fact that he's using an iPod classic throughout the whole movie.
+Jordan: Yeah.
+Darius: Which honestly is dated technology for 2017. By then we were all. Very much so. Right. You know, I, we had, I mean, music was on our phones by then. So yeah. man, he was, he was a throwback. He had the iPod classic. And that hardwired headset. I'll be honest with you though. Like sometimes I wish, I wish I can. Sometimes I want to grab like an old phone that I don't use anymore and make it my media phone. So that like social media phone. Well, just not even social media. Just like I'm sick and tired of listening to a song, open to Instagram and the song cuts off and Instagram screams at me. Right, So if I just had a phone that just for my YouTube music, for my podcasting, I could just.
+Jordan: I feel you.
+Darius: Play that **** at the crib now and walk around with two phones like a dope dealer, but for the crib, we'd be fine.
+Jordan: That's true. Yeah. I really hate that feature. Like when you're scrolling into music and like Facebook will stop it and **** like, I don't know why. I don't know why it needs to do that. I don't need to listen to anything on Facebook. But yeah, I was going to say, man, this cast is ******* incredible, yo. Like, I don't know how they got all these people in this movie, but I'm glad they did because Jamie Foxx was otherworldly in this movie. He needs to do more bad guys. Like he was ******* awesome in this movie.
+Darius: I got something for Jamie Foxx later.
+Jordan: Okay, Jon Barenthal, who's one of my favorite actors. He was great. He wasn't in this movie very long, but he was fantastic as well. I just want to shout him out.
+Darius: John Draper. Can't forget John Draper.
+Jordan: John Ham, Don Draper, one of the best to ever do it. Super dope saying him in an action movie because you just would never expect it. And he's like completely believable.
+Darius: I don't know what people always say like Jon Hamm was the only person who could be Don Draper because he was a totally unknown. Yeah, it's just to be that good at acting and be unknown to that age and then be that handsome, to be honest with you. It's just, that's never gonna happen again. Right. You know, Timothy Chalamet could get casted in a TV show and it'd just be Timothy Chalamet. No one knew who John Hamm was in 2007.
+Jordan: At all.
+Darius: You know, so. Yeah, that's just not gonna happen. He was literally waiting tables, I think he said. So.
+Jordan: Yeah. And he, and even like, have you watched a lot of his interviews at all? No. So I like to judge actors by watching them as interviews because that's probably close to their real selves. I mean, they're probably still acting to some degree, but you know what I mean? And then compare that to the characters, like when he, his interviews versus like him as Don Draper, his face doesn't really look the same. Like his manners are completely different. His voice almost sounds different. Like he's one of the great character, one of the great, he created one of the great characters in the history of American television. So I wanted to give him a shout out for that. dude's ******* incredible.
+Darius: Yeah, it really is, man.
+Jordan: Don't you miss when you could smoke and cheat at work?
+Darius: But someone made the point, like, man, the STDs that was floating through that office, man, I ain't seen not one condom in all 10 years that show was on the air. was just raw dogging all of Manhattan.
+Jordan: All the secretaries.
+Darius: Like, he was ******* junkies, teachers, secretaries, and I didn't see a condom one time.
+Jordan: Well, it was ******* fire. That's crazy. Have you seen Bridgerton at all?
+Darius: No, I have not, no.
+Jordan: But the dudes in the show, they're all rakes, you know what I mean? And so like ultra savages. And this one guy, he's like a super duper rake. And someone's like, he's such a great character, such a nice guy, but you just know his character was passing around all kind of ****.
+Darius: Listen, man, wrap it up or, you know, clap it up. Yeah, you know. Act two, offbeat escalation.
+Jordan: Real quick, I just want to go back for a second. So there's a scene where they're robbing the bank, the second bank robbery. And there's like the guy playing hero in the truck. And it's like, dog, what the **** were you thinking?
+Darius: Yeah.
+Jordan: You can get a cash reward for that. Like you just wrecked your car, maybe died.
+Darius: Yeah, we just talked about that at the barbershop the other day. One of the dudes, we works as a gas station. He was like, man, people don't really do because there's no one has cash. So he was like, man, I'm not, you can have, and ain't none of this ****. There's none of this smart, bro. Take it all. And it's insured at that, bro. Like, you know, the old saying is, man, when you're getting robbed, you have one job and that's to get robbed. That's it. Like, yeah, that's it. That is it. You get robbed. Your job is to get robbed.
+Jordan: Get home.
+Darius: Get home. Make it home, bro. Nothing they take is worth your life. Is that important?
+Jordan: Yes, absolutely.
+Darius: You still got what you got.
+Jordan: No, go ahead. Go ahead.
+Darius: Act 2 offbeat escalation. Just as baby thinks he is free, he is pulled back in for a high stakes postal office robbery. Tensions flare between him and the increasingly volatile crew members who don't trust his methods. So I don't have as rosy a view of the movie as you. So I have right down here. Does Jamie Foxx own the IRS or something? Like, was he back child support? Why did he agree to do this? is Ray. This is Django. Like, what is he doing this for?
+Jordan: Yeah, so I mean, if we're gonna be honest, I love Jamie Foxx. If we're gonna be honest, his filmography outside of those two movies and like Ali is not ultra pristine.
+Darius: I mean, yeah, I'd have to fact check it. But yeah, I mean, look, he's not, he's not a lead. He has been a lead a few times, but I don't think he's a natural.
+Jordan: What's his, what's his best movie since Django?
+Darius: What can you name it?
+Jordan: You gotta, you gotta Google it. You gotta Google it.
+Darius: Yeah, man, maybe he does owe the IRS. Just Mercy, and that was not a good movie.
+Jordan: Yeah, I saw that, yeah.
+Darius: Yeah, I mean.
+Jordan: I mean, it's not, there's not a lot there.
+Darius: No, there's got so.
+Jordan: Yeah, we got Any Given Sunday, Ali, Ray?
+Darius: Law Abiding Citizen was good.
+Jordan: Yeah, Law Abiding Citizen in Django. That's it. That's 5.
+Darius: You know, he got the lead in a Tarantino movie because Will's good on it, but he got it nonetheless. So, and he wasn't very good at Django. who's kind of the weak link in that movie. Great albums though. The albums are hit. The albums are great.
+Jordan: Yeah, albums are good. Yes.
+Darius: The albums were fantastic.
+Jordan: Slow Jams, one of my favorite R&amp;B songs of all time. Well, it's a rap song, but you know what I'm saying. Yeah, I love Jimmy Fox, but yeah, for act two. Okay, yeah, so there's, I think part of why I love those movies is one because I'm one of those people who like literally does not drive until they find the right song. So I just, I ultra relate to the character to people like no matter what's going on in his life, I'm going to find the right song to drive to. I'm not going to leave the house or pull out the parking lot driveway or parking lot until I find a given song that I want to drive to that day based on the weather or my mood or whatever. Do you have, so they talk about like, there's that scene where they talk about like hex songs or like curse songs or whatever, which those songs are all about dying. So if I was a bank robber, I maybe wouldn't want to hear those songs that day. But do you have a certain set of feel-good songs or lucky songs, things like that?
+Darius: Yeah, I mean, anything D-Lo these days is heat. I might literally...
+Jordan: Left risk on Bling now.
+Darius: Right thing on Blizzle, baby. I mean, listen. There's a few other guys.
+Jordan: Now, yeah, D-Lo owes you some money for sure.
+Darius: I might be his number one fan. I really, I mean, hard-pressed.
+Jordan: He's your beyoncé.
+Darius: I listen to him every single day.
+Jordan: And you be dead serious too.
+Darius: Oh yeah, it's not a bit. No, yeah, I got a few for sure. Depending on the mood I'm in, depending on where I'm going, if I'm at the gym, if I'm getting ready. Yeah, definitely. I'm drawing a blank right now, but for sure everybody does. So what are some of yours? Some of mine.
+Jordan: Okay, yeah, it depends on like, okay, so if I'm walking into the gym, I either like some R&amp;B or like some really hard ****. Like if I was walking to the gym, maybe like some Olivia Dean, I just love her. Or I'll bump like, Maybe like I'm that by Future or like New Level by ASAP Ferg and Future. Something like that. If I'm on the treadmill, I need something with like a really good, like consistent baseline or beat. I'm trying to think like, Put On, Jeezy and Yay. Love working out for that song.
+Darius: Passengers of Red Bonhoe, we look like some curly fries.
+Jordan: Yeah, or Freestyle by Lil Baby, that's a good song to work out to. Any of the Creed, any songs from the Creed soundtracks, that's like half of my workout playlist is those songs. Lord Knows by Meek Mill, that song, I probably burnt, if I had a CD, that **** would have been burnt because I played it so much. so like that's like working out stuff. If I like I need like a good upbeat song. There's this song called Ain't Too Cool to Dance by Lunch Money Lewis that I love. It's like a really good like feel good song. It's great for like Saturdays and sunny days, you know, type ****. What else? If I'm like chilling, I'm maybe doing some like some dark moody R&amp;B. So maybe I'll go with like Problems by Black or Let's see, like anything about the weekend. I'm a big weekend fan or. There's a song called Lovely by Billie Eilish and Khalid. Love that song.
+Darius: I listen to everything, man.
+Jordan: Yeah, what about you?
+Darius: Jay-Z's That Your Chick is up there. Okay. Meek Mills Monster is up there.
+Jordan: Yes.
+Darius: The Drake, the song. Or he's like, I got girls in real life trying to **** ** my day.
+Jordan: Oh, energy.
+Darius: Energy that's up there.
+Jordan: Yeah.
+Darius: Believe it or not, take care is actually a great workout album for me. DMX is that started something. Yeah, you know, I'm just listening songs now, but off the top that sexy red got a new one.
+Jordan: He wouldn't hang with that.
+Darius: I must.
+Jordan: And guess what? I do. I do.
+Darius: I mean, it is. I feel that song in my soul, man.
+Jordan: I do. I felt it right here.
+Darius: She just knows exactly what I had on my heart when she made that song.
+Jordan: That's my goal every weekend.
+Darius: He **** with me. I'm a vibe. I was like, you know what? You do look like a vibe. I would **** with you.
+Jordan: She does seem like a fun person to be wrong. I'm not even going to hold you yet. She's definitely a minstrel show, but she does seem like a lot of fun.
+Darius: Listen, man. I'm responding to that DM. She's a brag too.
+Jordan: Flewed out with you. Oh yeah, so there's a, excuse me, there's a scene where he thinks he's done his last job. So he burns the burner phone, starts dating Deborah. Really pretty girl, by the way. She's dope actress, Lily James.
+Darius: Was that old girl from the movie, the wrestling movie where everybody died?
+Jordan: Yes, that is.
+Darius: I knew I knew her.
+Jordan: Yeah, that's her. Yeah, that's her. Yes, Iron Claw. I forgot she was in that. Yeah, she's great. What was I going to say? Okay, so I love the part where he starts like delivering pizzas because he's such a great driver. And let me tell you, driving for delivery for pizza, a pizza place is not a bad way to make a living. I love driving. I love listening to music. So you're just kind of chilling all day. I did get a speeding ticket doing that once. That was unfortunate. And then the cop was announcing, he was like, oh, do you have any pizzas? It's like, Mitch, come on, man. Like trying to make chalk **** like. But yeah, you get cash, cash every day. You know what I'm saying? People generally give pretty good tips. So it's not a bad way to make some quick money. Save me during the pandemic for sure. So yeah, that was I thought that was a pretty dope scene. Funny scene. One of my favorite scenes in movies when they're casing the post office. Yeah, post office, right? Yeah. And he's got a little kid with him. The kid is like, look at the camera show.
+Darius: What was the scene? And I was like, I thought it was a nice touch. They steal the lady's car and her baby's in it. He takes that time to give her baby. And I was like, I bet she really appreciated that. I was like, that was very kind of him. Because he's like, Also, self-interested. You don't want to add a kidnapping charge. That's not a good one.
+Jordan: Do not. Or the death of a baby.
+Darius: Yeah, ready. The most unrealistic thing in this movie is he only got five years in the end for all this **** but.
+Jordan: Right.
+Darius: You definitely ain't getting 5 if you kill a baby. A white baby. No, not white baby. No. That Patrice O'Neal joke, he said, if I go sailing, I'm taking a white baby on a key chain with me. They gonna find my black ***.
+Jordan: It reminds me of that scene from Black-ish where there's Anthony Anderson's character gets on the elevator, or was gonna get on the elevator. And it was like a little white girl in there by herself. He's like, sorry guys, I was late, I had to take the stairs. And they were like, and someone was like, he goes, there was a white baby in the elevator. And they were like, why don't you help the baby find his mom? And they're like, have you seen me?
+Darius: Once I ordered some candy off of Amazon and I didn't read the description correctly, so I ended up getting a case of candy. And the girl I was dating at the time was like, well, why don't you just go hand extras out at the park? And I was like, you want me to go hand white babies candy at the park? White babies. I think I'm going to pass on that terrible advice.
+Jordan: It's actually funny, the lengths we have to go through, like it's black people and black men to, like, not look creepy.
+Darius: And we do not be creepy, but it just makes you look. Hand of candy either.
+Jordan: Well, yeah, for sure. But yeah, I wouldn't go to any children and hand them anything.
+Darius: It's just I was going with the theme of the conversation. I would, you know, if you just like recruising by, you saw a grown *** man handing candy to children. You feel like.
+Jordan: Probably shoot him. Probably just shoot him.
+Darius: I'm at least going to call the non-emergency 911 and be like, hey, you guys might want to swing a squad car pass there and make sure that's on the up and up.
+Jordan: Yeah, make sure that's like a resident or he has a child out there or something.
+Darius: It's not quite 911 level, but the non-emergency line might get a chat.
+Jordan: Yeah, that's what the Karens need to be focused on. So what else? Did you have the gun deal happening in act two?
+Darius: No, I had that in act three.
+Jordan: Okay, yeah, then we can go to act three, yeah.
+Darius: Act three, the final track, the high school is horribly wrong, forcing Baby to go on the run from both the law and his former associates. He must use his driving skills and his music to protect Deborah and survive. What I have is after that, so you want to tell the gun thing first?
+Jordan: Okay, yeah, so they're... They need to get some guns for the job, big job they're about to do. Basically, I don't know if it's like their final score, but probably their biggest score to date. And they go, tells all the time you go to the warehouse, meet up with some random dudes. They got to check your ****. Whenever you go in there, they have the crates of guns. They're using meat metaphors in case anyone's wearing a wire. And then Jim Fox character notices that there's an APD stamp on the crates for Atlanta Police Department. And he's like, **** that. They shoot everybody. Which it's crazy to me how he's the only one who noticed that like it's right there. Also, the crates came from somewhere, you know.
+Darius: Well, I mean, so it's not that unusual for for ex-cop guns to be brought up to be found in criminal circles because, you know, it happens. But this is clearly a sting. So it's not really right pertinent. But yeah, that was movie kind of jumped the shark at that point for me. I was like, all of these guys are also trained marksmen. Okay.
+Jordan: And, because they're just standing there shooting behind no objects.
+Darius: No, just, it's a classic movie trope where the enemies have no aim. Yeah. Like they just can't hit any, like it's just. The broad side of a barn. Yeah. It's just, they're just emptying clips into the air and no one's catching even a space bullet. Yeah. And meanwhile, the protagonists are like ******* sniper rifles. They're just like, you know, shooting the bullets are spinning around ****. And it's like, right.
+Jordan: That **** from wanted carving the bullet.
+Darius: Yeah. Jon Hamm turned into Thanos at the end. It was. He did. He's still alive. What the hell? I was like, dude, he did crash that car. The car has been totaled three times over. Yeah.
+Jordan: That's a Don Draper plot armor.
+Darius: You know, it does bring me to my question though. Is Thanos the new cultural reference for just like unstoppable force?
+Jordan: I'm pretty much I believe so. Yeah.
+Darius: Yeah.
+Jordan: I'd say so. I can't think of a more, a more mainstream one, depending on how into like, graphic novels and comic book shows movies and stuff people are into so I'd say that's probably the best one to use for sure
+Darius: and it's also just like the before times before COVID before the MCU was terrible right um you know it's it's it's cool that like it's it's nice that he's just you know a nice little Frozen in time artifact from before you know correct I feel like that is $13 uh you're up here again I
+Jordan: I feel like that whole movie is like a time capsule in a way. Like it's like the, like prior to sinners, that's the last movie I can think of that felt like a big event since this pandemic, like before the pandemic.
+Darius: Well, in game and if any, where we're after this, so. No, I'm saying Thanos.
+Jordan: He was in both.
+Darius: Oh, I thought you were talking about this movie because this is 2017. Oh, no, for sure. Barbenheimer kind of, but.
+Jordan: Oh, well, yeah, for sure.
+Darius: It was really. It really was Infinity War Endgame. I don't even think Barbenheimer hit where Sinners hit. So I guess that would be, it's kind of interesting though, because like what is the formula for a movie, for a cultural phenomenon at the movie theater? You know, Sinners, before Sinners, it was what, a three hour Nolan movie about a physicist?
+Jordan: Right. Who would have thought that was in combination with a movie about an iconic toy.
+Darius: Right. How do you get the people who wanted to watch one to watch the other? Right. Two totally different audiences. So like, yeah, I don't, you know, like I get how you can make Infinity War and in-game pop. And I get how sinners. No, I mean, if you would have told me, if you gave me the plot for sinners in the cast, I'd like that a bit of, I'll go see that. But like a cultural phenomenon. I didn't.
+Jordan: Yeah, I didn't expect it to blow up the way it did. Like I loved it and I knew it was a great movie immediately, but I did not know that it was going to take off, take off the way it did.
+Darius: Why do you think that was? I guess we're not even talking about this movie anymore.
+Jordan: But I mean, we just, yeah, what I think it blew up the way it did. I think when people people of it, I think it's a lot like I can't remember, I lost my point, but it's got vampires. People love vampires. Michael B. Jordan is a box office draw. Him and Coog, I mean, they're, you know, they're legendary already. I'd say, I think one, the music was ******* incredible. People love good music. And I think, honestly, like the passion that Ryan Coogler wrote in the script, it bled through the screen. And I think people really do are drawn to passion, like people, like it's just seen the land from La La Land. When you care about something, people will care about it because you care about it. And I feel like that's a big, a big reason as to why the movie did. So I also think like the movie just had so many like me moments and culturally relevant moments, even though there's a period piece, you know, like the no vision or we're supposed to be kind to another, being polite. Sammy, it had so many like quotables. I think a movie in order for a movie to be a big phenomenon has to have those things.
+Darius: Yeah, I mean, it was original and it had the hook. You have to go see the dance scene. You have to, you know, like, you know, it had the thing you can't get anywhere else. And it was original, you know, I think People are kind of tired of the remixes and the franchises and all of that. And it was a night, it was a breath of fresh air. But it's a good train back on the tracks. What else you got for act three?
+Jordan: You know what ****** me off is when, okay, so in movies when I look out for you and then you put me in harm's way. Yeah. So like when he warned the lady, don't go into the ******* post office because we're about to rob the ****. And then you go and get a police officer, a fat cop by herself with one gun. What the **** do you think he's gonna do? If I'm telling you, don't go in here.
+Darius: Yeah. If someone tells me, hey, I'm about to rob that place, don't go in there. I think Dunkin Donuts is open. You know what? That's an off day for me. Would you look at the time, man? It looks like I'd been wanting a latte. What is the coffee near me? Starbucks on every corner, man. And let me make sure I'm on the camera at the Starbucks. Get my alibis, right?
+Jordan: Correct. Yes, I need to be on public camera.
+Darius: You hear that? Order for Darius.
+Jordan: Yes. I need to be on CCTV stat.
+Darius: Order for Darius Thomas. You hear that? You bam. You got it. Boom. Got it. He asked later. You saw me here.
+Jordan: Yeah. So Starbucks. That's actually Jordan Baker. It's not. It's not just Jordan. You need to yell that name now. Yeah. I was like, what are you doing lady? You just got this poor guy killed for no reason.
+Darius: You know. Trying to do too much. She was doing entirely too ******* much.
+Jordan: Another person in this movie playing hero.
+Darius: Great soundtrack.
+Jordan: Yes, excellent soundtrack.
+Darius: So it reminded me of a bunch of songs I hadn't heard in a while. So what's a song you forgot about that this movie reminded you of?
+Jordan: Oh, that's a good question. I forget. Cause you hear it a lot or it's overused in commercials, but you just forget how beautiful of a song. Easy like Sunday morning is until like in this movie, like it seems so cliche, but like when you hear it with the music, with the visuals and the color, the lighting and the color green and all that, like it just really was like, damn, this is really a beautiful song. And I get why they put it in so many commercials.
+Darius: I love that song. because I love Sundays and I hate people who always talk about the Sunday scariest. Sunday scariest. And I'm like, you ruined it. You, it's a self-fulfilling prophecy.
+Jordan: Yeah, it is.
+Darius: It is. Like, you know, like Sunday mornings, man, you wake up, it's sleepy, get you some brunch, cook it yourself, whatever you want to do. I love Sundays, man. Football or no football, Sunday's a great day and I need y'all to stop ruining it as soon as you wake up, think about work the next day. Right. But for me, it was Barry White's Never Gonna Give You Up. I had forgotten all about that song.
+Jordan: Oh yeah, that's a good one.
+Darius: That's a great, great song. So I put that in the liked column on my, I switched from recently switched from Spotify to YouTube music.
+Jordan: Nice. Okay.
+Darius: Might have to actually check the whole soundtrack and just steal all the songs from it.
+Jordan: Yeah, I've had a hard time finding the official soundtrack for some reason. I'll have to try looking for it again.
+Darius: It probably doesn't have one because Yeah, I think that's what it is.
+Jordan: Cause I found a version of it, but I'm like, this was, but it's not, I know the movies in the order cause I love the movies so much. I was like, this is not it. Another good one is I like finding songs that are sampled in songs that I love. So like there's the song that's playing when it's the second robbery with the guys when they have the Michael Myers mass. And do you know that song Blow Up by J. Cole? That's the song it's sampling with the guitar where it's like, I just can't think of it. I forgot what it's called, but yeah, I thought that was super dope when I remember seeing I was like, I know this song. I was like, oh **** that's a sample. That's a great song too.
+Darius: All right, man, wh</t>
+  </si>
+  <si>
+    <t>Darius: Is this the worst movie we've reviewed? I'd have to go to our archive to see if we gave any more. Let's stay. Let's stay.
+Jordan: Hey everybody, welcome to the Out Trunk Pile with Jordan and Darius, the podcast where two friends started talking in a bar and never stopped. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordan B Writing.
+Darius: And I'm Darius. That's Steve's I love the area on all socials.
+Jordan: And today we're going to be breaking down A24's sci-fi horror feature, The Backrooms. Starring Kane Parsons, Chiwetel Ejiofor, Mark Diplis, and Sophia Lillis. Backrooms centers around a young filmmaker who accidentally clips out of reality. He finds himself trapped in an endless liminal labyrinth of yellow wallpaper and fluorescent lights. As he wanders, he must dodge terrifying entities while a secret corporation attempts to steady the portal. So I'll just toss it to you for act one.
+Darius: This is my bad. I wrote that, but he's not a filmmaker in the movie. He's an architect who owns a furniture store. So I don't know where I must have just cross wired on that. So act one, no clipping reality. A lost teen stumbles into a surreal endless maze of empty office rooms. He quickly realizes he is trapped outside normal space with only his video camera for company. Yeah, an hour into this, I had to shut it off and play Madden. So let me just foreshadow a bit of my rating on this.
+Jordan: You had a hard reset.
+Darius: I turned it on Friday night because I was taking Friday night in the house and I popped some popcorn and I'm like, let me knock out the pod movie. And about an hour into it, I was like, So no, this is not a friend.
+Jordan: This is not a Friday night movie. This is the opposite of a Friday night movie.
+Darius: I had to finish it Sunday afternoon. We'll put it like that. It is. Yeah, I'll be honest with the audience. It's a tough it's it's a tough watch.
+Jordan: They kind of momented it.
+Darius: I don't know what they did with it. It's I'm just the guy I watched it. I promise I did. I could not. I don't know what it was about.
+Jordan: Yeah, me too. I, I literally wrote down like every time I thought I knew what the movie was about, something happened and then I didn't know what the movie was about anymore.
+Darius: It's yeah, I was like, I have here like, is it about the scariness of loneliness? But no, not really. It's just it's a really, really weird movie.
+Jordan: Yeah. Yeah.
+Darius: I don't I don't know what you got on.
+Jordan: So this movie happens. I guess what I have for everyone is so I like to watch a lot of like reaction videos. So like I love music. So I'll watch like vocal coaches reacting to singers performances, stuff like that. So like I'd almost want to watch like a therapist react to this movie and see what they get from it. Because it starts off like with the found footage. I'm thinking like, okay, it's kind of like Cloverfield or like paranormal activity or something like that. And then it comes to like a guy in a furniture shop. I'm like, okay, so we're establishing the world now. And and then you think you kind of have an idea because you see the rooms. It's like, okay, it's kind of like furniture shop. And then you see the guy whose life is like falling apart. And you're like, okay, so this has to mean something here. And then it comes to the scene with this therapist, which And those are the best scenes in the movie because kind of have an idea of sort of what's going on because they're saying words. There's not a lot of words. There's no dialogue in this movie. So it's kind of hard to really follow. It's not hard to follow necessarily, but it's like.
+Darius: I take it like his he was going through a divorce. Right. Drinking too much. And his. Yeah. That was why he was with the therapist. But I don't. We'll get to it later. What I think happened with this is that, but I just have that for Act 2 notes and I want to stretch it out because I don't have much else to say about this damn movie. Right, okay, It's just not a good movie. I don't know what to tell the people. You know, I don't know how it's, very popular.
+Jordan: Yeah, I've seen it on social media a lot and made a lot of money considering what the budget was.
+Darius: It was like 8 bucks. That's... Poor Chiwetel's got to be like, man, I did 12 Years a Slave and 15 years later and still I'm not getting booked for anything. So let me do this internet movie.
+Jordan: Yeah, you know, that's what's crazy to me because he's a fantastic actor and he's been great in everything I've ever seen him in for a really long time. And I don't know why he's not bigger. It's very odd to me.
+Darius: Oftentimes when that happens, they're just ********* behind the scenes and people don't want to work with them. I don't know that to be the case for him. But if you ever see a prominent actor or actress, you're like, what the hell? What happened to them is probably because they just were the one wanted to work with them.
+Jordan: Yeah.
+Darius: Yeah, he's very good. And he does the best with this movie, which is just him running in yellow rooms and staring into the abyss. But, you have anything else for act two or act one?
+Jordan: Yeah, I mean, I guess so, because I mean, so I thought the handprints in the driveway with the therapist and her mom when she was a kid, I thought that was going to mean like more. I mean, it meant something, but first I thought what the movie was going to be about like the way your childhood impacts your adulthood and then it wasn't about that so it was like okay what was the point of the childhood memory I have a theory on that but I'll have to save that for act three I felt like it's almost like the movie is a metaphor for a maze but the problem is like the point of a maze is to get out of it like so there's a journey there and I feel like There was no journey here.
+Darius: Yeah, I think apparently, I guess it was like a science experiment where the point was them to not get out of the maze and they weren't supposed to find it. I don't ******* know. I'll be honest with you, man. I don't do well with bad movies that aren't even, like this just wasn't even entertaining and it was bad. And so, yeah, I just, like I said, I had to stop it. And the little cleanse. And, you know, I watch bad movies quite a bit, but this was and I was like right after I saw Tony, which is not Tony, not like the movie Tony about the Anthony Bourdain biopic. That's not really a biopic. Yeah. And like, that was really, really good. And the next day I try to watch this ******** and it was like tough, you know, it was tough. It's very I feel.
+Jordan: Yeah. yeah just made me want to go back to finish rewatch my rewatch of once upon a time honestly I just was like that movie had a journey but it had hope I just felt no hope in this movie
+Darius: well I mean yeah what were you gonna say I
+Jordan: was gonna say so when I first started watching it and he started to explore more into the maze and the yellow rooms and all that and it was like the everything first was kind of abstract like where everything was slanted but I couldn't tell first I thought it was like like a flat wall things gonna walk into but it ended up being a like a hill or whatever I thought it was like I thought it was like I'm supposed to be like the that Picasso painting where it's like the desert and the flat like melted clocks I don't know if that was supposed to be some sort of allegory there or not so I got frack one.
+Darius: I mean, we got a pretty good second out of it. Act 2, endless yellow. His fatigue sets in the endless buzzing lights and repeating hallways erode his sanity. Meanwhile, ominous noises reveal he is definitely not the only thing roaming these deserted corridors. So 45 minutes of nothing happened. And I think that's the problem you run into with this movie is that it shows the limitations of flipping a YouTube sensation into a movie. without Hollywooding things up. This is a 15 minute YouTube thing where the guy talks and explains something he's been thinking. And there's just there's no there there. There's not a movie here like, you know, and it was a viral YouTube video. I think I haven't watched it. And I imagine that YouTube video was not very long and they just tried to cash in on it. I mean, try they did. It worked. But I just don't think there's a movie here because there's no there's no There's no climax. There's no ending. It's just there's no there. There's it's just it's vapid nonsense. Like I don't understand this movie. It's stupid. Like, yeah, anytime if I have to. If your movie relies on explainers after the fact, after the credits roll, you didn't do a good job of telling your story. Correct. You know, if I have to go if I don't get the story in the box of the movie, then, you know, it doesn't mean you have to spoon feed the audience. Like we reviewed the prestige and like it's hard to follow it the first time. By the end, you know what's going on and you watch it second time and things get better and whatever. But this is nothing. It's just it just it's it's a it's 20 minutes of content that they tried to stretch and they just didn't do a good job of it. It stayed too true to the to the original content. It needed to be Hollywood it up.
+Jordan: Yeah, that's the problem. Cause like one, there's only two characters. There's it's a two hour movie and there's like 20 minutes of dialogue.
+Darius: Yeah, it's like it's a YouTube clip. Like they made a movie.
+Jordan: It's a YouTube short. It was so empty. Like I couldn't even imagine reading the script. Like it just says like you run into this room, you run into this room, you run into this room. The end. I don't get it. Literally for me for act 2, all I wrote was cameraman and girl.
+Darius: That's all that happens.
+Jordan: It's
+Darius: I got, I guess, a philosophical question. Two low budget horror movies went viral this year, Obsession and Backrooms. Obsession was good, so that's obvious. This movie was not. Why do you think this went viral? Like, why is this popular?
+Jordan: I don't know.
+Darius: People love this movie and I don't.
+Jordan: I need to watch some YouTube on this because I don't get it. I don't get the movie. I don't know how people love the movie. I mean, act three was kind of interesting, but so much didn't happen. By the time something started to happen, I was just like, can this be over now?
+Darius: I will not spend another second of my life thinking about this movie. God bless you. If you go to YouTube and figure it out, I won't be doing that. It is their job. Don't give me homework when the movie's over. It's your job to tell me what happened in the movie. Nah.
+Jordan: though check out a review and obsession yeah so I use right I usually watch the movies twice for the pod sometimes three times for this one I was like I'm just gonna do it once I can't do this twice yeah it's just for one you like I didn't really care about the characters because the characters were plot devices they're just pawns in a maze Like a guy going through divorce is not enough of a reason for me to give a damn about his quote unquote journey.
+Darius: It's such a YouTube clip. Like it's just they they they put a YouTube clip on the big screen.
+Jordan: Yeah. Yeah. I don't I'd love to interview the writer and be like, so what we supposed to like, what were you thinking? like literally what was your thought process
+Darius: I actually hope this writer never gets work again uh play in my face with this ******** uh you're ready to get into act three
+Jordan: So that's the only thing I have notes for. So yeah, let's get to it.
+Darius: Act 3, escape the liminal. Desperate to find a way back home, he follows strange anomalies through the maze while avoiding deadly entities, risking permanent loss in the infinite expanse of the unknown. I have here, this movie stops, but it never ends. I don't know what the **** the ending was I don't know what it was about it just stopped
+Jordan: yeah that's a great way to put it yeah my last note of the movie is and I think that's what the movie is trying to say is the maze is basically a metaphor for the human brain I think that's what they're trying to say because she was the therapist was saying like it's all your brain like you control it you know whatever but I don't know But that doesn't even go with like their conversation where he was saying, like, isn't it nice, like, to not be able to feel anything to be like furniture?
+Darius: I think as film critics, reviewers, a lot of people, there's a saying, I forget the name of it or who came up with it, but it's It's like never attribute to malice what can be explained by incompetence. It's basically don't assume. I mean, people know I'm not using big words here. People know what that means. And so in movie review, it's like, don't assume some grand plan. It's just a bad movie. They weren't trying to do anything. They weren't trying to make it a metaphor. It's just a bad movie. It's not that we don't get it.
+Jordan: It's just bad. And I feel like that whole, you don't get it thing is like, sometimes some things concepts are difficult to comprehend. And that's the point of rewatching movies and rereading books. But if it gets to the point where you walk away and you don't get anything from it, then you just didn't do your job as a artist. Like you didn't deliver it well to the audience.
+Darius: No, you know, it's over hit y'all with sayings, but it's like a great argument isn't one a genius understand, it's one a fool understands. So if your movie can only be understood by like. Ten people who, you know, who get the inside joke, then you made a bad movie. I don't know what to tell you. Like, you know, yeah, I don't I'm not an elitist about movies at all. Like, you know, I. I don't need it to be a high concept. It has to be good first. And then you do your thing. But this is not good. There's no there, This is a bad movie. And any attempts to ad hoc, you know, shoehorning explanations, I think are just giving the director and the writer too much credit. I just think this is bad. Yeah.
+Jordan: It's just like, what? it's like the end. It's like, okay, was that the big statue version of himself? That's supposed to be like his inner child. That's supposed to be his ego. I don't know. Never explained that. Why did they not explain to her what the hell she was just in? Who was that guy? What does MRI have to do with the maze? Yeah. What does MRI have to do with any of that stuff? Like, I just, none of them made any sense.
+Darius: You know, my best stab at it is some science lab was running an experiment and they walked in on it and they had to trap them in there because they didn't whatever they were experimenting with they couldn't get out but that's me mapping on things that were that weren't in the movie you know it's just you know I I don't really think I don't really want to over over think it overthink this one I just think it's bad like some movies are bad some movies Just don't do, they don't, they set out to make a goal and whatever happened just didn't work. I have no idea why this movie is popular. You say you want to talk to the writer. I want to talk to like Joe Blow fan who liked it. I'd be like, okay, well, explain it to me what it, like, there have been bad, there have been movies I didn't like that I understood why other people did. I don't get this one. Like, it's just really dumb.
+Jordan: It's like, remember that scene where he's like, It's like explaining a dog to someone and then having them try to draw a picture of it. And it's like, well, that's what this movie is. And I don't think that's what they meant for this movie to be.
+Darius: Yeah, they went for some high art concept and I just think they missed the mark.
+Jordan: Yeah, I need filmmakers to get back to focusing on story. Like get the story right first and then everything else will fall into place. You know, Sinners was a fantastic story. Obsession was a great story. Like that's why people like those movies. And then you throw in the relatability.
+Darius: Keep the main thing, the main thing. There's nothing wrong. tropes are tropes for a reason. You can lean into them. if we like the characters, we'll stick around. I think I mentioned this earlier in the review, but like I just saw Tony the movie last week and that was just a run of the mill come of the age, coming of age story of a young man, you know, leaving his leaving his hometown and There was something groundbreaking about that, but like, it worked and it was good. And if you make a good movie, you don't have to, you know, do all the special things, you know? Yeah.
+Jordan: You don't have to assign context and virtue to something that doesn't have either of those things. Yeah, I didn't get it. Like, I just. And then it was, you know, the whole where she's like, you don't have to change. It's okay. Maybe you don't really want to change. Okay. Like, that made sense. But. still doesn't go with the storyline. It's like you tried to combine like sci-fi with therapy and it just didn't work.
+Darius: The script should have been burned.
+Jordan: You know, at the stake.
+Darius: The script should have. This is why I say it should have been Hollywooded up. And I've said this before on the pod that like the suits are right more often than we give them credit for. This is 1 where the suit should have been like, nah, make this palatable. Like make this so the average person going to see the movie understands the ****** going on. You need, we need stuff to actually happen. You can't spend 45 minutes walking around staring into a yellow room. You know, like we need to pretty this up because it's not palatable. If your movie is only accessible to the 15 of your friends, then you need to keep that on YouTube. You know, I don't know what to tell you.
+Jordan: Yeah, also a horror movie that's boring and has no horror is going to be a bad movie every time.
+Darius: Yeah, foreshadowing my rating, but my rating will reflect the unique badness of this movie. Do you have anything else for X3?
+Jordan: The credits were great because that meant I was free from watching this movie.
+Darius: I just, again, I can go back to my point, man. It stops, but it never ends. Like this, like it had no ending. And I'm glad that it stopped. We'll go with that. So with that, what do you rate it?
+Jordan: The acting was really good, but I'm gonna give this movie 0 stars and I'm never gonna see it again. And I hope no one else ever sees it again.
+Darius: I didn't know zero was an option, but I gave it a one. This is, this the worst movie we've reviewed? I'd have to go to our archive to see if we gave any more one.
+Jordan: Let's stay, let's stay. Yeah, let's talk about that. I think it was something to discuss.
+Darius: You know, we don't have to fill time just to fill time, but let's see if we can stop.
+Jordan: I think Low Down Dirty Shame was pretty bad, but it was entertaining.
+Darius: Oh, I love that one. I was looking into the one star. We gave. Yeah, we've never given a one star. Well, this is our first one. One star, worst movie we ever reviewed. We spent two hours on this as community service to all of our listeners. And you can save your time, your energy, your space. We appreciate you listening to us, but this was a terrible movie. You could skip it.
+Jordan: We truly do. I'm sorry, guys. And A24, y'all really let us down. Y'all haven't done it yet. Done it often, but y'all let us down on this one.
+Darius: I appreciate A24 for taking chances and doing original things because this movie is original.
+Jordan: You know what I'll give them that.
+Darius: But um and we do need that original is like half of it but it has to be good too because I'd rather you do something stale and it'd be good than do something original and it'd be incomprehensible and incoherent.
+Jordan: And terrible yeah I agree zero stars and it and I feel like abstaining from entertaining the audience is not a substitute for making a good movie you know what I mean like I feel like they thought like oh if we make it make them think they're supposed to think a lot. That means we made a good movie, but you didn't and you didn't entertain me. So.
+Darius: Well, it's like, I've seen The Pianist. Did I find that movie entertaining? No, but I see how someone else would and I can tell it's a good movie. Right. You can do highfalutin artsy fartsy stuff and I can appreciate it, even if I didn't personally enjoy it. But this was none of the above. This wasn't artsy. This wasn't highfalutin. This wasn't high concept. This was just bad. It was just a terrible movie. Horrible. So, all right. Thanks for listening. My name is Darius. That's Dee's all up in the area on all socials.
+Jordan: And I'm Jordan. That's Jordan to be riding on all socials.
+Darius: Please rate, like, subscribe. We're at out the trunk pod on all socials. That is out the trunk pod on all socials.
+Jordan: And for any ongoing move recommendations, feel free to reach out to us via e-mail. That's out, well, outthetrunkpod@gmail.com, outthetrunkpod@gmail.com. That's a wrap. Thanks. Come to the movies with us. Come back next week. We're reviewing the photograph.
+Darius: All right, y'all.
+Jordan: Take care.</t>
+  </si>
+  <si>
+    <t>Jordan: Yeah, considering that movie, not **** happened in that movie.
+Darius: Yeah, you didn't even rate it.
+Jordan: There's nothing to say about the rating. Halle Perry looked good in those pajamas. The end. Hey everybody, welcome to Out the Train Pile with Jordan Darius. This is our movie review segment. My name is Jordan. That's Jordan me writing on all socials.
+Darius: And I'm Darius. That's these all up in the area on all socials.
+Jordan: And today we're going to be reviewing the cult classic Baps, came out in 1997, starring Halle Berry, Natalie DeSelle, rest in peace, Martin Landau, Ian Richardson, Pierre Richards, and Bernie Mac, also rest in peace. Baps is about Niecy and Mickey, who are two ambitious waitresses from Georgia who head to LA to audition for a music video dance role, hoping to raise money to open their dream business, a combination hair salon and soul food restaurant. Through a wild turn of events, they end up living in a Beverly Hills mansion, pretending to be the granddaughters of a wealthy, ailing millionaire's long-lost love. Along the way, they bring plenty of southern flavor, gold teeth, and sky-high hair to the upper class. That's all Steve for act one.
+Darius: Act one from Georgia to Beverly Hills. Niecy and Mickey pack up their dreams and heavy Southern accents to make it big in LA. When the video audition falls through, they get scouted by the scheming nephew of an aging billionaire, Mr. Blackmore, who offers him 10 bands, $10,000 to bring joy to his uncle's final days. Shout out Robert Townsend. I don't even know he directed this.
+Jordan: Oh ****.
+Darius: He puts people over there. Bernie Mac was in this joint. Faison Love was in this joint. AJ Johnson was in this joint. It's funny, we'll go back in 90s movies and just seeing all the cameo appearances. Yeah. It's funny. So movie opens with the breakfast diner and it just made me wish that Raleigh had actually had a good breakfast diner. Not brunch, actual greasy spoon breakfast diner. We did not have one of those. If you are listening and you are so inclined, start one.
+Jordan: Please. Yeah. First thing I thought of when I when they opened the opening scene was Waffle House.
+Darius: Man, I'm a ******* pork chops look so good. Hash browns.
+Jordan: Yeah, they did, man.
+Darius: Nothing like that exists in Raleigh.
+Jordan: I know, man. It sucks. It's funny. They made me think of like when I've worked in like various, you know, restaurants and fast food and all that stuff. And it's when the guy asks for like He's like, no, I wanted it hard toasted hard, but not burnt, whatever. And it's always the customers who are the most high maintenance. They give the worst tips.
+Darius: Yeah. Why'd you burn my toast, baby? This movie is so 90s because it's just.
+Jordan: It is.
+Darius: Just people telling jokes. They don't make no damn sense. Like, you know, there's really no plot. Being in the club without $16 is absolutely insane.
+Jordan: That should be a crime, actually. You should go to jail for that. What did you expect to happen? What did you think you were going to buy for 16 bucks? That's all I want to know.
+Darius: Just, I don't, like, stay in the crib, man. It's cool. Just lay low for a little bit.
+Jordan: Just sit out, wait, for the next paycheck. It's a Friday every week. It's cool.
+Darius: Yeah, you know, like the same people are going to be in the same spots. You ain't missing nothing.
+Jordan: Correct. Yeah, it's funny because I'm like, you're out on, but it was funny that when they met the dudes at the bar and they were like, all right, it's ladies night. And the guys were like, well.
+Darius: I thought that meant that they don't, dude. When's the last time you think Halle Berry's paid for her own beverage?
+Jordan: I mean, honestly, I don't think she's ever played ever.
+Darius: I really don't.
+Jordan: Woman that beautiful? Do you think she's, I don't think, yeah, no. Do you think she knows how much rent is?
+Darius: It's funny though, because this is probably the worst she's looked at a movie. You actually have to try. Yeah, of all of her movie looks, this is probably the worst one. They could make her look poor and broke if they tried. Like, if they tried, it did not work.
+Jordan: It just looked like she was in a Halloween costume.
+Darius: Yeah, it really did. It looked like she was acting.
+Jordan: Yeah, literally. Yeah.
+Darius: What else you got for act one?
+Jordan: So we got, okay, they're dancing in the, they're in the line for the video vixen. auditions or whatever, and they're dancing in the street like deranged prostitutes. And then you see the Hispanic guy and he's like, yeah, we, I want to cast you guys in a role or whatever. In fact, they were like, yeah, cool, we'll do it. Like, they didn't sound creepy at all to you or underhanded in any way.
+Darius: In the 90s, man, no one cared about sex trafficking. Also, the prize was 10 grand. So they were fly. They spend all their savings to fly to LA for one day to win 10 bands. And then what? I don't.
+Jordan: Yeah, I don't. Could you open a restaurant for $10,000?
+Darius: I don't know. no I don't know what it was if you could open the restaurant you couldn't still you'd have to like pay rent and have an apartment or something you know so you don't need to open a restaurant how much money again 90s movies but like how much do they think video girls made um I don't know it wasn't I don't know I wonder huh.
+Jordan: That's a good question.
+Darius: I don't even think you could get Well, you could now for sure. But in the 90s, you might get into an apartment with 10 grand, but that's three months. That's all your rent going to be burned up. So true. You got anything else?
+Jordan: Yeah, I mean, I mean, not much happens in act one, honestly. They're just they're with those bum dudes. Okay, actually, why were they dressed like it was the 70s? I mean, the dudes like who were in the club. Why were they dressed like that? What was with the fence? He's wearing a hat and a wig. I was genuinely confused.
+Darius: I don't know. The Robin Townsend movie. They just.
+Jordan: Yeah, yeah.
+Darius: And yeah, like it might have been like a theme party, but no one else was dressed that way. I think it was a very heavy-handed way of saying these were like older, washed, outdated losers. It just, very bad expanded with it.
+Jordan: Either that or that was like Robert Townsend's take on like Southern fashion in the 90s.
+Darius: Could be. Could be. All right. Act 2, the makeover of a mansion instead of letting Beverly Hills change them. Nisi and Mickey completely remodel the mansion's vibe. They teach the stiff butler manly how to groove, cook up comfort food, and form a genuine heartwarming bond with Mr. Blakemore, who finds a renewed spark for life. Is this a magical ***** movie? Because I feel like it is.
+Jordan: Yes, absolutely. 100%. I thought the same thing. This movie is like, if you take Bring Down the House, but remove like the nuance. Like bring it on the house and like it was there was an element of that, but it was like, that was the joke. I think they were dead serious.
+Darius: No, they were dead serious. Like she literally feeds him like seasoned food and he like comes back to life and the next day he's like.
+Jordan: Yeah, she's like, oh, she's like, oh, Master Johnson, I'm gonna get Master Johnson. I cook up some real good food for you, sir. She's like, nah, you need some kind of green.
+Darius: Yeah, that was not a healthy plate either. She's like, this is gonna be healthy for you.
+Jordan: Yeah. Even the butler was like, isn't this like high in sodium? And once you get diabetes and or.
+Darius: Hospital or whatever, like the plate was this big, like the portion sizes were out of control. And it's like, yeah, I mean, it's not deep fried, I guess, but that doesn't necessarily mean it's healthy.
+Jordan: She was like, I could go for you, sir.
+Darius: It really is a magical ***** movie. They like thought about a dance.
+Jordan: Yeah, they really did. They really, really did.
+Darius: Man.
+Jordan: The crazy part is this movie came out 97. Halle Berry got X-Men like three years later.
+Darius: Yeah. I mean, it's funny because I was like looking and I was like, is this like her breakout role or something? And she just took it. But like, no, she had done Boomerang.
+Jordan: Yeah.
+Darius: Jason's lyric. No, that was Jada Pinkett Smith. Yeah, she had credits like she didn't have to do that.
+Jordan: She had done ****.
+Darius: Yeah, she was just. I mean, she wanted I mean, she black. Maybe she just wanted to work with Robert Townsend. It was a legend, you know.
+Jordan: Yeah, that's probably what it was. I would assume that's what it was. Yeah. Yeah. They definitely played the magical ******* in this movie for sure. It made me think of. Okay, so I got a question for you. If you were to read make this movie today with like two modern celebrities, actresses, whoever, who would you cast as the characters as the two girls in this movie? So I have mine. I want to see if you have the same people.
+Darius: They have to be just as outlandish.
+Jordan: Yeah.
+Darius: I mean, she might be too old for the role now, but Tiffany Haddish.
+Jordan: Oh, OK. Yeah, yeah.
+Darius: Wyatt is her name.
+Jordan: Palmer.
+Darius: Palmer and Tiffany Haddish. OK, I would go with. But that's a good do it now.
+Jordan: Yeah. Yeah, I think so. That's a good duo. Mine was a sexy red, a young Miami.
+Darius: Well, I thought we were talking about actual actresses.
+Jordan: Oh, okay. Okay. Actresses. I guess I would. I would go Keke Palmer, too, and then I'd maybe go. It's like a young black actress. I mean, do we have we don't have a lot. Maybe like Chloe Bailey. I think that would be funny in that in that kind of role.
+Darius: Sexy red and young Miami couldn't read the script. So I don't really know.
+Jordan: That is also true.
+Darius: Get through the filming of the movie. I don't know. They still read with their finger on the page. You got anything else for Act 2, man?
+Jordan: Act 2, Act 2. Oh yeah. So I do love the scene where he sends the butler or whatever to the record store.
+Darius: Yeah.
+Jordan: And there's like a list of records that they need, they need him to get. And so when he walks in, the black dude's like, hey, man, so we got the classical section right over there.
+Darius: It was a funny movie. I laughed a few times. Well, I mean, I would do the same. You know, I mean, I might ask what you're looking for, but like, yeah, like the Kimmy G's over here.
+Jordan: So.
+Darius: I would assume that he was, you know, looking for Beethoven's greatest hits or whatever.
+Jordan: Right? Yeah. I will say, though, the best way to have my money is one of my favorite and most underrated songs from the nineties. I don't know if you've ever heard it before.
+Darius: I have. I just.
+Jordan: It's a banger. I love that song. Very misogynistic. So, like, maybe don't play around women, but it's a fun song to listen to.
+Darius: They don't currently listen to Spendat, so I don't really think they're quite discerning in the content. Not all women, token, disclaimer. But no, I mean, it's a magical ***** movie, but like, that's fine. It's 100%. Yeah.
+Jordan: It wasn't, it wasn't supposed to be anything important or culturally significant.
+Darius: Right. It's fine to make silly ****. I mean, we need more, whimsy in Hollywood. So.
+Jordan: Yeah, we do.
+Darius: Anything else for I2?
+Jordan: Yeah, that's all I got for Act 2.
+Darius: Moving into Act 3, we got the real princesses. The nephew's greedy scheme unravels when the girls realize they're being used to manipulate Mr. Blakemore's will. Despite the drama and a devastating loss, Niecy and Mickey prove that their heart and loyalty were always real, ultimately getting the happy ending and the business that they fought for. I love how they've done all of this in like 3 weeks. Right. Speaking of funny, man, AJ Johnson crying by the pool. I laughed out loud, man. What he said.
+Jordan: No, that was funny. That's funny.
+Darius: You shouldn't have to wear your Sunday clothes on Wednesday. That's funny. That was freaky.
+Jordan: No, he was funny. He's like, you should have a backyard.
+Darius: I want to eat too. I'll go to restaurants and they'll order food.
+Jordan: Yeah, What did he say they had like Parmesan and water or something like that?
+Darius: You said you should have to wear your Sunday clothes over Wednesday. Why does she have three outfits?
+Jordan: I have two days of clothes.
+Darius: That's poor, man. That is.
+Jordan: Yeah. No, that's.
+Darius: The trenches.
+Jordan: Yeah, that's like worse than the set it off.
+Darius: Oh, for sure. To no one's surprise. Critics hated this movie. You know, but it's a hood classic. But critics hated. Yeah. Critics hated, you know, what's the Napoleon Dynamite? Like every movie ain't supposed to be super serious.
+Jordan: So 98 on Rotten Tomatoes.
+Darius: Yeah. Critics hated it, but the hood loved it. And ultimately the hood did love it.
+Jordan: The hood.
+Darius: Critics. I mean, Halle Berry has a lot of movies like that, you know?
+Jordan: She makes a lot of. Yeah. Yeah.
+Darius: I mean, she's not a great actress, but she's just hot.
+Jordan: True. She, she's like, she, so I would say more so. I think she's a good actress. I just think that she's like, she's almost like Kobe Bryant, where like, as a legend, like all time great. But like, if you look at the shooting percentage, it's really not that good. But they gave you moments.
+Darius: And the highs were high. You got anything else for act three?
+Jordan: I did like at the end where He's passed, he's passed away. The old guy passed away. And they're saying like, they're telling the lawyer like, okay, hey, so like, just, you know, like we weren't actually related to his long lost love or whatever. And they're like, she's like, yeah, we knew, we knew, he knew that. She didn't have any kids. It was a nice little sweet touch at the end of the movie. That they had grown to love that guy for all of, you know, three weeks or however long they'd been in LA.
+Darius: I mean, he literally given them thousands of dollars and.
+Jordan: You know yeah fun of the lifestyle and shopping and all that.
+Darius: It's kind of this movie actually go ahead.
+Jordan: This movie actually is this is basically we take spin that and make it a movie yeah I was it's maps.
+Darius: He's been his last days with hookers I even it's like.
+Jordan: I thought that too because at the one point I was like are you not going to really?
+Darius: His last days tricking on escorts uh that just had his nephew found in a line and he on his dying bed he's with two escorts and two schemers like live a life that's a bad way to go your last couple weeks entertaining 2 strange women who are just there because you're rich yeah that's a bad that's a bad way to go that's a bad way to go out man who are lying to you about their connection and you know they're lying to you but you just want the company you're gonna because all you got you know that's the only person that's nice to you in ******* years What a miserable living. But yes, I found the scam. He went out with a smile on his face, you know.
+Jordan: He did. He did. Lawyer was cute, though.
+Darius: She was. What else you got for Act 3?
+Jordan: That's literally all I have for Act 3. I'm not even gonna lie to you. There's not a lot that happens in this movie. It's just like it's just him being funny.
+Darius: Yeah, and it's short. But I got a closing question. So the hybrid business model was a soul food hair salon, which is unsanitary as hell. But that's beside the point.
+Jordan: That's ****. That's disgusting.
+Darius: If we were to open a podcast studio with a hybrid business, what would the business be? I want to see if we have the same answer.
+Jordan: Okay. Oh, that's a good one. Okay, so podcast studio slash something. I'm going to go sports bar.
+Darius: I have bar. We got the right answer. Ding, ding, ding.
+Jordan: Yeah, probably we get the people drunk and just record episodes. There you go. Get these crazy sports takes off.
+Darius: All right. All right. Thanks for listening. My name is Darius. That's these I love you area on all socials.
+Jordan: And I'm Jordan. That's Jordy B riding on all socials.
+Darius: Please rate, like, and subscribe. We're at Out the Trunk Pod on all socials. That is Out the Trunk Pod on all socials.
+Jordan: And for anyone going to move recommendations, feel free to reach out to us via, oops, reach out to us via e-mail at outthetrunkpod@gmail.com. That's outthetrunkpod@gmail.com. That's a wrap. Thanks for coming to the movies with us. We'll be back next week with another episode.
+Darius: All right, y'all.
+Jordan: Take care.</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to Out the Trunk Pile with Jordan and Darius. My name is Jordan. That's Jordy B. Riding on all socials.
+Darius: And I'm Darius. That's Deez I Love the Ariel on all socials.
+Jordan: And today we're going to be reviewing The Best Man. This movie came out in 1999, starring Taye Diggs, Nia Long, Morris Chestnut, Harold Perrineau, Terrence Howard, Sanaa Lathan, Monica Calhoun, and Melissa DeSouza. The plot of Best Man sets his own Harper Stewart, who travels to New York to serve as the best man for his friend Lance's wedding. However, Harper's debut novel, an autobiographical story featuring thinly veiled versions of his friends, is circulating among the wedding party. His past secrets starting to destroy friendships and the impending ceremony. Toss to you, Fracklin.
+Darius: Act one, the arrival of the manuscript. The college friends reunite in New York for the wedding while Harper tries to keep his controversial novel under wraps. An advanced copy begins circulating, sparking curiosity among the group. And I didn't even have this written down, but you know, I just got to thinking. How did he think this was going to go?
+Jordan: That's what, okay, that's my point. Every time I watch a movie, I'm like, what the **** did you think was going to happen? You wrote a book.
+Darius: About- What does success look like here?
+Jordan: Yeah, when you wrote a book about ******* your best friend's wife when y'all were in college, you thought he would be cool with that? Like he thought he wouldn't figure it out? I don't understand. Also, why read the book?
+Darius: Well, to sell, but... Oh my God, they're reading it.
+Jordan: Breaking news, water wet.
+Darius: It's like if I wrote a book at the minimum, I'd expect my friends to read it. What did he, what was he like? How did he expect this to go?
+Jordan: That's by far the biggest plot hole in the movie.
+Darius: The whole premise is stupid.
+Jordan: Yeah, the whole premise is stupid. It only works if you're going to assume that Harper is an idiot. But he's not an idiot.
+Darius: It's just every time he's like, oh my God, you're reading it too.
+Jordan: Right. Damn, who else has my, who else has my best selling book that's about to come out?
+Darius: They're the best dad at his wedding. He's like, oh my God.
+Jordan: He's like, you have a copy. Yeah, it's like in the world of this movie, in the world of this movie, this book is basically going to be like ******* this generation is like Great Gatsby or Twilight or, you know, some **** like that. Some phenomenon that took over the world, basically. Like, no one would be like, it's like, who the **** heard Thriller?
+Darius: Yeah. It's just, it's hard for me to like, obviously it's a good movie, of course, but that premise is just once you get past the absurd premise, you know what it's like? It's like the TV show Suits.
+Jordan: Yeah, yeah.
+Darius: Like the premise of someone getting into the most prestigious law firm in New York without going to law school is absurd. But once you get past that, it's a good show. And so once you get past the whole premise of him writing a book, not realizing his friends would read it, it's a good book.
+Jordan: Yeah, so I always thought about that. I honestly think it was literally one stupidity, of course. But I also think it was just, honestly, I think it was guilt. And I think he just like needed to find some way to get it out. And I think some part of him wanted to tell Lance, but he didn't know how to. So he just did what a writer did and he wrote about it and it turned into a great book that he had to sell.
+Darius: Well, okay, so. All right. Obviously, the way he did it when they were actually because he slept with Mia while they were her and Lance were together, correct?
+Jordan: I don't know.
+Darius: I'm pretty sure she wasn't.
+Jordan: She wasn't talking to him. So like, is that a breakup? Is that a break?
+Darius: Come on, this is the best minute of his wedding. It doesn't matter. Okay, yeah, wait, that's fine.
+Jordan: Yeah. So they were.
+Darius: You told me y'all weren't talking no more. They're going to have my wife. What are you talking about?
+Jordan: They were together. But it was college.
+Darius: If it had been before they met at all, I say take it to the grave. But yeah, I mean, I would never put myself in this situation. Right. But I guess those are deeper things later in the movie. But let me ask you this.
+Jordan: Yeah, for sure.
+Darius: He plays Stevie Wonder's as for Nia Long's character. For my money, the greatest song ever written. It may not be the greatest song ever made, but as far as like songwriting is I think that's my favorite song written ever. It's just beautiful.
+Jordan: Okay.
+Darius: I won't bring it up on you right now. You can think of it later, but if you have an entry into the greatest piece of songwriting, you can share.
+Jordan: Oh, yeah, I got an answer for that.
+Darius: Oh, yeah. All right. Off the top.
+Jordan: Either Chase Will Come, Sam Cooke or Fast Car, Tracy Chapman.
+Darius: Great entries. Two iconic songs. I really.
+Jordan: It's just ******* they're like perfect songs. And she wrote, she was like ******* 19 when she wrote that **** or something.
+Darius: Yeah, that one's up there. That one's so, that song is so hot. It went platinum again by somebody else.
+Jordan: As a cover.
+Darius: It's somebody else's biggest song.
+Jordan: Right.
+Darius: And Luke Holmes ain't no hoe. He got songs. And that's still his biggest song.
+Jordan: Yeah, that's one of them. I'd go, Killing me softly.
+Darius: Yeah.
+Jordan: Roberto Flack or the Fugees, whichever one you know you want to do.
+Darius: A parcel to the Fugees. Sometimes me too is just better or the cover is just better.
+Jordan: I had another tip of my tongue. **** I'm blanking. Oh yeah. Reetha Franklin.
+Darius: I'll say speaking of covers being better than the original, Reetha Franklin's respect. was a Sam Cook song, I believe. Sam Cook. Oh, ****. Sam Cook song. She smoked them on the cover. Sam Cook. No, it was. There's the other old The Sam Cook. No, it was. Yeah, it was.
+Jordan: It was. Okay. Okay.
+Darius: So there you have it.
+Jordan: That's a good one. I got a couple more. We should. We can do an episode of this, honestly.
+Darius: Yeah, we're good.
+Jordan: Yeah, actually, it's funny. I actually, that's like my third line.
+Darius: Otis Redding note. Otis Redding.
+Jordan: Oh, that's what, okay. I was thinking it was, I was thinking it was that. I was thinking it was that. I was thinking Otis James.
+Darius: I just had to make, I'm not, I just, I knew that was wrong. So Otis Redding did respect and Aretha Franklin smoked him. So anyways, any other, any other entries?
+Jordan: Any songs ever written.
+Darius: Yeah, we can TBD it.
+Jordan: I would say this is not this is not like a ballad. It's a rap song, but rap is obviously songwriting. Spaceships, Kanye, GLC, Consequence.
+Darius: Spaceships. Yeah, that was hot.
+Jordan: That was hot. Spaceships. I could fly. Yeah, that's my ****. I love that song.
+Darius: If my manager insults me again, I will be assulting him after I **** the manager up.
+Jordan: Then I'm going to shorten the register up.
+Darius: I remember when Kanye was black. Shelly was the baddest one to me and she's the least famous one.
+Jordan: She was so fine. Oh my God. She was so fine in this movie. And the second one too. She, they always great. They always great. But yeah, she's fun as ****. She's bad. I mean, I mean, personally, I love me some Sanaa Lathan though.
+Darius: I mean, I would go Shelly, Sanaa, Nia, Regina, and I don't even like Monica Hall, I think. Call.
+Jordan: Monica Calhoun.
+Darius: Calhoun. Yeah. Just the test.
+Jordan: Yeah.
+Darius: All right. Respect though. I'm going to say RFP. She died. Her character died, not her. She's still with us people.
+Jordan: Sorry to this man.
+Darius: So he walks in the store with Nia Log and he says, So every so often you hear something that really dates a movie. He's about to check out and he asks, do you take Visas in here?
+Jordan: Oh yeah, Because places really didn't take certain cards. You know, like remember like the card growing up, nobody took was Discover.
+Darius: Yeah, I remember when I used to work retail, like there was a certain cards we didn't take or it was like, it was not universal. And now you don't even need a card. Your phone pays for it.
+Jordan: So yeah, now it's weird if you have cash.
+Darius: Yeah, it's gonna be, we're getting get to the point where it's weird if you have your card.
+Jordan: That too.
+Darius: I'm, that's where I draw the line. I need, there needs to be something when you spend money. I need to hand you the card. It's too much easy if I'm just.
+Jordan: Going to need to be able to do this.
+Darius: I don't need to just be able to do this. too much. There needs to be some friction in your consumption habits.
+Jordan: So that's why sometimes I just take out a couple 100 cash and just be like, so I can remember that I'm actually spending real money. And it's not just like a play thing on my, like an app on my phone that I'm playing with.
+Darius: One of my, something I still live by, man, before I go on a date, I always go and get a couple 100 cash because if my card is declined, I will not, I know.
+Jordan: No, I feel that happened to me once, but I had money. It was, I needed a new card and it got here in the mail, but I didn't realize it had gotten here yet. And I was at Bartaco. I mean, if it's written there, but it's, you know, card only, you pay like as you go. So I'm on a thing and I'm like, it's not going. And I'm like, oh ****. And she's like, you asked me out and brought me here with no money.
+Darius: She really said that to you?
+Jordan: Yes. So I literally had to got on the phone, call the bank to get my new, get the e-card. I got the e-card on my phone so that I was able to pay. It was fine. I was able to pay whatever. But I just never recovered. Like we're so friends.
+Darius: No, no, you could have just gone ahead and went home.
+Jordan: I wanted to kill myself. I thought about driving away, like walking out of the restaurant and just never coming back and just driving home.
+Darius: Swing by the store to get some cyanide and just end it. No, that's why to avoid that horrifying situation. I always go grab a couple 100 bucks cash just because it really, I know it always, it's ****. Like the system sometimes just don't talk and it would just be my luck. Like it was just, she really said, You brought me out here with no money.
+Jordan: Yes. Oh my God. Like, cause she thought, so I think she thought I was trying to finesse her. Cause she was like, is it cool if, like before I was gonna pay, she was like, is it cool if I pay? Like, and I was like, I'll let you put your card on file, but I'll just cash app you whatever. Cool. And the cash app wasn't going through, right? Cause it was linked to the card that was expired because I got the new card while I didn't see it in the mail.
+Darius: My God.
+Jordan: And we're sat there and we're like eating. And by the way, I ordered something unique on the menu. I didn't like that. The tequila wasn't hitting, so I'm stone cold. So I'm anxious. I'm wearing a turtleneck, so I'm like getting close to foot because I'm stressed. I'm like, it was the worst. Like it was like an episode of Insecure, bro. I wanted to shoot myself. After that date, I went to the bar and I got plastered. I was.
+Darius: You had her put her card down and then your cash app didn't work to pay her back.
+Jordan: Eventually it did because I got the new, I had to call the bank and get the, whatever. But no, it was awful. And the worst part about it was if I didn't have money, I wouldn't have been ashamed because I would have been a scammer. But because I had the money, it was worse because I knew it looked like I was lying.
+Darius: I almost want to cancel the rest of the segments and just talk about this. Oh my God.
+Jordan: No, and what the worst part is? It wouldn't, that was obviously awful, but you've actually seen the girl. Like she's like insanely attractive. So like, I really wanted to kill myself. I was like, oh my God.
+Darius: Oh, no. Oh, oh, no. Yes. I know who you're, oh my God. Yeah. You should have taken your car and driven it right off a bridge. I'll give you great.
+Jordan: I know. We hung out one of the time and it's just like, I think I just was so embarrassed when the first time it was, you know?
+Darius: She would have never seen me again. I would have been like, I just, what?
+Jordan: I recovered nicely, but that I still, whenever I see her, I'm still like a little bit embarrassed. I still think about it sometimes. Like it's.
+Darius: Fellas, keep a cup of hundo on you. Keep a couple 100 in the safe. At the crib, you never know. Keep a go bag, keep a couple 100 in the safe. And whenever you go out on a date, at least get 100 in cash. Do not. Also, you put your card down, I'll cash app you later. That don't even, that's not player either. Don't do that.
+Jordan: She's so fun. I still, oh my God. Oh my God.
+Darius: She should in theory be able to leave her wallet at home. Like there should be no, oh, I'm gonna send you this 30%, no, just pay for it. Especially the very first date.
+Jordan: The first date, yeah.
+Darius: In theory, she should not even have to have a wallet with her. Yeah, I don't even I don't even know how to get back to this movie. Would you feel betrayed if someone wrote personal details about you in a fictional book? If I wrote about this date.
+Jordan: Yeah, if you read about.
+Darius: If I wrote a book and I was like, I was at Bar Taco and my car got declined and the girl was fine. Would you be away? Would you feel away about that?
+Jordan: I mean, we might need 5 minutes.
+Darius: That's so bad. You tried to cash app her and it didn't work.
+Jordan: We would be having words. We would be having some words, man.
+Darius: I mean, the whole, all 17 of our listeners are gonna hear this now. So.
+Jordan: Oh no, like this situation is fine, whatever. Like it's funny. Like if I was a comedian, I would tell this on stage, you know what I mean? Whatever. But, you know, I mean, it depends on what the details were, but I probably would be a little upset, especially if, because if you want to air your **** out, cool. But run it by me first. Don't just throw me like.
+Darius: Again, it depends on the detail, but it's actually very easy to write fiction inspired by true events with plausible deniability. Like you don't have to like.
+Jordan: Because if he had put this **** in like the world of Hogwarts, I don't think they wouldn't even have thought that it was about them probably.
+Darius: He just, he literally just wrote a biography of himself. Yes. And was like, my name is Chad. And expected no one to know.
+Jordan: Yeah, right. He's like, so I kissed him for it after I ****** her.
+Darius: It's like, oh my God, you have me in the track one. Brokey. I'm just ******* with you. Bar taco. And it was declined for like.
+Jordan: $5. No, it wasn't even that. It was like, I would take the card on file because the card would like technically expired because I got the new one.
+Darius: She actually calls you out. She said you really invited me out.
+Jordan: Yeah, she was like, did you? She was like, did you really just You really just brought me out with no money.
+Darius: All right, I'm off it. I'm done. I'm sorry. I just did not expect it. Where do you get back to?
+Jordan: Well, actually, real quick for act what I got to bring this one point up. Also, like writing the book is one thing, but dedicating the book to the couple whose layership just blew the **** ** is psychotic.
+Darius: What's his name? Lance? No, Lance was a football player. Harper. Harper. Not a great guy.
+Jordan: Not a great guy. It's funny because he's a protagonist, but he's literally the villain.
+Darius: Yeah. And I don't know if the maybe it was. I don't know if it was poor writing or good writing because he's the protagonist, but you never feel sorry for him. He's not a great guy. Like in Brakeman, it's like Walter White is terrible, but you empathize with him because.
+Jordan: You know why he's doing the things that he's doing. Yeah.
+Darius: I never felt an ounce of anything for Harper. He's God.
+Jordan: I like even I forgot to bring this point up like you just like are basically dogging out your girlfriend like she's like, oh, I love you. I could do this forever. And he's like, well. He was not good to anyone in this movie.
+Darius: I concur. Act 2, Bachelors and Betrayals. At the bachelor party, tensions boil over as secrets from the past resurface. Harper's anxiety grows as the contents of his book threaten to reveal a devastating truth to Lance. Sorry, I'm still ****** **. What you got for Act 2, man.
+Jordan: I so if you were in Harper situation and Nia Long, who's I guess your college would have been crushed or whatever, says like one night only. Let's get it on. You going?
+Darius: Yeah, for sure. Not even close. No, no, not even. I mean, he's not married to Sanaa's character, right?
+Jordan: Yeah, he wasn't.
+Darius: They weren't married. You got to charge that one to the game if Neil Lunkum calleth. Sorry.
+Jordan: Yeah, that's true.
+Darius: Some stuff. You just got to be like, take one person.
+Jordan: You just got to. Yeah, it's a once in a lifetime kind of, you know. What I will say is that what my thing that annoyed me with her character, though, was like, you could have at any point in time flown to Chicago or had him come to New York or like y'all could have y'all known each other for over a decade. We said this point. Like, what was the holdup?
+Darius: So context of the time, air travel was much more cost prohibitive in the 90s unless people just didn't do it as much. And these are supposed to be, I think we are watching this, thinking of them present day as like, you know, seasoned elder. These are kids in their early 20s at the time.
+Jordan: Yeah, it's just like 27, 28.
+Darius: Yeah, I mean, it doesn't, I don't know. Like it just, if you're not in the same city, I mean, I can count on one hand the number of times I've flown out to meet a woman or flown a woman to me. It's been less than five. And it doesn't strike me as outrageous that they couldn't make that work in the 90s when air travel was much more of a luxury thing. And they were young and broke in New York City and Chicago. So I don't know. I don't think that's, obviously you'd like it to line up a little better than that, but it doesn't strike me as out of bounds.
+Jordan: Yeah, that's true.
+Darius: Strippers at the crib. How do you feel about strippers at the crib?
+Jordan: Like at my crib or at somebody's crib?
+Darius: Have you ever had a house party where like strippers popped out?
+Jordan: Yeah, I've had a couple times. Not at my house.
+Darius: A couple times.
+Jordan: Yeah, a couple times. Yeah, not at my house, at other people's houses. It was a, it was a, when was a friend's bachelor party.
+Darius: Okay, all right.
+Jordan: And then, and then the other was after Friendsgiving.
+Darius: Dude, what is happening in this podcast? Red flag. We got a challenge. It's time out. I got to go to the repay booth. I need to see the what. Yeah, we did the end up with strippers at the crib.
+Jordan: I mean, I didn't plan it. I just was told about it and told to bring ones.
+Darius: So you didn't know ahead of time?
+Jordan: Yeah, I didn't know ahead of time.
+Darius: So y'all had a ***** Friendsgiving planned?
+Jordan: No, It was really like a postgame. So what happened was we had Friendsgiving and then all the casuals like left. And then it was like...
+Darius: Any parties. It's like it was a regular party. And then the people happened in the real party started in the real party.
+Jordan: So we talked about this on my birthday party where all my friends came on.
+Darius: I could not keep up with 17 different conversations.
+Jordan: That's true. That's true. Keeping the trains. It was. Yeah, we talked about it on that party that that was the people that we had the, you know, the party with and The guys, my homeboys, they knew some girls who worked in that industry and they had them come over and put up a pole and.
+Darius: Where'd the pole come from?
+Jordan: Did they bring the pole or did he have it? I can't remember. But when was installed in the dining room?
+Darius: So y'all just moved the turkey and the dressing and the collars out the way and just brought in the ***?
+Jordan: And we made it rain on them hoes.
+Darius: So y'all DoorDash strippers after the Friendsgiving. Okay. How long were the strippers there? Did you feed the strippers? Did they get a plate?
+Jordan: I think they did. Pretty sure they ate. Yeah, I'm pretty sure they ate. Yeah.
+Darius: Were they on the clock while they ate? Did you like, I know they charged per hour. Did you stop the clock while they ate?
+Jordan: That I do not know. I'm not gonna lie to you. I was probably faded at that point. So I can't tell you. There's a picture of me in my friend's phone with like money and I'm just like.
+Darius: You is too ***** for me, bro. I, Friendsgiving is for charades. Let's do a little Pictionary, little karaoke. Why are strippers after Friendsgiving? That's too ***** man.
+Jordan: I don't know. They, we gotta, I gotta ask the boys about that. I didn't, I didn't, you know, I just partook. I did not plan. But it was a guitar.
+Darius: Friendsgiving is supposed to be when the college friends get together and like share pictures of the kids. You got. Buffy the body, busting it wide open on a pole, a homemade pole. Not even going to the strip club. You door dashed the strippers.
+Jordan: Yeah, pretty much they did.
+Darius: Okay.
+Jordan: Yeah, it was a fun time. It was a great night. I didn't do the girls. It wasn't, you know, it was a little more.
+Darius: Do you have to pay a premium? I guess it's not Thanksgiving Day. It's Friendsgiving. So yeah, Friendsgiving.
+Jordan: Yeah. So the week before. Yeah, it was cool. It was fun. Our homegirls, they loved it too, because girls like it just as much as guys do. it was a good time.
+Darius: I'm judging everybody that was in attendance. That's trifling.
+Jordan: That's fair. That's trifling.
+Darius: Would you date a stripper?
+Jordan: Like if she was still doing it or like.
+Darius: Actively stripping. Like hey.
+Jordan: Actively.
+Darius: Heading out towards 10 o'clock in my stilettos.
+Jordan: Stiletto pumps in the club.
+Darius: Is that a dated reference? Is that not that what stripper is?
+Jordan: No, it's a song.
+Darius: I'm old.
+Jordan: No, I don't know if I would. I don't know what I have to think about that. I don't know. What about you?
+Darius: I have. It's a bit of a different proposition at 37 than at the time. I think I was like 25, 24.
+Jordan: Got you, got you.
+Darius: But it really was less weird than you think. It really was. No, yeah. It was. Yeah, I mean, I've dated a handful of bartenders in my day, and it's not terribly dissimilar. They just work 10 hours.
+Jordan: It's the same work schedule. It's the same work schedule.
+Darius: They just work 2 hours and you work.
+Jordan: Around and they hang out until 5 in the morning. So it's not really that much different, honestly.
+Darius: I mean, it wasn't like I was married to someone having children with her. We were just having a good time. But yeah, I have. It really wasn't that weird. It was quite normal, except for the IELTS.
+Jordan: Yeah, I was Good friends with a dancer, shipper, a few years back. We grew up together and we reconnected and she just happened to be, we didn't meet through her job. And it was super cool. Like she, we'd hang out, live night, I'm a night owl, whatever. She'd cook for me. It was fun. I could probably, I probably could. I probably could.
+Darius: What you got for Act 2?
+Jordan: Anything else? What was I going to say for act 2? Oh yeah, so the card game with all the guys.
+Darius: Yeah.
+Jordan: And I'm going to say it's always the worst thing, you know, dog and his girls out the most, always talking about some loyalty and God.
+Darius: Yeah, I mean, yeah, fair. I mean, I don't know. Like he's a star football player. They were in college. By then, by the time the movie came around, he had cleaned his act up. So I don't know.
+Jordan: Yeah. But I always love that conversation, though, where Terry Tower is kind of like goading Morris Chestnut, kind of like be like, what makes you think that you like that she's exempt from being desirable? Pretty much, you know. He was out of.
+Darius: Pocket for that, by the way. What are you, her spokesperson? You go to the bachelorette party then, why are you here? You know, like you're supposed to be part of my wedding crew. Yeah, I just felt that was a little weird. Like if you, he was moving like he was her little brother. And it's like, yeah, I don't know. Nothing he said was wrong, but it's just a.
+Jordan: Yeah, he was writing everything he said.
+Darius: Just a bizarre. Why is this? Why you bring this up here? It's bizarre.
+Jordan: So I think, honestly, I think he did that to make a point to Harper. I think he was basically saying like, I just insinuated that she might have ****** somebody else and he choked me up. You did it. You actually ****** her. So what do you think is gonna happen to you?
+Darius: Yeah, that's what I took from it is that he read the book and had put 2 + 2 together because he was always, you know, Terrence Howard's character in the movie is like the audience. He's like, you know, coming in to say what we're all thinking. And I think that's kind of how I took that scene is like, he's speaking for the audience through the character Like Harper, we read your book. What's your plan?
+Jordan: What is your plan?
+Darius: I love Darren's character in this movie.
+Jordan: Me too. That would have role would have been so fun to play.
+Darius: Yeah, he was he's even better in the second one. Yeah, which we've already reviewed, but nonetheless, good movie. Anything else for act 2? You stripper at the Friendsgiving skipping out on the tacos. Any other bombshells you want to add to this act? Let.
+Jordan: Me think. No.
+Darius: Act 3, walking on down the aisle. On the wedding day, the group faces the fallout of revelations. Friendships are tested as they decide if the bond they share is strong enough to overcome the truth. Movie got a little stupid in act three. Yes, it did. Got a little, that last 30 minutes got a little stupid. That's okay though. They didn't really land the plane, but that's okay.
+Jordan: They did not.
+Darius: Beautiful cast, sparked the trilogy.
+Jordan: Beautiful cast, beautiful gowns. Well, I think the problem with Act 3 is because they built the bulk of the story on a betrayal. And then third act is just like, we forgive it.
+Darius: It's not, that was my biggest gripe with Wakanda forever. It was like they built up this huge rivalry between the ocean people and Wakanda. And then they just decide not to be rivals anymore. And it's just like, okay.
+Jordan: Right, everybody go home, pack them up.
+Darius: The core tension of this movie is never resolved. He's like, build it up, they build it up, he finds out, he damn near kills them and they hold one after school speech and everything's okay.
+Jordan: Yeah. It's like, yeah, **** it. You come my mom. Who cares?
+Darius: It's just. Didn't really like that. It just it all got a little too neat at the end. It was like. It ended a lot like Game of Thrones, where it was like, I have all of these strands out there. How do I wrap them up as fast as possible? And I don't even care if it makes sense. Correct. How do we get out of here?
+Jordan: And they weren't even getting Star Wars.
+Darius: No, no, not at all. We did get a great posse cut out of this. Best man I can be. Genuine Tyrese, RL and someone else. Great little song. Oh **** okay.
+Jordan: Yeah, that's right. Forgot about that. Yeah, that's what the, yeah, it's just like, so even like when he told his girlfriend, like, yeah, I was gonna cheat on you, but don't leave me. And she's like, okay.
+Darius: It just got, it just, it was like, Very sick copy where you hear the Hallmark music in the background and they just have a deep talk and everyone just accepts the talk as the end of the conflict. It just, I just didn't, the act three, it got a little stupid.
+Jordan: And then even him proposing at the wedding, which is the techiest thing a human being could ever ******* do. It's like the day after you just, like you have a black eye from trying to **** another girl.
+Darius: Still got the black eye, you're at the wedding, all is well, and you're proposing at his wedding and everyone's happy. And then we do the electric slide.
+Jordan: The electric slide. Because why? Of course, of course. Right.
+Darius: Do you have anything else for act three? I got one question left.
+Jordan: Yeah, I got a couple of questions for you.
+Darius: What's up?
+Jordan: If you were in Lance's situation and he was to the point where he was going to cancel the wedding, is there anything that someone could have said to change your mind?
+Darius: This is the woman I have decided to marry. Right. That is, I would probably still go through with that in the sense that I'm much more logistical about marriage than romantic. You know, It's as much of A logistical and financial decision as it is a loved one. So I would probably go through with that. But Harper's out of there. We can't be friends no more. You know, like I made a decision to be, you know, to be with this woman for the rest of my life. And I made that decision. You know, I just, I could, I'd be fine with that. I just could not look her in the face ever again. And let alone be in the wedding. Like, I've always said, the sitcom thing where the ex-boyfriend shows up and goes, stops the wedding. Why aren't the groomsmen stomping him out? I never understand.
+Jordan: Yeah.
+Darius: And so, no, I could see myself, because in a way, her betrayal is less stinging because she knows me. She's known me a shorter period of time. And just like the best man in my wedding. And this is not even if it was before me, I could it'd be tough, but I could see my way t</t>
+  </si>
+  <si>
+    <t>Darius: So apparently some chain restaurant in Texas, I guess it's there. Hooters called Twin Peaks is closing and someone said the restaurant is a as a dying breed because there's too much social shame in like going to ogle scantily clad women while eating chicken wings. I agree. You do look like a loser at Hooters in 2026.
+Jordan: Yeah, you do. Hey everybody, welcome to the Out the Trunk Pod with Jordan and Darius. My name is Jordan. You can follow me at all socials, Jordy B Writing.
+Darius: And I'm Darius. That's Steve's. I love your area on all socials.
+Jordan: And today we're going to be reviewing Boomerang, classic comedy, came out in 1992, starring the goat, Eddie Murphy, Robin Givens, Halle Berry, another goat. David Alan Greer, Martin Lawrence, Grace Jones, Jeffrey Holder, Eartha Kitt, the original Catwoman, and Chris Rock before he got his teeth fixed. And pre-slap. This was John with this one on there.
+Darius: We got to add the OG.
+Jordan: Oh yeah, the legend John with this one RIP. He wasn't listening on there either. Wow, Boomerang Stars. It's about a man named Marcus Graham, who's a high-flying marketing executive and serial womanizer who meets his match in his new boss, Jacqueline Boyer. As he experiences life from the other side of the pursuit, Marcus must decide between superficial perfection and a genuine connection that challenges his shallow perspectives. I'm going to throw it to you for Act One.
+Darius: Act one, we're going to call the hunter becomes the prey. Marcus enjoys status as a legendary bachelor until a corporate merger introduces Jacqueline. He is instantly smitten, but finds himself struggling to navigate a relationship where he lacks control. First observation is a bunch of these older movies. I'm always surprised at how formal the dress used to be amongst upper middle class. Yeah, both at work and at home. I don't know about you, man. I have not worn a tie since COVID. Like these people were just like having dinner at home in a jacket and tie.
+Jordan: Yeah, they were fly as **** though.
+Darius: Yeah, they were. The fits were fly. I'm just like, man, everyone is just so dressed up for regular day-to-day stuff. So that always stands out to me. What else you get? What you got for act one?
+Jordan: Yeah, I haven't worn a tie since. The last wedding that I went to. Makes sense. But yeah, so first, my first observation in this movie, well, obviously, insane cast, like super loaded. I also, I want to give Eddie Murphy a shout out, not only just for being a legend, but like for being one of the, to me, a testament to like a really like generous actor or collaborator is if you see them work with like the same people over and over again. And if you notice, you always see like In his early movies before they all blew up, you always saw Martin and his ****. You saw Chris Rock in his ****. You saw Tracy Morgan in his ****. He was one of those guys who, if he was up, everybody around him was up too. He put everybody on. And I always really appreciated that about him.
+Darius: Yeah, I have it here in my notes. You know, were Martin and Gina background characters in every black movie before they got this show? Because Gina's the neighbor. And I was like, damn, Martin and Gina were in House Party. They were in, they were in a lot of stuff before they got the show.
+Jordan: They were.
+Darius: So, it's like going back, you think, Like these people who had these huge sitcoms just kind of started at the sitcom, but they almost always had work they put in before, because you don't just get a TV show with your name on it.
+Jordan: Yeah, you don't just get a show.
+Darius: But I was a kid, I wasn't watching Def Comedy Jam and following the comic circuit. So to me, Martin started with the show. And I was like, clearly though, he put in some groundwork there. But yeah, man, Eddie is notorious for keeping his, you know, putting his people on, man, his brother. Made a whole career out of being Eddie Murphy's brother. Yeah, RIP. Charlie Murphy, RIP.
+Jordan: Yeah, that's true. Also, like he got so many legends in this movie, man. Earth the Kitt as just like the crazy, crazy boss. Man.
+Darius: Also, I believe he got, I think this was his first like non-comedic role, even though I mean there's comics.
+Jordan: Yeah, I think so. I was going to say, yeah, I think so. Because this really wasn't a comedy. It's really more just like a romantic drama, basically. Yeah. And he's, I think, from my mind, he's one of the, like, compared to comedians, he's probably one of the greater dramatic actors ever, compared to his contemporaries. I personally think he should have won that Oscar for Dreamgirls, but that's just me. Yeah, I always love when he does a serious role because he doesn't do them quite often.
+Darius: Yeah, I mean, honestly, I look at life like a serious role. I know there was funny moments in it, but I wouldn't call life a comedy.
+Jordan: It's yeah, it's a really sad story.
+Darius: Yeah. And so no, I mean, he's it's funny because I'm a little bit after Eddie Murphy's like his, you know, his his generation is like my dad. And they would fear him. Like you talked to some old heads about Eddie Murphy and he is like, nobody, like, I can't even, there's no one in comedy today that we would even compare like the way they think today. Pretty much like they'll still like he'll drop some terrible Netflix movie and old heads will watch that **** because Eddie Murphy's in it. Like they just don't like that's all he still to this day moves units just because he Eddie Murphy and the movies aren't even good anymore.
+Jordan: Anybody who was in their 20s in the 80s or 90s, Eddie Murphy's like God to them. Like when we were kids, my dad, we hadn't seen it stand up, but my dad would do the ice cream song. We'd eat ice cream as kids. And then growing up later, I was like, oh, that's where that's from. Like, cause I'd heard it my whole life.
+Darius: He was the star of SNL. Yes. Like just straight up LeBron James level prodigy for comedy. Yes.
+Jordan: He's literally a child prodigy.
+Darius: To this day, people say he's the greatest SNL cast member and he left show 50. Alone ever. All right, Act 2, taste of his own medicine. As Marcus falls deeper for Jacqueline, her emotional unavailability mirrors his own past behavior. Meanwhile, his friendship with Angela deepens, offering a grounded contrast to the corporate power games. And let me just say, Halle Berry as the everyday woman is just ridiculous. Yes.
+Jordan: You know, that's my first note.
+Darius: You have to do the last of belief to come to that conclusion.
+Jordan: Two very unbelievable things in this movie. This is one of the other one I'll get to in third act, but this is one of them, like the fact that Halle Berry is like the sidekick friend that you pass over to get to the other girl.
+Darius: The everyday girl, you know, the plain Jane. They even like put her in his like baggy, unattractive clothing and she still looks gorgeous in them.
+Jordan: And that stupid, those stupid *** hats she was wearing. What the **** were those fez caps?
+Darius: That was their way of like making, like ugly her up.
+Jordan: Yeah. No, not at all. Yeah. Have you seen not another teen movie?
+Darius: I have not, no.
+Jordan: So it's in the same vein as like the scary movies where it makes fun of all the genre, the 2000s, late 90s movies, you know, like she's all that. And bring it on and all that stuff, whatever. And there's the character who's like the obviously super attractive girl who they just slap glasses and a ponytail on. And they're like, ew, she's ugly. Like, you know.
+Darius: There's Zoe Deschanel. Yeah, So did Lola Rashawn and Robin Gibbons look alike or am I tripping? Yes, Because I was just like, it took me like, I've seen.
+Jordan: I never realized it until this movie.
+Darius: But I was like, wait, he has three women?
+Jordan: Yeah, Layla Rashaan. Yeah, she's they do look a lot alike. I think Layla has a softer face than Robin. But yeah, they do look a lot alike for sure.
+Darius: Once I once I figured it out, it was easy to tell apart. But like in the beginning, I didn't realize he has three women. What you got for act two, man.
+Jordan: Yeah, she took my Hallie and Robin point. That was that was the first thing I wrote down. I literally wrote Hallie greater sign Robin. Yeah. And then I also wrote something they kind of established, obviously there's an attraction in chemistry there, but they're like, oh, we're just going to be coworkers and keep it cool, blah, blah, blah, whatever. And he asked her to dinner because they got to talk about like the work stuff. And she's like, oh, I don't know. And I just wanted to say, like, there's nothing more annoying than when you establish a set of boundaries with someone and they try to act like you can't handle the boundaries.
+Darius: Yeah.
+Jordan: Like, it's like, you know, you ever like, like the girl or whatever. And she's like, Oh, let's just be friends. Like, okay, cool. But then, like, whenever you hang out, she's like, Are you sure you can handle, like, hanging out with me?
+Darius: Yeah, I guess I have experienced that, though. I will say, I don't know. Yes, I have experienced that. Yeah, but like, I didn't know that that was I forget who made that joke, the workload over a meal. Someone else made that joke later on. I didn't know it was a callback to this movie. But to be said, to be fair, inviting a co-worker over for dinner to talk about work. Why can't I go to a restaurant? Like why are you making salmon with rosemary and butter and all that?
+Jordan: Well, I said that before they cut to the scene because I thought they were going out to dinner. I didn't realize he was going to have her at the crib. Yeah, that was a little crazy.
+Darius: Dope crib. Was this in New York City? It was in New York City.
+Jordan: By the way, I think New York City is like the best place to shoot rom-coms or romantic movies personally. Like I think like it's made for those kind of movies.
+Darius: Yeah, but it's just, you know, this is a common trope that we go back to. I am sure Marcus did very, very well for himself at this job as a marketing executive. That was a multi-million dollar apartment.
+Jordan: That was probably Eddie Murphy's house.
+Darius: It's like ******* Central Park, Manhattan ******* penthouse suite. That's a CEO's apartment. That is not. I'm sure he did.
+Jordan: He had a grand piano in there.
+Darius: Yeah, I mean, that was a multi-million dollar apartment for New York City in Manhattan. You know, he was that dude. I forgot about Earth the Kid too, man. He hit that old lady. You got to do what you got to do to get ahead, I guess.
+Jordan: You got to do what you got to do, bro. But the funny thing is, it was all for nothing because she had no control over the company. I would have been ******.
+Darius: I think he was okay with it. He didn't look too.
+Jordan: I personally never rest in peace to the legend. She never really did it for me. So she did.
+Darius: I wouldn't.
+Jordan: Yeah, I would have needed the promotion.
+Darius: She's been an old hag my whole life.
+Jordan: Yeah.
+Darius: Is she gone?
+Jordan: Yeah, she's been gone 20 years. Yeah.
+Darius: This might have been her last movie. No, RIP to the legend, but out of hit, I would have **** it. I'll sleep my way to the top if that's what it takes. Obviously it didn't work out that way for him, but yeah.
+Jordan: Yeah, I get you.
+Darius: But he ended up sleeping with Jacqueline and it made work awkward, which is another podcast trope of mine. What lesson did we learn today, kids?
+Jordan: Do not **** your co-workers.
+Darius: Don't **** your co-workers.
+Jordan: Don't **** your co-workers.
+Darius: Don't **** your co-workers.
+Jordan: Unless you're on a, unless you have gotten that 30 day notice, then it's all systems go.
+Darius: Fair. You just, it just, it's never going, well, this, it actually ended up working out fine, but You're just playing with fire and you need that job. You are. There are other women on earth that aren't directly tied to your employment. And so you should **** them. Right. Don't ****.
+Jordan: That won't **** ** your ability to pay your bills and provide a life for yourself.
+Darius: Yeah. **** the girl at the jail. **** the girl at the bar. I wouldn't do that either, but don't **** your co-workers.
+Jordan: So yeah, church, church is cool.
+Darius: **** the girl at church. That's also an option.
+Jordan: Open mic nights, you know what I'm saying?
+Darius: Open mic nights. It's not your coworkers. Anywhere but your coworkers.
+Jordan: Yeah, anywhere but there. Neighborhood's also a bad idea, I'd say, but you know, get how you live. I concur.
+Darius: What else you got, Frank, too, man.
+Jordan: One thing I do really miss. Yeah, man, one thing I really do miss about the 90s is the fashion. Like every, like all aspects of fashion were like top shelf, like the dress. The dress clothes were like awesome. Like I love the style of the suits. I like kind of like a little bit of the baggy with the tapered look, you know, they had like the, you know, the HBCU **** on in the gym. The sweatpants were all the sweatsuits were always like fly as **** you know, the windbreakers and ****. I just really miss the 90s, man. Like the 90s aesthetic. What a time to be alive.
+Darius: Yeah. I agree. I think that if I could pick any era to be born in the 90s the economy was booming music was good and um yeah we have more stuff these days but I don't think we're happier I thought it was yeah it might it just would have been better to be outside before social media you know hell yeah and I know it's a joke to like I think the 80s would have been but I just think it was better before yeah I.
+Jordan: Think the 80s would have been really fun time to to be young in um as well. I love the music, love the fashion and **** at that time too. But 90s, 90s, like the go to decade to me. I also like, obviously, his move is called Boomerang. He's basically getting his karma in, you know, the form of this woman who treats him how we treated women. But her leaving that 200 bucks on the nightstand was ******* crazy. Yeah, she really treated him like a hoe. She treated him like a hoe the whole movie.
+Darius: That would have been it for me. actually I think it was it for him at the movie uh but ******* man although 200 in the 90s that might that's probably like fo now.
+Jordan: That's like $1,000 uh that's a.
+Darius: Pair of J's you know so.
+Jordan: Uh yeah man that's a few in the 90s.
+Darius: But don't tip me like I'm a ******* gigolo I don't like *** **** yeah what you you got anything else rag too bad um.
+Jordan: I feel like this movie is a great response to that thing that people say where relationships work best when the men loves the woman more. And this movie kind of shows, no, it doesn't.
+Darius: I like people who say this or people who don't.
+Jordan: It works best when both people care equally.
+Darius: Yeah. I just, who is keeping track of these things, right? Like who is, who is, who's balancing the beam to see who likes who more? It just, that's not the way things, to me that's internet dating. People who don't actually leave the house and date people in real life, they just debate dating on the internet all day because no one does this. No one has these conversations. I never, who likes who more? You just talking to this new girl, do you like her more? Nobody does that. That's internet stuff. That's not the way dating works in the real world. Yeah. You know, so anything else for act two?
+Jordan: Oh yeah. So there's a scene where they're in the store and the white guys doing the whole stereotypical white person thing when you're in a nice store following them and **** like that and saying, you know, they don't take They don't do layaway and ****. My thing is, I always hate when they do these scenes in movies where it's like, just leave. Like, I hate when they, at least in this movie, they didn't do a thing where like, it's like, oh, I'm gonna show you, I'm gonna buy a bunch of things to show you that I have money, you know? It's like, just leave.
+Darius: Yeah, I'm gonna teach you a lesson about boosting your commission today. Right. I know, yeah. It's like, You know, what was it like when Jim Jim Jones was mad because Gucci was ignoring him and he, like, went viral. And I'm like, you know, leave like what? Yeah, it is. It was. It was like I think it was some bakery in Colorado. And they had a they were like a Christian bakery and. This is a major case that went all the way up to the Supreme Court. And they, this gay couple wanted to bake a cake for their wedding and they refused based off of religious. I agree with it. And they sued them. And I'm like, the case went all the way up to the Supreme Court. So it was adjudicated there where the bakery factory won, right? But the whole time I was like, so you're suing them. And if they lose, you win the right to buy a cake from them. What do you, there's no other bakery in Colorado? Because I'm not going to sue you for the right to do business with you.
+Jordan: No, I just want more self-respect for all people. It actually, I was thinking about this today for some reason, and it's like, you know, obviously there's civil rights moving and, you know, the lunch counter things and all the protests and stuff, that happened in 60s and 70s, 70s, 50s through 70s, basically. And it made me laugh because I remember someone tweeted it was viral. It was like, oh, that just gets some unseasoned food.
+Darius: Well, okay. It's a little bit different when the state sanctions, you know, like you can't go to any diners or sundown towns. But like, I promise you, it.
+Jordan: Did make you think though, like You wonder if they went in there and then finally got a meal. If they were like, man, this **** was trash.
+Darius: This doesn't taste like Lowry's. Everything I eat tastes like Lowry's and hot sauce.
+Jordan: This dude not tastes like my grandma's cookies.
+Darius: Which is just dousing Lowry's and lemon pepper seasoning and then frying the ******* life out of the fish.
+Jordan: They put no foot in this cookie.
+Darius: Yeah, you know, just. I'm the same way, like we go downtown, these places with dress codes, and if the bounce was tripping, I'm like, dude, I'm just, all right, have a good day. I'm not, I'm not gonna beg you to let me into this bar to buy your drinks. Like, you're not, you're overpriced watering out. I'm not, I'm not I'm not going to show up looking crazy. Show up wearing regular clothes. And if it's not good enough for your establishment, there's 30 other bars on the street. I'll just go to the other one.
+Jordan: Yeah.
+Darius: Oh, it's not. It's never that serious where I'm begging you to let me come in and buy your highest.
+Jordan: Yeah, correct. And the **** really don't ever be lit like that anyway.
+Darius: So no, I can't. I cannot remember the last time time I went downtown, especially, oh, yeah, I live here downtown Raleigh. And at the end of that, I was like, damn, that was dope. That was a great time. I came here. Let's get in Act 3 so we can, we got these connected in connection issues. Act 3, the soft landing. Professional and personal lives collide as Marcus finally realizes what truly matters. He must confront his insecurities and make a choice between his ego and a chance at authentic love with Halle Berry. Tough, tough, tough call.
+Jordan: What you got for that case. I have three basically where one of the pivotal moments obviously is where they have a Thanksgiving dinner.
+Darius: He's coordinate.
+Jordan: His place is coordinate and they got to they got to wash the dish because he's, you know, got all the dishes all over the place. They crash him and Halle Berry crash and they, you know, hook up, whatever. And then they basically just started dating, which to me was weird because, well, for one, she basically was the rebound to me, right? Like that's a fair assessment. And then also, my thing is like, how did he think that was going to go with his friend? Like he thought he was going to be like, oh, happy for you.
+Darius: Yeah. Cause his friend like dated her for real. Like they went out a few times.
+Jordan: Like they dated, dated. Yeah. It wasn't just he had a crush.
+Darius: Yeah. That's rough.
+Jordan: She did friends on him though. So that was his to me. That's on him to keep to. If you're going to keep spending time with someone like that, you're betraying yourself. So for me, I feel like in that situation, all three of them were in the wrong in some way, shape or form. No, but I did feel like they kind of I did feel like they didn't dirty, though.
+Darius: Marcus was tripping. He could have. He could have, especially someone like him. He could have found another girl.
+Jordan: Yeah.
+Darius: Yeah. And then he went to his friend and had to tell him, like, I get it. And now I'm with I'm with David Alegura's character on this one. That was now. But yeah, me too. I don't know. Like, it's tough, though, because they did love each other. And if I'm following the logic of the movie. Yeah, the first two people, David Alan Greer and Halle Berry, never really date. Like, there's no. She was never dating him. He was dating her. But it was very correct. Friendly esque.
+Jordan: Yeah, she was. He was in the friends for sure.
+Darius: But she knew what she was doing, too. And so correct. Real life is complicated, man. I don't know if there's, you know, clear cut good guys and bad guys on this one.
+Jordan: Yeah. Well, that was my thing, too, because it was like, you know, she he then, you know, finally gets this **** together, back together after crashing out. And Robin sees he's got a **** together. So now she wants to **** with him again because she wants to see if she can still get access to him, which he grants. So he cheats. And then Halle Berry's mad at him. And I'm like, Whoa. You knew you was the rebound. You knew he really wanted her the whole time. He's been ignoring you this whole movie. He only ****** you because she was there and he was like sad. You know, I don't like for me, I'm very big on like, if you knew what this was in the beginning or if you knew who I was when we met and we have a certain arrangement, why are you acting like you don't know what the arrangement is?
+Darius: Well, so There's what you say and there's your behavior, right? And the things people do are more revealing than the things they say. And he can set up these arrangements and that's great. But, you know, you slept with that woman, right? And you knew how she felt about you. And, you know, it's easy to say, well, I never said I was your boyfriend, but like, I don't know, you were behaving like one. And so, you know, it's it's tough. It's That's a tough, I mean, I said, man, there's no dating is complicated.
+Jordan: There's no black and white in this movie.
+Darius: Yeah, dating is complicated and it was interesting to watch them navigate the intricacies and complications there that come with that. So is this movie good?
+Jordan: I think the second-half of the movie is the best part of the movie.
+Darius: Okay. Is that a yes?
+Jordan: Like I say, I'd say it's a good movie. It's not, it's not great. I think it's got a lot of the 90s stars, so I can't tell it quite if it aged well or not. I don't think the comedy aged great. I'd say you could do away with the first 20 minutes of the movie.
+Darius: Yeah.
+Jordan: But yeah, I think like, because some movies they start out strong and they just run out of gas completely yeah to me the test I'd rather I'd rather take a movie that ends well that has a strong finish then that has a strong beginning so I'd say that about this movie I will say though I the ending to me there's no real resolution like he just kind of brings the kids to her office and is like I love you and she's like okay cool let's get back together and I'm like well she's gonna know effectively cheated going to ignore the fact that you have to do it, the fact that his best friend had feelings for you. Like, I don't know. That's my only issue with the movie, really.
+Darius: Well, it was at a two hour run time, so they probably just clipped it there. I mean, I get it was fine. The ending was fine. I just. Yeah, you could tell Eddie Murphy had his fingerprints all over the script because, like, Marcus, like, I'm kind of I'm told he's a ladies man, but I'm not really shown it in any way.
+Jordan: Correct.
+Darius: He just kind of. There's like no beginning to the movie. Yeah, It's cool. I don't know. Like I've seen it before, but I've rewatched it for the pod. And it's just like, while I was rewatching it for the pod, I'm like, do I like this movie? Or do I just think that people in the movie are I'm familiar with the character, the actors and actresses in the movie, but do I like it?
+Jordan: Yeah. So, okay, interesting. So for me, I think if I were to like things that would fix the movie, I would fix the first act or rewrite the first act. Grace Jones character.
+Darius: Could do without that.
+Jordan: Why? And I think it's one of those things where, when certain actors want to, be viewed a certain way, so they take a drastic, if the comedy guy goes and does a movie where they play a serial killer, or, the drama guy goes and does some stupid movie to try to prove that they have a light-hearted side kind of thing.
+Darius: Joseph Gordon Levitt did that terrible movie with Scarlett Johansson, or he was like.
+Jordan: Yeah, Don John, yeah, he was like a guido or whatever.
+Darius: Yeah, he was like the director. It was really bad.
+Jordan: And he was on his way up. He had just an inception in the five days of summer. He really ruined his career with that movie. I just think I love Looper. That's my ****.
+Darius: He's just a supporting actor. You know, everybody can't be a lead. And he's a really good supporting actor. And that's right.
+Jordan: He's a really good big, big, big guy.
+Darius: You know, settle into that. But no, I mean, I just think this movie is cool. I just watched it and I'm just like, if the audience is listening, I really have a lot to add to the because it's very boilerplate.
+Jordan: Yeah.
+Darius: And it's just hire a bunch well they weren't famous at the time but hire a bunch of talented people give them a pretty bland script script of a of a playboy who meets his match and then falls with the everyday girl um I just find the most attractive people you can find and put them in those roles and correct you know I just if you yeah I I just thought it was cool it was I you know.
+Jordan: Yeah I think honestly I think the problem is Eddie Murphy I'm sure he did great with ladies. One, you're funny and two, you're movie star like, but I think he wanted to be seen as like a ladies man. And that's kind of what the whole point of this movie was. You know what I mean? And it just wasn't, he's just, I don't want to say he's not believable as a ladies man, but he's not believable as a, you know, like the James Bond womanizer type. You know what I mean?
+Darius: Yeah, I can see that. I mean, he hit Whitney Houston though. So I mean, he was somebody's like, man.
+Jordan: He did.
+Darius: And I did not know that. Whitney Houston's former person, former assistant Robin, I think.
+Jordan: Yeah, Robin. Yeah.
+Darius: Wrote a book about their lives together and revealed that Eddie Murphy, like, obviously they slept together. And then he like stood her up later or something like that in the book. I read that like 5 or 6 years ago. So.
+Jordan: That's crazy.
+Darius: Yeah. So he was outside in the 80s?
+Jordan: No, he was. There's that picture of him eating steak off a bottle's back in Paris.
+Darius: No one's going to ever ask him what he was doing, giving that lady a ride home that night.
+Jordan: Okay, we got to talk about that. Because in this movie, there's a scene where they're talking about they saw like a There was like a call, a phone text line with it. And I was like, I didn't know the timing of the incident. Let me Google this real quick because I got to know. Yeah, it happened in 97. So this is before that. Yeah. Okay. Because I was like, it's a little too on the nose. No, no.
+Darius: I mean, that shows his power, though, because no one ever asked about it again. He was giving her a ride home. He saw on the side of the road and he was being a good Samaritan. That's a story he's sticking to. No one has any more questions. That's it. We're just going to go with that one. He was like, hey, you need a ride home. It's like, well, you wouldn't give her a ride home.
+Jordan: So talk about talk about beating the allegations. Yeah. You know, what a world.
+Darius: Eddie Murphy, one of the most famous men on earth, is just giving random prostitutes ride homes.
+Jordan: Random hookers a ride home.
+Darius: We're not going to say what kind of prostitute, but you people got Google.
+Jordan: Yeah, I got the internet. Yeah, I got the internet.
+Darius: It's even more scandalous if you Do a little bit more Internet sleuthing.
+Jordan: Oh, yeah. I'm about to do a bunch of reading on this. The second I close this.
+Darius: You won't find much info. It's just like got an accident. Lady was in the car. Yeah, he said he was giving a ride home. Full stop. So anyway, what do you write this thing?
+Jordan: Well, actually, I got one last question for you real quick. Sure. Shake. Hear me.
+Darius: Yeah.
+Jordan: Okay. I was going to I want to ask you, do you think he actually ever had feelings for Robin Givens character or was he just was he just intrigued by the power dynamic because he for once was not in control?
+Darius: The latter for sure.
+Jordan: Yeah.
+Darius: When you for someone like him, it's always been easy. You never lose your your thirst for the chase. And she gave him that chase. And then he got in and it wasn't what he wanted. And he found Hallie. And, you know, this is all happening in 2 hours. So it was rapid fire. But, you know, he aged out of wanting the chase. But no, I mean, he just he loved the chase. He didn't love Robin Gibbons character. Right. So that would be my opinion. How about you?
+Jordan: Yeah, I think so, too. I think that that's what I think that's one thing that did make the the love story a bit tainted, not tainted, just made it a little it took away from the what it could have been in terms of the love story, I guess. Because it's like you didn't have a difficult choice. It was like, oh, this girl, you know, who don't like she doesn't like you are the girl who actually gives a **** about you. It's not a hard decision. And they're both stunning. So it wasn't like it was, you know, some homely girl who was just always there the whole time, that you friend zoned. It's Halle Berry. So it's not there's no loss either way.
+Darius: Yeah. Do you think Halle Berry and Eddie Murphy's character lived happily ever after?
+Jordan: Absolu</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Alpha Trunk Pod with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Deez. I love the area on all socials.
+Jordan: And today we're going to be reviewing Brown Sugar for our movie review segment. This movie came out in 2002 starring Tay Diggs, Sanaa Lathan, Mos Def, Queen Latifah, Nicole Ari Parker, and Boris Kojo. Brown Sugar is about Dre and Sydney who've been best friends since childhood, bonded by their mutual love for hip-hop. As Dre navigates a corporate music career and Sydney edits a major magazine, they both struggle to realize that their perfect match might be the person standing right beside them. Shocking. So I'm gonna toss it to you for act one.
+Darius: Act one, the roots of rhythm. Longtime friends, Dre and Sidney navigate their successful careers in the music industry. As Dre prepares for his wedding, they reflect on the day they both fell in love with hip hop. Let me just say there was, I counted it when it ended. There were 6 minutes of opening credits and that's a little long. The whole prologue, we had the credits running and you know, maybe tighten that up a little bit.
+Jordan: That's funny.
+Darius: That was like my first thing. I was like, damn, they're still showing people.
+Jordan: No, it wasn't. It was pretty long. Well, you know what's crazy? Well, I watch a lot of old movies and those used to have like 5th, those opening credits used to be like 15, 20 minutes. So this, yeah, it's a little bit of call to old Hollywood. Also, this is actually written and co-written and directed by the same guy who did the wood.
+Darius: Okay. They're similar. One West Coast, one East Coast, similar veins though.
+Jordan: Yeah, kind of similar vibes.
+Darius: Yeah. Boy meets girl, they pretend they're friends. They last a lifetime.
+Jordan: Right. I want to know how the hell he got all those cameos in this movie. Like all the legendary rappers and **** in there. Like when he, when I, Dougie Fresh beatboxing, Rick, Rick, Slick Rick freestyling and ****. Be Daddy Kane, all the rappers talking in the intro. I thought that was pretty dope.
+Darius: Tyler Kwali, Fabulous, had a cameo. Benny Siegel had a cameo. You know, this is, and I won't get on too much of A tangent. Before rap just became about getting a bag, there was much more of a collaborative nature to it. And so somebody hits up Big Daddy Kate and he's like, we're filming this movie and the topic is when did you fell in love with hip hop? That is enough for him because he just loves the art where if you called up, insert, You know, if you called a future with that, he'd be like, my fee is 70,000 and you would just, you just would get it. You know, I'm not trying to tell someone not to charge a fee. The bag of the game is the game. But like when you into when you in the studio with the attorneys and you write now legal paperwork, some of the art gets kind of shoved to the side. So right. When rap is just a hustle, we lose a little bit of the culture in that. And so I don't know how that, how we got there from that, but I think that's kind of watching the movie and you see, like, I don't think, you see what the budget wasn't there to pay these people for this. I just did it without the love and you just don't see that too much more in the game these days.
+Jordan: So yeah, that's true. And also like just black artists collaborating across media forms, you know, like a lot of people don't know like Spike Lee had a hard time getting Malcolm X made. He was running out of money. And so he just hit up everybody that he knew. You know, Michael Jordan didn't, I think, didn't tell probably winning. You know, he, like a lot of people helped get that movie made, you know. We don't want to see a lot of that anymore across art forms. But yeah, so I want to start out by saying, so now Lathan is a generational beauty. And I just love watching her in anything. She has such, like her range is incredible. I feel like it's one of the most underrated parts about her career, because she can play like the adorable girl next door and then also be like the heartless ***** you know what I mean? In like the family that prays, you know what I'm saying? She's incredible and I just love watching her. She's magnetic on screen.
+Darius: I concur, actually. For Valentine's Day, the movie theater I go to is running Love and Basketball tomorrow.
+Jordan: Oh yeah, I saw that, yeah.
+Darius: Four sessions, two before I get off of work. So might check her out. I have not seen, I mean, I've seen the movie, but I've never seen it on a big screen. So anytime they try to throw back a movie on the big screen.
+Jordan: Yeah, I **** with that.
+Darius: **** with that heavy. So shout out to Na Lathan, talented actress, beautiful woman. You said she could play the girl next door. Only in Hollywood is the woman that beautiful, the everyday girl.
+Jordan: Well, that's what I'm saying. Yeah, exactly. Like, in love and basketball, she's like the. The ugly chick that was like, that was just there the whole time. And I'm like, Yeah.
+Darius: Okay. To be fair, he didn't marry Tyra Banks in that movie, so.
+Jordan: Oh, yeah, that's true.
+Darius: You know, he was. He was doing okay for himself. And I think it wasn't a Gabriel. You took the prom in that movie. We own a whole different movie. Yeah. Yeah.
+Jordan: Yeah. Yeah.
+Darius: Yeah. On a hot dog is disgusting.
+Jordan: That is. That is. That's a war crime.
+Darius: I like mayo, but I'm not going to put it on a hot dog.
+Jordan: That's maybe that's like some like LA ****. I don't know.
+Darius: So bachelorette party. And listen, you know.
+Jordan: Okay, we got to talk about that. Yeah, I thought the same thing.
+Darius: I have a lot of female friends.
+Jordan: Yeah.
+Darius: Let me just say, if we're super tight and you end up at my wife's bachelorette party, which is a little odd, don't be answering to get to know him questions fast.
+Jordan: Yeah, shut the **** **. Yeah, shut the **** **. Don't answer the questions at all.
+Darius: You're making the block hot, man.
+Jordan: Yeah, bro. I literally, I wrote that down. I wrote bridal shower game because while she was supposed to throw the throw the answers, I'd have been like blue to everything.
+Darius: How about don't attend? Can we do that?
+Jordan: Well, that actually too, because she kind of walked into the wolves den on that one.
+Darius: That was, that was weird, man. And she was lighting them answers up. McKellen 25, this song, that song.
+Jordan: And it wasn't even that she just answered like the baseline level. She gave such detailed answers. It was like, you just told all her friends you were in love with the state. What is wrong with you?
+Darius: Yeah, pretty much. So I guess that answers my question. Was she being intentionally messy? Clearly.
+Jordan: She was stupid for sure. I wouldn't say intentionally messy because I don't think she knew what she, how she was coming across.
+Darius: How old were these people in this movie?
+Jordan: I think like late 20s.
+Darius: It's always hard for me to contextualize because they were adults when the movie came out and I wasn't. So they always just seemed like adults, like brothers than me. But they very well could have been playing characters in their mid to late 20s. So what else you got, Frank?
+Jordan: Yeah, so the hookup, not hookup, well, they just kind of may not, whatever, the little hookup they had before the wedding, the night before the wedding. I thought the only thing I wish that they had not done in that scene was they should, I feel like it would have been a little more potent if they had him like be kind of faded, because then you would kind of be like, oh, it was like a drunk slip up bachelor party night, like, you know, but he went over there in the daytime, stone cold sober.
+Darius: He shot his shot. That was a carnal desire that he just had to, I don't think there was all that wrong with it. Like they accidentally kissed and their ******* fell out. And sometimes that happens the day before your wedding. It's not people take it to be so serious. Like, man, it ain't that deep. Sometimes you just the moment catches you and you accidentally kiss. And her ******* went out for like 2 seconds, and then he left. And so that way we could charge to the game. I think so.
+Jordan: Yeah. And he wasn't married at the time.
+Darius: You could stay married tomorrow, but I don't know. I just. I wouldn't invite.
+Jordan: No, for sure. I would never. Yeah. It's funny. It's just this movie is like a testament to the. acting chops and just like the charisma of Sanaa and Tay Diggs because they both have played like super problematic people in movies and we never hate their characters.
+Darius: Oh, I don't, what was problematic about that.
+Jordan: Cheating before the night before a wedding.
+Darius: They didn't cheat. They kissed for a couple seconds and her ***** fell out. They stopped.
+Jordan: Okay, so do you, okay, do you define cheating as doing something that you would not do in front of your spouse or significant other?
+Darius: I understand why someone else would define it that way. I just prefer to live in a little bit of gray.
+Jordan: And so because he didn't put it in.
+Darius: No, it's just he got caught up in the moment. The kiss was not even 10 seconds long. And he left. I'm going to go ahead. That's a that's not a flag. That's a personal foul. You get two shots. OK, that's not we not flager foul, not a one or two, no ejection, little personal foul, ball out the side.
+Jordan: He does it. So the fact that he was in love with her, that doesn't make it worse.
+Darius: I mean, that's a variable the bride doesn't have. So right. I'm just saying. Sometimes.
+Jordan: No. Yeah. I mean, it's happened.
+Darius: Cooler heads eventually prevailed. Yeah, right.
+Jordan: That's true.
+Darius: They didn't spend the night together. They snapped out of it. He even touched a *****. The ***** came out and he was like, this is a bad idea. And he left. And so cooler heads prevailed. No harm, no foul ball outside. I'm cool with that. That's not cheating. It's not exemplary behavior, but I wouldn't call it cheating.
+Jordan: Okay. Interesting. Okay. So, okay, so what's your definition of cheating then?
+Darius: My definition is fluid. Oh, okay.
+Jordan: Is it non-binary too?
+Darius: My definition is on the spectrum of realities, if you will. Sometimes, depending on the context, Some acts are unforgivable, but in a different context, those acts can be. It just depends. Because the night before his wedding, that's a very high stress time. He went and saw his female friend. He was probably on like a like just like sometimes you just things are just moving fast and they kissed and they stopped kissing.
+Jordan: Yeah.
+Darius: Charge that to the game. going to ask you the most cliche question that everyone who watches the movie asks anyone who's watched the movie. When did you fall in love with hip hop?
+Jordan: The day I was born. No, I'm kidding. Probably, I guess the most clear, like, memory I have. I mean, obviously a group listen to my life, but I'd say hearing the college drop out for the first time.
+Darius: Okay.
+Jordan: I was 11. 11 years old, summer before spring of 6th grade, summer before 7th grade. And I think the first song I heard was either School Spirit or a New Workout Plan. And I just thought they were like the illest songs ever. They were like fun and catchy songs. Love the Beat, the Auto-Tune was I just always thought that was really cool, really cool art form to me. So with the samples of, at the end, I always loved that. And of course, the skits were incredible. We broke, broke, broke, broke. We ain't got it. Yes, that's probably, that's probably what I've, that was the first rap out my listen to cover to cover. So I would say that was probably the first time I fell in love with hip hop.
+Darius: For me. So I remember driving in my dad's car. At the time, he was just dating my mom. The guy I call my dad is not like my biological father, but for all intents and purposes, he's my father. And he was listening to eight ball and MJGs on the outside looking in. And I just thought there's a song called Players Night Out and lay it down and I just remember in the most innocent voice asking him if I could say the N word. And he was like, yeah, but don't you dare tell your mom. And we just drove around listening to that and I could rap along and say the N word. And I was like, this is the coolest thing I've ever experienced in my life. And so that was the day where, and then I just, from that point on, it was like, oh, I listened to it for ******* 10 years. I had to be like 7 or 8 years old. But A-Ball and MJG's album on the outside looking in. We listened to it on tape. And I think the first full album I listened to front to back was Tupac's All Eyes on Me. I would have to fact check that, but that sounds about right. So, yeah. So that's my answer.
+Jordan: That's a good one.
+Darius: Anything else for act one?
+Jordan: That's all I got for act one.
+Darius: Gonna hit act 2, scratching the surface. Dre grows disillusioned with his commercialized job and starts an independent label. Meanwhile, his marriage faces strain as he and Sidney realize their deep connection might transcend mere friendship and music. The song The Hoe is Mine, if we throw a Boss Mandelo feature on that, we got a hit. I'm just saying my man D-Lo could save that. I was like, I was listening to it and I was like, I could throw D-Lo on this right now. That's funny. And we could revive this and that would be the hottest song in 2027. D-Lo for the Super Bowl, 2027. Boss man D-Lo is doing the Super Bowl next year.
+Jordan: I think America would have an even bigger fit than they did in the last two years.
+Darius: I think his catalog is unimpeachable. 2024 to present day, no one's had a better run. Get that man a Super Bowl.
+Jordan: No, I love his music. I love his music. Birdie with the left hand. Judas Random.
+Darius: I just let Louie V. I'm cleaning this dove, baby. Hop out. I'm flyer than a dove, baby. See, he said cleaner than a dove soap flyer than a dove. The bird. That nice. I listen to him every single day. There are people. that I have actually stopped, asked me to stop sending them songs.
+Jordan: I believe it. I believe it.
+Darius: And then I cycle in new people who I send them songs and I could tell when they're getting sick of it. And then I just he's the best out right now.
+Jordan: So he's he's he's he's cool. I like him.
+Darius: What you got for act two?
+Jordan: Act two. So okay, so he's he gets married. They go through with the wedding. The woman didn't for a few months. I think it's brought Shaka wedding, basically. In that situation, would you have stood up and said, I refuse?
+Darius: So that goes back to my question. Well, no, I wouldn't have played. Like I said, some **** just got charged to the game. You didn't do anything, whatever. My question is, do wedding still do the who objects thing and why?
+Jordan: Yeah, some weddings do. It's optional from what I hear. I hear you can take it out if you want to. But I've heard it at weddings. I've heard it and I've not heard it at weddings.
+Darius: The only two people who can object are the people getting married. Who the **** cares when somebody in the crowd cares? I don't get it.
+Jordan: And I've never seen in real life anyone be like, oh yeah, don't.
+Darius: You will get dragged out. Don't do it. Right.
+Jordan: What?
+Darius: I don't. I've never understood it because I'm like, the only two people whose objections matter are the people getting married.
+Jordan: And groom.
+Darius: So like, it's my drunk uncle 30 rows deep is like, I don't think this should happen. **** are you?
+Jordan: Yeah. I want to. I wonder if it's ever happened in real life. I mean, I'm sure it has been. I wonder if there's footage of it?
+Darius: There's YouTube videos of like. you have to whiff through what's real and what's fake. But there's one that's really good where clearly like the groom's mistress pops up at the wedding. And she like, she interrupts the vows and she's just like, so this is what you left my house for this morning? Oh my God. Jesus. Damn. Yikes. You could see that it couldn't have been fake because you could see it in the groom's faces because they knew who that girl was. No, I'm sorry. You could see in the groom's men's faces.
+Jordan: Groom's men's faces.
+Darius: Because like, come on, man, they know who that girl is. They knew exactly who she was. They was like, oh.
+Jordan: Is crazy.
+Darius: No, that's funny.
+Jordan: I was actually exactly a couple months back and somebody commented about like what's the crazy **** you've seen at weddings and there's threads of like thousands of comments of people being like yeah I've worked at wedding venues and **** like that all you know for a long time and they go they all so many people were like yeah I can't tell you how many times I've seen the bride sneak off with the the best man or the groom sneak off with the maid of honor and **** whatever, and then just go back to the wedding and nothing happened. I'm like, that's ******* crazy. I got a little bit of a tricky question here for you. Have you heard that theory that people tend to love, people actually love the side piece more than they love the main, like significant other?
+Darius: I don't know if it's a theory, but I'm certainly Heard of heard of it. Yes, I've heard of it.
+Jordan: Do you think it's real?
+Darius: I mean, it just depends. A marriage is first and foremost a legal arrangement, right? And it's very, very, very recent in human evolution that people married for love, right? I mean, rewatching Game of Thrones, those are all political marriages, right? Correct. And so it doesn't strike me that millions, millions of years of evolution for marriage being one thing, still there's still some remnants of it. Like a lot of people, a lot of men and women marry for practical reasons and get there and find their passionate passion outside of the home. I remember reading Esther Perel's book on affairs. She's this renowned relationship therapist or whatever. And she hosts a podcast and she wrote a book about affairs. I think it's literally called The State of Affairs. And she has a section about the other women. And she tells a story about this woman who was a side piece, if you will, for this dude for like 40 years and like he died. And like the family didn't know about her. And like she's talking to her daughter and she's just like, you know, my mom's a widow who can't be a widow. You know, she's like, that was her life partner for 40 years, he just was married to someone else and like he's gone and she could, there's no closure. She can't go to the funeral. She doesn't get any spousal benefits. And, you know, but she was like that they were in love. That man loved my mom. But, you know, and so that was honestly one of the more profound chapters of the book was when she went into discussing the side pieces, if you will. So no, I mean, Nothing is universal, but it doesn't strike me as unusual that the affair would be more passionate than the logistics of day-to-day life, But again, also, it's like the Bridges of Madison County, another famous book about an affair. Everybody fun for three days, you know, Clint Eastwood shows up on your doorstep and you guys ****** for three days and then he leaves and you yearn for that your whole life. And it's like, well, you never had to do his laundry. Right. you never had to fix his lunch. You never had. You never seen him on a bad day. Right. he just throwed into town. he didn't age. He didn't. He never got a beer gun on you. He just this cowboy throws into town and sleep with him for three days. And then he goes off to the fair and you never see him again. But life is complicated. And that goes back to the act one section. What's an affair? Depends on the context. I don't mean that to be flippant. I was joking earlier, but I'm not one who deals with a lot of black and whites. And so it's entirely possible, in my opinion, to love your side piece more than your wife. And I don't think that automatically makes you a terrible person. It just depends on the context of whatever was going on. But I don't know if it's a theory as much as it's Just kind of how the things shake sometimes. So yeah.
+Jordan: Interesting.
+Darius: How about you?
+Jordan: Believe in it? More so I would say, do I think they love them more in general? I'd probably say no. I think when I do, I really do believe different people do bring out different things in you and different aspects of your personality and your mind and things of that nature. I also believe you can love more than one person at a time. Not saying you should, but I do believe it's possible. And I do believe it happens more than people want to say out loud. Yeah, I mean, I think. I mean, okay, we've all dated casually and dated multiple people at one time. And maybe they were someone that you dated and you, the bulk of the relationship was you pouring into them. And then maybe you were dating someone else and they were pouring into you. And you kind of felt like maybe you needed that balance or, you know, you needed one to be able to do the other sort of thing. I've, you know, been in, I've been in that situation before. So I think it is, I mean, all this love **** is complicated. Like, there's no rules in ****. It is, it is, it is very new. It is all very gray. And even to your point about, you know, Marrying for Love is, I don't think people realize how new that of a concept that is.
+Darius: It's not 50 years old. It's not 50 years old.
+Jordan: I was going to say, yeah, women were not able to have their own bank accounts until 1975. So, and that doesn't mean that year they were financially stable. So they still were, they still were having to be with people that maybe they didn't want to be with or maybe they couldn't get away from, So, yes, I mean, that **** is tricky, dog. I mean, there's no real rules. I mean, there's no rules in this. I mean, there's laws, but there's no real rules in this ****. There's just kind of what you feel like you can do based on whatever options you have available.
+Darius: Yeah, I mean, a lot of it in seldom is that, you know, a lot of men were willing to, were able to leverage financial stability in the dating marketplace in a way that's no longer as broad as it used to be. Now, obviously, it's still bold. No one wants to date someone who's completely out, you know, whatever. But it used to be you head down to the factory, get a job for life. And that basically came with the wife because they needed someone to work, you know, you know, and now you have to be likable in some way, shape or form. But, you know, talking about those grays, man, that's why when it comes to affairs and whether or not people leave when they find out, I'm always like, man, everybody's a hardliner when it's in theory, but when in practice and you built a life with this person and y'all got kids and a mortgage and y'all have shared friend groups and it's easy to say you blow all that up until you actually have to blow all that up. And everybody talks a big game. I don't judge people whatever they do. If you stay with the person that had an affair, if you leave, that's on your prerogative. But what I won't say is what I would do in your shoes because it's harder to untangle a life than you think. about how many married couples that are just basically one person now. And imagine having to disentangle the friend group alone to let's say nothing of, to go from, I believe it was Lil Rel, Lil Rel Howery, the comedian. He was like the hardest part of the divorce was just not having my kids in my home. I used to just, they were just there, was noise, there were my kids. And now it's like, when I miss my kids, I just can't go see them in the living room. I have to make plans to go pick them up or whatever. It's like, I can see why someone would look at that and then look at the disentangling of the finances and the mortgages and the friend groups. Let's have some, let's have some couples therapy. Let's see if we can make this work.
+Jordan: You know, that's true. Cause I mean, think about it.
+Darius: Like I see why someone would use that, you know?
+Jordan: Like in our friend group, there was, you know, some intermingling and there were breakups and that changed the nature of the friend group. Like it got complicated, got hard to navigate.
+Darius: So I don't know. That was just church and state.
+Jordan: Yeah. And that was just people dating for a few months. Like it was not, you know what I'm saying? These weren't marriages. These weren't lifelong bonds. So I mean, I can't imagine having to sever off half of your social circle. people forget when you get married again, your spouse's family becomes your family. So you do have those relationships with your wife's siblings and cousins and parents and so on and so forth. That **** is tricky. And going from that rope point you made is very important because going from seeing a family member every day or every holiday or whenever you want to see them to not is a big transition that people, you're not used to it. There's no training wheels or manual for that kind of situation. I remember, you know, my parents are divorced, you know, they've only been divorced for like 2, three years, something like that. And that first Christmas, When I was an adult, and that first Christmas without my dad, that **** was devastating. You know what I'm saying? I couldn't imagine that as a kid, you know what I'm saying? Or, you know, as a parent having to like walk my children through that, you know?
+Darius: Life **** is hard, man. And I could see why someone, male or woman or whatever, Looks at those two options and says, I'd rather just stay. I'd rather figure out what it was that led to this. And if they're willing to work on it and they're willing to be better, that's the best of two ****** options, you know? And sometimes a lot of people don't get choices. You don't get two choices. You get two ******. You don't get good choices. You got to pick the best of two ****** ones.
+Jordan: And you do have to work at that ****. Like it's not. every day is not going to feel like a rom-com. You know what I'm saying? They're going to there are going to be years where most of the year sucks and they're going to be years where most of the year is great. Like you got to ride it all out to see, you know, to actually know what you have in your person anyway. You know, there's that too. Like I remember there's an interview I watched with Will Smith and Jada and they were talking about their relationship and they were saying around 15 years into that relationship, they're really struggling and they wouldn't talk to like, you know who Ruby Diaz, the older black actor? She passed away, but You've probably seen her stuff. Well, she talked, they wouldn't talk to like a significantly older person and ask them for like marriage advice. And she was like, how long have you been together? And they were like, 15 years. And she was like, oh, that's nothing. You don't even know each other yet. Like, and that's a crazy amount of perspective to have on a lifelong commitment.
+Darius: I believe it was Ice-T that was like, he's been married like 20 something years and people come up to him and ask him for advice. He's like, I don't even know how to be married to my wife. I don't know how to be married to yours. Yes, exactly. I don't know. I can't give you no advice. I don't know to you. No, and then you'd be surprised, man. How many couples navigate that issue and you never know about it, you know? Every couple isn't for putting all their drama in different circles. So Real life is complicated and it's easy, very, very easy to say what you would or wouldn't do when you're, when it's not, when none of these decisions they know your part for you. Right. Yeah. So let's get into act three, man. Finding the perfect beat. Career shifts and personal revelations for a stray at Sydney to confront their true feelings. They must decide if they are willing to risk their lifelong friendship for a chance at love. And the third act is they fall in love, the end. Like, really, really goes on here. What you got for three?
+Jordan: Well, one of my favorite scenes from the movie is the where he finds out about the affair and they go to the restaurant.
+Darius: Yeah.
+Jordan: And he meets Richard Lawson.
+Darius: What a way to find out about an affair, too.
+Jordan: Bro, that is crazy. actually, so this off the cuff, but do you think she just, I don't know how to word this. Do you think she cheated just because she was always going to cheat or do you think she cheated because that was a reaction to her insecurities about their friendship?
+Darius: I think she was always going to cheat, but I don't, I think. I think she. She kind of knew, you know, you could look at the how they looked at each other and their inside jokes and their and their giggles. And you could, you know, that they're the type. She walks in the room and Andrea and Sydney stop talking, you know, and right.
+Jordan: Yeah. Good job of hiding it at all.
+Darius: No. And so. How many years you deal with that? I don't even I. Dre was checked out of that marriage from day one. Right. And so when he quit his job at the movie, the movie, the record label, record label went to Sydney first and ain't that weird?
+Jordan: I gave him the money.
+Darius: Right. And he gets home and he tells his wife, I quit my job. But I like you're the second person to find out today who actually found out was the woman I love. Like, you know, like, how is your wife the second person that isn't at work to find out you quit your job? Like, Because she's not the number one person in your life, And so correct. And I think she had an affair because she wanted to have an affair. She's an adult with agency. She can do what she wants to do. But yeah, it was not an unfounded skepticism that she had of their relationship.
+Jordan: Clearly, if you watch the movie. So yeah, she was dead on. Yeah, that's the thing I think with this movie is like even a lot of rom-coms, honestly, is that, you root for the protagonist and you root for the boy and girl to get together because they're best friends and, they're meant to be together, but they cost like a lot of harm in the course of that journey. And they were specifically, like these two were really out of pocket. Remember we reviewed like what if there was like a couple scenes where they did some crazy ****. Other than that, it was pretty much normal. Like they're all over each other hugging and kissing and she's calling him baby. And like, you know what I'm saying? Like they were kind of moving kind of crazy in this movie. And I know like the wife's supposed to be the villain, but you do kind of empathize with her because she knows she's #2.
+Darius: I've always felt that way. the classic sitcom scene where, the true love interrupts the wedding and then, you see a different world, the scene.
+Jordan: Yeah.
+Darius: And I'm just like, I've always felt for the guy who or a woman who gets lef</t>
+  </si>
+  <si>
+    <t>Jordan: It's literally like a nothing happens in this ******* movie. Hey everybody, welcome to the Alpha Trunk Pod with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's D's all up in the area on all socials.
+Jordan: And this is our movie review segment. Today we're going to be reviewing Children of Men, another movie recommended by a good friend of the pod, Erica. Shout out to you. That's where I got it from.
+Darius: It was on my list of things to do. And I was like, why did I put this on here? As I'm watching, I'm like, this isn't, who did I get it? Because it was like next, because I have a note with the list. That makes sense. Shout out Erica. Appreciate that.
+Jordan: Yeah, shout out Erica.
+Darius: 2 + 2 is 4. That makes sense.
+Jordan: A little patron and fan engager of the pod.
+Darius: Yeah, soon to be. co-host. Spoiler alert. Anyways, back to your drop.
+Jordan: Yes, starring Clavo and Julianne Moore, Michael Caine, Alfred from Batman, Claire Hope Ashete, and Chiwetel Ejiwafor. This movie is in a place in a dystopian world in 2027, where human infertility has led to a global collapse. A jaded civil servant, Theo Faron, is hired to protect a young refugee. He must escort her on a perilous journey out of militarized Britain after discovering she holds an American secret she's pregnant. This makes her the most important person on earth. So I'm gonna set this up to send it over to you for act one.
+Darius: Act one, we're going to call a world without hope. A weary bureaucrat, Theo Faron, is living a disillusioned life in a crumbling, infertile 2027 Britain. Nothing makes me feel older than future movies being the current here. He's reluctantly.
+Jordan: I was like, what?
+Darius: Yeah. They're like, in a far distant time. In a place far, far away. And it's like, yes, it's like last year. He's reluctantly tasked by the strange. activist ex-wife with a dangerous mission, securing transit for a valuable young refugee. And I always like to point out when there's a post-apocalyptic movie, because a lot of center-right people, conservative people, Republicans, whatever you call themselves, complain that Hollywood is like, all their movies have a liberal band. And Hollywood is very liberal place and it has a lot of liberal movies. But I like to always point out that post-apocalyptic movies are inherently conservatives because they're basically an ode to the Second Amendment. They show the downsides of having a big powerful government. They emphasize self-reliance and they show what a world would be like with like a total population collapse. And so these movies are basically what these movies basically highlight the advantages of conservative principles. So Walking Dead, The Last of Us, Children of Men, if you hated the big government and owned a bunch of guns and believed in growing your own crops and relying on yourself, you would do really, really well in a post-apocalyptic world.
+Jordan: So 1984, Fahrenheit 451.
+Darius: You know, so just want to point that out. Toss it to you. Act one. What you got?
+Jordan: So I want to shout out the director of this movie, Alfonso Cuaron. He actually directed Harry Potter and the Prisoner of Azkaban, the third Harry Potter film, largely considered the best film in the series. Shout out to all the Potterheads out there, so I want to shout him out.
+Darius: And the red bag was stupid.
+Jordan: Oh yeah, for sure. He literally like, I think he said, I think when we did interviews, like, dude, they wanted to do the 4th one because he did such a great job. And he was like, dude, I'm tired. I can't even, I can't even think about making another movie. It took like 2 years off after that.
+Darius: I know. I mean, he probably never, I mean, he probably is up 100 M's just off that one.
+Jordan: Probably.
+Darius: Just directing one Harry Potter movie. He's, it's amazing. He's still working. Anyways, shout out to him.
+Jordan: And this is a couple years after that. So I will say I really liked it. What was unique to me about this movie is it is set in the future, but everything looked old. I thought that was a really cool touch and very creative, especially considering the way it showed just how much things had fallen apart, so to speak. It reminded me a lot of like the Hunger Games kind of **** where it was just like bearing everywhere. But it also, you saw the class difference as well, where you could kind of see who's in that one condo with the guy who had that weird machine, son of that crazy machine. And then he goes outside and there's just people like damned around horse and carriage in the street.
+Darius: We take for granted just how much engineering and human capacity and governmental functioning goes into like making sure when you turn your faucet on, it's clean water every time. like making sure that when you touch your light switch, the electricity just works. That's not magic. Like a lot of government capacity and modern engineering goes into that. A lot of places on earth, it's not the case that every time they turn their faucet on, clean water comes out. It's clean water. The fact that like you take your trash and put it in a dumpster and it's gone in the morning and you don't know where it goes. No one talks to you. don't have to call anybody. It's just gone.
+Jordan: Right.
+Darius: Like that is like people don't realize that like that doesn't have to happen. And it's like, you know, if things collapse, it will stop happening. And I promise you, if your water stops running, you will feel it very quickly.
+Jordan: Yeah. And anyone who's traveling around the country knows just how important clean water or the difference in clean water. Because I remember I went to Jamaica once and I accidentally tried some of like the water, their water. Yeah. And I almost threw up like right away. It's such a difference. It's crazy.
+Darius: And when I was in Cancun, man, we you didn't even want to get ice in your cocktails because it was like, I don't really know. Can I get that margarita with no ice? Because I mean, they use their water. They're not using filtered water for the ice.
+Jordan: Right.
+Darius: So it was bottled water and cocktails with no ice. But it was all inclusive and they was free. So I still got the stuff. So one day on the pod, I'll tell the story about Me getting concussed in Cancun. So question for act one. Yeah. Do you have a go bag? Do you know what a go bag is? Basically a bag if things go left, you know.
+Jordan: Yeah, like if the world were to fall apart, I just pack grab that or pack my **** and go, do I have a go bag?
+Darius: Climate change gets so bad. We actually get hit with a real hurricane and there's flooding and you got to get in the car and go and you don't have time to think. You just got to go.
+Jordan: Yeah. I could pack pretty quickly. Yeah. I can pack pretty quickly.
+Darius: I mean, I'm not a doomsday prepper, but I have a go back. Birth certificate, social security card, a couple 100 bucks cash. Clothes, batteries, flashlights, first aid kit. Just a duffel bag that I keep. I'm not gonna say where I keep it, but yeah, I gotta grab that and grab something else. And then I'm out the door and I could be, I mean, it wouldn't even be 5 minutes. And so I think I always tell people, man, Always have a go bag because you never know when you're going to have to evacuate. And it doesn't have to be something this apocalyptic, but like, right, you know, your building catches on fire. Smoke is blowing in. You can't, you know, it's hot as a ************. You don't know. You can't see ****. You got, you know, you what if your medicine, you might have blood pressure medicine. I got.
+Jordan: Yeah.
+Darius: You got to go bag, you know. Always have a go bag because you never know when you'll have to evacuate.
+Jordan: Yeah, that's true.
+Darius: That's my advice for the people. Keep a go bag.
+Jordan: Yeah, I mean, I have a book bag and a whole bag that I kind of keep just in case I need to pack and run somewhere where there's something like that. Yeah, I can pack pretty quickly if I need to. I know pretty much what I would grab in case of emergency.
+Darius: Also have proof of citizenship. I don't know.
+Jordan: Yes.
+Darius: Your ID is not proof of citizenship. I keep my passport in my go bag. and my birth certificate, which are both proof that I was born in the United States of America.
+Jordan: Yeah, and that is really important nowadays.
+Darius: The 14th Amendment is still real.
+Jordan: Yes.
+Darius: It's basically impossible to amend the Constitution, so we'll be fine as far as the 14th Amendment. But anyways, Act 1, what you got? What else you got?
+Jordan: Yeah, actually, I was going to say, I was like, this movie was really, really far ahead. Well, it's based on a novel, but it's really far ahead of its time considering everything's kind of going on. Like when they show like the cityscape and things that are going on amongst the, in this, not archive, but abandoned society basically. With the kids in cages and all, they just made me think of ice and all that kind of stuff too, which I thought was pretty crazy. I guess I just wanted to ask you what, oh, go ahead.
+Darius: No, go ahead. I was gonna say, I think it was Thomas Jefferson who said, what do we have? It was like a democracy if you can keep it. People think Democracy is just something that exists. It's like, no, it's something you have to protect.
+Jordan: You have to fight for every single day.
+Darius: What were you going to ask?
+Jordan: Yeah, I was going to say, did you, did seeing that movie and kind of thinking of the parallels of today's things that are going on in today's world, did it make you like anxious at all or fearful or maybe less hopeful for the future?
+Darius: No, not really. Obviously, I'm not unconcerned, but I am, generally speaking, not very alarmist. And it's not good that the institutions have had to hold, but they have held. And it helps that he's 80 years old. You know, if he were 25 years younger, I'd be a lot more concerned.
+Jordan: That's fair.
+Darius: So yeah, I'm aware and some things are alarming. But no, my hair is not on fire. So that's to answer your question. So you.
+Jordan: Okay. Yeah, because for one, it's almost like, okay, if all you need to do is see one person do it to know that it can be done. And it's like, if you can see one person ruin, like break democracy in this country, then what reason is there for it to start back up again in a sense? Or how hard would it be to resume it? And then more than that too, it's also like, okay, it's his followers. Like what would they do? What lengths would they go to encourage and protect that as well?
+Darius: But none of them are as charismatic as him.
+Jordan: That's fair.
+Darius: They're not as funny as him. They're not as charming as him. They're doing like a bad impersonation. But also, you know, that's why I harp on people. As you know, I've said in a previous pod, you know, if you truly believe that this is an existential threat, then you need to be willing to do the art of persuasion and convince people. If it's truly like your life, you think the country's at stake, but you're not willing to fold on any policy issues, then you don't believe the country's at stake. You know, it's like, it was, I think it was Jon Stewart who was, you know, he did the the thing where he says, he has an uncle that's a Trump supporter and racist and people did the thing where they're screaming in the comments, like, if you could talk to him, then you, it's like, okay, well, do you believe this is an existential threat or not? Because if you're not willing to do anything that makes you uncomfortable, then you don't believe this is an existential threat. That's because your goal is should be if he's amenable to it. your goal should be persuasion. And if you're not willing to do that, if you're willing to just storm out of every room when someone, some Trump supporter says something you don't like, then you don't believe this is truly dire because you're not willing to do anything that makes you uncomfortable. You just, you're pretending to, but your actions, you know, reveal that you don't actually believe it's as dire as you say. So I'm willing to for work. That's why I, you know, and flexible in position taking. That's why I listen to people because I take the threat seriously. And I don't, I have very little patience for people who just want to storm out of every room that's, you know, to the right of center. Not even, I mean, these people to the right of Pete Buttigieg, they just want to storm out of every room. And it's like, well, then you don't believe this is a real threat. You just, you're pretending to because it's easy to fundraise that way. So no, I mean, Look, there are some images that are definitely disturbing and the movie can be a bit prophetic in that way. But no, I mean, it's democracy if you can keep it. these things, Rome, at one point, the emperors of Rome thought this would be forever. It's not guaranteed you'll be on top forever. It's not guaranteed this will be a country forever. You have to fight for it. You have to be willing to, you know, protect it. And so, you know, go out and do that every day. You got anything else for act one?
+Jordan: So I was going to say, we talked about this before in, I think when we did a weapons review where the couple had lost a child and they were on that double decker bus and they were talking. And it was almost word for word, the conversation that we had talked about where both parents are grieving and they're heartbroken in different ways, but one kind of moves on and one just like can't let go in a sense or not. I mean, they both can't let go, but in they're not letting go, one tries to just move on as best they can. And the other one just kind of It just stuck in that quicksand, so to speak. And I like that they had that conversation because it really showed an example of a perfect example of kind of how that can break a relationship and break a human, So I really like that conversation that they had.
+Darius: It's almost like 100% predictive. Like one parent will move forward and one parent will, I hate to say self-loath, but I don't know what else to say. And it will almost, they will resent each other for the choices they make if they will divorce. It's just, it's almost guaranteed. You know, you can write it in stone. So ready to get an act two of this platformer movie?
+Jordan: Let's get it.
+Darius: So the audience should know the movie is very linear. And so it's interesting. It holds your attention because it's a lot of stuff is going on, but it, you know, there's not, It's very much like if you've ever played like God of War video game and it's like, it's not really like a free-flowing like RPG choose your own adventure and just do your tasks and you go to the next task. So Act 2, the reluctant guardian, Theo begins a high-stakes cross-country trek to deliver the refugee to a secret sanctuary known as the human project. With both militant groups and the government pursuing them, he must rely on old friends to survive the intensifying chaos. Did you ever watch season one of True Detective? Yeah, I did. So Russ Cole, when he does that long shot, the 8 minutes when he's undercover and then he gets a guy and then it reminded me so much of this movie reminded me like those long one take shots where I just love season one of two detective. It's been awful ever since. But like Russ is undercover and then there's like the raid breaks out and he has to basically kidnap a guy and it's all in one take and it's all one long shot. And this movie reminded me of that. Also, I love when post-apocalyptic movies give us a glimpse of like the world that was before. Like you saw the Picasso paintings in this one. If you ever play like The Last of Us, they're in Seattle and you go into this huge convention space and you see like anime and it's like, what is this? And this, it's 40 years past the time, but it's like decaying. So it's a nice way to, ground the movie in reality. And so, yeah, what you got for that too?
+Jordan: Speaking of long shots, it's interesting. I'm glad you brought that up. This movie came out before the movie I'm about to reference, but it reminded me a lot of that movie Birdman. I don't know if you ever saw that with Michael Keaton.
+Darius: I've heard of it. I have not seen it.
+Jordan: Really, really good movie. And the whole movie is basically like 1 long continuous shot. And that's definitely what kind of jogged my memory when I went and when I saw this movie. Yeah, I really did like the long shots because I feel like that's kind of the The testament to a really, really good director. For one, just commanding the attention of a cast and crew for that amount of long period of time and everyone being locked in and knowing what they're supposed to do for that long period of time. Because, you know, it's maybe a 7 minute sequence, but they had to be doing the action before the camera started rolling and then keep doing it after, you know. And so it's really like a 15 minute probably setup. And you're doing that over and over and over again. Like people don't understand how many takes you do in a movie. And so I just really commend the production for their effort on that.
+Darius: And as a viewer, it almost focuses you, forces you to focus in a way.
+Jordan: Correct.
+Darius: When you're watching a movie with a lot of jump cuts and a lot of scene switches, it's just easy to get distracted. And like this one, you really feel like you're there with them because it's not jumping around. And so, yeah, I agree. That's.
+Jordan: It almost for me at least it, because I didn't find the pace. I wasn't a big fan of the pace of the movie, but it almost, because of the long continuous shots, you almost didn't want to break like with pausing and, **** like that. And so it almost makes you feel like you're locked and trapped in this world, which as a citizen, you would be locked and trapped in this world, which I thought was really, really cool. Excuse me, a really cool effect. of the storytelling method that he decided to use for this film.
+Darius: So the movie never explained the fertility crisis. What do you think it was?
+Jordan: I don't, I mean, I'm trying to think. Because they weren't, no one was really communicating with each other. Like the doctors weren't communicating with the other doctors and hospitals weren't communicating with the government and so on and so forth. I almost wonder if it was some sort of like, almost like a diet type thing or like some sort of technological like glitch or something, like maybe like something in the DNA that went haywire or they were having too much of some sort of insulin. I don't know what would cause that, obviously, but Was it a birth rate?
+Darius: So were people infertile? Did they explain that? Or was it just no babies were divorced?
+Jordan: Yeah, she said first people were miscarrying. Like a lot of she was having a lot of miscarries. She was a doctor or a midwife. And then They happen more often and then they happen sooner in the terms.
+Darius: Yeah.
+Jordan: And then I guess eventually no one was able to get pregnant.
+Darius: Interesting. It's probably, I mean, they didn't explain this. I doubt they know, but it almost seems like an evolutionary adaptation, but there's no reason for any animal to evolve, not to reproduce.
+Jordan: Right.
+Darius: You know, we're, I mean, we're currently as a species in a fertility crisis, at least most developed nations. And that's my question for later in the show. But yeah, it's just it's weird. It's hard to call it evolution. Yeah, I wish they would explain that. artistic people like to leave things ambiguous, which I think is often just lazy. So yeah, I don't know. Did it impact your enjoyment? I don't think it did for me. I don't think it impacted my enjoyment. Did it impact yours?
+Jordan: It didn't impact my enjoyment it just made me I just found it to be a storytelling flaw yeah or like a plot hole because I mean if the whole move like okay this is just dystopian society but it's because humans are basically going extinct yeah you kind of need to explain the root of the extinction you know we watched dinosaur movies watch dress part they talked about the ******* that the meteors **** you know what I mean like it just didn't make any sense yeah and also.
+Darius: Why would a fertility crisis inherently cause society collapse? People still seem pretty young. It wasn't an aging society.
+Jordan: People weren't dying sooner too.
+Darius: That society will collapse if population collapses, but not sure why in this world it had already done so. Because like the main character is like 35 years old and most of the people around him were of similar age. So why would they? stop, making sure the water comes out clean. Why would they stop making sure the electricity is right? Like, it's weird that they just, we sort of skipped some steps.
+Jordan: Yeah. And I can't remember if they talked about this or not, but I know obviously they lost their child, but did that fertility issue cause kids to die younger also? Like, I can't remember if they really specified that. Also, like logically speaking, this is not good, obviously, but if less people are being born, there's more resources for everyone. So wouldn't the economy be better?
+Darius: Not necessarily. This movie doesn't because everyone is young, but like, there's the reason why in modern world, people, when people say, why do we care that the population is declining? And it's like, well, for starters, I mean, it's just, you don't want an aging society because you lose your innovation. Most Fortune 500 companies are founded by people under 40. But 2, like, people have to, the labor needs to be, someone has to pick up your garbage and if you run out of people to do that. Right, that's true.
+Jordan: Yeah.
+Darius: So also, people are getting older, but you're not replacing them with young people. So. What happens when you run out of doctors? What happens when, who's going to take care of these old people? Because they're going to need doctors. And you run into a labor supply problem. You run into a tax death spiral because young people are productive and they work and they pay taxes to take care of.
+Jordan: Less taxes, less community programs.
+Darius: I know people don't want to hear this because it sounds like a conservative thing, but like one of the reasons you don't want a population to decrease is because the way Medicare is set up we pay taxes through our 20s, 30s and 40s so that we can collect in our 60s and 70s. But if you run out of people in their 20s, 30s and 40s to fund it, how are you going to pay it out? Take care of the people in your 60s and 70s. Yeah, it's, it just, it can, it can quickly go into a spiral where you don't have enough working age people to contribute their labor and their productivity and their taxes to take care to fund things, you know, and so people, societies need people. If you've ever played a video game like Donald Man or Civilization and you've ever gone through like a population collapse and like you're trying to rob here to pay Paul and there's a game called Banish where it's the same thing where you're like, you're just moving people around and you grow your civilization and the more hands you have, the more jobs you can do. But then you, let's say your society ages and they don't start having babies and it's like, okay, I need 12 pieces of iron, but I literally don't have a human being to go pick it up. And now because I don't have that iron, I can't build a house. And now this person died because they don't have shelter. And they just become, and now that person's dead. So now it's an able-bodied person who can't create a new person to add me to my labor pool. And so yeah, you definitely do not want to be in a society that's aging and dying off because it's not, yes, there'll be more resources available, but There's no one to cultivate them. There's no one to go and get them. So there's no one to cultivate them. So no, that's really all I had on that. Oh, you got anything else for act two?
+Jordan: Yeah, it was. I read a lot about like the reviews and the reception to this movie and it's like critically acclaimed. And I was reading up on it and I saw a comment or quote from a reviewer or movie critic, rather. And they they were like, That car chase scene was one of those insane car chase scenes in the history of cinema or in modern cinema. And I was like, Did we watch the same movie? I thought that car chase scene was like, so it's a climactic.
+Darius: Didn't the when did The Dark Knight come out, right? Oh, eight. I was going to say, I thought if it was a six, I'm like, even the most iconic one that year. Yeah, I mean, I thought the Julian Moore death was jarring and really shocking. And you rarely see a character not act bulletproof. So that was cool. Right. Michael Caine's character could have cut all of that. Don't really need to hang out in his garage. No. His cabin in the woods. Yeah. Then he died and then it literally was just like a rest point in a video game. Yeah. You know, so.
+Jordan: I feel like Act 2 was, there was not a lot of happening in Act 2. I think my biggest, one of the biggest issues with this movie is it was nearly two hours and it was only about 15 minutes of like actual things happening in the movie.
+Darius: Well, what about drag? Let's get to Act 3 then. Through the war zone. The final stage of the journey descends into a violent besieged refugee camp on the coast. Theo must utilize all his resources and will to navigate the deadly conflict and ensure the protected woman reaches her destination and a chance for the future. This woman is pregnant. It's revealed. And now he's like, I need to get her to the what's face to the end of the human project?
+Jordan: Project human checkpoint. He has to beat the game.
+Darius: So my thing is you get the baby there, then what?
+Jordan: I don't know.
+Darius: I mean, it's like, so I say who's?
+Jordan: Going to raise the baby? Who's going to teach the baby?
+Darius: Does the schools exist? Where's the food? So it's a lot like The Last of Us and like the end of The Last of Us, spoiler alert. Basically the game is Joel, the main character has to get, it's a zombie apocalypse, literally apocalyptic level, damn near extinction level event. And there's a lady, there's a woman with the cure. the little girl with the cure and he has to get her to this science lab across the country and chaos ensues. And so, but I've always said in the end, he realizes that she has to be sacrificed to cultivate the cure because it cures in her brain and he kills everybody and saves her in everyone's life. Well, he sacrificed humanity to save Ellie. And I'm like, how would they have scaled up the vaccines? You know, like they're in the middle. There's a million like politics have totally collapsed. There's no government. Everyone has their own political factions now. It's the most violent world you could ever live in. It's ******* chaos. You can't even, like, it's just insane. There's cannibals. There's every building is infected with zombies. You basically have to walk out in the open. And so even if you're able to kill her and create one vaccine, how would you scale it up to get it to people? How would you get people to trust taking it? This is the like, this is Again, post-apocular movies are conservative. Why would they trust the government at this point to give you this vaccine? True. You know, like you just show up at the door. I just watched a zombie eat my husband's face off. You're like, take his jab and you're going to fix everything. It's like, I'm good on that. I am cool. It's just, I've always like how, so they get the baby to the checkpoint and then what? Like it's still a fertility issue because Right. We're just going to, for the sake of the pod, say 18, 18 years old, they can start reproducing.
+Jordan: Yeah.
+Darius: And so you have to wait 18 years for this baby to get of age to reproduce. And this woman can do one at a time. And that's going to take 10 months. And you're going to get one baby. And you don't want to be inbred. So who's going to, it's just, it's logistically, it's a lot harder.
+Jordan: And they never explained, they never really explained like the miracle of her getting pregnant either. Like how was she able to do it and no one else was?
+Darius: I mean, I'm cool with that because The Last of Us never explained why Ellie was immune. They did it in the TV show later, but like, you know, genetic anomalies. Why do some people get, you know, Lou Gehrig's disease? I don't technically know. It's just genetics. Some people get a, dealt a bad hand of cards. And so maybe there's, she has some severely recessive gene that just did not take to whatever the rest of the world takes. And so that's fine by me. There's enough rare medical things that happen in the real world for me to believe this is just a rare medical event.
+Jordan: That's fair. Yeah. So did you, when I, they showed like they had like the long video game, basically battle sequence, and everybody realizes she has babies, everyone kind of stops. And then secondly, the babies pass, they're like, all right, let's kill everybody.
+Darius: Well, so, it's one of those things though, like you, we take peace for granted. The fact that none of us have lived through the Iraq war.
+Jordan: Correct.
+Darius: But over the arc of all of human history, peace is the rare thing. That's true. We've been at the one thing our species does better than anything is killing each other. That's what they know. That's innate to their human existence. And so they're not, the baby, they probably hadn't heard a baby crying 10 years, 20 years. Right. And so that after that initial shock wars out, wears off, they get back to doing what they do best.
+Jordan: Back to normal. Yeah.
+Darius: But like, again, man, we take peaceful transfers of power for granted. We take like, that's what politics is. Politics is the substitution of war. It's solving political disputes peacefully. It's not like, because before that, it's just Game of Thrones. I don't like that you're on the throne. I'm just going to kill you.
+Jordan: I'm going to kill you.
+Darius: Know, and like that.
+Jordan: And my friend's going to kill your friends.
+Darius: Correct. And it's just an endless death spiral. And so there's nothing that peace is rare. And, you know, we have a constitution that is held so far, but it's not guaranteed to. And it's not at all, no one thought there'd ever be another war in Europe and then Russia invaded Ukraine. That's just our life, and so, but that is the most normal thing, land acquisition wars is as human as air. So, peace is not guaranteed and peace is rare and peace is hard. And, so that's what you To answer your question, yeah, that makes sense to me that they would just go back to war because that's all we've ever done. So.
+Jordan: That's true. Yeah, I thought that was a nice touch. Did you, I liked, or maybe just reaching here, I felt like watching the movie and even just like the scene where they literally put her and the baby on the boat. It reminded me a lot of Moses, like the opening scene of like Prince of Egypt, like that, you know, this is like the savior. We're going to make sure this kid is safe. And then Jesus literal</t>
+  </si>
+  <si>
+    <t>Jordan: Hey, everybody. Welcome to the Out of the Trunk Pile with Jordan and Darius. This is our movie review segment. My name is Jordan. That's Jordy Rewriting on all socials.
+Darius: And I'm Darius. That's Deez Allupia area on all socials.
+Jordan: And this is a podcast where two friends started talking at a bar and never stopped. Today we're going to be reviewing Christopher Nolan's superhero masterpiece, The Dark Knight, starring Christian Bale, Heath Ledger, rest in peace, Aaron Eckhart, Michael Caine, Maggie Gyllenhaal, Gary Oldman, and Morgan Freeman. This movie is about Lieutenant Jim Gordon and DA Harvey Dent helping Batman successfully keep a tight lid on organized crime in Gotham City. However, an anarchistic mastermind known as the Joker emerges, plunging the metropolis into utter chaos and forcing the Caped Crusader to test his moral limits. I'll toss to you for Act 1.
+Darius: Act one, the shadows over Gotham, a ruthless new criminal destabilizes Gotham's mob syndicate through a daring bank heist. Meanwhile, Batman, Lieutenant Gordon, and the idealistic new district attorney form a powerful alliance to eliminate crime. That ruthless new criminal is the Joker, played masterfully by Heath Ledger. And my first observation, I'm sure you know this, but just for the audiences, for their information. Every Nolan Batman movie started with the villain in the opening like scene hiding their identity. So, you know, so we got Ra's a Ghoul in Batman Begins, Joker in the bank heist and Bane on the plane. Was that a plane hijacking, if you will?
+Jordan: Yeah, plane jacking, yeah.
+Darius: Cool little nugget in all of the Nolan Batman movies is you're introduced to the villain via some little stage trickery. So, and also these are the only three Blu-rays that I own. I would get out as well, so.
+Jordan: Okay, I do have that on Blu-ray.
+Darius: Yeah. It's just. Physical copies are way better. They are way better than streaming.
+Jordan: They really are.
+Darius: It's just. I ain't got space for all that clutter, but they're. What you got for act one?
+Jordan: So I love that the opening scene is first of all, great. It's an excellent way to start a movie. It's about a theater, man.
+Darius: I don't mean to cut you off. Yeah. I'm skeptical going into these things. I just was just like enthralled when he's like, I believe what doesn't kill you simply makes you stranger.
+Jordan: Makes you stranger. That line was crazy.
+Darius: It was like I blinked and the movie was over. I was like, this is completely washed over, which is the highest praise for me when it comes to a movie, a superhero movie. So sorry for interrupting you though.
+Jordan: Yeah, so it says the first heist. First of all, it's phenomenal way to start a movie. Zip lining across buildings, Gotham City, broad daylight, you know. Christopher Nolan famously does all his movies practically, so you know it's not CGI in some studio and some ******** you know what I mean? I love the way he, looking back now, it's like fun to break down the movie and like the strategy and the Easter egg and stuff like that. And the first heist was an excellent way to show the Joker's intentions, you know, because like Remember, he famously keeps saying, I don't care about money. So he's like, really just doing his **** for the love of the game. He's doing this to get leverage over the mob to force his hands so he can work with them, you know, to show his brilliance. You know, you have the school bus coming in right as like in line with other school buses when the heist is over. Having the criminals kill each other one by one so he didn't have to kill them. Also, I just love whenever like bosses or evil bad guys in movies work in secret with their staff.
+Darius: Yeah.
+Jordan: So they can kind of get a feel of what's going on, make sure the job goes smoothly. I thought that was brilliant as well. Yeah, man, that's just a great ******* opening season to a superhero movie. Like that's who who thinks of that? Christopher Nolan. But like, who else thinks of that? You know what I mean?
+Darius: That's why he's him. So let me ask you this. You are a superhero movie aficionado. Yeah. I can answer for me what makes this different, but what makes this so different? What makes this different for you? Like what makes this a classic without this like, cause there's like good for a superhero movie and then good. What makes this one shake the disclaimers?
+Jordan: Okay, that's a great question. I actually was gonna ask you that myself. So the thing that makes this movie a great movie and just so unique is that literally every single character has to make a difficult choice. Every single character, maybe it's when he's old, so we don't have to really do the acting, honestly, but Batman has to decide, is he willing to kill the Joker? Gordon and they have to decide, are we going to choose Rachel or Harvey to save, you know, when they're tied up? Rachel has to decide, am I going to stay with Bruce or am I going to go with Harvey Dent? You know, the mob have to decide, like, are you going to go full evil or are you just going to be like regular bad guys? Because they like, they're not they're not Are the mobsters bad? Sure. Are they evil? No. I even like how there's the scene where there's the cop who tries to fight the Joker when he's in the interrogation room and he's like, I know the bad guys who just needed the punks need lesson in manners or the psychos who do the **** for fun, you know? And that that's this movie does a great job just really illustrating that because like Michael J. White's character, you know, he's like, who is this dude? Like, you know what I mean? The whole movie is like, kill this guy, please.
+Darius: You know, you get that credit. You got a credit in a Christopher Nolo movie. He does like ****** kung fu movies on Tubi. How the hell you get in this Christopher Nolan Batman vehicle with speaking lines, not just like a background character.
+Jordan: Well, I think that's one of my favorite things about Christopher Nolan is because he people put this like hoity toity filmmaker tag on him, but he's genuinely just a lover of cinema. Like people **** on Fast Furious moves and you know, that's like a popular thing to do. He's like, I love those movies. They're a lot of fun. Who like who's to say what's good or bad? I love those movies, you know, and I think that's what makes Chris Fenolan a great filmmaker is that he watches and enjoys all kinds of films, you know, also like I would have loved to have seen Michael G White just do some sort of like martial arts because he is like a martial arts legend. I think it would have been dope to see, but even him, he had some of the funniest lines in the scenes in the movie, like him and Heath Ledger together were great. Yeah, I think that's what makes this movie different is that every character has an interesting choice to make. when the Joker says, if y'all don't kill the dude who says, I know who Batman is, I'm gonna blow up a hospital and someone you love is gonna die. And every character's like, all right, **** it, you gotta die, man. You know what I mean? You got the prison dilemma with the two fairies, you know, like no one wakes up. Think about it, like you're a citizen in Gotham and you didn't wake up to be thinking, hey, am I gonna kill 500 people on a boat who I never had no problem with? You know, I think And also just the social commentary of the prisoners didn't even, they didn't register with them that they would kill the other people. And they're viewed as the bad guys. But the civilians were like, **** them, let's kill them. You know.
+Darius: I'd hit that ************* button. Bunch of rapists and murderers on that boat. All right. You need to give it to me. I hate that. I they had their side. They're violent criminals over there.
+Jordan: That's exactly what that dude said. He was like, they had their chains. Yeah, they chose to lie and steal.
+Darius: That ain't even a day. No prisoner's dilemma. Ain't no dilemma for me. Yeah, I think. That's the part about Christopher Nolan's movies that make it special is that by and large they're not pretentious. Like the Odyssey has a giant Cyclops eating people. Right. You know, and. there's just the giant, giant dudes killing, the people turn into pigs and then interstellars and it's mathematical, but it's like the most pretentious movie.
+Jordan: It's a space movie.
+Darius: Yeah, it's a space movie. And there's time lapses and all kinds of **** like that. And I mean, the most pretentious movie is probably Oppenheimer. That might be my least favorite one of his.
+Jordan: And even that, I didn't find it very pretentious. Like, you know, The way he broke down like the elements, he just, he treated them like marbles. So he made it simple, for people to follow.
+Darius: The last hour of the movie was a congressional hearing for Commerce Secretary.
+Jordan: Yeah, but I'm a poly side nerd, so like, I'm a, you know, I thought that **** was thrilling. I'm a poly side nerd, so I don't, you know.
+Darius: I think Memento's is worse, but if I had to. Yeah, but I'm his bottom third, but it's a good movie. Don't get me wrong.
+Jordan: That's crazy.
+Darius: It's a good movie, but it is. I have not watched. It's not a popcorn movie since I left the theater. I've not watched one scene of that movie.
+Jordan: I watched it back once. I loved it, but I did break it up into thirds because it's a three hour movie about talking.
+Darius: And I even like it's I enjoyed it, but I knew when I left that theater, I was like, I probably never like, I'm not watching that. I haven't watched another scene of Killers of the Flower Moon. I love that too.
+Jordan: You know, like, yeah, that's what I don't think I'll watch ever again. Also, just really sad. Yeah. So to your point about Nolan not being pretentious, like even when people were asking him during the press run for Odyssey, they were like, oh, like you got these characters saying like dad instead of father, like, why'd you do that? He's like, I wanted to be accessible. You know, I wanted to use music that Feel the times where they didn't feel hoity-toity like an orchestra or something like that. it's not. I don't want people to associate my movies with basically with like British snobberies, basically what he was saying, Also, it's an adaptation.
+Darius: The great words of Jay-Z. If you want my old **** buy my old album, you know, the Odysseys of I bought it for a dollar. Go read that if you want the original, you know, right?
+Jordan: Yeah, exactly. Like it's supposed to be unique.
+Darius: If you wanted a word for word that exists for a dollar on Kindle go buy it yeah um what else you got fracked one.
+Jordan: Um so I love that there's only one villain that is in the whole Batman trilogy and that it's Scarecrow uh played by Killian Murphy um also he just is a phenomenal was a phenomenal comic book villain he like he didn't have huge roles in the movies but he was just like really really dope.
+Darius: He tried out for Batman and.
+Jordan: Um and they were like no.
+Darius: No, you got to get, you got to get some reps first. But Dolan called him back because I got this like small part. Well, it wasn't a small part in the first movie, but he was like, I'm not turning down. Do you think I'm going to keep asking me? Like, ****. I'm like, Urkel, I'm already outside. Like, yeah, who cares?
+Jordan: **** give me any other roles you got. I'll take, you know.
+Darius: Me and Oppenheimer winning an Oscar. So.
+Jordan: Correct. And he didn't get that role if he says no to Nolan. Probably didn't get that role if he says no to Nolan about, you know, playing scarecrow. Oh yeah, so I texted you this like last week. I was watching the movie just for fun even before watching it for the pod. And Christopher Nolan is one of the great visual storytellers as well, just like using like shots and symbolism. And one of my favorite parallels is like, if you go back and notice like the lighting and the layout of the new Batcave and because he's in that penthouse because his crib break out in the first one, it's the exact same as his boardroom where he's fell asleep in that meeting with Lyle. And it's almost like I took it to mean like, you know, he's Batman everywhere. You know what I'm saying? Like the Batcave and the boardroom are the same for him because he's still doing his investigation and he's still, you know, trying to, you know, make sure Gotham is in good hands, essentially. I thought that was pretty dope. visual storytelling. Also, people like to say, like, it's Christopher Nolan. Christopher Nolan's not funny. Like, it's not jokes in his movies. And this movie is hilarious. Heath Ledger was every line Heath Ledger had in this movie was hilarious to me. You know, he's like, you think you stole from us and get away? Get away with it. He's like, yeah. And when he has the grenade, he's like, let's not blow this out of proportion. That's pretty good.
+Darius: I mean, I could have used. Well, we already reviewed the Odyssey, so we're going to do that. But yeah, there's definitely a bunch of there's some some humor in this movie, but it's easier to do that when you're dealing with Batman and the Joker.
+Jordan: Right.
+Darius: You know, so it's the source material is humorous in general. So correct. You got anything else for act one?
+Jordan: No, let's look after act one.
+Darius: Act two, the escalation of chaos that. enigmatic antagonist unleashes psychological warfare across the city, targeting public officials. I have my Floyd Mayweather moment there. As terrorists pass rapidly throughout the city, the heroes are forced to come, escalating impossible moral dilemmas daily. I dare you to read a page of a Harry Potter book. Enigmatic is actually a hard word to pronounce. You know, 10 times fast.
+Jordan: Enigmatic, enigmatic, enigmatic.
+Darius: It's harder than it looks, especially when you didn't read it before. So it just kind of hits you like a speed bump.
+Jordan: Enigma, please.
+Darius: So is it is the Batman? I get it's true to the comics, but like the fact that he doesn't kill people is just a bizarre line to draw when Joker is like responsible for murdering half the city. Correct. And it kind of breaks immersion a little bit. I'm just like, you know, you could fix this.
+Jordan: With one with a full of a finger.
+Darius: You know, you've already committed 12 crimes today. Yeah, actually like law enforcement, right? You can fix your problem, buddy.
+Jordan: And you wear gloves. They wouldn't know who did it. Exactly. Yeah. So it's funny. I have this note for act three, but like, there's that remember the letter where she's like, I don't think there'll ever be a day where you don't need Batman anymore. I think that's part of the psychology behind him not killing people. I mean, I think he won't do it for moral reasons, but I think it's also like, but if I kill my biggest op, who Who am I gonna go against? You know what I mean? Like Batman does love the thrill. It is an adrenaline rush. You know, he does love the combat. He does love the confrontation and the violence, you know? And I think that if there is no confrontation, then there's no violence. And then what's he gonna do with his monster? The monster inside of him, I mean.
+Darius: That is true. You know what internet trend, it's kind of dived down now that I hate the most when like some obnoxious nerd is like, Batman could have funded social services instead of doing all of this. And it's like, okay, that would be a really boring movie.
+Jordan: That'd be right. And by the way, Batman did fund social services.
+Darius: You know, like, we're just gonna, I'm gonna dress him too as in a bat suit and then sit for student board or school board meetings. I don't know.
+Jordan: Yeah, like that's not. If I was a billionaire and you gave me the option to sign documents or fight people, I think I'm going to go with fighting people and flying off roofs.
+Darius: Yeah, it's just like, at first it was like a bit, and then I was like, oh no, y'all are serious?
+Jordan: They're like, no, he should be, he should run for Congress.
+Darius: No, in real life, I don't want billionaires being vigilantes, but the beauty of fiction is that it's not real. So much internet discourse is driven by people who don't seem to understand that fiction is not actually real.
+Jordan: Yeah, I think so.
+Darius: It's just people got to remember these things are fake. That's what makes them fun. We can correct. Once the movie is over, we that world is ended, you know, until there's a sequel or whatever. But what else you got for act two?
+Jordan: Oh, yeah. So the one of my favorite lines from the first Batman is when Rosa Gould says, you want to make yourself more than a man to put yourself to an idea. And I feel like The Joker does that just as well as Batman does. he's got, obviously the makeup and the outfit and all that, but like he's just a guy running around doing crazy **** but like everyone's still afraid of him. Everyone's still like, he walked in the room with the mob and no one did anything. You know what I mean? Like granted he had grenades, but they didn't know that the whole time he was in the room. You know, it's like that he was just like larger than life figure and just the perfect foil or a perfect fool to Batman in this movie because he was just so lawless and just had no rules and didn't care about any sort of impoliteness or moral, you know, boundaries, anything like that.
+Darius: A man who has like no, like when you deal with most criminals, like money is a motivation. The desire to be free is a motivation. But like Joker is the worst because nothing like he just wants chaos. He just wants to burn this place down and How do you control that? How do you work with that? How do you keep that? You kill it. But it's not an option, but you just, you lock him up and he's out in 30 minutes because he's willing to blow the police station up. You know, like there's nothing you can do for someone who does not care about. The most dangerous person is someone who doesn't give a **** you know?
+Jordan: Yeah, no, you can not **** with someone who has nothing to lose. What was I gonna say? Oh yeah, so one of my favorite scenes in the movie is when the guy goes to Morgan Freeman's office and he's like, so I ran through your numbers and he's like, shows the picture of the Batmobile. He's like, so what are you bidding for him next? I want $10 million a year every year for the rest of my life. And then Morgan Freeman, as only he can, just calmly is just like, so your plan is to blackmail this person? Good luck.
+Darius: It was a great, it was one of my great seeds. He goes, you psych your client or your boss, I forget. It was like one of the richest and most powerful men in the world. Spends his night chasing and beating up criminals to a bloody pulp.
+Jordan: With his bare hands.
+Darius: You know, probably should have paid that tab though, because they ended up getting in a little trouble later. Yeah. But It's true, though. Maybe they should have been better about hiding it. Why are you got schematics of the actual Batmobile available to regular employees? It's not a good idea. But no, that was a great moment of what again, Morgan Freeman did. Does any no one turns out Christopher Nolan's calls? He got everybody. So you got Morgan Freeman in his best Morgan Freeman character actor yourself just just nailing the line. So for sure you got anything else right to.
+Jordan: So this movie is really fun to me because of the chess moves that everybody's making everybody's platinum scheme. It's almost like Game of Thrones. Everyone is trying to like outmaneuver the next guy. Like I look back and I just realized like today watching the movie, there's a scene where Joker's provoking Batman to beat the **** out of him. And you think it's just because he's a psycho and he didn't care about pain. He wanted Batman to hit him so he could break the glass. So we could have something to threaten the cops with when he inevitably needed to break out to call the guy to blow up the blow up the prison cell. Like, you know what I'm saying? Like it was all a scheme. Like it wasn't. He does nothing random. Nothing is on accident. Like the fact that he thought that far in advance and everything played out exactly how he schemed it is insane.
+Darius: That I didn't I didn't even catch that was so like Joseph could not be actually crazy and playing all this stuff. So he like the schizophrenia stuff has to be like a right. Like it just doesn't.
+Jordan: No. Yeah, I don't think that gets.
+Darius: He's way too high functioning and far too calculated. Yeah, it's just. It's impossible for him to actually be crazy and do all of this. I've known crazy people. They can't.
+Jordan: They're not that smart.
+Darius: You can't send in a Wendy's and get their order right. Like, it's.
+Jordan: No, no, no.
+Darius: Like, how did you I texted you what to order and you ****** it up. Yeah. So I know for sure. You got anything else right to?
+Jordan: Okay. Yeah. So where do you think Bruce and I and Harvey were naive? Like when they were kind of like, I think I knew they thought they were going to catch the Joker, but the fact that now that they kind of factored in that he had cops on the inside too.
+Darius: It's not that they didn't factor it in. I just. What do you do? Give up? You know, it's like they had a mission. It was more or less a suicide pact. You know, Harvey was going to die for it. The only thing he wasn't willing to do was lose Rachel. And that's what happened. Turn him crazy. But you at a certain point, you just have to say, I guess I'm just going to die for this. I know this is the right thing to do, and I'm going to see it through to the end. And he that will until Rachel died, he had plans to see it through to the end foreshadowing to face. Yeah. So I don't I don't think they were naive. I just I just they knew the scale of the problem and they knew the difficulty. And when they failed, basically, I mean, I don't think, you know, that's one thing that makes the movie interesting is that the good guys lost.
+Jordan: Yeah, I think that's another thing too.
+Darius: That's rare for us. I mean, I can only think of it happening here in an infinity war. And then they erase the infinity war a year later. So it was like, this is that's actually a callback to the earlier question. What makes this movie different is there's actual stakes and consequences. The good guys didn't just fix everything. People died. The good guys didn't just fix everything in the third act. And you watch it and you can feel the stakes of the movie. It just doesn't feel like everything's going to work out. And it didn't. And that's not to say that everything, sometimes it's okay if everything works out. But my problem with MCU is that every movie just starts to feel like a trailer for the next movie because nothing actual, there's never anything, nothing's permanent. And so it's just like, am I watching a movie in and of itself or am I just watching a trailer for the next one? And it just start to, well, it hit me and in game when it just felt like why did what it everything that happened in Infinity War was just erased and it was like okay well why am I even here just these aren't.
+Jordan: Movies anymore right you know that's the problem with House of Dragons this season it was like nothing happened it was all set up for season 4 which is the last season so What the hell was the point?
+Darius: You just start to feel like a sucker. You feel like one of those people watching the cards on the street. It's like, is this, this is a head game. Like, I just, I just watched this movie and you just fixed it. And now the next movie, you're like, oh, but this time it's like, no, you're not. You're lying. It's never going to end. Yeah, but I did enjoy my time with it again. And that's why I love this movie though, because there's actual stakes. And then to go on to the next movie, Dark Knight Rises, you know, the stakes get even higher. Batman doesn't even make it out of that way. Batman actually dies. Bruce Wayne goes on, but you know, so that's what makes this one special. I should have said that earlier. So yeah, it's act three.
+Jordan: Yeah.
+Darius: Act 3, the soul of Gotham. With Gotham hanging in the balance, a desperate struggle unfolds to preserve hope. The caped crusader makes an agonizing ultimate sacrifice, protecting the city's future by carrying a heavy burden. Let me just say, in 2006, the cell phone GPS location thing felt so out of the world, creepy, futuristic, and that's just our world now. Flock cameras are just going to be around, I guess. We're just going to deal with being constantly monitored, which is not my favorite thing in the world. So it's amazing how literally made. What's that Morgan Freeman's character's name? I'm drawing a blank.
+Jordan: Lucius.
+Darius: Lucius quit the company because it was so such a violation of civilization.
+Jordan: Violation, yeah.
+Darius: Is that's just what we, 20 years later, that's just our work.
+Jordan: That's funny because I always felt like He was tripping in that scene. Like, I get it morally, but it's like, yo, we have a raging psychopath. We're in the streets. Can you help me with this one thing and delete it forever?
+Darius: Yeah, but it's like I get it. And in the movie for sure. But it's like. The reason why the rights have to be for everybody and the reason why, you know. Even the most serial killer, terrible person in the world gets an attorney is because if they don't have rights, none of us do. And so it's like if if you start making exceptions, oh, they you become the exception eventually. I don't know, you know, the first they came for me and first they came for this person, then they came for that person. And right, right. Eventually you will be on the inside on the outside of that exception list. And so on the yeah, you'll be on that list of people that are accepted outside of the circle of rights. So, you know, I wasn't in that. What you got for act three?
+Jordan: Was I did have I forgot I did have the reveal the Batman scene in Act 3 where he's got you got Bruce basically just trying to ward off all the cars with his Lambo.
+Darius: Oh yeah, man, we've dropped the whole act structure for this. Yeah, That was just a, you know, chapter one, chapter two, chapter three type thing.
+Jordan: Right. And I just want to say that it breaks my heart every time I'm watching that beautiful Lamborghini get crushed by the F-150. Oh my God, that car is a masterpiece. And also, I don't know if you know the car, a Lamborghini Marcelago. It actually means bat in French. So I love the symbolism there with that. But oh my God, that car was nice. I don't care how rich I am. I would throw up if I had to just get a new one.
+Darius: Yeah, because those can't be repaired.
+Jordan: No.
+Darius: They're not going to touch that. The scene, the highway chase scene, watch that in my living room. It was fully shot in IMAX, and it's just, you know, turn off all the lights, get the biggest TV you could find, get a soundbar, throw your phone across the room so you're not looking at it, and just watch that 20 minutes and just become engrossed in it. It's, you know, it's cinema, as a great Martin Squire once said.
+Jordan: Is that a bazooka?
+Darius: And he comes down and he's like, and he shoots a bazooka thing and then they're racing and then the little kids look at the bike and it just, that was probably the best 20 minutes of the trilogy.
+Jordan: Yeah, it's one of the best chase scenes ever.
+Darius: And then we find out Lieutenant Gordon is alive and it's going to be Commissioner Gordon. And it's just, it's good stuff. It's good stuff.
+Jordan: And it's the first time you see the bat pod. Remember the front wheels spin out because the car got totaled. that was so that was so. And he's like running through the mall and ****.
+Darius: Yeah, it's just beautifully shot. Yeah, really engrossing. You know, that's superhero movies at their best is when you give us that kind of spectacle and that kind of technical precision.
+Jordan: So I agree. And I will say, like, like after Harvey becomes two face, I was in favor of pretty much everything he did up until he got Gordon Gordon's family, like killing, killing works. I was cool with killing the mob guy. I was cool with. I think Ramirez got off light, but I was okay with him getting back in blood behind this lady. It was just when he kidnapped the kid that he took it too far.
+Darius: Yeah. I mean, he just it. I did a little Googling because I'm not a comic book person, but apparently Two-Face isn't really a straightforward villain in the sense that like he just leaves he, you know, he's a madman in the sense that his brain is warped. Like sometimes he does good things, sometimes he does bad things. And it's kind of I mean, he only had like 20 minutes of screen time, but you kind of you kind of see it reflected in the script of the movie.
+Jordan: Yeah, he was more of a I mean, it's like a corner flip. Two-Face, like he really was just kind of a morally kind of shifty kind of character. And in the comics and in the show, he like was still in love with Rachel who was alive. But they obviously couldn't be together because they were on two different sides of the law. But yeah, and also, like even going back and watching, like there are scenes where you can kind of tell words and Ramirez were on shady **** like the glances they kind of give during certain scenes and stuff. And even like back to The scene where Joker comes into Bruce's penthouse, the cop holding the badge is worse. And like first it looks like he's being held hostage, but it's like looking back, I'm like, oh no, he was working with them. He was pretending to be held hostage. So I love that the performances both those actors play because they didn't have big roles, but they just did a great job of like helping the twist of the story.
+Darius: There are no small roles in Christopher Doe movies.
+Jordan: That is true.
+Darius: Yeah, he's, yeah, he, yeah, he's an efficient, efficient scorer. If you're in there for 10 minutes, you get some shots up. So.
+Jordan: You're getting shots up. Yeah.
+Darius: He does not, he doesn't waste nobody's time, you know.
+Jordan: No, not at all. And plus, we're just gonna dope *** movie set with legends pretty much every movie he makes. So. There's really no locks.
+Darius: He brought back Razagul for, well, Liam Neeson for The Dark Knight Rise.
+Jordan: Five minutes.
+Darius: It was great. It was like, it was great flashback. He lets you get some shots up now. He don't, he don't waste your time.
+Jordan: You work with him one time. You got a job for life.
+Darius: Yeah. But to be fair, like he's not out there working with scrubs, so.
+Jordan: No, not at all.
+Darius: You know, so every director does that like. You know, Tarantino, his people.
+Jordan: He's hiring Samuel every time.
+Darius: Samuel. Brad Pitt being a lot of them.
+Jordan: Yeah, Brad Pitt.
+Darius: Michael Mann is in a lot of them. I think he's dead now. R.I.P.
+Jordan: Who else? Who else?
+Darius: Walter Goggins.
+Jordan: Yeah. Christoph Waltz.
+Darius: Yeah, yeah, yeah, that's true. Anyth</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to Out the Trunk Pod with Jordan and Darius. I'm Jordan. Jordan will be writing on all socials.
+Darius: This is Darius, D's I Love and Area on all socials.
+Jordan: And this is our movie review segment. Today we're going to be reviewing Friday. Black Classic came out in 1995, starring Ice Cube, Chris Tucker, Nia Long, Tommy Tiny Lister Jr., RIP, John Witherspoon, RIP, Bernie Mac, RIP, Anna Maria Horsford, don't know if she's alive or not. And Regina King, the legend.
+Darius: Anna Maria is still with us. But quick interjection. Ezel, RIP. AJ Johnson, he is also not with us. He's not on the list. But I have him on my list as of an RIP as well. AJ Johnson, we lost him as well. RIP Ezel. We lost a lot of people in this list.
+Jordan: No, a lot of people in this movie. Yeah. so Friday, after getting fired on his day off, because how do you do that? Craig Jones spends a long Friday on his porch with his friend Smokey. The duo navigates neighborhood eccentricities, local bullies, and a drug dealer's looming deadline. Over 24 hours, Craig must find the courage to stand up for his future and also survive. So I'm gonna toss it to you for act one.
+Darius: Act one, the morning after, which After what? The Craig deals with the fallout of losing his job while Smokey introduces a high stakes problem involving a local supplier. They settle onto the porch as colorful neighborhood characters pass by. In the spirit, the beginning of the movie, the Jehovah's Witnesses pop by and Craig slabs door.
+Jordan: Mother Gibbs.
+Darius: In the spirit of ignoring the Jehovah's Witness, I have a confession. I ignored the carolers this year. Every year, little kids at the church down the street, they walk the neighborhood, they knock on the door and they sing carolers.
+Jordan: Oh, that's sweet.
+Darius: But it's odd though. I just didn't have it in me this year. So I just ignored them. I heard the knockings and they went next door and they sang for the neighbors. And I just, I had mad no mute the whole time. I was just playing mad. Keep on the door.
+Jordan: Christmas cheer.
+Darius: But I feel like there's a good place to get that off my chest. So what you got for act one, man?
+Jordan: Well, I can top that. So the Jehovah's Witnesses used to come by our house too. And my dad got sick and tired of it. So one day they came to the house and he just opened the door in his drawers and they never came back. You know.
+Darius: I get it. That's, what religious do. They have to recruit. But, I wasn't just, and honestly, the kids are sweet. I've opened the door and listen. I'm not a Grinch. I just didn't feel like it that day. I think it was cold too. And I was just like, man.
+Jordan: And it's like, do you sing along? Do you clap? What do you record them? What do you do?
+Darius: It's just one song, quick little 90 seconds.
+Jordan: Oh, it's one song.
+Darius: And you know, I got to hear them sing for the neighbors. It's an apartment complex. So, you know, you could really just do one and we could knock this off. And we all can hear it, you know? So what you got for act one, man?
+Jordan: Yes, I see. So this movie has like when it helped make a lot of careers. And also there's like so many legends in this movie, like, the Job's win is Marla Gibbs from Sanford and Son, you know, Esther, cousin Esther, Aunt Esther, you know. I also want to say that one thing that really annoys me is when you tell your mom something and tell her not to tell your dad something, and she goes and tells your dad that thing.
+Darius: As a grown-up, though, I do understand, like, They're married.
+Jordan: I get it.
+Darius: I get it. I get it. The parent, the parents are a unit.
+Jordan: Yeah.
+Darius: And they are navigating the household as a unit. And now you could. I'm almost certain that they tell every, you know, everything. It's just a matter of how you want it to, how you want to disperse that information. But like, yeah, I'm not if one of like, because they're her kids too. So like if my if one of my kids came to me with something and said, don't tell Your wife. I'm like, that's my wife. Of course, not keeping secrets from my wife. Now, will I tell her like, hey, this is what we're dealing with? You know, don't go do this. Sure. Yeah. But like, you can't. I'm not keeping something about your child from you.
+Jordan: The fact that she immediately told him like that night.
+Darius: Yeah. No, it's different. Like when you tell your mom something, she tells all her church friends, that's a violation.
+Jordan: No, yeah, that like, yeah.
+Darius: It's safe to assume with any married couple, if you tell one, you've told both. That's just the way.
+Jordan: Yeah, correct. Yeah, I view them all as a conglomerate, you know.
+Darius: That is a pretty safe assumption. One should always make.
+Jordan: 100%. Yeah, I remember I told one of my friend's husband something. I didn't tell my friend because I assumed that the husband was going to tell them. And she was like, why didn't you tell me? I'm like, well, I told him that's telling you.
+Darius: Most of my married friends, I just view them as like one person. Yeah. And so. Tell one, you tell all. Yes, but no, that is, I understand how Craig in that spot thought it was legit. Also like, you know, did you think he wouldn't go find out you lost your job?
+Jordan: He wouldn't go see you running the house all day.
+Darius: And getting fired on your day off is egregious.
+Jordan: That is crazy. I love that they never confirmed really not that he actually was stealing boxes.
+Darius: So there's a scene at the end of the movie where Ezale is like running with boxes, but maybe it was at the beginning. And Friday lore is that it was Ezale. And, but it wasn't Craig.
+Jordan: Yeah.
+Darius: But I mean, you got to keep in mind, 1995 camera technology was not 4K.
+Jordan: Also, getting fire for stealing boxes is crazy.
+Darius: Well, stealing anything will get you fired. It's not really the boxes. But so yeah, that's a piece of Friday lore that's never been confirmed or denied by anyone in the know that it was there's a scene where Ezel is just like running with boxes and they think that's him.
+Jordan: Yeah.
+Darius: But, Smokey had a point. You got to be a stupid ************ to get fired on your day off. You really, really do. Nothing. It was so dated because he's like, I had to go in and pick up my check. And I'm like, you had to go into work on your day off to get paid to. Yeah. Thank God. Thank God for direct deposit. But direct deposit have some ******* dated *** things. Yeah. What you got for a go about?
+Jordan: Yeah. So Ice Cube don't look no damn 22.
+Darius: No.
+Jordan: He looked a smooth 35.
+Darius: The budget was like 1,000,000 bucks, so there was like no makeup. And so he's just like, he's just wearing like, Like no one, the camera work is shoddy. No one is like in makeup. No, like the colors are all muted. And it's like, no, they didn't know. Chris Tucker did this. I think he did this for like 10 bands. Like it wasn't the, I think John Witherspoon said in a Vlad interview, they all made like $20,000 to do this.
+Jordan: Yeah, I believe it. Hopefully they had got a percentage of the back end.
+Darius: I don't know. I'm sure because he started actually he became a movie star, so.
+Jordan: Yeah, but I say he became a movie star. He got too big for it. Honestly, I mean, what would be the point? What was I going to say? Oh, yeah. So I love how the scene where I forget what the girlfriend's name is, but she calls him and she's like, Craig, I ain't heard from you, da, da, da, whatever.
+Darius: Where the **** you going to the show with last night?
+Jordan: Yeah, and she's laying him in the bed with another.
+Darius: I was. I think on my 30th view of this movie, before I do this, it took Twitter to tell me that was going on in it, because I never really noticed it. The dude was just laid out. He's just like, oh, you, who's your mama? That is insane.
+Jordan: That's crazy.
+Darius: And the dude was knocked out sleep. So whatever they did, he was out of it afterwards.
+Jordan: Yep.
+Darius: And That's Friday for you. Did you know Deebo was inspired by now arrested but legendary L.A. figure B.U. Big U. He did interviews with Vlad. The guy who recently he just got arrested for extorting rappers for checking in that guy.
+Jordan: Let's see. He was doing gang ****. Yeah.
+Darius: He was the inspiration for Deebo's character. Okay.
+Jordan: No, I think I forgot that.
+Darius: He's a known bully in South Central. known so much that he was basically inspiration for an iconic black character named Debo. People say he was literally just, by the way, like Debo would have just had to whoop my *** because you're not going to run my pockets like that.
+Jordan: No, In front of my house, at my own house.
+Darius: You pull it up and I got to hide **** bro. Just whoop my ***. That's less embarrassing. That's more dignified than just letting you run my pockets like this. You know.
+Jordan: Yeah. Also, I don't know how nobody shot him.
+Darius: Yeah, but the thing about bullies is it's like, even if you lose the fight, you still won. Letting them know that they're going to have to fight prevents it happening next time. Because people, they don't want to fight you.
+Jordan: No, not every day.
+Darius: Win, lose, or draw, I don't want to fight. And so I'm just gonna leave this ************ alone because he's going to fight. But I'm not, I'm gonna keep ******* with you because you're not gonna fight. So yeah, man, you just had to whoop my ***. And if you do, that's fine. You come back and we'll do it again tomorrow. But you're not just gonna punk me.
+Jordan: No, then I help you break into a house and I don't get paid for the **** that I helped you do. Are you kidding me?
+Darius: I got it in my notes right here. Got a little casual breaking and entering, you know, a felony with like a 10 year prison sentence. Guy drives off for work and they're like, hey, you left his window open. Would you like to come Have you been a felony this morning? Oh, sure.
+Jordan: By the way, the window that was open was protected by bars that they broke off.
+Darius: Just a wild, violent felony that they just decided to casually do on this Friday morning. And also like it was like, hey, you want to run to Chick-fil-A get some breakfast? Oh, yeah, sure.
+Jordan: Yeah, right, yeah. Like, let's go to the store and get some get some chips. That's like what they thought that thought of that was like. What is crazy to me because You're robbing people who have just as much or less than you.
+Darius: Yeah, this is the project. And also.
+Jordan: Yeah, I'm like, why don't I go somewhere nice and rob them?
+Darius: Well, I will. I will say is that people who live in the hood, they their world is quite insular. So like going.
+Jordan: Yeah, for sure.
+Darius: You know, going 30 minutes outside is like a *******.
+Jordan: It's like going out of the country.
+Darius: Correct. And. Stanley was clearly like the guy in the bad neighborhood who had his **** together. Who had ****. Yeah.
+Jordan: That car was nice.
+Darius: Every guy in one of those, like every neighborhood has like one of the dudes like that who just like kind of works for the post office and just has like a really good regular job. But in that neighborhood, that's really well off. And so that's kind of what I gathered from Stanley.
+Jordan: Yeah. I think he was like, the defendant for Kirkland. Remember, they'd be like, oh **** they got, they got black eyed peas. Yeah.
+Darius: You know, they're all, there are levels to it. You know, he took care of his grass, you know.
+Jordan: So yeah, he did. Speaking of grass, there's Parker. Who's out there watering dirt in our underwear?
+Darius: Daisy Dukes, you know.
+Jordan: Yeah, Daisy Dukes.
+Darius: Yeah, Daisy Dukes.
+Jordan: By the way, she's still fine.
+Darius: Oh, yeah. Oh, yeah, they did. I think it might have been AI. I'm old and get you fooled by the old, but they did like an age up of all the characters from all the movies. And yeah, Miss Partner still got it. Yeah, very much so. But bigger scenes, the biggest, bigger, biggest scene stealer. Bernie Mac, the ****** or Felicia?
+Jordan: That's tough. Okay.
+Darius: I just don't know it.
+Jordan: Yeah, I can't remember his name. I would go with the I'm going to go Felicia. I'm going to go Felicia. Yeah. I think it's hard to. She's the cause of the classic line. She kind of calls all the controversy and like some of the drama in the movie, like, you know, when he was about to get his money, she saw her in the background. That's why she didn't get, you know, he didn't get he didn't get paid. She's a crucial part of the storyline. Also, if she didn't get slapped, then Craig and Debo wouldn't have fought. So yeah, I'd say she's kind of like the linchpin of the movie, actually. So yeah, I'm gonna say, I'm gonna say Felicia.
+Darius: Yeah, it's tough to argue with a line so iconic, people usually don't even know where it's coming from. It's kind of like Stan, like people don't even know the song, but still say Stan.
+Jordan: Right.
+Darius: But man, Bernie Mac, man. Oh man, it's just, he's just Bernie Mac. Everything he touched, he just stole the scene on every time.
+Jordan: And by the way, that was like this one of the another 90s movie that he had the similar cameo in where he was just like an obnoxious preacher. Remember him in ***** **** with Jimmy Fox and Tommy Lee Davidson?
+Darius: What's the one with Bill Bellamy? How to be a player?
+Jordan: He had to be a player. Yeah, he had the same kind of role.
+Darius: Bill Bellamy was ******* his wife. Yeah, he. It's because when King of Kings of Comedy came out, he was like the guy no one had ever heard of. And so that's really what blew him up. But like on the underground scene, on the comic circuit, he was he was him. The guy. So yeah. Ready to get in act two?
+Jordan: Yeah.
+Darius: Act 2, the midday grind. The heat rises as big worms deadline looms over Smokey. The duo encounters a series of distractions from unrequited crushes to neighborhood thieves while trying to secure the necessary funds. My favorite part about 90s movies is they act like weed was like fentanyl. Like it is cracked or something, heroin or whatever. Yeah. Craig smokes one weed and completely in his mind.
+Jordan: It's like it was written by someone who had never smoked before, but you know Cube had smoked before.
+Darius: Oh yeah. I think this was like Cube's first script. And it was. Well, I mean, I would say it shows, but I don't know, to knock it out, to come up with a cult classic on your first run, you know?
+Jordan: Yeah, pretty good. I mean, I'd credit a lot of that to the casting. I don't know who was in charge of that. And also Chris Tucker was just otherworldly, you know?
+Darius: It used to be. I don't know what happened to the comedian pipeline, but like the black comic pipeline used to just be so ripe with talent. You could just do something like this and just grab some like Chris Tucker did a couple of Def Comedy Jams. I don't think his standup was that great, but like you could see the charisma.
+Jordan: Yeah.
+Darius: See, okay, this is going to translate to the screen. Yeah. And clearly it did. I mean, he's the biggest star of these movies by 1,000,000 miles.
+Jordan: Correct.
+Darius: If you just include acting, obviously Ice Cube is a, you know, rapper, but.
+Jordan: Yeah.
+Darius: I don't know. I don't know. I just wish. Okay, let me look like this. If they were to.
+Jordan: Yeah.
+Darius: Now I hate reboots, so no reboots. But like if we were to rewrite a script. Two guys from the hood get into shenanigans with new with new comedians. Who would you book for it?
+Jordan: You're talking about sketch or stand up or any.
+Darius: We can do IG, stand up, whatever you got. The characters got to be in the 35 though. If we can't, we not, you know.
+Jordan: Right. Okay. I would go. That's tough because I don't know if there are a lot of good young comedians out now, at least from what I've seen. I mean, okay. **** I can't remember his name, the Spanish kid from SNL. He's really good. I cannot remember his name, though. I would do, I'd obviously cast Drewski. Who else? I'm trying to think.
+Darius: Give me Drewski and DC Young Fly and make.
+Jordan: Yeah, that's why I was forgetting.
+Darius: And make DC Young Fly the comic relief, the Smokey, if you will. And they have Drewski just play it straight and just have them get it. It's just a 2026 Stoner Classic. Hollywood needs some new ideas. I keep hearing about a Friday 5. No, Ice Cube. It might be a great 50.
+Jordan: What the ****? Yeah, no, I don't want to see that ****. I don't. They had enough Fridays in their day.
+Darius: Next Friday came out before I was in Friday after next came out in 2002. That was my first year of high school. It's just over. You know, I don't know why.
+Jordan: Yeah, we should bring everybody back for what? Y'all are not the Avengers.
+Darius: Give me some new ideas, some new ideas out there.
+Jordan: Yeah, I agree. I agree. Yeah, I'd love to see like Drew Ski and maybe DC and Flying like a buddy cop comedy or something like that, you know? Yeah, there's not a lot of comedians now. I feel like that's... It's funny because... young comedians.
+Darius: I don't, I think would IG skit comedians go on stage, they're not very good because they're not.
+Jordan: Yeah, no.
+Darius: But a lot of them, I think, with a script and good direction could be in a conduct. Could they carry it? No, I don't think, you know, I think there's only a few that could actually carry roles. But, you know, I don't see.
+Jordan: I like Mark from RDC World.
+Darius: Mark, his acting gets a bit loud for me, but he's good. I think that's why I say with like good direction and good acting, the coach and producers, like there's talent out there for, the problem is just Hollywood just doesn't make these kind of movies anymore. So true.
+Jordan: Yeah.
+Darius: So in the sequels, did you miss Smokey or did Mike Epps hold it down well?
+Jordan: Yeah, I miss Smokey, honestly. I just think. No disrespect. Yeah, he's really good, but no disrespect to Mike Epps, of course. He's a legend. But I just think Chris Tucker is leaps and bounds. Like he's just one of the all-time greats, you know, and his levels to this. And that's just, you know, like Mike Epps couldn't have done the Rush Hour trilogy. You know, he couldn't have done Dead Presidents. You know what I'm saying? He could have done Money Talks. I just think Chris Tucker is different. Like I remember there's a story Jamie Fox tells where He was a comedian coming up or whatever. He was like, he was good, but he was kind of inconsistent, whatever. And he's like, I was in a really like down point in my, like I just wasn't confident in my ability at the time period. I had gotten too comfortable. And he's like, there's this kid that came out, this like tall, skinny kid and a white beater and some dickies. And he shut the place down. And he said, that kid turned out to be Chris Tucker.
+Darius: Yeah. I mean, He just, like you said, there are levels to it. And I do think the series missed Smokey. But, my day day was a good character, so I'm not too bad. What you got for act two, man? What else you got for act two?
+Jordan: Speaking of Chris Tucker, Smokey might have been the first person in history to ever be catfished. You can come by here.
+Darius: I won't call you. But if you don't come by here, I'm going to call you.
+Jordan: I'm going to call you. She already pulled up. He said she said like Janet Jackson. ***** got to call me. And it was Endel from the Parkers. No, that was crazy. You know what's bad? when the girl describes her friend as she's nice. If you ask what she looks like.
+Darius: This is the power of ***** because he was in the word like he's a drug dealer is threatening his life. He's trying to come up with the money, but he makes time for his blind date.
+Jordan: Right.
+Darius: Which I don't like what were they supposed to do?
+Jordan: That was she just stopped by to say hello, I guess.
+Darius: Well, this is This is 90s, man. You can you could you could date on the on the cheap. So just pull up and let's kick it on our porch with a date.
+Jordan: No food involved, no snacks, nothing. Just talking out the truck of your car.
+Darius: Parking lot pimping, man. What else you got, Frankie?
+Jordan: I always really liked the conversation that Craig has with his dad about like manhood and just fighting with your hands as opposed to using guns and stuff like that. But it wasn't 90s and it was a different time. I think those days are over, unfortunately, long over. And also I do, I will say, one of my pet peeves is just in like life and society is like telling people to be moral in like an immoral environment. I just find that to be Self-sabotaging, if you're in a lawless land, you can't operate by laws because that'll get you killed, Right?
+Darius: It only works if everybody abides by the laws and regulations.
+Jordan: Correct.
+Darius: You know, especially in this neighborhood where there's basically no police enforcement or at least going to the police is, you know, socially stigmatized. But I do understand what he means in the sense that, you know, the guns are forever. The black eyes gone in a couple days. There's the movie goes on later. Him and Deebo both went home that day, you know. Deebo, in the sequence, Deebo's in jail, but you know what I mean? No one died. And, you know, bar fights, you might get arrested. You might spend a weekend in the pokey, but you know, you're fine. But the guns, That's a lot more permanent for both parties. And so the wisdom is, I mean, I have in my notes here for act three and I was just like, man, it's so 90s that they did put the gun down. Yeah. But you know, you win some, you lose some, but you live to fight another day is great advice. It really is.
+Jordan: Yeah.
+Darius: I don't really have a more eloquent way to put that, but that's what I have to say. There's nuggets in here that actually do last.
+Jordan: Yeah, there is. It's a silly movie about nothing, but there is some good dialogue and messaging in here.
+Darius: I concur. Act three, the final stand. As night falls, the pressure reaches a boiling point with the dangerous confrontation. Craig is forced to choose between his father's wisdom and the violent reality of the neighborhood streets. How damn bad you got to be to do a drive by over $200. Over $200.
+Jordan: Like, and I know it was 90 cents and inflation is a thing. And I know they're in the projects, but $200 is not worth going to jail for the rest of your life.
+Darius: They use more than $200 worth of bullets. Right. You know, like just the ammo you use costs $200. Like they spray the whole ******* neighborhood. Like you, right, no aim, just shooting **** ******. Babies could be in the backyard playing ball, nothing. Just spraying for 200 funky asthma.
+Jordan: No, this is crazy. Yep. Yeah, that was insane. Also, like, okay, so say you did hit him. You're not getting your money. Good job. Now you got murder on your on your on your books.
+Darius: This is 3 strike 90s, man. You murder was going away forever. I know all of them dudes have felonies. All none of them guns is legal.
+Jordan: None of them. You are that car when registered. They don't have a license.
+Darius: Every single piece of this is illegal. Even the gloves you bought probably stolen. So you going to jail for the rest of ever over 200 funky *** dollars?
+Jordan: And the funny thing is.
+Darius: Smokey had a hundred. It was really, he counted out 20, 40, 100, 20, 100.
+Jordan: He had a hundred.
+Darius: Like you couldn't just let him, okay, give me the hundred. Wait a week. Whatever you do, you owe me to. I know he was smoking the weed too, but yeah, bro, if you kill your dealers, where's your money coming from? Faison, another.
+Jordan: Yes.
+Darius: What did this movie, you know? He's gone completely off the deep end now, but. Yeah, dog. Another.
+Jordan: Physically and mentally.
+Darius: Yeah, he's, he yelled glad just, just yelling. But.
+Jordan: Yeah.
+Darius: This movie. That's when you know it's over.
+Jordan: That's when you know it's over.
+Darius: They fit a lot of 90 minutes. They did.
+Jordan: They did.
+Darius: They fit a whole lot of that. What you got back there?
+Jordan: Oh yeah. One thing that was so unrealistic to me was after the house gets shot up and There's a whole shoot out there, Craig and Smokey are on the roof and **** whatever. And the bad guys leave and everyone in the neighborhood decides to come outside in the street to see what happened. Ain't nobody doing that **** in real life.
+Darius: Also, I know it's the hood and I know police are not great there, but like that kind of shootout has caused the police are coming. You got to stop that. Like all machine gun fire for a solid 90 seconds, right? Also like running and jumping into the hood of a truck and just like laying still like a little kid playing hide and seek. I'm gonna just lay real still and hope no one sees me. That's a wild gamble with your life.
+Jordan: When they here, I'll be quiet. When they leave, I'll be talking again. He'll be like, shut the **** **. I'll be like, okay.
+Darius: Bro. There's just no way I'm going to have this one dude in the neighborhood who can just pull up and shake me down for whatever nickels I have in my pockets. And I'm just gonna accept this forever. Right, what are you, what? So I can never have money on me in case he shows up.
+Jordan: I never understood that. Also, it's three of y'all, just jumping.
+Darius: As Smokey said it, man, let's jump him.
+Jordan: Like, I don't know why. You can't beat all y'all at the same time.
+Darius: What about the time he tried to choke me in Smoke's backyard? Oh, that was different.
+Jordan: That was different.
+Darius: You know, it's just as an adult watching it, I'm like, this is way less dignified than losing a fight. He just would have had to whoop my ***. Yeah. The idea that like this dude just can just.
+Jordan: Just steal everybody's ****.
+Darius: Just steal all of my ****. And I got to put it in everybody's house. I can't have nothing. You know, we good, bro. You just got to whoop me. And if you do, that's fine.
+Jordan: My grandma gave me that chain.
+Darius: Snatched it right off his neck.
+Jordan: Yeah, that was crazy, man. And that was a nice chain, you know, considered where they're, you know, what they had. Yeah, it was about to say. Oh yeah, and even like, another thing that was a little off to me was when there's like the final scene, everybody's outside after the shooting. And Debo slaps Nia Long for being mad at him for slapping her sister. And Craig's dad just like stands there. And I'm like, you just gave this whole speech about manhood. And you just sat there and watched another dude smack a woman and you just like, did nothing.
+Darius: I mean, he's an old man. You know, like there's a lot of young men there. I, you know, that's a young man's fight. And all those young men there, I mean, Craig did what he was supposed to do. Yeah, but I understand why. And again, it was his daughter. And yeah, he's an elderly man. I mean, John Witherspoon, I don't know how old the character was supposed to be, but you got at least what, 50s, all of his 50s. So yeah, that's a lot to ask old man to just stand in there and basically get his face punched off. Especially with all these young men watching it, you know, so. But Craig pulled up, beat up the bully, got the girl. And which one of y'all hollows got people shooting at you? Broke up with the crazy girl.
+Jordan: Yeah, broke up with the crazy girl.
+Darius: Not a bad day, not a bad day.
+Jordan: And got lined up on a low-key date with me along at the end, you know?
+Darius: Yeah, not a bad Friday. Oh, not a bad Friday at all. He's still unemployed. Still owns big workers money. No, Smokey got his money because he got it off a D-Bo.
+Jordan: That's right.
+Darius: Knocked him out. Smokey took his money. So.
+Jordan: And he got to keep his 100. So he basically made $100.
+Darius: Oh, the best part or the craziest part is like, Craig is down and out. You know, the drug dealer is going to kill him. And he's like, yeah, hey, sister, can you borrow me some money? And she laughs at him. And his mama laughs at him. I'm like, he's like, I'm going to die. Yeah, literally. Oh, I thought that was a little strange.
+Jordan: Like, yeah, it was weird. And nobody, nobody was willing to help.
+Darius: He's like, I am going to die if you don't give me $200. And granted, it was a 90s, but still we're talking about 200 bucks. You know, like, yeah.
+Jordan: I just want to ask for 20 bucks from everybody and find a way to get to it.
+Darius: A little, little, yeah. So, well, I guess my question is, you know, all movies create an archetype. This was the 90s stoner classic. Yeah, I believe it was the OG. What is the white counterpart?
+Jordan: To Friday? In the 90s or just in general?
+Darius: In general. I have a good one. I could start and you could just play off that if you want.
+Jordan: Yeah, I was going to say Pineapple Express.
+Darius: That's what I had. Pineapple Express right here. Is Pineapple Express the white Friday?
+Jordan: Yeah, I think definitely 100%. Yeah.
+Darius: Well, that was anti-climactic. That was my answer. Seth Rogen took that baton and rolled it.
+Jordan: He did, he did. He did an old career out of smoking.
+Darius: You can't underestimate how much this movie helped Ice Cube transition from gangster rapper to family movie man.
+Jordan: It did, it really did.
+Darius: He gets to play it straight. He gets to beat up the bully. He gets to bring the girl home. And all of a sudden he's in, are we there yet? Boom.
+Jordan: Yep, that's it. Are we there yet? 21 and 22 Jump Street. Ride along. Yeah, ride along. Ride along 2. What else? He basically carved a good movie career out for himself. You know.
+Darius: He's one of our legends. He's off the deep end now, but he's one of our legends.
+Jordan: What are you ready to move? I'm going to give this movie. I'm going to give it 3 1/2 stars. I love Chris Tucker. If we don't get this movie, we don't get Chris Tucker's career. He's one of my favorite comedic actors of all time. This movie has like 15 legendary lines. You know, Neil Long is in it. What more can you say?
+Darius: I'll piggyback 3 1/2 stars. It's 90 minutes, b</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out the Trunk podcast with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. You can find me on all socials at these all up in your area.
+Jordan: And today we're going to be reviewing Game Night. This movie came out in 2018. starring Jason Bateman, Rachel McAdams, Kyle Chandler, Jeffrey Wright, Billy Magnuson, Sharon Horgan, Lamorne Morris, Kylie Bunbury, Jesse Plemons, Michael C. Hall, Danny Huston, and Chelsea Peretti. I know it was a lot of names, but yes, the cast is that loaded with that many people that you do know from other stuff. So game night features a group of competitive friends who meet regularly for game nights and find their latest event turned upside down when a murder mystery party they are participating in becomes a real life kidnapping case. They must work together to solve the game before it's too late. So I'll toss it to you to set the table for act one.
+Darius: Act one, we're going to call the setup. Max and Annie, a highly competitive couple, are hosting their regular game night. Max is successful and charismatic brother, Brooks, joins in and plans a murder mystery party with the grand prize, a vintage car, which he claims is a real life kidnapping. Start off quick observation. Shout out homegirl. I have not seen her in a long time. A friend of mine named Liz. One time I was at a murder mystery, it was someone's birthday party. And I was at a murder mystery and I was the only black guy there. And just, it was a group of friends that just, it just happened to work that way. And so picking roles because you have to pick the roles for the murder mystery. Right. And you know how there's just literally it wasn't random. No one was trying to be funny. It was just like a random drawing from the hat. And I drew the criminal. And you're not supposed to tell people what you drew, right? And so Liz looks at my card and she looks at me and she goes, you want to switch? And I go, yes. And we switched. So shout out to Liz. I will forever be indebted to you for that because I did not want to endure that awkwardness all night. without telling anyone and she did it discreetly and I'll forever be appreciative of that.
+Jordan: So that's funny.
+Darius: Have you ever done a murder mystery game night type thing?
+Jordan: Yeah, actually, my family is really, really big into games. We don't have to get my super often, but when we do that, we go all the way with it. We did one, my mom had ankle surgery last summer. So she was out of commission for a few months. So we had a bunch of stuff at the house. People come over and see her because she couldn't really move and stuff. And so for her birthday, we did a murder mystery game that was really, really fun. And then so my couple months ago, my mom and aunts and my little cousins and my sisters, they did like a girls day where they did the murder mystery thing where they did the costumes and everything. So they like made like French bread and had little mustaches on and all the cute little costumes and stuff. So yeah, my family's big into that kind of stuff, the pageantry and all that. I **** with the murder mystery games. They're always fun, fun things to play.
+Darius: I'm not really big into playing pretend, but I'm a good sport about it. So, I could take it or leave it. But you got pregnant one, man.
+Jordan: So I love how the movie starts where it, because we all know that like one couple that just loves to like have events and host events and stuff. So that was very realistic. Also, I've been to a lot of bar trivia nights and that's about as real as it gets. They can get pretty serious. And they're always just really fun to do. I don't do them as much anymore because I just be busy during the week and also going out on Tuesdays is just not very plausible or smart at this point. I do want to say I want to shout out Jesse Plemons who plays the creepy neighbor because that dude is unnecessarily terrifying and hilarious in this movie and is an ultimate scene stealer.
+Darius: I call him our generation's Walter Goggins and just like the best character actor. He's just everything he and he just kills. Not quite handsome enough to ever be lead, but like every, always in a supporting role and he's always a character actor. And I've never known Walter Goggins or Jester Plemons to be in anything bad. And so if I see them on the rundown, I know the movie is going to be good.
+Jordan: That's a fact.
+Darius: Just like I call him our generation's Walter Goggins.
+Jordan: Yeah, he was even as a kid when he was in Mike, like Mike, he was a terrifying villain in that movie.
+Darius: He was in Friday Night Lights as well, right?
+Jordan: Yeah, that's right.
+Darius: And he was Todd from Breaking Bad was his like first real like, you know, prominent like, you know, he just he did the he has an HBO show where he plays the husband who has an affair with Elizabeth Olsen. And so that's really, he doesn't do, he doesn't miss.
+Jordan: Everything is good in everything. He was in Judas and the Black Messiah. I don't know if you saw that.
+Darius: I have not seen that, but I saw he was in it.
+Jordan: Was, that movie is incredible. He was so good. He had like, it was like a smaller role, but he was great in that movie. He plays like an undercover cop or, yeah, an undercover cop. And yeah, he was ******* fantastic in that one too. He's just, he's great in everything. I've seen him in. So I just want to give him his props. Also, I do want to say Jason Bateman is for my money, he's one of the greatest comedic actors of all time. I feel like I don't know why he's never mentioned with the greats, but to me of this generation of like great comedic actors like the deadpan guys, it's like him, Topher Grace, I'd go, who am I thinking, who am I forgetting? I'm forgetting somebody, but like the guys who just are great at the deadpan with the wit, with the sarcasm, he's Ben Stiller, that's what I'm thinking of. He's right there with anybody to me when it comes to the comedic timing.
+Darius: I think he'll get his props because most people prefer over the top physical comedy.
+Jordan: That's true.
+Darius: It's not my cup of tea, but that's usually, people prefer to be told when to laugh and not to get the joke.
+Jordan: So that is true.
+Darius: If you had a house in the suburbs, would you be the hosting couple?
+Jordan: I probably would. I'd be definitely for sure. I thought that'd be fun. Well, at least maybe like before the, if I had kids, like if I had kids, maybe not so much. That's just a lot of, lot of **** going on. But if I'm just a single, not single couple, but a couple with no children, then we'd probably be doing a lot of hosting for sure.
+Darius: You remember that time, you remember the R&amp;B group TGT, Tank, Genuine, and Tyrese. It went, someone I think it was Tank left and Tyrese said him and Ginuwine were about to go solo together. He was like, we kicked Tyrese out the, we kicked Tank out the group. So Ginuwine and I are going solo together. That's not what those words mean.
+Jordan: What else you got for act one? Oh yeah. So one of my favorite scenes in the movie is when they're coming back from like the grocery store and they see the neighbor and he's like petting the dog. He's like, hey guys, And they're like, he's having a game night and they're like, no, we're just going to go home and eat. And he's like, but you got 3 bags of scoops. And he's like, yeah, they run special.
+Darius: Which, you know, they don't go bad.
+Jordan: They don't go bad. Also, the bag is half air. And also I can **** ** some nachos. I do love chips and salsa, so I could be late any day of the week. But yeah, I just thought that scene was hilarious. Even when they get in the car and he's like, what? and they're like no one said anything.
+Darius: And the dog that his wife left him for what else you got for act one?
+Jordan: Okay yeah so on so do you have obviously so you're not being like murder mystery games but like is there like do you have go to games like when you're at a game night or if you were to have a game that where you're like okay I can beat anyone at this game.
+Darius: Oh black people or white people that's important.
+Jordan: That is a good correct That's a good. Okay. So let's do both. Let's do both. Black game night and white game night.
+Darius: Black game night. We're going to get some Uno going.
+Jordan: Okay. How do you how do you play? How do you play Uno? What are your rules?
+Darius: I go by. I mean, I'm flexible. So whatever the house wants to do, but we normally we allow stacking.
+Jordan: Okay. Colors and numbers.
+Darius: Numbers. Okay. So no colors and numbers. You're right, but I'm flexible. House rules. White game nights tend to be more. Less card focused. Pictionary. Pictionary. What's the one where you're that is Pictionary where you're drawing, right? Yeah. What's the one where you just yell out clues?
+Jordan: Charades.
+Darius: Charades.
+Jordan: Or taboo.
+Darius: Yes. There's also this is getting really nerdy. Settlers of Catan. depending on how nerdy the crowd. That's super nerdy. And so just depends. I'm flexible. I can play it all. But my go to would probably be charades on white game night and black game night. So how about you?
+Jordan: White game night? Actually, I don't even know if I've ever been to a white game and now think about it.
+Darius: Just like when you said you pretended you didn't know a backstreet song last week. No, I'm so black. I don't listen to that with white people ****. I didn't even heard a backstreet song before. Cut it out.
+Jordan: No, I don't know. I **** with Nsync. I **** with Backstreet Boys. Let me see. I'm trying to think. Probably like maybe like Scrabble or something like that.
+Darius: Scrabble is a fun game. Scrabble is it doesn't scale. It gets just once alcohol gets involved and there's like a larger group, it just gets to be. It's just hard to do.
+Jordan: That's true. And then Black Game Night, Taboo or Uno. Yeah, I'm really, really good at Taboo.
+Darius: What else you got for Act 1?
+Jordan: Heads Up is a fun game too, also. I'm a really slept on game. And you can play it anywhere. Yeah, okay, so I wanted to ask you, so there are some people who treat like game nights and like couples game nights as like a litmus test for like the success or health of the relationship. Do you have like, have you ever seen that or?
+Darius: No, that's a little too deep for me. No, because, okay, it's rare that there would be a couple where that was my only, like, sample to use. So, like, if I'm at their house for a game night, I've usually hung out with them in other venues. So I doubt that I would just use the game night as like a live test. And if it's a couple that I don't know at all or I've never hung out with and it's just like a friend of a friend, I don't care enough to do like, I don't care. Right, right. Will they make it? I don't know these people. So like, if I know them well enough to care if they make it, I would have a larger sample than just that game night. So to answer your question, though, I would not use it as a litmus test, litmus test for game night.
+Jordan: Okay.
+Darius: But, you know, it's I don't know. I don't know if it means anything, to be honest with you. Like, I mean, obviously, if they hollered and fussed and throwing **** that's not a good thing. But, you know, the way they interact with each other on the game, I don't think means anything bigger is without void of context, anything outside of that, you know? So.
+Jordan: Right. Got you. I think. Yes. I have for game one or game one act one.
+Darius: I mean, game one would work. Well, we're going to go into act 2, the game unravels. The group believing it's a game, witnesses a staged kidnapping of Brooks and begins following clues to rescue them. As they get deeper into the mystery, the lines between reality and the game blur and they realize the stakes are much higher than they thought. You have to know something once and start getting thrown through tables. Yeah, bro.
+Jordan: They were, they tore that plate, they tore that kitchen to pieces.
+Darius: Like that one?
+Jordan: And they were like, and they're like, wow, they're really method.
+Darius: Yeah, like they're destroying tables. Like you can't fake this. You think these people, how much do you think they're getting paid to be thrown through a table?
+Jordan: Like, you know, like they're literally bleeding and punching each other in the face.
+Darius: That's where the movie started to lose me. I was like, all right. Can we get some more Jesse Plemons? Cause this is this stuff. The Denzel bit was funny. I thought that was funny. Yeah.
+Jordan: That was a pretty good impression. Yeah.
+Darius: That was probably my last like laugh out loud. Where he was like, what do you drive? BMW. Three. That 3 series is the baby beaver.
+Jordan: They remember he was like, So what his house is like, she's like, he had a two-bedroom condo. She's like, and a room he used for an office.
+Darius: He's like, well, okay, so it is not unusual. This is not unusual for a wealthy, famous person to have like a very nice house in the suburbs where he keeps his family and then a condo in the city where he does his dirt. So it does that in and of itself. That doesn't mean it's his primary residence that he took to a condo. That's true. You know, there were a lot of football teams just like, let's say, you know, you work for the let's say you play on the Panthers basketball team, whatever. Charlotte, a lot of them will just like rent a spot to do whole **** together. And just pass keys around and that's a fact. And then they go in the suburb. So that's true. The condo alone is not, it wasn't Denzel. The picture was funny, but like it's entirely possible for a wealthy, prominent man to just have a spot to do some hoeing in that's a bit less extravagant than the home he actually.
+Jordan: That's true. Like, have you heard about the house the Cowboys had in the neighborhood? We called it the White House. You have to say the White House. Yeah.
+Darius: So that is not an unusual circumstance. That's just because we heard about it because it's the Cowboys, but that is a prominent fact.
+Jordan: That's true.
+Darius: Steve McNair got killed in his hope head. That was a two-bedroom condo in the city of Cincinnati, Tennessee. And his mistress killed him there. That's just where he took his hose. But that wasn't his house, you know, right? So no, it's not about that. So that's true.
+Jordan: But no, that **** was crazy. I would. I would never let that go. No, no, I would never let that go. Like, so remember we thought you ****** in jail and it was a dude.
+Darius: Yeah, it was just a dude. Just a dude. And a three series beamer and a two barrel condo. Troy was bad, though. I got.
+Jordan: Yes, she's fine. So I know.
+Darius: But yeah, because she's not a great actress, but she's fine as hell.
+Jordan: Yeah, she was in a I first saw her in a movie with Jonah Hill called The Sitter. It's like this really funny comedy. I was like, Oh my God, who is that? Yeah, I don't know. She's not more stuff. I mean, I guess we get it, but she's very beautiful.
+Darius: She's not in a lot of stuff because she can't act. But what else you got for act two?
+Jordan: Oh, yeah. So I love the bar scene where they go to track down his brother. And they still think it's a game with that, but they don't know that it's real. And then they, she's like, get on the floor, hands on your knees. Or no, what'd she say? Like hands in the air, put your face on the floor. And the guy's like, I don't know how to do that.
+Darius: Yeah.
+Jordan: And she's like child's pose, like yoga. And she's like holding the gun like it's like a frisbee, just all willy nilly in the air. And then they finally realise that it's serious when they see their brother.
+Darius: Yeah, tied up and beat up and he's just like, no, this is not a game. This is real.
+Jordan: I'm about to die.
+Darius: I'm about to die. You're here to rescue me. Yeah, so I thought that was funny. Like she kept the bad guys at bay and didn't even know she was doing it.
+Jordan: Right.
+Darius: So yeah, that was humorous. Would you want to know if your girl knocked down a celebrity?
+Jordan: That's a good question. I actually was thinking about asking that too. Yeah, I wouldn't. I would want to know.
+Darius: I wouldn't care as long as I ain't wearing the jersey anywhere.
+Jordan: Yeah, like I wouldn't care. But I just out of curiosity, I would want to know.
+Darius: You know, I take the what I don't know won't hurt me as long as it was before me and you ain't got me wearing the jersey. Like that's true.
+Jordan: Yeah. Like if it was not during us, it's fine. I don't, you know, if you know he picked you up on the sneak, you can take that to your grave because that we'll just call it a hall pass and leave that alone.
+Darius: If your girl is bad, someone prominent has DMed her before. That's just.
+Jordan: Yes, that's true.
+Darius: It's just that's just the game. The game is the game. Everyone has access to everybody now. So that's a fact. It's just it's like my boy was like, I don't want to I won't use his name, but he just he He found this picture of his granny. And he just one day was just like, I don't even want to know how my granny got a picture on Al Green's tour bus. Like, I don't even know.
+Jordan: Oh my God.
+Darius: Why are you on Al Green's tour bus, Granny? I don't, even, I don't want to know. Like, I don't want to know. He was like, I was going through the photo albums and she was on Al Green's tour bus. And I'm like, I don't even want to know.
+Jordan: Yeah, I would never ask that question. I remember even like a few years ago when the Freaknik documentary came out.
+Darius: Yeah.
+Jordan: And we were hanging out at open mic and my boy Will was like, hey, did y'all y'all's friends today with the Freaknik so y'all can know whether or not you need to watch the documentary.
+Darius: It's a whole lot of marketing directors and attorneys and administrative assistants that got some Freaknik footage floating on the world. We all come from somewhere, man. Your parents wasn't always old and lane, you know? Yeah. he was like, man, she was on Al Green's tour bus smiling. That's wild.
+Jordan: Oh, no. Damn, that's crazy. Well, at least that's how you know she was good looking.
+Darius: Hey, you know, Granny was outside. She was out.
+Jordan: She originated outside.
+Darius: Circa 1975. She was she was whatever black perversion of Woodstock was. She was there.
+Jordan: Right. Yeah. She was out just after Brown People Board of Education. Yeah. She was outside with Ruby Bridges.
+Darius: Yeah. She was at, she was on the chilling circuit. Put sending it out.
+Jordan: What else you got cracked? That's crazy. Okay, so after they all kind of reconvene and figure out that **** has gotten, **** has gone left, they go to the weird neighbor's house to use his complete police computer.
+Darius: And he has a picture of them. And he's like, you don't have a picture of all your best friends. Oh, we established we were best friends.
+Jordan: Best friends.
+Darius: Jesse Plemons is the only saving grace for this movie, man, because he really was a star of this movie. He was like, you have a picture of Gabe now? He's like, you don't have a picture of all your best friends. I don't want to be eaten by you tonight. So I'm going to shut up. Yeah, that was funny.
+Jordan: And then even he had like the shrine to his ex-wife in the office.
+Darius: Yeah, he was. He killed it.
+Jordan: I actually would like to see him. I would love to see him do more comedies because I feel like his chops for that are underrated.
+Darius: Yeah, it's true. I mean, he could, he's so, again, he's our Walter Goggins. He's so versatile. Yeah. He could do it all. He does. I mean, he's done funny. He's done, you know, drama. He's done evil. He's done good guy. Yeah. You can name a situation where he didn't do great. Maybe the movie wasn't always great because I don't think this movie was great, but he always steals the scenes he's in. Correct.
+Jordan: Yes.
+Darius: So I want to, earlier I say he's never been in a bad movie. That's not true because I'm about to get this movie report rating. But he always steals the scenes he's in. Yeah, that's true.
+Jordan: That's a fact.
+Darius: I never, every time I leave the theater, I'm going, I'm thinking about what the scenes he was in.
+Jordan: What he did, what he said.
+Darius: And that's prominent in my mind, even if whether the movie was great or not, that he's who I'm thinking about when I leave the theater.
+Jordan: Yeah, it reminds me of, there's some advice that Tom Cruise gave to Glen Powell to actually convince him to take the role in Top Gun. Because he auditioned for Maverick, he didn't get it. They'd offer him a smaller role and he was like, I'm good. And Tom Cruise told him, he was like, you know, I don't make great movies. I'm in movies and I make them great. Yeah. basically play all, no small actors, just small parts, so on and so forth, whatever. But he just puts a 50 every time he's in a role. Like he's never, the movie may not be great, the movie may not win awards, whatever, but you can always go and see a movie that just comes in and you'll know that you're gonna know, you're gonna walk away impressed with whatever he did in whatever scenes he was in.
+Darius: Speaking of Glenn Powell, Fraud alert. We need.
+Jordan: They tried to make him like the next Tom Cruise. They did, they did, they tried.
+Darius: He was in that rom-com with Sidney Sweeney, another fraud alert.
+Jordan: Anyone but you, yeah.
+Darius: And I just, two very, very attractive, young, fit people, not sure the acting chops are there. So putting you on fraud alert, you got a couple more duds before we're out.
+Jordan: Yeah, that's true.
+Darius: What else you got for act 2?
+Jordan: I think that's pretty much all I got for act two, because I got act three starting where they go to the kingpin, whatever you want to call him's house.
+Darius: Act three, we're going to call this the high stakes finale. With their lives on the line, the friends race against time to save Brooks from a perilous situation. They use their collective skills and knowledge to outsmart the criminals, leading to a climactic showdown and a shocking revelation that changes everything. This is where the movie collapses into one long, pointless chase scene. And it was tough. It was, they ran out of movie. They literally were just like, yeah.
+Jordan: It's like, we're just going to do wild **** in here. We're going to have a chase scene. We're going to fight on a plane. There's going to be a fight club in it.
+Darius: My God, this third act was rough. It was like, man, they are out of movie. They need to get to the end, but they're contractually obligated to get to 90 minutes.
+Jordan: And yeah, I think they had about 75 minutes of real time movie and they had to throw in 20 more minutes.
+Darius: Man, it was rough. I don't really have anything for act three because it was God awful.
+Jordan: Yeah, the whole thing about like they tried to do like the character development thing, but they just didn't go because they were like, you don't want kids because you want to be like your brother. And that's why you, like they.
+Darius: Didn't make us care about the characters before that, though.
+Jordan: So that's the right. That's my point. That's the problem.
+Darius: You can't. You know, these are just NPCs going from, you know, and so at the end, you're trying to drop an emotional revelation that no one cares about because we don't know these people.
+Jordan: Correct, because you tried to reverse engineer the lack of plot development or character development. I think they should have shown like, they should have started off to me. I would have started the movie off with like scenes of him and his brother as kids playing games and him just losing nonstop at games. And then I would have cut to the scene of him being at trivia night and meeting the girl. And I feel like that would have brought things together a little bit better personally, just from a story compelling perspective.
+Darius: I'm fine with the dumb comedy with the thin plot that doesn't really makes sense, but it has to be funny. And this movie just wasn't really that funny. You know, if you take Jesse Plemons out of it, there's like the funny white joke at the beginning where, you know, he makes the name something that's superior. She says, white people. I laughed at that.
+Jordan: Oh, yeah, yeah.
+Darius: Denzel bit. I laughed at that. Everything else was just a token chuckle. And I just.
+Jordan: Correct.
+Darius: So you have a comedy. with the flimsy plot that isn't really all that funny. What do we have here?
+Jordan: And we have nobody to really root for.
+Darius: No, there's no. Like I said, they held me together until act three when they clearly ran out of movie.
+Jordan: Correct.
+Darius: And yeah, they didn't land this plane.
+Jordan: Yeah, like even like the hang. If we talk about one of the greatest comedies ever, of course, we're not prepared for that, but just following the template of something a story that takes place over basically 12 hours. the hangover, they took about 20 minutes to show their lives before the hangover. You know what I mean?
+Darius: And also it was funny. The hangover was funny. And it's funny. Hey, you know, like there's still quotes paging Dr. derogatory. You know, it begins with F, you know, like the weird speech at the Wolfpack speech.
+Jordan: Oh, we're looking for strippers and cocaine.
+Darius: Yeah, like just, it was funny.
+Jordan: One of my favorite lines of all time from that movie is when Stu was losing his **** and he's like, I gave you guys drugs, whatever. He's like, Doug could be faced out on a ditch somewhere with a meth head, but ******* his corpse.
+Darius: The ***** pack. That was funny.
+Jordan: Yeah, the ***** pack.
+Darius: They run into Mike Tyson. That was funny.
+Jordan: Yeah, the tiger. It was funny.
+Darius: This movie, Game Night, just didn't, it wasn't, it didn't bring jokes. And if you, I don't mind a, like Friday, it's one of my favorite comedies. That movie, nothing happens in that dumb.
+Jordan: Nothing happens in that movie.
+Darius: But it's funny. everything doesn't have to be Citizen Kane. I'm not that movie critic, but like, you have to do something well. This didn't do anything well. Like, you know, like, it's rough. It was rough, man. I don't, I hate to be, you know, because I bashed the movie last week. So I don't want to be the guy that's just overly negative, but I'm not. I didn't like, you know, And this is funny because I picked this movie. It just was. I saw it in 2018 in a theater. I don't know if maybe I was high or something.
+Jordan: I don't know. I remember it being better.
+Darius: Not held up.
+Jordan: Yeah.
+Darius: I also just think things are funny in a theater because comedy is contagious. Laughter is contagious.
+Jordan: Yeah.
+Darius: So you're harder to make laugh sitting at home on your couch, which is why I think, you know, like comedy, every comedy you like on Netflix is way funnier in person because laughter is contagious.
+Jordan: That is true. Also, I think the thing with comedy is, unlike thriller and action and rom-coms and **** is it can only hit at its best the first time.
+Darius: Correct.
+Jordan: Like, so every time you indulge in it or to experience it, gets a little let, it loses quality in a sense, because humor doesn't always have a great repeat value, you know? It's not like rap or, you know, music or, you know.
+Darius: Or it's so funny. that you watch it three or four times and it's really funny and you just grow to like the plot. Like Friday, I like the plot, even though it's not about anything, Right. House parties like that. movie ain't about nothing. But like you stick around long enough because you like the funny and the rap battle and the dance battle. And sooner or later, I just start liking the plot.
+Jordan: Yeah.
+Darius: I don't see myself getting there with game night. I don't think that's going to happen. So Yeah.
+Jordan: I mean, we got the, there's like the twist where at the end where it's like the first part of the setup was fake. Or yeah, it was fake that they thought was real was fake by the creepy neighbor. And then they're like, okay, cool, we're good. All right. And then he gets shot. And then they realize that the other guy is real. So that was like a twist on the retwist. I'm just trying to recap the movie, but that's pretty much it, honestly.
+Darius: Lag over the play, unsportsmanlike conduct, loss of down.
+Jordan: Yeah, they saved the day. That's pretty much it, honestly. I don't really have much to say about this movie. I will say though, Bring back cool credits in movies because I did love the credits in this one where they have like the it kind of shows that he'd been stalking them the whole time and it's got like, the cool little special effects and ****. As a movie guy, it's just like **** I like watching.
+Darius: But yeah, this movie was not off fast enough.
+Jordan: This movie was not great. Sorry guys. We're going to have a good one for you next week.
+Darius: What do you rate it, man?
+Jordan: I'm going to give this one. I'm going to give it two stars.
+Darius: I'm going to give it two as well. I saved my ones for totally unwatchable garbage. Yeah. This was watchable until the last 15 or 20 minutes. It just, yeah, it just doesn't hold up well. I laughed more than a handful of times. And if you can make me laugh a handful of times in 1/2 an hour, you got it too. So, all right. Thanks for listening. My name is Darius. That's these all up in your area on all socials.
+Jordan: And I'm Jordan. Jordan be riding on all socials.
+Darius: Please rate, like, subscribe. We are out the trunk pod on all socials. That is out the trunk pod on all socials.
+Jordan: And for any ongoing movie recommendations, feel free to reach out to us via e-mail. We do check it daily, so we will hit your back at out the trunk pod at gmail.com. That's out the trunk pod at gmail.com. That's a wrap. Thanks for coming to the movies with us. We'll be back next week reviewing. Good boys. Thank y'all. Take care.</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. I'm Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's these. I love the area on all socials.
+Jordan: And today we're going to be reviewing the movie Good Boys. This movie was released in 2019 starring Jacob Tremblay, Kenneth L Williams, Brady Noon, Molly Gordon, Midori Francis, Will Forte, Lil Roe Howery, Retta, and Millie Davis. Good Boys is about 3 6th graders named Max, Lucas, and Thor, like God of Thunder, who find themselves in a series of misadventures while trying to attend a party. Their journey involves a stolen drone, a desperate quest to replace it, and navigating the complexities of their friendship and the cusp of adolescence. I'm going to toss it to you to open up for Act 1.
+Darius: Act one, we're going to call the pre-party panic. Three pre-teen friends are invited to their first kissing party. Their mission to learn how to kiss and fit in leads to a series of escalating missteps, including a disastrous drone theft. First observation question off the bat, is this like a sort of like a modern take on super bad? Is that what we're trying to, what we're going for here?
+Jordan: Yeah, I think basically that's kind of what the vibe was. Yeah.
+Darius: All right. Makes sense. That's kind of what I was thinking. when I was watching it, I was like, this is just like a prepubescent super bad.
+Jordan: Yeah.
+Darius: So yeah, it is amazing how much older teenagers seem to them at that age.
+Jordan: Right.
+Darius: You're watching the movie through the eyes of them and all of the teenagers just they seem older to me watching it because of through the eyes of the kids. But right now they're they're like 14, 15 years old at the time as well. So interesting now.
+Jordan: Yeah.
+Darius: But you got fract one.
+Jordan: I love how this movie does a great job of perfectly illustrating like how stupid kids are.
+Darius: Yes.
+Jordan: Because like, it's just you just think about like all the **** we thought as kids, like the rumors that we heard, like, remember we were kids and it was like, Sierra's a man and like, or like, or like, I'm trying to think like you could get like, some sort of disease from drinking the water fountain or like the stupid **** that we believed as kids. This movie did a really good job of like showing that.
+Darius: Or like the, like there was like this little muck lake around and we thought that it was like a monster in it. And it was like, yeah, No, it's not a thing. So.
+Jordan: Yeah, I remember like in my neighborhood, there was a rumor of there was like, there was like a haunted house and like some girl died there.
+Darius: Like evil old lady on the block.
+Jordan: Yeah. So I wanted to ask you, when you were a kid and you were first, if you ever did this, I don't know, whatever, but when you were first on the internet, looking at girl **** or inappropriate **** whatever, did you ever get caught doing any of that stuff when you were a kid?
+Darius: No, because I was always more tech savvy than my parents. So I knew how to delete my browser history. But yeah, certainly, certainly indulged, which not to make, not to get all deep, but like, Right. It's like, obviously I turned out fine, but like one, the first exposure was like 14. So it was just not obviously old enough, but like, right, a ******* grade school. And two, it was on the family's computer. So like there was an element of of a friction there. Now, I couldn't imagine being a parent with, you know, every smartphone having just three clicks away from like graphic ****.
+Jordan: Right.
+Darius: And you, you know, you have to decide if you're going to get your eight-year old one of these **** machines, basically. Right. Like, man, we're a long way from, you know, me, you know, stealing your dad's magazines to whatever the **** you could find.
+Jordan: Or like. Yeah, I remember when I was a kid, like, it'd be like we like if my dad like my dad used to like fell asleep watching TV, like downstairs, whatever. So sometimes, you know, it'd be we watching like whatever movie and then, you know, late night cable would come on and Like me and my brother, we'd like, at the edge of the stairs, look at, I'd be like, look, at that on the TV, **** like that, whatever. And now it's just like everywhere. Like you can just scroll Twitter and it's like right there. I'm sure you see on Instagram. It's like, how is this able to post on Instagram? Like, that's crazy.
+Darius: Dude, as someone who's recently returned to office, I had to turn off auto videos on Twitter. Because people do not respect back. So I haven't worked in the office in roughly a decade as the audience knows at this point. But back then there was like a daytime truce on posting wild **** because there was an understanding that people were at work. You were at work. Not no more, man. Especially that for you tab. No, yeah, And like I know like my Instagram algorithm, at least that's sort of like tailored to me. so it's I don't really get too much of it on there, but there's some like I say my for you tab is basically sneakers the gym cooking an *** and But it's like tasteful ***. It's not ****. It's just me, you know, IG models and stuff.
+Jordan: Yeah, I feel you. Yeah.
+Darius: In their profile, there's a link to probably something more explicit. But the actual IG pictures are tastefully lusty.
+Jordan: That's hilarious. And I remember, so we had a, we had a family computer. I think my dad may had to work a lot of time at the time, whatever. But I remember I was like 12 and I first started like looking for **** on the Internet and I didn't know how to delete history or anything like that. And my dad's a software engineer. So, you know, God. Yeah. So he was one time he was like, you remember saying, I want to talk to you. I'm like, yeah, what's up? And he's like, he started listing names of the actors that I was Googling, so to speak. And I was just like, no, I don't. That name didn't sound familiar to me. And then they were like, yeah, no computer for a month.
+Darius: No, I never got caught because I knew my parents weren't tech savvy. And so, well, let me tell you, stumbling upon as parade.com for a 14 year old boy is like, it's like finding a pot of gold.
+Jordan: No, yeah.
+Darius: Oh, just like that. What was it? Darkling where he's jumping in the pool of the dark wing.
+Jordan: Yeah, yeah, yeah.
+Darius: That's that's kind of what it was like.
+Jordan: No, for me, it was a, it was a, the ones I liked when I was like a kid or whatever, kid, teenager.
+Darius: Don't really have to say it.
+Jordan: Oh, yes.
+Darius: It's fine if you don't want to do that. Yeah, yeah, yeah. I went for the most like, you know, benign one for **** right? But yeah.
+Jordan: Yeah.
+Darius: Well, this was back before, like now, this is like, there was actual websites and now it's just YouTube, but ****. And it's just way, again, still inappropriate, but just much more appropriate within its inappropriateness. Like, Correct?
+Jordan: Yeah, it was tastefully distasteful.
+Darius: Again, man, I wouldn't give my kid a smartphone until they were a teen, and then they're like 16 years old.
+Jordan: Yeah, no, it's pretty crazy. And all these ads where you can like message people in other countries and **** it's just really, yeah, it's crazy.
+Darius: I think schools should ban them. I don't think parents should get their kids them. Every parent you tell about school banning phone, they start talking about school shooters. First of all, you're not John Wick, ain't **** you can do. You ask, you ask them like, well, what happens if there's a school shoot? I'm like, what the **** you going to do?
+Jordan: Like, by the way, you them texting you, they get them killed.
+Darius: Right. You're just, first of all, do you want a hundred teenagers texting and calling? You're just signing, you're just putting up a red flag of where to shoot you.
+Jordan: Hey, we're over here. Yeah.
+Darius: Furthermore, it confuses law enforcement. Like law enforcement has to coordinate a counter and to get these kids out. And if you have, if you're telling your kid to go here and Right. I get it. You want the illusion of control, but that's all it is. It's an illusion. You're only going to make it worse texting your kid during an emergency like that. And you know, I get it though. But yeah, I feel you. They are so bad for learning. The content on them is so inappropriate for children. I just don't even know how it's an argument. Ban them from schools. Anyway, I don't even know how we got here, but where are we at? What else you got?
+Jordan: Yeah, so there's a scene where they're riding bikes, like the opening scene with all three kids. And they're like, we're 6 graders now. And then the kid, Thor, he's like, yeah, and in 6th grade, everybody gets a **** ***. And they're like, what's that? And he's like, it's like when a girl jokes you off until you ***.
+Darius: A little early, buddy. That's like more 9th grade, 10th grade. Right. You know, it's. A little early, right? Sixth grade, you're still making out. You know, you might. Yeah, yeah, yeah. Grab a butter, too. But, you know, the **** *** started about the ninth or 10th grade, you know?
+Jordan: Yeah. If you have a healthy childhood.
+Darius: Fair. If you have a few. Yeah. Let's get out of here before we get in trouble. Do you remember your first beer? Yes. Do you remember your first beer?
+Jordan: See, I don't. I think. I mean, I think when I was like maybe like 12 or 13, I like took a sip of like some of my parents like liquor one time and I obviously didn't like it. Like, I think I tried like some hypnotic. I was like 13 once. Like, I don't remember my first year, though. I think I think I might have been in college when I had my first beer.
+Darius: I was in eighth grade. We were we got some ********. We and we were in the woods and a guy out there was just drinking beer. I don't know why he was drinking beer in the woods. You know, whatever. He was just like, he just gave us a beer and we split it and we sipped it. was nasty as hell. I don't even remember what kind of beer it was. It was ****** beer. But I remember it. It's my first sip. The weed was ********. Don't even think it got me high. I don't even know if it was weed. But I definitely remember it because I was in the woods with my boy Kyle, my boy Quincy. And we had a beer and some ****** weed. So anything else for act one?
+Jordan: Oh yeah. So even like when they're in, when they're drinking the beer, like in the one like cool kid, he's like, oh, I think I'm drunk. Like, it's just like really like the way kids lie is crazy.
+Darius: Like, well, if you have zero tolerance and you are in the sixth grade and you drink actual real beer, drunk? Probably not. But I mean, I imagine that, you know, I remember in the eighth grade, like those two sips, I was not normal. And so you have no you have no tolerance for it. And you're all in your body. I mean, there's a reason why they have age limits on these things.
+Jordan: Right.
+Darius: It's not just to be annoying. It's because you should not give a developing body poison.
+Jordan: Yeah.
+Darius: Yeah. So.
+Jordan: Also, I thought it was funny where they were at the skate park and the cool kids had scooters. It just makes me think of when I was a kid, the coolest thing in the world was like those Heelys, like the shoes with the wheels on the back.
+Darius: Yeah. Did they light up?
+Jordan: If you had those, you were, yeah, if you had those, you were like a Jetson or some **** like, you know.
+Darius: Our other bikes, man, if you had a cool little Schwinn mountain bike or not mountain bike, the little joints with the, you know.
+Jordan: With the BMX things.
+Darius: Yeah, we would. Man, Saturday, I'd do my little chores in the morning. I would leave and I'd just be gone all ************* day. I, you know, have no idea where I was.
+Jordan: Yeah, For us, it was like, yeah, if you had a bike, you basically had a car. Yeah, pretty much. And if your bike had the kegs on it, you were cool as ****. Like I remember like I got, I was big into like BMX and **** like that. And like, I love like Tony Hawk and stuff as a kid. So I had like a little ramp and like a little skateboard and all that ****. Like you can tell me ****.
+Darius: Got anything else for act one?
+Jordan: And that's all I got for act one.
+Darius: Act two. We're going to call it the desperate scramble to replace the stolen drone before their parents find out the boys must embark on a wild adventure across town, encountering high schoolers, rebellious girls, and facing unforeseen obstacles in their quest. This is definitely. It was obviously like a present day movie, but it was clearly written by people who either don't have children or don't didn't don't know how raising children is today because this is written by latchkey kids. Right. No way this could happen in the modern helicopter parenting environment. Like it's just no, like, yeah, it's a modern movie. It's clearly made for present day, but it's written by people who just have no idea what kids are like these days. Like there's no way no parents let their kids just roam the neighborhood anymore. Like when's the last time you like were just walking your neighborhood and you saw kids just being kids? Like it's not a thing Yeah, that's true. It's like, it's just, these are clearly latchkey kids and it's just, it felt out of place me watching this. I was like, no kids live like this anymore. Like just walking around the neighborhood and seeing kids outside and they're going from house to house and no one's checking in and no one's that. It's just like, yeah, it's clearly written by people who either don't have children or aren't familiar with how, you know, whatever's going on. Correct.
+Jordan: Yeah.
+Darius: So.
+Jordan: Yeah, that's true. So they hear about the kissing party, obviously. They're trying to learn how to kiss before that. So they get the drone and of course they break the girls catch the drone and they hadn't break it. I don't think they'd broken the drone at that point yet. And they're like at Thor's parents house and they're like, all right, we got to get some weapons. And they're like, all right, mom, I found my my parents have a lot of weapons or whatever, and it's just like all sex toys. Yeah, that **** was crazy. And then like, I think we got some an all beads.
+Darius: Yeah. Oh, God. I do remember that. Honestly, I found that I just was a little uncomfortable, man, watching these kids with with sex toys. You know, I just. I don't know if I'm getting squeamish in my old age, but I was just like, I don't know, man. This movie, man, it should have been PG-13. I knew the spots where I was supposed to laugh. Right. But it just felt weird. Like were these child actors? Yes. Were there laws going on? I was just a little creeped out to be honest.
+Jordan: Yeah, like they couldn't, they couldn't watch the movie, like obviously without an adult. Like they couldn't even, I think I read something where like a lot of the kids didn't know what the words they were saying meant. And one of the producers was like, just ask your mom when you go home.
+Darius: Yeah, I'm weirded out. To be honest with you. Okay. So there's not a HBO special about this movie in 10 years?
+Jordan: Yeah, I hope they were all, I hope all the kids were taken care of and protected and things of that nature.
+Darius: It just, I just was like, man, I don't know. I, you know, maybe I'm just getting a little sensitive in my, in my old age, but what else you got back to?
+Jordan: I thought it was interesting like that the, one kid's parents got divorced and they like showed how that really does affect kids because people act like kids are stupid or like that they don't know certain **** or whatever. But when you're a kid and your parents get divorced, like I had friends who, we all had friends whose friends got divorced when we were kids and like that was a big thing. Like sometimes they had to move away or like the kid got really depressed or they started acting out and doing wild **** like that. That definitely like can change their trajective, like a kid's like formative years. So I thought they did a good job of like, I mean, obviously it was very silly and funny, but they did a good job of like showing that like that **** does affect kids because they are human beings. People forget that, I feel like, especially when they get older. So I like that they focused on that as well.
+Darius: I wish they had done a little more, but I get that they would have been out of place in a movie with this tone. Tighten up. Life is life, kid. You know, like, All that ******* crying. Stop all that damn crying. Tighten up. Your parents are getting a divorce. I get it. sucks. But you know, I don't really do whining. I don't do self-loathing and I don't do whining. But Thor could sing, right?
+Jordan: Yeah, he could sing his *** off.
+Darius: He's very good. Did you as a child have any secret passions or interests you were afraid of being teased about?
+Jordan: I'm trying to think. Yeah. yeah I mean like I was a band kid for a couple years in middle school I wasn't like ashamed of like people picked on me because I like played the trombone and I was like really short as a kid and I had like a big *** music case so they're like oh the case is bigger than you like this so that was like frustrating and then you know there's the whole thing of like like did you ever get called an Oreo as a kid?
+Darius: Yeah well affectionately called Professor but Yeah, I mean, I mean, yes, certainly there was a there's a certain level of stigma to young black children, especially young black men who don't present a certain way. Right. Anyone who says there wasn't is just lying.
+Jordan: Correct.
+Darius: But I mean, yeah, I mean, certainly, certainly, but I was it was always came from a place of affection where I was just like, my nickname was Professor. So.
+Jordan: So for me, it wasn't so much at school. Well, I got called over at school, but like. whatever. But at the church we went to, there was a lot of kids there who weren't in the most stable of situations at home. And I think there was like a little bit of resentment there too. There was some resentment sprinkled in with just like ignorance as well. And like I remember like when they learned that like I played tennis growing up, like I got had lessons and I was like really, really good. And And they were like, black people don't play tennis, like that sort of thing. it was like the high school, well, you didn't see that movie, but it was like one of things where like you'd skate picked them for doing something that normal people do, but like, because it's what you don't fit the archetype.
+Darius: Well, okay. So tennis is not tennis is very much an upper middle class leisure activity. It's not something that everyone.
+Jordan: But like, I didn't play in the country club. I played like at ******* courts at ******* you know, Lynn, at the Lynn, Lynn, Lynn Road Park or, you know, it wasn't like, you know, I was at some golf club. But I get you're saying, Lou.
+Darius: Did you draw and do other sissy **** besides tennis?
+Jordan: What?
+Darius: Tennis, not bad. Like, I was cheating. I still hooked.
+Jordan: Well, no, I did everything. I did it. I was one of those kids who did everything. So I loved basketball, so I hooped. I did, I was big into sketching for him and I just like stopped doing it. I started writing poetry and I was like 12. What else did I do? I mean, obviously I love movies. Like that was a big thing for me too. Just going to movies a lot, watching movies and ****. I think at one point I either wanted to be an actor or wanted to go to film school at various points of like life and adolescence. Yeah, I was one of those kids who was just genuinely like into everything. Like I tried pretty much everything. I did Taekwondo with my brother for a couple of years. Like, yeah, my parents kind of very much supported like us like doing **** that we enjoyed and having different hobbies.
+Darius: fair enough where you're secretly good at like really good at it like there's something okay what's one thing you're secretly good at that people would be surprised to know?
+Jordan: Like now or as a kid?
+Darius: As a good one yeah well as a kid because it's the frame of the movie so.
+Jordan: Yeah I mean as a kid that's a poetry guy because I wasn't really telling people that I did poetry um I would say now um what am I secretly good at um I mean, any sort of like, anything involving throwing, I'm pretty good at. Like, I'm really good at darts, like **** like that. Um, any, any like competitive, like guessing or trivia games, I'm like freakishly good at, uh, like taboo or, you know, jeopardy, **** like that. Um, that's what comes to the top of my head right now. What about you?
+Darius: Well, so, I mean, I would've said cooking before I started posting cooking on Instagram. Um, secret passions of as a kid. Like, so I love sports games, but I didn't like, like, head to head or online sports gaming. I like to play offline franchise mode. And that was like, people just did not understand why I would enjoy that. And so yeah, searching for sliders for Madden, I think I found this website called Operation Sports. where they would have people who would like upload sliders and everything. And like you could, they would, we would e-mail each other, e-mail, e-mail this before e-mail, we would mail each other memory cards. Yeah. And so we would have rosters in that way. And that's actually how I've met a lot of, I call them my internet friends, like most, like most people I interact with on Twitter. And we used, we met talking on the Operation Sports forums.
+Jordan: Yeah.
+Darius: And we would just talk about sports video gaming and then they would get into off topic segments where we would talk about real sports, like actual, like the live events. And then we would talk about the other video games and things like that. And then we all kind of sort of migrated over to Twitter into our own little hubs. And so I mean, I've been talking ****. I met some of them in high school and we're still cool today. So, okay. So yeah, I guess that would be like, people would like, I guess, tease me and be like, you want to play against the computer? That's boring. And I always found that more interesting than playing head to head against other people. I still do. I still play with my brother and things like that. But, you know, I found a whole internet community of other people, like-minded people who like to do that, who probably were teased for the same exact data play, you know, so. shout out to my OS friends.
+Jordan: I'm with you I actually so I don't really like doing franchise mode I like superstar mode and then I'll or I'll play yeah I'll do superstar mode obviously quarterback and then I'll play defense or sorry offense only because I don't always like playing defense I'd rather just play offense the whole time if I could so I just do that so I can just practice offense like nonstop I did think of another secret passion though Especially like growing up, I was always really big into Greek mythology.
+Darius: Yeah.
+Jordan: I always thought that was like the most, the coolest, like most interesting **** ever. Like the story, the stories are great. The, you know, the, mythological creatures and the, you know, Mount Olympus and all that. I had like this, like, I bought this like ******* massive, like, Greek mythology storybook, like probably 7 or 8 years ago. Yeah, it's all of all that **** like Hercules, ******* Oedipus, Clash of the Titans, Wrath of the Titans, all those.
+Darius: Yeah, I've always enjoyed world building with like, so World of Warcraft, everyone knows what that is. I would write like sort of like fan fiction based off of my characters in World of Warcraft and just I don't know, just build a world that way. Part of the reason why I like offline franchise mode is it's like in my head, I like build stories around the characters in the game. And so I can do the NFL draft in the game. I can draft rookies and build their stories up and all that shit's make believe. But you know. Yeah. What is fiction if it's not, you know, make believe? So I like. So as a kid, it was weird. And so you just play the offline franchise and you draft the people and you get all these creative players almost onto your team. And I built background stories for them. And sometimes I'd write it down and flesh it out from there. And I do that with other video games that single player games. And I've grown out of it a lot now. I don't game nearly as much as I used to, but I still enjoy sort of like the writing of the fan fiction around my franchise modes and so okay if you'll ever catch me like post a clip like there was like it was like that was like a year six of a Madden franchise and TJ Hawkinson is my tight end and like we couldn't We couldn't, we just, the cap budget, he was like his last year on the team and it was in the Super Bowl and I made sure I got him a touchdown because it was his last game on the team and all this **** is fake, it's mad. But I really felt good because he's been, I've played so many games with him and I was like, it's your last, it's your last year on the team. We got to let you walk because the rookie behind you is better, but it's a blowout. We're going to keep you in the game for this one last touchdown. I don't know, I felt good. And I'm like, this **** is all fake. **** is all in my head. This is a ******* character in a video game. But it felt great.
+Jordan: That's hilarious. But it's like, I don't think there's anything wrong with it. Like I think passion is supposed to be like that. Like I actually told, I was on the phone with somebody the other day and I was talking about like the books I'd read so far this year. I told them I was like, you're going to think I'm crazy. It's going to sound weird when I say this, but I was like, I told her I was like, I actually finished Harry Potter and the Deathly Hallows, which is the final book for the first time this year. And I was like, I didn't want to finish it because when you finish it, then it's over. You know what I mean? And I kind of always never wanted to like officially be over. But I was like, okay, well, I got to finish at some point, you know? And it's not like I can't go back and reread or watch some movies and stuff, but it was just like a nice, I don't know, like memory to kind of hold on to, like a little piece of like childhood, so to speak, to kind of leave undone in a sense. It makes sense. So, yeah, nothing wrong with having a little bit of passion, you know?
+Darius: You know, it's just you never want to lose your imagination.
+Jordan: Correct. Exactly.
+Darius: It's like a little piece of your childhood. You want to get attack 3.
+Jordan: Yeah, that's where all the good **** happens.
+Darius: Act 3, the party's resolution, the boy's journey culminates in their arrival at the party where they must confront the consequences of their actions. They're changing friendships and the realities of growing up and leaving childhood behind. Did not have an observation for this one other than are you still cool with anyone from grade school?
+Jordan: Yeah, a few people were found on Facebook and Instagram and **** like that. So we kind of keep in touch. Don't speak often, obviously, but it's always just good to see them on the net or like I've run into some people maybe downtown every once in a while or out at like a bar or something like that. That's happened a few times. But I moved away when I was 12 from a lot of my childhood friends. So it was a little harder to, you know, kind of hold on to because for cell phones, you move away. It's like you died.
+Darius: So yeah, it's like you moved to Mars, right?
+Jordan: Yes. And then you're only ******* 50 minutes down the road. So yes, like from grade school, not really high school. Obviously, I got a few few people I'm still cool with. But yeah, I was I was always kind of a floater anyway, so it was I just tend to lose such people just, you know. So yeah, what about you?
+Darius: My best friend, Jeremy, I've known since sixth grade. That's no one else from grade school. I know some people from middle school, but I don't keep in touch with them. Somebody I went to middle school with in high school, no, he went to Armstrong. We went just middle school with, but we never, we just kept in touch. Like we're both sneaker heads and we both flame emojis each other's sneakers, I guess that's keeping in touch. And no, after that, most of my friends I met as an adult. So. Right. But my best best friend I've known since 6th grade.
+Jordan: Okay.
+Darius: So what you got for act three?
+Jordan: Oh, yes. Well, I do want to say that one of the worst things that can ever happen to a child outside of like tragedy is their parents coming home early from work or from a trip?
+Darius: Again, no one was supervised, but.
+Jordan: Yeah, I mean, we got, I got so many asks from just them coming home early. Like if only they came home like at 5:00. But.
+Darius: That's kid logic though, because like, why would you think someone arrives home at the same time every single day? Yeah, that is true. And why would you not build yourself more than like 30 minutes of wiggle room? That's how kids think.
+Jordan: Like you didn't wash it. I didn't wash it. You didn't wash a dish. You didn't put the meat out like nothing.
+Darius: Like mom gets home at 5:00. I'm good until 445. Like no, that's not.
+Jordan: That was literally our logic. And like my dad, he always had like flexible work schedule because of his jobs. And he just loved like surprising us, like coming home in the middle of the day and **** like that, especially like summer breaks. Like he would sneak in through like the deck door or whatever ****. And we'd be doing **** we weren't supposed to be doing. And yeah, it was a wrap. Like I remember one summer, I was one of those kids who just like tried everything, like just because why not? And I was like, I wonder if we jumped off the banister onto the foyer, like, could we make it? And I was like, let's just stack up all the couch cushions and try it. So we were going to try it. And luckily we didn't do it. And the second we put like the last couch cushion. on back on the couch, my dad came home. We were like, oh, thank God.
+Darius: You know, he probably know like he just let it go.
+Jordan: You know, that's probably that's probably what happened. That's probably what happened.
+Darius: As a parent, sometimes you like respect the ingenuity. You're like, you didn't get away with it, but I respect how close you came.
+Jordan: So I'm like, yeah, man, I remember actually had an incident kind of similar to it to with the kid where he direct the house with the drone. So I was speaking to movies and I was always speaking to like filmmaking. So one year for Christmas, I got a camcorder. So I would just record random ****. And I always love like doing flips and handstands and stuff like that. So I practice, but I was practicing like in the house. And so I set up the camcorder in the dining room so I could record myself. Like I'd run from the foyer and f</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out the Trunk Pile with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Deez all up in the area on all socials.
+Jordan: And today we're going to be reviewing The Judge. This movie came out in 2014, starring Robert Downey Jr. Yes, Iron Man, Robert Duvall, Vera Farmiga, Vincent D'Onofrio, Jeremy Strong, Dax Shepard, Billy Bob Thornton, Leighton Meester, sorry, and Leighton Meester. This movie is about a high-profile Chicago lawyer who returns to his small hometown for his mother's funeral. He's forced to confront his estranged, respected, but discerned father, who's also the town judge, who is soon suspected of murder. The son must put aside their bitter differences to defend his father in a high-stakes courtroom drama. So I'm gonna toss it to you to open up Act 1.
+Darius: Act one, we're going to call the homecoming and the accusation. Hank, a successful and arrogant Chicago defense attorney, returns to his Indiana hometown for his mother's funeral, forcing A tense reunion with his two brothers and his estranged, rigid father, Judge Joseph Palmer. Their strained relationship and family secrets resurfaces. Hank attempts to leave only to learn the judge is suspected of a serious crime. Off the rip, Robert Downey Jr. is an elite actor, and I will never forget Marvel for what they took from us for all that time. He could have done so much iconic stuff that he decided to tell bad jokes in a costume. Never. I will never, ever. Anyone seen Mara Shala Ali? Where's he like?
+Jordan: Yeah, no, they put that. Yeah, they put that thing on the shelf. They put that thing on the craziest shelf. All that for mood that ended up not getting made, bro.
+Darius: It just absorbs.
+Jordan: Somebody a moment needs to go to jail for what the **** they did to him.
+Darius: He was at the highest of highs and, you know, no one's heard from him. Also, that's obvious.
+Jordan: It's a very part of the story. How can you not figure that out? I don't.
+Darius: It can't be that hard to write a script for ******* blade, man.
+Jordan: No, bro. Just get some pretty black people. Don't want some leather. I don't understand.
+Darius: I won't say the opening song. I looked it up. It's called Phantom Witness has to be like the universal. This movie is serious opening song for all of Hollywood.
+Jordan: Oh yeah.
+Darius: Soon as it starts, I'm just like, I know that song. It is just everyone, every piano plays it just like, okay, lock in because we're about to cry. All right. What you got for act one?
+Jordan: First of all, I ******* love this movie. This cast is loaded. Everyone drops 40 in this *****. But I love the opening scene of this movie, where it starts out with almost like a relic of each of the characters' interests. It starts out with the judge's glasses on his desk with the newspaper. Then you see the baseball glove, and then you see the camera for the other son, and then you see the hydrangeas for the mother. And then you don't see anything for Robert Downey Jr's character, which is kind of his place in the family as the black sheep. I thought that was a super dope detail right there.
+Darius: Yeah, I'm sorry for yawning. Yeah, I agree. Did they ever explain why Robert Downey was like, the blacks? Like, what did he do? I didn't watch the movie. I like, they kind of said the dad hated them, but I never got why.
+Jordan: Yeah. So remember he got, he was got stoned with his brother and they were driving and they ripped the car.
+Darius: He's the one who was, yeah.
+Jordan: That ruined the brother's baseball career. And I, I think the older brother was the dad's favorite, honestly. And I think that's really what it was.
+Darius: I think the older kid played sports and. Right. Okay. It doesn't make sense. Sorry, I missed that. I was just like, because.
+Jordan: He was supposed to go pro, basically. So I think it was I think it was like, oh, you ruined my favorite kid's shot at a huge future. So.
+Darius: Barbershops across America are filled with dudes who thought they'd go pro if, you know, they didn't hurt their knee. So what else you got for act one?
+Jordan: I love that they suddenly showed he's still as much as he hated his father. He still had a great relationship with his mother or still had love for his mother with where the fact that he had hydrangeas at his house and he was watering them.
+Darius: When he was pulling off in the car, he's like, take care of my hydrangeas. We know why, but yeah, I mean, it's often the case when the relationship is strained between one parent, the other parent like secretly keeps it Keeps in touch, right?
+Jordan: Yeah.
+Darius: So.
+Jordan: Yeah, I like that. Even just like, man, like I know this movie's supposed to be like, it's just a strange relationship between the father and son, which it is. But his dad was a ******* ***** ** ****. Like, I'm just gonna keep it stag with you. Like, yo, like, first of all, for me, if one of your kids didn't **** with you, you're a ***** ** ****. That's just like my general rule in life. Because kids are so forgiving and every kid wants their parents to be their hero. So for your kid to like, actively reject them from reject you from their life. You had to be on some wild ****.
+Darius: I mean, what he said, what he said about his wife having an affair was just insane.
+Jordan: I would have swollen him. I'm sorry. I would have swollen that.
+Darius: I mean, I just said, absolutely. I wouldn't even say it to someone I didn't know, much less my child.
+Jordan: Yeah, that's ******* crazy. Even remember at the repass where he like he sees him and he's like giving everybody hugs and he calls him Henry and shakes his hand like they're ******* business associates.
+Darius: Didn't that feel a little cartoonish to you at some points? Honestly, I've seen some strained parent-son-child relationships.
+Jordan: I don't know, man. I've seen some wild ****. Like I've seen some crazy **** like that.
+Darius: Ain't capable of being cordial at your wife and mother's funeral. That felt a little cartoonish to me.
+Jordan: I don't know, man. Listen, my grandma passed almost a year ago to the day. Actually, three days from now, it'll be a year ago to the day. And yeah, you know, rest in peace. She's in a better place. And the **** that people were saying to and about each other during that week when we were all back in town, it was like, no, like y'all are, not only are y'all as bad as I remember, y'all are worse. Like y'all have gotten worse as human beings. I don't know, dude. I've seen some crazy **** bro. Like, I've seen like, where, you know, parents pit, like create this like competition between the siblings and that they act like, you can tell they want that between the siblings, you know?
+Darius: Yeah.
+Jordan: And I don't know. I mean, I've never seen it so much where I'm not going to hug you and shake everyone else's hand, but I've seen that energy before at functions and stuff and at events.
+Darius: I've certainly seen dysfunctional families before, but they usually can keep it tight for a funeral. You know, like usually it's like in the interest of respect for the deceased. Well, yeah, you ain't got to think, you know, you ain't got to. throw a parade, but just, hey, how's it going? Oh, cool. Da, da, da, da, da. Yeah, pivot.
+Jordan: Usually you see that and then the ******** starts. So that's fair. That's fair.
+Darius: Maybe just because like, it's not that I'm a pushover or I'm just not like. I'm just not too, it's fine. I can say hello. I can do some pleasure. Even if I ******* hate the person. It's just not that hard. I totally, you know, like it's just, it's really, I don't find it difficult to just be like, hey, how's it going? How's the kids? Da da da da da. Okay, cool. All right. That's it. You know, you don't have to, me, obviously this is a movie.
+Jordan: Right.
+Darius: You're putting your feelings ahead of the bigger picture when you decide to bring up any grievances.
+Jordan: That's fair. That's true.
+Darius: Public spaces where it's just wildly inappropriate.
+Jordan: So yeah, that's a fact. Yeah, he definitely could have handled that. We could have handled everything better to me. I agree. So I actually wanted to ask you, do you think because I like that they showed like the wife, he did have relationship with his wife and, you know, he's crying at the at the the grave site and all that. So I want to ask you, do you think it's possible to love your spouse that much but hate the people you made with her?
+Darius: We only hated one. Well, true.
+Jordan: Yeah. Which actually to me makes it worse because if he hated all of the people, okay, you should be ****. But to hate one child so egregious, so aggressively was insane to me.
+Darius: One people hold multitude. So yes, I do think it's possible. Yeah. I wouldn't categorize the I wouldn't categorize it as hate. I wouldn't say he felt like You robbed my oldest son of his dream and then left to go live yours and you didn't and I like now I have an adult dependent child that You know, I'm solely responsible for while you get to live the big shot life in Chicago. I think a lot of there's a lot of latent resentment, latent resentment for small town people to the people who leave and go.
+Jordan: Yes. Yeah, absolutely.
+Darius: And so you have that.
+Jordan: As one kid always stays.
+Darius: One kid always stays. You have the fact that he left and he's probably a snob about it. He's probably always talking about the yokels back home. And you injured, you were primarily responsible for the injury. That is the reason why like having a like a mentally incapacitated adult child is just a lot. It's very labor intensive work. And that's a reminder every day, you know, of it. And, you know, I don't know.
+Jordan: That's the brother with the mental issues. He was he wasn't in the car.
+Darius: Oh, ****.
+Jordan: It was just it was the big brother. dude from Law and Order.
+Darius: Okay, well, that's the point, Stance. You robbed the oldest son of his dream and then you would have to go live yours and you're a snob about it because he wasn't, I could tell he was a snob about it just by I also wanted to point out the mismatch in lifestyles. Scott has his fly *** crib and these vintage cars and he's the last row of coach on the plane. That doesn't make any sense. Oh yeah, that didn't make any sense at all.
+Jordan: Like you're not private or first class.
+Darius: He'd be first class. He would be private. Yeah, true, You don't, that doesn't, like you're his big shot attorney and you would row 36C. I don't believe it. I agree. But no, I don't think he I don't think he hated them. I think that human beings are complicated and there's a lot of resentment for the small, the small town people toward the people who left and then he's just not leaving. And then you also left after injuring your brother. So but do I think it's possible? Yes, I do think it is possible to hold those two things in conflict.
+Jordan: Yeah, I also I think because they never really said at what age the the separation started so I wonder if it was maybe he just was rebellious and doing stupid kid and then his dad was such a **** *** by by his by his standard that was just like beyond the pale and then the car accident was just like the final straw type I mean you know they didn't really explain it all you know the timeline of it your kid's graduation is absolutely high school and I was gonna say yeah high school and college and law school is crazy.
+Darius: Did I ever tell the story about the dare to not do drug speech that? Yeah, I'm getting old. I'm repeating stories on the podcast. I still haven't lived that down. That was a ******* fifth grade, like after school special speech. The idea that you would miss graduation is just patently absurd. I've never.
+Jordan: Yeah, no, actually. Yeah, I remember my 8th grade ceremony. I like didn't tell my mom there was one, I guess. And she was like, why didn't you tell me? Like.
+Darius: The teachers called my parents. My parents will, my mom answered the phone and was like, situated she was neglectful. She was like, these things are important and you should show up. What you talking about? You ready to do act 2? Yeah. Act 2, the defense and discovery. Despite their mutual contempt, Hank reluctantly stays to represent his father in court, beginning a complex high-stakes trial. As a courtroom drama unfolds, Hank's investigation into the case uncovers dark family secrets, a past tragedy, and a surprising private struggle his proud father is facing. Chad to getting that old thing back in your hometown. In totally unrelated news, I will be back home next month. Leave that right there. What you got for act two?
+Jordan: You know, I actually have a question I want to ask you. And you just, I'm gonna go ahead and just go ahead and do it now then. So say you come back to your hometown and you see your old flame and she has a kid that looks like their age can be around the time y'all like let saw each other. What do you do? Like, would you ask her?
+Darius: Oh, thinking it's mine.
+Jordan: Yeah.
+Darius: Is there a dude in the picture? Are we mapping the movie over where there's no?
+Jordan: Yeah, yeah. Mapping the movie over. Yeah, yeah.
+Darius: No, I would ask. Yes, I would leave it alone because if there's a dude in the picture, I'm not hearing that.
+Jordan: Right.
+Darius: But if it's if she's just a single mom.
+Jordan: There's a joke there.
+Darius: I'm not going to say it. If she's just a single mom. Then I would probably, I just, I would have to know. So I would ask, yes.
+Jordan: Yeah, Also, I'd be really disappointed because damn, she was fine.
+Darius: Yeah. Is that the, so that's what I had a question. So did you see Top Gun Maverick?
+Jordan: Yeah.
+Darius: Is that the same old lady back in your hometown thing? Same character? Yes, because I didn't look it up.
+Jordan: No, that's a different actress. So the one in this movie, I actually love her, Vera Farmaga. She was in Up in the Air with George Clooney. She was The love interest in the departed Leo and Matt Damon.
+Darius: She's the conjuring lady, right?
+Jordan: Yeah, that's her. Yeah. And she was in. What was that show on FX about Norman Bates and his mom? Bates Motel.
+Darius: Okay.
+Jordan: Yeah, she was she was in that show.
+Darius: Yeah. Very talented actress, but no.
+Jordan: She's great and everything.
+Darius: If I returned back home and an old fling had a child that looked suspiciously like me, If she brought it up first, that's tough. Yeah, right. I would, I would, I would only ask.
+Jordan: If you're in college already, like, what do you even do at that point? I don't know, you know.
+Darius: I would, I would, I would ask if she were single. Yeah. But if there was, if they were, if, you know, if she was married or had kids, and I'm not injecting myself into that.
+Jordan: Yeah, I feel you.
+Darius: What else you got, Frank?
+Jordan: Yeah, I want to say, I want to say both ways Bobby is a crazy ******* nickname to call another man.
+Darius: In those small towns, man, being gay is like being anti-Christ. Like, no, yeah, seriously, yeah. Like, that's, it is not.
+Jordan: You're literally putting your life at risk.
+Darius: I mean, not so much.
+Jordan: You're not putting your life at risk, but your life could be at risk because of the way people treat LGBT communities in small towns.
+Darius: You are risking lowering your quality of life. We'll put it that way. Like people will treat you differently.
+Jordan: Basically in the 80s, remember like they graduated high school in the 90s. So early 90s. So yeah, that's yeah, that's a.
+Darius: America is a big country and some of them backwoods are rural. Backwoods. Yes.
+Jordan: So yeah, man, I remember I went to a friend's house for a cookout in Zebulon a few months ago. And Zebulon is like, really like kind of like out kind of in the sticks. And I was driving, I saw a gas station and it just looked like I wouldn't book them in there.
+Darius: Like, just, if you ever was it the Green Book, we it's not totally irrelevant, like, get your gas during the daytime.
+Jordan: Yes, And use cruise control.
+Darius: Yeah. these cars now will tell you to the mile when you need some gas. So I'm sorry. That is also helpful. But I know you get. So he his dad gets popped for vehicular manslaughter. Was it? I mean, it ended up being first.
+Jordan: Degree murder, but voluntary manslaughter.
+Darius: Yeah. First degree murder was overcharging. But let me just say jury selection is ********. Like you shouldn't like the fact that you can pick and choose the jury. Yeah. If it's going to be, because what happens if you allow jury strikes is that the only people who are on juries are people who can't get out of being on juries. And there's a self-selecting mechanism there. That's why I always say people, if you can, especially black people, and you get called for jury duty, you should do it because we are, you know, there's a lot of bias in jury selection. And it's important. It's a civic duty and it's important that our juries aren't solely just the people who can't get out of it because the people who can't get out of jury duty are the people who are too dumb to figure it out. And so, you know, I guess I always say if I get called for jury duty, I'm going to do it because it's one, it's my civic duty and it's important for black people to do it because we're underrepresented and there are biases in court systems that for everyone. And it helps to have diverse juries. So I just wanted to get that out there. What else you got cracked too?
+Jordan: Yeah, I want to say, so they mentioned the fact that the father was at one point an alcoholic and is now recovering and sober. And I just want to say, if that's how this ************ was acting when he was sober, when he was drinking and they were little kids, he had to have been a ******* terror.
+Darius: I don't think he was winning any Father of the Year awards. No, not at all.
+Jordan: And he was a judge. He could do whatever he wanted.
+Darius: That I mean, judges, especially in those small towns, may have.
+Jordan: ****. Yeah.
+Darius: A men's authority.
+Jordan: You're like the mayor.
+Darius: Pretty much more powerful than the mayor.
+Jordan: Yeah. Yeah.
+Darius: And the town was a mayor as a figurehead. So, you know, true. But I want to say, you know, as someone who What am I? I'm 37. And my father, I think his birthday is next month. I'm not going to, I think he's in his 60s or something. Just the whole father slowing down thing is because, you know, like, you know, Pops hit 60 and they hit the 70. I mean, this guy was 74 in the movie, 72, 72.
+Jordan: Yeah, 72.
+Darius: And it's just like, you know, it just kind of hit me a little different when it's just like, man, Your parent, no one, nothing prepared you for your parents aging. And so no, there's a what is that? The John Mayer song Stop This Train. And when he's just like, you know, I don't know how to say this. I don't want to see my parents grow old. And it just, you know, yeah, it's just the song is called Stop This Train because he wants to stop the train of life because it just keeps moving and there's nothing you can do. And it's one of my favorite John Mayer songs. And it reminded me when I was listening to this, just like seeing his parents age and there's a line in the song where he's like, what does he say? He says, so scared of getting older, I'm only good at being young. And it's just like, just, you know, I kind of felt it. Cause he's just like, he comes home and his dad, if you, especially when you move away, when you come home and everyone just ages and they just, you just don't see it cause you're around them so often. You're around them not often, and then you just come back and you notice that things change.
+Jordan: It smacks you in the face.
+Darius: And their gait's a little different. They're just not as witty, and it's just like, when did this happen? And it's just like, well, then while you were away. Yeah, right. Yeah. You know, it's just so anyways, what else you got for Act 2?
+Jordan: Yeah, I was thinking the same thing. I mean, my parents are relatively young. They're in their late 50s, you know, like my mom had ankle surgery a year and a half ago and That was, a temporary situation, but it was like, for those couple few months, it was like, damn, this is what it would be like, when they get older and stuff. And, my dad, he's getting to age where he's starting to need glasses, but it's like gradual because we'd be out to eat and he would like, not tip by accident. And they'd be like, you sure? This is what you mean? And he'd be like, oh, sorry, let me give you 20 more bucks. Like, you know what I mean? Like subtle **** like that. So it is, it's not, it's not sad because they're just, getting a little bit older, but you start to think about, but for sure. Yeah. Right. I'd rather them age than, right. So that **** does kind of start to hit you subtly or even like, my dad lives a few yards away, which is not crazy far, but we see each other every few weeks, every couple months, depending on who's busy, you're traveling and you kind of like notice like, oh man, like he's like his beard's more gray or, you know, stuff like that.
+Darius: It happens quick, man. Yeah, you're hidden. I think it's like your mid 40s is when you're kind of you're the sandwich generation. Your parents are aging into needing more help. And then you have kids who obviously they're kids and you help. And so you're just kind of juggling, you know, taking care of people. You're reread like you have to like you re-raise your parents. They become infants.
+Jordan: Yeah.
+Darius: And so right. It's tough. It's tough.
+Jordan: Yeah.
+Darius: Was that bathroom scene the most powerful in the movie to you?
+Jordan: One of I won't say it was the most powerful for me. It's definitely one of them because I mean, eventually we're all, Lord willing, we're all going to have to do that for our parents. You know, we hope that they are old enough to in a weird way to be able to have that problem, if that makes sense. And I mean, they did it for us for ******* you know, until we were three. So it's the least we can do to pay them back.
+Darius: Obviously, you know, I just feel like something changed with Robert Downey Jr.'s character in the sense that like, that's when, you know, he, he's.
+Jordan: He humanized him.
+Darius: He humanized the father. He was not like the evil judge. He became his like actual father. And yeah, they were, it was like that after that scene, they became father and son. And then, yeah, honestly, the movie gets a little longer than a tooth after that. But that's kind of what I like. transition after that scene to where they were like adversaries and then they became like partners in whatever endeavors.
+Jordan: Yeah, I agree. It's funny. So I just finished Will Smith's book called Will and his dad passed away from cancer. Maybe like seven or eight years ago, something like that. And his dad, he had a somewhat contingent relation with his father. His father was alcoholic and was a piece of to his mom and stuff like that. So he, naturally growing up had certain negative feelings towards his dad. And he said, you know, when his dad got older, when his dad got cancer, like he wasn't the big ogre, scary ogre to me anymore. He just was like a man. And he could see like the scared child inside of him, you know? And he said like that, you know, humanized him a lot. And he said there were similar experiences, with the bathroom scene and stuff like that, where you have to take care of your father. And it's like, man, it's just a person, that had problems and mistakes and didn't know how to deal with them. And that I know I have to like forgive and, try to be in our relationship with him before it's time to go.
+Darius: One of the hardest things about adulthood is realizing your parents aren't actually superheroes. They're just people.
+Jordan: Yes, that is that is very true.
+Darius: And as the old saying goes, once a man, twice a child. So, you know, you'll be sandwiched there. Anything else for act two?
+Jordan: So I wanted to talk about the cancer diagnosis and all that. I just thought it was ******* crazy to me that he just like hid from his children that he had cancer stage 4 for a year and then was just like working every day like the **** was normal. I personally don't think he should have worked on anything that was really selfish because you were in obviously no condition to be presiding over legal matters. I think that actually was pretty narcissistic on his part to be honest.
+Darius: Yeah. I mean, the first scene, he's like making some guy give his car keys to his ex. And I don't even think you can do that. But yeah, that was crazy. That was some small town ****. No, right. I get it in the sense that once you tell someone you are terminally ill, you see you. I've always said I wouldn't tell anyone. I just wouldn't. I would. One, I don't like attention into Once you tell people you see, I would cease being Darius and I would just become the sick guy. And that's all people, I've read about this stuff. What was it, When Breath Turns to Air? Was that doctor who wrote the book as he was dying? And he's just like, it's literally all anyone ever wants to talk about. Like no one ever asked me about a TV show anymore. No one ever asked me about the game. And he's just like, I wouldn't want that. I would rather People treat me like Darius until the end. I just wouldn't. I wouldn't tell anyone. I wouldn't go. I wouldn't go out like Chadwick. I would 100%. No one knew with Chadwick except for like his wife and his family knew. Yeah, that's pretty much it. But like Ryan Cooler didn't know Michael Jordan didn't know. And that's I imagine it's something similar to that where it's just like, yeah, you become your disease. That's all anyone ever wants to talk about. So no, I wouldn't tell anyone. I get it. I do.
+Jordan: That's true. Also, I do want to just a little footnote here. The fact that he was like, oh, I don't want my legacy to be ruined like Ulysses S. Grant and Ronald Reagan. First of all, Ulysses S. Grant, he won the Union and he beat the Confederacy. Went on to help black people in the restoration era, sorry, reconstruction era. Ronald Reagan, on the other hand, is looking up on us smiling right now because the **** he did to black and brown people in the 80s was ******* crazy. And I don't know what proud legacy there is to honor about him, respectfully. It's funny though.
+Darius: I agree with you, Ulysses S. Grant. Although he did sort of botch the Reconstruction era. Fair. But my funny, it's this internet thing where everyone treats Ronald Reagan like the boogeyman. And then you look at his electoral maps and it's like, I don't know, man. He was like one of the most popular presidents ever. Like people talk about Ronald Reagan. He's the character from House of Cards where he just like got into the White House on accident. His second election, he won 49 states in 84. He was an immensely popular president.
+Jordan: He was crazy popular, yes. He also was very evil to black people.
+Darius: But the people, people, black people could vote back then. Like, he won these elections fair and square.
+Jordan: I know, I understand it, but I just could not let that slide in this movie where they acted like he was like, He tried to moralize like people do JFK. And it was just like, no, that's not the same.
+Darius: I imagine you're just a conservative white dude in small town, Indiana.
+Jordan: Well, to him, he probably was a hero. But you know, I just had to get that off my chest as a policy major. I needed to say that. I needed to say that.
+Darius: I just find it so funny how the internet treats Ronald Reagan like he like stole an election or like he snuck into the White House and like he wasn't one of the most popular presidents in United States history. Yeah. I mean, he won two elections in landslides.
+Jordan: I mean, I don't think he was for black male teenagers.
+Darius: I don't think he was a good steward.
+Jordan: He cut a lot of funding that helped a lot of people.
+Darius: I mean, the vice president signed the Americans with Disabilities Act. So, yeah. That's the other thing too. He won the two elections and his vice president won a third. He basically won three elections.
+Jordan: No, I get it. I understand. I get it. I just. I just couldn't let that pass.
+Darius: I just find it fascinating how diff like. We will never see another president win 49 states.
+Jordan: No, never.
+Darius: It's just.
+Jordan: Well, if we ever see another president.
+Darius: Yeah, we will. But I just, the Ronald Reagan thing is so funny. Listen, I don't, I wouldn't have, I wouldn't have, I wasn't alive, but I wouldn't have voted for him.
+Jordan: Yeah, I wouldn't have voted for him.
+Darius: Yeah. And, you know, but it's just, it's fascinating to me how people treat it like it was, you know, Bush score 80 or 2000 and a split. But he just won. He won two giant landslides.
+Jordan: No, he did. He beat he won those elections fair and square and nominated.
+Darius: Hondale 49 to one. But anyway, that's actually crazy. What else you got for act 3? This is act two. Sorry.
+Jordan: Yeah. What did I want to say? Oh, yeah. It's always weird to me how when a parent is an ******* to their certain children or to all of their children, they just are like, nice as **** to the grandkids.
+Darius: I've Yeah, so I get it though, because you parents have to say no grandparents get to say yes. So yeah, and part of the job of being a parent is being mean. And that's not the job description of grandparent. So true. I thought that was I thought that was a cool way to humanize him.
+Jordan: And it was it was I thought it was interesting how he was like, I've been wanting to meet you for so long. And it's like, well, you put it sounds like you didn't put any effort to connect with your son. I don't know what made you think he was going to send his daughter to you.
+Darius: I mean, the people in the small towns don't leave, but I will say his other two brothers seem to revere him. So they did.
+Jordan: They did.
+Darius: I mean, he was two out of three and sons that loved him. So Robert Downey was the outlier. And I believe if the movie was the movie was clearly told from the perspective of Robert Downey Jr. because it was a Robert Downey Jr. vehicle. But I wish we could get like almost like a split screen because I feel like we didn't get the full reason why his end of the falling out. Because again, three sides of every story. Because it just strikes me as strange that the other two brothers, I mean, the other two brothers revered their dad and we're skeptical of Robert Downey. So like, if everybody hates you, know, what did JJ say to Kanye? If everybody crazy, you</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out of the Trunk Pod with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Steve's I love the area on all socials.
+Jordan: This is our movie review segment. Today we're going to be reviewing Love and Basketball. The movie came out in 2000 starring the lovely Sanaa Lathan, Omar Epps, Alfrey Woodard, Dennis Haysberg, Regina Hall, Gabrielle Union, and Harry Lennox. Love and Basketball is about next-door neighbors, Quincy McCall and Monica Wright, who grew up sharing a burning passion for basketball. Over the years, their childhood friendship evolves into a complex romance while chasing professional dreams. Navigating personal setbacks and shifting priorities, they must eventually decide if their love for the game matches their love for each other. So I'm gonna toss it to you for Act 1.
+Darius: Act one, the first quarter, young Monica and Quincy meet his children in Los Angeles, bonding over their shared athletic talent. As they enter high school, their competitive nature sparks a deep friendship and a romantic tension. I just want to say off the bat, and I can say this because we're the same age, so I was her age when the show was filmed. Kyla Pratt was a young Darius, one of young Darius's first crushes. Not particularly in this role, but in 101.
+Jordan: Yes. Yes, Lord.
+Darius: And for the viewer or listener out there, that's not weird. She, I just looked it up on my phone. She's 39, I'm 37. So I was literally her age when I thought.
+Jordan: Yeah, right.
+Darius: She was a minor at the time, but so was I. It's not like we were 40.
+Jordan: Right.
+Darius: So I mean, people, people like, yeah. So like, I always say like, this turtle was one of my first crushes and they'll be like, she was a teenager. And I was like, I think I was 4. Right. But shout out Kyla Pratt, man. I feel like she gets under-discussed in the 90s baddies discourse.
+Jordan: Yes, absolutely. She gets slept on. It would be an early 2000s. This movie has like 70% of my 90s crushes, like literally. I don't think all the people are missing is like, is Reagan Gomez, Maya Campbell, and Topanga, I think.
+Darius: I mean, we got, we got a Tyler, Tyler Perry, Tyler Banks, Tyler Banks. Something you wanna tell us? Cameo, we got Gabrielle Union was in this one.
+Jordan: Yeah, Gabrielle Union, Regina Hall.
+Darius: Listen, man, Quincy McCall's running through him.
+Jordan: Yeah, man.
+Darius: In one movie, he got Sanaa Lathan, Gabrielle Union, and Tyler Banks.
+Jordan: Yeah, and then it was Mia from Best Man was the side piece.
+Darius: I don't remember that, but go for it.
+Jordan: The girl he, the girl that when she went to his apartment.
+Darius: Oh yeah, that was her. That's a, that ain't the same tier, but she's cool.
+Jordan: Well, fair.
+Darius: There are levels to this.
+Jordan: Also, Monica's teammates were fine as **** too.
+Darius: Yeah, Aimless faceless teammates.
+Jordan: Yes. I love this movie started out with one of my favorite songs of all time, Love and Happiness.
+Darius: Yeah.
+Jordan: That movie fits with any soundtrack, any movie ever. It's just that movie. The song is just so goaded. It's a little good movie. I just wanted to shout that out.
+Darius: Al Green's superpowers. He just made being in love sound so easy.
+Jordan: He did.
+Darius: He did.
+Jordan: He really, really did.
+Darius: He really did. Sorry for interrupting you. What'd you say?
+Jordan: No, that's a fact. Yeah, actually I was thinking about that this week. I've listened to a lot of R&amp;B lately and I think that's the problem is R&amp;B like We have very few R&amp;B singers who sing about people that they like.
+Darius: Yeah.
+Jordan: Like it's always like, they ain't **** this girl ain't **** this guy ain't **** **** you. And it's like, okay, well, it's clearly they gave you some sort of positive experience, which is why you missed them. Can we talk about that a little bit?
+Darius: Nah, man. I got an Al Green playlist that he's just one, truly one of 1 voices. Just yeah, nothing like it. Not you've never heard anything like it and to Just he just the songwriting was just the pen was crazy And I don't know if you wrote all these songs back then it was much more collaborative, but he was One-on-one when it came to the tunes man And shout out to Dennis Haysberg Quincy's father Can't should never be in a man's book. I co-signed it Yeah, **** that.
+Jordan: I like that. That's something I want to teach my kids for sure I also love that he was like he was hard on him and he, you know, you know, be a man and all that stuff. But he also he didn't like what he also told him that he loved him on a regular basis and hugged him and **** which I think is equally as important. I feel like in a lot of movies and shows, black dads, they don't always show that part of black fatherhood. So I love that this movie does that.
+Darius: You know, that's part I think that's big part of Uncle Phil's popularity is.
+Jordan: Yeah.
+Darius: Now, the writers definitely softened him after the first season. That was actually a note that they got back. You know, it was like his behavior to will it so off putting. And so they softened the writer, softened him up quite a bit by the end. Yeah. I mean, he was basically a surrogate father. What else you got for act one, man?
+Jordan: So I forgot that his dad played for the Clippers, not the Lakers. But as when I was watching me, I was like, I've before, like Blake Griffin, I'd never seen anyone in real life ever wear a Clippers jersey out in public.
+Darius: The only notable Clipper I could think of was Elton Brand before Blake Griffin.
+Jordan: Yeah, yeah, I think so. That's it. I mean, did.
+Darius: Yeah, this is Elton Brand. We get into some like Corey McGetti and Stromile Swift, but like those players aren't notable. Just Elton Brand.
+Jordan: Yeah.
+Darius: Just want to say this is this movie. I saw the scene and I was like, this is where people got it from. The scene when they first when they first have sex. This is why people think Maxwell's This Woman's Work is a love song, because it was playing during the scene. I need the people to understand that song is about a miscarriage. It's not romantic. Stop playing it at your weddings. Stop posting it in the background of your Valentine's Day post. Listen to the lyrics of the song. It is not in any way, shape or form romantic. It's literally about him struggling with this life, very complicated pregnancy and individual miscarriage. And I found the source of this epidemic and it's this damn scene where they played it in a very romantic way. and it's just not a romantic song. I need people to listen to the lyrics of the song that you like.
+Jordan: Correct. And the reason people think it's romantic when obviously Maxwell's voice is like God level. And two, it's the harp. That harp makes you think it's like a ******* lovely song. I mean, it's a lovely song, but a song about a loving experience. It's not romantic. It's not. Yeah, right. Romantic. Sorry, portraits of words. Yeah, romantic. So at this point, I want to make up highlight it further in Act 3, but I love that this movie shows the The struggle of gender roles at the time, like the fact that, her mom was from her mom was from the south, her mom was from Atlanta. So she's kind of more of a southern belle. And then her sister obviously kind of followed in that same same aesthetic, whereas Monica's character or Monica was, you know, tomboy loved ball, you know, all that. And that was kind of the push and pull between her and her mom because they just couldn't see each other. They couldn't hear each other, you know. And I mean, that's a big theme of the movie, both genders really in terms of struggling with their identity and how to best represent that while also maintaining their authentic self. But I just love that this movie developed characters that had their own individual lives and identities. And of course, the love story is a central, you know, glue to hold it all together. But it also focuses on their families and kind of shows why they are the way that they are in a way that's not cheap or manufactured?
+Darius: I agree. I think I think it just kind of showed a good balance of the positive qualities a father brings to a relationship or to a parenting and the positive qualities of mother brings the parenting because the dad was just a good contrast with the mom, you know, He knew she would grow out of it for the most part. And he just kind of let her be free. And the mom wanted to be a girl. But like some of that was actually what she needed to hear. And it was just a good little balance of the the the different perspectives and attributes fathers can bring to parenting and mothers can bring to parenting, you know?
+Jordan: So, yeah.
+Darius: Anything else for Aqua?
+Jordan: Yes, already already birthed through my nineties crush point. But we cannot understate the talent and beauty that is in this movie. Got to, you know, young Gabrielle Union. I feel like up until like 2003, all she ever played was like mean vixens in movies.
+Darius: Because she's not a great actress. I'm sorry. She's very, very, very attractive woman, but she just can't act. And so point me to the movie where she was like, wow, this is cinema. I'll go watch it tonight or tomorrow, but I haven't heard. She can't act. She was so bad in those things like a man movies just.
+Jordan: To be fair, I think everyone was bad in the second one.
+Darius: Well, yeah, fair. All right, act two, the halfway point. Now at USC, both athletes face the pressures of collegiate sports and personal turmoil. Their relationship is tested by family secrets and the different paths their professional careers begin to take. You know how I feel about whiny *** grown men. I was not just was not feeling Quincy's despondent behavior during this act. So I will expand upon that later. But what do you got for act 2?
+Jordan: So my first note for act 2 is, you know why this movie had like a relatively small budget is because there's a scene where they're working out the other girls college team and they're benching with no rack. That's a really good way to hurt yourself.
+Darius: Yeah. Which is crazy because I thought this movie had a run. It doesn't feel like a cult classic. I thought, I mean, I was young. No, not at all. I remember it being in theaters and being popular.
+Jordan: Yeah.
+Darius: Oh. What else you got, Frank, too?
+Jordan: One of my favorite scenes in the movie is when they're in basketball practice. And she rips old girl and pulls up for three in the three in transition and holds the goose. And then the coach is like, I love that. Let me see you do that again. Do it for the whole practice. I mean, that's my favorite scenes.
+Darius: As a freshman, you shouldn't be doing that. You should be. Yeah, that was that wasn't a great look as a freshman. So she was a little, you know, she needed, she needed some humbling. Yeah, especially, you know, On the like women's basketball is so much more competitive than men's basketball because there's just so many there's just so there's so much less opportunity, and so right No girls, they, that's those are those are tough. That's tough. And yeah, she was only there because someone else had to leave Some I guess another girl got pregnant and.
+Jordan: Yeah the girl got pregnant Tanya Randall got pregnant.
+Darius: Which I don't even think is legal anymore to kick someone off the team for getting pregnant, but This is 2000. And it was just, Monica came in a little, little, little, little hot-headed and she got humbled a bit and it worked out for her because she kept her head down and she took advantage of the opportunity when it came to her.
+Jordan: So yeah, and I think a lot of people don't realize is like this movie just came out in 2000, but it's set during college in like 88. So at that point, talking about the competitiveness of women's basketball, WBA hadn't been created yet. So literally it was like, you're going to hoop, you're going to go to college and then you're going to go overseas.
+Darius: Yeah. And the overseas spots aren't plentiful, you know, is like, right. And, you know, so yeah, this is it. You have to look at it if you're watching this movie like this is the NBA to them. You know, that's this is the highest level of the highest level. And. when they go play overseas, that's a step down in competition than USC. it is USC, man. That's where Cheryl Miller went. You know, this is serious business, you know, so hell yeah. Was she wrong for leaving him on the night that she had curfew?
+Jordan: I don't think she was wrong, but I get why he was mad. Like that's one of the situations to me where like no one was in the wrong. It just was this it just was what it was like she had she had to make curfew because she was she had to hoop she's there for college she's like that she's on scholarship I'm assuming that's probably how she's paying for school you can't miss you can't miss no games and like you know what I'm saying you're a freshman already you're already on a short leash remember there's no WNBA so you don't know like this really is it for all you know you got to you got to you got to go to bed and I get why he like he could have I'm assuming he could have went into her dorm I'm gonna guess So, she wasn't wrong.
+Darius: I found his behavior irredeemable. First of all, the pouting, the whining. And then it's like, if any, like she said, if anybody should have understood, it should have been him.
+Jordan: And then- Correct.
+Darius: I just, I found it so off-putting and irredeemable. He's just pouting like a big *** baby. You're a grown man. I get that you're going through some personal turmoil, but men are supposed to hold it down. Men aren't supposed to cry and pout and ***** and moan. And yeah, I just found it disgusting. Then he's ******* up in basketball because I guess he's stressed or.
+Jordan: Yeah, exactly.
+Darius: Whichever one of these buzzwords they have. And I just, I'm glad that she left him there. took care of her **** and went and sought what she needed to see. And it worked out for her. And I'm glad it didn't work out for him. There. Men should not be rewarded for pouting.
+Jordan: That's valid. That's valid. And also like I wrote this down, but I don't think first of all, if you're not married, you should never put your goals over your, pick your partner over your goals. I also think if you're under 30, you should never put your partner over your goals. I think that's just wildly stupid and irresponsible personally. So for the listeners out there, do not move for the partner. Do not pass up that job opportunity for your partner if you're under 30. That's just silliness.
+Darius: Under 30 is a little late in life. That's a little millennial Peter Panish, but definitely not in college and definitely not before you're married.
+Jordan: No, I'm saying if you have like us like actual opportunities, you know what I'm saying? Like you have a job offer. Take care. You know what I'm saying?
+Darius: And also, like I said, if you're not married, well, yeah, you should be married at that point. You know, if you're moving together, you should be married. So, yeah, no, certainly not in college. You know, the worst, like the boy meets world where Topanga turned down Yale for him. He turned out Yale to be with your high school boyfriend. High school sweetheart.
+Jordan: Yeah, that was ******* nuts.
+Darius: Yeah, bad message to say.
+Jordan: He definitely was an anchor for her. Looking back at it, like as an adult, as a kid, you're like, oh wow, that's so romantic. And as an adult, you're like, she ruined her life basically for him.
+Darius: Yale is one of the most prestigious universities in the world, not just the country, the world.
+Jordan: Yeah, the world.
+Darius: To turn that down for ******* your neighborhood high school boyfriend.
+Jordan: Corey Matthews.
+Darius: Pure insanity.
+Jordan: Yeah.
+Darius: You got anything else right too?
+Jordan: Yes. I mean, so there's the affair, obviously, then he starts to crash out. He starts spiraling. And then they have their breakup. Did you think that? I don't know where this. Like he he do you think she was being immature by not wanting to be friends with him after the breakup?
+Darius: No. Friends, no. I'm not opposed to staying close with some with an ex, but like immediately afterwards, especially when you broke up with me on some ****. Right. You know, because you basically asked me to put my lifelong dream to play high level basketball. Over you to listen to you cry about your family troubles.
+Jordan: Right.
+Darius: That's why you broke up with me. No, I don't. No, absolutely not. I have no problem with not being friends with him anymore. He was he was an unrepentant jerk in Act 2. I just not a fan of Quincy McCall. So I guess he was a junior, I think, because his dad was. I don't know. But anyways, I was not a fan's name was. Dennis Hayesburg was his dad's name.
+Jordan: Yeah. Yeah, that's it. Yeah, it's just it's interesting to me how naive he was like you thought your dad, the ex NBA player, rich in Los Angeles, was being faithful to your mom. And he was a he was a scout, but he was taking meetings at 1 a.m. Where the **** do they hoop at 1 a.m.?
+Darius: Nowhere. Nowhere. Thrown back because your parents are supposed to be your superheroes. First time you realize that they're human is a bit jarring.
+Jordan: Jarring.
+Darius: The way he just crashed out. And I mean, he act like he was cheated on. It is, wow, man. Yeah. Tighten up. Like you.
+Jordan: Yeah, I did like this movie. A big tenant of this movie is that your parents are people too. And I love that they show that because again, We don't really get that in black movies, I feel like. So I love that they kind of showed that like his father was a good father. He just wasn't a good husband. And I just wasn't a good. He wasn't a good husband, but.
+Darius: Well, I guess they got divorced, so.
+Jordan: Yeah.
+Darius: I was going to ask something controversial, but I don't feel like I don't feel like it.
+Jordan: Okay.
+Darius: An affair is not in and of itself a permanent stamp of bad spouse. But I've said this before that I just I think real life is complicated. And it's not they're not mutually exclusive. Like you can be a good husband that had an affair. That doesn't mean that all husbands who have affairs are good husbands, but are good husbands.
+Jordan: Right.
+Darius: Yeah. Like Life is life and life is complicated. So it's not automatically a rubber stamp of bad partner. You know, people people recover. Like I've said on the pod the other day, the people who recover from affairs, you never hear from, you know, so right?
+Jordan: They keep that.
+Darius: They're not the ones ******** about it on Facebook. You know, the reason why they work through it is because they didn't they invited you out of their business, right? So Correct. Yeah. It's got to be careful with this.
+Jordan: He did bring up. Yeah, he did bring up a good point where he kind of he brought up the fact that like, you know, they didn't plan to have Quincy. They didn't plan to get married. It just happened that she got pregnant when she was young. So he married her. Doesn't mean he didn't love her, but that does matter. You know, yeah, like life is life. Life is hard. Life is complicated. There's no, you know, all the **** is difficult. We're all like, There's no roadmap to this ****. But yeah, getting caught with the PI is crazy.
+Darius: The PI, man, they was making out in the hotel lobby. You know, I. Yeah, this surveillance day you might. This is 2000, but now with ring cameras and cell phone cameras and this, that you might just want to be James.
+Jordan: Bond to get away with it. Yeah, you might just want to stay faithful people out there. There's no way to hide it. I don't know how you do hide it, honestly. This day and age you got to be James Bond to get away with that ****.
+Darius: Pretty much, man. You got anything else for act two?
+Jordan: No, that's all I got for act two.
+Darius: All right, we are going to go into act three, the final buzzer. Years later, after playing internationally and facing injuries, Quincy and Monica reconnect. One final game of 101 determines the future of their relationship and their shared history on the court. This movie reminded me that Tearing your ACL used to be like a catastrophic thing.
+Jordan: Yeah, it was a death sentence.
+Darius: Yeah, I just, you know, we've gotten so used to a year off back as good as new, but yeah, like the way, I mean, The way it felt like he died, his career ended, basically. And so it was just, it was a nice little, oh, this is, it was the first time the movie felt a little dated. So yeah. What you got for act three, man.
+Jordan: Yeah, I thought the same thing. For act three, I saw, we'll talk about the conversation she has with her mom in the kitchen. The second one, after she told, before she, after she told her that she was better. better than the girl that he was going to marry. I love the fact that first of all, they finally aired their **** out because, they both were looking down at each other. I just think that the mom didn't want to admit that she was looking down at her. So she was able to say like, you look down at me because I'm a housewife. I did love that she kind of broke down like my dream was being home so I could spend time with y'all so I could be there for the **** that matters. I could get you ready for prom and your big dance and give you my mother's pearls, you know, a family heirloom. aside from the fact that, obviously I could have had a career, but I chose family life over, she did basically what he wanted, Quincy wanted her to do in college. And then of course, it was crazy though, like not going to your child's games. I don't, that's insane to me. But she did point out that she kind of realized, she thought that she never wanted her there, which is why she didn't go. And one of my theories on parenthood is that like one parent's always like there in terms of like physically present. but the other parent is the one that the child really needs more. And they often rarely never make that connection. And that's why I feel like every kid, a lot of kids for the most part have one parent where they're like, this parent understands me, this parent gets me, but I really want this parent to see me. And I feel like they can't see me. And I feel like this movie did a great job of showing that.
+Darius: Yeah, it's fine to feel that way as a child. It is wild disrespectful to come at your mom like that.
+Jordan: No, she was out of pocket.
+Darius: I was wondering why I'm like, what did she do to you? Like, what? Like, why are you? I just, I don't even know where that came from. I was like, all right, so first of all, you actually, okay. The movie wanted to make her out to be, Coella Deville about the basketball. And she was just like, hey, let's do your hair. Hey, how about you wear a shirt? Like she played all through high school, all through college. I'm sure ************* parents paid for it. What do you, what do you, what do you, how do you just, why do you ask people? What are you crying about? Like you came at your mom like that because she was a stay-at-home mom. All she ever did was make sure that you were straight. And You followed your dreams all the way to Europe. It was ******* ******** about it.
+Jordan: You got all the support you needed.
+Darius: You reached the highest level of basketball and you're mad that she didn't she didn't clap hard enough in the 8th grade. Give me a ******* break. These people are ridiculous. Pops got you a job at the bank. You in the suburbs. You living next to professional basketball players. You were a great.
+Jordan: Yeah, let's keep it a stack. That was not the separate. Those were mansions.
+Darius: Yeah, had a pool in the back. Correct. And it's like, you have NBA players next to you. Whatever your dad doing, the money's rolling in. Your mom didn't have to work. Right. And so I just thought, I don't know where this animosity came from. You got to do everything you wanted to do. So occasionally she wanted you to wear a dress to church. I get being frustrated as a child, but as a grownup, You got to. You got to. You got to charge that to the game. I don't know. I don't get it.
+Jordan: Yes, that's a good point. I think we do need to remember that these all these characters are super duper young in this movie, too. But they're like 17 between 17, like 24, pretty much the whole movie. So I don't know how mature I would have been at that point if I felt like I wasn't being supported in my dreams, although she was supporting her dreams.
+Darius: Under what pretest would she feel that way though? What do you want them to do?
+Jordan: I mean, I guess we don't know. I mean, I guess we don't know. Yeah, but I was going to say, I think that that's maybe what it was. Maybe that they weren't. They didn't visit her enough in Europe. I don't know. Yeah, I thought like her. I mean, her mom would say like. little things. But I mean, she wasn't malicious. She wasn't out to kill her dreams, you know, she wasn't the like the Tyler Perry mom who's like, I'll destroy her children, you know?
+Darius: Well, yeah, Tyler Perry would have written it so over the top. She would have literally had devil's horn.
+Jordan: He traded me for $10 in a fix.
+Darius: Yeah, right. It was so bad. Can we be honest for a second?
+Jordan: Yeah, what's up?
+Darius: Let's play for your heart is corny as hell.
+Jordan: Oh, of course.
+Darius: That did not age well. I was a little cringe. This is ******* like what?
+Jordan: That's how you know that this movie was written by a lady. I mean, I don't mean that in a bad way. Writer, director. She's actually great. She's made a lot of great stuff since this movie as well. Don't give her props. Sorry, go ahead.
+Darius: I was going to say, I think, yeah, I was going to say, I think she's pretty successful, but that was just corny, man. And, you know, prom coms need a little corny, but that was like, man, this is, they literally were like keeping score. And it was a little cheesy. So it was a call back to the door when they were playing for close. But it was, right.
+Jordan: Yeah, so Gina Prince by the Wood, that's her name. I want to make sure I got it right. She did Secret Life of Bees, The Woman King with Viola Davis, Beyond the Lights, and Disappearing Acts. So yeah, she's legit. Yeah, so okay, so women, a lot of women talk about this movie and they say it's a horror movie. And they usually reference the basketball scene because he beat her and then dunked at the end. And I think I think it literally was just like they were competitive and they were they, love basketball. So he was like, I'm going to beat you. So, I can beat you. Now I'm going to let you know I love you and I'm choosing you.
+Darius: Got to establish that.
+Jordan: Am I crazy?
+Darius: I think we should probably phone a friend, a female. We're not going to, but I agree with you. But we're both men.
+Jordan: Yeah.
+Darius: You know, I would definitely win. Got established dominance. But why do they say it's a horror movie? That scene alone? Is there is there discourse that I missed?
+Jordan: I mean, I think I mean, I think the way he acted, he treated her kind of like **** in college. He did a little bit, but they're 18. Who cares? I mean, who cares?
+Darius: But they're 18, you know, jerk, a whiny man baby who had severe main character syndrome and could not understand, could not put himself in anyone else's shoes. It made his problems the whole world's problems. I understand that.
+Jordan: Yes, he was very selfish. But there was never a point where I didn't think he loved her.
+Darius: And also she still achieved every, she went to Europe and played for a championship. So it's not like.
+Jordan: Yeah.
+Darius: It would be a horror movie if she gave all that up to stay at USC with him and pop out babies.
+Jordan: And became his wife and yeah.
+Darius: It was actually kind of like, it's almost like a, and granted I'm a dude, but it felt a little feminist that she went and left. Yeah, I thought the same thing. And went to Europe and won a championship and came back and then made to the league. said, and then it ends with him clapping, watching her poop. And so. Exactly. to me, the message was, you can have your cake and eat it too, because Monica did.
+Jordan: Yeah.
+Darius: But again, I'm a dude, so I don't know.
+Jordan: And chase your dreams first.
+Darius: Yeah, she did everything. She checked all her boxes before she came back to his regions.
+Jordan: Correct. And by the way, If we're going through the stack, she was better comparative to her competition than he was to his. Yeah, I mean, he's remember, he was coming off the bench when he got hurt. He was a scrub.
+Darius: He was a scrub. And then he got hurt. And he was, I mean, he's just, he, yeah, he was, yeah, I'm with you. He's a scrub. So.
+Jordan: Yeah, so I don't, I didn't really get, I don't really get it. I do. I think she loved him more than he loved her. You could make that case. Yeah. But they did love each other.
+Darius: Yeah, I mean, I don't know. These things ebb and flow, sometimes.
+Jordan: True.
+Darius: These things ebb and flow. So, but it ends with him being stay at home daddy clapping, baking cookies while she goes to work playing basketball. So I'm not sure.
+Jordan: Right.
+Darius: If the wrong message was conveyed, even though I think that he was, he was not, he was not a great guy in college. So, but who amongst us was?
+Jordan: Right, who at 18 was like, oh yeah, I'm ready to be a husband and a great, great boyfriend.
+Darius: Yeah, like, I'm sorry, but if, not handling your first breakup well is a death sentence, then I'm out of here. Yeah, I'm glad there was no internet back then. Or that there wasn't Internet, but that.
+Jordan: Yeah, we got to get people to grow. And yeah, that's why I don't do the digging up of tweets.
+Darius: Like if you tweeted it when you were a teenager, I'm charging it all to the game. I don't care. If you had given me a Twitter or an Instagram account when I was 16 years old, ain't no telling what to be on there. So I have a full moratorium on anything said before the age of 18. I'm not doing it. So Beyond that, case by case basis, but if you are a teenager, you see them tweets from like 2015 and I look up and the dude's 22 today, charge that **** to the game. I don't care. Yeah. I just don't care what a 15 year old said on Twitter, you know? It doesn't.
+Jordan: Right. It was probably just song lyrics that people didn't know.
+Darius: You got any else Rag3?
+Jordan: Yeah. I think that's all I have for act three. Okay. So have you ever played one-on-one for someone's heart? And if so, would you let them win?
+Darius: No, I have not. And no, I w</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out the Trunk Pod with Jordan and Darius. I'm Jordan. You can find me on all socials at JordanBWriting.
+Darius: And I'm Darius. That's Deez. I love the area on all socials.
+Jordan: And this is our movie review segment. Today we're going to be reviewing Love Jones, came out in 1997, starring Lorraine Tate, Nia Long, Isaiah Washington, Lisa Nicole Carson, Bill Bellamy, and Bernadette Speaks. Love Jones is about Darius Love Hall, not of out the trunk pod fame. Smooth.
+Darius: My namesake.
+Jordan: A smooth talking poet meets Nina Mosley, a gifted photographer in the Chicago Jazz Club. They bond over shared passions, but they're what? Oh, fledgling romance is quickly tested by past relationships and internal doubts. The 2 navigate the is it love or just a thing dilemma in the city. So I'll toss it to you for act one.
+Darius: Act one, the blues of beginning. Darius and Nina meet at a poetry reading where he performs his brother to the night. Their instant connection leads to a rainy first date that challenges their cool, detached exterior. Off the rip. I feel like everyone is just pretending to like jazz music. Like is this like in this movie or in life music with no lyrics. Who's still doing this? Who is like, who is like, hey man, put on that, put on that latest jazz album. Do you even know that? I feel like jazz, I look at jazz like I look at like ventriloquist dummies. It's like, Before we actually had actually entertaining things to entertain us, we like pretended this was good. It was like, I don't see his mouth moving. It's funny. Ha ha, the doll is talking. It's like, no, like now we have TV, so we don't have to pretend that anymore. Now we have songs with lyrics. We don't have to pretend to like jazz anymore. That's my point.
+Jordan: As a band kid, jazz is cool. I'm more of a blues guy myself. So if you're gonna ask, like, I'd rather listen to blues than jazz. I feel like jazz is for people who have a lot of time on their hands. You know what I mean? Like when I'm in the hustle and bustle of my day, I can't just bump out right. I can't just like I'm working and **** and I'm like, you know, peak like performance. I can't just like vibe out to like the sax. You know what I'm saying? So it's not great lifestyle music depending on your lifestyle.
+Darius: A jazz hour will be like 60 minutes. I'm like, you listen to an hour of music with no lyrics. I don't believe you. I feel like this is added to the list. Sushi, jazz music. It's just things that opportunity to like.
+Jordan: Nah, chill out on sushi. I love sushi. I **** with sushi.
+Darius: No, I think we're all, it's a game of telephone. We're all just pretending to like sushi.
+Jordan: Nah, I love sushi. That's not an act for me.
+Darius: I just don't, every time I've had sushi, I've been like, okay, it's fine. Like if we're out with a group of people and they wanna go get some sushi, I'm not gonna, that's fine. I can go roll with it. But like I've never on my own accord be like, damn, I'm gonna go get some, I'm really craving some sushi. Never.
+Jordan: Really? I love sushi. I can eat that every day.
+Darius: All right, man, what you got for act one?
+Jordan: I love this movie. One of the things I love most about this movie is the cinematography. It just really, it shows like the reality just of like everyday life and of black people and also just the beauty of the city of Chicago. Like there are so many scenes in this movie where it literally just looks like a beautiful photo that you would have framed like in your dining room somewhere, you know? Sexy funny because I was talking about this yesterday, the other day with a friend who's thinking about getting into photography and I was saying, one thing that may help with that is watching movies because you'll see it's looking for photography in a way. It's just obviously motion picture and you can see how the shots are set up, shot composition, what's in the background, what is the director wanting you to focus on, things of that nature. So this movie is a perfect example of that. Also want to say that the opening poem that that guy's performing at the first open mic meeting that they go to, it always makes you think of that Kendrick poem from Butterfly where he's like, **** **** ain't free.
+Darius: I forgot. Man, I haven't, I haven't spent a butterfly in a while.
+Jordan: **** **** ain't free.
+Darius: That's pretty good.
+Jordan: That's the first thing I thought of, yo.
+Darius: That was a great album. Random question. Did he perform any of the songs from that album on the tour?
+Jordan: From Pimp Butterfly.
+Darius: Yeah.
+Jordan: Let me think. Let me go to...
+Darius: Did he perform all right? I know he performed all right.
+Jordan: Yeah, he did all right. Yeah, he did all right.
+Darius: So he did. He did.
+Jordan: No, and he did King Kunta. He did. Oh, yeah.
+Darius: Okay, cool. All right. Random aside. But what else you got for act one?
+Jordan: One thing I love about 90s movies, and I don't know if it's just nostalgia, you know, because you think that **** is better when you grew up, when you watch the growing up, but just like movies with people who look like real people.
+Darius: Yes.
+Jordan: Like everyone looks unique. It's not, they don't all look like the ******* bold filter from TikTok or the insert filter from.
+Darius: They didn't all go to Miami, both men and women.
+Jordan: Yes, correct. Everybody looks different. Everybody looks, you know, they're all beautiful people, but they all look very different. You know, And I love that it's a movie with black people who don't, it's not, oh, we didn't find a bunch of Eurocentric looking black people or ethnically ambiguous looking black people or, you know, a bunch of sandpaper, you know what I'm saying? A bunch of Zendaya look alikes. She's beautiful, but you know, get my point. You know, so yeah, I just wanted to point that out.
+Darius: We need some sort of like marker for when you veered into too woke. You know how the Fat Joe Jadakiss podcast has the flag? I we do that. George is being a little too like ethnically ambiguous black people.
+Jordan: You know what I'm saying? Like, no, she's not ethnically. She's clearly black. I'm saying like, **** I don't know. I had somebody on to my time. I'll think of it later.
+Darius: I think Halle Jerry is a good one.
+Jordan: No, she looks black.
+Darius: All right. I don't know. I you lost me.
+Jordan: So I maybe like Zoby Kravitz or somebody like that.
+Darius: Fair enough. All right. Getting an address from a woman's checkbook and showing up at her home. Ill advised. Don't do that.
+Jordan: Yes. Don't ever, ever do that. I don't care how well y'all hit it off at the open mic night.
+Darius: You know, also, you know, And this might be my own sensibilities. Off the rip, the overly ***** poem. It's a bizarre.
+Jordan: Yeah, it was a crazy shot to shoot. That actually was a crazy shot to shoot.
+Darius: It worked, but this is a movie. Something else I'm like, man, this is. Yeah. Y'all have it. You ain't, you just met this one. Like, you only know her name.
+Jordan: You only know her name.
+Darius: You know, you haven't shared an appetizer yet, and you just pulling up ***** poems off her.
+Jordan: That's a bold strategy. Cotton, see how that works out for him. You know, he definitely, like, it's, you know, a rom-com or rom-dram, whatever. So, you know, you're supposed to like the couple and all that, which we do. But the **** he did was There's like the romantic and then there's stalking.
+Darius: Yeah.
+Jordan: And he crossed that line very well in this movie.
+Darius: I don't even, I guess. Euro stepped over that line. That line. No, I thought I loved, it's just something about 90s movies. It might be this, it'd be every generation feels this way, but it just looks like the best time to be alive. I was alive in the 90s as a child. I wasn't outside. Being outside in the 90s just looks like the best time to be outside.
+Jordan: So much fun.
+Darius: The music was, I think the 90s had some of the best music.
+Jordan: Yep.
+Darius: Like you say, everyone looked normal. Everyone could just be chill. It wasn't, everything wasn't for the gram. And I know about the sound old. People did take pictures and everything. People did. But it did. It did. It just looks like a better time to be outside.
+Jordan: Yeah.
+Darius: I just I always get nostalgic when I watch these 90s movies because I just I wish I was an adult for it, you know?
+Jordan: No, me too. I wish I was at least like. I wish I could have at least been a teenager in the 90s. I feel like that even would have been like peak, you know, it just feel like everybody like people were more. I don't know, aware. They were more social.
+Darius: More social, less socially awkward, which is the same thing. But yeah, just you went outside looking for adventure in a way people just don't anymore. You know, the way they're out, they're walking in the rain. And he just like, you want to go check out some reggae spot. And yeah, it's on the other side of town. And like, They just go **** it, and what would it like if we wanted to go hear some live music on a Wednesday night, where would we even go here? And the people know we live in Raleigh. I wouldn't even know where to go. Right. Like just.
+Jordan: Yeah, no, I yeah, I don't know where to go. Actually, I don't think.
+Darius: The cities were just more alive. They were more serendipitous. Yeah, people were just more adventurous. Like you. You didn't leave your house with an itinerary. You just let the day happen to you.
+Jordan: Right. And I feel like another thing too is that I've noticed is like, they, everybody in the movie that didn't know each other, they became friends throughout the course of the movie.
+Darius: Yeah.
+Jordan: And like that doesn't really happen in life anymore. If you don't have your set friends by age 22, like, or 23, you're gonna have a hard time making friends. Like I know that, like I've talked to people, adults, you know, in their 20s and **** about this, where they're all like, I don't know. how to make friends as an adult because there's nowhere to go. Like, you know what I mean? Everywhere you go, you go supposed to go with your friends. But if you're supposed to go with friends and you don't have, a lot of friends, like, can you go or people are socially awkward now, so they don't want to go without their friends. So they're not meeting people, even though that's what they want to do the most, you know?
+Darius: I will say that people, have to be a party to your own rescue. You know, you're not going to make friends watching Netflix every weekend. You have to, you have to. Take some risks. Yes, it might be awkward to be the only person there without a group, but how else are you going to join a group if you don't show up? True. Yeah, that's true. You have to, the worst thing in the world, you know, like what's the worst thing that's going to happen? You're just going to go there and it's going to be, feel left out and you're going to go home. Okay, fine. But the upside is you might need some people and, you know, you have to be, you have to take some risks. And I feel like people have lost that risk-taking feeling. everything is safety first, safety this, and that's important, but a life without risk is a dull one. So, we'll take a quick little jab at you right quick. So, as an ex-poet, what do you miss about the stage? When you miss most crazy? At some point, you're just an ex-poet.
+Jordan: Ex-performer. No, I'm actually planning on getting back on stage this month.
+Darius: I'm just going to keep bringing it up.
+Jordan: I know, and I appreciate it. You do need friends like that to push you and stuff, you know, as a compliment, because that means you don't think I suck pause. Correct. So, you know, major pause.
+Darius: No, man, when you get on stage, man.
+Jordan: I got some pieces in mind. I got one piece. I may be maybe ready to perform. I don't know yet. So I may go tomorrow. I may wait and save it for next week. I'm not sure yet. But yeah, what I miss most about the stage is the uncertainty.
+Darius: Yeah.
+Jordan: Because you go up there and you don't know if your piece is good. You don't know if your piece is going to connect with people, if it's relatable, if you sound crazy when you're saying it, if you overshared, if you think you look stupid or, you know, whatever. That's the only thing I miss because you go up there and it's you. Like writing is kind of the most, probably the most lonely of all the creative endeavors, I'd say, because no one's there when you're doing it. And even if people are there when you're doing it, no one's, I'm the only person in my head, you know what I'm saying? I'm the only person that have had my experiences. So you have this thing where you think it's just you and you don't really know until you start speaking. And even like the first couple of lines, no one wants, there's this weird thing where like, There's performance anxiety, but I also feel like there's like a listening anxiety as an audience member where no one really wants to be the first one to say they connect with whatever you're saying, depending on how vulnerable it is. So like, it's almost like the first couple of months, people kind of wait and see like, well, I look crazy if I were a snap or if I relate to this, you know? And then once a few people start, then it's like, okay, cool. Everybody can acknowledge that they connect with that thing, you know? So much so to the point where there are pieces I performed where It doesn't maybe get a lot of live audience feedback, but that's sometimes how you know you're doing really well because it's so honest that people are uncomfortable. And then they'll come up to you like after the show and like, yo, I really connected with that or I really **** with that or they'll DM you. So I'd say for me, the best part of performance is the uncertainty. close second would be the rush, like the high you get is it's like, I've never done like hard drugs, but I'd imagine it's like, you know, doing cocaine or some **** like that, you know what I'm saying? Or a Valium or something like it's like it's like it's such a like you feel like you're like buzzing and you feel like 8 feet tall when you get off stage and you know you killed it.
+Darius: Fair enough. Well, they say poetry and stand up are the only art forms where you can't you have to practice in front of people, you know, you can't If you write a song, you write a rap, you write a song, you can play it in your garage until you get it right. But you'll never know if your joke is funny or if your poem lands until you actually do it in front of people. So you have to practice.
+Jordan: Correct.
+Darius: You know, you don't get a parachute, you know, so.
+Jordan: No, not at all.
+Darius: You can do what the rappers do and release a snippet, a leak to see if people like it and pretend the leak never happened if they don't. And even that two fingers touch it, that'll never see you release.
+Jordan: And that **** is never coming out. That **** is never just in the light of day. Thank the Lord. And honestly, for me, I feel like the whole snippet release thing, being an artist is scary. So I acknowledge that. But to me, it's just like the height of cowardice. Just drop the ******* song, bro. Put it, put it out. And then you'll get the feedback that you want. can't tell if a song is good if you play 40 seconds of it.
+Darius: A little quick snippet. And then, yeah. And also, like you said, it's 40 seconds. Well, hell, these songs nowadays ain't but a minute and a half. But, you know, clip 40 seconds from a lot of songs, it would sound crazy. You have to, you know, a song is a story. It's a journey. You posting on story with 30 seconds of it playing and using the comment section to determine if you're going to release it. That's not artistry. Like you said, that's cowardice.
+Jordan: Correct. Yeah. So there was that conversation at the table with the previous main cast of the movie. And they're talking about romance and like whether or not it's dead, what romance means to each of them. Someone's asked you, what does romance mean to you? And do you feel like it's something that once it's dead can be reborn or revived?
+Darius: What does romance mean to me? You know, I want I once had a friend. I mean, I still have a still my friend, but he he's a ***** you know. Mary guy all the time, you know, and so he once asked me, like, don't you know, don't you want someone to go do stuff with go out that a lot. And I once told I responded, I said, you know, you have it backwards, you know? I'm ineligible. I'm a handsome guy. I can get a date. Like I can find someone to go to a museum with, to go to a theme park with, to go to the bar with. It's finding someone to do nothing with. That's hard. And so I wouldn't say that romance to me is having fun doing nothing and being in each other's presence without, because again, everyone's fun bar hopping in downtown Glenwood, you know, that's easy.
+Jordan: Right.
+Darius: But Post it up on a Sunday watching football. You're not getting on my nerves. That's love, baby. Like. So I was. That's what I tried to tell y'all. What did you say?
+Jordan: That's what I tried to tell y'all. I made that joke about not dating during football season. Yeah. Cause I don't want to have to make anyone feel ignored when I'm watching football. It's just a joke. I do date during the season, but you get what I'm saying.
+Darius: No, I mean, it's true. It's Finding something I don't mind doing. Finding someone I don't mind doing nothing with, I would say is what romance is to me. How about you?
+Jordan: To me, romance is kind of a two-part answer, I guess, is making someone feel special on a regular basis, more than just on special occasions. And I'd say to me, The pinnacle of romance is world building. It's like creating and establishing that relationship where it's just the two of you and it's literally like a whole world, not just in your head, but in real life. Like when you're just like, you said, like in the bed on a Sunday or you're just chilling in the living room on the couch, binge watching or trying to figure out what to watch or just sitting and talking. Like some of my favorite moments in relationships were just. sitting up talking late at night for hours with nothing, like no music, no sounds, just us, you know, being together, exchanging thoughts and experiences and stories and laughs and stuff. I think, you know, and talking about like the future and things and it actually being something that you both want as opposed to it's some sort of fantasy one's projecting onto the other where you're just actually able to exist as you as your authentic self. Like I've been in a lot of places where like I where you just knew you couldn't really be your full self, like not even that you weren't acting, but it was, maybe a toned down version, things of that nature. So it's like, you know, you can kind of let the, let the facade down, let, you know, let, all of the, armor away and lay it all to the side and just kind of be with your person.
+Darius: I agree. Yeah, it's, When you ever meet a couple and it feels like they speak their own language. That's.
+Jordan: When Yes.
+Darius: They're locked in. You just like.
+Jordan: Absolutely.
+Darius: They say words that are only funny to them. Like they're words that you could recognize the word, but it's only for them because there's some context that everyone else is missing. You know, they were walking in a grocery store and they saw it and it was some joke that they had. And, you know, six months later it pops up and they just fall out laughing and no one understands what the **** they're talking about. Yeah. that's it right there. That's that magic. But enough mushy **** Act 2. The rhythm of doubt. As their relationship deepens, the return of Nina's ex-fiance creates a rift. Insecurity surfaces, both Darius and Nina hesitate to admit their true feelings, leading to a frustrating emotional stalemate. Man, when he said, you must be going to see some dude, man, he said. He was ******. If you pause the movie, you could see the steam coming out of his ears.
+Jordan: Yes. Actually, if you rewind 10 seconds before you said that, when she says, oh, she remember she lists like 8 things she had to do in New York before she mentioned the dude. And then she's like, yeah, I got to talk to this dude. And he was just like, Like, you could all see him almost go like this *****. Like, yeah, well, he.
+Darius: Well, first she said, I got to see a friend. And he knew he knew what that was. He said, Yeah, yeah. So right.
+Jordan: First it was about a job. Then was about a friend. Okay.
+Darius: And then it was what it was really about. So. Right. What you got for act too bad.
+Jordan: Yeah. Yeah, I always. So there's the scene where she before that, where she's talking with her friend and she's like, you should tell him you're gonna go. If he's mad, he cares. If he doesn't just go do your own thing. And I appreciate the friend was like, be honest with him. But I hate that whole thing of like, go test your partner. And if they pass the test and you can be with them thing, you know, like it's first of all, it's the height of manipulation and emotional abuse. And 2, it's like, if you give people a test like that, people are, what else would you call that? Emotional blackmail, fine. It's like if you give, if you put someone in a position where they're forced to either look vulnerable, possibly pathetic, or, you know, hold on to their self-respect, they're going to choose to self-respect. Yeah, for sure. No one's going to be like, oh yeah, and no one's going to be like, oh yeah, I don't want you to leave. Stay with me. But you're in contact with your ex, which means you're already entertaining it. That to me is all the doubt that I need to sever the relationship.
+Darius: Like a wise man once said, man, if you want to be chased, go rob a bank because I ain't got it. Like, I'm not.
+Jordan: Yeah. What was he supposed to say?
+Darius: Yeah. I wouldn't have reacted either. I mean, obviously his feelings are hurt and he communicated that in a way that kept his dignity. But no, I mean, like he said, y'all weren't anything. Y'all were just sleeping together. And he had no right to say that, Yeah, yes and no. I think people get real technical when they know they're doing what they ain't supposed to be doing. We never had to talk. I never said I was your boyfriend. Okay, but yeah, we all grow here. You know, there's a reason why she said Fred last. It's because she knew, you know, there's a reason why she approached that real slow. And it's because she knew. what was going on. And so I feel like people love to play. This is not law school. We're not lawyers and you know what was up. So.
+Jordan: Cause you know what you was doing was wrong.
+Darius: We kind of alluded to it earlier, but man, so many 90s movies rewarded men for not taking no for an answer.
+Jordan: It did, it did. This whole movie is just coercion.
+Darius: Oh man, dude. Popped up at her crib. She's like the first date. She's like, no, you're not coming in. And he's like, I just want to have a cup of coffee, please.
+Jordan: Let me just have a cup of coffee.
+Darius: Wow, man.
+Jordan: He was doing a lot of begging.
+Darius: The OG in me wanted to jump through the screen like, go home.
+Jordan: Go home, Roger.
+Darius: She told you she wants you to leave, bro. Just leave. What is you?
+Jordan: Yeah, man, he did a lot of, yeah. If this was happening in 2025, He'd be in that group that girls use to talk about dudes. And it'd be like, don't date this guy.
+Darius: He's on my door, Stephanie. He wouldn't go home. Are you kidding?
+Jordan: He found my address with check.
+Darius: Yeah, it's like.
+Jordan: To see me and I didn't want to see him.
+Darius: Yeah, it's not a good look that's rewarded, but I mean, movies are fiction and it's. on people's families and parents to raise them to do the appropriate things. So I'm not blaming the movie for inappropriate behavior, but it's not a great message to tell young men that this is an appropriate. to just show. But you took her out. Y'all had a great time listening to reggae music, got a little grind, cool. Got a little good night kiss. She's like, not tonight. You need to leave. The night's over. Get out.
+Jordan: Get out of there.
+Darius: There's no more questions after that. You need to go home.
+Jordan: Yeah, you lived to fight another day.
+Darius: It was the first day, man. You made some good progress. Y'all went to two spots.
+Jordan: Hell yeah.
+Darius: Good little dance. Good night kiss. She let you walk her home. Take that one, man. She didn't.
+Jordan: She didn't call the police after you showed it to her house unannounced. Yeah, man, you up.
+Darius: Take that one and go and go home, man. There's another thing. You might, you know, just you go take another shot at that one. You good. You're doing well, right? You know, I agree. What else you got for act two, man?
+Jordan: I was going to say, yes, going back to the X. So she did that. And by the way, even like so she goes back to the X, they have a fight. and she doesn't get a job in New York. And so she basically ends the engagement that she resumed, I guess, and then just goes back to Chicago and then was mad at him for moving on.
+Darius: Yeah. This is where the act two to act three where the writing gets a little. Yeah, I'm like, yeah, what is she mad about? I even
+Jordan: Yeah, I didn't get it.
+Darius: I've dated some pretty unreasonable women. This is beyond the pale. Like you left me to go be with your fiance and you come back to got attitude because I'm seeing somebody like that is me. That's me. This is not even real. It's hard to believe there's a real person.
+Jordan: Yeah.
+Darius: Like you. We were cool. We were *******. We were late.
+Jordan: I'm trying to think. Right.
+Darius: Go ahead.
+Jordan: No, I'm trying to think if I can think of anyone who would who would actually be have that audacity. It's you know, that's actually insane, though.
+Darius: I mean, it's appeared like psychopathy.
+Jordan: Yeah, unwell.
+Darius: Listen, man, I don't know if this needs to be said out loud, but if you dump me to go link with your ex-boyfriend in another city, I'm not waiting for it. Like you can't.
+Jordan: No.
+Darius: Now, if you come back. And we find ourselves in a good place to where we could bring back up a conversation. I don't know, like real life is complicated. Cool. But to expect me to sit by the phone crying while you were away, that's absurd.
+Jordan: And wait for you.
+Darius: Right.
+Jordan: Yeah, that was crazy. And by the way, if it had worked out, you wouldn't have came back. So again, why are you mad?
+Darius: Yeah. I mean, he was a rebound. I guess that is a good question. I'll ask three. Act three, we're gonna call finding the harmony. After time apart and self-reflection by one party, the pair must decide if their connection is worth the risk of vulnerability. A chance encounter leads to a final realization about their future together. And I'm gonna wing this here. Did you see the Twitter prompt that was like, Name a movie where the woman is the bad guy and it works out for her. I have a suggestion.
+Jordan: Yeah. This movie. Yes.
+Darius: People want the obvious Jenna from Good Forrest Gump. But can we offer up Nina from Love Jones? I just don't think she was going to ask you.
+Jordan: Is she the villain in the movie? Is she the problem?
+Darius: I just don't think that she comes off well.
+Jordan: No, not at all. I think if not for Nina, Nina, well, Nia Long's charm, it'd have been a long time ago when people realized she would have, she was quite a succubus, quite frankly. Like she was just like siphoning **** from dudes. Like, you know, your ex came back and you were still not quite over him, which is kind of fine, which is cool. You rebound with this new guy, then you toss him to the side to go back to the ex. You didn't get your job and you didn't want him to have control over you. or provide for you which however you wanted to phrase it you go back to back to Chicago expect this to wait for you you mad that he didn't wait for you because he had motion which you knew when you met him which is why you liked him and then you date his friend and then you're mad at him for not asking you if you ****** his friend What?
+Darius: The only thing we're missing is her to reveal that she has AIDS and a son that she's going to leave with him. That's really it. I mean, she's checked all the other boxes.
+Jordan: Yeah, and like she was like the whole thing about she, his old, his ex called him at night one time and she thought he was cheating.
+Darius: Yeah.
+Jordan: I don't know if he was or not, but I think if he was cheating, he wouldn't have the number on the ******* refrigerator. I'm just guessing.
+Darius: Well, I mean, are stupid. So that's not necessarily.
+Jordan: Well, are stupid. True.
+Darius: That's true. No one they waiting on a girl, girl in a car, text. Oh my God, it happened. Like what you text come through.
+Jordan: Yeah, you're right. You're right. You're right.
+Darius: I can't believe this 10 year old technology bit me in the ***. I do want to take a moment of silence. We did mention this off the top. You mentioned she was Nia Long's charm. She was so fine in this movie.
+Jordan: Dude. Yes.
+Darius: Oh my God. I was just like. It takes a lot for me to be starstruck. She is gorgeous in this movie, man. Just out of this world. Anyways, I just, we can't go a whole pot without mentioning that.
+Jordan: No, you're right. There's a reason Harper cheated.
+Darius: Oh my goodness. I just. Yeah, there's a couple scenes. Yeah, no, that shot where she. It was like, man, this is cinema.
+Jordan: No, this is cinema. Martin Corsese.
+Darius: No, there's a scene where she's, it's raining
+Jordan: and she's like sitting by the window in like a nightgown or whatever. Like, that's about as beautiful as any woman's ever looked on cinema. Yeah, man. she had, but she had a lot of ******* nerve in this movie. Like that **** was outrageous. First of all, you date, you come back and you date his friend and then you're like, you're playing the victim because he took you to a party with his friends. Where the **** did you think y'all were going? You thought he was going to have you with strangers that you didn't know. Come on, man.
+Darius: Right. Y'all link. The first link y'all had was at everyone's house. This is what they do. Right. The 90s. back to, nostalgia. People didn't have to have a whole lot of bread to kick it in the 90s because just kicked it. They, we prepay, we want you play cards, you have to go out. There wasn't no sections and ****. You could just kick it, bring a bottle, bring a deck of cards and we might kick it all night. So that's what they did because they're</t>
+  </si>
+  <si>
+    <t>Darius: I hated this guy. Imagine adulthood. Imagine having to parent with this ******* man child as your ******* husband. I just, anyway.
+Jordan: Hey everybody, welcome to Out the Trunk with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's D's all up in your area on all socials.
+Jordan: And this is our movie review segment. We're going to be reviewing Mrs. Doubtfire. This movie came out in 1993 starring the late great Robin Williams.
+Darius: Were you born in 1993?
+Jordan: I was born 92.
+Darius: Okay. All right. It's my time in making sure it's that first movie where you were not born in.
+Jordan: So it's not. He had the late great Robin Williams, RIP to a legend. Sally Field, Pierce Brosnan. He was a really good 007. Harvey Feinstein, Lisa Jacob, Matthew Lawrence and Mara Wilson. Some movies about. Robin Williams character, he's after a difficult divorce, a loving but irresponsible father loses access to his children. Desperate to be near them, he undergoes a total physical transformation, adopting the guise of an elderly, prim, British nanny to secure a job in his ex-wife's home. So I'm gonna toss it to you for act one.
+Darius: Act one, we're gonna call the divorce a desperation. The father, Robin Williams, is devastated after losing custody of his children. Learning his ex-wife needs a housekeeper. He secretly creates a completely new identity and is hired for the job. Let me say off the bat, first scene, nothing dates a movie faster than seeing Smoking Indoors. Right? It's like seeing a payphone. I'm like, whoa, what?
+Jordan: It's like a hate crime nowadays.
+Darius: It is impossible to explain to someone, I would say 25 and under just how you pick this cigarette smoke used to be. And just how it's honestly an example of how government regulation can work. We've pretty much completely removed cigarette smoke from public spaces in a matter of what, 20 years. Yeah. You know, it existed for 100 plus years and in 20 years of laws and enforcement and regulation, we have made it so you can breathe in a restaurant again. So anyways, shout out to government, good government. But yes, Not only were there, like, it used to be the case that when you booked a hotel room, you had to specify non-smoking.
+Jordan: Yeah.
+Darius: When was the last time you were even asking section, you're not smoking anything. Yeah. So that's a good point. It's just weird to see everyone smoking inside.
+Jordan: Right. Even your point about the payphone. I remember one time my aunt like texted us and she was like, They were on vacation somewhere and my little cousins had never seen a pay phone before and they saw one and she's like, they were so, or it was, maybe it was easily a pay phone or a phone booth. And she was like, they were like, they thought it was like a time machine or something. Like they thought it was like the coolest thing ever. Cause they'd never seen one.
+Darius: Yeah. My niece didn't know what an actual like CD-ROM floppy disk thing was. Oh yeah. She was just like, I was like, well, that was thumb drives before we had them, you know, USB drives. Like it was like 5 megabytes of Which I don't even think is like 10 pictures now. It was storage to be very expensive.
+Jordan: It's like one report and that's it.
+Darius: Yeah, pretty much.
+Jordan: No, go ahead.
+Darius: What you got frag one?
+Jordan: Yes, I wanted to say one. I love this movie. I love movies that use city like the backdrops of cities like as a character in the movie. And I think San Francisco is a beautiful city. My mom goes there a lot for work. travels there a lot for work. She loves it there. And I miss when movies, it's kind of throwback in the way because movies nowadays, everything's like on a set with a green screen and ****. Like nothing's outside or on location anymore. So I think it's really dope that they dope to see a movie where you can see they're actually there at the city that they're supposed to be in.
+Darius: And it's San Francisco pre-tech boom. So these homes were like with regular people living. Those are multi, multi-million dollar homes now. But they exist where like working class people used to be able to afford those before, Google and Facebook and Amazon to Seattle, but all of Silicon Valley moved in. So it was it was yeah, it's it did feel lived in a way that you don't see very often. Let me just say that Robin Williams character was such a ******* loser. I hated this guy. You don't get to chase dreams when you bring children into this world.
+Jordan: Yeah.
+Darius: Your responsibility is to make sure that they are cared for. And you, they didn't ask to be here. You brought them here.
+Jordan: You.
+Darius: Don't get to chase dreams when you have children to take care of and you're not taking care of your. You're bouncing from job to job and you're doing these voiceovers and whatever. Yeah. I just.
+Jordan: Which is good money. I don't know why he ****** that job up.
+Darius: Yeah, he the over the scene is him quitting a job because he's some idiot. Oh, my God, my boss is me and make me do something. Okay. But like, you have children, like, you don't.
+Jordan: Right.
+Darius: I hated this guy. Imagine having to parent with this ******* man child as your ******* husband. I just. Anyway, what you got for act one?
+Jordan: Yeah, a couple of things I want to say for act one. So obviously we talked about obviously Robin Legend, Robin Legend, Robin Williams, you know, passing him being a legend, all that. This movie is a testament to his, like, I don't know if you, how much the viewers maybe who don't know, he's like legendary for his improvisational abilities. And a lot of the classic scenes and moments in this movie were not in the script. I watched a lot of interviews where we're with, I actually saw an interview with the kids from the movie who are obviously grown up now. And they were saying like, we would do like 40, 50 takes because he would just, he never did the same thing twice ever. And I thought that, I think that's really dope. I love when actors are given the freedom to just kind of create and play and stuff like that in movies. And the directors are not so much of an egomaniac where they will keep those takes, you know. So I wanted to shout out him for that. Also, pretty much everybody who's ever worked with Robin Williams has like a story of him just being unfeelingly kind and looking out for them without them knowing in a way. Like the oldest daughter in the movie, she was in high school and she missed a lot of school obviously to shoot the movie. And her school was like, when you come back, we're going to actually expel you because you missed so much time. And he hand wrote a letter to the principal of the school and was like, hey, like, can you not? The school actually framed the letter and put it in the principal's office and still expelled her anyway, which is kind of * **** ****. But just a testament to his character as a person. Yeah.
+Darius: The school made the right decision. You didn't, you didn't, you weren't in school. I don't care if you were climbing on set, but that's not.
+Jordan: Well, so they have school on set, they had to do 3 hours a day. But because she's in Canada, I guess their rules are maybe a little different. I don't know.
+Darius: As an administrator of the school, I signed this paper saying you completed the coursework and you graduate when you didn't. No. I mean, I don't know how it all worked, but no care. Wherever you were, that's fine. That's between you and your parents. We'll go get your coursework from wherever you were. But you weren't in my school under my care. So no, I can't say that you graduated when you... I don't know. It wasn't a registration.
+Jordan: They just didn't, they just like didn't let her go back to school after she finished the movie, which I think is kind of crazy. But and even Ethan Hawke, who was in Dead Poets Society with Robin Williams when he was a young actor. Robin actually gave him his agent, who I think he might have said he still has or had for a long time after that. So just want to shout out Robin Williams, gone too soon. And he's one of my favorite retainers ever. So I wanted to give him his flowers.
+Darius: Likewise, obviously gone way too soon under tragic circumstances. And the stories about his kindness and generosity are boundless.
+Jordan: Yeah.
+Darius: For sure. I'm just saying in defense of that school administrator, okay, you have a letter from Robin Williams. That's great. Did you pass the class? I'm sure he's a great guy. I will certainly, dear and dear to my heart, but you weren't here. I don't know what you were doing.
+Jordan: I mean, they knew she was on set. It wasn't like she was playing hooky.
+Darius: Okay.
+Jordan: But yeah, Also wanted to shout out the director of this movie, Chris Columbus. He wrote Gremlins. He also wrote a couple other big 80s movies. He was kind of a steward of John Hughes. He wrote like, and who directed 16 Candles and Breakfast Club and you know, all those classic 80s movies. He also, Chris Columbus directed the first two Harry Potter movies. So I will always have love for him just for that alone. And he did the first two Home Alones as well. So shout out him also another legend.
+Darius: Home Alones, good movies.
+Jordan: Yes, great movies.
+Darius: Prime example of a nineties movie that would be ruined if everyone had cell phones.
+Jordan: If everyone had phones. Yeah. Yep.
+Darius: Whole premise falls apart. So.
+Jordan: Yep. Hey, man, you forgot me. Yeah. Oh, ****.
+Darius: You got an Uber to the airport? Yeah, yeah, sure.
+Jordan: I'll send you the. All right. Let's look you a quick flight.
+Darius: Yeah. What you got for act one?
+Jordan: It's funny because watching this movie as a kid versus watching as adult, it is such a different experience.
+Darius: I have that note here.
+Jordan: When I was a kid, I was like, I mean, I definitely have more empathy for the mother now as an adult because he was able to quit those jobs because she was so stable in her job. And she had to be so serious because he was so unserious and lackadaisical. I mean, I have issues with some of the things she did throughout the movie, which I'll get to later. But yeah, definitely like as a kid, I was like, I don't, why are you divorcing him for throwing a party yet?
+Darius: I didn't get off of work. You were at work pitching some big client and then your assistant calls in the room and was like, Hey, the cops are there's an emergency when you get home and there's ******* barn animals in your living room. My other favorite thing, and this is jumping around a little bit, like she divorces the loser and like she, this is way later in the movie, but like she comes over to visitation and he's like, he cooked spaghetti. And she's just like, my God, he's so grown up. Forty something year old man with three children and he makes a pot of spaghetti. And everyone's just like, oh man, look at all this maturity. We like the violin started playing and it was like, oh, it's like you got to be ******* kidding me. It's the first time he's ever cooked for his children and he took a divorce.
+Jordan: You're right, he was a loser as a father. And the fact that you just wrote from the whole movie, and you're like, that ***** wanted to take his kids from him.
+Darius: He's in court, like, I just need my kids. And the judge is like, well, get a job, dude. Like, what are you talking about? You live in a ******* barn and you don't, you're unemployed. And I'm supposed to take them out of their stable home with the wife that makes all the money and has the house. Okay. Yeah. Question for you, Rag one. Let's get back on track. Would audience would audiences be able to suspend belief enough if the movie was released today? Because it requires a quite a bit of a suspension of belief. Right.
+Jordan: If you come out today, would audience be able to? No. Yeah, I'd say no, because, like, who do you know that's going to do makeup and you like that? Like, you know what I mean?
+Darius: It would almost have to be an animated movie to pass.
+Jordan: Yeah, I think so.
+Darius: Or just so over the top silly, like a Medea type movie.
+Jordan: Yeah, I was going to say, yeah, like a flubber or **** like the clumps or something, you know, something like that. Another Professor type ****.
+Darius: The audience would have to be in on the joke in a way that this movie was like, this movie was serious. Was serious. Yeah, it wasn't. You're supposed to believe that he was convincingly tricking these people. And you do, at least at the time. But now, now I'm like, this guy clearly.
+Jordan: It's clearly him. It looks like him.
+Darius: But like, you know, I mean, the 90s was everyone's a bit more cut off. It was less connected. So you could actually believe that. First of all, it wasn't like a man wearing makeup and a dress was like not as socially acceptable as it is now. It speaks to desperation. Correct. And you wouldn't even, it would never occur to you that a man would be in that dress because it's 1993. Whereas now if You saw a man in a dress out in a bowling alley, it would be unremarkable. Yeah, you'd be like, okay, you might remark at it, but it would not be like, you'd.
+Jordan: Be focused on like, I want to make sure I get their pronouns right, as opposed to being shocked by the side of it.
+Darius: Correct. You would fumble through the right things to say, but you would not be like completely blown away at the fact that it exists.
+Jordan: Correct. Yeah. That's a good point. So I did want to ask you, obviously, so she comes home and she's mad and they're having an argument and she's like, she says like, I get a cake and buy some gifts or whatever she had bought for her son and you throw a party. And she's like, I say this and you do that. And I don't mean, she wasn't highlighting that he was undermining her, which he was. I felt like she almost was saying that she felt like she was in competition with him for the kid's affection. So I want to ask you, did you did you get that sense as well as to? Because there was a lot of animals she had for him, justifiably so. But I think some of it was competition as well. Yeah, I mean, kind of admiration.
+Darius: Kids don't like vegetables and no one likes the parent that makes you eat vegetables. Everyone likes the parent that throws a party. It doesn't care about your grades. It doesn't make sure that you just live off of your teeth and floss. Yeah. And, you know, says witty characters for a living. it's easy to be fun when you don't have a job that stresses you out because you just quit because it's annoying and you just get to come home and throw parties with, you don't have to worry about who's paying the mortgage and you just get to read funny characters and the kids love you because they don't have to balance a checkbook. They don't have a boss at work. They don't have to deal with the police outside because you violated several statutes with barn animals.
+Jordan: City ordinances.
+Darius: But what I've noticed with parents like that, though, is that as the kids grow and they mature, they begin to resent the parent that never set boundaries.
+Jordan: Yeah.
+Darius: And the parent that the grown-up parent, they start to see it from their view more. Because kids want structure, kids want structure, kids want boundaries, kids want rules. And they just don't know they wanted it until, you know, it's too late.
+Jordan: Right. Or until they don't have it.
+Darius: Right. And like I said, man, he had the easiest job in the world, which was just Chuck E. Cheese. So Chuck E. Cheese. Yeah. Anyone can be a great parent when your only job is to take them to Chuck E. Cheese, you know? So, right. but she certainly felt in competition with him because she's, it's a little bit, in a way, it's a little bit like politics, right? voters vote for Republicans when they want to go to dad's house for a weekend and eat candy and shoot guns and drive real fast and, say bad words on a podcast and da da da da. But they, Monday comes around and kind of vote like.
+Jordan: You need public parking that's free. You need to pay your taxes.
+Darius: You want to go to the doctor, you want to go to school, you want safety.
+Jordan: You need that insurance, that's revised you by the Affordable Care Act.
+Darius: They vote for Democrats when they want a mom, when they want someone to make sure they eat their vegetables, when they make sure they can go to the doctor and make sure that their school works in line. And that's the yin and the yang of politics is that, you know, you see that in this household where it's like, The kids are voting for the Republican dad right now because he lets them go camping on weekends and shoot guns and eat candy and throw parties. But sooner or later, they're going to be like, okay, but like my stomach hurts. Can you take me to the doctor? Yeah, he's going to be out of the doctor. You don't have no money. I ain't got no doctor money. Yeah, look, I'm just here to have fun. You know, free market. Yeah. That's what you got for you.
+Jordan: Yeah. So there's a scene where she comes to his house for the first time and she picks up the kids and she, he said she got there, dropped them off an hour late and she's there to pick them up an hour early. Did you feel like she was being petty doing that? Or did you worry or were you on her side when she was doing that?
+Darius: No, that I was not on her side with because the rules are the rules. They are his children. And do I think she was being intentionally petty? No, I just think that she She didn't value his time as a parent at all because he just he was her fourth child. You know, he didn't she didn't see him as a co-parent. So like the idea that his time with his children will be valuable to her was just not something that ever occurred in her mind. Right. And so she's thinking like, why do you want a more time? Don't you know, don't you want to go do something? Child like this is responsibility. You don't want that, you know? So, yeah. I just don't think she ever took him serious, nor should she, because he didn't take himself seriously.
+Jordan: So true.
+Darius: Yeah.
+Jordan: Well, that's one of the only thing with my one of my issues with her was because it's like, okay, well, unless this guy drastically changed and turned into class clown, he was this when you married him. So how much of this did you sign up for? Now you're just mad that you somewhat that someone gave you the pin.
+Darius: Yeah. I see that often. Like there was this. story about this, like this thread on one of those sites where the guy was like, the women were like, my husband eats up all of my leftovers and he's not considerate and da da da da da. And every time I read that, I'm like, it's just hard for me to believe that there was, he got married and then a month later he just became this inconsiderate. Like it's hard.
+Jordan: Right.
+Darius: People don't hide it for that long. She probably thought he was fun and he's funny and I'm sure he was a blast to date before the kids came around. He's all, always on his adventures and so on and so forth. And that's why you don't select, you have to, obviously there should be some passion and some fun involved in all that, but that stuff fades and you need to have solid underlying fundamentals when you're selecting a life partner because you know, you just can't always select for fun. So, no, I mean, I disagree with her the way she handled the visitation. She was inappropriate for that.
+Jordan: Yeah, I hate that.
+Darius: That's about the only time I sided with him over her. So you want to get his act too? Yeah. Our act two, the double life and the competition. Living his dual life, the disguised father connects with his children while learning essential life skills. A new relationship in his ex-wife's life causes complications and jealousy. For the audience, if you're one of the five people on earth who hasn't seen this movie yet, the wife needs a nanny for the kids 'cause obviously her fourth child moved out and he decides to dress up as the nanny so he could spend time with his children while a noble pursuit. This is now I'm editorializing. But what an insane invasion of privacy and a violation of trust. Yeah, he was tripping. He was tripping.
+Jordan: Honestly, I didn't realize how much a violation of privacy it was until watching it today and yesterday. Cause like, I was like, you know, they had really personal, intimate conversations as like friends.
+Darius: Yeah. She's talking about a sex life and all kinds of ****.
+Jordan: Yeah. As a kid, you just didn't really, it didn't register with me like that, watching the movie. And you just, yeah, no, that actually was crazy. I think that's the thing she was most ****** about when she found out. Oh, that's actually, we'll go to that later. But yeah, no, that's a good point. Yeah.
+Darius: And she's, and he's using the Catwoman costume to like be the parent, the hard parent he couldn't be to the children. And God, this guy is just a piece of work, man. He just like, Be a ******* man. Put on your, if your kids need a stern hand and some discipline, as a man, provide that. Don't dress up in a costume to pretend to be someone else to make them do their homework. You're just, he's just a pathetic excuse of a man. Just a disgusting, pathetic excuse of a man. But I will say I laughed at the social worker scene with the cream falling in the coffee. That was actually quite funny.
+Jordan: It was not one of the things that was not in the script.
+Darius: It wasn't.
+Jordan: I read apparently the, no, the mask was real. But the melting part was not. So the heat lights for the camera were so hot that it was just melting off. And so that just actually happened. And he just rolled with it and was like, oh, well, look, 3 lumps.
+Darius: That's funny because I was like, that's disgusting. That's the one scene where I'm like, It's tough for me to suspend belief here. Like she really doesn't know anything's up. Like she never sees them in the same room together. This sister is 40 years older than him. And like he's literally like in scene and he leaves and he changes and he comes back.
+Jordan: It's like Superman and ****. Like Clark, where'd you go?
+Darius: You're straining credulity here. But I stuck with it. was, I laughed really, really hard at that scene.
+Jordan: No, I actually forgot how funny this movie was. Robin Williams is the ******* goat man. Also, like, that's one of my favorite GIFs to use of all time is where he opens, where he pops his head up with the cake face. Hello.
+Darius: And then the mask falls off the thing and.
+Jordan: Oh, and the truck runs over it.
+Darius: The kids there. Yeah. That was, that was hysterical. Yeah. Also a little weird. Talk about evasion of privacy. Why is the court like assigning him a babysitter? to, like, check it.
+Jordan: That was crazy.
+Darius: He was a danger to the children. He wasn't abusive. He just was a loser. Yeah.
+Jordan: And I think that was my biggest issue with the wife, because, like, you letting them think all this crazy **** about him and, you know, that man was not a danger to those kids.
+Darius: Not a danger. No, but yeah, you know.
+Jordan: Like, if you were to say negligent. I'd maybe hear you out but he was not a dangerous to those kids.
+Darius: No but like the first meal he ever cooked for them was like Chinese takeout that's spaghetti like I don't know like I don't think yeah I don't think.
+Jordan: That's actually crazy that you're 40 and can't cook.
+Darius: I don't think that the parent that I don't think it's fair to her that he gets to be the fun parent so I think it's totally fair I agree that she can be honest about him to her children like this is not Don't lie. Don't say that he's something that he's not, but don't lie the other way either. Don't sugarcoat it, you know.
+Jordan: I get that. I'm just not in favor of when parents do the whole **** talking one, the other parent to the kids. I just don't think that's ever good. And also kids grow up and they see eventually kids will realize, okay, maybe both were wrong or okay, this parent was actually the problem and we thought it was this parent the whole time, stuff like that.
+Darius: So I say you have some level of empathy for him. May I ask why?
+Jordan: I mean, I think I just love the movie and love Ron Williams so much. I think he just did such a good job of, I guess, because he wasn't malicious and it wasn't I don't think that he was set out to make her like I feel like okay in Crooklyn like the dad Woody sucked right yes but he was kind of I feel like he was kind of out to make her to be the bad guy you know what I mean because he like wouldn't work and he wouldn't play music to make money I don't I just in this situation I don't think that he set out to do the things that were hurting his family.
+Darius: I think it was a prime example of what people like to call this weaponized incompetence. It's when husbands pretend like they they're incompetent because they know their wives will just get sick of it and just do it. And you are not incapable.
+Jordan: I mean, he definitely needed to grow up for sure.
+Darius: Understatement of the year. You're not incapable of No, that was insane. And then you throw a party. And then, oh, but I love my kids. Okay. But you're not their friend. You're their parent. And he weaponized his incompetence in ways that made her look like the ***** to the kids. And that's just a heavy burden to carry. He's selfish. He's selfish as all. Everything he does is prioritizing what he wants. I mean, I can't remember a time watching the movie where he put someone else's needs before his own. I just can't recall. I mean, yeah, you just. I hated this character.
+Jordan: So do you think Mrs. Doubtfire forced him to adapt or do you think that was in him all along?
+Darius: I think it was in him all along. It's just he never had to use it because I guess by definition, that means it's forcing him to adapt. So yeah, I mean, people change. But just to me, it's unbecoming of a man that it took all of this.
+Jordan: No, I agree 100%.
+Darius: You had to lose everything and get divorced and lose visitation of your kids to grow up.
+Jordan: Yeah, this wasn't. This wasn't insecure where like, people say like, she that was part of his character development. He needed that arc to motivate himself, so on and so forth. This was not that. And I think that the argument is ******** but this was not that.
+Darius: But furthermore, man, you got children now. Yeah. Lawrence ain't handle kids. You can't you can't quit your job until the fifth season, but you know what I mean?
+Jordan: Like, yeah.
+Darius: When you have children, it's not about you anymore.
+Jordan: Right.
+Darius: It's just not. You don't get to prioritize your needs when you make decisions when you have children that's not to say that you always have to be on the back burner but time to grow up and grow fast when the kids start showing up I just don't have a lot of yeah.
+Jordan: Bro you gotta put your **** together or have your **** together.
+Darius: So I have a lot of sympathy for it when you when these kids are depending on you and you're just not showing up for them or not giving them what they need you're giving them candy and every kid wants candy but you're not giving them the tools they have to be productive adults right yeah anything else Rack 2.
+Jordan: Oh, yeah. When I just love how one thing he was going to do was openly hate on Stu.
+Darius: Yeah.
+Jordan: The new boyfriend.
+Darius: Yeah.
+Jordan: Where he just be like, Oh, are you overcompensating or damn, your skin is ****** ** or throwing the orange at him at the pool.
+Darius: I'm Team Stu.
+Jordan: No, I get you. I get it. Yeah. He was he was the father that they that they should have had.
+Darius: Yeah, he's an adult.
+Jordan: Yeah.
+Darius: Robin Williams is just another. He was a fourth child. And so. when he's at the drink place or the iced teas, and he's just like dismissing, he's just like, the guy is just a loser. And it's just like, I felt that in my soul, like this beautiful woman with three great kids was just wasting her time with this complete utter waste of human space. It's just a gross, pathetic excuse of a man. And I felt his disgust when he said that at the moment. He was, he was very just like, he wasn't playing Captain Sabahoe or nothing. He just was just like, no, to be that grown and to have three children in this world and to just.
+Jordan: And not be working and just have no obligation to cook, have no.
+Darius: Sense of duty to them, to know, to know.
+Jordan: Yeah.
+Darius: No sense of duty to your role as a provider, as a protector, as someone to shepherd these children into adulthood. I just found it to be distasteful. Yeah.
+Jordan: So I want to ask you, what did you think about the conversation that Mrs. Doubtfire had with Sally Field's character about, like, what actually happened in their marriage.
+Darius: Where she was like, go ahead. Sorry.
+Jordan: Where she was kind of like, you know, at first I was cool with the fun that she kind of was like, then I was serious enough for everybody. And then he couldn't be serious at all. And then she kind of said, like, I didn't like who I was with him, so on and so forth. And you can kind of see him realizing like, damn, I really ****** **. What do you think about that conversation?
+Darius: Again, violation of trust and privacy.
+Jordan: Yeah.
+Darius: But no, I mean, I thought that was probably the first time she'd ever been honest with him.
+Jordan: Right.
+Darius: And you could say she never said that to him, but what do you, what was he ever, when was he ever an adult to receive that conversation?
+Jordan: Right.
+Darius: And she probably did say it to him in so many ways.
+Jordan: In certain ways.
+Darius: Yeah, like these things don't blow up like the movie. Like she came home and there was a, and she just a party and she screamed like she had been hinting at this for a long time. And he just wasn't listening because he wanted to play with balloon animals or whatever he was doing at the time. And so I thought that conversation was quite poignant. It was movie magic.
+Jordan: Yeah.
+Darius: But I mean, clearly she still loved the guy, but he just was like, she just needed a grown up that he wasn't willing to.
+Jordan: Yeah, I think she loved him. I think she just stopped liking him and certainly respecting him, which is valid.
+Darius: And once they stop respecting you, it's a wrap. Yeah, it's over. All right. Act 3, the unmasking and the resolution. The father's secret identity is finally exposed during a chaotic evening with his family and new friends. The family must then navigate a new reality following the fallout of the deception. This is where I put my note. It's a good movie to watch as an adult versus a child. Because again, as a child, you're just rooting for</t>
+  </si>
+  <si>
+    <t>Jordan: Hey guys, welcome to Out the Trunk with Jordan and Darius. I'm Jordan. You can find me on all socials at Jordy B Writing.
+Darius: I'm Darius. That's Deez. I love the area on all socials.
+Jordan: And for our movie review segment, we're going to be reviewing Nick and Nora's infinite playlist. This is our first ever request. Shout out to you, Erica. So just be on.
+Darius: Appreciate you, Erica.
+Jordan: Yeah, hit us up on all socials out. Oh my God. Out the trunk pod and out the trunk pod at gmail.com. We do listen to your requests, so we do want to watch the movies you guys want us to watch and break them down for you. This came out in 2008, starring Michael Cera, Kat Dennings, Alexis Zena, Ari Graynor, Aaron Yu, Raffi Gavron, and Jay Baruchel. This movie is about two music-loving teenagers named Nick and Nora, who have a chance encounter in a club and are thrown together for a sleepless all-night adventure in New York City. Joined by friends, their quest to find a legendary secret concert begins a first date full of unexpected twists and turns. So I'll toss it to you for acting one.
+Darius: Act one, 5 minutes of fake dating. Nick, heartbroken, meets Nora when she asks him to be her temporary boyfriend. They quickly bond over music and are tasked with tracking down Nora's very drunk best friend during a chaotic night in New York City. Off the rip, I counted an iPod, burn CDs, and a flip phone for all the dated technology in this movie.
+Jordan: Yeah, man. That **** really was 20 years ago. That's crazy.
+Darius: Yeah, man. And I was like, Do we have burnt CDs in 2008? And we did have burnt CDs in 2008. Yeah. It was a transition year.
+Jordan: With the little swirly mouse pad or whatever.
+Darius: Yeah, it was like, everybody didn't have iPods though, because that was some money. And so. No, it was like 1000 bucks back then. I still had the thick CDs and the CD player in the car. So.
+Jordan: Remember Zunes?
+Darius: Oh my God, yeah. I used to, I had to sell a couple of those at GameStop. So I've worked at GameStop for like 8 months and it sounds as awful as it was. How old are these characters supposed to be in this movie?
+Jordan: That we didn't talk about that. Okay, so Nick and Nora are seniors in high school. Nick Nora and the girlfriend and the drunk girl are seniors in high school. The other people, I have no ******* idea. They don't look like they're supposed to be teenagers in high school.
+Darius: I was guessing early 20s. Are they really supposed to be seniors in high school?
+Jordan: Remember, they're talking about going off to college.
+Darius: Yeah. Okay. That's some continuity issues. Seniors in high school would not be just, I mean, weren't they drinking in the movie?
+Jordan: Yeah. Well, he wasn't and she wasn't. Just the girlfriend. Actually, it was just the one friend, I think, that was drinking the whole time.
+Darius: That makes sense. What you got for act one, man?
+Jordan: For the listeners, boys, girls, gay, straight, whatever you are, how old or young, when you're getting over an X, delete everything. I'm gonna say that one more time. Delete. everything. Get rid of the phone number, get rid of the phone, get rid of the text thread, pictures, videos. You want to make it like they never existed.
+Darius: I don't necessarily agree. So the problem with Google Messages is deletes are kind of permanent. Like it used to be the case that it would go to a folder. At the very least, you should move it to your secure folder so it's outside of the normal.
+Jordan: Yeah, or at least hide the, put in your hidden album.
+Darius: Yeah, don't play from the CD to the new girl.
+Jordan: No, Jesus Christ. Don't do that.
+Darius: Bad idea.
+Jordan: And if you have a wall dedicated to her in your room, maybe you want to put those in a photo album somewhere under your bed.
+Darius: Maybe just don't do that. That's weird. Don't dedicate a whole wall to your significant. Somebody cheated on you. Just don't even the height of your love. You're building a that's a shrine. That's weird.
+Jordan: That was a shrine. That was what they call it a prayer closet or whatever.
+Darius: Yeah, don't do that. That's weird.
+Jordan: No, that's actually insane.
+Darius: So, you know, go ahead.
+Jordan: No, go ahead.
+Darius: So I always wanted to start a band. So my question to you is, what instrument would you play in a garage band?
+Jordan: In a garage band? I'm either. It's tough because I've dabbled in both.
+Darius: Used to be in the band.
+Jordan: No, I played in band. I was in band. I would either do beat drums or guitar, preferably electric. Yeah, I did. So in middle school, I was in band. I played trombone and I played snare drum. I wanted to learn drum set, but I didn't have, we didn't have one. And so like, you know, it's kind of impossible to learn if you don't have one. That's our ******* wrong guitar during the pandemic. I do want to actually want to pick that back up because it is a fun, fun hobby. Yeah, I'd say probably guitar or drums. What about you?
+Darius: I think I'm a I'm a roll with piano. No, piano isn't a band. No, I would play bass. I would be like the Nick from the bass is I can blend in with the background, man. I don't like being the center of attention. So yeah. bass barely even gets a solo. So I like that. I'd be bass. Okay. Bass and background singer. Cause like I can hold a note, but I can never be good enough to lead the singing. Okay. Like a good background singer. I can do that. So bass and backing vocals is probably what I would do.
+Jordan: Okay. I think I'd be want to be like a maybe like a Dave Grohl or like Phil Collins where I can play drums and or guitar and sing front man switch off maybe something like that. I'm pretty versatile. So Yeah, I want to do a little bit of everything.
+Darius: Makes sense. What else you got for act one?
+Jordan: I found it really interesting that this movie is all about music and I couldn't. There was like not one memorable song on this soundtrack.
+Darius: Was this before? So this is definitely before two broke girls. Was this before the social network?
+Jordan: Was she in the social network?
+Darius: Well, Michael Cera was Michael Cera was. No, this is, oh, that's Superbad. What the **** was he in? Superbad, right?
+Jordan: Yeah, Superbad. Yeah.
+Darius: So this is before or after Superbad?
+Jordan: I think it's either right before or right after. Let me Google this here. Superbad was what, 07?
+Darius: We're about to find out.
+Jordan: Yeah, 07. So this is right after.
+Darius: Okay, cool. So this is probably filmed at the same time. This is before he was big time because they had no budget.
+Jordan: Correct. Correct.
+Darius: We spotted a continuity issue off the bat with their ages.
+Jordan: And this is 3 years after 40 year old virgin. So yeah, they were, she was a little known at that point.
+Darius: She was a 40 year old virgin.
+Jordan: Yeah, she was the daughter.
+Darius: I mean, I watched that movie, but I, you know, I didn't know who Cat Jennings was until Two Broke Girls. And then I didn't like go back and listen to.
+Jordan: Oh, man, everybody in high school was in love with her after 40 year old virgin.
+Darius: I was not in high school before the old version came out because I'm old. Not to catch things though, very attractive young lady.
+Jordan: I think we're the.
+Darius: Same age, but you know what I mean.
+Jordan: I feel you.
+Darius: Go ahead.
+Jordan: Oh, yes. I was going to say, so I don't want to say, she had like the ********* friend ever. The drunk girl who just would get sloppy everywhere, just to the point where you got a babysitter all night.
+Darius: The drunk homie. I think you got one time with me.
+Jordan: One time.
+Darius: One time to be, don't get me wrong, we all drink and have a good time. Like, yeah. Look, somewhat annoying is fine.
+Jordan: Yeah.
+Darius: One of your quirks is you be right up here on people. That's fine. One of my quirks is I get annoyingly philosophical and ranty. That's fine.
+Jordan: That is true. Yes.
+Darius: That's throwing up. We got to carry you to the car.
+Jordan: Puking and.
+Darius: Kicked out of the bar because you can't hand yourself. You trying to start a fight. You grab it on a girl.
+Jordan: She blocked out twice.
+Darius: One time with me. I will never go out with your *** again.
+Jordan: No, for real. No, **** ***. Like puking at a house party is fine because that happens. Puking in public. No.
+Darius: And there's a puking is fine. Puking on **** is not fine.
+Jordan: Puking in a grocery store in the ice cream aisle.
+Darius: That mouth starts watering, it's time to hit that bat. Don't tell, it's not, unless you just spinning, it's not a secret. Like you can feel it coming. I've been doing this a long time. I know when it's coming.
+Jordan: No **** *** **** *** yeah.
+Darius: Like you got one time. I'm gonna make sure you're straight. Cause you the homie, get you home, get you safe, make sure you don't vomit on yourself. But we done after that. Like I'm not. If I see you, it's cool, shake up, whatever. But we not going out ever again if you get sloppy on me. Cause that **** is, I cannot stand a ************ who cannot handle their liquor.
+Jordan: No, it's annoying, dude. You gotta watch him and make sure not trying to fight nobody and ****. And like, even when she was with those three other guys, not his friends, but the other guys, it was like, that was big like train energy too. Like I'm like, yo, dog, like.
+Darius: They want to get to fighting. They get to. being weird with women, which I don't play that. And then screaming and **** puking and **** sweating and ****. One time. I'm gonna get you home safe, put you in an Uber, whatever. You ain't got to piggyback for the Uber or nothing. But we're done after that.
+Jordan: It gets to a point, especially like, I know like we go, we go out a lot and **** whatever. But it's like, I'm not gonna get but so fated at certain spots because like safety, like you're in New York City at night and you're a girl.
+Darius: They are too far as I'm willing to get hammered at. And that's because I know people in there and I know I'm there. Other than that, if you notice, when we branch out to other places, I'm really scaled back drinking, of course. But it ain't no. We get there. Hey, let's do a shot. I'm gonna do that little shot. Then it's sip time that we, you know, correct. So ready to get an act 2?
+Jordan: Yeah.
+Darius: All right, act 2, the pursuit of Fluffy. Nick and Nora navigate the city with their friends, desperately searching for the secret concert of their favorite band. Where's Fluffy? Their buddy connection faces interference from ex-partners and various mishaps. And let me just say off the rip, we all have a story about a time we miss some hints, right?
+Jordan: Yep.
+Darius: One of these days we might share them on the pod, but I've missed some hints in my day. I got a few that are pretty bad. Never anything like this. She was throwing ***** at him for 90 straight minutes.
+Jordan: All night. All night. All night. Buddy was just like the beyoncé song.
+Darius: I just. I admire her persistence because I couldn't.
+Jordan: But when he got out the car, we. Bro.
+Darius: We talk about Jennings now. Jennings, whatever.
+Jordan: But that's my dad. I said, you're already kicking your coverage and you fumbling too.
+Darius: Not even getting coach. Bro, you know. Again, I'm not gonna stand before you and say, I ain't never missed no signs. Cause there's definitely been times where like even 2 weeks later, I'm like, oh no. I've done that, I've done that, I've done that.
+Jordan: I'm like, there are times where I think back like on **** like a year ago and I'll be like wanting to punch myself in the face.
+Darius: Then I read that text thread and I'm like, that's the sign I missed. Oh, that's bad. But nothing like that. She was literally throwing.
+Jordan: She changed clothes for him. She put on a bra for that dude. Oh my goodness.
+Darius: Anyways, what you got, that was my quick observation for, also one more thing. This reinforces my belief that shared missions are the best first dates. Like I'm not opposed to going out for a drink, going out for dinner, but like a shared objective always makes for a better first date because it gives you something to talk about that's not just dating. Correct. And so, you know, get out, go for a hike, go for a walk, bowl, obviously feed the woman later or whatever, but share an objective is going to make it way less like a job interview, way less stuffy. Exactly. Yeah. From a OG. What else you got? What you got for act two?
+Jordan: I do want to say Nora was like, great, I loved her. But she had a lot of audacity because you doing all that and you mad at dude for like not being over his ex who he just broke up with. And you had to see a boyfriend secretly the entire ******* time.
+Darius: Be like that. I don't know what to tell you.
+Jordan: Be like that. No, it'd be like that. And that should be annoying because I'm like, what you mad at me for?
+Darius: She like, I got a boyfriend, but you know, He's on a heels. He's on a performance improvement plan. And right now he's on a pimp.
+Jordan: He's on a 90 day probation period.
+Darius: And you know, we're interviewing his replacements. Would you like to come in for a conversation?
+Jordan: Correct. She's like, we already got the savage package drawn up and everything. We got the papers.
+Darius: We got the papers. Pip is technically a performance improvement plan, but truly it's a paid interview period You don't bounce back from a pip. No, you don't Well, if you if you ever get a pip this is for the audience if you ever receive a pip Just know you need to start looking for a job. It doesn't you can't recover from that They tell you you can recover from it. You can't actually recover from it. That's just them starting the paper trail So I have seen it happen one time in my near 20 years of corporate America experience. Somebody recovered from a PIP 99% of the time. It does not matter. That person is it's.
+Jordan: Yeah, you'll be gone within six months.
+Darius: Even if they rescind it, you're one bad performance month away from being back on it. And no one wants you don't want to live like that.
+Jordan: So yeah, you can't live like that. You know, especially not with this job security out here.
+Darius: Treat your pimp like a paid interview period. You're paying you. It's a time for you to interview for the next job.
+Jordan: Like it is a walking two weeks notice.
+Darius: Yes.
+Jordan: So I would ask you, what are, it's obviously a move about music and concerts. So I want to ask you, what are five acts you would do anything to see, dead or alive? Like bands, single performance.
+Darius: I have not seen before. Yeah. Okay, so nothing I've seen before. Because I've already seen Prince and Outcast and they'll be on the list.
+Jordan: Okay.
+Darius: All right. So Stevie Wonder, James Brown, Queen. Michael Jackson, just because you have to.
+Jordan: That's crazy.
+Darius: I'm, you know, you know, I am not the biggest fan of her music, but I think she's the greatest voice of all time and I just would want to hear it. So Whitney Houston, Whitney Houston. Yeah, I think Not the best albums, not the best songs, but there's, I've never heard voice like that in my life.
+Jordan: Yeah. That's actually an interesting dichotomy.
+Darius: Yeah. I mean, she just, she was with Clive and, you know, she made pop music. She made crossover music. She did. That's fine. But like I told my.
+Jordan: But no one's ever like, she had a classic album, which is kind of weird.
+Darius: Like I told my friend, he goes to church and he's religious, but he listens to like more contemporary gospel music. And I said, I like my gospel music old school. Like I want to hear, I used to smoke crack until the Lord save me gospel music. Like, you know, so there's nothing wrong with it. It's fine. But like I don't like that color purple.
+Jordan: Ending scene where she walk into church.
+Darius: I don't like suburban gospel music. We got too bougie. We got black people who made a little bit too much money. I like struggle gospel. So like, I think Whitney Houston is the best vocal talent I've ever heard. And so I would like to hear her in person. And in a concert setting, you're not listening to an album. You're just listening to the hits. So the answer, Queen, Whitney, Stevie Wonder, James Brown, Michael Jackson. So you. Yeah.
+Jordan: I'm going to go Michael Jackson. Since I'm talking about Dead or Alive, if you bring back 2013 Kanye West. Spiritually dead. Yeah. Morely bankrupt. I'm going to go.
+Darius: I missed a really good point in our series segment. But anyways, I'm not going to rehash it.
+Jordan: So I'm going to go prime Mariah Carey. I would go. Maybe like I'm trying to think. Uh. Oh, Celine Dion and Janet Jackson, because I would pray to God that she would call me up on stage.
+Darius: I don't have anything appropriate to say about her calling me up on stage. Exactly. What observation? This movie is so New York City.
+Jordan: It is, it is. I **** with movies that are like city. heavy, though.
+Darius: Like, it's just I've never lived in New York City, but I used to travel there frequently for work.
+Jordan: Yeah.
+Darius: And there's just nothing like it, man. I don't think I could live there because I don't I wouldn't want to bring my groceries on a dirty train. Yeah, but just like this, like the end of the movie, we'll get there. But it's just It's just so alive and it's always alive. Like, it just, there's a feeling, there's an energy to it. And it can be 7 a.m. at the diner eating breakfast. It could be 11, it could be 3 a.m. walking around outside. It's never, it's the city that never sleeps. You know, it's just, there's nothing like it. So what else you got for act two?
+Jordan: One of my favorite scenes in the movie is when they, they find the drunk girl and she's in like a burlesque show or something like that.
+Darius: Yeah.
+Jordan: And they're singing their version of 12 Days of Christmas and they go five Tay Diggs. That was egregious.
+Darius: That's pretty bad. So you asked me the question about the You asked me the question about.
+Jordan: He's never been in the allegations. No, no.
+Darius: All right. So the movie's about playlists, right?
+Jordan: Yeah.
+Darius: Kind of. It's named, but whatever. Right. What is one song that always pops up on your playlist? One for R&amp;B, one for rap.
+Jordan: Okay.
+Darius: I should have preflighted this. I'm sorry.
+Jordan: No, you're good. You're good. A rap song is going to always be online, like any kind of playlist or just a playlist.
+Darius: You just obviously it's not going to make on all of them, but just like if you scrolled your Apple right now, you'd be like, damn, this is on a lot of them.
+Jordan: Okay. Okay. Probably the original.
+Darius: I buy you some time. The original question was like, what's a song on a playlist you give a girl? But I'm like, no one does that.
+Jordan: I mean, I'd be like to send playlists out. I send playlists to like my friends. I'd say, okay, so a rap song that's always going to be in a playlist. Probably for me, I would go either We Be Steady Mobbing or Emily.
+Darius: I like that. I'll give my R&amp;B Jeffrey Osborne's Love Ballad because I'm 97 years old.
+Jordan: Okay.
+Darius: I just love that song. Okay. And my one rap, it was my question. I didn't even prepare for it. I would say R&amp;B. Life goes on by Tupac off of All Eyes on Me. So.
+Jordan: Okay. Yeah. Okay. My R&amp;B song would be because I love you by Lenny Williams.
+Darius: Oh, I like that one.
+Jordan: That's playing the record.
+Darius: I just didn't hear him anymore.
+Jordan: Hear him no more.
+Darius: Watch television till television went off. That man was in agony.
+Jordan: In agony. It's funny. I remember I told, you know, when you're like young, you don't realize the full scope of what a song actually is saying. Yeah. So I remember I was telling my friends one time, like five years ago, five years ago, I was like, yeah, I'm gonna play that song on my wedding. We're gonna dance to that song. And they're like, Jordan, you know that that song is he's singing to his new girlfriend after he finally got over his old girl, right? And I was like, oh.
+Darius: He said, finally I went to bed. I found myself waking up a few hours later in the tears. He just stopped singing. He just, he just talked for four minutes. He talked for four minutes. He just, he just stopped singing and it worked.
+Jordan: I need to know what that woman was doing to that man. And we need to see what she looked like.
+Darius: That's going to be, it's going to come with a not safe for work warning.
+Jordan: Yeah. Like, Jolene, you know, this is a one on Twitter is like, well, we need to see Jolene because we see the pictures of Prime Dolly Parton.
+Darius: So this movie needed a B plot. This movie needed a B plot. I love the A plot. It was cool. But it needed a B plot. It needed a B plot. Like the drunk girl didn't do it for me. And like every scene that she was in, I just wanted to end.
+Jordan: That vomit scene was one of the grossest scenes I've ever seen in my ******* life.
+Darius: I'm just glad they stuck to vomit in that scene because I thought it was going to go way worse. And Yeah, it just, I found the B plot lacking. I see what they were trying to do, but they needed to punch that up a little bit or just scrap it and just make the movie even more insular. So that's what A Lot Like Love did, and I enjoyed that. So what else you got, Frag 2, man?
+Jordan: Yes, I was going to ask you, at what point do you cut someone off? But you said like after one puking time that was going to be a wrap.
+Darius: Yeah. I mean, I will stall you out if it's your birthday and you get out of.
+Jordan: Okay, I was going to say, because yeah, we've we've we've seen that.
+Darius: Birthday, New Year's Eve, and Big 40. Big 40. And if you make it home before it all falls apart, that's fine.
+Jordan: Yeah.
+Darius: I don't mind putting it in an Uber. I just do not want to handle bodily fluids. Like I'm just, that is a deal breaker. I just don't, I don't want to handle your vomit.
+Jordan: No, I get you. I get you.
+Darius: If you get me, I'm too old to be fighting. So if you get me in a situation where I'm fighting and I know you was at fault, you know, sometimes your boy be wilding.
+Jordan: Yeah.
+Darius: And like if a fight happens because of external factors, of course, but like, If you go and grab somebody's girl's *** and he swings on you, I'm going to break up the fight. But he had every right to swing on you. I swing on you. Yeah. You know, it is just that that drama, that vomiting that can't handle himself. That **** ****** me off. And you got one of them outside of your birthday.
+Jordan: I agree. Or like the the mean drums that you just like talk **** to people for no reason. I hate those.
+Darius: You got anything else for act two?
+Jordan: No, that's all I got for act 2.
+Darius: We can pivot in to act 3 of sunrise in the city. As Don approaches the group's chaotic surge nears its end. Nick and Nora confront their past relationships and decide what the future holds for their unexpected music fueled connection. Music fueled? There was no music in this movie.
+Jordan: No ******* music in this movie.
+Darius: Let me just say.
+Jordan: She was one band performed. Well, 2 bands. That was it. Yeah.
+Darius: She was his ex-girlfriend was wrong. Yeah, was too wrong and don't make a right and leaving her stranded was a ******** move. Can't cosign that one, buddy. I can't get with that. This is pre-Uber, pre-cell phone, pre-location tracker. No, I can't get with that one. You got to make sure if she's in your care, you got to make sure if she gets home safe, regardless of how you feel about her.
+Jordan: That's true.
+Darius: You know, like that's just.
+Jordan: You have your house on the way out.
+Darius: Right. If she is, if a woman is in your care, as they need to make sure she gets home safe. Yes. And so can't get with that one. That one, I wasn't feeling that one. Even as bad as she was and as off duty as she was. Can't do that one, man. I can't get with that one. So yeah.
+Jordan: I have a question. It's like, cut more Vitorgo, but like, where the **** were the parents at?
+Darius: That's why I want to know how old they were, because I'm like, I think in the early.
+Jordan: These kids are up till 6 A.m. on a Friday. I'm guessing it's a Friday.
+Darius: But okay, so that's why I think there's continuity issues. The movie was written like these were early 20 somethings in New York City.
+Jordan: That's the problem. Yeah.
+Darius: And they change one thing in the writing where they go, we're not high school seniors. We're This would all make sense, right? And so tighter editing, bigger budget. So I'm willing to.
+Jordan: They probably couldn't afford to have them in a on a set shoot on a college campus. Yeah, it makes sense.
+Darius: Yeah. And so this this kind of things happened before streaming where movies would just have weird continuity issues that just didn't make sense. And so I'm stalling them out for that. But I will say you saw the beauty of New York City in that They go back to her record place, pops record place and studio.
+Jordan: Yeah.
+Darius: They do whatever they did. And then they just leave. And there's stuff to do in New York City at 430 in the morning. Like this just like, ain't **** open in Raleigh at 430 in the morning. I don't even think Waffle House is open. Like this?
+Jordan: There are some gas stations that are open at 430 in the morning.
+Darius: New York City like. It's hard to explain to people who've never been, but like, you literally can just walk outside your house at 430 and go do stuff.
+Jordan: Yeah. No, seriously. Yeah.
+Darius: And it doesn't cost you an arm and a leg. Like you, it's not like Vegas where if you go somewhere at 430, there's $100 cover. True. You can literally just get dressed, walk outside and find something to do at 4 o'clock in the morning. It's, there's nothing like it. There's nothing else like it. So what else you, what's your record?
+Jordan: Yes, I love that they made the city a character in the movie. I think it's really important when you're in a cool city and movies do that. Oh, yes. So her boyfriend, Tall, how the **** old was that guy? Because he was clearly not a child and they've been together for three years. So she would have been 15 when they met. What's up with that? Also, I hate that trope of like in high school in movies where it's like they just casually have the high school girl dating like a ******* 24 year old. Like that's normal or okay. I mean, it happens, but it's not okay is what I'm saying. But I'd say they do it again.
+Darius: I just don't think they meant for these kids to be in high school.
+Jordan: Yeah.
+Darius: I'm wondering why I was different questions. It was just like, the ages don't like the the age and the continuity doesn't add up. So I just decided to frame it as these are 22 year olds in New York City.
+Jordan: Yeah, that makes sense.
+Darius: That to me lined the movie up a lot better. But I did enjoy the movie. I love me too.
+Jordan: I liked it. Me too.
+Darius: You know, I guess my question is kind of a closer. So but it just made me nostalgic for a real nightlife. And I've aged out of going places at 430 in the morning, but just the fact that they're just walking around and there's **** to do. You know, like, yeah, like, and it, there's just, it just reminds me when we were walking around in downtown Raleigh the night before Labor Day. It's just so dead. Just so it's like, I'm not trying to sit in the club. I get that. But like, yeah, ain't a ******* record. Like they went to a record shop. They went to, you know, hot dogs. They just, there was just **** to do.
+Jordan: And like 2, 3 concerts.
+Darius: Like it ain't got to be a huge concert. Just where can you go hear live music in Raleigh? Just on a whim.
+Jordan: Yeah, nowhere.
+Darius: They just were walking around and finding it. And yeah, that's not atypical. Like, it's not just the movie. That's how it is there.
+Jordan: And so yeah, that's one thing I do love is that it is one of the cities that does live up to its reputations, like in real life.
+Darius: The thing is, though, like New York City is a city to live in. It's not a great vacation city because the things that make it great are living there. Yeah, it's it's the rent like. I used to travel for it, so I was there enough to where I got to feel a little bit of it. But it's not the same as like, people will see like on Twitter or TikTok or whatever, someone posts their New York City apartment and it's like tiny and they're like, I could never live in there. It's like, yeah, you don't understand. People just aren't home a lot in New York City. Yeah, but so they're not home. Like they're just not home a lot, right? They don't spend a lot of time in their place outside of sleeping. It's kind of just like a hotel where they all their clothes are, you know, like it's different. What you got for act three, man.
+Jordan: I love that when he got out of the van and then he, you know, she ****** ** and then she goes back with the dude and he's like basically trying to get her to pay the tab pretty much. I love that showed like the instant regret of just making a comfortable decision right away. And then even just like when they all link back up outside the show and ex is coming, they just like show their *** in front of everyone. It's like, yeah, no, they're always gonna show you why you left in the first place.
+Darius: Yes, 100%. Especially to reconcile that soon, you left for a reason.
+Jordan: Right, exactly. And I like that in order to choose each other, they had to choose themselves first. Like they had to say like, no, I'm not gonna be with you. to go on and be actually together. I thought that was a dope, a dope message for like, especially for young kids, because like your kids, it's, everything feels so big, but no one ever tells you like, just because you're young and it hurts doesn't mean that it's just intense and part of the process, you know?
+Darius: That's my problem with most breakup albums is they all sound like people in high school where just like, you know, the sky is falling and the pain hurts. There's like, there are very few breakup a</t>
+  </si>
+  <si>
+    <t>Jordan: Hey, everybody. Welcome to the Out the Trunk Pod with Jordan and Darius. It's our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's these. I love the area on all socials.
+Jordan: And today we're going to be reviewing the cult classic of the year, Obsession. This movie came out in May of 2026, starring Michael Johnston, Indy Navaretti, Cooper Tomlinson, Megan Lawless and Andy Richter from the Conan Show. This movie is about a guy named Bear, a shy and insecure music store employee who secretly longs for his co-worker and childhood friend Nikki. After an awkward encounter makes him feel like he's lost his chance forever, Bear snaps a supernatural one-wish Willow novelty charm, wishing Nikki to love him more than anyone else on Earth. The wish works, but her affection rapidly spirals into an unhinged, violent, and codependent nightmare that turns his dream romance into a fight for survival. That's Steve Fracklin.
+Darius: Act one, the One Wish Willow. Bear returns home to a grieving loss, and during a trip to a local crystal shop, he stumbles across a novelty trinket called One Wish Willow. Following a botch attempt to tell Nikki how he feels, a desperate bear snaps the branch in two and wishes for her total devotion. First observation off the rip, we have already discussed the issues regarding payment with the cast in a previous episode, what's on our mind, June 9th. you can go back and listen to our thoughts on that. So we're not ignoring that. We've just already discussed it and we're going to keep it, you know, to the movie in this one. So, you know, we'll put the link in the notes and you guys can listen to what we have to say about that. But First observation, I've done this before, beating a dead horse here. Bunch of part-time record employees had really nice houses. How are they affording these, like Bear lived by himself and he worked part-time as a retail employee. I don't even like he was never at work, but a handful of times in the show.
+Jordan: And there was never any customers in the shop.
+Darius: No, it's like he could not have made more than like 11 bucks an hour.
+Jordan: Right.
+Darius: And, you know, not bad. You can afford a two-bedroom home, standalone single family dwelling.
+Jordan: Yeah. In 2026.
+Darius: Shout out to him. So what you have?
+Jordan: Yeah, congrats to him. My first note for act one is Indy Neveredy's performance in this movie is otherworldly. I'll go into it more later. But everything she does in this movie with her face and her emotions is why actors should never, ever, ever get plastic surgery. Because if they had, they would not be able to, certain actors who will remain nameless would not be able to do this performance because they can't move their face from here down.
+Darius: It's funny you say you shall remain nameless and that's like half of Hollywood. I don't know. It'd be easier to name the ones who haven't had plastic surgery.
+Jordan: That's true.
+Darius: But, you know, we don't shame, but, you know, I got you. What else you got?
+Jordan: So the opening scene where he's doing the practice, asking her out or whatever thing with the server and his friend, it's kind of interesting because it Like the lines themselves are very like romantic. And like, if you were put them in the poem, like, wow, this is a great poem or something like that. You know what I mean? But because you know it's about a girl he doesn't know if she's into, it just comes across a totally different way. Also because he's practicing it, that makes it, that cheapens the sentiment.
+Darius: I'm shooting my shot this tonight. Let me, you know, get some reps up in the mirror before I do this. I ain't too cool to admit I have done that.
+Jordan: Oh no, hell yeah, for sure. Sure. I visualized before I go on dates and **** like that. Absolutely. So I'm not going to run a lot.
+Darius: I'm a bit more seasoned now, so I can a bit lighter on my feet, but I've definitely, you know, rehearsed some lines before. I mean, Barrett isn't, I don't think he's 22 years old in this movie.
+Jordan: Yeah, 22, 23, something like that.
+Darius: Yeah. So, you know, we're all a little weak at that point. So.
+Jordan: Oh, for sure. But it was funny to me because where his friend is like, dude, you're doing too much. He's not into this kind of **** whatever, you know, she's more like the chill approach, I guess. And it made me think of this. There's this episode of How Much Your Mother where it's called a like a Doppler Dahmer theory, meaning where if like you like the person they love and it's considered romantic, I say anything where he's outside with the boombox, right? Where if you compare it to like if they don't like you, it's more like some Dahmer **** where it's like creepy and stalkeration and a super red flag.
+Darius: Yeah, it goes both ways.
+Jordan: Yeah.
+Darius: You know, there's there's, we all have like, there's a woman in your phone, she texts you and you're like, right. And the woman you jump when they text. So like I kind of, right. It's the old flirting versus sexual harassment meme.
+Jordan: Yes, the meme. Or the, what is it? The Rick Ross where it's like his shirt off. It's like, get a job, fat. And then it's like Lizzo and it's like, body positivity.
+Darius: Yeah. so it kind of it goes both ways for sure.
+Jordan: Yeah, for sure.
+Darius: I had it. So to me, the movie really doesn't the ball doesn't start rolling for like 45 minutes. And so I think I clocked it at like 40 minutes where I'm like, that's so interesting. I wasn't it my own part, especially on first review, because I didn't even catch him snapping the willow tree on the first review. I was like, I had to rewind it. Because I didn't see it in the theater. The first time I saw it was when it hit like a premium new movie on Amazon.
+Jordan: Gotcha.
+Darius: And and so I was like, I was on my phone a little bit. Did I miss it? And I had to go back. It's real subtle because he's in the car and she's walking up to the house. Yeah. And he's just frustrated and he's just like, I wish Nikki would love me forever and more than anyone in the world.
+Jordan: More than anything in the world.
+Darius: Yeah. And he just snaps it and. I missed it on the first run. So like that whole 40 first 40 minutes until they're in that restaurant and she goes.
+Jordan: No, We're having a nice date.
+Darius: That was when I was like, when did the movie start? Oh, okay. Let me go back and see. You know, so yeah, it started a little slow for me, probably because I wasn't paying close enough attention.
+Jordan: So that's so interesting. So for me, it was kind of similar. I thought that for me, when I first watched it, I was like, this movie is 15 minutes to 20 minutes too long. And then on the rewatch, I'm like, it actually could have been a little longer. Not that I needed that, but just like the pacing actually is way better the second time around. For me, I picked up a lot the second on the rewatch because I'll just go and say it now, but like the he learns in act three that his friend and Nikki has been hooking up on the low this whole time. And so I was like, okay, well now I gotta go back and rewatch everything with him and her with Bear and Nikki and then with Nikki and I'm sorry, with Ian and Bear to kind of see the dynamic between the two friends to kind of figure out what his intentions were with him. So I went back and watched it and his friend was kind of on some ********. Like, it's not the whole movie. Like, he's like, you know, be mean to her. Call her freaky Nikki when he knows she doesn't like that. You know what I'm saying? It's like, that's kind of like sabotaging your man. You know what I mean?
+Darius: So, okay, you have to keep in mind, he found this out through a girl who had a crush on him and I forget her name.
+Jordan: Sarah.
+Darius: Sarah. So it's like how I believe that Ian and Nikki were hooking up for sure. But like she was like, it was off and on. It was a two year thing. It was nothing serious. To me that just reads and it's probably maybe me reading my own situations into this. Like we ain't really hooking up. It's just sometimes we're drunk in the same vicinity. And it's like, It's not a what are you doing tonight?
+Jordan: It's more of like a over here type thing.
+Darius: Yeah, proximity thing. And so I don't, I mean, it would have been nice to tell, especially given how passionate Bear was about.
+Jordan: That's my main thing.
+Darius: Yeah, I'm with you. Actually, I retract all that. Ian is crazy.
+Jordan: Cause like you knew he was in love with her.
+Darius: Yeah.
+Jordan: And like, if y'all are keeping your **** low, that's cool. But to try to like play a hand in him pursuing her is kind of nuts.
+Darius: And then giving him bad advice at that.
+Jordan: Yeah, that's really my thing. It's like giving him bad advice. And then like, I went back and watched it. When I watched it again, where he says, Bear goes, Bear was like, don't do it at trivia night. Do it when you're hanging out with her solo. But he said, well, whenever I ask her to hang out solo, she always invites you. And it's like, okay, well, so that, that was like the first hint. And like, okay, it might have been a little more serious than I think he let Sarah on to know about them too, you know?
+Darius: I mean, and then I'll. Yeah, no, maybe, maybe even. I mean, these are young people too, man.
+Jordan: I mean, that's, that's true too. Yeah.
+Darius: And I could see myself in Ian's situation not, you know, it's like, That's crazy. She keeps inviting me. Ha ha. I could see myself doing that. Now, would I encourage him to make a fool of himself? No, but I can see how Ian handled it to a certain extent.
+Jordan: Yeah. And then speaking to that point, like, When you go back and watch it, it's like she really did tell him like 8 different ways and she was not interested. Like he, so they're at the bar at trivia night, he orders a pina colada. First of all, that's step one. What the **** are you thinking ordering that in front of a girl you like? I mean, you can put it in there, I guess. Put some rum in there. But yeah, you have to do that.
+Darius: If you have to ask for the alcohol, it's not a drink.
+Jordan: Yeah. If you go up and ask for a Shirley Temple, they ask you if you want a virgin or not in front of Coca-Cola, too.
+Darius: And they won't put the jack in there unless I say with a jack.
+Jordan: Right. Yeah, I'll get a rum and coke.
+Darius: Hold the rum in a while. I want some jack. Yeah, me neither.
+Jordan: Yeah. Yeah, that was misstep number one. What were you what were you thinking? And then, you know, he was like, Oh, she's always so nice to me. But like, she gave the money to a homeless guy. Like, she's clearly just a nice person.
+Darius: Yeah.
+Jordan: You know, what else was it? Here's my thing where Ian was a ****** friend, where he gives her a ride home, but before they leave the bar, he's like, Make sure you get your girl home safe. And then that says Nikki up to go ill. that was really ****** **.
+Darius: That was a player. That was that was foul. Like that was foul. She didn't belong to nobody and y'all was ******* and that's totally fine. I'm not, I'm not, you know, I'm not one of those people that, you know, just because you liked her doesn't mean she's off limits. But at the same time, you don't, you don't have to rub it in. You don't have to, you know.
+Jordan: Just put him in position to look stupid.
+Darius: Yeah, you just, if you know what it is, and that's your man's, just steer him in a different direction. Don't really, don't encourage him to make a fool of himself. Just be like, that's what I didn't get. You know, I would have maybe been like, hey, listen, I can only say but so much, but that one, that one ain't the one, you know, there's 30 other women in here.
+Jordan: Right.
+Darius: Maybe focus on one of those?
+Jordan: There's a pretty girl also in that friend group who is in love with you. Like, I would have just been like, hey, you know, she likes you, right?
+Darius: I don't want the Nikki if we keep it in.
+Jordan: Thank you. I mean, or as bad at least.
+Darius: You know, it's, I don't, you know, both of them were decent.
+Jordan: They're both very attractive. Yes, very attractive women. Yeah, that's what I thought was crazy. And then even when she was driving her home and she was like, oh, I like that I can talk to you about this kind of stuff. You know, I don't really get talk like this with anybody else. And then she said, you're not a complete brick wall. For me, I took that to mean she views Ian as a brick wall, meaning she wanted more with him, something more serious with him than he wanted with her.
+Darius: I mean, listen, it feels counterintuitive, but hearing a woman tell you, you know, I can only talk about this stuff with you. And it's not, it's probably not.
+Jordan: That means you're her best friend. That means you're her best friend. You are her, she views you as a human puppy.
+Darius: Yeah, like that means, put another way, she doesn't feel like she has to put on a good foot forward for you.
+Jordan: Yes.
+Darius: You know, she's able to be, you know, a mess in front of you. It's probably not, because she doesn't see you romantically. Correct.
+Jordan: Yeah.
+Darius: It's and then the guy she is always, putting her best foot forward for is a dude she's sleeping with. So, Correct. Stated preferences versus revealed preferences. You got anything else for Ag1?
+Jordan: What else, what else? Oh yeah, even like where she's like, oh, do you like Sarah? Sarah wouldn't stop asking about you. Like.
+Darius: Another giant sign. Women do not like to share. No. If she's into you at all, it don't even, she could have a man. If she's into you at all, she's not gonna put her home girls on. That's not a thing.
+Jordan: No. Yeah. That's annoying. I hate when they do that, but whatever.
+Darius: That is so not a thing. Women do not put their homegirls on. They will hoard every decent man in the vicinity before they put their homegirl on if she actually likes you. If she's willing to put you on, it's because she's not into you at all.
+Jordan: Yeah, no, that's actually true. I had to learn it the hard way. I was very young when I learned that lesson and I was like, oh, That's why this friend group is weird.
+Darius: You know, and we're going to get to that later. That's why I extend bear a lot of grace because he's very young. These are. Yeah, I do not think these people are 25 years old.
+Jordan: No, not at all.
+Darius: Did they buy alcohol ever in this movie? Yeah.
+Jordan: That's the only reason I think they're over 21 because remember, they have the bar ordered shots.
+Darius: Oh, yeah, yeah. Yeah. Okay.
+Jordan: So I think they're 2223.
+Darius: I was thinking these are just like. But if that scene wasn't in there, I would have thought these kids were like, after high school, working a little part-time job, just kind of floating around. Yeah, same. But yeah, you're right, they're old. But they're not over 23. You know, they're not that old. So I actually, people are hard on bear on the internet. I guess we'll get to that, though. But I will say the theme of the movie. Be careful what you wish for.
+Jordan: Oh, yes, for sure.
+Darius: 100%. He got exactly what he wanted.
+Jordan: And, you know, that's another thing, too. It's like the he made literally the worst wish possible. He could have just said, like, I wish he liked me. I wish you would **** me. I wish we could be friends with because I wish we could date for a little bit or something like he made it the most extreme wish possible.
+Darius: That's why Despite them not dating or aging the characters in a movie, you could tell he's young. Because that's a child. Like, I wish he loved me more than anything in the world. Right.
+Jordan: And he just said it. He just said it so flippantly.
+Darius: You know, it's like in the whole wide world, you know, it's just like, he sounds like he's young, you know?
+Jordan: He sounds like a kid. Yeah, even like I like the irony of that because like in any movie involving magic or wishes or genies or fantasy or anything, in Game of Thrones for the most part, aside from Jon Snow, And that one dude who died eight times, it's you can't make anyone fall in love with you and you can't bring back anyone from the dead. Like those are the two biggest universal rules of magic. So I love that he just blatantly broke that offer. One wish.
+Darius: Yeah. Yeah. You know, it's a reoccurring theme. We discussed this before, man. If you you shouldn't trying to convince someone to love you is is for movies. It's not a real thing in real life.
+Jordan: It's not. It's the worst thing you could ever do to yourself.
+Darius: Never stop feeling like an audition. You will always feel like you're like the next day you got to audition all over again. Yeah.
+Jordan: Yes. I literally had this conversation with somebody the other night. I told him that, you know, we talked had this conversation. We were talking about like, we were talking, I think Twilight, whatever, like Edward versus Jacob. And it's like, well, one was one had the role and one was auditioning the entire time, you know, and.
+Darius: You just you owe yourself more a more fulfilling relationship than one you feel like you're always.
+Jordan: Just holding on to the rope.
+Darius: It just like barely, just like I made it through the day and tomorrow I go play tug of war with this thing again. It's like, no, man, you want it's not supposed to be easy, but it ain't supposed to be tug of war every day either. So.
+Jordan: No, you never want to overextend yourself for sure. This movie does do a great job of like showcasing attachment styles. You know, I go to a little bit later kind of his But yeah, it's like, you know, you also just don't want to be like once you, you know when someone likes you for the most part, like, you know, people think they're subtle, but they're really not. Like she said, Sarah's very obvious, you know? And then, you know what Nikki was like, when I like somebody, you'll never know. But the truth is, looking back on it, it actually was obvious that she was into Ian the whole time.
+Darius: There was a tweet I saw the other day. It was a, an older gentleman, and he was like, when a woman likes you, she'll help you, know, even if you don't have, even if you ate the smoothies or you didn't do this right, she'll help you, know, like, okay, let's bring this back here, you know, like, so.
+Jordan: That's very true.
+Darius: Because you don't get an instruction manual, but she'll get, you know, if she likes you, she'll, okay, she'll give you that. She'll give you that paragraph. That's what we're looking for. And so you add anything else for act one.
+Jordan: No, that's all I had for act one.
+Darius: All right, we're going to head into act two. Love turned unhinged understatement of the year. Overnight, Nikki transformed from a casual, friendly coworker into an intensely affectionate, attentive partner. It doesn't take long for Nikki's affection to curdle into suffocating, terrifying possession. She begins gaslighting bear, isolating him from a circle, duct taping doors to keep him from leaving. Yada, yada, yada, yada, yada. It gets, it goes on and on for there. Let me just say, we said this in the Odyssey. It's so important for movies, even serious movies to have moments of levity. Yeah. When she stands up and says, And I know one thing, I love Bear more than anything in the world. And the scene where the people at the party are looking and that black dude is looking like, I'm the only black guy here. There's a crying white woman. Let me get my pass.
+Jordan: Get the **** out of here.
+Darius: As a PSA to all the fellas out there, if you were at a function.
+Jordan: And a drunk white girl start crying. Get the **** out.
+Darius: It is time. Your night is over.
+Jordan: Yeah, your night is over, young man. Please. Have you heard that quote? White tears equals 50 years.
+Darius: The way they pants to the six people who are strangers and they're just looking like, they're looking like anyone would look like, what is it?
+Jordan: What the **** is happening here? No, my favorite is the white girl sitting on the back of the couch and she's just like.
+Darius: Because they're not privy. This is just like any of this.
+Jordan: They just met these people, I'm assuming.
+Darius: Imagine being at a function and just like, look, obviously that's awkward. Her boyfriend is like pulls a card to kiss. I thought everything there was normal. Like, no, you're not going to kiss this girl in front of me. That's for sure. You know, like that was valid there didn't immediately laugh it off like throw the card away or whatever. He was fouled for that. And I heard the chair back was a little much, but with the reason. And then she just went way left with the bottle.
+Jordan: Like oh oh oh ****.
+Darius: So backtrack a little bit when did it get weird for you?
+Jordan: The obsession I'm trying to think I mean right away to be honest like where it was like because like what I love about this movie is she wasn't like under a spell and then the ending happened and then she broke out of it. She was trying to fight her way out of the spell, the whole movie, which I thought made it really interesting because she was still in there the whole time. I have a note here.
+Darius: I love that they kept a little of her in there.
+Jordan: Yeah, me too. Like where she would switch off and be like, oh my, like when they kissed and she like was like, oh **** what the **** am I doing here? Like, you know what I mean?
+Darius: Or Interesting theory about that in the next act.
+Jordan: Yes. Crazy ******* theory. I think it's right though.
+Darius: I saw that clip before my third watch for the pod and I was like, it all lines up.
+Jordan: Yeah, I got to go back and watch it again. Yes, I love that. Even like after she freaked out with the bottle, she like breaking the bottle again. That was her trying to break out of the shell, you know, trying to break out of that.
+Darius: Reflection in that bottle.
+Jordan: I think so. I think so. Which makes a lot of sense.
+Darius: It got weird to meet the duct tape door. That was when I was like, That **** was crazy. That was the first time I watched it. I was sitting on my couch and I'm like, okay, she's a little obsessive, but when does this And he liked the camera. It's great cinematography. The camera like turns and he looks at it and he looks crazy and like, what the **** is he? And he's ******* like, where does he find them? Did he have so much duct tape?
+Jordan: That's like 200 feet of duct tape. It's like a football field out there.
+Darius: Oh, that was when I was like, okay, we it's officially where The movie requires.
+Jordan: She was off the rails.
+Darius: Yeah. Like, why isn't no one like calling the police? But that was when I was like the duct tape. So yours was earlier than that?
+Jordan: Yeah, I knew she was going to go left pretty early. And then also for me, it was when, she, he opened the door with the duct tape and she was standing there. I was like, she's going to be standing in that same spot when he comes back home. and then when she started peeing I was like she's gonna stand there all day she's gonna be playing like a tree and he came back and she was covered in like vomit and bile and.
+Darius: She did not empty her faculties all day.
+Jordan: No not at all.
+Darius: And the first watch I was like did she really **** herself and then I like yeah then the camera pans and like make sure you know and she did not move from that spot all day no dude she cooked his cat That **** was crazy. Built a shrine for the cat first. What else did she do? We already covered the scene at the restaurant where she just like.
+Jordan: **** the **** out.
+Darius: Have you ever had a **** out like that in public?
+Jordan: I actually did.
+Darius: Like a woman **** out like you like that?
+Jordan: Yeah.
+Darius: On you like that in public. Yeah.
+Jordan: Not to that quite to that degree. We were in a restaurant. she was really loud, like she, I don't know if she just couldn't hear herself, but she just was always really loud, and we're talking about love is. blind and it was the first season and there was a character on the show where he was the character the guy was bisexual and he was waiting to tell the person but he waited until after they met and after he proposed you know and so I was like to me sometimes you can't always tell but on this guy you could tell and so I was like you know I mean, I don't know why she was surprised, because I mean it was pretty clear. And she's like, what do you mean? I'm like, come on dude. Like she's like, what do you mean? I'm like, it was pretty obvious. She's like, well, how so? And I'm like, we're like, come on, it was like 2020 at the time. Like, come on dude, let's not be obtuse here. And then she's like, That's so like, that's so rude. And she's like screaming. She's like, that's biphobic and whatever. And I'm like, we're in a Chinese restaurant. And then people start like looking and ****. And I'm just like, okay, like you're nuts. And so that happens. Then we finished the night.
+Darius: You went out with one of them, the peak wokes. You said it was a 2020? That was their peak woke.
+Jordan: Yeah, like 2018, 2019, something like that. Yeah. And then we're in the parking lot. We're talking about it. I'm like, you misunderstood. Like, that's not me at all. Whatever. And then she was like, do you find embarrassing? I was like, you were screaming in a ******* restaurant, of course, whatever. And then I was like, I just had a moment where you're like, you ever have a moment where you're just like, wait, what the **** am I doing? So then I was like, you know what? This is our third date. You did not get me a gift. We're going to bring this to the litmus test now. I want gifts.
+Darius: Ain't got me nothing expensive, but I definitely want what she said. It was a token of appreciation to share.
+Jordan: A token of appreciation. You know, it's more what's under my segment, guys. And I literally I was just like, you know, it's our third date. We should not be arguing at this point. Clearly, this doesn't work. And I just called it right then there in the parking lot.
+Darius: I didn't get screamed at, but I definitely.
+Jordan: Yeah.
+Darius: What is she? told me like I was like part of the evils of capitalism or something. And it was just one of those.
+Jordan: Oh yeah, I remember you told me this story.
+Darius: And I can't get it too many specifics because it's work stuff. But she just was just like, how do you look yourself in the mirror? How do you sleep at night? And I may have sat on a bed of money. I think it's a madman line. Don Draper told one of his hipster girlfriends that joke. And and that was the last time I saw that one. She she that's funny. I was an evil capitalist and so on and so forth.
+Jordan: So I remember I have a story similar to that. I was back when remember when like on like the dating apps you could put like songs listening to profile or whatever. So this girl had that song with Meg the Stallion and DaBaby before all the shooting and cancellation and all that stuff. And so I quoted his opening verse from that line, being funny. And the line was, you know why these ******* love me, question mark. And so she's like, probably because you're disrespectful. And I was like, that's from the line of the song that you posted in your own ******* bio, you idiot.
+Darius: You say *******.
+Jordan: Yes. That's the line.
+Darius: Because baby don't give a ****. Rappers are funny, though. We say. I'll be rolling the weed. What do you say? You know why these ******* love me? Because baby don't give a ****. I'll be fixing their wee watch you ***** ****. It was just like logistically.
+Jordan: Yeah, it was something. Yeah. And then he's like, I hear from the back because she nasty. That's how she give it up. Some **** like that. Yeah.
+Darius: Oh, yeah. You know, I would not lead with with with ******* as an opening line. It's tough, tough sell.
+Jordan: But I mean, she got it once I explained it. She was like, Oh, my bad. I'm sorry.
+Darius: She has a good sport about it. Yeah. You know, I would scrap that one. It's a strategy. Throw that play away. That was dead on arrival. Why didn't Bear go to the police?
+Jordan: Because he'd have to explain what he did to her.
+Darius: Yes, that's why he didn't go to police because what he did was coercive.
+Jordan: Yeah, coercive for sure.
+Darius: You know, he was not a great guy as far as what he did. He snapped the willow in a moment of extreme frustration.
+Jordan: Correct. And he didn't know it was real.
+Darius: He didn't know what he was asking for, but he was.
+Jordan: He proceeded to essentially roofie her.
+Darius: I forgot they were *******. Yeah, you're right. It's. Yeah, he. So still, though, like I say, he didn't do it because not because of his own self-preservation. I think he didn't go to police because he actually liked it.
+Jordan: Yeah, he did. At first he did like it.
+Darius: Until she killed the old girl. Spoiler alert. I don't think he had. He enjoyed it. Yeah. When you're hiding bodies in a trunk, it's gone way left. But I think up until that point. It's probably his first girlfriend. He's never had any attention. Right. And yeah, I think I think a part of him enjoyed it.
+Jordan: So I think so, too. And I honestly wonder, I don't think he knew that Ian and Nikki were hooking up, but I do get the sense he probably liked getting the one up on his friend. Yeah, like he didn't know that they were in competition for her, but I think He liked the idea of being like, you told me I couldn't get her basically. And I did.
+Darius: Yeah, I think the part that makes you suspend belief is that like she smacked her face with a glass at the party and no one was like.
+Jordan: Police.
+Darius: You know, it wasn't that no one did anything in the moment because I could definitely see myself being so shocked. Just being shocked. Especially with like some hysterical white woman I've never met. that much blood and everything. But the fact that the next day everyone's just like, hey, you playing checkers tonight? Like there was no conversation about how weird that was. a bit like, all right. But no, I mean, Bear was certainly at best manipulative. And like you said, could be liable for some criminal conduct. You know, I don't believe he meant it to that extent but at the end of the right so you buy a trinket at a store and who thinks it's gonna work like you know like this is like oh it's like you wish upon a star and then it works and then from that point on he definitely uh was running foul but I don'</t>
+  </si>
+  <si>
+    <t>Darius: I know everyone's excited for doomsday, but to watch that trailer of CGI slop after this, just like, dude, I don't get it. Marvel, you have just as much of the same budget and resources as what are we doing here? Y'all.
+Jordan: Cause even Marvel, you'd be like everything you CGI and Marvel, like everything. Like remember the white suits in Avengers Endgame? Those were CGI too. Like it's actually kind of crazy.
+Darius: I'm just like, y'all ain't no indie shop. Y'all can afford this. Like what?
+Jordan: Yeah, bro.
+Darius: Just do it right.
+Jordan: You have a wardrobe department.
+Darius: You ******* have Disney money.
+Jordan: Like it's like even like the captain. Hey everybody, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. My name is Jordan. That's Jordy B riding on all socials.
+Darius: My name is Darius. That's D's. I love the area on also.
+Jordan: And today we're going to be looking at and reviewing the movie of the summer, the great Christopher Nolan's instant classic, The Odyssey. This movie obviously was released this month, July 17, 2026, starring the great Matt Damon. We do like his apples paws. Tom Holland, Spider-Man, the lovely Anne Hathaway, the great Robert Pattinson slash Batman, Lupita Nyong'o, Chef's Kiss, Zendaya, Great MJ, Charlize Theron, and Samantha Morton. The Odysseys follows the brutal conclusion of the Trojan War. The wily Greek King Odysseus attempts to sail home to Ithaca, but after defying the gods, his journey becomes a harrowing decade-long psychological and physical gauntlet through treacherous seas, reality-warping entities and monsters. Meanwhile, back home, his wife Penelope and son Telemachus fight to hold on to their sanity and the throne against the vicious, parasitic swarm of noble suitors. So I'll talk to you to open up back in one.
+Darius: Act one, the beach at Troy. We start off right into the grimy, exhausting aftermath of the Trojan War. The legendary wooden horse isn't a clean victory. It's A claustrophobic, traumatic deception that leaves Odysseus carrying an immense weight of guilt when he mocks the natural order of the world and the gods. His fleet is swept into the uncharted, unknown. Going to date the podcast because we're probably releasing this right away. This movie came out four days ago. How many times have you seen it?
+Jordan: I've seen it twice.
+Darius: Same.
+Jordan: I watched it again last night.
+Darius: How much better was the second viewing for you?
+Jordan: I was going to say it definitely got better for sure. I think it's going to be one of those movies where it just gets better every time you watch it, honestly, like centers, like it's just going to be great every time. And yeah.
+Darius: It's just once because the narrative structure can be a bit confusing, but once you know what's a flashback and what's present day and yeah, once you know the beats of the plot, I mean, the second time I left, leaving that theater, like, man, that's a masterpiece. Yeah, no, really.
+Jordan: Yes.
+Darius: First time I left and I was like, that's a really good movie. But yes. You know, did you see it in IMAX or was that regular?
+Jordan: I saw it regular. I didn't, the IMAX was showing like 10, like 11 o'clock showing and the seats weren't good. I was gonna try to get another, get a ticket later this week or maybe next week.
+Darius: I think I'm gonna see it in IMAX later this week, but it's. It really does make a difference because there's shots on the beach where when I saw a regular Thursday and then I saw it in IMAX Sunday and you don't get the scale of his army until you get those wide shots. And I mean, I don't know. I'm just kind of speaking in broken sentences right now, but it's.
+Jordan: Yeah, I was yeah, I was talking to a friend from the bar at no spot Friday night about the movie and I was saying I kind of break it down to him like you got to see it in IMAX because I saw it in regular but I've seen the clips on socials of the IMAX screen I was like it's not like a zoom in it's just that the perspective been cut like the ratios been cut so like you know it's like I told him like for example like this is regular vision you know and then IMAX is the full right and so like it just Your face looks big if it's just this. But if you can see everything, your face doesn't look big. So it's kind of the way this, like you said, the way the scale is done in this movie. First of all, it's a great viewing experience.
+Darius: Yes.
+Jordan: Honestly, I think I'm going to buy the Blu-ray or the DVD when it comes out because I want to get all the special features and see all the behind the scenes stuff. But also, They deserve their money again for this movie. It was, it was, it was that great. I don't, I almost would feel like I'm robbing them if I bought it on sharing for six bucks. You know what I mean?
+Darius: Once I go see the third time, third time is a given. We, this is one of, this might be a four or five one.
+Jordan: **** *** **** *** bro.
+Darius: But the third time, **** we'll be, I'll be at $100 in ticket sales. Yeah, I mean, 3 tickets. That's before I'd have bought popcorn and soda, but, and I don't, it's like, man, Okay, so let me just ground some of this. What I will say is like the first viewing, the cast is so famous, it's a little distracting.
+Jordan: Yes.
+Darius: And then the second viewing, you do start to see them as characters in a story. Because we were at a bar Saturday and we were talking about Tom Holland's performance. And I didn't really buy it, but I bought it on the second one. I was like, yeah, I'm not watching.
+Jordan: Go ahead, go ahead. No, you go ahead. Yeah, like he was supposed to be the weak link. Like he wasn't supposed to be him with a capital H. You know what I'm saying? Like that was, I mean, I went to a bigger point later with this movie, but that was kind of his journey was he basically was Simba. You know, it's like the boy trying to be the king, you know? And so he had to grow into the role. Like even his clothes, like if he noticed his clothes were almost bigger on him at the beginning of the movie than at the end where he's wearing the armor and it fits and **** it's like tailored to him, you know? And plus, again, like you said, it is kind of hard to be like, okay, because you're like, okay, well, that's the Punisher. That's Spider-Man. That's MJ. That's the other Batman.
+Darius: That's Matt ******* Damon.
+Jordan: Right, that's Good Will Hunting. There's Catwoman in here. That's Jason Bourne.
+Darius: Dr. Dre is in the corner. Right, I wrote that down.
+Jordan: I wrote that down. Dr. Dre is in here.
+Darius: He's good.
+Jordan: He was really good. I need a buddy cop comedy with him and Robert Pattinson. Somebody needs to write that.
+Darius: You know, you see this list of a bunch of famous people and you're like, did he just hit his Rolodex? Nah, man. Even though everyone is super duper famous, everyone was really well casted.
+Jordan: Everyone was perfect.
+Darius: I just down to Zendaya as Athena was just like a nice. Like, I didn't buy it at first. And then the second time you watch it and it's just like, because I didn't even really. I mean, I've read the Odyssey, but it was like 10th grade English class. That's ******* 25 years ago. I don't remember no ****.
+Jordan: It's like, it's weird because we didn't read it in school.
+Darius: Like I read the Giver in high school. Could I tell you one page of any action on the Giver? No, it's just, you know, back then you read to complete the assignment. And so I didn't know that when I'm watching it the first time, I didn't know that he's with Calypso. And that's the present time. And so I'm just like, can we fast forward to him talking to this white woman and get back to the one-eyed Cyclops? But the second time I'm settled in and I know what's going on and like, okay, I get this. And like, I could see her tricking him and making him forget his, it's just, people go see it a second time. The first time.
+Jordan: Yeah, you have to see it multiple times.
+Darius: The first time almost is just, it almost doesn't count.
+Jordan: You knew it was great, but it was just like so much. You're kind of like, I literally like, I obviously can't take notes during the movie. And I was going to see it multiple times so we could give a good review. But I was like, oh, I'll make voice notes when I get home. And I was like, my voice notes, it's like me rambling for two minutes. And I'm just like, He was great. Travis Scott was great, man. And like also it was a perfect way to open the movie because like you need, it's an epic movie, you need an epic opening. And him being, you know, banging the stick and a man, a fleet, you know, whatever. I was a little nervous.
+Darius: The first thing I saw was Travis Scott.
+Jordan: I was scared. I was scared. I was scared. But you know what? Chris Nolan has only let me down twice.
+Darius: Which 2?
+Jordan: Yeah, I hated Memento. Tenet, it wasn't for me, but I really did not like Dunkirk. I'm not going to lie to you.
+Darius: I love Dunkirk.
+Jordan: I did, which wasn't for me. I'll have to give it another shot.
+Darius: But so I have a folder on a hard drive with all of his movies. And I actually have copies of the Dark Knight series. And I just been, honestly, a three hour movie in a theater. This movie didn't really count because it's just that good. But I had to work my way up to like, it's almost like you got to get in game shape for that. So the week before, I was going to go see it Thursday. Monday, I watched Interstellar. Tuesday, I watched Deception. Those are 2 1/2 hour, 3 hour movies.
+Jordan: Okay.
+Darius: And so I just to train myself to sit through this and the rest, like my plan is now is to memento. No, we're going to skip. But I'm going to watch Ten and I'm watch Dunkirk. I'm going to watch Oppenheimer. I'm gonna watch the prestige and just go back to the class. Just go through the whole folder because.
+Jordan: Yeah, I think I'm gonna do that too.
+Darius: You know, I have a bold proclamation at the end of this pod.
+Jordan: So Okay, so I actually started watching Interstellar last night. I'm halfway through, but I was like, I'll be dead for work if I finish this movie. So I had to cut it in half, but I feel you. So yeah, I and speaking to just people understand just how big this movie this movie is going to make a billion dollars like guaranteed I went online yesterday all day trying to get good tickets and I checked like the seven o'clock show I was like seven o'clock on Monday I'll have to do it to myself that **** was sold out like like go ahead yeah like I again I saw it last night and literally at the end of the movie people like applauded like so.
+Darius: There's some self-selection here, because when I saw it in IMAX, I saw it Sunday morning at 11 A.m. And that was moviegoers. The people in there were serious business. And the woman who sat next to me, I swear to God, 3 hours, I didn't hear a sidebar conversation. I didn't see a cell phone light. Nobody really got, I mean, I'm certain someone got to use the bathroom. I just didn't notice. But no one that I saw got up to use the bathroom. It was just in a trance for three straight hours. And I can't remember the last time movie did that I mean I feel you um 3 hours and no one is distracted it's just we it was like we were in the middle of the woods watching a movie with no cell phone coverage like it was yeah yeah.
+Jordan: I did uh I did go up get up to go to the bathroom uh the first time I saw it but I literally sprinted to the bathroom and sprinted back in like 90 seconds um I was like it's a boat scene they're going to an island I should be safe here.
+Darius: When you get to see it in IMAX, it's almost like the IMAX turns off your bladder because you just do not want. It's so engrossing. It feels like you're on that boat in that sea, rocking back and forth. It is absolutely, it is an experience, man. And like I saw Oppenheimer in IMAX. It was cool. It was better, clearly. You know, I saw Project Hail Mary and IMAX. I've seen, I saw Interstellar and IMAX. This is just different. It feels like you're in his army, just like an extra in the army. Okay. Just, you're just there with them. It's nuts.
+Jordan: Okay.
+Darius: What else you got?
+Jordan: Oh, I didn't get anything. I haven't actually what you said. So a friend hit me up, friend of the show, shout out to you. She hit me up before right for recording and was like, are you gonna go see it in 4D? And I was like, dude, I have to go see it in 4D, bro. Have you seen any clips of people like in the theaters with it?
+Darius: I have not, no.
+Jordan: They were like getting hit with water and ****. Like the seats are moving. It's like they're in the boat. I'm like, yeah, I gotta find a theater somewhere in the US to watch that movie in 4D.
+Darius: There's A 70mm theater in Georgia. And I swear to God, if I could get a ticket, I'm going to six hours. Because What is life meant? Like, this is, this is a once, this is the one movie where it matters.
+Jordan: Yeah, you got to go on an Odyssey to see the Odyssey.
+Darius: One, if I can get a ticket on a weekend, what the hell else is I doing that weekend? Why not?
+Jordan: True facts.
+Darius: Yeah, like it's a far fetched because the tickets are sold out upon being sold out. But right, if I could, if I could score a 70 mm ticket, that's honest to God. It's worth the flight for me. If I could score a 70 mm ticket, I'm not mad at that, man.
+Jordan: I'm not mad at that at all. Okay, so we talked about the, you mentioned the time jumps and it being non-linear. So I think for this movie, when it was really well done and two, I think it was actually really necessary.
+Darius: Yeah.
+Jordan: Because in that time period, there was no online, you know what I mean? Like, I mean, it's mythology, but you know, I'm saying like, they didn't have e-mail or text. They couldn't be like, yo, man, this happened. Yo, they're in the boat. Just saw XYZ happen, you know, or, oh, **** the horse got people in it, you know? So it would all be from hearsay, which means it would take longer to get to get around to everyone. So it kind of I did kind of like that because it would show everyone would be confused. No one would know what the **** is going on because like even the Game of Thrones are sending ravens. They're not even sending ravens and **** in the Odyssey. So everyone would be clueless and lost unless you're actually plotting some crazy ****.
+Darius: Yeah. And also, you know, he had a heart out at three hours, which is fine. I'm totally fine with movies really shouldn't be longer than three hours. But the way it's narratively structured you can't really capture the passing of time telling Journey in present time it has to be through flashbacks with him regaining his memory talking to Calypska Calypso Calypso and yeah if you just showed him because he's with Calypso for seven years so to make that work it just wouldn't the first hour is the journey and then an hour with Calypso and then an hour and they just wouldn't it has to be told through flashbacks and normally I think it's a cheap trick but it's the only thing that worked you know?
+Jordan: Yeah I agree yeah I think so too I just and he did it so well man like it's like the way Shout out to Christopher Nolan, just one of the all time greats. I said, I watched the water theater. I was like, Yeah, I think you might be the goat. Like, I was.
+Darius: I was foreshadowing. He's to me, he is the greatest. Like, I don't think.
+Jordan: Because he writes and directs, you know.
+Darius: I. Who's I mean, I looked at that folder, man. This is before I had even seen the Odyssey and I was like, yeah, no one's touching this. Like, yeah, you know, it's tough. It's tough when you got. When the Dark Knight rises in the bottom tier, right? Like none of those. I mean, memento was bad, I would say. And the following almost doesn't even count because it was his first one. Yeah, but. There are like any and he he produced he drops every three years. And so it's not like. Yeah, and it's like to have this kind of quality dropping every three years. I mean, Oppenheimer was three years ago. And most people would drop in Oppenheimer and disappear for five, 6, 7 years.
+Jordan: Five, 6 years.
+Darius: He came right, I mean, he was writing this in 2024. He came right back.
+Jordan: And I don't know if you watch any of the interviews for this movie yet or whatever, but the cast, like they've all talked about, they all said the same thing. Like, he kind of almost is a decent, like he's a great leader. They're like, he doesn't do anything that he's not willing to do himself. There's a scene in the movie where there's the head of Athena shaking. He's moving the head. He's like, it wasn't done right. He's like, I'll just do it because then I can get my vision out. You know, I think I remember there was an interview, Robert Downey Jr., he was like, when they were doing oppenheim, he was like, dude, do you ever go to the bathroom? Because they all were like, I've never seen him go to the bathroom. I've never seen him. He's always by the camera. He's always in the camera. And he was like, Nolan goes, yeah, he goes 11am, 6pm.
+Darius: Yeah, Matt Damon said, though there's a scene, we're jumping around a little bit, but there's a scene where he has to tie himself to the mast of the boat. because the lady singing a song and it's so intoxicating. It makes you go to her. And he's like, he knows what an actor needs because he was like, we're going to shoot that today. And he says something. He says, we'll shoot, we'll shoot it till we like it, which is something, you know, you rarely hear from a director. Normally they just put a timestamp on things. We'll do three takes. We'll shoot it till we like it. And he's like, take an hour to get in the right headspace, because that's actually a difficult scene to shoot. Because he's like, the way he did it, he was on the boat by himself. And he's like, I have to scream with an IMAX camera in my face, tied to a boat and it can't look stupid. And he's like, it took me a long time to get into the right headspace for that. And he's just like, you know, that's a great boss, you know, putting people in the position to succeed. You know, the actors are the players, but like the coach has to call the plays. And you know, He's the greatest. He's my favorite coach, movie coach, director of all time.
+Jordan: Mine too, man. Yeah, I watched that interview too. I saw a clip of him, Damon reversing that scene. He's like, yo, he told him, we're going to shoot your coverage first, right? Like you said, they had to take a ferry out to get to the boat to shoot. And he's like, so I took the ferry by myself. So I had an hour to just get my mind, get to go there mentally to shoot the scene. He's like, only a great director. It would take a great director to know that I needed that to shoot that scene, you know? Man, this movie's amazing. So, okay, so a big tenet of this movie, no pun intended, is Zeus's law, which is basically hospitality and treat others the way you want to be treated, which I really liked. And I really always love the idea of like, this is in other movies and fables and stuff too, of like treating people as though they may be God in disguise. You know, like if you think about like Beauty and the Beast. Like, that's kind of what happened in that story. You know, the prince was evil to a beggar. The beggar was a magician and turned him to the beast, you know, whatever. So like, I really thought that was a super dope way of framing it. And I love the way it just showed that theme stuck throughout the movie. You know, it wasn't just a quick little plot point. I mean, we'll talk about the monologue Odysseus gives later in Act three, but I thought that was some great world building.
+Darius: I agree. The whole the whole movie is about what happens when you go against tradition and upset the natural order of things, you know. And so, yeah, you want to get into act two so we can actually get it to the meat of the movie.
+Jordan: Yeah, I just got one more point for one. Because I love this quote, this line that Anne Hathaway said in the movie, or said in Act 1, the structure is nothing without people's respect for its meaning. I thought that line was ******* brilliant. One, I spoke to the political tone, undertone of today. And 2, just, you know, the fact, it reminded me a lot of the Game of Thrones monologue where Varys is given the riddle to Tyrion. And he's like, power resides where men believe it resides. It's a trick. It's a shadow on a wall. You know, and I just thought that was ******* brilliant writing.
+Darius: I agree man um I wasn't crazy about a lot of the politics of Ithaca on my first watch mostly because everything else is just so much like just cooler more interesting the second one once you you know the action beats are coming you're kind of you're not in a rush to get back to them because you know they're coming you watch it and it's like to me that's some of the best stuff in the movie you know um just uh Penelope and Her interactions with the with her son. I forget his name. Telemachus. Yeah. And Antonius, I think his name is Robert Patterson.
+Jordan: Yeah.
+Darius: And so the politics of Ithaca is a bit of a drag on the first viewing, but on the second viewing, it definitely grabs you in a different way because you just you're not in a rush to get back to, you know.
+Jordan: Yes.
+Darius: The journey, which will start with Act 2, the hallucinatory gauntlet. The middle of the film plays out like a psychological survival thriller. Rather than campy creatures, the encounters with Polythemus, the Cyclops, the witch Circe and Calypso feel like fever dreams are manifestations of grief, hunger, and disorientation. At the same time, we cut back to Ithaca, where Penelope is trapped in a nonstop agonizing bacchanal of greedy suitors taking over her palace. The Cyclops was the coolest thing ever. And I have this thing and like sometimes when I don't know what to watch, I'll just pick like seeing some movies that I like. Me too. I will be watching that Cyclops movie, that Cyclops scene over and over and over and over and over.
+Jordan: Yeah, that **** was dope.
+Darius: That **** was hard. I didn't see it coming. And like, I didn't get it at first because I was like, wow, they just moved the boulder, but like the boulder is *******.
+Jordan: They can't move the boulder.
+Darius: Yeah, it's literally like trying to move.
+Jordan: It's a skyscraper.
+Darius: Yeah. And it just. I mean, I don't want this to just be us saying he's the goat over and over and over again.
+Jordan: But man, it really might not even be up for discussion. I'm not going to hold you here. Like, bro, what? So yeah, it's a 60 foot puppet that they built. And then they had real sheep just living in the cave. Like they shot that sequence for two weeks. So they just lived in a cave for two weeks with sheep. So what they did was they actually had an actor, I believe his name was Bill Irwin, play the Cyclops also. So they shot him with like the blue screen suit and then they shot him in like a miniature cave so he could do all the voices and you know, all that stuff. Man, that **** was ******* brilliant, dog. Like I, when I, assumed that was CGI, like I was like, oh, that's obviously like CGI. They're looking at a tennis ball or whatever, you know, whatever. The fact that they built that **** dog,
+Darius: I realize everybody ain't got his budget or his like freedom. But man, it makes it hard to watch CGI slop now because it's just like I feel like I was in that cave, man. And when he says, you know, why did he say something? He's like, do you talk to ants?
+Jordan: Do you talk to ants?
+Darius: That was my one kind of criticism. I have two criticisms of the movie, but my one was like it needed more humor. I thought that just something to break the tension in the room. I got it. Did you do you talk to Grace? I thought that was funny. And it was it was a nice little breather because it is. It's a tense. It's an intense movie. And it is, man. And it's just, you know, a couple of chuckles here and there would have been a nice little break. But that's my favorite scene of the movie. And that's the one I'll rewatch over and over and over again is a Cyclops.
+Jordan: That scene was dope. That wasn't my favorite scene, but I did love that scene. And then even like where they were like, we got to, maybe we should go in groups of two because we lost two men.
+Darius: Because that was like a deal. He's like, I guess he gets full after two.
+Jordan: Yeah. What else do I have for this? Oh, I want to say they ****** *** the gods literally every chance they had. Like them dudes were dumb as hell. I mean, they were in a death situation, of course, I understand. But everything they were like, if you built a manual of what not to do on a long trek home, they could ride it.
+Darius: And then he just shoots the arrow at the ******* thing.
+Jordan: I was like, what are you doing?
+Darius: He yells at his name so he knows that he's Poseidon. Thus he gets on the boat. Someone said, listen, about the second island, I'm gonna be like, look, I'm gonna wait till y'all get back to this boat. Every time we leave and go up somewhere, it goes way left. Because they get to the second island. And did you know that was like a bunch of seven foot tall actors?
+Jordan: Yeah, I did. So yeah, so they had seven foot tall stuntmen for the Giants. And then they had like really, really short guys for the stunt doubles for the soldiers. And then I think they just shot it far back.
+Darius: Where do you find 37 foot tall actors?
+Jordan: No, dude, I have no idea.
+Darius: Like, you know how rare 7 foot tall people are? And the ones that aren't in the NBA, like.
+Jordan: Right. Where do you find these dudes? How do you cast that? I don't know.
+Darius: I know everyone's excited for Doomsday, but to watch that trailer of CGI Slob after this. Just like. Like, dude, I don't get it. Marvel, you have just as much of the same budget and resources. What are we doing here? Y'all, I don't.
+Jordan: I don't know, man. Cause even with Marvel, you'd be like everything you CGI in Marvel, like everything. Like remember the white suits in Avengers Endgame? Those were CGI too. Like it's actually kind of crazy.
+Darius: I'm just like, y'all ain't no indie shop. Y'all can afford this. Like what?
+Jordan: Just do it right. You have a wardrobe department.
+Darius: You ******* have Disney money.
+Jordan: Yeah, it's like even like the Captain America movie, the one with Sam Wilson, Anthony Mackie, it's shot in, they're in DC, right? You can tell that they did CGI and they CGI'd some ******* cherry blossom trees and ****. I'm like, just shoot outside, bro. Walk outside. I don't understand. That's also what made this movie great is they shot in like 7 different locations. They shot in Morocco, Iceland.
+Darius: They were on a boat in the city.
+Jordan: Italy. Yeah, they were. Yes, they were all in boat. The dolphins were real.
+Darius: That was.
+Jordan: That was not planned.
+Darius: Yeah.
+Jordan: Yes. Yeah, I think Matt Damon said that they were there was a day where it just like the waves were really, really ******. And guys who had been on the sea for two months just started puking and Crystal was like, Hey, do you mind if I shoot you? And that's in the movie.
+Darius: Yeah, I read somewhere that it was like 80 something hours of footage that he had to cut down to three.
+Jordan: I believe it.
+Darius: And that might be, you know, considering you said they were in a cave for two weeks.
+Jordan: Yeah.
+Darius: Now, how much of that was footage he intended to use? Who knows? But I believe it because he's the one director where everyone's calendar is just clear. You don't have to worry about Tom Holland has a center. You know, we got to get through this because Matt has to be.
+Jordan: They moved back to Spider-Man so they could make this movie.
+Darius: Right. And if you look at what they took as pay, like most of them were taking clear pay cuts.
+Jordan: Yeah, I saw, I saw, you saw their payments, bro. Yeah.
+Darius: Now, granted, granted, none of them missed any meals. Matt David probably done a movie for 15 million in.
+Jordan: 20 years.
+Darius: A three hour epic where you're the lead. Epic. Yeah. He might have made that for his little cameo on Interstellar. Like, you know, like. Right.
+Jordan: And he was just a voice actor for half the time.
+Darius: Yeah. It's.
+Jordan: Yeah, man.
+Darius: They just did it off the love because this is when Christopher Noah calls you go, you know?
+Jordan: Yes, correct. Absolutely. And they still brought their A-games. Matt Damon said, like any shoot or any day on this movie would have been the hardest day of any other day in my career. And this movie would have been harder than any movie ever in my career. But every day was the hardest day ever. But they were all in it together. You know, they were all like the crew was in it. The crew was in the boats, in the water and **** you know? They said it felt like an indie movie because everyone's all together. Everyone's all in on it. I think they said they shot the beach scene with the horse before they shot the coming out of the horse scene. And he asked Chris like, so how are we going to do it? He's like, I don't know. And he's like, so they just figured out. He's like, I think we're going to get in the horse and shoot.
+Darius: What was I going to say? Shout out Elliot Page. We didn't have her on the cast, but she had a very small piece of the story, but it was a critical piece.
+Jordan: Yeah, he was important.
+Darius: The way they spliced it to where he dies in the, you don't see who's inside the horse at first, and then it comes back later and you see that they were all inside it, the Trojan horse. Me too, bro. Me too. Now I'm just putting these scenes in my head and I just want to see them again. Yeah. Normally when I see movies two or three times, there's stuff I wish I could just fast forward through in the theater.
+Jordan: There's not a scene I would skip.
+Darius: There's one at the end I would move along. We'll get there.
+Jordan: Okay. And even like, so And also we do, okay, so we do have to talk about this, like the, because there's no fan base that's more racist than like the fans of fantasy in terms of movies. So they were like, oh, Lupita Niago, she's not Greek. And it's like none of these people are Greek. First of all, it's Greek mythology, it's not real. And then they were flipping out because they people thought that Elliot was playing Achilles when she didn't, he didn't play Achilles. So I love that plot twist and people are still freaking out about it. But she was, she was great. She was incredible. What else am I going to say? Oh yes, you want to do you want to get to the my favorite scene in the movie with the pigs? Yeah, go for it. Okay, first of all, okay, so they get there, they're on the island and they start walking past like they see like a jaguar and a lion and like a leo</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to Out of the Trunk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at JordyBriding.
+Darius: And I'm Darius. That's Steve's all up in the area on all socials.
+Jordan: And this is a podcast where two friends started talking at a bar and never stopped. Today we're going to be breaking down Christopher Nolan's psychological mystery thriller, The Prestige, starring Hugh Jackman slash Wolverine, Christian Bale slash Batman, Michael Caine slash Alfred, Scarlett Johansson slash Black Widow, Rebecca Hall, that's just her name, David Bowie, the legend, and Andy Serkis, another legend. The Prestige takes place in Victorian London with two rival magicians becoming obsessed with creating the ultimate illusion after a sudden tragedy divides them. As their bitter feud escalates, both men resort to deceit, sacrifice, and dangerous scientific discoveries, risking their sanity and lives to outdo each other. I'll toss to you for act one.
+Darius: Act one, the rivalry begins. Two ambitious stage magicians part ways after a tragic accident during a water tank trick. Their intense rivalry sparks a dangerous game of sabotage as each strives to dominate London's theaters. That accident is because of a mistake by Christian Bale's character during a magic trick, Hugh Jackman's wife dies, literally like drowns on stage. So It's up from there on out and the movie starts. I don't want, I thought of this, but I read it somewhere else. So I want to give credit because I want to bite. But Matt Iglesias made the great point. He was like, this movie came too soon in the Nolan filmography. Filmography. Like if he announced today, I'm going to do a period piece about two magicians, it would be a billion dollar franchise. But in 2006, people are like, but a period piece with two magicians. But no, like he has so much clout now that this would be, because I mean, I think this is a masterpiece. So I'm going to go ahead and spoil it. Yeah, me too. Spoil my review. But I'll start with, I just think it came along so early that it'll just be overshadowed by the bigness. Like it's not a big movie, but like his movies have gotten so big and existential and The Odyssey and the atomic bomb and Dark Knight. Dark Knight Rises. Yeah. And so like the scale of it is small. It's ultimately about a petty beef between 2 magicians.
+Jordan: Yeah.
+Darius: But I think it's like literally heaven is best. So me too. It came along a little too early. But I'll start with the regular observation that man, Michael Caine's accent was thick. I almost had to subtitle a couple of scenes. I was like, dude, you must have just came from over on the pond because it was tough early.
+Jordan: There's that running joke of him where people say of him were like, you have to use his accent to say his name. So instead of saying Michael Caine, you say my cocaine.
+Darius: I mean, I guess maybe it was coached out of him later on, but man, in this movie, I was like, dude, I had to because The opening scene, he's explaining the three stages of a trick.
+Jordan: And you didn't know the words he was saying?
+Darius: I could not tell. And it's this alongside scene. And I'm like, I actually need to hear what he's saying. And I had to rewind it. And I'm just like, I finally just Googled like, what does this dude say? All right, I know what he's saying. So we go, what you got for act boy, man.
+Jordan: That's funny. So my first note is Michael Caine's voiceover is peak. because I think he just has underratedly like one of the great voices of all time I know obviously we talk about like you know Morgan Freeman and **** even Heath Ledger had a like legendary voice you know I can't think my mind's going to play right now but you know what I'm saying Denzel has a great voice you know and Michael Caine is never really referenced in that kind of category but I think he should be because it just I don't know the way he inflects the voice with the emotion and save for act three you know where he really brings it home. It just is on another level. So I love that this movie had him do the voiceovers.
+Darius: One of the great character actors of our time.
+Jordan: Yes, absolutely.
+Darius: And like you said, he's Alfred. Speaking of the magic trick, do you buy the theory that the movie is structured like the three steps of a magic trick?
+Jordan: Yeah, I do. 100%. It's Cause it really almost feels like 3 movies. Like you could break this up into a mini series and 3 45 minute episodes and it would flow and hit the same way.
+Darius: What struck me on upon watching it was just how much it all holds up. Like normally movies with a twist, you go back and you're like, okay, there's a little movie.
+Jordan: The twist is the whole movie.
+Darius: Yeah. Or just like, it should have been obvious that people in the movie, like, When you rewatch it, you're like, that doesn't actually hold up. This would have da da da da da. Everything kind of holds up, man.
+Jordan: Yeah, you get it.
+Darius: The twin character never actually speaks in scenes.
+Jordan: Like, yeah, and if he does, it's a muffled voice. He says like 4 or 5 words. He never looks anybody in the eye. He's kind of slouched over. So you can't really get a clear look at him, you know?
+Darius: And once the once the fingers get shot off, you stop seeing his hand in scenes. And so, yeah, man. It holds up. It holds up really, really well, even after the twist. So what else you got back one.
+Jordan: I want to say, well, Christian Bale is one of my favorite actors of all time. I think he's one of the 10 greatest actors ever, if you ask me. And Christian Bale and Hugh Jackman acted their ***** off in this movie. They were both ******* phenomenal because they both playing essentially 4 characters a piece, you know. And also, I love the fact that they were both playing these roles in the midst of playing their biggest roles ever. Cause people **** on comic comic movies and all that, whatever. And it's like, but you can still be a phenomenal actor. I know. You can do, you can do, you can do both. You know, you can be skilled at making great movies and also do the fun comic book **** too. You know what I'm saying? Like you don't have to do either or. I mean, MCU is different because you got to sign for like a picture, 6 picture deal, whatever. But I love that they were both able to do that together in the midst of, you know, their biggest movies ever. So Okay, so we obviously know that the twist is that Christian Bale's character has a twin brother and they've been living half-lives for, we really don't know. So I wanted to ask you, there's the scene where they go to that first musician's show, The ******** and they kind of watch him at the end of the show where he's like waddling out with the fishbowl. And you see the admiration in Christian Bale's character's face and he talks about him. And I can never tell if That's where he got the idea from, or if he had already always been doing it. And because he'd been doing it, he knew how difficult it was. Do you do you think do you have any theories on that?
+Darius: I believe like so the. The part of the movie is that the two characters focused on two different things and it was like Hugh Jackman's character was about the spectacle and the showmanship and the. Yeah, the selling and just Christian Bale's character was just committed to the trick, committed to the craft. And I believe from birth they were they were doing this, man. I don't like literally from birth, but I believe for this to work and for everyone to be so bought in. Yeah. To the in the end, giving your life. One of them gave their life to it. Right. That has to begin in your formative years. Then again, why they would do all this for some magic tricks. I don't ask that movie to be realistic. I actually, they stay true to the world that it was built. And that's why I love this movie, because the stakes are comically low. Right, It's like, dude, you could just say like, hey, man. But it's just, they care so much. And it's, great. It's movies are supposed to be stretched so much. Yeah. And it's like, why? Okay. And it's just like, they said in the end, like every one of the audience knows that they just, they know they're being fooled. They know it's that actual magic, but they.
+Jordan: Right.
+Darius: You want them. It's part of it. Like, like when I turn on the movie, I know these stakes are low, but like I'm enthralled with it because everyone is committed to this bit. Right. So I mean, it's, you know, it's a masterpiece.
+Jordan: And I also think like it kind of perfectly encapsulates the perspective of passion, right? Like the things that mean the world to you might not mean anything to anybody else. Like to us, that's just like, why are you doing all this for a magic tree? Like that's kind of crazy, right? But it's like, if you were, if someone were to ask us, why are you doing all that for a podcast?
+Darius: Yeah.
+Jordan: They look at us crazy, right? You know what I'm saying? Like, you know, if an athlete, you're doing that for a ball, you know what I'm saying? Like it's, if you can apply that to anything that anyone is devoted to.
+Darius: I read, I'm reading a book about Chris Hayes book about attention. And there was this paragraph in there that just really hit home. Why, we, why we put so much into the podcast. It's, I won't, you know, read online. I'll tell you about it later. But yeah, it's just like, you have to keep yourself intellectually honest. You can't just work, go home and watch TV, or you're just writing with just rot. And so obviously this is different for them because this is their job. But yeah, like you got to It's okay to find something obscure and obsessed over it. To the point where you're cutting off fingers, but it's a movie.
+Jordan: Yeah, right. I also just like this movie, one, it's just phenomenal movie. Like this is to me one of Christopher Nolan's best screenplays, scripts, however you want to call it, whatever, writing jobs, if you will. Like the symbolism and the foreshadowing with the birds, he kept focusing on the birds, the two, the pairs of birds, you know. The scene where Christian Bale meets his wife and she's got like her nephew and they have to kill the bird to do the magic trick. And the kid's crying and he's like, no, look, I have a bird here for you. And he says, what about his brother? And he pants Christian Bale and he's like, damn, Like, you know what I mean? Like just the foreshadowing of that.
+Darius: Or just like how the wife could pick up on something was off when like one brother loved her and one.
+Jordan: One brother didn't.
+Darius: And yeah, that's something a wife would pick up. Like something is off here. And yeah, he kind of communicates that without giving it away. Yeah. I mean, it's one of I think it's his best writing, just like straight pen. I don't think it's his best movie, but it's his best writing for sure. I'm not mad at that. It is airtight. Like there's no holes in the storage whatsoever.
+Jordan: Nothing doesn't make sense. There's nothing. There's not a wasted scene. Everything you need every bit of this movie.
+Darius: It's every bit of the runtime. Yeah, it's rare you see, at least in movies. writing this crisp and this airtight and this clean, you know, the same thing. But you know what I mean.
+Jordan: And speaking of the speaking of the wives and the because you have Scarlett Johansson's character too, like it's, you know, there's I feel like it was fine for the second brother when he had no one. But when he fell in love, it almost made him dislike Sarah more, if that makes sense. Like, I think when he had no one, it was like, okay, cool, I can pretend to love this girl, whatever. But then when he actually fell in love, I think it got harder for him to fake it, if that makes sense. But they had, again, total devotion to the lie, total devotion to the craft, total devotion to the trick.
+Darius: I mean, this was the only thing that mattered was, I mean, his wife triggered warning, like hung herself because she literally, the confusion She thought she was going crazy. And what it was, they were just literally tricking her.
+Jordan: Yes, they were literally tricking her.
+Darius: So yeah, I mean, it's...
+Jordan: And she knew he would never tell him the truth.
+Darius: No, you cannot tell anyone your tricks, you know. So ready to get in Act 2?
+Jordan: Yeah.
+Darius: Act 2, the illusion of sacrifice. One magician unveils A jaw-dropping teleportation illusion. driving his rival to obsessive obsession. Desperate to uncover the secret, he seeks out a radical, mysterious machine built by Nikola Tesla. The magician who did the teleportation first would be Christian Bale's character, and the one who got obsessive would be Hugh Jackman's character. We said this earlier. This is just for you. I know people say this A lot. But you really do have to watch this twice. The first time, right after. And the second time is where, a lot of Christopher Nolan movies are like that, actually. But that second time is when you're really like, oh, this is a masterpiece. But I do, to go back to a thing we've discussed on the spot before, bass player or lead singer.
+Jordan: I wrote that down, too. Yeah.
+Darius: Jackman, man. He just wanted to be in front like he had it. He was good.
+Jordan: He had it.
+Darius: And he just he could not stand being under the stage when everyone got the applause.
+Jordan: Correct.
+Darius: And it's just it's just wild. You know, it is. Yeah. He had every the whole crowd fooled and but the one person that fooled was his rival and he didn't get the applause and he literally was undoing so.
+Jordan: Yeah, I love that detail that Christian Bale's character was always like, he was always a step ahead because he was like, it's so interesting how he comes out before he does that trick and he's overweight and drunk, you know? And then it was like, he has to hate because he knew him so well. From like a psychological perspective, he was like, I'm sure he loves taking those bows under the stage.
+Darius: You know, as someone who often shines spotlight, I must admit, it would suck. That would suck, bro. You're in a ******* moldy basement with rats and **** and all your work is being applauded upstairs.
+Jordan: Some drunk ******** upstairs, like, thank you.
+Darius: And then just the feeling that your whole life's work is in his hands at this point. Like, yeah, you can't, if at any given moment, like he has all the power, he can ruin it.
+Jordan: Correct.
+Darius: Keep in mind, like this is 1890s London, like This is his whole world. I know it sounds silly that you can't do magic tricks anymore, but think about the scene of the movie and the world that the movie built. This was everything. This was, you know, Space Jam, the Monstars taking his powers, you know, like that's how important this was. It wasn't just his whole And he's already lost his wife.
+Jordan: So he's literally already lost everything, And then.
+Darius: Not only is he not getting the praise, but like his, this dude, he has to hold his breath the whole 3 minutes that man's on stage. And then he starts ******* with him, not coming out late. And it's like, you can't, you can't have it.
+Jordan: Yeah. And I think that's, that was like, to me, the one of the greatest ways to highlight the difference between the two characters is that one, Christian Bale was kind of had the luxury of he's doing it with his brother. So you don't care to let your brother shine. That's fine. But like some drunk ******* you found on the street, you're going to feel a way about that.
+Darius: You're identical twin brother. You literally share DNA and two. It's almost not just to me, they're one character split in two. Like I don't like they were interchanging. So like, Some nights he got the praise and the other nights they switched up. And that's why he had to cut his fingers off because, you know, they had they were they were doing interchangeable things. That's what kept the bit so solid.
+Jordan: Correct.
+Darius: And, you know, it seems obvious that they were twins, but like, you know, this is 1890 twins weren't like.
+Jordan: Yeah.
+Darius: Let the movie wash over you. It's you have to. It works. It really works. And the makeup.
+Jordan: It really, really does.
+Darius: When you look at them, you can see Christian Bale in there. But on the first, I don't know anyone on first few who says they knew it was a twin.
+Jordan: No, the first, yeah, the first time I saw it, there was a split second where I was like, is that him? Because I was like, no, that didn't make sense. So I just disregarded it.
+Darius: I want to rewatch, you can see the camera chicks and they, you know, but it's like.
+Jordan: Yeah.
+Darius: It's like The Sixth Sense. I don't care who you are. You didn't know on the first watch. Right. You just, you're retro, you're retconning, you're it.
+Jordan: And even if, and even if you did like, because it's such in passing, you wouldn't, you wouldn't be sure anyway.
+Darius: You just not, you're watching a movie and it just, the way it was set up upon, I don't believe anyone who says, if you've never seen it before, And you've never Googled anything about it and you went into it ice cold. I do not believe you if you say you saw the twist coming. I don't believe you.
+Jordan: No, no, no, no. Yeah, I agree. I was going to say. **** lost my train of thought. Okay, so. Oh, go ahead, go ahead.
+Darius: Oh, I was just going to ask, do people still go to magic shows? Is that still a thing?
+Jordan: Not that I know of.
+Darius: I was like, are they just like ventriloquist dummies where it's like a thing that we like look at and we're like, people actually were entertained by that at one point. Yeah, I think The fact that we could just Google the tricks now would kind of kill it.
+Jordan: Yeah.
+Darius: I always give you some time to get your train of thought. What were you saying?
+Jordan: And I appreciate it. Yeah, I was going to say, yeah, that's actually really nice. I literally wrote down everybody wants to be the prestige, you know, nobody wants to be the turn. And the pledge is cool. But like, you know, and I think I think that's part of what Hugh Jackman's beef was with Christian Bale. I think his character is He was the better magician. He also was the purest in terms of just love of the craft. And he saw through you. know what I mean? And I think sometimes when you meet someone who really can see you, that's almost like a triggering thing. And I think he really felt like, because remember, he never trusted him from the beginning, even before his wife died. He just never ****** with him. And I don't know if that was like a jealousy thing or what, but it always felt like, I don't like that this guy knows what I am and I got to figure out what he is before he figures out what I am.
+Darius: In defense of Hugh Jackman's character, he did, you did accidentally kill my wife. You can't just yada yada past that. This is not a petty beef. He's like, yeah, he's like, oh, he was jealous. I don't know, man, he didn't kind of kill his wife.
+Jordan: Well, I'm saying before, even before that happened, there was, he had like, he clearly had an issue with him.
+Darius: No, but a lot of people frame the movie like he, it was a petty jealousy. It's like, well, okay, but like his wife did drown in the film.
+Jordan: She did die, yeah.
+Darius: That's not petty. There's nothing petty about holding beef over that. But no, clearly Christian Bale's character was a better musician. And it was just, it was almost like, Clyde Drexler, right? It's like, you're going to be that guy. You know, it's like no matter like Clyde Drexler to this day just, you know, he hates Jordan because, you know, he just he was labeled the next Jordan. And like, it's just sometimes the other guy is just better. And it really felt a lot like, you know, he's don't know it's almost like LeBron KD Paul George type thing where it's like yeah Paul George on the Pacers you're just not going to be TC it doesn't matter what you do you know so yeah I mean it didn't in the end though he did kind of well we'll get there in act three but you got anything else for act two?
+Jordan: What I meant to actually this next one do you do you what not do you think he tied do you think he knows or knew what type what he tied?
+Darius: Can you repeat the question I'm sorry.
+Jordan: When the wife died yes do you think he tied the wrong knot?
+Darius: Yeah I don't I I don't know.
+Jordan: I feel like if he had he would have just lied and said no I didn't but because you said I don't know I'm almost like did you tie regular knot and then change your mind halfway through or did you tie regular knot and then just second guess because she died?
+Darius: Based off of what I know watching the movie I would say I don't think I don't get homicidal from Christian Bale's character I can't I get obsessive about the trick, but I'm not sure how botching a trick and killing your partner's wife would do anything. It seems like a continuing accident that became like a a war. But I don't think if I had to guess, I would say I don't think he did it on purpose.
+Jordan: Yeah. And I also like people forget, like the wife was game. She was like, yeah, I can do it. I can get out of it. We can practice this, whatever. Like they were both, you know, in favor of taking the risk. So it always like, I mean, grief obviously ***** up your mind and also you still have a right to me and she did die. But like, it's also like she was kind of game and He was in favor of taking risks. And also, like, if you didn't like yourself in a glass box of water, you could just drown, period. Like that also is a thing that could happen.
+Darius: You know, it happens quick. Yeah, I don't think you did it on purpose, though.
+Jordan: Yeah, me neither. I think that's what that's what, from my perspective, what makes Hugh Jackman's character the villain of the story.
+Darius: Okay. Why is that?
+Jordan: Why is he the villain?
+Darius: Why is he the villain?
+Jordan: I'm sorry. Because you killed a guy and planned on raising his daughter by faking, because you faked your own death. That's pretty villainous.
+Darius: True, I guess. But you did kill my wife. The whole, the whole, you know, spoiler alert, but the trick to Hugh Jackman's trans. transporting man was he was literally cloning himself and drowning the clones.
+Jordan: Yeah, right.
+Darius: So that's pretty villainous.
+Jordan: I'm like, you killed like 50 people.
+Darius: For a magic trick. And it was like at the end of the movie, we're jumping all around, but the end of the movie like pans out to just like rows and rows of like drowned cart. Yeah. Like man. And he never knew. Although I do believe that He knew that he would be the clone that comes out the other side.
+Jordan: Correct.
+Darius: So because otherwise, how would the if the new person lost the trick?
+Jordan: Wouldn't make any sense.
+Darius: Wouldn't make any sense. And so he was dedicated to traffic crafty guy. Anything else for act two?
+Jordan: Yeah.
+Darius: Act two.
+Jordan: Yeah. So, okay. Yeah. So what made you what do you think made Scarlett Johansson flip?
+Darius: Old-fashioned charm. like he's women like ambition and she found just like extraordinary talent, ambition. And what she found in him was the better musician, the more successful musician, the one who mastered the art. She's over there to steal his tricks because her old dude couldn't figure it out. And, you know, cuff your chick. He just got, she just upgraded, you know, upgraded to being someone's side chick, but.
+Jordan: Right. I just think that she.
+Darius: Went from an all-star to an all-NBA player. Sometimes it happens. And so like, it's obvious anyone watching who the better musician was. And so she wanted to be with the better one. Keep in mind, like magicians watching the movie.
+Jordan: These are rock stars.
+Darius: Yeah. So like, you know, he's a bigger rock star. Happens all the time.
+Jordan: Yeah. I forgot this point. I also love the parallel of their rivalry compared to Tesla versus Edison.
+Darius: Yeah.
+Jordan: I thought that was super dope and it gave it a nice like grounded feel to it because that, did really happen, with those two guys. And they actually did work together too, which is, what happened with Bale and Jack. So I thought that was a pretty dope storytelling element.
+Darius: Yeah, it's the movie does a good job of staying grounded while being supernatural when it needs to be. So it's like a good blend of both. And it's in a believable way, So.
+Jordan: It's honestly like I kind of was like, damn, did these machines exist back then? Like it's he did it so well. I was like, wait a second. Hold up. Did I miss something in history class?
+Darius: Yeah, I mean, it's the first time I watched it, that was I didn't see that coming because I didn't see the movie going supernatural. And then you, you know, again, you rewatch, you see the hats in the field, the two black cats, different things like that. And it's like, obviously the clones were working, but like, you're just not, your eyes aren't, there's a lot of trickery where they're moving your eyes in different places to keep you distracted. And that's what makes the movie so great. It holds up. You got anything else right too?
+Jordan: I did want to shout out the blocking in this movie, like the way they position the actors, on the sets in terms of relation to the camera. Like when they do the scenes with Hugh Jackman and his body double or whatever, or stunt double, whatever you want to call them, the way they make it so that you never see both their faces at the same time. So you can just use a double and swap out, you know, with the marks on the floor and stuff. I thought that was super dope. And even the way they shot it, like, it's Hugh Jackman playing both guys, but like the prosthetics is different and his performance is so different. You're almost like, wait, is that just a guy that looks like Hugh Jackman? And I thought that was a dope testament to his acting too, because he was talking.
+Darius: About the drunk guy.
+Jordan: Yeah, the drunk guy. Yeah. Because he kind of looked different.
+Darius: He did look different. I would have. It was believable. If you told me that was a different actor, I believe it. But he obviously. It's easier to just have him do it and just, switch the things around. It's remarkable how believable the movie is, even after you know the tricks. Right. So, yeah. Heading into Act 3, the ultimate trick, the obsession reaches a deadly climax when the horrific truth behind both illusions is revealed. Both men face the ultimate consequences of their secrets, proving the ultimate sacrifice required for illusion. But toss to you for Act 3. What you got?
+Jordan: So what I love about Act Three is that it shows the consequences that both guys, all three guys played from living a double life. You know, you have Sarah killing herself. You have what's her name? Scarlet Johansson. You know, she's kind of like, are you okay? Like, what's going on? Whatever. But because it was the other brother, he was like, I mean, I kind of loved her, but I kind of didn't. I really love you. And then she's like, also just the audacity of trying to play like the indignant mistress where she's like, how dare you say that? That's so inhumane. I mean, it wasn't humane, but it's like, okay, lady, you were inhumane for cheating.
+Darius: Life is complicated, man. You can, I don't think it's, look, obviously it's a ball of emotions, but like, she's cheating with him and she loves him. And she's also appalled that he doesn't care that his wife hung himself. I don't think that's a contradictory set of beliefs. It's just, you know, human beings are messy.
+Jordan: Yeah, that's true. And then you have, you know, Hugh Jackman, you know, everything they did to each other. You know, Jackman lost basically a knee bail, you know, the two fingers. And then at the end, you know, you have him being like, you went around the world. You spent a fortune for nothing.
+Darius: Because he discovered a cloning device.
+Jordan: Well, that's enough for nothing. And then even, you know, where he one of my favorite scenes was the the role reversal of where they read in the journals and they had the voiceovers. It's like, I got you. Where it's the one where he he realized the Tesla, which is the fake name he gave him to send to America so he could have live his life. He didn't think he'd ever come back to England, I guess. and then you know on the flip side he's like yeah you're gonna die in here because I'm alive.
+Darius: I mean just like the commitment to the bit like yeah you know Bail like one of Vale's characters died for the bit you know yeah and like you know he knew this twin brother would carry the legacy on a retired the greatest musician ever musician magician ever and that was enough for him he knew that the streets would his name would ring out forever so.
+Jordan: True. When did you start to realize that he was a twin? Was it the what he said to him when he gave it said his last goodbyes?
+Darius: No, I didn't know until the twist was revealed in the movie. The first time I watched, I had no idea until when Hugh Jackman's character gets shot in that in the basement of that theater. I was like, okay, well, where we was it? Is it Michael Caine? Like what's going on here?
+Jordan: Yeah.
+Darius: You know, once he, you know, they did get You know, Christopher Nolan does this. They just start, it gets expository. He just starts talking plot.
+Jordan: Yeah.
+Darius: No, he just like, oh, you have a twin? But let me tell you about my cloning device. And it's like, I'll lie.
+Jordan: He does like explaining ****. He does just, I think he just likes explaining ****. I'm not gonna lie. Cause that's in a lot of his movies.
+Darius: Yeah. He just like, you know, Hugh Jackman's characters like knocks on the screen. He's like, hey, let me tell you what's going on. And normally I hate it, but I'll allow it in this one because Everything else to that point is just so airtight that, honestly, the crowd, the audience probably needed an explanation at that point.
+Jordan: I'm about to say, yeah, it was pretty shocking, for sure. I mean, first of all, I was just like, what? Like, I kind of suspected when he was, when he threw the ball, I was like, I'm sorry about Sarah. Like, I didn't mean to hurt her. You know, I'm sorry about a lot of things. Live your life. I kind of was like, wait a second. But when he came out of the shadows with the gun, I was like, what? I think I immediately rewatched the movie the first time I saw it because I was like, there's no way.
+Darius: Did you see this in theaters?
+Jordan: No, I saw it at home. I think I was in high school, so maybe not too long after it came out, probably like 07, six or seven, maybe 08 when this came, when I saw it for the first time.
+Darius: I saw it in theaters. I was either a senior in high school or fresh out. And Yeah, I mean, everyone leaving that theater was just **** ****</t>
+  </si>
+  <si>
+    <t>Jordan: Welcome to the Out of the Trunk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. That's Jordan to be writing on all socials.
+Darius: And I'm Darius. That's Steve's all up in the area on all socials.
+Jordan: This is the podcast where two friends started talking in a bar and never stopped. Today we're going to be reviewing Reservoir Dogs, starring Harvey Keitel, Tim Roth, Michael Madsen, Chris Penn, Steve Buscemi, Lawrence Tierney, Randy Brooks, Kirk Bates, Edward Bunker, and Quentin Tarantino, who also wrote and directed the movie. After Diamond Heist collapses into chaos, surviving criminals regroup in a warehouse and try to determine what went wrong. As suspicion spreads, alliances fray, loyalties are tested, and every conversation becomes a pressure point in Quentin Tarantino's sharp, violent, dialogue-driven crime thriller. So I'm gonna toss to you for Act 1.
+Darius: Dialogue driven is an understatement. Act one is a job before the fall. Sharply dressed crew prepares for a high stakes robbery, but their limited knowledge of one another creates immediate tension beneath the cool talk, coded names and professional confidence. So I used to confidently say that the starting four run of Reservoir Dogs, Pulp Fiction, Jackie Brown and Kill Bill, we'll count that as one movie, is the greatest four movie run for a director ever. I just I had not seen Reservoir Dogs in a while, and I must say it doesn't really hold up.
+Jordan: No, it does not.
+Darius: So even accounting for Reservoir Dogs being a little weaker than I remember Pulp Fiction, Jackie Brown, Kill Bill.
+Jordan: No, for sure.
+Darius: We're still talking about a top the top four run for me ever. So yes, up there. Let's start it off with a question, or I already started off, but the question, is it safer to do a robbery with complete strangers or with a close-knit group of friends?
+Jordan: Yeah, I'd rather do it with a close-knit group of friends. That way I know who needs to do what job, who can handle what, who needs what, who can do what information, who to trust. I have a rapport with these people. I know how they think. I know what they can handle. Yeah, I'd rather do that than do it with strangers because anything could happen like in this movie or in the Dark Knight where they could snipe you to get a bigger cut.
+Darius: That is true. I think it's a trick question. It is safest to do it alone. You don't. No co-defendants. I thought you were going to say don't do it at all. Well, fair. But no, the old adage, the easiest way to get away with the crime is to do it by yourself. And when you start having 2, 3, 4, 5, 6 people, something's going to go wrong, someone's going to snitch, something's going to, it's like, how many rappers are currently on trial because their friends talked? So,
+Jordan: All of them.
+Darius: Yeah. It's like, I'm honest, that's why I don't believe in conspiracy theories in general, because if you tell me that more than four or five people have to coordinate on something and keep it a secret, I'm like, probably it's not true. It's just not, I know people too well and like, You know, you can't agree on, like you couldn't get three people to agree on pizza toppings and you're going to get them to plan these elaborate conspiracies. I don't, I don't believe it.
+Jordan: So like, yeah, yeah. I mean, just think about how, yeah, just think about how hard it is to plan a surprise birthday party for sure.
+Darius: Yeah, it's just. It's just, it is.
+Jordan: So you mentioned that with life changing stakes.
+Darius: Life changing stakes. And then everyone has to agree on a plan. Everyone has to execute that plan without ******* up. Then everyone has to keep it a secret. And that means. And then the conspiracy will be 10, 15 years old. And I'm like, you mean to tell me for 15 years, no one ever. was trying to impress some woman and got too loose lip. No one ever had a falling out because they was talking to the same girl and then some dude got mad and went and told and no one ever got too drunk at a bar.
+Jordan: And it was like, well, he did this, and this.
+Darius: And no one borrowed some money and got ****** about it and decided to snitch off that. Like nothing went wrong. I'm gonna need more.
+Jordan: No one got a bigger cut and then read everybody or got a smaller cut and then read everybody out.
+Darius: It's just, it's hard for me to believe these things.
+Jordan: Yeah.
+Darius: Speaking of rats.
+Jordan: I hear you.
+Darius: What you got practical?
+Jordan: Okay, so this series is going to be, it's going to sound a little crazy, but to me, Quentin Tarantino is the ditty of the film industry. the scale of the deviancy. He does a, apparently he has a weird foot thing, but whatever. I mean, he's a total self insert. Like he wants to be a movie star so bad in the same way that Diddy wanted to be a rapper. Ray likes like the Suge Knight thing was like all in the videos dancing. Okay. Come to death row type ****. Like he's always just in his movie randomly for some reason.
+Darius: I thought you were going to go with these talented hack who just knows how to hire right people. I was like, I don't know about that, man, but I'm with you with that.
+Jordan: Oh. Although his work is a derivative of a lot of Asian cinema. That is a real thing and valid criticism. But I was going to say, yeah, just the self-inserts. There's this famous story where he was in a movie with George Clooney, I think it's called Desperado, and they play brothers. And he directed it, and I think he wrote to me too. And I remember he called Clooney and was like, hey, so I have this movie role for you. We look alike, so we're going to play brothers. Clooney was like, what?
+Darius: Oh, hey, you do not look like him. Not at all, buddy. It's not at all. So regarding the criticism of being derivative of Asian, I mean, if you like him, they say you're paying homage. If you don't, you say he's, you know, it's a criticism. I mean, that's fair. I mean, I don't. Any movie is a derivative of something, so I don't get what they don't understand why he gets it in knowing us. But, you know, I like that's true. He knows me. I think he's completely lost his fastball. Everything absolutely hateful eight has been bad, but I like him and I think his nineties run is out there with the greatest director runs ever.
+Jordan: So yeah, his nineties run was legendary. The second half of Hateful 8 is really good, but I think he sticks too much to the whole nonlinear story thing where like every story didn't have to be told that way. You could have just told it straight up and it would have been entertaining. I don't know if it's just like a hacky thing where it's like I want to have a long runtime just because. It doesn't feel like that's a thing with him.
+Darius: I think what you think about the lost a little bit of their tightness when his director, when his editor died, that Sally Lady.
+Jordan: Oh, okay.
+Darius: And so there's a clear break and they just get really long winded and less tight. And I think Sally died. I don't know when, but if you look, if I remember looking it up and I'm like, yeah, that's when the when the he lost his right hand. the person, the one person who could tell him, cut that. That's stupid. And once you lose that, you have no governor. And if you've, ever worked with a writer who's not used to being edited, it's tough. You know, that's the people who have to edit George R.R. Martin. So what else you got for act one?
+Jordan: Yeah, so I do want to shout out also just the, I'm not, I don't think this movie is as legendary as everyone says it is or said it was at the time to me. at least. But I will say that it does have extreme cultural relevance. I remember I remember the intro to Laugh in My Pain, Kevin Hart's Stand on Special. He did a version of this movie in his opening sketch where he was like, Mr. Pink, Mr. Black, Mr. Blonde, Mr. Blue, Mr., you know, whatever. So I always remember it from that. And a lot of the actors and writers and directors They came up in the 90s after this movie came out, referenced this movie because Tarantino was an unknown writer director and he wasn't going to get the movie made. So he had to write like a lot of dialogue stuff that an actor would want to do. And because he was able to cast Harvey Keitel, he was able to get his movie made. And if you ask Ben Affleck and Matt Damon, they'll tell you like, if not for Reservoir Dogs and like do the right thing, we wouldn't have written Good Will Hunting.
+Darius: I mean, I understand. It's almost like playing an old video game to where you could see where it was iconic for its time. But like the controller scheme is so rated, you just kind of it's just hard to you can't put yourself in your in the body of 1992. Because I remember when I first watched this movie and I just wasn't as into movies, I absolutely loved it. And it just kind of was a little lukewarm for me when I watched it last night. I just was kind of like, it was one of those movies, some movies I watched for the pod and I don't feel the urge to grab my phone. And this was not one of those movies,
+Jordan: Yeah, it kind of reminded me a little bit of Usual Suspects. This came up before that, but it like that movie was just had a little more sauce to it than this one did. I mean, granted, the budget was low, so I kind of get why you had to just have everything dialogue. But yeah, so did you have a favorite quote unquote color slash character in this movie?
+Darius: I guess the main character, Tim Roth's character, mostly for a point that I get at later in the segment. But I would say his, even though he just lays on the ground sprawling around for an hour with an amount of
+Jordan: blood that was screaming.
+Darius: Yeah, he'd have bled out four times over. Yeah, you could tell he had no budget because that blood looks so fake and there was so much of it. He was like, dude, you bled out four times. Like you would have died.
+Jordan: Right. Like at the end in the final. There's blood like on the wall. I'm like, he was 5 feet away from that wall this whole time. How the hell did that get there?
+Darius: Yeah, it's he did. You could see him working with it's, to bring it back to Pokemon, like you could see the limitations of the technology at the time and you can appreciate the scale of the engineering that they did with an 8 bit megabit cartridge on their Game Boy while still acknowledging the game's ******* impossible to play today. You know, it's right. Yeah, it's just it's a tough it's a tough. watch to watch six dudes in a warehouse scream at each other. Yeah, with no.
+Jordan: And it's a heist movie with no. Right. And it's a heist movie with no heist.
+Darius: Right. And it's like. He says he didn't do the heist because it was like his creative director. I'm sure he just didn't have the budget for you got to get another set and then you have to get the people. You have to break the glass. You have to get the. My guess is he just didn't have the budget.
+Jordan: So you've got to get the extras.
+Darius: And, you know, you've already paid the actors, so let's just put them in a warehouse and act like the robbery never happened. And it'll be my artist, artist brain, you know? So it worked, though. It really did work.
+Jordan: Right.
+Darius: The movie works, even if I can say that it's not my favorite movie that I've watched before. So what else you got? Fract three. I mean, act one.
+Jordan: I would have shot blonde the second he I would have shot blonde the second he walked into that warehouse. Any dude drinking a soda that cool after a robbery where he killed like 5 people, you got to die.
+Darius: Yeah, you know, but you'd want the cool you want a cool customer in light of the high. Did they ever say how much money they were stealing?
+Jordan: No, they just said it was some diamonds from Israel.
+Darius: Okay. I mean, it had to have been in the millions to get all these people to do this. You ready to get attacked too?
+Jordan: True. Yeah.
+Darius: All right, Act 2, paranoia in the warehouse. Survivors regroup after disaster, piecing together conflicting accounts while suspicion turns the hideout into a pressure cooker, where loyalty, fear, and self-preservation collide. We'll go with you. What you got for Act 2?
+Jordan: For Act 2, okay, so I have where they take the hostage for Act 2. So I guess Honestly, this one, I just have like one question that kind of summarized the whole thing for me. What was Mr. Blonde's agenda? Because I just I don't get anything that he did. I don't understand why he did anything that he did. Just like nothing didn't make sense. I still don't like. I'm like, did I miss something? Was he trying to, like, throw people off the scent as to what they were doing? I just didn't get it.
+Darius: My suspicion is, well, I don't think it was explained, but my suspicion is people have. People were introduced to Quinn with Pulp Fiction, which is an all time top 10 classic. And they sort of retconned how they feel about Reservoir Dogs. That's a, yeah. And it's like, I have a bit where I'm like, sushi is one giant game of telephone where no one, we're all just pretending to like it. This movie might be a giant game of telephone. We're all just like, Man, Reservoir Dogs, that **** was, you know what you're supposed to say about it, but it's not, yeah, right, It's like, 'cause I'm, it's hard just you, they don't show just heist and they're, it's a, yeah. It's a movie about trust. And it's like you were repeating what you heard from a game of telephone.
+Jordan: 100%. It's yeah, I'm just like, it's like people like, oh, no, you don't get it. You don't get it. It's like, no, I get it. That's the that's the problem. Yeah. It just felt like a really hollow script. Like these characters don't really have a lot of distinct, distinct things about them. Yeah. I mean, the most interesting thing about them is their nicknames. like I don't even with the color thing, it's like we spend only one day with them in this course of the story. Even then, it's hard to remember who's what color, because it's like, okay, I'm like,
+Darius: which character, which the actor?
+Jordan: Oh, yeah, Michael Madsen.
+Darius: It's telling that When most people reference this movie, they reference the diner tape, the diner banter about tipping, which is in the first 10 minutes of the movie. And I suspect it's because they cut the **** off after that scene. Have you seen Pulp Fiction? Yeah. You see that scene about the tipping? It's the first nine minutes. Did you watch anything after that?
+Jordan: Yeah. Right. The way the camera panned around all of them, it was so cinematic.
+Darius: It's a good commentary on tipping. It's like, okay, cool. I got that. 9 minutes into the movie. Do you have anything else for it? It is the most compelling thing in the movie. Right.
+Jordan: And by the way, that conversation had nothing to do with it really is, honestly. And it's funny because it had nothing to do with the plot at all. They never came back around in any way, shape or form. It was just like. They feel like he just needed an icebreaker to open the movie.
+Darius: Yeah, it's, you know, it had nothing to do with the plot because there was no plot. I will give him this. Correct. The flashback where Tim Roth is explaining the art of being undercover and repeating a lie and making sure it is overarching. I found that compelling because often I did too. Often liars forget that they have to have an overarching umbrella over the lie and they will tell lies that make sense there, but then a lie later doesn't, once you compare them to, they don't add up. And so, it was interesting to watch them explain the art of lying in the sense that like, no, you have to rehearse it because it has to feel like the truth. It has to feel like second nature. And you have to make sure that when you tell your story in its entirety, the lie you told in line 3 lines up with what you're saying in line 11. You know, in book editing, a lot of book editors, a lot of their feedback will be something that happened in the winter doesn't make sense with what you said. It happened in the spring. And so like that happened.
+Jordan: Okay, got you.
+Darius: Yeah, things out. And so it happened. And what is creative writing, if not writing what is essentially a lie. And so you're stringing it along and you just forget what you said already. And so, you know, that was a good, I found that compelling to explain the art of lying. So that is, there's some positive feedback for the book. Yeah, I got that.
+Jordan: I agree too. I like that scene too, because when he brought up the point about like, you have to know, be able to tell was it a hand, paper towel dispenser or was it an air dryer? Because the story he told where he's in the bathroom with the weed, it has to be an air fryer, air fryer, air dryer or something that makes sense because that would fan the fumes of the weed, which would get the dog to going crazy. which would make the situation all that much more tense,
+Darius: And that's something a bad liar would overlook. And so you have to. Right. I found that was that was compelling. That and the tipping scene are the two compelling things in this movie.
+Jordan: You know what annoyed me in this movie though?
+Darius: What?
+Jordan: Yeah, so what I found annoying is like just the random racism in this movie. Like, have you noticed Tarantino just kind of throws it in some of his movies where he just like, they just randomly drop hard ERs and it's not, it's not Django.
+Darius: You know, I do notice it. doesn't bother me. This is fiction. It's a bunch of white dudes who are criminals in the 90s robbing banks. It doesn't strike me as odd that they would use the N-word.
+Jordan: Yeah, that's true.
+Darius: I have this ongoing Twitter bit when I was like, so much of the discourse is driven by people who don't realize fiction is fake. It's like, you know, it doesn't bother me. These are fictional characters and it is a close knit, all white group of criminals who are probably They're probably racist. I mean, that just, it just doesn't strike me as out of.
+Jordan: Yeah, for sure. Yeah, that's true.
+Darius: You know, so I mean, I do see what people mean with his gratuitous use of the word. And sometimes it does feel a little cartoonish, but yeah, it just doesn't bother me. I don't really, it doesn't really bother me. To be honest with you. It never feels like the character wouldn't use the word. And also, you know, it, you, Not you, but a lot of people. You can't on one hand claim that their racism is pervasive and everywhere and never want to see it depicted. Like you have to kind of be everywhere.
+Jordan: Yeah.
+Darius: So, you know, it's, there's another point of contention I have with something else that's in movies, but I'm not putting that in the pot. So.
+Jordan: Okay.
+Darius: Yeah, I'll tell you that off air. But yeah, so anyways, yeah, I mean, I understand the critique. And it's not an invalid critique. I just, it just doesn't bother me. So.
+Jordan: I hear you. Oh, ****. I forgot. We're, wait, we're still in Act 2 or Act 3. I'm tripping.
+Darius: Act 2 and sign. Act 2.
+Jordan: We're in Act 2. Okay, yeah. The scene where Blonde, the crazy one, goes off and just like slices dude's ear off. And then he's about to like light him on fire. Again, it just didn't make sense because I'm like, you kidnapped this guy in theory to get information only to burn him alive.
+Darius: Well, he was crazy. And that's probably why you don't do crimes with psychopaths. But yeah, I don't really, honestly, that part of the movie is a little hazy for me because that's probably when I was scrolling Twitter. I was like, it's just. It's just six white dudes yelling in a garage. And I'm just, how much of this can I watch? It's, it really is.
+Jordan: It is. It is. Honestly, it's just.
+Darius: And then Tim Roth is.
+Jordan: On the ground with a.
+Darius: Bunch of saint blood just mailing it in, just yelling in the worst acting you could see.
+Jordan: It's just not even bad acting. It's the bad accent for me.
+Darius: It's just. Yeah. You know, it's a rough watch. It is short. That's good.
+Jordan: That's the one really good thing about this movie is that it is short. And things do happen in the third act because for the first 70 minutes, nothing really happens.
+Darius: Well, speaking of third act, trust runs out as accusations harden and options disappear. The remaining players confront the cost of secrets, loyalty and pride in a finale built on tension and irreversible choices. You know, it's kind of clever to do a robbery movie that isn't about a robbery. It's actually about. So it's kind of a prisoner's dilemma because it's like. You're building this thing where you're testing people, but everyone has a personal incentive to lie. But if nobody lies, we all get away with it.
+Jordan: Right.
+Darius: But to me, that's just every crime, you know, like every criminal organization. if you're caught and you're in a situation, you have a personal. I just don't think this is as groundbreaking as people wanted to believe.
+Jordan: Yeah, and it's not that it's not like it's one of the earlier heist or crime movies. So I truly don't get the lore behind it. I mean, I know it was 92 and I wasn't, I was born, but I wasn't there, you know, in the theaters. But I just don't get it because like there are certain movies you watch no matter how old they are. And you're like, I get why back then they were like, oh wow, that's crazy. Like, I mean, I remember watching the Cat Burger with Cary Grant. It came out in like the 60s. So a heist movie where like one of the guys is a cop is kind of standard. I don't get it.
+Darius: I think, I really do think my theory that people love Pulp Fiction because it's great and retcon this one. Yeah, it's like.
+Jordan: Yeah, I think so too.
+Darius: It's like your favorite sitcom. You go back and watch season one. You're like, yeah, they were still warming up. You know, it was like, you know, it was a little shaky.
+Jordan: Right.
+Darius: It wasn't.
+Jordan: Yeah.
+Darius: It doesn't matter what sitcom. It's specifically for sitcoms. It's like the office. Yeah, specifically for sitcoms because you have to part of the joke is being on the inside and knowing the characters. Those first seasons. are often they don't know each other. Yeah, a bit choppy. And this is like season one of Quentin Tarantino's discography. It's like.
+Jordan: Correct.
+Darius: Yeah, I can see the makings of the the genius. But, you know, this was this was it wasn't fleshed out yet. And I think like most great things, we retcon the beginning of them. So no. Anything else for act three?
+Jordan: That's true. Yeah. Oh, would you do anything different with the ending? if you wrote the script.
+Darius: Well, yes, I would make it good. So, you know, what specifically I would do differently, I don't know, but just having them all shoot each other and fall down and insane.
+Jordan: Yeah.
+Darius: To answer your question, yes. What would I do differently? I don't know, because I would have making I would have changed so much leading up to that point. But yes, I would have made it. What would you what would you have done differently?
+Jordan: I would have I think I would have had the boss guy, the bald dude was got named Nice Guy Eddie. I think I would have had him be revealed to be a rat in the end. And maybe I can make off with the money with the diamonds.
+Darius: Well, Jack Nicholas and the departed type action. I'm with it. Yeah, if they had like revealed him to be like some inside person in the sense that like, not a cop, but maybe whatever, the manager of whatever place they were robbing or something like that. yeah, Just give me something that makes me feel like I didn't waste any money. Yeah, just like I just, I just watch these dudes yell in the garage for 60 minutes and you just roll credits on me. **** you. Yeah.
+Jordan: And then they just shoot each other. That's it. Like, I haven't seen the weasel.
+Darius: But I feel like yeah I had I don't remember it being this mid to be honest with you.
+Jordan: Yeah and even the fact that like the most the least interesting guy just walked away with everything.
+Darius: Yeah so what else you got for act three man?
+Jordan: Um that's all she wrote Tarantino.
+Darius: So I mean, I do have a, I know your answer to this, but is this movie good or is it just pretentious?
+Jordan: Yeah, I think it's pretentious. And everything we know about Grentin Tarantino, he's even more pretentious now, but he was younger than so he probably was more pretentious because he was less accomplished, if that makes sense. Yeah, this is a very pretentious movie. It's like, I'm going to make this movie about people while not actually studying people in the movie.
+Darius: I agree. You can be highbrow, but it has to be good. And this just isn't very good. So with that, what do you rate it?
+Jordan: Yeah, the intro was cool. I did like the third act. I'm going to give it I'm going to give it two and a half stars.
+Darius: Oh, two and a half for me as well.
+Jordan: Okay.
+Darius: I can't give it a three because I don't want to watch it again. And my own personal rule is you can't get a three if I don't want to watch you again. So 2.5, he stumbled out of the gate a little bit, and I'm glad that whoever was around back then loved it, and he got to go on one of the greatest director runs of all time.
+Jordan: Yeah.
+Darius: Shout out to him. All right. Thanks for listening. My name is Darius. That's D's I love the area on all socials.
+Jordan: And I'm Jordan. That's Jordan Rewriting on all socials.
+Darius: Please rate, like, and subscribe. We're at Out the Trunk Pod on all socials. That is Out the Trunk Pod on all socials.
+Jordan: And for any ongoing movie recommendations, feel free to reach out to us via e-mail. That's outthetrunkpod at gmail.com. Again, outthetrunkpod at gmail.com. That's a wrap. Thanks for coming to the movies with us. Come back next week for another episode.
+Darius: Thank y'all.</t>
+  </si>
+  <si>
+    <t>Jordan: And we support y'all in wearing less and going out more because we will also be wearing less and going out more.
+Darius: Correct. Thank you guys.
+Jordan: Everybody, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Steve's all up in area on all socials.
+Jordan: And today we're going to be reviewing the classic, one of the best movies came out in 19 of the best movies of all time, The Sandlot. Last movie came out in 1993. Dang, that was a long time ago. Starring Tom Gweary, Mike Vitar, Patrick Rena, Chauncey Lapardi, Marty York, Brandon Quinton Adams, Grant Gelt, Shane Obezinski, Victor Demantia, Dennis Leary, Karen Allen, and the legendary James Earl Jones, RIP. Set in the summer of 1962, 5th grader Scotty Smalls moves to a new neighborhood and desperately wants to fit in. He's taken under the wing of Benny Rodriguez, the leader of a local neighborhood baseball team that plays daily at the neighborhood sandlot when Smalls accidentally hits a priceless baseball autographed by Babe Ruth into the backyard of a legendary terrifying neighborhood dog known as the Beast. The boys must hatch a series of increasingly wild plans to retrieve it.
+Darius: And we're going to go with act one, the new kid on the block. Had a lot of hits. Scotty Smalls arrives in town, completely lacking any baseball skills, but Benny invites him to fill their 9th spot anyway. Smalls struggles initially, but starts to find his rhythm with the crew, learning the ropes of the neighborhood dynamic. Nothing to do with the movie. Do you believe Babe Ruth is black?
+Jordan: I have this on here. That's crazy. I have this on here. Yo, I've seen enough Dominicans to know, to know when I see one. He looked real ethnic in them pictures, bro, especially when they had like a, they had a twinge of color. He looked, yeah, I think he was definitely ethnic for sure. It would explain the trend of, you know, Latinos, the Latino, you know, presence in baseball. I think so, man. I think he was. Yeah, it was.
+Darius: The features are there. it's just passing meant something different than it does now.
+Jordan: Correct.
+Darius: And I just, obviously we'll never know for sure.
+Jordan: Yeah.
+Darius: There's a little bit of internet folklore in it, but if I had to bet $1,000, yay or nay, I'm betting yay. So yeah. What you got Frank one.
+Jordan: I agree. so couple things. first, my first observation is moving your kid who's graduating the 5th grade 2 weeks before summer break before he goes to middle school is one of the more, it's like social suicide, bro. Like imagine that you have all your friends, you think you're going to middle school with these guys, you move to a new neighborhood, school gets out. What the **** are you supposed to do all summer?
+Darius: Yeah. Yeah. Well, I mean, he got a job, though, right?
+Jordan: Like, yeah, that's true. Yeah. It was for a job. It was.
+Darius: Yeah. What do you do? Like, certainly. Well, yes and no. I think at that age, though, you just back then you just went outside and you hung out with the kids in the neighborhood and you kind of had to know that that was going to happen. So this movie was set in the it's made in the nineties, set in the sixties. And anytime I watch a movie, it's set in the 90s, but it's kind of a similar point. I'm always, the first thing I notice is just how poor everyone used to be. Like these houses are tiny. These, every car is junk. Like nobody's ever doing anything, but just kind of hanging out. And it's just, this is a wealthy suburb in this show.
+Jordan: But that's what I was going to say. Yeah. In that time period, they were up remote of class.
+Darius: Right. And so it just, to me, it's just, It doesn't, like, anytime I watch an old movie, the first thing I notice is just like how much living standards are higher than they used to be because these are wealthy people in the show. And, this would be the, I mean, you watch, you look at the sandlot and you watch the backdrop and these houses look like it looks like boys in the hood. Yeah, they look like they're collapsing. And so, you know, shout out to progress.
+Jordan: Yeah.
+Darius: I did like the multicultural group of people. I did think that it was it was interesting that it was accurate for the time in the sense that back then this was considered multicultural. Like there was an Italian guy, the Bambino, what's his name? Gambino, something like that.
+Jordan: Yeah.
+Darius: The redhead.
+Jordan: The chubby kid. Yeah.
+Darius: Then he was obviously Puerto Rican. Yeah, there's a black guy. Yeah, there's a Dutch guy. And like, this was like they weren't all just white in 1960. This was actually distinct cultural and ethnic differences. And so that was true to the form of the time.
+Jordan: Yeah, especially for California in the 60s. Now, what I would say is it's funny, though. Well, I'll say that for another part, but yeah, it is. I like that they have had a diverse friend group, especially considering that time period. Like if they were in Virginia, That story would have not have had a happy ending. I did think it was interesting though that the fact that like the kid, his mom had probably been married to his stepdad Bill for at least a little while. Obviously, they knew him wanted to move states with him, whatever. I thought it was interesting that they kind of showed like the, I don't want to say subservience, but just like the gender roles of the time period, because like You married a guy probably for security because your dad, your husband died, when you were, you had a little infant, basically, that had such a, I don't know what the word is. I'll say cold relationship with your son that he didn't feel comfortable calling him dad or playing catch with him. You know what I mean? Like looking back and watching as a daughter, I'm like, well, it's kind of crazy that you would do that. But then it's like, well, she probably more so married for the security than, you know.
+Darius: Yeah. Married love was not really a decision made in love back then. she needed the financial security and this is the 60s. It wasn't easy for a mom with a young child to find a man who would even give her the time of day. And so she had to take What did she had? What did she got? And so that was a survival mechanism or anything.
+Jordan: And I mean, women, white women weren't really working at that point, right? 60s.
+Darius: That really wouldn't, no women were.
+Jordan: So, yeah, true. Well, black men were like, you know, being mammies, I mean, mammies, nannies and, you know, **** like that.
+Darius: I mean, like a wage earning I mean, everyone's working. She's working, keeping the house going. I mean, like a job with wages that you can pay for things like she didn't. For by and large, men were still the vast majority of the workforce in 1962, I think.
+Jordan: Yeah. I also want to say like there's this thing with like actors and period pieces where they say like people have what's called iPhone face where like that person has the face of someone who looks like they know what an iPhone is. Yeah. And I feel like everyone in this movie actually does look like they could be in the 60s, which I think is kind of cool.
+Darius: It helps. It was made in 1990. So.
+Jordan: Yeah, true. So it wasn't that far away.
+Darius: Yeah, hold on. So this is 1993.
+Jordan: I think the mom definitely looked like she could have passed for 50s or 60s.
+Darius: Won't get old. So this movie was made in 93. It was set in 62.
+Jordan: Yep.
+Darius: If a movie, if that same time period, if a movie came out today, it would be.
+Jordan: Set in like 99.
+Darius: We're old men.
+Jordan: Someone said they'd be like this retro 90s setting.
+Darius: That 70s show, if it came out today, would be like that 2016 show.
+Jordan: Yeah, that's ******* nice, dude.
+Darius: 2006 show.
+Jordan: They'd be like, remember that classic album, Views?
+Darius: Yeah, it's like. Yeah, it's, so culture was stuck for a while. I think we're getting out of it. But yeah, it's yeah, that movie.
+Jordan: Yeah.
+Darius: If I remember watching Sandlot thinking these, this movie is from like a prehistoric era and that would basically be a movie in the 90s now.
+Jordan: So yeah, so I love that this movie is about baseball. It's not like one of my favorite sports necessarily, but I like, I feel like baseball Has some like the best just uniforms period like the jerseys all look dope. I love they have buttons on it looks really cool that the baseball hats obviously they're a fashion statement in our community, you know. So it got me to thinking like what are some of the best nicknames in sports? Some movies, you know, Babe Ruth, you know, Great Bambino is, you know, a big backdrop in the movie. What are some of your favorite sports nicknames of all time?
+Darius: That's a good question. Gotta love William Refrigerator Perry.
+Jordan: Yeah, that's a good one.
+Darius: Clyde the Glad Fraser is a good one. Oh, that's tough. We don't really do nicknames anymore. I mean, the greatest is magic, right?
+Jordan: Yeah.
+Darius: I think I don't know anyone who calls him Irvin anymore. No one. I think if you told me he actually legally changed his name, I believe you. Yeah. those are the ones off the top of my head. How about you?
+Jordan: I go Air Jordan. Is Tiger Woods considered nickname? Because I think it's like legally his name now, but at one point it was his name. Yeah, Tiger Woods. King James is hard slash the frozen woman. Chosen one rather. What else? What else? I'm trying to think. Who else has a great name? Pretty Boy Floyd. Floyd made with this like early era.
+Darius: That's my name when there was a better nickname though.
+Jordan: True. That's true. But I love like all those old gangster movies and ****. So I love the callback to that. What's another good one? Trying to think. I mean the great one. That's pretty amazing. It's simple, but it works.
+Darius: What is it? Mean Joe Frazier. That's a good one.
+Jordan: Yeah. Mean Joe Green. Who else? Who else? That's going to bug me.
+Darius: Well, it's not bad audio. Just naming.
+Jordan: Yeah, you're right. So Vincent Vincentity is good. Vincentity was a good one.
+Darius: Vincentity was a good one.
+Jordan: Yeah, that's all.
+Darius: That's everything else for act one.
+Jordan: Act one. And that's all I got for act one.
+Darius: All right, we can go into act 2, the legend of the beast. The summer heat peaks as the boys play their hearts out, square off against a rival Little League team and navigate pool days with Wendy Peppercorn. But the real trouble begins when Smalls borrows his stepfather's Babe Ruth signed ball and it flies straight over the fence into the domain of Hercules. I did love that because I wasn't expecting him to do this, but when he does the scheme to sneak and kiss Wendy Peppercorn, Smalls, a narrator, says it was sneaky, rotten, and low. It was nice that they acknowledged that was pervy as hell. Yeah, I didn't expect them to, but I appreciated that there was enough self-awareness in 1993 to be like, yo, that was wild out of pocket.
+Jordan: That was wild.
+Darius: Little boys can be a bit pervy, so I get it. You know, I'm not trying to throw them in the gulag, but at least can we acknowledge that there was sneaky, rotten, and low. I was going to believe what he said.
+Jordan: My favorite part is like he kissed a woman. He kissed you long and good.
+Darius: So gross. Faking a drowning.
+Jordan: And like all your friends think you're ******* dying. You're like traumatizing the **** out your friends. And then the kid with the glasses, he's like, oh my God, it looks like a dead fish. And then he looks up and he's like.
+Darius: I don't, do you know, like something I noticed is like the modesty of the swimsuits.
+Jordan: Yeah, yeah, yeah.
+Darius: Granted, it was a community pool, but, you know, swimsuits don't look like that anymore. No, you do not appreciate it. But I was just like, those are those look like, like Jim, like I've seen more risque outfits at the gym.
+Jordan: Facts. Yeah. Agreed. Let's see what else I have. So one of my favorite sees in the movie is when they they celebrate beating the snobby kids in baseball. And they go, they all go to the carnival and they give each other, they give them the dip, the big, big chew.
+Darius: Have you ever had chew into Echo?
+Jordan: No, I've never had it. I've never had it. I had friends who did it in high school.
+Darius: It's so gross.
+Jordan: I don't know why we thought that was cool.
+Darius: I did it in high school too. It's just, it's like literally, it's like chewing. Like the insides of a cigarette, but the texture is snot. It's just awful. It's really bad.
+Jordan: That's gross.
+Darius: I don't get it.
+Jordan: It's funny. So I do smoke cigars and I've had cigar hangover. Have you ever had a cigar hangover before?
+Darius: No, I have not.
+Jordan: So I've only had it one time. And the difference between like a cigar hangover and like liquor hangover is when you're drinking, you feel fine during. It's the next day that sucks. It's sleeping that makes it worse. With cigar hangover, you feel that **** in real time. Like when you're drinking, you have that one drink, you're like, oh, if I stop now, I should be good. Cigar hangover, you smoke it and you're like, oh no. And you just feel like you're gonna throw up for the rest of the night. Like you, it like it, like I had it once my head was spinning. I like, you just felt like if you moved, you would throw up. Like that **** is so uncomfortable.
+Darius: Is there, do you know what triggers it?
+Jordan: Basically, it's like everybody's tolerance is different, but it's basically like it's like a magic number, I guess, of puffs, if you will. And once your body hits that point, ejectosito, because it's like, it's just, it's over.
+Darius: Is it like seasoned cigar people know when they're one puff away?
+Jordan: Yeah, for sure. Like you kind of get to that point and you're like, okay, yeah, I'm good. I don't need to finish this.
+Darius: Yeah, I know exactly when the next shot is just too many and it'll ruin.
+Jordan: Right.
+Darius: The night I'll be fine, but the next day it will be shot. No pun intended. So I just be like, nah, I'm done with shots. No matter who orders them, run around, whatever. I'm like, nah, I think my, this is still fun limit and I would like to keep the night fun. Right. I did love how, through adult eyes, these are all minor problems. Now, they were best baseball is a whole different thing, but like that's yeah. The way they kept the purity of it being through a 10 or 11 year old's eyes and like that 4th of July game may as well have been the World Series, but it was clearly like the fireworks and the neighborhood game and there's a mythology around the dog that like is peaking game of telephone where it's like he ate a child and the kids, the cops came and told him we're going to lock him up forever. The dog is 50 years old and it's just forever. And it's just like, this is what little kids do. They just, the imagination runs wild and there's, you know, the adults know it's full of **** but they let kids have fun, you know?
+Jordan: Yeah, I love that too. Cause like even like watching a movie, you know, it's like that fence in the movies, like 6 feet tall. In real life, if through the eyes of a child, if probably like, the fence was probably 3 feet tall, or basically the size of a tennis net, and they just were like. **** we can't come over there like, cause the big dog's gonna eat us. And you know what I mean.
+Darius: And no one ever thought to like knock on his door and be like, hey, we hit a baseball and y'all can we get it? Most reasonable people will be like, yeah, sure, I don't care.
+Jordan: And they're like, no, he's crazy. He'll eat you too. Like, no.
+Darius: It's like, you need me to get my dog and keep him in the house while you do it? Like, it's like, we live in a society. You can, sometimes you knock things in my yard, you can go get it. It's not, you're not breaking any laws.
+Jordan: Like, they did a great job of like showing like the innocence of kids, but also them being stupid at the same time, even when they're arguing with the kids who had the baseball team, the insults were like, it was **** that we said as kids, you know what I mean? You play ball like a girl.
+Darius: It's just, it's just so funny, man, because it's like, you know, did any of them think, hey, let's just ask him if we can get our ball out of his jaw?
+Jordan: Like, what? It's, yeah. And it's funny because in the 60s, that was the whole era was like about, I mean, aside from obviously segregation and racism was a white to white, white to white people. It was about civility and friendship and camaraderie and manners and all that. So it's like, you could have just knocked on the door and be like, hey, our ball went over your fence.
+Darius: You know, They're kids, though. So, right. I have it here. You mentioned it earlier. The stepdad was weird, right? I wasn't true.
+Jordan: Yes, he was weird. He was kind of an *******. He's an *******. He's an *******.
+Darius: He wanted to go to the end, but I'm just like, why are you this standoffish with a 10 year old, dude? Like, don't you feel ridiculous? Yeah.
+Jordan: Right. The fact that his mom has to like chaperone him asking you to play catch with him. Like, I don't understand.
+Darius: I'm glad they didn't go into that too much because I doubt we would have kept the good vibes of the movie because that guy was weird, man.
+Jordan: He was weird. And I wasn't sure if that was like what it would have been. I almost wonder maybe now looking as an adult, like if there was scandal around marrying a woman with a child from a previous relationship, even though the father had died, like I wonder maybe if that's what it was.
+Darius: Especially in these elite suburban spaces that they're probably the only blended family in the neighborhood, Right. This wasn't, I mean, that today that's not even abnormal, but in 1962, a divorce at all, obviously she's a widow, but these things were just exceedingly rare. And, you know, he probably heard the whispers or whatever, you know?
+Jordan: So you got anything else for act two? I think that's all I got for Act 2. Yeah.
+Darius: All right, we are flying through these. We got Act 3, the great retrieval. With time running out before his stepdad notices, the boys construct an intricate, ridiculous mechanical contraption to fish the ball out. When everything fails, Benny has a literal dream encounter with the babe himself, inspiring him to lace up his PF flyers and tackle the challenge head on. I must admit, I enjoyed Act 2. more than act three because I found the summer hijinks more interesting than the pool, the Fourth of July, the tobacco, the carnival, the coming of age story. I just find that more compelling than them going, it just became like a sitcom where like, let's try this episode and just, I just kind of lost it right there. So quite the engineering prowess though for children.
+Jordan: Yeah, for sure. For 8 years old, 10 years old, whatever they are, to build that.
+Darius: Spoiler alert, Catapults went on to be very successful. They were smart kids.
+Jordan: Yeah. One of my favorite of their retrieval tactics was where they had Yaya on the string, like the Mission Impossible scene. And it's like, he had the ball, he got scared by the dog. It's like, just throw the ball over. What do you, had one job. You literally had one job and you couldn't do it.
+Darius: They're kids, man. Like they just, the guy was blind. one one afternoon during a lemonade on his board. He's like, why are these kids like flying in my backyard? What's going on? But it just it was nice to see kids without the helicopter parenting. So much of playtime today is structured. It's either, you know, if this were modern day, they would all be on like a baseball league team. And there's nothing inherently wrong with that. But like, there is something to kids navigating social dynamics without parents overseeing it. And so it was good to like, you know, watch the hierarchy develop and then come up with plans together and then figure it out. And, you know, like they took those lessons through, you know, their whole lives. So yeah, I thought that was cool to just watch, you know, these kids are just roaming the neighborhood, playing in the sand lot. The parents had no idea where they were. As long as you're home before the sun went down and It was just, it just, I think if you could, you don't want everything from 1962 for obvious reasons, but that's something that we could probably try to get back, Yeah.
+Jordan: I agree. It's funny because this neighbor, this movie reminded me a lot of my childhood. Like that was me and my friends in the neighborhood running all over the place. You know, we, our school was across the street, so we would go over there and play football like in the summer times and **** like that.
+Darius: We played baseball with four people. One in the outfield, one pitcher, one catcher called the ball and strikes and everyone taking a turn swinging. And we didn't keep score. We were just out there swinging a bat.
+Jordan: Yeah, just playing St. hockey with no skates.
+Darius: Hopefully the kid with the basketball hoop in his yard is home so we can play there.
+Jordan: Yeah, I was a kid with the basketball hoop. So yeah, we played in my house. One of my friends had a trampoline in his backyard. we were at his crib all the time. And he had a swimming pool too. So I was like the money house, low key.
+Darius: We put a, we put a, my boy Kyle, he had a trampoline in his backyard and we used to put the sprinkler underneath it, which is just surprised none of us broke our neck on that ******* thing. But we, I mean, we was, it was basically like a ******* water park. We put the sprinkler under the trampoo and we would just bounce and just we're like little kids. There was a ******* tree. We would jump off the tree onto the trampoline with the water underneath it. is a miracle none of us broke a bone out there. Yeah, for real. Bill character though. I definitely injured myself a few times, but yeah, the metal around the trampoline would shock the **** out of you because you'd have the water conducting and you'd slide across it and you know, but it was, I wouldn't trade it for, well, I would trade it for a few things, but I wouldn't trade it. I wouldn't trade my childhood I wouldn't trade a low-tech childhood for a high-tech childhood.
+Jordan: Yeah, me neither. Yeah, all the silly **** we did, riding bikes. You know, there was a big creek like in our neighborhood that our parents told us not to play in. Of course, we wouldn't play in it. We found like a tunnel. I think it might have been sewage. I'm not sure. Looking back on it. You know, playing in the street, playing in the street with our school shoes on. You know what I'm saying? All that stuff. Yeah, man. Those were the days, man. It's funny because even to the point of how big things are to a child's mind. So my office now is around the corner from my old house when I was a kid. So I would drive by there sometimes just, tripped up memory lane literally. And the fields we played in felt ******* huge. And it's like, The size of a bedroom.
+Darius: We just play football in my yard because I thought I like we had the big yard and one tackle football with no pads, no helmets, just smacking the cold Minnesota ground, which is just insane. But yeah, it just felt like the biggest yard in the world and it was maybe 20 yards. Yeah, it was a whole football game on a 20 yard field.
+Jordan: So yeah, all time QB.
+Darius: I have it here. Adults should get able to, should be able to pick one summer off every decade to just like, have a summer vacation where they don't have to work. Like give me one a decade. Obviously you can't have them all the time because you know who's going to work, who's going to, When you go to Chick-fil-A and it says we're closed for the summer, you're not going to like that. So someone has to do these things. And so if we can just stagger it so that every adult gets one summer off a decade and we can make it work economically, I'm down with that because like a summer vacation.
+Jordan: I think it will be a better place.
+Darius: You know, just the whole thing just made me, you know, long for just the The waking up and just going and not having the lack of constraints, the lack of responsibilities. It was a good walk down in real life.
+Jordan: Yeah, that's one they don't tell you about growing up. It's like you didn't really, like, you didn't even think about it when you were a kid, but when you grow up, you're like, oh **** no more summer breaks.
+Darius: No, you got to work through it. But that first summer after morning, they went places.
+Jordan: Yeah, like that first summer break after college graduation, you're like, oh **** this is it. Like it's over.
+Darius: No, there's no. And the thing is, it's not just that you get the summer break. It's not just being off of work, because most jobs come with some sort of PTO. It's everybody being off at the same time. And you can just call up your friends because you were all either in school or whatever, college school, whatever. And just like, everyone's off this week because it's this break. Everyone's off this summer because it's this. And it's just now it's like, Y'all wanna go to Vegas for the weekend? Oh, let me see if I can get this. Let me see if I can do that. We gotta get a babysitter here. Let me talk to my wife. So much more has to go into it logistically.
+Jordan: So much more planning.
+Darius: When you were, you know, when you're a kid or in your early 20s, it was just, it's July, no one's working. Right, who's ******* what?
+Jordan: You got a summer job, okay, when you get off.
+Darius: Right, like when we go, you know, nothing else is going on.
+Jordan: Yeah, like even in college, we got our summer jobs, like we get off work or whatever, and then we, Shower and change. We'd go grab a couple of 40s from the grocery store, drink those, Uber to our other friend's house. We'd pre-game there with liquor, and then we'd go downtown and, you know, **** the city up. Like, you know what I'm saying?
+Darius: Just be able to.
+Jordan: Coordinate with everybody to spend a weekend together and ****.
+Darius: Or just like there being no collateral damage. Like man, we used to drink. Yeah. Four, 5, six shots of crown to pregame and beer all night and then you just wouldn't wear on your stomach. Like you just, you were fine. No. Man, like try going on a two week without it just drinking beer and **** man. You're not gonna feel great.
+Jordan: It's going to be 4 days before you feel fully normal.
+Darius: Yeah. The bloat, the gut rot, the, you know, the lack of consequences for poor diet is just something that when you're in your early 20s, you don't realize. Yeah, that's the hardest part. What else you got for act three?
+Jordan: Yes, this is one of those movies, man. It's almost like a. like a soul food, like a chicken soup movie where like it just makes you feel good every time you watch it. works every time. It never goes stale. You know what I mean? Like I still laugh every time at the same lines, at new lines, you know? There's never a memory that doesn't trigger from childhood. It's just like the writers and whoever and the makers of this movie, they did an excellent job of just like creating a love letter to childhood, period. And the fact that it transcends decades You know what I mean? Like it's a 90s movie set in the 60s. We're in 2020s. We grew up in the 90s and 2000s and it hits the exact same way as it probably hit everybody who were adults when the movie came out. It's incredible.
+Darius: It's just, I like that. Okay, let me ask you this. So now, I mean, that's a childhood we could all relate to. We just told stories about it. Are we the last generation who can relate to that kind of childhood of just like low tech, leave the house, gallop, just wander the neighborhood. No one's calling the police because a band of teenagers are just walking around. Right. You know, no one's known. You could pop it to your friends. You knock on your friend's mom's door. And even if they're not home, they offer you something to drink because you're a sweaty, tired child. Child. You probably smell terrible because you've been in the sun for three hours.
+Jordan: Oh, for sure.
+Darius: And like, What do kids even, they even relate to that anymore? Are we the last generation who can relate to that?
+Jordan: I feel like we are because I think it back to now, so many of my friends' moms like stitched me up after like falling off my bike or I have really bad allergies and carry, especially in the 90s had like, or in 2000s had a lot of just like flush and not wildlife, grass and shrubbery everywhere, So I would like be breaking out like in hives from the pollen and ****. And my friend's mom just like wiped me down like the calamine lotion, like, cause I was like breaking out everywhere, I think so because my neighborhood now their kids playing and **** but they're like on electric scooters and they all have phones. They're still outside, but it's just different.
+Darius: Yeah, I think, I don't know. I just. I live in the community and I see the kids outside and they I don't know maybe they can maybe they can because they seem to be obviously I'm sure they have phones but they out they be outside all day especially during the summer all the kids seem to be friends in the neighborhood. I'm sure they don't talk to me. I'm ******* almost 40 years old, but they seem to get along all the neighborhood kids and they seem to have their interpersonal dynamics that, you know, I can notice just like, you know, walking, throwing garbage away or going for a jog or whatever. So maybe, not. Who knows?
+Jordan: And you make a great point about like helicopter adults And even just like helicopter, I'd say institutions, like did you see that? There's a clip that went viral on TikTok. There was a couple of kids who got like reprimanded by police and security guards in North Hills. They just were like eating ice cream. And they were like, yeah, there was some, there was a fight earlier. You guys were in it. You're banned for life from like North Hills and ****. They were like, we weren't even involved. We just got here 10 minutes ago. We were just in the movie theaters. Like we weren't even involved. The cops were just like overly aggressive with them and ****. You know what I mean? It's just like And I remember some of that happened to me when I was around the same age in North Hills. And we went to the movies and we were, my siblings were outside waiting for our parents to pick us up. And they were like, do y'all have IDs? And they were like, my siblings were like, no, we're minors. And they were like, well, you can't be outside as minors. We're going to detain you. We have a center over here where you guys can go. And I was like, well, I'm an</t>
+  </si>
+  <si>
+    <t>Darius: What do you want to watch next week?
+Jordan: Let's see. When will that episode come out?
+Darius: This will come out the 24th.
+Jordan: Okay, so the next one will come out on Halloween. So we got to do like a good one. You got any in mind?
+Darius: Good scary movie. Yeah, you want to want it to be a thinker or just some dumb slasher type ****.
+Jordan: Let's do a thinker.
+Darius: I mean, it's. Or do you want to do like be hollow?
+Jordan: Yeah, that's true. Yeah, **** it. Let's just do dumb slasher ****.
+Darius: Let's do your next.
+Jordan: Okay.
+Darius: Have you seen that?
+Jordan: No, I don't think I've heard of it.
+Darius: I think I got a copy of it on a hard drive already. If not, I can just get one, but it's...
+Jordan: Came out in 11.
+Darius: Yeah, it's... Okay. Literally, it's really dumb, but it's...
+Jordan: Hey everybody, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at JordyBWriting.
+Darius: And I'm Darius. That's D's all up in the area on all socials.
+Jordan: And today we're gonna be reviewing Sleepy Hollow. This movie came out in 1999. It stars Johnny Depp, Christine Ritchie, sorry, Christina Ritchie, Miranda Richardson, Michael Gambin, Casper Vandien, and Christopher Walken. Sleepy Hollow takes place in 1799 when New York Constable Ichabod Crane, an eccentric investigator, is sent to the secluded village of Sleepy Hollow to probe a series of brutal decapitation murders. The terrified localist insists the killer is the legendary headless horseman, forcing the skeptical Crane to confront A terrifying supernatural reality to solve the mystery. So I'm gonna toss it to you for your intro.
+Darius: Act one, we're gonna call the assignment. Skeptical New York Constable Ichabod Crane is dispatched to Sleepy Hollow to investigate a series of brutal decapitation murders attributed to a legendary headless horseman. He meets the townspeople, including the mysterious Katrina. Off the rip. Johnny Depp has aged terribly. I couldn't even recognize him. Yo, he has. He has.
+Jordan: It's crazy because he aged great at one point and then it just like fell off. It's like, I don't know what happened.
+Darius: I don't know if he stopped paying the surgeon or what. Yeah. He looked. I did not know it was him until I had to like, I was doing the rundown. He looks like a different person. You could not tell me side by side that was one person 30, 25 years ago. And don't get me wrong, I'm one of those people who believe people age, that's fine.
+Jordan: It's okay, yeah.
+Darius: Man, good CGI for $19.99 though. What you got for act one?
+Jordan: Yeah, I was gonna say, when we talk about like great director and actor collaborations or duos, I feel like people sleep on with Johnny Depp and Tim Burton. They've pretty much anything like cool and creepy that Johnny Depp's ever been in. Tim Burton probably directed it. What do they do? Edward Scissorhands. I'm sure you've seen that one. What's it called? It's the animated one. The bride corpse. What's the corpse bride?
+Darius: We got Dark Shadows, Sweeney Todd, Corpse Bride.
+Jordan: Sweeney Todd is dope.
+Darius: The subject of the podcast movie, Ed Wood, Charlie and the Chocolate Factory, Alice in the Wonderland. I think this is a biography. And Alice in the Wonderland again. I have not seen any of those. Really. movie that we're reviewing today.
+Jordan: That's crazy.
+Darius: They're all cartoons, you know. It's audience.
+Jordan: I mean, I think only one is only one is not live action. They're all the other ones are all live action. Yeah, Sweeney Todd is ******* fire. It's based on the play. So it's like a musical movie. It's actually really dope. I don't know if you've been to that or not, but it's a cool movie. Just I love them together as a duo. Also, I love when you take kind of old stories or like fairy tales and you kind of flip them on their head. And I think this movie was I like that's what I love most about this movie is the way it kind of takes a children's ghost story and turns it into a really cool whodunit.
+Darius: It is a it is straight up a who done it. Do you think it's it's friendly to a first time viewer?
+Jordan: So do you mean like in terms of tone or the way the story is told?
+Darius: The way the story is told. Like, I'm not someone who demands like a lot of exposition. But you're just kind of dropped into the world.
+Jordan: Yeah. And crazy **** happens.
+Darius: And crazy **** happens, but yeah. It's just, I just don't feel like it was set well. Like is the world, because like Johnny Depp's character, and one of my questions is, did you share his skepticism of the supernatural? But I'm not supposed to, it's like I don't understand if I'm supposed to understand this world as supernatural or if it's, or if these people are crazy or if he's not, I don't understand if it's well founded for lack of a better way to phrase it.
+Jordan: Okay, I get what you're saying. Okay, yeah. I think so because I think this movie was made to be rewatched.
+Darius: Yeah, for sure.
+Jordan: So I think this movie, like the first time I saw it, like the first time I saw it, I think it was maybe like 19 or 20. And when I got to the end, like my head was blown. No pun intended, you know. And then, and then it was on like TBS or TNT and it was like Halloween season. So like they re-aired it right away. And I was like, Okay, cool. Because I was like, okay, I need to figure out what the **** I missed for the first hour and a half of the movie, you know. So yeah, I'd say it's not friendly for first time viewers, but it's not meant to be because I think it's supposed to be rewatched.
+Darius: You can tell it's of an era where people just went to the movies and saw **** all the time. Because you got the DVD and you just watched it over and over and over again. It's very much of the era because they it's hard. I watched it twice because I didn't know what happened the first time I watched it. And I rarely watch the movies twice. So yeah, I get you.
+Jordan: I think the thing is that made it makes it a little hard to follow is there's a lot of characters that play big roles, but because you weren't familiar with them at first, you're like, wait, okay, who did what and what role did they play in the conspiracy? And you know, so I think, at least from my perspective, when I first watched it, what Or if I haven't watched it in a while and I'm like, wait, hold up, what happened? That was what was what threw me for a loop.
+Darius: Well, so like Game of Thrones is similar where there's just a lot of characters and a lot of bad written stories, but you know, a good writer sort of creates an event to where.
+Jordan: Yes, it's not.
+Darius: They're all together. But they're like, there's a reason why. Like, so the first episode of Game of Thrones, you're meeting all these people. But You know, Robert Baratheon's Hand of the King died. So he's traveling north to give the job to Ed at her Stark. And so that gives you a reason to go Sansa Stark, Lady of Winterfell. You know, this is Terry Lannister. Oh, the ******. Let's talk. You know, your dad hates you. And it just yeah, in a way that feels very natural where like the events are explained to the viewer in a way that doesn't feel like the fourth wall is breaking. So I just feel like this movie needed a little of that. Like you need to create something that gives the characters a reason to explain things in a way that's good.
+Jordan: I agree. I agree. Yeah, that's a good point. I'd say so too. Because I think there's two or three major scenes where there is a lot of exposition. And I think everything else is more implied.
+Darius: Yeah.
+Jordan: And I think that's what makes it a little hard for a first time viewer, especially if you're not used to watching these kinds of movies.
+Darius: It's like a video game that you just kind of like. It's like a save file that wasn't yours and you just start. Yeah.
+Jordan: It's like, it's like we like traded PS5s for a week and be like, wait, what level am I on right now?
+Darius: You're just like, oh, I got the buttons. I know I've played a PS5 before, so I know that Square does something. I know like, I know how to slash, but I have no idea what's, I'm just slashing things.
+Jordan: Yeah, it's like when you play Tekken the first time, you just press X over and over again.
+Darius: Yeah, it's like, you know what, you have enough muscle memory from watching these kind of movies to kind of set a scene for yourself. You're doing it by yourself.
+Jordan: Yeah, that's true. That's true. What else do you have for Actor White? Yeah, I think one thing too is that because Ichabod is not from this world and he is a foreigner and you sing everything from his POV and before a lot of the movie, he is confused and lost. And I think that's kind of a part of, we're supposed to be on the journey with him and I think it's part of why the story was told that way. Yeah, I.
+Darius: Wouldn't call it bad. It's just I would have went a different way about it. But no, I wasn't. Yeah, this wasn't a bad one.
+Jordan: I was going to actually ask you about that in one of the later segments. Yeah.
+Darius: Was this Johnny Depp's? Was this earlier? I mean, obviously it's earlier than now, but was he a certified ticket at this point? This is a big role.
+Jordan: Yeah.
+Darius: It's just him. You know, it's really just him.
+Jordan: It's just him.
+Darius: The whole movie, like, which is a lot of young actor.
+Jordan: Yeah. I mean, I'd say this is one of the first few, because I mean, this is after what's eating Gilbert grape. But this is like right a few years before Pirates of the Caribbean. Let me see.
+Darius: This is great radio.
+Jordan: Remember, he got his big break doing TV when he was in 21 Jump Street in like the late 80s, early 90s. Yeah, but he wasn't a movie star yet.
+Darius: So, they weren't going out all the way out on a limb wondering if he could carry good. He's I mean, he acted the **** out of this. He was very, very good.
+Jordan: He ******* bodied this. By the way, he's like one of the more, I feel to me at least he's one of my favorite actors and I feel like he's one of the more slept on actors too.
+Darius: But that's what happens when you go do stuff like pirates is people start not thinking you're an actor.
+Jordan: And even that, I don't think anyone else could have played, could have played, would even have thought to have played Jack Sparrow the way he played him.
+Darius: Leo says I never put on a suit because you can't take it back. Yeah, a superhero costume.
+Jordan: Right. Yeah. I was gonna say, yeah, so I also wanted to shout out Johnny Depp out as well. Like I think casting him, who was at the time period like a Hollywood heartthrob type as like a quirky, squeamish detective, I thought that was a really interesting turn. And for him to be able to pull that off is a testament to his acting ability. Also shout out Tim Burton because I love like the dark gothic tone of this movie. Like it's always cloudy. the set pieces are incredible. It really looks like an old village in the 1700s. it doesn't, it doesn't look like some set that they like just slapped a barn on.
+Darius: It doesn't look like they're in LA with a green screen.
+Jordan: Right.
+Darius: No, this was that. You could tell this was back when studios would actually like pay for mid level, like mid, mid budget movies. It's not a mid, but mid budget movies. Ready to get an act too?
+Jordan: Yeah.
+Darius: Act 2, we're gonna call the investigation. Crane's scientific methods clash with the town's belief in the supernatural as the horseman strikes repeatedly. He uncovers a conspiracy and must accept the ghostly reality to find the Hessian's grave and his missing head. I knew it was somebody they knew when the monster thing didn't kill Johnny Depp. He had him and he just like stabs the other guy's head and he looks at it and he rides off. I was like, all right, so this is Clearly an inside job at that point. So yeah.
+Jordan: Okay. Yes. I was going to ask you. So at what point did you realize there actually was a horseman and that it wasn't like Scooby-Doo where like a guy, it's a guy in a mask.
+Darius: The end. I didn't really. I thought it was. Yeah, I didn't like spoiler alert, but we started years old, but like he's being like mind controlled almost by. Yeah, by another lady. And so I didn't put that together. I just thought like I just took it for what it was like, this is just a monster, a headless horseman.
+Jordan: Yeah.
+Darius: That's just running around chopping people. And I was hoping and expecting the story to, you know, my thought was this was a hokey, this town is built on an ancient graveyard and he's looking for his grandma or like, that's how I, that's where I thought the headless horseman was going. I was wrong, obviously. But at that point, I knew That's where I thought it was going until that happened. And I was like, okay, I understand he's the main character. So maybe there's some, you know, plot armor there. But it was like, I just feel like this is an inside job now. It feels less supernatural now that they just, they felt very intentional that they left that spot. So what you got back to man?
+Jordan: Yeah, I forgot to answer your question from earlier where you asked me, is it the town? Was it supposed to be the town people were crazy or he was just a skeptic? I think town people were supposed to be like normal people.
+Darius: Yeah.
+Jordan: And he was just a skeptic. But I like that they showed why he was a skeptic because they kept doing the dream sequences where it was his mother and his mom practiced witchcraft. She was a good witch. And I don't know if that was his father or not, but someone saw her practicing witchcraft and killed her for it.
+Darius: The dream sequences being So modern threw me off. I was like, okay, is this like some of the village **** where they're not actually in 1799 and you walk to the highway and it's modern day. But yeah, I don't really, is there, did he ever give a reason for that direction there? Why were the dream sequences so much farther along in the timeline?
+Jordan: No, I never, I never even thought to look that up to be honest with you. I would imagine because it is It's obviously he had a traumatic childhood, but before she died, he had a good childhood. So I'm assuming that was him looking at his childhood with rose colored glasses, something like that.
+Darius: Yeah, because the dreams look like 1955, not 17. And I was like, okay, so maybe this is, so I'm trying to, this is the first view and I'm trying to really piece together what I can. And so that threw me off for a little bit. Also, houses were really small in 1799.
+Jordan: They really were.
+Darius: You know, as a society, we've gotten a lot.
+Jordan: We've come a long way from an architectural standpoint.
+Darius: I was listening to a podcast about basically it's like how things work and. Oh, yeah. Okay. First he was explaining, you know, how we get energy and how we get water and how that's like, you know, food and stuff like that. But he's like, people don't understand that the average person today lives better than like the kings back then. And the example he used was like Calvin Coolidge, president of the United States 100 and some years ago. His son went and played tennis and stubbed his toe, scabbed over, got an infection, died of sepsis. Holy ****. He was like, today you'd have just gotten some ibuprofen and some antibiotics and been fine. You get better health care today as a postal worker than the president of the United States got 100 years ago. Yeah. No, that's real ****. Yeah, I don't even know how we got there. But houses were really small back then is how we got there.
+Jordan: That's true. Did you see that viral tweet where it was like, imagine blowing your ACL in like 1850? Yeah.
+Darius: They probably see Bernard King's knee.
+Jordan: Yeah, I was gonna say that's what made me think of it too. Yeah, that **** was crazy. And he was the first guy to ever come back from ACL, which I did not realize. A legend in many folks.
+Darius: Well, he put the uniform on again. He never came back. True.
+Jordan: He was out there just getting cardio.
+Darius: Oh, man. Yeah, it's kind of wild that a torn ACL used to do that. But now it's just like, people look at it like you do a little six, seven month bid and you back. Which is not always the case, but it's often the case.
+Jordan: That is true. Agent Pearson kind of ****** the people's perceptions of how devastating that injury is.
+Darius: Get well soon, Juju Watson, get well soon, Kyra.
+Jordan: Yes. Oh yeah, I was gonna say, I really like, one thing I liked about this movie in terms of the storytelling was the callback to the Salem Wood.
+Darius: Yeah.
+Jordan: With, what happened to his mom and him being so skeptical of Katrina when he saw, when she had like a little spell book and all that. I thought that was really cool storytelling because it, was about 100 years from the time in the movie.
+Darius: Yeah.
+Jordan: But again, that's two generations. So that would have been his grandparents. He would have heard that story from his great grandparents. Like, don't be don't be doing witch **** because they'll kill you pretty much probably. So.
+Darius: There was just a lot less entertainment and things to do back then. So stories just stayed around. I, it's like.
+Jordan: That was TV back then.
+Darius: The quality of life and standards of living did not change much from 1799 to 1899. And so a book or a story or a wives tale, like they couldn't watch a Netflix movie. So it was like, just tell that story again. All right, what else you got, Frank, too?
+Jordan: Okay, so I know you mentioned where you realized that someone was controlling the Helless Horseman when he just stabbed the **** was he the notary? Not the notary, whatever position he held, the fat guy.
+Darius: That's one of my drives at this is that everyone else is just nameless and faceless, except for kind of.
+Jordan: That is true. This movie was very much like a Johnny Depp vehicle. Yeah.
+Darius: They were like NPCs in the everyone else. But so, I don't know who the hell he was because they were all the same people.
+Jordan: Yeah. I'd say the only other characters I really, really remember is Katrina and the little kid that helped him the whole time because he was just by his side the whole movie. I think that's all I have for act two. But I'll go to the actually wasn't actually for act three then. So If say you were a writer on this movie, what would you have changed in the script to make it more audience friendly or just in general, like what specifically would you have done creatively different from this movie?
+Darius: I would have written a B plot and used that as a way to world build for the viewer. And so I don't know what name, you know. So plot A is is the horrorless horseman, headless horseman cutting everybody's heads off. Yeah. You know, movie was an hour and 40, 45 minutes long. You know, maybe plot B gives. No, plot B is some crazy lady in the attic who, you know, I don't ******* know, but like, I would have written something plot B and given, it would have served 2 purposes. It would have given another character something to do to give the viewer something to contrast with Johnny Depp.
+Jordan: Yeah.
+Darius: And it also would have served as a way to world build for the viewer to just hold their hand. I don't want my hand held the whole time, but just there was very little world building in it. And I understand why they didn't. But yeah, that's oftentimes the B plot is to hold the viewer's hand a little bit. Like the A plot is it's what you're supposed to follow. And the B plot is like your vegetables that you sneak into the, like, you know how you got to give your dog its medicine. So you put it in the candy. Yeah. So like the B plot is usually some vegetables and that's how you sneak into to the viewer, you know. So that's what I would have done.
+Jordan: Okay. I mean, I think I'm trying to think.
+Darius: I think that's all I got for act three. We're going to call the reckoning. Crane identifies a person controlling the horseman's murders, leading to a climactic chase. He must defeat the villain and restore the ghost to his resting place to save the town. And Katrina kind of gave this away the earlier segment, but I would have found the movie a bit more compelling if they had more characters and the other characters had something to do. But like by the end, I didn't actually care who did it. Yes. It was like, I kind of like, even after it was explained to me who did it, I don't really, okay, all right. A lady that was there did it. was like, did they explain like, do you like, do you know why she did it?
+Jordan: Yeah, basically. So the, remember they went back to that cabin in the woods that Katrina, her father used to live in.
+Darius: Yeah.
+Jordan: And there was the archer on the fireplace, the symbol.
+Darius: Okay.
+Jordan: So you know, back then every family had a crest. So that was this evil stepmom, that was her family's crest. That was their home. And they basically got evicted so that they could give the home to Katrina and her father when they were younger and poorer. I think that's pretty much basically she had a resentment pretty much ever since then for them. And then she just happened to kind of grow up and be a witch and she was attractive. So she used that to basically kill, get into the, get in with the family, kill the wife, take over as a new stepmom. And then the will was rewritten Yeah, so the will was when the will was adjusted, everything would was going to go to Katrina's dad. But because of the channels that had to go through because of the baby with the widow from the other guy, she had to kill everybody off. She basically had to have a hit list to get everybody off so she could get the inheritance pretty much.
+Darius: Clear as mud. What else you got for actors? It's just so many characters, I can't even name their names to make the story make sense. Bit cumbersome, but we got there.
+Jordan: Yeah. If this is a regular movie, I promise guys, I would be able to name the names of the characters. No, I mean, look.
+Darius: These people know us by now. If they're new to us, they'll learn, you know, we don't, we're transparent here. If it's hard to follow, we're not going to. Pretend it wasn't. It's a good movie.
+Jordan: It's just. It's a fun movie.
+Darius: It's not a good first watch. Like you need to that first time.
+Jordan: This is not a.
+Darius: You said this when we review Memento. Let that first one wash over you. Yeah, don't try to just put your eyes on it, put your phone away, let it wash over you.
+Jordan: Yes, throw your phone outside.
+Darius: The second one is the real one.
+Jordan: Correct. This is what I'd call, this is not a tweet or text movie.
+Darius: No, not a second screen movie.
+Jordan: No, not at all. I will say to me, one of the hallmarks of a really good horror film is like the big like crowd scene, like where there's like the big angry mob or like the town hall meeting or whatever. So the church scene is always one of my favorites whenever I watch this movie, because you kind of see like, okay, because we have all these characters and they never really interact with each other because everything's in secret. So there are always all these back channels and backroom conversations. And then when you see everybody get together, you're like, oh, Okay, this is the dynamic. This is the hierarchy. And then you kind of realize we thought Baltus was the bad guy, but he actually was getting played by his friends the whole time. And then **** just goes haywire.
+Darius: I like it. I like it. Would you have preferred a supernatural or real? A supernatural or an explanation grounded in normal physics and reality? I don't, you know, I don't want to besmirch people who are into supernatural things. So supernatural or grounded in the physics that we're aware of.
+Jordan: Okay. I think for, because I view it as a Halloween movie. So for a Halloween movie, I prefer it with a supernatural, but I think it could have been a really cool, excuse me, like plot twist or storyline and character development if they were to show like this person hired this person to just kill people or they had something on this person and they just had to make them kill people to cover up whatever crazy secret would drive you to kill people to keep from being revealed, something like that. I think that could have been really cool. I think one thing I also probably would have done as a screenwriter on this movie, one tweak I would have made was I would have opened the movie with the murder scene just like they did because it builds intrigue and it was interesting and It was a different tone for that kind of movie. And then I would have done like, okay, a month earlier or something like that. And I would have shown like a day in the life of the town where **** was all good.
+Darius: Yeah.
+Jordan: And then I'd cut to New York with Ichabod.
+Darius: To answer your question earlier, I would have used, I would have tied in the Salem stuff, using a B plot is like, you know, some lady is accused of being a witch. And in her defending herself not being a witch, she does a little world building. And so off the top of my head, I know that sounds clumsy, but obviously if I had the time to screenwrite it, I could polish it and make it full. But that's kind of, off the top of my head, I would have done that and used that as a way to, in the movie we reviewed last week, like Nick and Nora, Like I didn't even like that B plot, but you can see the world building within it where she's just like they're in chasing her. They're talking to each other.
+Jordan: Correct.
+Darius: And they're explaining, oh, this is how I know that band is da da da da da. This is how I know that he's plays bass. This, you know, like just there's ways you can do it. There's tricks you can do as a writer, you know, to sneak the vegetables in. So.
+Jordan: Yeah. I'm with you. I think I like your point about having like a random character, a random citizen in the town be like a B plot character.
+Darius: Yeah.
+Jordan: Cause that, cause they would be closely, they're closely, more closely relatable to us as a viewer who is not a part of this world. And, you know, before the Horseman was revived or whatever, the town would have been normal. So a normal human would be like, what the **** is going on? people would be moving out or fleeing or you know stuff like that.
+Darius: Because as it stands it's like this Johnny Depp showed up in the world created like it's not like you know it's all like it's all it almost felt like no one talked to each other off screen they're just all there to interact with Johnny Depp and you know it's nothing's perfect it's a it was a good movie but that you know we're here to critique and that's my critique so okay for sure you got factory.
+Jordan: I so I will say like I go back and forth on this with this movie because the fact that we hardly ever see the wife makes makes the twist that much more interesting when it's revealed that it's her. And then when you go back and watch, you try to look for any tales like in her performance or, you know, and she shout out to the actress, Miranda Richardson. She did she like doesn't really give anything away during she just seems like very like just like a sweet housewife, you know, and she's like a murderess. But I kind of wish we could have seen more of her. She would have had more scenes just to like have more familiarity with her to even to increase the shock even more.
+Darius: Well, that's to me, that's like a novice's idea of a good plot twist. A good plot twist, it's cheap. A good plot twist upon second viewing is obvious to the viewer. But it's like, it's shocking the first viewing, but upon the second viewing, you can see the seeds being laid. If there's no seeds laid, it feels like you just picked a random person and said they did it, and you just flip it. Right, It's just like, good writing and a good plot twist is almost like a double-sided belt. Like, you know, it's a shocker. And also the crumbs were there. It was in your, the shock was in your face. It's like The Sixth Sense. When you rewatch it, you could see that no one's talking to him. But you'll notice that the first watch. It's just that that's a good shock to a plot twist. And then at night, Shallahem didn't get another one. But you know, ever again, one hit wonder with 12 shots at it. But yeah, I mean, yeah, that's a good point.
+Jordan: Yeah.
+Darius: If you rewatch it and it's still not there and it's still crumbs, then it just feels like you picked a random person that said they did it, you know?
+Jordan: Right. Like I even like so remember the their servant girl was like hooking up with one of the older guys that was in the plot in the conspiracy. I think like it would have been cool to have show more of her relationship with the wife because they probably would have been more closely together because you got the housewife with the servant. I'm sure they were cool. They both in the house all day, you know, whatever. And then like that would have made like her killing her more shocking and more ruthless. And, you know, it would have been like, okay, that's how she was able to know about the affair she was having with old dude and you know, how she was like, it never really They never really showed just how she came to know everything about everybody in this town.
+Darius: Yeah, that's the other thing too, like none of these murders landed with me because I didn't care about any of these characters. Right. It's just like random kids getting chopped off.
+Jordan: Yeah, it was just like, oh man, that's sad, but all right, who did it?
+Darius: I know I'm supposed to feel something, but I don't, you know, so.
+Jordan: The only one that really hurt was when the one with the little kid hiding in the basement.
+Darius: Yeah, that one was tough. When she snatched them off the ground, that one was rough.
+Jordan: Yeah.
+Darius: Are you ready to rate it or you got anything else?
+Jordan: Yeah, it's more of a general question, I guess, about movies. So we always talk about a lot about like what we change in terms of like writing the movie. But I want to ask you from a creative aspect, would you rather be the writer of the movie or would you rather be the director?
+Darius: I'd rather write. Yeah, I'd rather write directing is I mean, it's different. No **** but yeah. Directing is more of a technical job than a creative job. And if I'm going to be in the movie industry, I'd rather be on the creative side of things. They're both needed, but like, you know, they're both kind of, you know, writing is a technical job too. But if it's, you know, writing is 80% creative, 20% technical and I would say directing is like a 6040 split, 60% technical, 40% creative. And, you know, I'd just</t>
+  </si>
+  <si>
+    <t>Darius: I feel I did like the date that it did have him lose and I also one thing I will say I forgot to mention is like I liked that this movie had them just like being arrogant greedy materialistic ********. Instead of like misunderstood people who had a tough situation, they have hearts of gold. You know? Yeah. They ain't all Robin Hood, you know.
+Jordan: Yeah. One scene where you buy turkeys and I'm supposed to believe these guys are, you know, there for the community.
+Darius: Hey everybody, happy New Year and welcome to the Out the Trunk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Jordan: And I'm Darius, that's these, I love you, Ariel on all socials.
+Darius: And today we're going to be reviewing the cinematic classic, State Property. This movie came out in 2002, starring Beanie Siegel, Emilio Sparks, Memphis Bleak, Dame Dash, Sundy Carter, and Jay-Z. This movie is about, takes place in the gritty streets of Philadelphia. Gritty streets, the mean streets. The Broad Street bully.
+Jordan: This is classic American cinema. I will never, ever, ever disrespect. The Beans, the ABM, sorry.
+Darius: The ABM, yeah. A frustrated hustler named Beans decides to bypass a slow grind for quick riches, forming his own loyal crew. He ruthlessly seizes control of the local drug trade. However, his rapid rise to power invites dangerous robberies and unavoidable consequences from the local law. So I'm going toss to you for Act 1.
+Jordan: Act 1, we're going to call the takeover. great hope song. Beans grows tired of being broke and organized his friends into the ABM crew. Ain't all about that money. They begin a violent campaign to take over North Philly's drug blocks, disrupting the established order. I love that it said inspired by true events. So that just could be a lie now. Like I don't.
+Darius: Yeah. Cause who is this based on?
+Jordan: Well, it was a generic drug dealer movie enough. It couldn't be based on anybody.
+Darius: Right. Anybody who did drugs ever sold drugs ever.
+Jordan: The movie starts. My favorite, like, well, my favorite. There's a lot of about this movie, but it starts with like, they're just in the strip club, middle of the day. He's like, hey, man, want to sell drugs? Like, hey, we can do that. All right, bet. And then the next scene, they're drug dealers.
+Darius: Yeah. Like, okay, where'd you get the drugs from? Who'd you get the drugs from?
+Jordan: Not it.
+Darius: What's your plan?
+Jordan: They're in the strip club, broke, smoking cigarettes. And he's just like, man, let's get some money. Like, all right, man, we can do that. We go get our crew together. Okay, cool. And then the next scene, they're big dogs.
+Darius: And then they have money. And then they have money.
+Jordan: You gotta love it, man. Off the bat, was this the OG Tooby movie?
+Darius: I think so. I really think so. I think paid in full came before this. So I'd probably say paid in full.
+Jordan: Paid in full. Or felt like a theatrical release. All right.
+Darius: Oh, that's true. That's true. Yeah.
+Jordan: This was straight.
+Darius: Yeah.
+Jordan: This ain't hit nobody's. This was at the rear.
+Darius: Yeah, you're right. This was straight to DVD. And I'm pretty sure this was recorded on a self on a self flip phone.
+Jordan: I got a 1080p version and that **** looked like 480i, a DVD with scratches. It looks terrible.
+Darius: This movie looks like, I remember my dad would bring home the bootlace from the barbershop, you know. And we had a raw cut of X-Men Origins Wolverine, like without the special effects. And it's just before all the green screen and **** is in there. And he's just like, It'll say like, claws grow. Like Memphis Bleak. That's what this movie looks like.
+Jordan: One of the few opening scenes, Memphis Bleak walks to the club and he's just some guy sitting there and Memphis be like, what's up, man? And the dude stands up, he's like, do what you do, *****.
+Darius: Yeah, But that's my favorite part of the movie is everybody gets shot, but there's no blood at first. They just fall down and then you see they're covered in blood in the next shot.
+Jordan: I cannot stress enough how this was like ******* Scarface to us, to me and my friends, man. We watched this **** over and over and over again. What you got for act boy, man?
+Darius: As I say, this movie is like, it reminds me a lot of Goodfellas. If you take away like the writing, cinematography, if you're if you remove acting, you know.
+Jordan: Everything. If you removed all the good parts, what you have left is black and good fellas.
+Darius: What you have left is state property.
+Jordan: Man, he's like, they pull up on Memphis Bleak in the next scene. He's just walking around. He's like, hey, please. He turns around to shoots him. And just shoots him.
+Darius: By the way, why are they doing everything in broad daylight? Why does everything's going to be happening in broad daylight?
+Jordan: The police don't show up until it's time to be arrested. Like there's just like murders, guns, everyone's just shooting people in the club. Memphis bleak.
+Darius: Everyone has horrible aim.
+Jordan: It just like leaves the club and I guess it's just walking in an alley.
+Darius: Right. I love it.
+Jordan: What you got for act one?
+Darius: Yeah. Yeah. So I want to talk about like, so I can't remember what it was. I mean, you probably more well versed by this than I am, but what was it that happened to Bean's voice? He got, he got like sick or something. I believe it was his voice to change.
+Jordan: I believe it was some form of cancer, I believe.
+Darius: Yeah, I couldn't remember what it was.
+Jordan: What happened to Betty Siegel's voice? This is great radio to Bean.
+Darius: Because I remember like he Remember he was on Breakfast Club a few years back and his voice was like completely different. I know he's actually recording a new album now and they're going to be able to use the AI voice filter. So he's still writing his raps, but it will actually be his old voice, which is actually kind of cool.
+Jordan: Ironically, voice suffered severe damage after he was shot in 2014, affecting his vocal cords ability to rap as he once did.
+Darius: Okay, that's what it was. Okay.
+Jordan: No, he did.
+Darius: I heard stories about, he did live and do all that ****. So, yes, I was, it was, people talked about it, but you kind of, when you hear his music, it doesn't feel as drastic as when you watch a movie and hear his speaking voice, the change in his voice. So I thought that was kind of interesting. Yeah, the strip club shooting idea. I put that in my nose. Yeah. So I don't know about you. I've never shot anybody, but I know if someone walks up to me and says and says, do what you want to do. I'm going to assume their way to shoot me. So I'm not going to just stand up in front of them and give them an open target. That's just me.
+Jordan: Well, shoddy acting and cinematography aside for dudes like this.
+Darius: Like he thought he was just going to square off.
+Jordan: It reminds me of that scene. The opening scene admitted to society or the second scene admitted to society, the flashback where Kane, his dad kills the guy and the guy's drinking a beer and he's like, I'll tell you, I'll pay you money when I pay you, better **** ** ****. And people are like, was he not nervous? And I was like, that dude has probably had a gun pulled on him 30 times in his life. Like it's not atypical. Cause like people are like, it's unrealistic. The gun was in his face and he's drinking beer and he just, That wasn't unusual. The previous 29 times someone pulled a gun on him, they probably didn't shoot him. And he probably thought he was bluffing. Yeah, that's true. If I'm going to give this movie the veneer of credibility, that would be my answer. Is that they're just really, really used to having guns pulled on them. Because you see in the scene where they pull up on Blizz, and Blizz turns around and shoots the car, they're just like, hey man, chill out. If I, if I start walking on the road and you turn around and shoot at me, I'm not going to be.
+Darius: Like, Hey man, chill out. I'm going to run you over. You're like, hey man.
+Jordan: What is going on in your life where that, where you're just up and shooting because someone called your name?
+Darius: Yeah, that was kind of crazy. Although to be fair, if you're walking on the street and someone just rolls up on you and screams out the window, you're in that environment, I probably would assume it was about to go left.
+Jordan: I would not turn around and open fire. I mean, I'm probably clutching.
+Darius: I'm probably clutching.
+Jordan: Yeah, you know, you are acutely aware of your surroundings, but.
+Darius: Yeah.
+Jordan: Even, I mean, that was a gross overreaction. But even, what was even more absurd was how nonchalant they were about it. Like, hey, man, chill the **** out.
+Darius: Like, hey, man, it's us.
+Jordan: Like you threw a football at them. Like, you know, like.
+Darius: Yeah, They acted like it's like, you know, you tap somebody's shoulder and they looked through all the.
+Jordan: You know, it's me, man. Stop all that ********. ****. It's like, all right, man. Okay.
+Darius: Yeah, they have, they was playing Ding Dong Ditch. That was crazy. Yeah.
+Jordan: Minor inconvenience, like being shot at.
+Darius: Yeah. I wouldn't say like, I mean, the fun thing about this movie is like just watching all the mistakes and just like the flaws in strategy and stuff like that. Like the, They're like, okay, we're going to be drug dealers. We're going to get rich. All right. And then they go to the guy who, I guess, is the big drug dealer. And they're like, and then they just kill him in the alley. Yeah, they just shoot him in the alley. Beat him in the alley.
+Jordan: You slow stopping my business. It's my business. It's going to stay mine to the day I leave it, ************.
+Darius: When you leave it.
+Jordan: He said, come outside and dress me like a man. Yeah, he beat him with the bat. That was actually. for for the quality of of uh production in this movie the bloody head actually didn't look too bad actually it.
+Darius: Looked real it looked real.
+Jordan: Yeah it did it did oh I don't know I think that was the whole budget.
+Darius: Uh yeah that was it that and um maybe like Jay's chain in that one scene.
+Jordan: Yeah well I think ho brought his own uh uh oh yeah that's true that's true costume uh broom so what else you got for act one um.
+Darius: Yeah. Even now, the one thing that did actually remind me of Goodfellas was when the weed guy was like, **** you, man. Yeah, he's like, what you say, you roll up, you say? Well, hey, you roll up. And then he shot him in the hand. He remember when Tommy's character played by Joe Pesci shot Spider in the foot.
+Jordan: Yeah.
+Darius: He's like, we wouldn't say I'm a good shot.
+Jordan: It goes back to what I was saying earlier, man. This is just how these people settle disputes. They don't.
+Darius: Right.
+Jordan: They don't. This is just how disagreements are resolved. Right. You said, **** me, therefore I'm going to blast your hand off.
+Darius: Yeah.
+Jordan: And like, Blizz is in the back just high giggling. Baby boy is just like. Don't kill the Like, you know, he's not. Did they like throw some ice on that **** man? Don't bleed on the sofa. Like this is the level of violence that these people are used to. Is it?
+Darius: Yeah.
+Jordan: Psychologists have said it borders on like being in a war zone. So yeah. It's a stupid movie with not great writing, but some people live like this, believe it or not. Yeah, that's true. Yeah. He's like, why do you need a gun at a at a kickback at your daughter's birthday party?
+Darius: Right.
+Jordan: And none of these guys like, I mean, they didn't announce it in the movie. They're not registered.
+Darius: No.
+Jordan: And that was like his his girl's little brother. And he's just like, bullying him costly. Oh, that's right.
+Darius: It was a brother. I forgot about that.
+Jordan: Yeah. Want to get an act too? Act 2, the cost of the crown, the ABM, all about that money crew. Because my favorite part is like they just have it on their license plates. Like just this is a crime car police. ABM crew expands their territory, leading to a bloody turf war with rival kingpins. While money rolls in, internal friction develops and police intensify their investigation into Bean's operation. Some of my favorite lines. in the movie, we're in this act, we got put your 3D glasses on ***** because we coming straight at you.
+Darius: Yeah, I did like that line.
+Jordan: We also got when we found out that Blizz was a snake and then they set him up and then he's talking to baby boy when they're buying the jewelry. He's like, I see through window tint. And like.
+Darius: So I actually watching that scene, I actually thought that the jeweler was going to be like a fed or like undercover or something like that, because I was like, and I thought that was going to be their downfall. Yeah, that I thought that was going to be their downfall.
+Jordan: This movie borrowed from a lot.
+Darius: It did.
+Jordan: So in this act, he runs into he kills the no name drug dealer where they pull up on him on the street and the guy takes off running and Liz Memphis Bleak's character just shotguns him. Then he runs into it with butter. And butter is like the first big time dope dealer he deals with.
+Darius: Yeah.
+Jordan: And the hit on butter was one of the dumbest things I've ever seen in my life. They walk into a basketball court, they stand still, just like they just start shooting. No movement, no cover.
+Darius: Just they don't duck like they don't want sideways or anything. They just are like. Boom, boom, boom, boom, boom. It's a 10 step, like it's a 10 step duel.
+Jordan: Yeah, like it's literally like I challenge you to a duel. And of course, none of their guys get hit. Of course, all the other guys get hit because it's a movie. And it's like a video game. The bad guys don't, you know, get hit.
+Darius: Bad guys don't have aim.
+Jordan: And then Memphis Bleak walks up and I wanted those forces so bad. He had some black and white, black and red, low top forces. And he shoots and he's like, butter, baby. And then he flips the coin, flips the coin, and he walks into the car. All of this is a broad daylight. No police. No one's, they've been shooting for half an hour. No one calls the police.
+Darius: Yeah, like just, okay. And then also like, you need to tell me, you need to tell me a big time drug dealer was at a basketball game out in the open and only four people there have guns with him.
+Jordan: Gotta love a good hood movie, man. He flipped the coin.
+Darius: The coin flips.
+Jordan: And he's like, only so long fake thugs can pretend. And then he gets in his car. He's like, man, this is cinema, man. This is great. What you got for act 2?
+Darius: I love that they just gloss with the fact that Bean's character is like on top of this drug kingpin. and it's running all these people and all this, big enterprise and has no idea how to talk to people. Yeah. Like, he's just cussing everybody out. He's going off people for no reason. Like they go to Miami to get the drugs from the. That was whatever.
+Jordan: I have it in my.
+Darius: Oh, that was Mexico.
+Jordan: They flew to Mexico with guns and flew back with drugs and how?
+Darius: Yeah, right. They don't have passports and they don't have driver's licenses. Let's be honest here.
+Jordan: Guns was probably shaved cereals, bags of cash.
+Darius: Right.
+Jordan: You know, just head to Cancun. And this is post 9-11, so none of those just like.
+Darius: Right, correct.
+Jordan: You had to go through TSA. Correct. So, you know.
+Darius: You're getting fully searched.
+Jordan: They're in Mexico and they're like, we've here. Stop that guala guala ****.
+Darius: Yeah.
+Jordan: He called Spanish guala guala.
+Darius: I was like, what does that even mean? The writing is so bad in this movie. It's hilarious. Like if you, if you put, if you put like a soundtrack to this movie, like a, like the comedy soundtrack or like a laugh track, this could be like one of the funniest movies ever.
+Jordan: He said, it gets there and he's like, you want to get a drink? He's like, nah, Papi, we know drinky.
+Darius: Yeah. No, Papi, just bring me the drugs, man.
+Jordan: Oh my God. And he's just like, hey, man, talk English. I don't want to hear that guacal ****.
+Darius: Yeah, right. And then of course, every like big time drug dealers movie has like 2 ***** ***** making out.
+Jordan: Next to him. I mean, that doesn't strike me as odd.
+Darius: No, I don't think that's odd.
+Jordan: It's just funny. Yeah. Butter with the young nameless, faceless white lady.
+Darius: Yeah, right. And name with the two girls.
+Jordan: Who was the dude that? So Blizz comes up to him and he's like, we hear that you want parts or whatever. And then Blizz ***** his girl and they ended up. That's how Beanie got. You smoke them both. Got them both. Which, by the way, I thought it was immoral to use the police. I don't know how that worked out.
+Darius: Yeah, that's a good point.
+Jordan: Nonetheless, though.
+Darius: It was a great play, though. I would have done the same thing.
+Jordan: The empire rises and falls. So which else you got, Frank, too?
+Darius: Yeah, the thing that was stupid to me that one of the big mistakes he made was like, well, several things he made. He did a lot of stupid ****. This whole movie is him just doing stupid **** basically. That's the plot. Is where when he gives the guys the rings and he gives them the speech about, oh, we family and then whatever, and then he brings the girls for the OGs, he just lets the young guys just stand there and watch them like, you got to break everybody off. That's where, that's what breeds resentment.
+Jordan: But he, but the thing is he was, he was giving them something to look forward to. True. Their outer circle. This is the inner circle. And he said, you know, once you put this ring on this **** is for life. That mean there ain't no getting out. And if anybody want to get out, get the **** ** out my ****. And so that was like, That was given to youngins like, okay, you keep putting in work, you'll get your ABM ring and your high price escort. I don't know if they're high price, but your escort.
+Darius: Yeah, you're going to get your $100. Yeah.
+Jordan: Oh man, something was bad though.
+Darius: No, they were fine.
+Jordan: Yeah, I mean.
+Darius: Also, it was great to see women who look like real women in movie. Like they didn't like filters and fake teeth and all that stuff.
+Jordan: That was 2002, baby. You go watch music videos back there. Like that Tip Drill music video?
+Darius: Yeah.
+Jordan: All the women look normal.
+Darius: Yes.
+Jordan: They don't all look, they don't all, they're not all ideified.
+Darius: Yeah.
+Jordan: And I don't know about you, man, but when I was growing up, Tip Drill was basically ****. Like I don't know.
+Darius: Yeah. We, I took a, An African American like film and culture class, whatever. And we watched like the unedited version of the music video in class. That **** was crazy.
+Jordan: Sounds like some HBU ****. What did you come back to? Here's how twerking is the resistance.
+Darius: That was literally just about like the objectification of women or whatever.
+Jordan: I know it was because that sounds like some HBCU ****.
+Darius: I was about to say, yeah. So I did like that. There's a scene where they're trying to get do business with their buyout. The one guy who did the car detailing **** I can't remember his name. And both big, both businesses were trying to, you know, recruit him basically. And he was like, I don't know, man. I need some time to figure it out. And before he got killed I was thinking to myself like you reminded me of Walter Walter Frey from Game of Thrones where they called me late Walter Frey where he's like I'm just gonna weighted everything out and see who kills who and I'm gonna choose their size so that way I'm not ****** and I think that's what he was trying to do but it didn't work because you know Beans is an idiot so or in the movie his character so if I was him I think I would have been like yeah I'm rolling with you I'd have told them both the same thing I'd have been like yeah I'm rolling with you **** them and I'd have given the information on each other and let them wipe themselves out and then I would have won
+Jordan: I don't think that young man was cut out for that role. He looked a little jittery and I don't know if he was capable of playing Beans and was it Dolla?
+Darius: Yeah, that's it, yeah.
+Jordan: Out of their, out of each other. So you want to get to act three?
+Darius: Yeah.
+Jordan: Act 3, the crumbling empire, the fall of man. Betrayal surface within the inner circle as the pressure of the law mounts. Beans must face the reality of his choices when his empire begins to crumble under extreme external pressure. And let me just say, you have to admit, Beatty Single is a good actor.
+Darius: He's decent. He's better than I thought he was going to be. He's decent. I think he just, I think he just talked a little too slow for some of those monologues. Like the pauses were too much. He was decent. He was decent.
+Jordan: He's a good actor. He carried this movie. He's the only thing interesting in this whole movie. That is true. And he's in damn near every scene. I thought, you know.
+Darius: And he had to remember, he had to know all his lines, you know? Yeah.
+Jordan: He was the only one who didn't read, sound like they were reading off a script. Memphis Bleed can't act for ****. Baby, sorry, Emilio Sparks can't act for ****.
+Darius: Dame couldn't act for ****.
+Jordan: Jay-Z, God bless him.
+Darius: He might have been the worst. First of all, I didn't know what he was saying half his scenes. I'm not gonna hold you. I was like, what?
+Jordan: It's bad filmmaking, but he was talking like in code on the phones. But it was stupid.
+Darius: Yeah.
+Jordan: And yeah, I'm glad he I'm glad he knew his lane. Cause he's like in the car and he's like, kidnap his *****.
+Darius: Yeah, I thought he was joking. I didn't know he was serious.
+Jordan: Nah, man, this is real St. ****. It never made any sense to me that Dame would, okay, so you, ruthless rivals. You kidnap his woman. You murder her friend in front of him. But you hold up the deal as far as like exchanging her for in charge of the like the doesn't.
+Darius: The for the money.
+Jordan: It just seemed strange that maybe there is some honor amongst even the worst of all thieves So yeah, what else you got for act three man?
+Darius: Yeah, I thought that was interesting too. I also didn't like It could have went left with him killing the best friend while they're on the phone because it because if he killed the best friend they're on the phone and beans thought you had killed his girl You weren't getting the money and he would have smoked you. So, like, that was that was a big risk. I thought that was kind of stupid. And then I was going to say, yeah. So how did how did you feel about, like, the whole snitching thing with him and the lawyers arguing when he was when he got locked up?
+Jordan: I mean, these dudes don't snitch, so that was never an option.
+Darius: Yeah.
+Jordan: In the 5 million. I mean, what's your question? Like, what do you mean by how do I feel? Like, what do you disagree with?
+Darius: So I actually think, I personally think snitching happens more often than people think or want to admit. Like, I think most people actually do snitch. I think more people snitch than people who don't snitch, honestly.
+Jordan: That's how cases are built.
+Darius: Right.
+Jordan: But in the interest of the character of the movie, he just wasn't going to do it. Like he'd rather spend the rest of his life in jail, not even on his worst enemy. And so He offered him 5 M's and he thought it would work. My question is, so that's D-Nice and baby boy. What was your plan when the shootout works?
+Darius: What was your plan?
+Jordan: Like, cause you still. You thought you were just gonna go home.
+Darius: Yeah, like, cause let's say you do win and you kill everybody and you get out of the courthouse. Where the **** do you go? Like, what are you doing? You just kill cops and judges and lawyers and security guards.
+Jordan: You just thought you were just going to take like.
+Darius: Yeah, just it was going to be cool.
+Jordan: What was what did success look like? You know.
+Darius: That's that's what that's what I wanted to know. And honestly, when I watched it, I thought Beans was in on. I thought he knew what was going to happen. I thought the 5 million was the bait to get dude to come to court. So I. Yeah.
+Jordan: Yeah.
+Darius: I'm like, Yeah, dude, so you kill the cops. Okay, cool. What? You're going to be able to run for the rest of your life. You don't have passports. Did you have enough cash for people to live off of? Like, what was your plan?
+Jordan: Yeah, it's a they had nothing.
+Darius: Yeah.
+Jordan: My favorite part is that so the audience knows Betty Siegel gets killed by Amir, who's I don't know. Does she still make music? I doubt it. But if you ever listen to Jay-Z's Can I Get Us? She's the girl on that track. But anyway, she kills Betty Siegel in the courtroom. My best part, this not is in this movie. There's a state property too, believe it or not.
+Darius: Yeah, I saw that.
+Jordan: And it starts with Beans recapping what happens in the courtroom, getting killed. And he's like, man, that **** ain't happened. And they just reverse it. And that's the start of the movie. The second movie literally starts with Beans like.
+Darius: That's funny.
+Jordan: Recapping and he's like, then I got laid out in the courtroom. No, that **** ain't happened. And he like does a literal rewind. And he redoes the scene without him dying. And somehow he gets it's really if you thought this was bad. State property too is unwatchable. Like it's so bad. Anyways, so when I should refract?
+Darius: Yeah, nothing else that was stupid. Talking to him, talking to his boys on the prison phones and just being very explicit about everything that he wanted to happen.
+Jordan: Yeah. Again, the movie only works if like the police are just like on vacation. The entire police department.
+Darius: They just are all in comas.
+Jordan: Because the movie covers the span of about 18 months. It's not long.
+Darius: Right.
+Jordan: And yeah, he's just. He's putting bribes in motion. He's calling denies like, you need to kill this person. You know, this person got indicted. Yeah, it does not hold up to any logical scrutiny.
+Darius: Nothing.
+Jordan: You have to you have to watch this understanding at the time. You know, this was pre-internet. Well, I don't know if 2002 was pre-internet, but pre the ubiquitous nature of the Internet. And people weren't you could just drop a movie with plot holes if people just accepted them for plot hole. Like they didn't care. We didn't have an endless stream of things to do. So if a movie had a plot hole, we just worked around it. Anything else for Act 3?
+Darius: I'm trying to think. I mean, really, Act 3 is really just the. Kidnapping, snitching, and the court shootout, court shootout.
+Jordan: Damon Hove won, you know? So.
+Darius: Oh, yeah, that's right. Damon Hove won at the end.
+Jordan: In the second movie, Dame is.
+Darius: Unlike real life.
+Jordan: In the second movie, there's no Hove. By then, I think they fell out and Dame.
+Darius: I must say, I think they.
+Jordan: The new. It's really stupid.
+Darius: Yeah. You know what it did? This movie did make me think, though, like the one scene where James in the car butching the Hove and he's like, well, you should go handle that. You should like, you should fix that. I feel like that's how all the conversation went in real life. Like I feel like it was Dan complaining and Jay just been like, you should fix that.
+Jordan: Oh man, there was a scene, I forget the podcast, but they like recorded a barbershop and Hove in 2015, maybe he did a B-sides concert. And on that B-side concert, he had a lot, like he had like Beanie Siegel and Young Chris and the young guns and a lot of people just came out because that was, that was back from the state property days when he used to hang with these and they go to the, they're talking about it in this podcast some years later. And they're like, dude, you would like, after the, after the concert, Hove was like, where y'all at? You know, I'm at the studio right now. I need, you know, y'all want to hop on this track. This is ******* Jay-Z.
+Darius: I remember this. I thought 2002 Beyond.
+Jordan: This ain't, this is 2015. Owner of title billionaire beyoncé husband Jay-Z. And he calls you up a dusty St. rapper from 20 years ago. He ain't heard from him. And he's like, come, lay 16 bar. And they like, man, we hit a party instead.
+Darius: Oh, yeah, I saw that. I remember seeing that interview.
+Jordan: And then the dude hosted the podcast was beside himself. He's like, Hove asked you for a verse. and you hit the club instead. You could have went to the studio and put a track down with ******* Jay-Z and you went to the club instead.
+Darius: A song that you'd be able to eat for the rest of your life.
+Jordan: And that's why someone was like, that's why Jay-Z don't be around these no more. They not serious people.
+Darius: No, that's real ****. They're not. And honestly, it's like that in a lot of with a lot of like rappers and ****. Like I remember there's an interview where Cam was talking about like dips, the dipset days and he's like, yo, dwells was just as good of rapperizing. He's just as talented as I am, maybe more so. And he's like, we would have to bribe him to get him to come to the studio. We'd have to like pay him to come to the studio because he was so obsessed with just like girls and just like **** ****. And he'd be like, yo, we can, you can rap and then **** girls afterwards. Like, you don't have to like, you know, some dudes really just don't want it that bad. They don't love it. They don't love the sport.
+Jordan: They just don't. They're just unserious people.
+Darius: Yeah, like Ben Simmons. You don't love the game.</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Steve's I love you area on all socials.
+Jordan: And today we're going to be reviewing Still Alice. The movie came out in 2014 starring Julianne Moore, Kristen Stewart, Yes from Twilight, Alec Baldwin from Everything, Kate Bosworth and Hunter Parrish. This movie is about a lady named Alice Howland, who is a renowned linguistics professor at Columbia University, who seems to have it all. However, her life takes a devastating turn when she is diagnosed with early onset Alzheimer's disease as a Brazilian, Brazilian, wow. As the brilliant academic begins to lose her grip on her memories and her language, she and her family face an agonizing test of love, identity, and resilience. So it's also to you for Act 1.
+Darius: Act 1, the slipping words. Alice is at the top of her professional game. when she begins to uncharacteristically forget words during a lecture and gets disoriented while out for a routine jog on her own campus. A subsequent trip to a neurologist delivers a shocking diagnosis, early onset Alzheimer's. And let me just say, I didn't want to interrupt you at the beginning, but you'd be hard pressed to find a more perfectly casted movie.
+Jordan: No, yeah, really.
+Darius: And everyone fit into their roles perfectly. And I just, I felt like I was a fly on the wall for some family drama. And yeah, it's just like I everyone was like perfect for their role and it was perfectly casted. And I did. Well, I'll just go for you for your first one because mine is a little later in the act. So what you got for your first observation?
+Jordan: First observation, man, Julianne Moore, like literally like the performance of a lifetime and a career in this movie, like she was so brilliant. The way you can not only just like the character you see the deterioration of her, state of being, but it's almost like her face looks different throughout the course of the movie. Like she looks like she like aged throughout the course of, the whole ordeal. she was mindful while also being absent-minded at the same time because of the, condition she's portraying, it wasn't like she was, playing some drunk who blacked out, you know what I mean? It could have been very camp or very tasteful if done improperly. And she did the complete opposite. Like her performance was incredible in this movie.
+Darius: Yeah, she performed it in a way that made you feel like you were watching
+Jordan: your mom or something.
+Darius: Not even like your mom, just like you were watching some like lifetime show about times in an old people home, you know, and it was Um, you know, there's just little things where and like the way the family, that's why I said the family casting was so perfect because in the beginning they just caught it, but didn't like, you know, your parents get a little older or whatever. And like, right, he, you know, she, she's setting out a charcuterie board in the beginning and like, uh, I think her son's girlfriend or whatever says, hi, and then when she comes out and hands it to the table, She like repeats a question that she had already asked her. And even the girlfriend just kind of did what anyone would do. They go, yeah, it just answered it again. And it's just there are so many moments where this movie could have become cartoonish and they just never gave it to that. Yeah, that desire. What I liked about it When she visits UCLA for her lecture, she's talking to her youngest daughter who, you get three kids, there's always one like wayward one. And she's got one kid who's in law school, one kid who's in med school, and one like basically a struggling actor. And she does what any linguist married to, you know, a Harvard researcher would do. She wants her child to go to college. And her child is just like, stop trying to make me Me, you. or just like everyone else in the family. Right. The movie does a good job because that character, Kirsten Stewart's character, is the one who ended up accepting their mom for where she was. She was the only one who was trying to fix her mom. And she could have been petty about it, you know? Yeah. It's just, you know, revealing my true feelings about the movie, but it's just a really, really great way to It's just a smart movie, for lack of a better word. It's just a really, really smart movie. And so I just thought that was really good. What else you got for act one?
+Jordan: That's funny, I put the same thing. I had that for act 3, but I thought it was interesting that the quote unquote most disappointing child was the one who saw her, who had the most clear vision of her. She's the one that saw her the best, you know. Like you kind of brought it up earlier, the way they show the slow decline in her, you know, cognitive abilities was incredible, like just the, you didn't tell me that we had dinner plans tonight or, even the bit with the girlfriend. Like I watched the movie twice and I missed that. Like it was so subtle. I missed it, and it just kind of shows like we all forget things. So it's easy to pass it off as, oh, she's just forgetful or, oh, she probably has a lot going on. You know, she's a busy professor. She's got, you know, students and office hours and all this stuff to keep track of. She's writing books. She's giving speeches. Who could juggle it all, who could possibly, you know, remember everything.
+Darius: Of course, she forgot my name. She's, you know, she's. Right.
+Jordan: She's an important lady. She meets a lot of people every day. You know, she sees, teaches 100 kids.
+Darius: But it just becomes like a lot of coincidences. You know, like she gets the review at work and she's like, students are noticing like you're trailing off in class. And yeah, it is just. Yeah, just every. the big moment that hit her is when she went jogging and got lost. And I've read that's how it is, like the little slip ups you could excuse, but then something happens that just makes you go, whoa. And then you'll see, you know, whatever happened. I love the note of the urologist where she's just like, he's like, because you're so smart, you've probably worked around it way longer than you believe. and you're probably more advanced. Like her deterioration felt rapid, probably because she was so smart, she had learned to manage it without knowing she was managing it. And she was actually further along in her disease than anyone knew.
+Jordan: Yeah.
+Darius: So how long was she probably meticulously taking notes because She was forgetting. Yeah. And so I just thought that was a nice little touch on how the movie explains away the obvious trope of the genius person being mentally ill. It's like, no, she's probably a lot sicker than we know because she's worked around it for so long. Correct.
+Jordan: And the drop off would be, would not be precipitous. So if it was not a precipitous drop off, no one would notice because she was already so much smarter than probably most people she was around anyway.
+Darius: Correct. And everyone just probably feels like, man, she's feeling normal.
+Jordan: Right. Yeah. They're probably like, oh, she's having a rough day or, you know what I mean?
+Darius: She used to knock out that crossword puzzle in an hour and now she's doing it and she's not finishing them, you know? And so.
+Jordan: Right. Yeah. And even like, I think that's her intelligence and her, you know, self-sufficiency was part of a big part of why she felt the need to keep it a secret. I don't think it was just so to protect her family or to ego protection or anything like that. I think it was more so just like, I don't want to accept that I'm quote unquote less than I used to be or I'm not as sharp as I once was.
+Darius: Agents wild though, man, because like, it's hard to, you know, yeah, it's like, there are little tests I do to keep myself sharp. That's a question I have in act two. And it's like, it's hard to discern what's like, you know, why do I work out? And it's hard to discern what's something I should, go to a doctor to see what injury and what's gonna recover. And that line changes as, you know, I'm approaching 40. You know, there are things now where it's like, I'm working through this bicep strain and it's, I'm on week five or six now. And this, it's, I'm still not carrying like heavy loads. And I know 10 years ago, this would have been out of three days. Like I wouldn't even have taken time off, you know? And now it's just like, your body just stops responding like it used to and it's hard. it's a mind because you you still remember the resiliency of youth and you just she's a little older she's I think she was 52 in the movie or something like that and um I mean her poor husband it's just it's hard I understand why how it could happen and you just not even know it's happening because like the doctor said you just learn to work around it you're smart enough to almost trick yourself
+Jordan: correct and even especially with technology now that you can just make I I I'm can be forgetful from time to time. And I just put a lot of **** in my notes. Like if I, let's say I had it, I wouldn't know because I'd be using my notes anyway. So there's all these failsets we have, which makes it harder to keep track of our decline or, you know, we're also so reliant on technology. Our mind is doing less work.
+Darius: Yeah, like I said, I won't step on my question later, but like there are things I do in analog that, you know, I just, If you don't use it, you'll lose it. And I just remember one, like, I don't like, how many numbers do you have memorized, do you think?
+Jordan: Oh, ****.
+Darius: I just, I thought about that the other day and I was like, I have my sister's number memorized and ex-girlfriend's numbers memorized just because it's just, I knew her from when we didn't, you know, have self before that. So it's just like, yeah. And my parents' house phone, because it's been the same my whole life. But any number that I've gotten in the past 15 years, it's just a name in my phone. It's not a number. Right.
+Jordan: Yeah. That's funny, actually. Yeah, same. The numbers I memorized, my house phone, we didn't even use a house phone anymore. So what do I need that number for in my head? My mom's phone number, she's had the same number for forever. My dad's phone number changed a lot, so I don't have his number memorized anymore. It's funny, actually, I remember having this conversation with an ex-girlfriend and I was talking about that and I was like, I only phone number I know is 911 of my mom's. And she like was mad that I didn't have a phone to memorize to the point where she's like, I memorize numbers that important to me. And it's like, okay, I'll memorize number like chill out. But like, yeah.
+Darius: But like, it's like, there is something to you automate that. and move that out of that cognitive load and make room for other things too. I can't start a fire from scratch with sticks and leaves anymore, but that cognitive burden is onto more complex tasks. Like I'm not, I can just turn on my stove and now I can cook things that a caveman never would have figured out because he was too busy starting fires with sticks and letters. So there is something to, have we moved memorization of phone numbers out and move something else in? It's like, I don't
+Jordan: need to know how to start a fire, but I do need to know how to change a tire.
+Darius: Correct. So let me ask you this. Set it up for the audience. The Alzheimer's she had was genetic. Well, all Alzheimer's is genetic, but this was like her early onset was very clearly pass down to her children and as like a 100%, you will get it if you have the gene thing. And there's a science behind it. I'm too dumb to know. Would you take the genetic test to learn if you had it? Like two of her kids did it and one didn't.
+Jordan: That's funny. I was going to ask you that. For something like that, yeah, I would want to know so I can kind of start building the safeguards or, you know, figure out how to plan my life out or, you know, like Yeah, I want to know. If I, like we said, if I wasn't married, I'd think to myself, would I want to get married? Would I want to have kids? If I'm going to have this decline, I don't know that I would necessarily want to do that. Or if I did, I'd be like, let me get a head start now. You know what I mean? **** like that. So yeah, I definitely want to know so I can kind of just make sure that I'm in the best place possible when it does hit.
+Darius: Yeah, 100% want to know more information is better. Well, in this case, I think more information is better. But there is something to the reason why a lot of doctors, especially like diagnostic, hate full body scans is because everybody has like a piece of cancer somewhere. And like most of it will never progress to like a level where it's actually. But if you if you scan a whole body, every scar, every this, and now you're just wearing these people to death for a lot of times in elderly men, they'll be, they'll get prostate cancer, but they're so old that they'll die of something else before the prostate cancer ever presents as an illness. And so it's like, you weigh the cost of treating them. And, you know, it's like, you can, like knowing you're sick before you have any symptoms, That does lower your quality of life even before it's time to lower your quality of life. You're, like there is something to that, but I would want to know something this serious, especially when it comes to like this is something that we know genetically is passed on. My kids are coin flipped to get it. Yeah, 100% would want to know this one.
+Jordan: Yeah, I agree. Actually, so I was going to ask you, her two of her kids took the test, one didn't. The one kid that had the results or one of her It was turned out to have it or was going to have it basically. Would you have told your mom when you got those results?
+Darius: The morbid thing is she wouldn't remember anyway. But I would want giving that she was going to deteriorate in a way that like What does she have a good year left of memories? I would want her to just have those good that I wouldn't even tell her I took the test. I would just take it. Yeah, I wouldn't tell her. I would just tell her I didn't take the test. And then after she, you know, lost it or whatever, maybe I let my dad know. Yeah, okay. In this in this case, but like, no, she's got a year left of not a year left of life, but a year left of the mom that you know. And like, you know, I'll take the time. I'll just tell her, no, I'm not taking the test and just Right, and I wouldn't want
+Jordan: to put that guilt or blame on her anyway. Yeah, that's probably my biggest reason behind not telling her. And also, I love my mom, but she does, she's not great with bad news. So I definitely wouldn't. Nah, I'm going to save you some anxiety and I'll just keep that to myself.
+Darius: Yeah, you just. I would want to know, but I would want to be the only person. I've said before, even if I knew I was like sick, I wouldn't tell anybody. I just wouldn't, because once you tell people you're sick, you become your illness. You're not even their person anymore.
+Jordan: And that's a big point of the movie, you know?
+Darius: so like if I, was diagnosed with some cancer or something, nobody would know beyond like, if I had a wife or something, but.
+Jordan: Yeah. And honestly, keep it a buck, depending on how long I had left to live, I might just take care of myself. I'm just going to be honest with you, know what I mean? If it was like some long-term **** all right, I'll just live it out, whatever. If it's some short-term **** I'd be like, **** it, I'll just, you know, I'll just clock out.
+Darius: Yeah, I mean, cancer treatment's gone pretty far. It just all depends. But yeah, I don't think I would chat with Boz with it, man. Y'all would find out with the IG post hit. I wouldn't want it. I wouldn't want it. So you got anything else for that one?
+Jordan: Yeah, actually, yeah. I forgot we talked about New York, the city of New York earlier. We were talking about the Knicks and the Spurs. New York has to be the worst possible place on earth to be when you have some sort of cognitive decline, like early onset Alzheimer's. Like imagine she was like on the subway and got lost or had an episode. I remember she went running without her phone. She had the habit of running without her phone. Like, She could have it anywhere, in a city like that. And people in that city are mean as **** too. You know, they're not going to help you out.
+Darius: So she did wear the bracelet. Yeah, the memory impaired bracelet, I think. What is it? New Yorkers are. What is it? Nice and.
+Jordan: Was it nice to each other? Mean to everybody else?
+Darius: No, it's something like. I forget the same, but like, I think New Yorkers are certainly rude, but that's the culture of everyone being on the way. But I think if some old lady was having a memory loss episode that she'd be all right. But no, I mean,
+Jordan: she's not old, so they would just think she was maybe insane early onset.
+Darius: Yeah, that's true. And she's in Columbia, so that's right in the heart of New York City. So yeah, that's true. That is true. And there's no cars. I mean, these people were right, so they could afford cars, but you get what I mean. So.
+Jordan: Yeah.
+Darius: Anything else, Rag1?
+Jordan: There is a couple of like dark, funny moments in this movie where she was arguing with her husband and she's like, I'm sorry, I have Alzheimer's. When she just didn't want to go to the dinner.
+Darius: Yeah. Well, I think. Well, that was funny because it's like. I thought that she did forget, but it almost becomes like, like she forgot, but she was still cognitive, you know, aware enough to know to pretend she didn't, you know, and so because she didn't want to worry him. And because it clearly was out of character for her when she come home talking, he had, you know, completely missed it and the meeting was important to him. I think she honestly forgot because of the illness, but she was she was smart enough to play it off like she just covered up like the lesser of two evils you know and so right
+Jordan: it's like either I forget now or I forget that when we're there something when we're there so
+Darius: they did a good job of illustrating how hard it is on the husband to like kind of you know he still has to live it's like you know his life didn't just stop right and it's like your wife isn't dying she's just losing her mind and so that is there's no there's an end to your wife inside, but that is not an end to like this ordeal, Right.
+Jordan: So that sucks, And they didn't make a good job of showing that because you do feel like she's dying. Like, I, that's the experience I had like watching the movie. It felt like, when she was like, whenever she was preparing food, I was like, oh, she's going to have an accident and cut herself and, you know what I mean? And **** like that. So I think they did a great job of showing like, again, it's not a death, but you are losing the person that you once knew, you know? And
+Darius: Alice died, but the body is still there. And it's just like, that's almost worse because it's like, you never get to move on.
+Jordan: I'm sure it's almost like every day is a funeral.
+Darius: Yeah, I'm sure. Well, the daughter probably just gave up the acting thing to be our full-time caregiver and they could afford home aids and things like that. But It's going to be hard. He said he moved to, well, spoiler alert, he moved to Harvard or Minnesota Mayo Clinic.
+Jordan: Minnesota. Yeah. And even like, I think this story obviously is devastating and sad, but this is the happy end of the spectrum because they were so well off. They could get her the care she needs. And, you know, a lot of people, if you're, you know, not in that position financially, what do you do?
+Darius: You let them die, basically. On that morbid note, act 2, fighting for footing. As the disease progresses, Alice fights to maintain her autonomy and connection to her career and family. She creates a folder on her computer with a series of basic questions to test herself daily alongside the hidden devastating video instruction manual for her future self, trigger warning, suicide, all the above. You know, I said earlier, I love that they didn't do dramatic **** like make her yell an ex's name or insult someone inappropriately. But like there was a tension in waiting on those, like they were making out at the beach house. And I just was like, she's gonna call him an ex or something. And it just never happened. And I just thought that it was nice that they didn't take that cheap trope out, but the tension from waiting on it was good. It's a really well-made movie, man. The way they worked the cameras to show how disoriented she was. And, you know, it just, the movie.
+Jordan: Was in the background sometimes.
+Darius: Yeah, it was good. It was really, really well-made.
+Jordan: Yeah, I agree. A little bit off topic, but it is slowly related to, loosely related to this movie. Have you seen, there's a real viral the other day or TikTok or something? And it's about how like, working in an old people's home, they like lose their memory and stuff. And the joke was basically like, they lose their memory, but they can still remember to be racist.
+Darius: Oh, yeah. I think people, I think I would love to see some actual percentages on that, but I mean, it happens, I'm sure. Yeah. I mean, it's like the Tourette's thing. We, Right, I don't know what to do with that, but I would love to see some actual data on that. Cause I think it's, I think people are gassing it a little bit. But yeah, I have seen those jokes before for sure. Which is why I'm glad it's just like the movie didn't take those cheap, dramatic shots. Like, oh, she's, she's gonna call his girlfriend a *****. And it's like, you know, like this is just, that's just cheap, you know, so I agree.
+Jordan: Yeah. So even speaking of, the deterioration, when they showed her finally having an accident because she couldn't find the bathroom, that was very tastefully done. It wasn't some, camp. She slipped in her own **** and in a public space, some **** like that. It was very tactfully done. And you just felt this like you almost knew it was going to happen during the scene. You're like, oh no, this is where it really gets worse for her. And kind of see the level of the loss of memory.
+Darius: That's when it fell off a cliff. Because she comes outside and she's like, when are we going to dinner? He's like, Monday, when it's on Sunday. And she goes inside, comes out and asks the same question. And then she's walking around the house and you kind of knew she was looking for the bathroom. And then cognitive decline is terrifying. Like, I don't know. Like, I just, I'll take anything over that. Like losing your mind like that. And that feeling of like you're in your home and you don't know where anything is and you just can't. It's like remembering a movie title, but it's where your bathroom is.
+Jordan: Yeah, that's crazy, man. I didn't even think about it like that. **** that's crazy.
+Darius: That's insane, man. And you're not elderly. You're a relative young woman.
+Jordan: It's even like, remember she was in the refrigerator and she pulled out a bottle of shampoo, you know, like subtle **** like that. Yeah, man, that's tough, man. I don't I wouldn't have said on anybody. I mean, I'll just say, but like, that's just, man.
+Darius: The pre-suicide note. And it's like, she wasn't aware because like, you're not, if you're reaching the point where you're not remembering the logic games, you're not going to be able to, and obviously they showed the scene, like she's not going to be able to follow those simple instructions.
+Jordan: Yeah. And even that was really well done because honestly, when she The first act she recorded in the first act, I thought she was saying, take these pills every day. I didn't think she meant take them all at once. I didn't realize that was, I didn't realize that what she was saying until the second time that clip came around.
+Darius: And then she like walks up and then she can't and then she walks down. Well, that's another pills. Yeah, it's just they did a really good job with it. But speaking of the logic games that she had, man, do you have any logic games that you played to stay sharp?
+Jordan: I do crossword puzzles every now and then, not super often, but I do do those from time to time. I mean, I mostly just like ask myself questions, kind of keep myself abreast of what I'm remembering, things of that nature. Like if I'm reading a book, I'll ask myself questions about why would the character do this, why would the character do that? I'm almost in conversation with the book to try to make sure I'm sharp and, you know, things like that. Or I'll just like look up a random topic and just read things about that. You know, I just try to keep my mind as fresh and engaged as possible when I have the mind space to do that. I think that's probably the thing that the things I do most. I mean, like I write a lot, but I you can't read a lot. You can't write well if you don't read. So like I'll read, you know, a lot of poetry and stuff to kind of sharpen my, literary devices, metaphors, any more references, things of that nature. Those are probably the... biggest things that I do to kind of keep my keep my mind sharp.
+Darius: Um you know speaking of poetry one of the things I do is uh reciting rap lyrics but like I'll just kind of track off and see how far I can get before I stumble and obviously you can't look them up um you'd be surprised because remember when you were a kid you just knew every song yeah new songs are harder and it's like it's you know If you don't use it, you'll lose it. And it's just, it's harder to remember songs than it used to be. Just like, I think it's like the same way it's like easier to learn a language when you're young. And so I love to just cut the track off, recite the verse as long as I can. And when I stumble, go like, let's do it again and redo that.
+Jordan: Interesting.
+Darius: Okay. Lately, what I can, there's verses I can like just no music, no nothing, just recite them. just add new ones to the queue and different things like that and just try to learn verses. It's harder than it sounds, people. Try it. One thing I'm doing lately, so a new tech forward way, using AI for good is I have an AI chat in Gemini that's just like re-teaching me algebra. And so I'm just like, You know, we're, we're using, we're basically, it's just like freshman algebra all over again. It's like re teaching me things. And a lot of it comes back quick, because it uses real world examples, but I'm like, give me this example, no hints. And then I'll work through it on a piece of paper. And, you know, it's just kind of, it's like more or less hiring a tutor. Yeah. And so like relearning algebra concepts as an adult is, You good, useful. It's a dooku. I have a Sudoku puzzle book that I bring in my office backpack. Get slow at work. **** with that. And the New York Times crossword puzzle are my. Yeah, those are the things I do to interest. Just make sure it's like a you know, there's a if you ever watch the West Wing, the the president in the West Wing does balance multiple sclerosis, I think. And one of the ways, because he's president, you have to keep sharp cognitively. Believe it, believe it or not, this used to be a matter of national concern. The president was like, not too old for the job and old and firm. But he would play chess with his chief of staff every day to make sure he's still sharp. And so like, it was just like little things like that to make sure I'm staying on top because, You can get dumb if you don't use it. So you got to keep.
+Jordan: I think about that a lot. It's like when you have kids, you got to remember everything that they need to learn in school so you can actually help them with the homework.
+Darius: And it ain't, you know, I don't think the general public schools are rigorous enough in math, but like it's still, it's harder than you think. And so there's no reason why. middle school students can't start on algebra. Why are we waiting until high school for this? And so like, we just, there's nothing like we, anyways, long stories, we're too much, be your whole self and not enough math and reading. We don't, schools need to be teaching kids how to read and do math. And once we get that back to up to regular, then we can do the extracurriculars.
+Jordan: And I think as adults, it's really important to remember to keep learning too. in school, you learned literally like 50 things a day, and as an adult, not so much, because you're just doing whatever your job is, you're doing that same thing over and over again, unless you get promoted. So it's like, you got to really work hard to make sure like, damn, did I learn something today? Did I learn something this week? You know, did I read something? Did I use any sort of skill set other than what my job requires? You know, did I do any math today? Things like that. So I think that stuff is really important to to kind of keep yourself sharp if you're nothing else so that you age well and also just so that you're not just a zombie out here.
+Darius: Not a zombie, you know, not just like doom scrolling on your phone. That's just brain rot. And so yeah, even when I just like watch a movie for the pod and my phone's away, I got to feel my attention span return. I've said this on the pod before, but like, you know, just get out the phones and do something that, you know, keeps you sharp because if you don't use it, you lose it. So anything else for actors?
+Jordan: Something really cool, interesting I saw somebody say is if you're going to doom stroll, doom scroll, at least do it while you're on the treadmill or like while you're taking.
+Darius: That's true. You know, do it while you're taking a walk, you know, don't get me wrong, you can have some fun podcasts, but have some smart ones too, like ours.
+Jordan: Yeah.
+Darius: And you know, just like mix it in a little bit. Like we, you know, said earlier, like I could couch rock with the best of them, but maybe 10 hours of video games, you know, weekend or in a day. It's a lot, you know, get up, get some air. meet, hang out with some friends like that. Your social muscles matter too. and I'm not the best at it, but you have to use it. that people say they have social anxiety and when they're in crowds, it's like, well, it's a muscle. You haven't used it in a while. That's that tension. And when you go to the gym and that weight is harder than it, and you remember, that's the same feeling when you're out. You haven't been out in a while and you don't know what to say or like that. That's that muscle tension. That's important. Yeah. Like you can't. Part of life is saying saying a joke that doesn't land and navigating, like it's not the end of the world.
+Jordan: You need to talk to people that are not going to connect with you so you know what works.
+Darius: Correct.
+Jordan: **** I lost my train of thought. And also, if you're going to play video games, find some games that make you think, you know.
+Darius: I mean, just mix it in, you know. A couple of strategy games won't hurt. Little Civ, little SimCity. Mix it in there with your call of duty.
+Jordan: So I think sports games are good for that too, because it's all strategy at the end of the day.
+Darius: That is true. That is true.
+Jordan: That's all for ac</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out the Trunk Pile with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy B Riding.
+Darius: And I'm Darius. That's easy. I love me, Ari on all socials.
+Jordan: And today we're going to be reviewing Stranger Than Fiction, came out in 2006, starring Will Ferrell, Maggie Gyllenhaal, Dustin Hoffman, the legendary Queen Latifah, Emma Thompson, and Tony Hale. This movie is about a man named Harold Crick, who's an isolated IRS auditor governed by numbers and routines who begins hearing a narrator's voice chronicling his life. When the voice predicts his imminent death, Harold must find the author responsible for his story while learning to actually live the life he left before it ends. So I'm going toss it to you, set up act one.
+Darius: Act one, the narrator in the head. Harold's rigid life is disrupted when he hears a woman's voice describing his every move. Panicked by the realization that he is a character in a tragedy. He seeks help from a literature professor. I just want to say shout out to original movies, man. Yeah. I've never seen a movie like this before. It was truly an original concept. And you don't see that very often, even though I think this movie is 20 years old. But you get what I mean. Like they don't It's hard to do original things. It's risky to do original things. And we should applaud people when they try.
+Jordan: Agreed.
+Darius: And Will Ferrell can act, so.
+Jordan: He can.
+Darius: What you got, Frank?
+Jordan: I'd actually like to see him, I was going to say that, actually, to piggyback off your point, I think, to me, the great test of a comedic actor is how good they are at drama, because comedy is actually harder than drama, because you're supposed to feel something. You're supposed to do it having a specific reaction to a joke. You know what I mean? There's only one reaction you can have and that's a laugh. And if you don't laugh, you didn't do your job as the comedian, entertainer, so on and so forth. So it was great to see him in a dramatic role. I actually kind of wish he'd do more of them because he was really, really good in this. What was I going to say? We actually, so I wanted to ask you, is this your first time seeing it? Yeah. Have you seen this before?
+Darius: I've never seen it before.
+Jordan: Okay, yeah, so we actually watched this in high school for a creative writing class, kind of just, you know, they wanted us to understand perspectives and, you know, narration and different literary devices and stuff like that. So, and this movie does a really good job of showing those things.
+Darius: Your teacher was probably just hung over and needed a break and put the movie on.
+Jordan: That's also possible.
+Darius: As an adult, as someone who was dating.
+Jordan: She was an older lady, but.
+Darius: I found out that movie day was often just, they went out the night before. So little behind the curtains for those listening at home.
+Jordan: No, that's real.
+Darius: When the teacher put on Remember the Titans, was it Friday? Because it was a thirsty Thursday the night before. So that's usually what happened. If you heard a voice narrating your life right now, what genre book would it be?
+Jordan: God.
+Darius: Probably should have re-flighted that one. I didn't, we had so much else going on. We can come back to it. What else you got for everyone?
+Jordan: No, that's cool. I'll figure. Right now, what genre, it would be like a coming of age drama.
+Darius: Okay. I'm into that. I'm into that. Yeah, I'm kind of into that.
+Jordan: Metamorphosis phase right now.
+Darius: Okay.
+Jordan: So yeah.
+Darius: What's the pokémon? I was going to sound like a really big dork and talk about pokémon evolutions but butterflies become butterflies I won't say the actual pokémon but uh yeah so makes sense you don't know one got you.
+Jordan: What you say you're gonna pretend like you don't know the name of the pokémon got you um yeah so I think um what was I gonna say um I really like one thing I like about this movie is that It does show how easily you can just get caught up in just being on autopilot in your life and kind of the things that can happen when you don't actively like make decisions and you just get caught in this routine. You're almost like a walking simulation. Because he very much, again, like you said, I'm a character in my own life, but he wasn't even the main character. He was just like some side guy with like miscellaneous, you know what I mean? Like he's like that coworker that you see that you kind of forget is there some days yeah.
+Darius: He's the people in the background of the coffee shop where like the main characters are like talking and they're just extra in the show um yeah I mean sometimes I feel like that where it's just like you get into this routine and you just do you type for a living and go to the gym at the same time every day um go to work every day cook every day and you know yeah play video games and go to the same places on the weekends and it could just feel a bit repetitive, if you will. So, yeah. Yeah, I guess if I were to answer my own question back to me, what genre of book would it be? Like, **** heralds. I don't know what you call the drama book that would never get made because it's nothing happens. Not a lot going on, man. Just boring.
+Jordan: I think you call that some of the movies we've reviewed. Yeah. What else you got? Okay, so I wanted to ask you, if you had someone narrating your life, like famous or maybe just anybody, who would it be? And you can't say Morgan Freeman.
+Darius: No, I mean, I would want it to be a woman. And let me go with Halle Berry. Okay. I just think I love her Twitter presence.
+Jordan: She does have great commentary.
+Darius: I think she has the best pulse of the culture. I mean, for a 50 something year old woman. And she blends the old with the new very well. And I think that she would do a good job keeping the pace of my extraordinary, ordinary life. Which movie was that? Extraordinary, ordinary life. Oh, it was the one where he was he could, like, go in the closet and reverse time. About time. That's what it was called.
+Jordan: Oh, okay. Okay.
+Darius: Yeah. Anyways, off topic. What you got for what else you got for act one.
+Jordan: So one of my favorite quotes in this movie, and it's so realistic, is where he's on the bus with Maggie Gyllenhaal's character, and there's a narrator voiceover, and she goes, Carroll quickly calculated the odds of making an *** of himself in ratio to the amount of times he stayed to chat. And I've been in that situation where I'm like, if I say here no longer, will I say something stupid? And if I think I'm going to say something stupid, I just leave.
+Darius: It's usually when I switch to water. It's usually a good time to do that when you feel like you're losing your ability to filter saying dumb things.
+Jordan: Yeah.
+Darius: Usually a good time to put the beverage down and get up some water. Order some food, take a lap.
+Jordan: Yeah, take a lap, get some fresh air, phone a friend.
+Darius: Or just go home, you know?
+Jordan: That too.
+Darius: That's usually a sign when you As I'm dropping things when you're when you're losing, when you can feel that filter dropping and like that, the things that you know would stay buried reach like right here. So I let me let me switch it up. So when I head into act two or you got anything else for act one?
+Jordan: Yes, I do have a question for you. I guess you're pretty you probably do have this then. Do you have a morning routine similar to the intro?
+Darius: Wake up, I drink. So I wake up, I feed my cat right away because he eats at 7am. And then I have, take my water jug and I have two glasses of water. And then I go brush, I have one glass of water and then I turn on the air filters in my apartment. I have my second glass of water and I brush my teeth and then I have my third glass of water. And while after the third glass of water, I refill the water bottle. And then that's my 4th glass of water. That's the break between that. And I start the day with four glasses of water. And then I pour my coffee and I have a banana and I work. That's what I do every single morning. If I have to go into the office, I shower in between the 4th glass of water and before I pour the coffee. But my bag is already packed the night before for work. So I can just like literally out the shower and I've already had my clothes picked out. down to like t-shirts, draws and socks. Like they're already out for the office tomorrow. Okay. And so from the moment I get out of bed at 7, I am in my cubicle working by 735. Gotcha. And so maybe I get out of bed at like 650, just depending. But that is The most obvious answer to your question ever is yes, I do have a roti. That is the gist of it. Down to that's if I go into the office, the banana is at the office. If I don't go into the office, the banana is right when I get the coffee. So got a banana every day. The first thing I eat every morning is a banana and some black coffee. How about you?
+Jordan: Yes and no. It changes like you on days when I'm in the office. When I'm working from home, I usually just get up about 15, 20 minutes before work, wash my face, maybe get my body moving a little bit so I can have some sort of energy, turn my lamps on. I'll maybe check my phone real quick, see if anything crazy happened overnight on social media or in the news. I will pick out, I mean, I work from home most days, so I'm just wearing like gym **** or whatever, hoodies and stuff. I usually like to shower around like 9 or 10 A.m. It's kind of like my reset for the day if I feel like the first half of my day didn't go as planned. It's kind of like my insurance policy. And then I'll pick out whatever audiobook or YouTube stuff I want to listen to while I work or I'll find an old album or I usually have a song I listen to for the first like 30 minutes of the day just kind of get myself in the mode of like working without just scrolling and looking for a song and **** like that. And then on days where I go into the office, get up around 630, 645. I don't like ironing, so I put my clothes in the dryer so I can do that while I shower. That's very millennial.
+Darius: I don't know.
+Jordan: I just, I wasn't sure if that was like millennial coded or not, so I just throw my clothes in the dryer, speed wash, speed, speed dryer. I have my Alexa, so I'll play music, get in the shower, get out, get dressed, drink some water real quick. And then I have my backpack. All I need is my badge, throw my headphones in my Kindle and my work laptop and my book bag. And then I speed to work. So that's my morning routine for office days.
+Darius: I try to make every decision that I have to make the night before. That's why, yeah, the clothes are picked out. The shoes are going to wear it picked out. The watch I'm wearing is picked out. The cologne is picked out. And so all I got to do is wake up, feed the cat, drink my water. And I'm dressed to go to, I can leave, I can literally just shower and leave out the door. Office days, I mean, remote days, I'm not getting dressed. No one does that. That's like. Correct. I don't even remember when they tell you nobody does that. Nobody gets dressed to work in the room next to me. And so my first shower on remote days is when I get home from the gym. But Friday night before I go to the bar, It depends. So if I work all day Friday, it's a little different, but I take a lot of half days Friday for two reasons. One, a half day counts as an office day. So I only have to go in two days that week if I take a half day Friday.
+Jordan: Okay, got you.
+Darius: At my level of tenure, I get a lot of PTO and I don't, when you work remote, you never have to call in sick. I don't have any kids and I don't really take long vacations. I just take a lot of three day or four days or four dayers. And so I just have a lot of PTO to burn. So I don't really work a lot of Fridays. But so Friday I work out 1030, get home about 1230. That's usually when I like allow myself some fast food. So I'll probably get like McDonald's or something. And then 2 o'clock, I nap till 4 o'clock, get up, clean my place until 530, play video games until 830. And that's when I shower and I'm at the bar by 915. And that's literally what I do every Friday. Oh, the video game switches. But right. Yeah, because if I don't, I need a nap. Otherwise I'll be yawning in that ***** at 11 o'clock. And so I feel I work until like two o'clock and then I'll take a nap until four, 430, clean the crib until 637, whatever. And then just play video games until 830, 830 shower. See you. with a beer in a shot by 915. So it's all it's nice borderline autistic. And I don't mean that borderline. Right. So I'm not that rigid about it. Like sometimes we go different places. But if we're if sometimes I go a little earlier, sometimes I'll go to the spot that's walking distance from my crib. But I usually like to do that on Saturday and just not go all the way out. I do on Friday. So it just depends. Right. I feel you. Yeah. That's it.
+Jordan: Nice.
+Darius: On pod Tuesdays, I get home because that's an office day. I get home about 345 and then I'll just lay and sit down and reset until 4 or 5 and get ready for the gym, be there 415, work out, go by 6, eat, fold, close, 730, start prepping for the pod. lights on. So it's all very much like Harold. That's enough of my routine today. You want to get into act two.
+Jordan: Yeah. Let me see. Oh yeah. So act two, one of my main, I haven't read the prompt yet. yeah, go ahead.
+Darius: Act 2, righting the wrong, Harold tracks down the author, Karen Eiffel, while simultaneously falling for a rebellious baker he's supposed to be auditing. He struggles to balance his growing humanity with the knowledge that his story is ending. What do you want to tell the people?
+Jordan: The only one of my main issues with this movie is that they never really show or explain why Harold is the way he is. And I don't just mean like the bored employee thing. I mean like like just he's just so like vanilla and it's like they never explained like if something happened to him as a child or like you know what I mean like they never I wish they had dived more into who what made him what he was as opposed to just him realizing that his life sucked.
+Darius: I have it here literally for this segment we're starting to think alike. I've actually never seen a movie do less with more. This is an incredible premise that just doesn't do anything. It's a two hour long day in the life TikTok. And I was like, okay, is something going to happen?
+Jordan: It's like they took it's like they they they realized like the the reason behind or the methodology behind the characters in Fight Club. They didn't try to go any further. And I'm like, you had it right there. You couldn't you know what I mean?
+Darius: Yeah, I mean like the bulldozer through his apartment, I guess was something that happened. But even then that just like just happened. Nothing else goes with it. It's just, it's a great premise that just.
+Jordan: It's a really good premise.
+Darius: Just needed better writers. Yeah, I agree. Like I said, it felt like a two hour long day in the life TikTok. I like those 30 seconds at a time.
+Jordan: Yeah, me too. Me too. I think my thing too is that like every, he's literally the least, every other character in the movie is more interesting than him.
+Darius: Yeah.
+Jordan: I think that's also a problem, which is the point of the movie. I understand that. But I just wish they'd given us a little more reason to want him to live. Not that I want him to die, but like, you know what I mean? Yeah.
+Darius: I know nothing about this character and I spent an hour and 50 minutes with them.
+Jordan: Right, exactly. Like I know his name's Harold. He wanted to play the guitar, so he did. He worked for the IRS, really good at math. Creature of habit. And that's all we know about Harold. But I did like the scene where he stays after He's doing the auditing at the cookie show, at the bakery. And she's offering him the cookies and he like ***** it up because he's like, oh, he's so rigid that he's not willing to understand. He didn't even understand that she was like just genuinely showing a gesture of kindness. And it just got me wondering, so I'm going to ask you now, you may need time to think so I understand if you do. What's your most, have you had a most obvious fumble like that? Like with a girl where you're like, you realize later on like, oh my God, she was like, you know what I mean? I really ****** that up.
+Darius: I actually, I didn't do it on purpose. Yes, I don't know if I can share that story though. It goes back to it's work-related, so I can't really do it. But yes, I mean, everyone has those stories where they're like sitting in their room and they look at the sky and they go, It might have been three years ago, four years ago, five years ago. And it finally hit you that she was throwing it at you and you didn't even catch it. So I certainly.
+Jordan: It's funny because like I'm sure there are several times where like women have thought that a guy wasn't interested and it's like, no, he just genuinely had no idea what the **** was going on.
+Darius: Well, so women are bad at flirting.
+Jordan: That's also true.
+Darius: And. Yeah, I guess. Well, I mean, it's easy for us to say that because maybe we're just not picking up, you know, two different genders, right? And we communicate in two different ways and sometimes those wires don't cross the way they should. But certainly. Yeah, I can't even tell that story either because it's. Yeah, that's bar related. Yeah. OK. Yeah. I mean, certainly it has happened to me and certainly I have. I'm trying to think.
+Jordan: Let's see here. Oh, actually, yeah, I have one. I was at a bar for the Super Bowl a couple years ago. This is after I'd gotten suspended that one time. And I was sitting there and there was these two girls and they're both cute, whatever. And one of them, kept asking me questions about the game and stuff like, okay, so how's that a fumble or what's a fumble? Like **** like that, and how do they know, what's that line mean, the yellow line and all that kind of stuff. And I remember, I think I was texting you and I was like, yo, I'm in here trying to watch the game and this girl won't shut the **** **. You know, and you were like, I was like, you were like, what do you mean? I was like, she asked me all these ******* questions. And you're like, what are you, like what kind of questions? I was telling you what she was asking me. And you were like, dude, she's interested in you. No woman is out to watch Super Bowl that doesn't understand what the scrimmage is. Yeah.
+Darius: What's A fumble. Yeah. I actually do have one that's shareable. Now I think about it. So I was in Minnesota for my dad's 60th birthday party in December. And we're checking into the hotel and my sister has a hotel plug. And so like it just a dirt cheap plug. And so I had to wait on her to land and get situated and come to the hotel because it's in her name. And I'm just sitting there scrolling my phone, charging my phone. and the front desk lady and I are just talking or whatever. And she's just like, what are you, where are you going tonight? And I was like, well, I'm here for my dad's birthday, but today I'm going out with the fellas. And she was like, she's like the, she's the front desk lady. And she's like, oh, where do you like to go? And she told me about this place. I think his name was like plush or something like that. Okay, so what happened? Because I had time to kill. And I'm like, is there anywhere to drink around here? Like, there's no bar in here. Is there a bar around here? I'm on vacation. **** it. And she was like, no, but around the corner, there's this lounge called Plush. I'm just using that. I think that was a name. And that's, you know, where a lot of me, like, that's where a lot of people RH go, whatever, whatever. And I'm like, what time? You know, like, Where is it? And she's like, it's like, it's like, it's a hall. So I couldn't go and whatever. And then she asked me, I asked her what to do and she keeps bringing up this bar. And the next day, so I went out to fellas and then that next day, coming downstairs to buy some bottles of water and she's the front desk lady again. And she's just dragging. And I'm like, you all right. She's like, yeah, I went out with the girls last night. And to be honest, because they had snowed in Minnesota. And she was like, I was I knew she was like, I knew we were like, I wanted my employees to be able to get back here. So I got them rooms in the hotel because she's the manager. Just let them sleep here.
+Jordan: Right. Okay. Yeah.
+Darius: And I was like, oh, that's cool. And I was like, she was like, so I just figured I'd go out. And I was, where'd you go? And she said, plush. And I stayed here last night. I was like, ****. So that is a good one.
+Jordan: She was literally wingmanning for you and the boys.
+Darius: No.
+Jordan: She was interested in you, but I think she probably planned to have your boys with your homegirls. Some of your friends get with my friends so we can be friends.
+Darius: Clearly they had went out because she was looking rough. And it was like 10 in the morning. It wasn't even no early *** time. And she was like, yeah, I slept here last night. I went to plush. And then like all that math just hit my head. And I was like, first of all, use your words. You should have said, would you like to meet me at plush tonight?
+Jordan: Yes. Yeah. Thank you.
+Darius: I'd have been like, yes. Let me text the group chat right now.
+Jordan: Correct. I mean, even I remember that time we were at the bar and that girl was talking to me and you and platinum blonde hair girl was like, Jordan, that girl's like into you. What are you doing?
+Darius: Sometimes. I mean, listen. What was I supposed to do? Just show up at this place because you said you was going to be there and.
+Jordan: No, because what if you were wrong and you look like an *******?
+Darius: Or just a ******* stalker. That's what I'm saying, yeah. Some guy at the hotel that you checked into just popped up.
+Jordan: Hey, Becky.
+Darius: So yeah, I guess that is one time where I did not see it coming. Do you have anything else track to?
+Jordan: Yeah, so I actually wanted to ask you, or yeah, do you think this movie in some way, served as a precursor and social commentary on what we now call the male loneliness epidemic.
+Darius: No, not really. I mean, it's hard because it feels like a relic because there's no cell phones in it. Right. And cell phones. And I don't even think he's like using a laptop in the movie. So they're still doing audits?
+Jordan: He was using calculators and ****. Yeah.
+Darius: And so A lot of the loneliness epidemic is a technology driven phenomenon. So true. I wouldn't say that like the technology is making it easier for people already inclined to be introverted to further isolate.
+Jordan: Right.
+Darius: But he didn't have any of that. And so and also like he had friends. He went to the office and he talked to them. They shared math equations and whatever. He met a girl in the movie. So I don't know. I think that without the technology, it's hard to make a true corollary there, but I could see how someone would see it that way. But it was shocking in how low tech the movie was and how modern it felt. Like it didn't feel, well, I mean, maybe we're just old.
+Jordan: True.
+Darius: The picture was like, I don't like how old these pictures of 2006 look.
+Jordan: It's like I was there.
+Darius: Yeah. Cause what year did this movie come out? 2006.
+Jordan: 06? Yeah.
+Darius: And it looks old.
+Jordan: 06, yeah.
+Darius: You know, like you notice the things like there's no cell phones, no one's texting, no one's on the internet. People are using pieces of paper. And I was an adult. I was 18 in 2006.
+Jordan: Yeah.
+Darius: Oh, man, we're getting old.
+Jordan: Damn. Yeah, that was my freshman year of high school.
+Darius: Damn, man. 20 year old movies are about our adulthood.
+Jordan: It's so depressing.
+Darius: It's not great. My 20 year high school reunion is this year.
+Jordan: Damn.
+Darius: Yeah.
+Jordan: So how do you feel about that? That makes you feel the way about your life.
+Darius: The alternative is dying young, so I'll take it. So no, I mean, getting old don't bother me, man. I feel good. Um, I'm in good shape. I'm in a good place. Um, you know, I don't, I'm good. I don't really have, obviously, you know, here and there you'd like things to be better, but you know, don't bother me. Things hurt a little bit more. I can't, you know, squat and bench press as much as I, well, depends on the day. I have to warm up my shoulder a little bit more, but.
+Jordan: Yeah, because you're left or right shoulder.
+Darius: Right shoulder, shoulder impingement, parchment, partially torn rotator cuff. It's one of those things that surgery wouldn't be worth it. So it's just constant maintenance. But no, man, I don't. I don't mind getting older. I'm smarter, more emotionally mature, and I just make better decisions. So I don't mind it at all. How about you, man? Feeling gray hairs?
+Jordan: Yeah, I've got a few grades coming in. It's weird because like, I don't feel bad about it. I just I just I'm aware of it now. So it is a bit of a shock, you know, and I am aware that like I do need to put in more effort to like be healthy and to have a good life and quality of life. And I'm more aware of like, me wanting to have a good quality of life, especially like, not as I get older, but when I'm old, I think about, I mean, I'm in my early slash mid 30s, but, my grandfathers didn't make it past like 65, so I want to surpass that. And, there are things I can do that's largely in my control outside of, getting hit by a bus or something.
+Darius: Yeah.
+Jordan: Or, something a terminal illness or, so I'm more aware of things like that. And that's something that I think about a lot is just making sure now is like, okay, say I do want to have a family. It's like, okay, well, I want to make sure I'm able to be there for them, you know, for the long haul for a long time and stuff like that. But other than that, I mean, I feel pretty good. But again, it's better than the alternative. And, It's a natural part of life. It's not a bad thing. It's just something that people, you know, don't talk about or people make you feel like you should feel away about it. But, you know, it's like we're supposed to, that's how it's supposed to be. You know, it's sort of like, people, you know, grieve their parents when they lose them, obviously as they should. But somebody said something, heard someone say he wants, it's better to grieve them than to have them grieve you. And they would rather you grieve them than them grieve you. So I think about it like that. it's better to, get old or get older and, stress about a few gray hairs or, maybe not be as in shape or maybe not run as fast as I used to, as opposed to, being in a box. So. That's true. So, compared to that, we're all doing great.
+Darius: I was, you said like, You want to get older and too many of us die young. I just, I get that and that's real. And there are definitely like health issues. But anytime you see like, they'll put up like the list of black celebrities that died before age 55 or 60 or whatever. And it's like, That's crazy. I'm sorry, but if you take up a heroin addiction, that's going to lower your life expectancy. That has nothing in it. I don't know if you can't just put that in there with the guy who like.
+Jordan: No, yeah, you're right, you're right, you're right, you're right. That's real ****.
+Darius: I don't know if you need, I know if anyone needs to know this, but if you take up ******** drugs, probably not going to live to see your grandchildren.
+Jordan: Yeah, that's real ****. Again, addiction is a disease, but yes, that is true. Like, if it's something, not addiction, but if you can control the things that go in your body outside of an addiction, then you have a better, obviously better shot. And also just eating healthier is important too, you know what I'm saying? Like my grandfather, he had, but my grandfather's, I think, had diabetes, had to get amputations done and stuff like that, you know? So watching them perish was not, it was not a fun or easy process at all, So I really think about that a lot and I want to make sure that I don't suffer the same pitfalls.
+Darius: You definitely, I mean, you definitely want to take care of yourself and make better decisions in the aggregate. And, those things all contribute to a long life expectancy. But who was the dude from the wire who passed? Bald-headed guy, Detective Daniels, Lieutenant Daniels.
+Jordan: ****.
+Darius: Whatever point, like you'll see these lists and they'll like put Michael K. Williams, like all the actors that died from the wire. And it's like, okay, like, okay, Williams had a fentanyl overdose.
+Jordan: Yeah, unfortunately.
+Darius: RIP and all, but like he had to know that that's gonna like, right. I hate to break it to you, but if you're a regular user of fentanyl, you're probably not gonna be around very long.
+Jordan: Yeah. It sucks because it's the same thing with Matthew Perry, who's played Chandler in Friends. He wrote an amazing book about just like his life and about the struggle with addiction. And, you know, like it sucks because like the ending is so eerie because the ending is actually really, really hopeful and really, really happy. But he died like 2 years after the book came out. So it's like, you know, he thought he was kind of out of the woods and then, you know, he couldn't, you know, make it out. But I remember I saw a quote where Jennifer Aniston said, like, I mean, obviously they're still grieving. That's a heartbreak you'll live with forever. But she said, you know, we basically had grieved him while he was alive because we pretty much knew that he wasn't going to have, you know, the full capacity of life.
+Darius: He wasn't alone for this world. He's a junkie.
+Jordan: Yeah. Yes, unfortunately. You know, like that's because he was doing ketamine before he passed.
+Darius: RIP though. Act 3, the final draft. Harold meets his creator and reads the masterpiece she has written for him. Facing a choice between his own survival and the completion of a perfect work of art, he prepares for his fate. Didn't really have anything for Act 3, man. What'd you got? I got one question, but I don't want to lead with that.
+Jordan: Okay. I have one question also. I will say I did. From A storytelling perspective, it was really cool to see like the just the turmoil and misery of being a writer that and all the things that writers go through. they say it's like the loneliest process, the loneliest of all the creative endeavors. And this movie does a great job of illustrating that because she's basically just tweaking the **** out for two hours and trying to figure out the best way to give a character the send off that they deserve. You know, and it makes you think of like JK Rowling is, phenomenal writer and she talked about like the ending of Harry Potter. Sh</t>
+  </si>
+  <si>
+    <t>Darius: What do you like about this movie? Let me ask you that.
+Jordan: Hey there. Welcome to the Out of Trunk Pod with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's Steve's I love you area on all socials.
+Jordan: And we're going to be reviewing Take Me Home tonight. It's movie came out in 2011, starring Tofer Grace, Anna Faris, Dan Fogler, Theresa Palmer, and Chris Pratt. This movie is set over the course of a single night in 1988. A recent MIT graduate struggling to figure out his future poses as an investment banker to impress his high school crush at a massive Labor Day party. As the night unfolds, his deception spirals into chaos and life-changing revelations. Someone toss it to you for Act 1.
+Darius: Sorry, the Zoom messed me up. Act one, the deception begins. Matt Franklin is working at a sun drenched video store, much to his father's shaken. He reluctantly attends a high school reunion party with his sister and best friend, where he bumps into his longtime crush, Tory. To impress her, he impulsively lies and claims to work at Goldman Sachs. This game reminded me of GTA Vice City. It was very, I know it wasn't set in Miami, but it was very GTA. Vice City-esque. And also it was like a White Friday.
+Jordan: Yeah, yeah, yeah, yeah, yeah.
+Darius: You know, minus the whole having compelling characters and being funny. Minus that, it was like Friday for my people. What you got back one.
+Jordan: We talk a lot about like, obviously the movie is about nostalgia in the 80s and stuff. But one thing that I really miss about movies as a kid who grew up in the 90s is movies with like cool opening credits. Yeah. It's like the sequence with the yearbook and the signatures and the old photos and all the kind of 80s paraphernalia and flashback stuff. I thought that was really dope. And I love when movies have character, no pun intended, like that.
+Darius: That's dope, man. What was your favorite Grand Theft Auto?
+Jordan: Wait, did you say what's my favorite Grand Theft Auto?
+Darius: Yeah. That's a question I had.
+Jordan: Oh, that's a good one. I think. I think GTA two is probably my favorite. That's when I played the most as a kid.
+Darius: So yeah. San Andreas for me. Yeah, it was the one set in L.A. with basically Bloods and Cribs, but they just switched the colors around. Ballers versus Grove Street. But it was very set in the 90s. Easy E was a character, but they didn't call him Easy E. He was called, I think it was Ryder. And, you know, I would, I am anti-remaster in general, but if they remastered that and doctored up the graphics, I would run that one back. So I would say San Andreas is my favorite Grand Theft Auto. What else you got for act one?
+Jordan: I got like, so I feel like one thing they just kind of gloss over in the movies that like, his parents are like low key rich. Yeah. Because the fact that you can pay for your kids MIT education out of pocket, and that was only 1/4 of your savings as a police officer in LA is kind of insane.
+Darius: Well, so this is the 80s. College was a lot less expensive back then.
+Jordan: Yeah, that's true.
+Darius: But still, people weren't, I mean, cash out of pocket for the full ride is nuts. Yeah. I would be so infuriated if my child got into MIT and didn't want to go.
+Jordan: And just wanted to chill.
+Darius: I hate all the ******* dudes, all the ******* chases I had to do and crack rocks I had to confiscate and times I had to tackle a dude with a gun in his hand.
+Jordan: Just to put you in MIT. Yeah.
+Darius: And you don't want to do it. This is, man, you be your own people.
+Jordan: Yeah, this movie kind of is a little bit of like, it's low-key a like case study for like white privilege in a way. Because think about when they steal the car, it's like, well, yeah, you can steal a car because your best friend's dad's a cop. It's the 80s. You're white and you're obviously like from a successful family. At least one of the kids is. You're going to be okay if you get caught.
+Darius: Yeah. I mean, they're snorting cocaine. Like it's Pixie dust. Like, this is it's illegal to do. White people and drugs, man. White people just talk about drugs like. They do. Like it ain't that even, like there's no laws against it. I'm like, man.
+Jordan: Just like it's nothing like, and they're so open with it. It's like, you know, like I could be a police officer. I mean, I'm not even like, you know, whatever, obviously, but it's just kind of crazy. Like, it's a lot. Like I can't tell you how many times I've been offered. Coke in at the spot we hang out and it's like, no, dude, I'm cool. Like, yeah, do your thing, bro, but I'm good.
+Darius: I can't say that I have. What kind of vibes are you giving off where you kick you on that stuff? I've never been offering cocaine at the spot. I can't say that I have.
+Jordan: Drunk white dudes in. Maybe I don't know. Drunk white dudes in the when they want to talk in the bathroom, like, no, I'm cool, bro. Like it. You have that. I just came here to pee.
+Darius: And wash my hands. That's a whole lot going on there. What happened to Topher Grace? Is he still in Hollywood?
+Jordan: Yeah. Is he in a show right now? I think he, I feel like he's in a show right now. Let me check here. Cause he was in that show.
+Darius: Spider-Man or something?
+Jordan: Well, he was Venom on Spider-Man 3. He's been in stuff recently. I just can't remember what it is. But he was one person who turned to be normal from the cast of That Seventies Show because everybody else turned out to be weird as **** at the very least.
+Darius: He was in Flight Risk, I guess, which was a Mel Gibson and Mark Wahlberg production last year.
+Jordan: Oh **** okay, I don't know who's in that. Oh, he was in Heretic. That was that horror movie or thriller with Hugh Grant. I haven't been to watch that.
+Darius: Okay, that's what it was.
+Jordan: He was in that show Home Economics for two years, two seasons.
+Darius: And the only normal cast member. What's wrong with the Ashton Kutcher? He's normal, right?
+Jordan: So you know about Danny Masterson, right? Yeah, So Mila Kunis and Ashton Kutcher wrote like character like letters for him.
+Darius: We've done this before. That's what you're. We just said the same thing about Tory. We not.
+Jordan: I know, but sexual assault is different, bro.
+Darius: So for that, dude, show me one judge that's ever read a letter and be like, oh my God.
+Jordan: Well, fair.
+Darius: This is.
+Jordan: It wasn't going to make a difference. It wasn't going to make a difference. That is a little. I don't know, bro.
+Darius: When people's family and friends get jammed up with the law, they do **** like that. And.
+Jordan: Yeah, but it wasn't like it was drugs or like, you know, Something nonviolent.
+Darius: I am not. First of all, the eyes I even wrote it is small. Like if that's what you got for them being weird, I can't get on board with that. That's what people do.
+Jordan: Well, that's fair. She also said something about like she don't shower or bathe or some **** like that.
+Darius: This is my. This is what I mean when like this is why like the cancel culture loss because y'all way overreached.
+Jordan: Now I didn't care. I'm not canceling you. I'm just saying.
+Darius: It's like now it's well you can't you wrote a letter to a judge because your friend who you weren't at the party you didn't do any crimes you didn't do anything you wrote a letter you wrote a character letter to a judge and therefore I don't like you any like that's just it's too many degrees removed they didn't like this is why that whole branch of activism lost because it's just overreached.
+Jordan: So the thing was too was people like were saying that like Topher Grace was like stuck up because he wasn't really super close with the cast for the most part, I guess. And it turns out he just maybe he knew some **** or saw some ****. I don't know. But so that's mostly why I say that. He's a really good actor.
+Darius: He's a good actor and he didn't have, you know, he can be normal. That's fine. You don't have to write the letter. But the idea that like Someone says, well, that cast was weird. And I'm like, okay, what did they do? And you say, Danny Mash, I'm like, yeah, gone. And I'm like, what did Miley Kunis and Ashley Kutcher do? And you're like, well, they wrote a letter to a judge at his sentencing and it says some nice words about them. I'm like, would they, did they participate in the crimes? No. Did they? That's all you got? I just, I don't know, man. I think we might be, we're casting too wide a net.
+Jordan: It's possible. It's possible. No, you're good.
+Darius: That's what people do when someone posts free Tory. You just, that's just what people do when their friends are incarcerated. You would do it if one of your friends got incarcerated. I mean, I don't know what anyone would do, but like, it's not atypical behavior at all. because they know the whole person. And even the most heinous of crimes, people aren't the entirety of their existence isn't their crimes. And they wrote a dumb letter to a judge who probably didn't even read the ****. And they threw it in a folder and gave him a sentence. Like, it's not that deep.
+Jordan: Good point. So the so they steal the car to get to the party so you can kind of impress the girl. that he lied to about his job. He told her he worked at Goldman Sachs when he just works at a movie theater or a movie store.
+Darius: That's the kind of lie 18 year olds tell because like you don't think about how it's going to work long term. You're just telling a lie to get you to the next lie.
+Jordan: To get you to the next. Yes, exactly. He's like, I just need to get to a point where I can talk to you later. And that was his, which is interesting because like, He went to MIT, he graduated, probably did well at school. He could have just said he was an engineer. He didn't have, she wouldn't have asked what company and he could have made-up anything and she wouldn't have been able to disprove that.
+Darius: That's the kind of lies young men tell though, because like they don't. It's just a lie to get you to the next sentence. It's not a lie to set up a story. It's like, yeah, I work on the moon at Goldman Sachs. I do big things there. I wear a nice suit. It's like, okay.
+Jordan: No, that's true. Like I remember when I was, this is like my first adult relationship and I was, I'd just gotten laid off from my first job out of college and I was at meeting some people in my ex's life at the time. They're like, oh, what do you do? And I was like, oh, well, I'm not really working right now. I'm between jobs. What are you in? Like, what's your what fields you in? I was like, oh, I'm in communications. Mass communications. Mass communications. I tweet. I'm on TikTok.
+Darius: Same difference. I communicate to the masses one way or another.
+Jordan: Right. I run an independent social media operation. There you go.
+Darius: Vice president of Darius LLC. You got anything else for act one?
+Jordan: Yeah, I'm the CEO of Jordan Inc. One employee, and he doesn't even get paid. I'm a manager of 1.
+Darius: Sole proprietorship. We have no revenue.
+Jordan: Correct. Nothing but expenses. No revenue, no capital. No prospects or investors.
+Darius: No, just sole proprietorship. One man shot.
+Jordan: One man band over here, girl. There you go.
+Darius: You want to go to Act 2.
+Jordan: Yeah, so where do you have Act 2 starting? When they get to the party.
+Darius: Sure. Act 2, spiraling lives and wild antics. Matt's lives gains momentum as he and Tori spend the night traversing various parties, including one at the home of a drug dealer. His sister and best friend navigate their own complicated night, which includes A dramatic car theft and a disastrous run-in with the law. Matt's fake confidence attracts him to Tori, but the pressure of the live builds. Just, you know, I always want to be transparent with the audience. I did not watch the last 30 minutes of this movie. I couldn't do it. So if you see me veering all the way off topic, that's why I'm not going to lie to you. No, just for the audience. I told you I ain't watched the rest of the **** but I don't want them to think I'm lying to them and pretending I watched something when I didn't. I did not watch the last 30 minutes of this movie.
+Jordan: I hated it.
+Darius: So anything for Rag 2?
+Jordan: Yeah, so there's the scene where they're at the party and you could tell that his friend Barry was just like anxious or nervous because they were around a bunch of people he probably hadn't seen in four years. when you feel like you're not where you want to be in life, you don't want to see people from your past because they're going to ask you what you're doing and you don't want to answer that question. So I'm assuming that's why he wanted to like do the coke so bad. And then there's a scene in the bathroom where he's like, this is ****. And then it hits him and he just walks out the door and you hear the music play and he's just like on some other ****. This reminded me of like, have you ever been at a party and like someone takes an edible and they're like, this is trash. And then like 4 minutes later, they're on the moon.
+Darius: I mean, everyone has a story like that, man. When I was in California, I was dating this one girl and she got me some caramels that were like, they were created for like stage 4 cancer patients, basically. And I ate it Friday and I swear to God I was high until Sunday afternoon. It's just, it's tough. It's tough. So be careful with those things.
+Jordan: No, yeah, I learned my lesson. I was at a show in Fayetteville for a friend's feature a couple of years ago. And this girl had like these gummies and they had like, she'd refrigerate them and then they melted and then like re solidified. So you couldn't quite tell the size you're supposed to take. But I was like, I'll be here for a few hours, whatever. So I finished it and it didn't hit me at all. So I was like, okay, cool. I didn't really drink. So I drive home. I'm like an hour and a half away from home. So I'm driving and I'm at this part in the state where there's just like nowhere to stop it just did not look safe it looked very much like you know and this **** hit me and I was like oh no so I like roll down the window and I have my head out the window like the scene in the dark night with the Joker where he escapes to jail and I'm just like doing this the whole drive home.
+Darius: Yeah man but to loop it back to him like walking it off man you I've been there where like you like you're so drunk, you need like a little pit stop. And so you go to the bathroom, splash your water on your face. And then when you walk out, you're a new man. So I get it. There was a scene, by this point, I really wasn't paying much attention to the movie. There was a scene where he was like about to **** some girl in the bathroom. What was going on with that? And then another guy walks in, I just was just like, this is dumb. What happened there? I want to explain that one to the audience.
+Jordan: Yeah. So he's at the party. A lady can tell he's high. She's like, Oh, you want to do some? She's like, All right, cool. They go to the bathroom. She's fine as hell. So they're about to hook up. And then, like, the dude she was sitting next to comes in and he's like, Yo, like, we're in here. She's like, No, you're with me. So basically, I think they were assuming they were a couple. And that's just like what they do. Like, he was a cuck. And because they recognize that. Barry was like young and dumb or whatever, there's an easy mark. I think that's pretty much what that was, which was insane. Yeah.
+Darius: Have you ever been caught at a party you weren't supposed to be yet? Like your parents told you not to go and you went anyway. Like you ever have your house party moment?
+Jordan: Actually, I luckily I never had any of those moments. I either didn't go or got back in time. I mean, I think I probably broke. I mean, I broke curfew, but they never like found me. They just I dealt the next day or, you know, I was kind of kid where like, if I did something bad, I buy. Yeah, I did this. So you should let's just like, let's just get it. Get it over with.
+Darius: When I was in 8th grade, 87th grade, me and a boy. Quincy, I think his other guy's name was Rudy. Just middle school friends. We caught the city bus to the bad part of town, the hood or whatever, to meet these girls at this party. And it was worth it. But I got a lot of trouble because I don't think we even got to the party to like 11 o'clock. Mind you, we're like 14 years old. 11 o'clock is like 4 A.m. Yeah, that even, like it was. We had, I snuck out past when I was supposed to be in the house. This is before cell phones. So my mom had to like call around and I didn't get to go outside for a long time after that. But the house party with the girls?
+Jordan: Yeah, you kind of got to.
+Darius: It was worth it. was worth it. If you are, you know, it's a seminal moment in a young man's life. Yeah. risk life and limb to *** ****. I did not *** **** that night. I was in middle school, but I thought I was. I had comments in my wallet. It did not happen, but I definitely thought I was.
+Jordan: That'd be the worst when you like, when you bring them and you're like hoping and you just know, and then you go home with them still and you're like, damn it.
+Darius: I mean, I was in middle school. I just, I brought them everywhere. It's because middle school.
+Jordan: Yeah, I feel you.
+Darius: He just just, you know, a ***** teenage boy. And, you know, always got to be prepared. But no, that was a good party. It was a good time. But I definitely paid the price for it in my freedom for a long time after that. So anything else rag to?
+Jordan: Yeah, I was someone ask you, would you have told her was when he when hooked up with Tori and was like, Yeah, so I actually work at the video store. I saw you earlier today. Would you have told or would you have just kept them?
+Darius: You're asking 22 year old me or 37 year old me?
+Jordan: 22 year old you.
+Darius: I would alive. I kept that lie alive. Yeah. 37 year old me would have felt that that was inappropriate and deceptive and came clean. But I would be lying to you today if I told you that 22 year old, 22 years old, I was as honorable as I am today. Yeah, I would have just lied. I just thought like a 22 year old man. Just think one line to get me to the next line and go from there. So.
+Jordan: Right. And then also it was like you waited, like you did it right after too. Like I think I maybe would have told her like I would have taken her out and then maybe I would then I would have told her maybe it would have felt that would have been a smoother landing than like right after because it just makes her feel like a conquest.
+Darius: I would have tried to follow time off that lie. All right. I've had my fun. And the truth.
+Jordan: And the truth is, it's the 80s. It's so easy to ghost people. You just have to don't call them. That's it.
+Darius: Yeah. Like, 22 year old me would have been like, I mean, what's one more? I'm going.
+Jordan: What's one more? You already did it once, you know? Yeah.
+Darius: She likes me. I'm going to blow all this up by telling her how we're going to video for what?
+Jordan: And also like the odds of you ending up together forever are astronomical anyway. So, you know.
+Darius: Let me get one more hack at it before we.
+Jordan: Before you never click this back one more time before we pack it up.
+Darius: No, I lied. I kept that lie alive. What else you got cracked too?
+Jordan: Have you ever been involved in a dance off? No.
+Darius: No. Absolutely not. I'm not having a problem with dance off. But me, no, not my speed, not at all.
+Jordan: What's your go-to dance moves?
+Darius: No, I will say I will forever be resentful of COVID because that was the one time a popular dance came out and we were inside. Okay, it was the one time The TikTok popular dance I could actually do came out. Did you do the Tootsie slide? Oh yeah, We were in the house and I was like, what the ****? I could actually do this one and I wouldn't look stupid. And we're locked in the house. That is the most, obviously.
+Jordan: That's funny.
+Darius: I will say that is the thing I resent most about COVID, which kind of reveals the privilege of my COVID experience. But Correct. I was mad. I was like, this, I can do this. And I won't look stupid. Even Roger Goodell could do this.
+Jordan: Right.
+Darius: And we were inside. And so now, I mean, And that's talk about a song that got lost in history. It did.
+Jordan: But I haven't heard that song anywhere ever. And it was since.
+Darius: As hot as a song could be during COVID.
+Jordan: Right.
+Darius: So that is my thing. All I did in during COVID was man was bake order sneakers because the sneaker market was dried out because no one else was buying sneakers going anywhere.
+Jordan: Yep.
+Darius: And ordered a lot of Uber Eats and Grubhub and.
+Jordan: Yeah.
+Darius: Drank too much and baked a lot of things and loved my sneakers.
+Jordan: Yeah, that's when I had my first pod. I did that. We would like to get drunk and record the pod. I went some of the times, did that. Watched movies, took walks. I would just drive. I just get up in my car and drive just up and down Glenwood Avenue for hours. You couldn't get out and go anywhere. Yeah, man, it was awful.
+Darius: And the thing is, it was only the inside part was only like 60 days. It was from March to May in North Carolina. But that **** felt like a prison bid because I would get it would be like Saturday because I work from home already from my previous job, previous role. But like when you don't go out like Saturday, my going out was just like a walk. And I was there was this podcast. It was They discontinued it now. They did like the Tyler Perry cinematic universe and they would watch his movies and talk about how bad they were. Jinx. And I just remember walking around the ******* arena. I won't name the arena because I would get my location up, but it just just like, this is my Saturday night, just walking around. And I'd get it out at 7 o'clock and that would be it. And then I'd call myself, it was either Jameson or tequila and watch, and there wasn't even no sports to watch. And just, that was, I don't, that **** is trash. Anyways, Tuesday Slide.
+Jordan: It was, yeah. that was a bad time. I remember I got so bored at one point. I would just like, I think back when I was, I worked pizza part-time, whatever, and I would get off work and I'd drive downtown, I'd go to a cigar bar and the inside area was closed because it was COVID. So they had literally, it was wintertime and they had like a heater outside. People would just sit out there and smoke.
+Darius: And even when things opened up, it was like half of what you were used to and just everything sucked. Anything else back to or you want to go to act three?
+Jordan: Oh yeah, so I did, I did isn't a much like that kind of the 80s 80s movies I did like the uh they had all the party archetypes like they had like the the philosophical like Stoner dude where he's like everything changes but nothing changes and you had like the crazy thought you know and the the uh the preppy white boys with the the turned up collars and you know all that um also the the preppy white dudes remind me of every guy I went to high school with.
+Darius: I agree. That was a nice touch on a movie that otherwise didn't care much about details. Act 3, the unmasking and the reckoning. The night culminates in a massive party where Matt's lie is exposed in front of everyone. including Tory and his father. He must face the consequences of his deception and decide whether to chase the life he wants or the one he thought he should have. The movie ends with Matt making an honest choice about his career and his relationship. And let me just say, drowning in a ball got to be on 1000 ways to die. Like you're just rolling around having a good time. And then that water starts to level. I just. Yeah, that's got to be up there, man.
+Jordan: That's a really bad way to go.
+Darius: But, you know, I watched a video on YouTube and there's apparently an exhibit in a museum somewhere. I forget where you get to like sit down in like a what would have been the Titanic ship and get to feel what it would have felt like if you were on the ship when it was like sinking. And they're just like sitting there and the water just it's just rising.
+Jordan: And there's nothing you can do.
+Darius: There's nothing you can do. Like you're so far away from the top, let alone the The life raft and that water is ice cold. Yeah. And that's just it. Like there's that's it. This is your fate. You're you got about 90 seconds left on Earth.
+Jordan: And you're a popsicle. Like that's a really, really bad way to go.
+Darius: That's that's rough. That's rough.
+Jordan: Yeah. And Rose definitely had enough room on that ******* door to let Jack live just for the record, but for sure, for sure.
+Darius: But yeah, man. And then not only that, but you got to realize no one's ever going to find your body. No, it's like your people aren't even going to get a proper burial or anything. This is just it. So true.
+Jordan: And then also there's no communication really back then besides by letter. So like if you didn't tell your family you were going on the Titanic. Like you were ******. I mean, you were ****** because you died, but they were ****** because they didn't know what happened to you. Probably. There's still.
+Darius: A few people from 911 who are still technically missing because they the family can confirm that they like lived in New York at the time and would have been in the area. But they have, you know, this is before you were sharing locations and texting people all day. Right. They're like, well, She lived in that borough. Like you kind of know that they probably got caught up in 9-11, but there's no real proof of it. So technically they're still missing. Like by now they probably have death certificates and everything, but for about a decade they were still missing, you know. That's crazy. Yeah. Cause how else, you know, You grew up in Indiana and you send your kid off to college in New York City and they just had to stay. And then on 9-11, they text you in the morning. Hey, how's it going? You know, I'm going to go get some coffee and then head to work and then you never hear from again and you never get their body because everything's pulverized.
+Jordan: Yeah.
+Darius: And you never get that close. You don't know. Were they in the building? Were they near the building? Were they, you know, you don't know anything. You just have to wait until the state declares them dead. So that's sad. I concur. What else you got for act three? I will say this. The fact is that I didn't watch the last 30 minutes. I've at least had things to say.
+Jordan: Yeah, you have been on topic.
+Darius: No, but it's not.
+Jordan: You're like, Man, Spades is fun.
+Darius: Yeah. What's your favorite Grand Theft Auto game? Well, we'll get back on topic. What about Act three?
+Jordan: So I did like the conversation that he had with his dad after he got arrested or when he was getting arrested, I guess, whatever, where he's kind of where he's letting him out the car. He's like, dude, just take a ******* shot, bro. Like shoot your shot with life, essentially. And again, where he said like, you're not a fairy because you're worse than that because you've never tried at anything. I do always like that conversation that he had because I feel like that's pretty relatable. And I think I was around the same age when this movie came out. I was like 19 or 20. So I was kind of in a similar place in life. So that always hit stayed with me a little bit. But yeah, I mean, there's not a lot that happens in 30, honestly. It's really to see rise the ball, survives. His sister breaks up with the ********* boyfriend played by Chris Pratt. And then he gets the girl's number, which I will say, getting a girl's number after you hit is kind of legendary.
+Darius: And what name do I put in this? Well, it's 88. So the number was the house number.
+Jordan: The house phone, yeah.
+Darius: You know, you had to have some real, that sometimes the number came afterwards. Oh, I was born in 88, so I wasn't around at the time. But you know, it could have, I understand how logistically that might just be the case. True. Yeah, man, the talk with the pops. I remember mine. I remember, sitting in the basement playing **** ironically, Grand Theft Auto San Andreas, and my dad sitting down with me and asking me, okay, so like, what? What's the plan? So I'm forever grateful for that conversation, too. But I remember that conversation vividly. Another seminal moment in a young man's upbringing. Yeah. Yeah. Anything else? Factory.
+Jordan: Yeah. Okay. So, yeah. So let's pivot. Let's pivot off that then. So you had the conversation with your dad, I guess you were like 18, 19 time period.
+Darius: Give or take. Yeah.
+Jordan: So what was not different? I guess what was the connection for you? Like we have to talk about like locking in and I think I'm guessing you're just like in happened to some point in your mid-20s. Was there something that he said that you didn't really click for you later on in life or was just like your maturation process that kicked in and you were finally able to kind of connect all the dots?
+Darius: Well, it just he Yeah, I just, I don't, he, the quote was, you don't want to be one of these do nothing. And he said, those kind of dudes that just, they'll work a job here and there. They'll kind of float by and then they just come and go. And that's just kind of it. He was like, you want to put your stamp on life. You want to go do something. You want to go be something. You don't want to just float around making ends meet. And I mean, honestly, it kind of clicked in almost immediately. Because, I mean, very shortly, because at the time I was working at GameStop and I was, an assistant manager. I had my key. I made my little $10 an hour and I thought that was life and, very shortly thereafter, I went and applied at another, at a place that I can't say. And, that's when I don't, I just got really motivated after that. Like I just, that place gave a pathway to like, you could actually see a pathway to like middle class stability and a career. And I just, I just really wanted that. And that's why that conversation stuck with me because it was like, I thought I was doing well. I thought I was doing fine. I was an assistant manager at GameStop and I was, you know, I still, He was like, Nah, you're not. This ain't it. Right, right. Yeah, you, you. It's like he could feel that I was getting comfortable in mediocrity and he just was like, we don't do mediocre.
+Jordan: And so yeah, the same what we do.
+Darius: And so, yeah, that's kind of what it was. It was like I could it was a disappointment and it was like, you</t>
+  </si>
+  <si>
+    <t>Jordan: Hey everybody, welcome to the Out the Trunk pod with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's D's our lucky area on all socials.
+Jordan: And today we're going to be reviewing the drama, which came out this year, written and directed by Christopher Borgli. It stars Zendaya as Emma, Robert Pattinson as Charlie, Alana Ham as Rachel, Mamadou Effie as Mike, Sidney Lemon as Pauline, Hannah Gross as Alice, and Anna Baryshnikov as Sam.
+Darius: You're impressive on those names, man.
+Jordan: Right? Pretty good. And they said we can't read.
+Darius: There you go.
+Jordan: The drama takes place days before their wedding. Emma and Charlie seemingly solid relationship is shaken by an unexpected confession from Emma's past. As celebration turns into uncertainty, Charlie must decide whether love can survive doubt, moral judgment, and the frightening realization that he may not know his fiance as well as he thought. So I'll toss it to you for act one.
+Darius: Act one. The perfect week begins. Emma and Charlie appear ready for marriage, surrounded by wedding clans, close friends in the comfort of a relationship that seems stable, romantic and fully understood. First observation, Zadaya can act when people let her. When she's given some space to stretch and she's not put in a box. I was very impressed with her in this movie. She held her own and never stood out like a sore thumb. And it was actually a lot of emotional, like this was a tough role.
+Jordan: It really is.
+Darius: And she held her own and I didn't think she had it in her, given her output lately. shout out to her well said what you got for act one yeah that's she was really good.
+Jordan: Uh I think uh once she got away from Sam Levinson and that Euphoria set she was really able to like fully be an actor you know after leaving Disney um you know growing up obviously um yeah first observation about this movie this movie uh was paced incredibly well um it feels like a hour and 40 minute panic attack. The stress and anxiety that you feel in this movie is like insane. Like the first time I saw it, I was like, what the hell is happening? Like I legit was like, is my life ruined? Because that's what I felt like watching the movie. And even watching it again for the pod. When it starts to go where **** starts to get left, I started to feel stressed. I'm like, I don't think I can handle this. I had a rough week. I don't know if I can mentally do this. So that's testament to the great writing because you really feel everything that every character is feeling.
+Darius: It perfectly captures the falling in love, but it kind of, they do a good job of making you feel like something is amiss before you really know what it is because I don't know about you, but I didn't know what this was. I just.
+Jordan: Me neither.
+Darius: At this point, if Robert Pattinson did, I'm giving it a fair shake. And I just kind of was like, well, okay, what do we, is this like a rom-com, but it's not romantic? It's not what's going on here. It's like a, it's very gray for lack of a better word.
+Jordan: Yes.
+Darius: It just felt like you just knew the mood was gonna shift. But let me just start by saying that the opening scene She's deaf in one ear and you just can't, you don't pick that up right away. But when she turns around and just like, he's fumbling all over himself because he ****** **. He thought she was deaf. He's lying about having read a book. We've all done that. Right. Dude, nothing's more relatable than lying about saying you read some book to get it. Right.
+Jordan: Deep performative male right there.
+Darius: And so And she just looks at him and she's like, you want to start over? And I was like, that was so, I love that.
+Jordan: Was really, really nice. That was, that was like a such a kind gesture. And it's funny now because like, I just really thought of it like, that's what like, she does it for him the entire movie is do you want to start over? Like, and just how important that message is in the course of the relationship I mean we'll talk more about that later but yeah she like I thought that was great because like it's peak awkwardness because she walks away he goes to the book she left on the table to take a picture of it so he can Google it real quick to talk about it as an icebreaker he's talking to her she has one headphone in he realizes he thinks he's bombing but he's not she can't hear him you know and then when she starts talking he's like wait what the **** I'm sorry I'm not hitting on you like just like the perfect like display of awkwardness and like it was so well done because like in the movies, it looks so cool or whatever. It's like the truth in real life, it is nerve-wracking and it is awkward and you don't know what to say after you say hello and your name. Like it, because you can literally say anything and **** it up or make it go well. So I love the way they perform that scene.
+Darius: And let it be a lesson for you fellas. If she likes you, she'll help you out. You know, like there's no, None of us are that smooth as that in the movies. But, you know, she likes you. She'll help you out. She'll point you in the right direction. But like, I just thought that was really cool that she.
+Jordan: Yeah, me too.
+Darius: Clearly found him handsome in some regards and charming. And she was just like, swipe the slate clean. Let's let's.
+Jordan: Yeah, let's just.
+Darius: You know, I'm deaf right away.
+Jordan: Yeah, I love that. Have you ever had a girl do that? Something that for you in real time.
+Darius: Not that overtly, but I have definitely bombed in a way that she kind of laughed and cleared the deck, if you will. just like control alt delete.
+Jordan: Yeah.
+Darius: I could see like her laugh was like the. the cut paste and clean, clean document, control A, cover it all.
+Jordan: Control Z, undo.
+Darius: Yeah. And never, straight up want to start over, but just like a laugh. And how about this? And then she starts talking and then I can, and that's me ground myself, get my bearings about me and kind of even, and it's a signal to me to just chill and, you know, go places with that. But certainly not that movie, not cinematic. But yes, right. How about you?
+Jordan: Yeah, for sure. I remember I was at a mic one time and I saw this girl. I thought was cute, you know, and I kept like stealing things throughout the night, you know, and at the end of the night I kind of just like introduce myself and Instagram. And then I was like, I want to come on too strong. So I was like, Hey, like, I may hit you up on there, like, if you're cool with that. And then she was like, Just take my number. I was like, okay, cool. Save me a day.
+Darius: Yeah, I mean, I don't know if I'm showing my age. I'm not asking for, I'm a grown man. I'm not asking for your Instagram. Like, it's like we are not, I'm not here to like your posts. I'm here to talk to you because I like you think throughout the dinner and we are not, we're not, we're skipping the whole, let's like each other's posts and no.
+Jordan: Yeah. This was 29, this was like 2019. So I was like 27, 28.
+Darius: Okay, that does reframe things. And then I'm not a native social user, so it is different. But man, like, oftentimes I'm getting socials after we've already been out and ****. Like, cause I just go straight to numbers. If she's not wanting to give me her numbers, she don't let me know. So like, I don't really need to be looking at you. Me post nothing interesting anyway. So, but yes, I have. I can't remember. Well, if it if it started on Instagram first, it was usually I can't remember anyone. I've I've never got an Instagram first. It's always been a number first. But I've met I've gone out with women I've met on Instagram, but it was usually.
+Jordan: Yeah.
+Darius: In a casual, friendly setting and then, you know, like go to something else, but never. Yeah, I have your Instagram. That's yeah. as young dude stuff. So what else you got for act one?
+Jordan: Oh, yes. I love the scene where they show him, show him and her working on their vows, you know, with their separate friend group. And he starts to tell a story about how he whispered in her ear to like test if she was deaf or not. And he's like, I love you. I want to marry you. I just don't know how to say it. I'm petrified to ask. And then Because his boy and he's crying. He's like, yep, no, that's all. That's pretty good. Yeah, I think you got it.
+Darius: Shout out to, what was his name? I just say black dude in the movie.
+Jordan: Mama Do Afi. Mama Do Afi.
+Darius: Talented guy.
+Jordan: He was really good.
+Darius: He was really, really good. We'll pick it up later, but like he kills a scene later in the movie that is the whole movie. But I hope to see him in some more stuff later. Yeah, he was great. He was really good in this.
+Jordan: Yeah. 24 to hold on to him.
+Darius: You know, sharing that. I don't know, man. Writing vows just seems so personal and intimate. I'm not sure if I would just, like, want to share that before the actual wedding day. Yeah.
+Jordan: But, you know, I feel you.
+Darius: Who knows? I don't know how these things go. I never been married, so. Yeah.
+Jordan: Yeah. One of my friends weddings last year, they they did a portion of theirs, like, actually in private. which I thought was kind of cool. And then they did a version or a different part of it, I guess, in front of everyone I thought was pretty dope. You would you write your own vows or you would just go with the standard?
+Darius: I mean, I wish I could hopefully go with the standard. It covers all the bases. You know, I'm not a creative writer, so if she's cool with the standard, we can just knock that out for better or worse.
+Jordan: Yeah.
+Darius: Sickness and poor death does part that covers it.
+Jordan: Amen.
+Darius: You know, I don't really have anything to add. No notes. Clearly, you'd write your own.
+Jordan: Jesus is my ghost writer.
+Darius: Yeah. You know, like, I don't know, man. If ain't broke, don't fix it. So I feel you.
+Jordan: I'm not mad at that. Because I think that's all I got for act one. You have anything else for act one?
+Darius: Nah, I mean, head into act two. The movie begins, basically. Truth enters the room. A private revelation changes the emotional temperature, forcing the couple and their friends to confront trust, forgiveness, and a difference between past mistakes and present identity. Given that this movie is a little bit on the more obscure side, I'll go ahead and explain that basically they sit down, they get drunk. bridegroom, maid of honor, best man. And they all just in stumble into a conversation that no one should ever have. And it was like, ever, ever, ever. Like secrets about yourself that nobody knows. And some lady like put a handicap kid in the closet, forgot what black guy did.
+Jordan: But his girlfriend was getting bit by a dog and he like, oh yeah, got her out the way.
+Darius: Yeah, don't do that. Not chivalrous at all. And Zendaya's character, Emma, said that she planned a school shooting and just didn't go through with it. So talk about a big joker.
+Jordan: Right.
+Darius: And by planning, we don't mean like contemplated it. Like she had videos.
+Jordan: No, she did. She like recorded a manifesto.
+Darius: Yeah, had a manifesto, had videos, was practice shooting guns. She had done enough to be arrested. Like it was not. If they arrested her, it wouldn't have been like a thought crime. Like she actually took actionable steps towards this. And so that's bad, which brings us to my first observation that, it's okay to lie a little bit. Everybody don't even know everything.
+Jordan: Yeah, please. She'd even better off being like, I had a train rent on me.
+Darius: Yeah. You know, Dave Chappelle episode where like man on the streets and he's like, He stops a couple and he's like, what's the wildest thing you ever did? And the dude just says something normal. I got drunk. And the girl is like, I had a train ran on me in college. It did. Well, they asked her first. And she said, I had a train ran on me in college. And they asked the dude and he's like, having sex with ******** here without a rubber.
+Jordan: Oh, yeah, that's right.
+Darius: You know, it's just.
+Jordan: Yeah, some **** you just take to the grave.
+Darius: It was, I'm assuming these characters in their late 20s. So this was 10 years ago, maybe 15 years ago. 15 years ago. You've grown out of it. Yeah.
+Jordan: Maybe leave that one in the dress. I would have. Yeah, man, for sure. 100%. Even the next day, I'd have been like, sometimes I get drunk and tell crazy lies.
+Darius: I think she tried that.
+Jordan: Yeah, she did. She was like, I'm just drunk. And she was like, oh, so that makes it okay.
+Darius: Yeah.
+Jordan: No, that **** was crazy. And I love how even though when she explained it, it's like, of course it never ever makes sense. But like sometimes you like in certain movies and shows, you're like, I can see how they reach a breaking point. With her, it was like, Two things that happened.
+Darius: I didn't do a good job of setting her up. Or maybe she just wasn't an empathetic figure. Maybe she just. Which brings me to astute observation that I didn't catch the second time around. She doesn't have any friends. All of her friends are through him. Her maid of honor.
+Jordan: ****. You're right. You're right. Yeah, you're right. You're right. Damn, you're right. Because of the wedding vows. She said we met her. Damn.
+Darius: She has no friends.
+Jordan: And you're right.
+Darius: Your maid of honor you met through your husband or fiance. That is genuinely bizarre.
+Jordan: Is a huge red flag. That is right. I didn't think about that.
+Darius: You don't have any, not a sister, not a cousin, not an auntie, not a college roommate. She had no friends in this movie. The wedding was all his guests or people she met through him and like her dad.
+Jordan: Yeah. And then her. She had that one friend from work, but that's from work. Yeah. I didn't think about that. ****. And yeah, that's crazy.
+Darius: It's the second time too. I was just like, I didn't unpack this and I haven't yet, but yeah. I feel like that's on purpose. Obviously, clearly no stone left unturned, but it gets to the what I'm, you know, question in the third act. But yeah, man, it's.
+Jordan: Damn, you're right.
+Darius: It's hard to believe. I want to what happened. She had no friends in middle school. Okay, fine. But like, she didn't make a single friend until she met him. And yeah, that's a bit of a real.
+Jordan: Life based on what she did for work. That's yeah, that's crazy.
+Darius: And she's true. Exhibited a short temper a lot of times. Yeah, she did. Yeah, she wanted to fire the DJ for using drugs.
+Jordan: Doing drugs.
+Darius: Maybe not. I don't know any DJs that are sober.
+Jordan: Yeah, to me, if it was, you know, the what the officiant of the ceremony for sure fire them if it's a DJ that just tells me they're a good DJ I'm gonna be honest with you um.
+Darius: Also just like the idea that like I kind of might have saw you doing drugs totally unrelated to the event right what is that?
+Jordan: And the wedding's in a week.
+Darius: And the wedding's in a week and it it it It reflects a sort of impulsive anger management issue.
+Jordan: Yeah.
+Darius: When given what she was planning before.
+Jordan: Right.
+Darius: It's, you know.
+Jordan: Yeah. Okay. I hear you.
+Darius: It's some, some, some, some, some flares are going up, you know.
+Jordan: Yeah.
+Darius: But was she a friend too?
+Jordan: Right. So I meant to bring up for act one. So the friend, the girl, what was the character's name? **** Rachel.
+Darius: Yeah.
+Jordan: Is this me or did you feel like she always hated Zendaya's character? Yeah, I feel like the entire time.
+Darius: Hated. No, but given the time, I just didn't think she was like, it's one of those things. Not skeptical. It's just like one of those things where it's like your your your boyfriend's best friend meets a girl and she's just a little too. I don't know, personal and comfortable. And it's like, you want me to be your maid of honor? I barely know you. Sure, I'll do it because I don't want to be * **** ***** it. But it's just like, she's just weirded out a little bit like anyone would be to be.
+Jordan: That's very. I never thought of it from that perspective, honestly.
+Darius: You know, it's just like, you know, you know what? We'll be out right at the spot.
+Jordan: Yeah.
+Darius: And there's the people we're close with the five or six inner circle. And then there's like, Someone will come up that we barely know, maybe know, don't know, whatever. And they'll just chat and they just kind of sit down and we're like, stay there. They'll actually want to talk to you. Yeah. And we really. So it's just kind of like, I just felt like that.
+Jordan: And we can't have our conversation anymore because you're here.
+Darius: Right. And it just, I just, and like, this is a good example. Like, I love sports as much as the next person, but it's seemingly the only thing he could talk about. And so it's just like, that's the kind of energy I'm getting. I'm like, from her and her. And it's like.
+Jordan: Okay.
+Darius: She kind of is cool, but like.
+Jordan: Why not fly like that? Yeah. Okay. That's a good point.
+Darius: That's a good point. It's just I didn't get hatred. I got.
+Jordan: Yeah.
+Darius: You know, just a little too familiar, you know, like maid of honor is a high praise, a high position.
+Jordan: And yeah, that's a real. Yeah.
+Darius: It's just. It's not something you want to do flippantly and to just thrust that on someone you haven't. I mean, a year, maybe, you know, it's just.
+Jordan: Yeah.
+Darius: You're right.
+Jordan: That's a good point. I didn't think about that. And then she was. And you know what? I think this might have been her first relationship, too. Because if you think about when they were at the table and they were doing the vows, And she was like, I'm about to cry, whatever. And then she said, like, she had like a, she's having a panic attack when she realized how much she had feelings for him. And they're like, is he like your first like love or? And then she's like, I think my first crush. And she was like, you're 30. So basically like she's just had a very lonely existence before all of this.
+Darius: And I just think the best man in the maid of honor, their spidey senses are just tingling about her. And they're just like, there's something about her. That's a little off and it gets confirmed with the school shooting thing. Yeah, I just think they were always like. She's weird.
+Jordan: You know what? That's that. That actually changes the way I viewed the movie now because I felt like she was like on some haters the whole time. And then I felt like when she found out about the planning of the shooting that she was like, yes, ha ha. I finally had a thing I can like really like, like just. expose all the hate I actually have had for you this entire time.
+Darius: You ever have your homegirl meet a dude and you're just like something about him? He ain't done nothing wrong. But I'm not going to say anything because I won't feel like a hater. And right. You know, I don't want her and she's happy. But it's just something about him that that just doesn't like, you know, you're like, your spidey senses are tingling. And that's just kind of what I felt that they had for her the whole time. Yeah, that's great.
+Jordan: I think you're right.
+Darius: Nothing actionable, but just the gut feeling that this is something is off here.
+Jordan: Yeah, I think you're right. Yeah, because even like when she's like, my cousin got shot and it's like, well, one has to do with the situation. But I think I think you just were like, you know what? Not going to let it rip because I thought you were weird the whole time. But I guess because I think cousin Day is just so likable that you like she naturally becomes sympathetic, even though the character may not actually be sympathetic because they didn't do enough. They didn't do a great job of building up why exactly she could get to that point. Like, for example, a joke about 13 reasons why. And there's a kid who gets bullied throughout the course of the show. And he starts to rebel and do teenage **** like vandalism and **** to kind of get back at some of the other kids, whatever. And then he gets found out, he gets suspended, comes back to school, he's rehabbed and trying to really be a normal kid. And they do some physical abuse to him with a broom. And so he plan to do that what she planned he pulled up to the school dance with a with a bag a duffel bag and some of his friends like talked him down from it you know whatever it's like in that situation was like you kind of wanted him to go through with it because you know what it happened to was so traumatic in this situation I just I they didn't do a good job of building up why exactly she had planned this in the first place not that this is whatever be excuse but it's just like you know.
+Darius: Is the 13 reasons why on Netflix by chance?
+Jordan: Yeah, it is. Yeah.
+Darius: That's sort of overly heavy-handed explanation sounds about right for Netflix. I as you're explaining, I'm like, this is really on the nose. Right. Nice little call back there, but I do think they did a little bit more seasoning on it, but I'm glad they put that heavy-handed.
+Jordan: Yeah, for sure. For sure. Yeah.
+Darius: I do think they dropped some nuggets in that. I don't think there was a reason. I think she was just a crazy *****. I really do. Like, someone bumped into you and you dropped your book. Yeah. I do think it needed a little bit more seasoning though. The movie was short. It was an hour and 40. So, you know, I could take it to two hours and put a little bit more seasoning on it. I'd be cool with that.
+Jordan: Yeah, I hear you. You know, it's crazy, though, because I've been like liking tweets about it. So I've been seeing more of the discourse about the movie online is everyone's like viewing her character as a sympathetic figure and everyone else is the ******* in the movie?
+Darius: Don't be watching these movies, man. They be scrolling. You know, it's a dialog heavy movie. There's not a lot of action sets. How many people talking about the movie have actually seen the movie? And how many saw it without scrolling their phone? What were you saying?
+Jordan: Like there are several memes of the girl, Rachel, character Rachel, the picture of her with like the evil face and the glass of wine at the reception. And people are like, this is the real villain of the movie. And you know.
+Darius: I don't know how much that is.
+Jordan: And her character wasn't likeable, but you know.
+Darius: No, and the wedding toast is inappropriate. However you feel about her, just don't go. Yes. You know, don't go.
+Jordan: I'd rather you do that.
+Darius: But also a lot of discourse is that like Zendaya is very attractive and this lady was kind of not. And so it's like she's being mean to the pretty girl. Yeah. Not to say this woman was ugly, but clearly like there are levels of Zendaya.
+Jordan: Zendaya is. Right. Correct.
+Darius: No, I don't know these people, so I don't want to cast aspersions, but like I wouldn't question one's media literacy if they think that the maid of honor was the bad person in the movie. No, she shouldn't have given that speech. We'll get to that later. No, that was a totally appropriate move. Watch the movie, people, and watch it without your phone. Put your phone in another room, sit down and watch it. It's again.
+Jordan: Remember that it's not Zendaya.
+Darius: Yeah, it is a character in a movie. acted really well.
+Jordan: Yes.
+Darius: And in a way that I thoroughly enjoyed. So while we're in act 2, I just figured throw this here. Robert Pattinson might be like our Daniel Day-Lewis, like a person who just kind of does For sure. Well, I mean, Daniel Day did Abraham Lincoln, so I don't know.
+Jordan: True.
+Darius: But he's going to be the person that just does like obscure artsy stuff and pops in to win an Oscar every 10 years. And he's going to work a little bit more than that. But I'm very, very excited about him, man. He's extraordinarily.
+Jordan: Me too. I think he's the best actor in the world right now. Artist objective, of course, and have a lot of actors I love. But like to me, like if he's in the movie, I'm going to see it.
+Darius: Do you think he could carry like a two hour epic like you think he could do like well he wasn't in that like you think he could be the main character in like a two hour movie where he's in 80% of the Saints?
+Jordan: Yeah absolutely absolutely to me the second-half of the movie is really just his movie uh where he's just freaking out the entire movie and I I think his his range what he can do with his voice we can do with his face the like He has two back. that scenes where they're cut together of him crying and they're completely different cries like I know I know that probably not worded greatly but like it's just insane like you know what I mean you.
+Darius: Have to watch the movie to get it he's extraordinary in this.
+Jordan: Um his range is insane like like in Mickey 17 he plays his character's cloned like a million times over of course you've seen the movie and but like each character is visually different like they almost seem taller like he like the way he does changes his body for roles and like I think he's I think he, I don't think there's anything in regards to a genre or film or performance that he can't do.
+Darius: I agree. You still got to see him do it though, because it is, it is something different to do Marty Supreme, to do, you know, Wolf of Wall Street, to do Sinners, to do.
+Jordan: Yeah, for sure.
+Darius: To be the main person on the screen for 85% of a movie where you're just talking and no one's bored. You know, like that's hard. That's the last level of of movie superstardom and those roles get Oscars. And I think he can do it. I mean, he's young.
+Jordan: Oh, yeah, for sure.
+Darius: But it's got to see him do it. I think he can, though. I really do.
+Jordan: Absolutely. Yeah. So one of my favorite scenes in the movie, because this movie is like very, very funny in like a dark and creepy way, where they're right after the have the big, wine scene and everything goes to hell. And then they're at the photographer and she's like, so I'm going to shoot you. I'm going to shoot you. I'm going to shoot your mom. I'm going to shoot your dad. Where's grandma? I'm going to shoot your grandma.
+Darius: And then they proceed to have the most painful photo shoot I've ever seen.
+Jordan: And she's like, Zedaya's like, and she's like, yes, put your hands on his chest. look at that diamond girl.
+Darius: Let's get some music in here.
+Jordan: And the poor lady in the back is looking at Robert and she's just like.
+Darius: Happy on wedding day. You ever go to somebody's house and you can just tell they just fighting. Yeah. It's like, do you want me to come back? Because I can't. I really, it's not a big deal. Clearly you're kitchen in the air.
+Jordan: And yeah, dog.
+Darius: You might have got the invite 2 hours ago and you said, I'm going to pull up at 7 and you just kind of did. And you sent them like, I'm on my way to bait and response. So you just show up because that's what you everyone agreed to. And then you're like, oh, maybe I should just go take a lap. You know, like, yeah. Or even like, come back.
+Jordan: Or even like if you've been at a party and you can tell the couple that gets to the party just got done fighting. Like, you know what I mean? That type of stuff. I remember, yep, time to go.
+Darius: I could have caught that hit a little earlier. But let's get this trade back on the tracks. That was funny. The awkward photo shoot was funny. And that's a difficult scene to do to be awkward on purpose and not look fake. Again, man, I can't, you know, I'm beating a dead horse here, but the two leads in this movie were phenomenal, you know?
+Jordan: Yes, they were. he wants to smile so bad, but his body won't let him. And she wants to pretend, but she can't pretend by herself because then she looks crazy.
+Darius: This is like 3 days off from the wedding, Right?
+Jordan: Like this is just like peak worst timing ever. Another one of my favorite funny scenes is where he's like replaying all the time. He's replaying like that montage of him with like her younger self. as a couple.
+Darius: Yeah.
+Jordan: And they're on the like watching like romantic views and ****. And he just was like, just completely exasperated and just like, what the **** am I marrying? That scene was pretty funny, too.
+Darius: You know, he's he's kind of stuck at this point. You ready to get tag three?
+Jordan: Yeah, he really is. Did you have the DJ and the co-worker scene in act three?
+Darius: Yeah.
+Jordan: Okay.
+Darius: All right. Act 3, wedding day reckoning. With the ceremony, with the ceremony approaching, Charlie and Emma face the full weight of uncertainty, deciding whether fear, judgment and unanswered questions can coexist with commitment. The coworker scene we were just referencing, you know, technically speaking, Charlie was the only one with like a genuine betrayal here.
+Jordan: Yeah, right.
+Darius: Her issue. Like she never did anything to him at all, really. This is 20 years ago and it's certainly disturbing. But, Charlie, Charlie, Charlie went for the goal. I mean, at that point, you might as well do it. You're not really. I don't think it's going to make a difference. Clearly it did. But what she got for actually that?
+Jordan: Yeah, you're going to take that *** but you might as well have, you know, might as well. They have finished. And even like the way she's just like, after they finish, like he decides to not go through with it. She would tell she still was down. She's like, you ripped my shirt. Like, and she just like slowly walks away. She didn't run out in shame, you know, whatever. And then they have to go see the DJ. And there's that awkward firing scene where she's like, it doesn't matter. We're not going to call the police. But like, we did see you smoking crack outside.
+Darius: I just I struggle to understand what the big deal was. Well, I do understand that she's crazy. And so that's what she clearly does not do well with surprises. Things not going her way. Or just like when you have to deal with other people, you deal with there's variables to it. And she doesn't have any friends. She's never been in a relationship before. And so she's just not used to variables. And so Yeah. So I don'</t>
+  </si>
+  <si>
+    <t>Jordan: I think maybe the movie would have worked if she had just casted Jay Ellis.
+Darius: I don't think there's any there.
+Jordan: I think Lakey's a good actor. It's just, you know.
+Darius: This plot was 3 pages long, you know.
+Jordan: That script is like literally had to have been like 10 pages.
+Darius: It could have literally just been boy met girl conflict the end.
+Jordan: Yeah. Boy met girl conflict, Kendrick concert credits.
+Darius: It's stupid.
+Jordan: Welcome back to Out the Trunk Pile with Jordan and Darius. This is our movie review segment. We're the podcast where two friends started talking in a bar and never stopped. I'm Jordy. My name is Jordy B Riding on all socials.
+Darius: I'm Darius SDS. I love the area on all socials.
+Jordan: And today we're going to be talking about the photograph, a 2020 rom-drom written and directed by Stella, Stella Maggie, starring LaKeith Stanfield, Shante Adams, Issa Rae, Ilan Noel, Rob Morgan, Lorel Howery, Courtney B. Vance, and Chelsea Peretti. This movie takes place after a famous photographer's mother, a famous photographer dies. Her daughter discovers a hidden photograph and answers Now, in unanswered questions about her family's past, her search connects her with Michael Block, a journalist following the same story, as both navigate grief, ambition, and the possibility of love across generations. Tell us to you for act one.
+Darius: Act one, the photo that opens the door, May inherits a photograph and letters that complicate how she sees her late mother. Michael's reporting brings him into May's orbit, creating a quiet spark built on curiosity and shared loneliness. Fun fact, this is the last movie I saw before COVID. And so it came out February 2020. That was the last movie. Well, not probably the last movie I saw in the movie theater. And so it was. We'll get to that later. While it's not the best movie, it does hold a place in my heart, for lack of a better word, in that it was from the before times, if you will. So right, right. What you got for act one?
+Jordan: This movie is. Cool. It's got a good story, really good premise. Beautiful gowns. Beautiful gowns. But no, but all seriousness, one thing I love about this movie is getting to see Issa Rae play an adult character. Because her character, Insecure, is like fun and we love Issa D, but she can be, you know, almost cartoonish at points. So it was really nice to see her play like a mature, somewhat self-assured woman. on screen, especially on the big screen, too. I like when TV stars try to transition into other projects. Also, we need more black love stories that are not completely marred by trauma and abuse and addiction and all that stuff. So that's one thing I do love about this movie.
+Darius: People say that, and I do agree to a certain extent, but movies need conflict. And yeah, but no, I agree. There does We need more black movies with lower stakes, if you will. Yeah. So let me ask you this, man. Was everyone mailing it in this movie or was it just me?
+Jordan: Yeah, I saw that I tried to trick myself when I watched it to make myself think it was a good movie because I love everybody in the movie. Yes, they mailed it in. Actually, they didn't even mail it in. They airdropped it. They sent that **** via Bluetooth.
+Darius: Songs where they just emailed each other old verses.
+Jordan: Yeah, that's what it felt like. There was zero chemistry between Issa and LaKeith. He's trying to be like smoldering and sexy, but he's like whispering the whole movie. She's just kind of there. This weird jazz score.
+Darius: You like Kanye West? She's like, oh, but he was lit though. It's like, oh no.
+Jordan: So I actually tried to Google the age of the writer and director because it felt like what 50 people, 50 year old people think 30 year old people talk about on dates. Yeah, it was like, yeah, no, I love Kendrick, but no, I love Drake. It's like.
+Darius: I've never once had a Kendrick versus Drake debate on a date.
+Jordan: Not on a first date. No.
+Darius: It's just not. Most women just aren't into rap like that.
+Jordan: Is true. And if they are, it's like. Meg and Glow and Moneybag. Yo, we're not discussing rap, you know, on our first date. Yeah, no, not at all. I don't think so. I don't think I've ever talked about rap on. No, I don't think I've ever talked about rap on a first date. No.
+Darius: You know, it just feels like it was coming off the high from Insecure Lake. Lake Keith just had a few big credits. Yeah, let's go get this money right quick. Little, little, little. let's just get this bag right fast. Yeah, I think so. But this is clearly a cash grab. Like, yeah.
+Jordan: I literally wrote low vibes. Like this movie is very like, in the words of Earthy Girls, low vibrational. Just.
+Darius: No, like Lil Rel, there's a scene, Lil Rel and his wife and Issa and Lake Lake Keith are like preparing for a storm and they're having a glass of wine. And it's just like, it's just not.
+Jordan: It's like super artificial couples double date banter.
+Darius: What'd you guys do during the storm? So she winked. I said, oh no.
+Jordan: Oh, he smiled. That'd mean they had sex.
+Darius: It's just, you know, I don't think they, this one is making the, highlight reel when they get inducted into whatever Hall of Fame, Walk of Fame, whatever.
+Jordan: Yeah, it's gonna stay on the cut room floor. they gave it not their best and it showed on the screen. It's weird because this writer, I really like some of her stuff. She wrote a, directed a really good movie I love called Everything, based on a novel. It was a pretty dope love story. So yeah, I was, yeah, I had avoided watching this movie because I was hoping that it didn't disappoint me and it did disappoint you, I'm not gonna lie.
+Darius: You know, we'll get into another disappointment. In act two, do you have anything else for this one?
+Jordan: I will say I did think the couple with her mom and Daniel from Insecure, I think they had great chemistry or a better chemistry. That's what I got for act one.
+Darius: May and Michael grow closer while Christina's younger life unfolds alongside them. The film compares two romances shaped by timing, ambition, emotional guardedness and the fear of repeating old mistakes. That's what I wanted to get into. I hated the why it felt like I was watching two different movies. There was no interconnection between the two. There was no reason for the flashbacks.
+Jordan: Not at all.
+Darius: It just felt like they were padding runtime. And I don't. Yeah. It's just very disjointed.
+Jordan: It's very, that's a good, that's a good way to put it.
+Darius: It's not difficult to follow. It's actually very basic movie.
+Jordan: It's, that's the problem. It's too easy, but it's supposed to be like some mystery and it's not.
+Darius: It's like a. watching a Netflix sitcom that keeps switching to something else and I can't stop it. And it's like, yeah, It's like, can you stay on one story?
+Jordan: It'd be like, it almost felt like if you, like say you got like paid for the ad free version, but then ads kept coming up. That's what it felt like. Cause like, so I almost wonder if they wrote the script and one story was supposed to be the primary story. either the flashback or the current time. I can't figure out which one it was. And then they got some sort of notes. And then they were like, okay, let me flesh this out. Because we got half of both. Like we didn't really get a full fleshed out love story on either side.
+Darius: Well, spoiler alert for act three, but I think that the writers thought the reveal of her being his daughter would just matter a lot. And it just didn't.
+Jordan: It was clear as day the whole time.
+Darius: It was telegraphed from a mile away. It was the only reason they would be telling us the story. There's no other reason for us to see these flashbacks.
+Jordan: Correct.
+Darius: And I'm not really sure what Michael Blocker was there reporting on. That wasn't really fleshed out. It's just, it's nothing.
+Jordan: They didn't finish anything. It's like, it's like they took like a bunch of voice notes, put them together and said, here's a script.
+Darius: Which is wild, it's damn near 2 hours, which is long for a rom-com.
+Jordan: That's what's confusing because I like I've tried to write notes. I have like 7 lines.
+Darius: I had this one. It's an expensive *** soundtrack. Soundtrack.
+Jordan: Yeah, Ari Lennox.
+Darius: Yeah, we got, there's Al Green, I think in here. Al Green.
+Jordan: Yeah.
+Darius: He's litigates. You're not using his **** unless you cut a check. So.
+Jordan: Okay, he's still alive.
+Darius: Yeah, he's with us. He's 80.
+Jordan: Oh, ****. Okay.
+Darius: But Al Green is notorious for he want his brain. I mean, he'll let you use it, but you coming up off from duckets. Yeah. He snatched, what is it, Griselda?
+Jordan: Oh, yeah, yeah.
+Darius: They interloped something of his and he let him run it up because it was super popular and he came back and snatched all of it. So that's what they do now is they don't they won't pull it. They'll let you run it up.
+Jordan: They'll **** you with the royalties.
+Darius: And then it gets to a point was like, do you really want to pull your most popular song right now? Because, yeah, you may not get royalties on to perform it. and so you got no choice but to cut the check and then yeah.
+Jordan: That's what uh that's what Sting did with uh blue face um for Lucid Dreams.
+Darius: Like blue face the pimp rapper dude.
+Jordan: No I'm sorry not blue face I'm sorry young blue my bad.
+Darius: Oh yeah I was like um blue face.
+Jordan: Yeah no no no no no no young blue my bad ****** him up **** that up yeah um so yeah soundtrack is pretty good um **** lost my share of thought was about to say okay so.
+Darius: Go ahead.
+Jordan: No, go ahead.
+Darius: No, I was trying to save you while you thought.
+Jordan: Okay, cool. My question is, it just me or did this movie want to be Love Jones really, really bad?
+Darius: I have right here. It's a Love Jones rip off. It's very much they tried to do a little millennial Love Jones. Yeah. Except. I mean, you just can't compare the sex appeal of Neil Long and Lorenz Tate.
+Jordan: Correct.
+Darius: Issa Rae like Keith Stanfield, like, especially in the nineties, like, you know, like Lorenz Tate is an extremely handsome man. You know, Nia Long is an all time beautiful one.
+Jordan: All time. Like her face literally like it's generational.
+Darius: Yeah, it just lights up the screen and then you put them together in a movie that's mostly about nothing and like, that's enough. And they tried that they thought they could be enough. And while I think Issa is very beautiful, she's not. sex symbol, Nia Long. Yeah. there's just not a carnal reaction when you see her. She feels like, see Nia Long.
+Jordan: She feels like a friend to you, to me.
+Darius: No, I'm not saying I wouldn't date her.
+Jordan: She's a beautiful woman. I'm saying like, just what I like the energy I get from her on screen. It's like very like I root for her because she feels like a friend.
+Darius: Yeah, she like. Yeah, Nia Long is just sexy, and that's just there's, there's cuteness and attractiveness and there's sex.
+Jordan: Yes, this is very, very cute.
+Darius: Right. You know, but there she's not. Yeah, anyways, to get you back to your point, this did try to be Love Jones and it did not succeed in doing so.
+Jordan: Yeah, down to the ********** photography storyline.
+Darius: Another half-ridden piece of string of nothing.
+Jordan: That's my thing is like she's, I guess apparently she's supposed to be like, I'm not supposed to be a famous photographer. So she's like, that's what the article's about. But they didn't even do a good job of showing that because they showed like a little home video and it's like, how I'm supposed to know that means she's famous.
+Darius: Well, they completely dropped Lake Keith's character as a reporter after they got him to where he needed to be. He just stopped. Yeah, I'm a reporter. Okay, cool. That's good character development. So you're here to report on the famous photographer and then he just kind of stops that one. They just use that to get him to Issa and then they just stop.
+Jordan: Right, right.
+Darius: Fleshing that out. So I don't really care about.
+Jordan: Correct.
+Darius: Then he's getting a job in London, which is like the laziest romantic trope in the world.
+Jordan: And correct.
+Darius: It's just a lot of empty threads.
+Jordan: Yeah. And then even like it's a mysterious photo. It's a picture of a woman. The hell's serious about it. I still don't get that. I watch a movie twice. I don't understand.
+Darius: You know, shout out to your dedication for watching this twice. We'll give you that. It's not bad.
+Jordan: It's not bad.
+Darius: Okay. This might be a northerner thing. Are you familiar with the chain restaurant Boston Market?
+Jordan: Yeah, of course.
+Darius: That's what it is. It's like, this is Boston Market. Love Jones is Thanksgiving dinner. You know, it's just.
+Jordan: Yeah, That's a great way to put it. It's. Yeah.
+Darius: Boston Market is cool.
+Jordan: Yeah. Love the cream of spinach?
+Darius: You left the meat in the freezer. Got to have something to eat right out to Boston Market. Little roasted. Yeah. But like Thanksgiving got love in it. You know, Thanksgiving got a little soul in it. And yeah, this is Boston Market. You know, it's not a bad movie. It's just. Just needs a little seasoning.
+Jordan: Yeah, that's it. Yeah, that's a good way to put it.
+Darius: The writing is also great. I don't like the. No, the. They're parallel movies. And it's funny because I was more interested in the flashbacks.
+Jordan: Me too.
+Darius: They hinted at the mom being a prostitute. Never went anywhere with that. They hinted.
+Jordan: Her mom.
+Darius: Yeah, May's the flashbacks mom. Yeah, the grandma.
+Jordan: OK, yeah.
+Darius: It's just a whole bunch of empty threads, for lack of a better word.
+Jordan: Yeah. it doesn't really make sense. I mean, yeah, just, it's okay. So I did, okay, maybe I was thinking about it. It's like, I think, yeah, literally, because it's like, what do you say about this movie? Okay, so, but I have been thinking about it and I wonder if the movie is supposed to be more so almost like a meditation on black women's rush to each other and black motherhood and slash black womanhood and how those can flip with each other. And I think maybe they just didn't flesh it out all the way. Because like her mom had to, you know, she wanted to chase her dreams. She felt like she couldn't do that and have a relationship with **** what was his name? I can't remember. Daniel from Insecure, whatever his name was. NPC guy. NPC, NPC country guy. who was cool working on the boats. And because she was so hard to chase in her dreams, she kind of let her daughter fall by the wayside. I don't know if that's the point of the story, but they didn't do enough because like the letter, she didn't say much in the letter either. Like it was just a lot of.
+Darius: Also, so you just raise a child by yourself. Like that's easier. That's the easier to chase. That doesn't make any sense. And it's just I hesitate to give movies more credit than they've earned. um maybe it is a a a reflection on you know black womanhood and black motherhood but it could just be a bad movie like I don't really think right um we might just be giving them a little bit too much credit when um there's just no there there you know so I mean I don't know it's possible but absent someone on the team explaining it to me I'm just gonna go with nah it's a bad movie you got anything else ready to?
+Jordan: Actually, I just thought of this. And even the way the fact that I'll just say the grandma and their mother, they both didn't tell anybody they were sick. They both just like died young, it sounds like, or I mean, his mom maybe was in her 60s, I guess. There's no information there because there's no plot. NPCs. just like you so you mean somebody like you have a daughter who's out of state and you're sick and you didn't bother to tell her you were sick or say goodbye or anything like it just so much just didn't make sense in this movie.
+Darius: It's just it's we make fun of it a lot that like there are a lot of movies where the main characters it's like as if everyone else are NPCs and The main character, when they leave the room, they just kind of freeze. But this movie, even the main characters are NPCs. Nothing is fleshed out. It's like.
+Jordan: Yeah, there's not a single, like, I can't think of a single interesting thing in this movie at all.
+Darius: Nothing. It's just it's just nothing. It's there. Let's get into act three. Try to land this plane, choosing what to carry forward. As May understands more about Christina, she must decide how much the past should guide her present. Michael faces his own choice about career, honesty and emotional risk. What you got for actor? Realize I burned through my act three stuff from that to you.
+Jordan: Should he have left her alone knowing that he had applied for a job in another country or anything for a job in another country?
+Darius: That's the other thing too. I'm not sure how much time passed.
+Jordan: Yeah, right.
+Darius: Or like, because you can watch this movie and come to the conclusion this was like a two weekend fling or they were together or three months, six months. I just I have no idea. And I'm not to say that I need them to put up on the screen three months later. But you need to give me some indication of what is going on here.
+Jordan: Yeah.
+Darius: So, I mean, I got this. If you found a secret letter, you know, like. Someone passes and that you have a key to their bank lock box and you find a letter, would you read it?
+Jordan: Yeah. Um. And it's my parents or just like someone in my family's.
+Darius: I don't want to put that in the universe.
+Jordan: Oh, God.
+Darius: You got to be somebody.
+Jordan: Yeah. I think, yeah, I'd read it. I'd read it. I think for one, let's be honest here. Our ancestors did a great job of not opening up about things. And 2, I mean, they wrote the letter. I presume someone could read it. And It's important to have keepsakes of the people you love. And also like, my phone's being like memorabilia and stuff like that. Like, we do write letters and stuff like that to each other and have written letters and, keep those things because you can't replace, put a value on those, So I'd read it for sure. Or at the very least, I'd keep it.
+Darius: I'd 100% read it. I'd like to say something benevolent about, you know, that's their secret. And now I read that ****.
+Jordan: You want the tea.
+Darius: Yeah, man. I'm not going to lie to our listeners and viewers. I'm reading that **** 1000%. Now, if they were still with us, I would honestly honor their wishes. But presumably, if I have the key,
+Jordan: I'm not going to lie.
+Darius: I'd probably still read it then, too. I don't know. The thing is they could find out and I wouldn't want to have that conversation. But if they're going and if I have the key to a safe a lockbox, it's really on some sort of some sort of executive of the estate or some, they've trusted me enough to give me the key to their lockbox in death.
+Jordan: Right.
+Darius: So I figured they want me to read what's in the ************. Like I don't.
+Jordan: Yeah, right. You left it here for me for a reason.
+Darius: **** it's in there. You like, so I was on a flight from LAX to Minneapolis, a red eye. circa 2011. And this lady to my right had severe fear of flying and she had a panic attack on the takeoff and the landing. Oh ****. And I took my headphones off and just coached her through it. And when we got off the plane, she wrote me like the most lovely handwritten letter on a piece of paper that was, you know, ripped off a corner of a note. And I still have that in my safe. So, and it was just like, I'm not going to go get it, but it was just amazing. Like you're so sweet and enjoy your family in Minnesota and stay warm in the cold. And, it was just that's those stuff that like you said, man, that handwritten stuff. I've never seen that lady again. I don't know her name. And she just, you know, right. I flew a lot back then and, you know, just coached her through it as she was like sweating bullets. And so, yeah, I think, I guess if I, if I kicked the bucket, someone would find that in my safe and that would be a, a window into my personality and my life. And so those things, those things do matter.
+Jordan: No, really, for real. I remember like, well, so I keep a lot of stuff like that. Like I, when I graduated high school and college, my family, they got those big card boxes where you could put the gift cards, not gift cards, but just cards and stuff, whatever. I kept all those whenever I was like, stressed or homesick or sad, I'd go back and read those to remind me like, people care about me, people are rooting for me, remember why I was there, things like that. Or even I remember my senior year yearbook, that's the only yearbook I got from high school. And I don't remember what happened, no, to this day what happened, but this girl I was cool with in class, she was like crying about something. I don't know. And but I just signed my yearbook and she did and she wrote really nice letters. She was like, I was having a really ****** day and like your smile just like helped make it a little better, and I'll never forget that, So I think handwritten stuff like that is really important because you just never know what people need, what you mean to people, even people that you don't really know very well.
+Darius: Yeah, my nieces, they don't do it anymore. They grown. Hell, one of them was married with a kid. For Christmas, I would, in lieu of gifts, have them write me letters, tell me things about their life and stuff like that. And what gift you're going to get me? Like I got any video game I want. So that's actually something that I can't just go out and buy. So those are in the safe too, man. I got every Christmas card any other fellows and their kids have sent me, every birthday card I've got. I finally got people from back home to stop sending me birthday cards. It's like a stack this stick. And they finally listened to me. Like this is just, this is junk. That's crazy. The text of happy birthday accomplishes the same thing. But I kept them all though, because that stuff doesn't matter. But yeah, I got in my safe man. I got any other fellas who sent me Christmas cards with the kids, the kids pictures. The Christmas cards, the wedding invitations. I keep all that ****.
+Jordan: Yeah. Save the dates. Yeah.
+Darius: Yeah, man. Anything else for this movie about nothing?
+Jordan: Actually, I do. Did you see that they canceled the ten year anniversary insecure tour?
+Darius: They said it was scheduling. I got a feeling they looked at them ticket sales and was like, we can do this **** on the tickets.
+Jordan: Somebody said they the tickets were like 300 bucks.
+Darius: Look, I think I do. They said it was scheduling, right?
+Jordan: Yeah.
+Darius: But the tour was announced last month. So what did you book in the last?
+Jordan: Yeah, that was the quickest ******* descheduling issue I've ever seen.
+Darius: They hopped on a Ticketmaster saw them blue dots and was like, we cool.
+Jordan: Yeah, they look crazy as hell going out there with 50 people.
+Darius: What are the I love that show down. What would I? Why would I buy a ticket? What would I ask them?
+Jordan: What would I ask them? I don't understand.
+Darius: Are they even taking questions from the audience? Like it's just.
+Jordan: Oh, good point. Good point.
+Darius: What are they performing? I don't understand it. Like on tour to do what?
+Jordan: I don't get it either. Yeah, I don't know, man. Tom's hard out here. You know, maybe they just thought I was going to get some money and it didn't because, you know.
+Darius: I know JL is tired of doing those bad Amazon Prime movies.
+Jordan: Yeah. Yeah. I'm sure he's waiting for Top Gun three.
+Darius: She's where he gets like eight lines. You know, he's just got greenlit for a show about four male friends.
+Jordan: Yeah, I saw that.
+Darius: People are excited. And look, she's a very talented person, but I need people to understand that insecure was lightning in a bottle.
+Jordan: That was probably the best thing she'll ever make. I mean, with all due respect.
+Darius: It means I mean, it's not even a diss.
+Jordan: Yes.
+Darius: Like, you know, Martin never did Martin again. You know, Will Smith only had one Fresh Prince. Like, you typically only get one iconic sitcom. You know, yeah, Brian Cristen got to a lot of guys.
+Jordan: And that's, yeah, and that's 20 years apart, or 10 years apart, you know?
+Darius: If it goes, if it goes down that that's the only notable work she ever does, that she's still a legend.
+Jordan: You're still a legend for that, yes.
+Darius: It's lightning in a bottle. It's perfectly casted. It's perfectly written. It's perfectly timed. I think if it comes out after COVID, it's different. And some things are time capsule and they're lightning in a bottle and people need to, obviously she's going to keep working. I don't think she's 40 years old, but temper expectations because nothing will ever be that good again. I mean, it's highly unlikely.
+Jordan: And I think you got to be okay with that because even if you let's say whatever you do does 70% of that, that's still ******* going to be that's still going to be incredible. You know what I mean? I remember when I watched an interview of Daniel Radcliffe when he was doing press for like the last Harry Potter movie and Ellen DeGeneres, she asked him, she was like, how do you feel about knowing that you're never going to have this level of success or whatever for a project like this again. And he's like, neither will anyone else. He's like, no one else is going to have this either. I don't know. It's fine.
+Darius: There's a calm in knowing this is as good as it's ever going to get.
+Jordan: Yeah.
+Darius: You know, yeah, it's just if you accept that in the moment and you don't chase that high, obviously you keep working. But, you know, I. It's neat. People need to be okay with maybe if insecure is the best it ever gets, and so maybe that's just our show. Like our parents had friends in Seinfeld and that's fine.
+Jordan: Yeah.
+Darius: You know.
+Jordan: Yeah, I agree. I think so too.
+Darius: Cause if you, I guess our parents would have had to live in single and Martin.
+Jordan: But you get what I mean. Yeah. I agree. Cause like even now, if you like, that's the beauty of like streaming is like any, actor from any show I've loved over the last like 30 years, they still to this day say because of streaming kids discover, new teenagers discover it every year. So there are kids now who come up, like, I think, I can't remember who it was from which show, but one of the long running sitcoms from like the 90s and 2000s. And they were like, kids come up to me now and go like, hey, you look just like that character from that show. Are you her mom? Just like, you know, the show came out before they were born.
+Darius: You don't know what aging is.
+Jordan: Right. So, and that's going to be okay because they're going to be teenagers, young black kids in 20 years, 10 years. who are going to find that show on HBO Max or whatever streaming service is done at the time. And they're going to watch Loki Happy and it's going to change their life.
+Darius: If I may throw Netflix and them bone, I was rewatching. I mean, I'm always rewatching like Jamie Foxx show just picking random episodes. And it is what jumps out is just how low the stakes are in each episode. And I say this to say, bring back some whimsy in these shows. These shows are too heavy. You know, there's an episode of Jamie Fox where Uncle Junior is trying to fix the electricity and he gets shocked and he loses his memory and it's just 22 minutes of **** **** and it's amazing yeah it's okay like sitcoms the whole point is the absurdity if people get too caught up and making sure the continuity is right and there's a it's okay just like they're supposed to be dumb let them be silly.
+Jordan: So yeah I agree all right man what do you rate this thing fun I love Issa Rae. She's a legend. And because of that, I'm going to give this movie 2 stars.
+Darius: I'm going to go 2.5. It's not a good movie. It is a perfectly mediocre movie. You know what? This is a good movie. When you got people over you to put something on the TV, that kills some time and ain't no games on. So you just throw this movie on. There's no cursing, there's no nudity. You can just throw this on and it works as perfect empty background noise.
+Jordan: Yeah, that's true. When I was stranded in Charlotte, because of a madman with a gun, I just watched the movie and it was great.
+Darius: Just a point of clarification. The issue was in Greensboro. He was not under any sort of danger.
+Jordan: Oh yeah, no, sorry. Yeah, no, yeah.
+Darius: And so it just messed up his travel chain. But no, 2.5, Issa, keep working hard. Can't knock them all out of the park.
+Jordan: Can't win them all.
+Darius: No.
+Jordan: And we're rooting for you.
+Darius: All right. Thanks for listening. My name is Darius. That's Deez I love the area on all socials.
+Jordan: And I'm Jordan. That's Jordan to be writing on all socials.
+Darius: Please rate, like, and subscribe. We are Out the Trunk Pod on all socials. That is Out the Trunk Pod on all socials.
+Jordan: And for any ongoing movie recommendations, feel free to reach out to us via e-mail at outthetrunkpod at gmail.com. That's outthetrunkpod at gmail.com. That's Rap. Thanks for listening to us, watching us. And we'll be back next week. We are, what are we reviewing?
+Darius: Next movie we'll be reviewing.
+Jordan: We're going to be doing a movie, guys.
+Darius: We'll be reviewing a movie. Thank you.</t>
+  </si>
+  <si>
+    <t>Jordan: Yeah, now Lauren Lena, definitely her career is just like, her career is just like being insanely gorgeous.
+Darius: Yeah, she can't act for ****.
+Jordan: Hey guys, welcome to Out the Trunk with Jordan and Darius. This is our movie review segment. My name is Jordan. You can find me on all socials at Jordy B Writing.
+Darius: And I'm Darius. That's these. I love the area on all socials.
+Jordan: You can also find us on all socials, our podcast at Out the Trunk Pod. on all socials, clean across the board. Today we're going to be reviewing This Christmas. This movie came out in 2007, starring Loretta Divine, Idris Elba, Regina King, Chris Brown, Delroy Lindo, Makai Pfeiffer, Sharon Leal, Columbus Short, Laz Alonzo, and Lauren London. Yes, the cast is that loaded.
+Darius: I was going to ask what the budget was for this, but in 2007, I don't even think it's that time yet. They got all them for 13 M's.
+Jordan: Yeah.
+Darius: Could you even get Idris for 13 amps today?
+Jordan: **** no.
+Darius: You couldn't even get.
+Jordan: You'd have to start a GoFundMe.
+Darius: Yeah, like you might, you could get, you could everybody, but Idris, Chris Brown, Regina King is not answering your calls.
+Jordan: Oh, hell no.
+Darius: But you could get.
+Jordan: Everybody else you can get.
+Darius: Lauren London, I don't know how much her, adherence is. But. She can't act anyway. Hey, sorry for cutting you off. Let's get to it.
+Jordan: Beautiful gowns, beautiful gowns. Okay, so this Christmas is about the Whitfield family as they reunite in LA for the Christmas holiday. Their first full gathering in four years, their matriarch, Medea, welcomes her six children, each arriving with their own personal drama, secrets and baggage. As holiday tensions rise, their individual crises from debt and military AWOL status to infidelity and hidden musical ambitions, threatened to unravel the festive spirit and test the unbreakable bond of family. I'm gonna toss it to you for act one.
+Darius: Act one, we're gonna call Secrets Beneath the Tree. The 6 Whitfield siblings and their significant others gather at my dear's house, home for Christmas. Arguments about some of the family business ignite and the unexpected arrival of the eldest Quinn introduces new tension and a lingering resentment toward my dear's live-in boyfriend. There was a scene early in the movie where Idris Elber's character is running from bad guys, which is called bad guy one, bad guy two. Yeah, dude. Two movie tropes popped out. One, breaking a bottle over someone's head is not easy.
+Jordan: That is on my bucket list.
+Darius: But those are breakaway bottles on set. That's not how it happens in real life. Do not jump through a glass window. You will.
+Jordan: Window. Yeah.
+Darius: You will die. A piece of glass is going to cut your carotid artery and you're going to bleed out on the floor. Do not. You will like one. They don't shatter like that. Like you're going to. Right.
+Jordan: They always make it seem like it's just so no pun intended breakable.
+Darius: Yeah. Like you see this all the times in movies that will kill you. Don't do that. Does your family do a big Christmas?
+Jordan: A big Christmas? I don't know. It's usually like 15, 16 of us. So medium size, I guess. So pretty much. I mean, Christmas is a big, big thing in our family for sure.
+Darius: So you buy gifts for all those people.
+Jordan: No, God, no, hell no. We do. So we do Secret Santa with my siblings and then maybe we'll still buy each other something. Obviously our parents. And then sometimes maybe we have once in a while every other year. So we'll do like a Secret Santa with the cousins. And that's pretty much it.
+Darius: When I used to go home for Christmas, we just did for the kids, like the grownups. Yeah. There was like four of us. We'd secret Santa it for the grownups and then everyone just bought for the kids. But hell, the kids are grown now. So right. Nothing made, man. So that's way off topic. But yes, I went home this weekend and it made me feel really old. What you got for act one?
+Jordan: Same. My youngest cousin did her first college visit a couple weeks ago and I was like, why the hell is she on a college campus? And I was like, oh my God, she says, it's time for her to go to college. What do I have for act one? I love jazz and I love Speakeasy. So I love that the movie started out with like a nice jazz score and it's like a dope like dark moody jazz club. I love going to those. I thought that was a dope way to start a Christmas movie. I also want to say that this movie is a perfect testament of like parent slash black parent logic. Like you can't sing, but you can ride a motorcycle.
+Darius: Yeah.
+Jordan: You can't have an expensive camera, but you can have a motorcycle.
+Darius: Add that to the list of things don't do in real life. Don't ride motorcycles. One of my really, really good friends is a firefighter and don't ride motorcycles. Oh, damn. Don't ride motorcycles, man. It's, you know, the helmet technology is great, but yeah, you're still flying 60, 70 mph and it's just with no dog in the air. It's like there's no mechanism to keep you from smacking against the concrete.
+Jordan: Just raw dogging any surface.
+Darius: Yeah, like you are. The human body is not meant to smack into concrete at 65 mph. Right. We weren't quite we didn't evolve for that.
+Jordan: So yeah, we're not that strong. Yeah.
+Darius: No, you will spontaneously come. Well, I guess it wouldn't be spontaneous, but you will combust.
+Jordan: Yeah. Or that. Yeah. What was I going to ask you? Oh, so there's a scene where everybody's getting to the house and it's the ****** husband showing everybody the Escalade with his name on it, which is So tacky. And then you got this sister pulling up with the BMW rental. The first time you watched it, did you think that she had like feelings for him?
+Darius: No.
+Jordan: Like a thing for him.
+Darius: I mean, well, she had a thing for his, you know, displays of wealth. But yeah. I didn't see that.
+Jordan: Okay. I remember the first time I thought, so I was like, is that sexual attention or does she actually hate him?
+Darius: No, I just, I didn't see that. I just thought it was, if you've ever had, showed it to a family gathering, like when everyone's showing up, it's just real warm and fuzzy. And that's kind of how I took it. Yeah. Okay. Yeah. So the movie is a little bloated. There's like, there's a subplot for each sibling. Right. So we got the oldest has his gambling issues. Regina King's character has her husband cheating. Lauren London has a sneaky link.
+Jordan: Yeah.
+Darius: Chris Brown. I guess he's singing.
+Jordan: Yeah.
+Darius: Oh boy had a white.
+Jordan: Columbus Short married a white girl.
+Darius: And that was a wall. Who's it? I think that's all of them. That's.
+Jordan: Wait.
+Darius: I thought she had six kids.
+Jordan: Three girls, three guys. So it was. Sneaky, Chris, Idris, and Columbus. We did those.
+Darius: Sneaky, cheater. And what's the third one?
+Jordan: Stealing cheater?
+Darius: Lori London. Regina King.
+Jordan: Stealing cheater. Oh, the other sister was just successful and didn't have a man.
+Darius: Oh, okay. Which one would you have cut?
+Jordan: Oh, storyline. Yeah. Okay. I want you to cut. I want your.
+Darius: Subplot.
+Jordan: I think I would have. Yeah, I would have cut the successful sisters. Lack of love life storyline. They could have done without that. They tried to give us some false depth with that whole story about him seeing her in freshman year, freshman year. And okay.
+Darius: Yeah.
+Jordan: Playing saw cute girls freshman year. Yeah. I see cute girls every day. Yeah.
+Darius: I would have cut that or like Columbus shorts, military slash white life. Just felt very 2007.
+Jordan: Yeah. So I think I would have I would have kept the dynamic of the white wife. I would have cut the military storyline.
+Darius: Yeah. But even that one, it just felt real 2007 that this is like still some taboo thing. And 2, like they made it taboo, but then it was like one scene later, nobody cared. So it's like, why do we even do this? Right.
+Jordan: Yeah. That's a good point. Because if they were like, if they had more of an issue with it would have made sense for him to be not ashamed, but to be reticent of it. But they were so nice. It was like, okay.
+Darius: It was standard. Oh, okay. Right.
+Jordan: Yeah. It wasn't like it wasn't like his mom was like, damn, what did I do? Does he not love us? Or, you know, that would have been more interesting layers to peel back if they were going to do that. So yeah, that's not a bad take.
+Darius: What did you have? Anything else you have for act one?
+Jordan: Yeah. So first of all, that husband, obviously he wasn't **** because he was a cheater, but he just really wasn't **** as a human being, like flying out on Christmas Eve to.
+Darius: He was the **** his sister on Christmas Eve.
+Jordan: In New York is nuts. You know, like he was a ***** ** **** obviously, but like the most apt thing he did to me was like ******** on HBCUs for no reason. He was just like, so why'd you go to the school with the?
+Darius: Yeah, I mean, it was almost like Tyler Perry villain.
+Jordan: Yeah, it was a little bit like Mike from when I get married.
+Darius: Which is like he made his wife drive from Colorado to Atlanta to Colorado solo in a snowstorm.
+Jordan: Yeah.
+Darius: He wanted her to die. He said they gave her like 200 bucks. It was like drive across the country.
+Jordan: He was like, here's the pocket change.
+Darius: I'll meet you there.
+Jordan: Just here you go. I'll meet you there. You could just buy another plane ticket.
+Darius: Like, you know, I think he just was not interested in her well-being.
+Jordan: No, he just really hated her. He truly hated her from the depths of his soul. No, that husband really wasn't **** dog. And then also like, so do you think that he, remember he kept trying to push her to sell the dry cleaners and to get the money for whatever investment he was doing? Do you think that was his exit strategy?
+Darius: I was thinking it just sounded like his money wasn't as long as he was leading on. Oh, got you. So that's kind of where I went with it. What could have been? I don't see, like, dudes like that aren't ever going to actually leave. Like, they get everything they want right now, Right?
+Jordan: Because you got someone who's weak and insecure.
+Darius: I don't really call her weak and insecure. I would simply say that he has his wife at home, which takes care of house, and he has his woman in daughter, you know, that just is around at his beck and call. So why would he change that up? You know? Right.
+Jordan: That's true.
+Darius: And later on, which, we'll get to that in a later act, but like he's doing just fine. Right. All right, man. Act 2, unwrapping the truth. During a night out, baby's hidden talent is revealed. Claude's big secret comes to a head and Kelly pursues a romantic connection. Back at home, Lisa grows suspicious of her husband's infidelity while Quinton's past dead sketch up to him, creating a dangerous situation. So Chris Brown's character. Yeah. Goes to, you know, the club plays tries to try a little tenderness. It's believable in 2007 that a crowd full of club goers club goers would immediately know try a little tenderness and he would get a pop for that.
+Jordan: Yeah.
+Darius: With music education was what it is today. Do you think a crowd of random people in a club We know an Otis Redding song today. And do you think he would get a pop with it?
+Jordan: No, because as I ended our what's on my segment last week, the grandmothers are in their 30s now. So no, their classics would be like confession. Like, you know what I mean? That would be their like throwback.
+Darius: But no, I mean, Otis Redding died in the 60s. So even in 2007, like, I don't think it's that. I think it's of the headphone culture. Like no one, when you're taking a road trip, everyone just has a soundtrack to it.
+Jordan: Yeah, you don't have any music that you would not hear anymore.
+Darius: Also algorithms, you're not coming across something that isn't already in your sphere. And so I just thought it was very 2007 that you're still like a song that in 2007 was 40 something years old.
+Jordan: Yeah.
+Darius: A crowd full of 20 somethings knew it. And it was, I mean, it's a movie, but I believe it in 2007. I do not believe anyone would know that song. Try a little tenderness in 2025.
+Jordan: The problem is there's no like live radio is not a big thing anymore. So, you know, like going to school was when I heard with my parents was when I heard certain songs. And if you're going to school with your parents now, they're streaming music. So they're streaming what they like. So you're probably not hearing you may not hear that kind of music. It's like that scene from Abbott I mentioned where it was like, what's a favorite classic songs of y'all? And that one kid was like, a Millie.
+Darius: Yeah, I mean, look, I get it, but I just think it makes me a little sad that music education is dying because most people, I mean, 2025 people would think that was Otis. He was getting ready to play. Right, **** yeah. It's the hot, it's the original. But no, a lot of kids would think, oh my God, this Kanye West song is going on.
+Jordan: Yeah, I love this album. Watch the throne.
+Darius: No. What you got for act two, man.
+Jordan: Yeah, you know that had O7 written on it because they walk in the club and they're playing a song with that guy on it.
+Darius: Yeah. Which is wild because by 2007, everyone knew.
+Jordan: Everybody knew. Everybody knew.
+Darius: Yeah.
+Jordan: But I do that. I'm not going to hold you. That is one of my favorite Jesus songs, unfortunately. So yeah. So the guys, he's talking to his wife who no one knows his wife yet at the bar. They're talking. The guys, there's a guy talking to her. He's like, no, we're together. Whatever. He comes back after. And it's like, they're not talking **** but they're, speaking out of turn. Were they asking for it? Or do you think they're just like driving the stupid?
+Darius: Sure, they were asking for it, but I almost think that's immaterial. You can't pull a gun on somebody for making you mad. That's not. Yeah, that's not people. That's a common mis. A lot of people don't understand, like, my gun is registered. Oh, I have a concealed carry. Fine. Right. That's step one. It doesn't give you the right to pull a gun on anyone that ****** you off. Right. You still have to identify like a threat on your safety or your property or something like that. And no, I mean, it could be, you could have paperwork as long as stuff your pockets full.
+Jordan: The constitution, yeah.
+Darius: Hits on your woman and you shoot them in the head, you're still going to jail.
+Jordan: Yeah, like it's like legally carrying gun is not the same as like just being able to shoot people.
+Darius: People willy-nilly. They really do.
+Jordan: They really think like, but I have a permit. It's like, no, dude, you don't have a permit to kill. You're not the bond.
+Darius: You still need to practice good, you know, de-escalation tactics, good problem solving skills, good conflict resolution.
+Jordan: Critical thinking.
+Darius: Just can't shoot people that make you mad because they said something off color about your wife.
+Jordan: Yeah, you can slap them.
+Darius: But that's the thing.
+Jordan: But you can't shoot them.
+Darius: You got a gun on your waist. You get smacking people. It's just a matter of time. I would just advise people to. If you can just go home and live to fire. There's no direct threat to your safety or your well-being or anyone you care about. Take, just leave that **** alone. Anyways, act two, what you got?
+Jordan: I had this scene in act two. The scene where Idris Elb was talking to Loretta Devine about his dad. And she's like, she said, something I really thought was so accurate. And I feel like we don't talk about enough in societies. Well, she said men, but I think some people just in general, but she was like, some men are just too selfish to be married.
+Darius: Yeah.
+Jordan: And I really love that she said that because First of all, their dad wouldn't ****. Like, you just leave and just go play music and like, that's it. Like, you don't just see your kids anymore.
+Darius: Like, ironically, Delray Lindo's character and Kirkland. Kirkland. Yeah.
+Jordan: Yeah.
+Darius: Some men are too selfish to be married. It's me. I'm It's me.
+Jordan: I'm.
+Darius: Yeah, I get hurt.
+Jordan: I feel like honestly, a lot of people slash a lot of people are too selfish to be married and even more people are too selfish to be parents.
+Darius: Yeah, I would agree with that assessment, but I do think it can become a self-fulfilling prophecy where people never get married because they never want to have to stop centering themselves in anything. But you don't really learn how to do that until you have to do it, you know? Right.
+Jordan: Yeah. Being considered is not As easy as we make it seem.
+Darius: It is not going to come natural to you if you never have to do it and you're just floating single, no children forever. Like why would you ever learn those? You never had to flex that muscle. So.
+Jordan: That's a fact because like getting a relationship after being single for a long time, it's like going to the gym after not working out in a year. Like you're like, it's like being sore as ******. You're like, wait, how do I do this? What?
+Darius: I was supposed to text every day.
+Jordan: We text you today? Yeah, right. I got to text you every day. Wait, I got to call you too? Like, you know? I should ask you when I'm at the store if you need anything. Like you kind of forget all those, muscles.
+Darius: All those little considerations every day that you make for someone else. They, like I said, you don't flex those muscles for a while. So. Uh, God, you got Frank too.
+Jordan: Um, did, do you understand why, uh, Columbus Shore was so weird about his marriage or, or did you feel like, like, have you ever been in that situation or would you, how would you have handled his situation? Uh, yeah, the marriage because it, Basically, based on what the family's reaction, we assume that's the first white girl he ever brought home.
+Darius: Probably. Definitely. I just, given the family's reaction, I don't know why he was, he would know these people better than anybody, right? And they didn't care. So.
+Jordan: Yeah, his mom was super sweet when they, when the bookies came home and she was like, oh, you're staying with us. If you're friends with him, you're going to stay at this house.
+Darius: You know, I understand, given that, I don't know the age, I mean, I would understand why you'd be hesitant to just pop up married with anybody.
+Jordan: Well, yeah.
+Darius: You know, like just, we haven't met this person. Was there a wedding? I weren't invited. You know, I would be more afraid of just throwing them miles. Like, we don't go together. We're not, we're full blown married. Man and wife, yeah. And that's, that would be, I would be more concerned about that than the fact that it was a white woman, you know. I understand, but given his family's reaction, I think he was a bit over the top in his concern. Do you, what about you?
+Jordan: Yeah, I think, I mean, I get the hesitation there for sure. But like you said, like with his family, with his family particularly, I didn't get it. You know, if they were more conservative or traditional, I would have understood. I wonder if maybe the underlying theme was because her parents didn't accept him, that he thought his parents wouldn't accept her. I wonder if that was if that was what this was his thinking. Also, I did like that they added that in there because it would have been fake to just act like that's not a thing, you know. So they couldn't ignore that reality there. But yeah, I don't know. I mean, I definitely wouldn't get married without telling my family. That's not. I wouldn't even want to think about that conversation.
+Darius: Big wedding. Are you or you want to elope? You 100% want a big wedding? Are we kidding?
+Jordan: Yeah, we're going to **** **. I will say Now, like it, because I think to me the idea of a wedding would be where both families are actually intermingling and it's actually a family. Now, if the family's like didn't get along or I didn't like her family or something like that, maybe I would maybe modify the the size of the wedding based on that.
+Darius: But ideally, what kind of beef could it be where y'all acted a fool at a wedding? You know, like, that's true. Not get along. Okay, cool. Yes, for me.
+Jordan: Because I wouldn't marry. I wouldn't put myself in that situation anyway.
+Darius: So I mean, if I love somebody and I want to marry somebody, I wouldn't let any not like it.
+Jordan: No, for sure.
+Darius: That's what you're saying. You're just not coming. But I don't know why anyone like how much like How little decorum do you have to have to pop off at somebody else's wedding? Like, you can't put this **** you can't leave that **** at the door at a wedding for a day, for one day.
+Jordan: For 5 hours, 6 hours, whatever.
+Darius: Really, like, it's, I just, I don't understand how people are, they lack that self-control, you know? So, Mr. Joe, Ma Dukes is dating. Mr. Joe is Delroy Lindo's character. The kids kind of kind of knew, but didn't really, whatever, whatever. I guess the dad was, they were divorced or was he dead?
+Jordan: They were divorced.
+Darius: Okay. So how would you feel about that? Mom's back outside. Mr. Joe pulls up. Hello, Jordan. You like poker?
+Jordan: You play video games? Man, I don't know. That would be weird. I mean, I know it's gonna happen, but I don't know. I think I would just be more concerned just about figuring out like what kind of guy he is. Like, is he like, is he good to my mother? Is he good for my mother? That sort of thing. I'm pretty good at reading people, so I would, you know. I wouldn't be over like overjoyed to meet the person, probably maybe not, I don't know, depending on how soon and **** you know, anything can happen. But I would just be, I mean, I wouldn't handle it the way Quentin did. Like he was like overly aggressive with it. Like he was just, it was like, dude. Yeah, for sure. Yeah. So I mean, I know it's a reality. I mean, I'm okay with, I mean, I'm aware of that and okay of that. I want both my parents to be happy and have love and companionship and stuff. So I'd like to think I'd take it pretty well.
+Darius: Yeah.
+Jordan: Now if he was trying to like do too much or, that would be one thing.
+Darius: It's different because y'all all grown. Like it's not like he's trying to take you to the park.
+Jordan: Correct. Yeah. So it's right. It almost be like a co-worker or something at that point, you know, it's not like we're going to have some close bond or, so to the jazz club. Right. those days are those days are over. So it really wouldn't that wouldn't matter. But you know what I'm saying? As long as my mom's good, then I'm good. You know, that's kind of how I've always approached that, you know, meet certain parents, friends, you maybe didn't like them, maybe you didn't. But if they're good to your parents, you were cool with them. If not, then **** them. That's kind of how I approach it.
+Darius: At a certain point, you just got to except that you trust someone's judgment and yeah it may not be for you to understand so that's true yeah I think a lot of adult children when their parents get back outside they act like you know the person has to date them too and it's like no not really you know like yeah I tell my boy like and your mom's 60 something years old man like she got grandchildren you know it's like right You just have to trust their judgment at some point, Yeah, that's true. The dude ain't 30 years younger than her trying to collect the life insurance check. Correct. Yeah, It's the dude is age appropriate and you know, it's deacon so-and-so and they met down at the church house and they go to bingo hall together. You just got to live with that. Yeah.
+Jordan: So as long as he has his **** together and you know, treating her right, then you know. There's nothing more for me to say, like, in terms to her about it. You know, what I'm going to tell her, like, don't see him. Yeah. Oh, what else you got too bad? I will say I did always strongly relate to Quentin a lot whenever I watch the movie, just in terms of like when you were, you know, obviously my my parents got divorced when I was an adult, but I was a child when they were together. So you see, you see things and, you know, even though I knew that there was a better their better, their best lives were probably not with each other in that capacity anymore, it was still hard to accept. Like that doesn't make the loss or the grief any less significant. And, you know, it took me a long time as a child and a young adult to accept that reality, even when I knew that it wasn't good or was different. And so, like, I totally get the fact, like, you know, she, she, you know, everybody was like, why is he so hung up? Why, why can't he let it go? You know? And it's like, I get it because he was a grown man, but you still have those, those childlike, you know, ideologies and attachments, obviously, to your family. And it's a natural thing to want your family to be together, you know? And when you grow up with people who you kind of realize, maybe we're not meant to be together forever. That's a painful thing. And I remember I was talking to somebody years ago about this and they kind of said, the first joy or love that a child should experience is the love their parents have for each other. And I was like, holy ****. Because you don't think about it like that. You think it's supposed to be the love they have for you, but you know the love they have for you, but you see the love they have for each other. And so that's kind of what everybody's first model is ideally supposed to be. So I always, you know, understood why he had such a hard time getting over that that hump, which we get through with that. But I'm glad that they addressed that because they could have made it like some off screen realization and that just wouldn't have been. I think that's what makes this movie different from other Christmas movies.
+Darius: I concur. Didn't necessarily agree with everything Quinn did. He's a little too grown. But yeah, I could understand why it would be a transition. Speaking of transitions. Act 3, the reckoning and reunion. Quentin receives unexpected help regarding his debt. Lisa confronts her husband in a dramatic fashion. The siblings rally together to deal with Claude's consequences. Baby finally takes a stand on his future, leading to a climax where the family confronts their secrets and finds a way to move forward via a soul train line because Had to end on all the cliches. This act gets off the rails a bit here. This is where you feel the bloat of all six storylines having to, you know, be landed here.
+Jordan: Resolve themselves.
+Darius: Yeah. The baby oil scene. Well, that's spanking. I was going to say earlier that I know she's not leaving him because you don't do all that when you're leaving. So he's a couple baby pleases away from being right back in there. But yeah, this is this is this act got a little bit off the rails for me. Yeah, we had the solo of the movie title to end this movie. We got the Soul Train line. All right.
+Jordan: Which, by the way, is not even it's not it's a Christmas song, obviously, but it's not even a church Christmas song.
+Darius: The Soul Train line. I was like, all right, man.
+Jordan: Well, that was the actual actors. That wasn't the second one at the end of the movie. That was the actors. That wasn't the That was almost like a blooper reel, pretty much.
+Darius: I got you. Doesn't make it any less corny. Act 3, what you got there?
+Jordan: Well, speaking of that line, the Soul Train line, that was the first time I realized that Idris Elba was British. I did not know for like a long time that he was British.
+Darius: So if you if you watch The Wire, his accent slips a lot in there because he's a newer actor and he's trying to do a Baltimore accent and.
+Jordan: Right, which is. One of the more unique accents you'll ever hear.
+Darius: And he does a good job, but it slips here and there. And also like, the wire was a low budget affair. They weren't doing reshoots.
+Jordan: I'm about to say yeah, the cameras were not great. Right.
+Darius: No, man, British people, they be doing American accents really well. I didn't know old boy from Get Out was British until.
+Jordan: Oh yeah, Daniel Kaluuya. Yeah.
+Darius: Until he spoke. A couple other British people. A lot of the Game of Thrones people were British and you wouldn't really pick it up. So, you know.
+Jordan: Yeah. Who else was it? Like a lot like Christian Bale. A lot of people didn't know he was British for a long time. What was I going to say? Really nice church. Great cathedral look. love when movies have a good good you know background scene did you notice the white guy who was definitely like was lip syncing in the choir go back and watch it there's a scene there's a point where he's just like has his mouth open is just like zoned all the way out.
+Darius: I've been there those songs get long and they get they do get long I'll never forget, man, when Christmas fell on a Sunday, the Christmas day.
+Jordan: And you had to go.
+Darius: Yeah, we had to still go. We would never miss church on Sunday. And they preached like it was any other day. And it was like 1 o'clock in the afternoon. No kids had open prep. Everyone was just over it. But nah, man, whatever happens on Sunday happens after church, even if it's Christmas.
+Jordan: Damn, that sucks. That was one thing my parents, like we never went to church on Christmas ever. We never had to do that. Thank God. We, it wouldn't have went well. I wasn't going to ask you. Oh yeah. So the scene where Chris Brown was talking to Loretta Devine and he's like, basically just reading her, not reading her foot. He's basically just telling her about herself and letting her know kind of, you know, like you holding yourself back for us and it's causing you to resent half of us. So you should just live your life. Really glad someone told her that. It's always funny when it's like the youngest kid because they always say the youngest kid like doesn't give a ****. So I think the movie was pretty accurate with that. That scene.
+Darius: The youngest usually has the most clarity, though, because they yeah, they got to see their parents as like the final form the whole time. And you know, that's why Quentin was all like hung up on her d</t>
+  </si>
+  <si>
+    <t>Darius: All right, cut there. What do you want to watch next week?
+Jordan: Have you seen Sleepy Hollow?
+Darius: I've never even heard of that. I mean, I've heard of it. I don't even know what it's about.
+Jordan: It's a horror slash thriller with Johnny Depp. Miranda Richardson. The duty played Dumbledore. Christina Richie.
+Darius: I'm in.
+Jordan: Okay. Cool for Halloween.
+Darius: I'll get a copy up either Thursday or Friday. So Sleepy Hallow it is.
+Jordan: Hey guys, welcome to Out the Trunk Pod with Jordan and Darius. My name is Jordan. You can find me on all socials at Jordy V Writing.
+Darius: And I'm Darius. That's D's all up in the area on all socials.
+Jordan: This is our movie review segment. We're going to be reviewing weapons. Just came out this year. Starring Josh Brolin, Julia Garner, Alden Enrich, Austin Abrams, Benedict Wong, Amy Madigan, and Carrie Christopher. Weapons is about where nearly an entire 3rd grade class in a small town mysteriously vanishes from their homes in the middle of the night. The shock community fractures. A teacher, a grieving parent, and others are drawn into an escalating, terrifying search for answers, questioning what supernatural force or human evil is behind the disappearances. Let's toss it to you, frag one.
+Darius: Act one, we're going to call it the vanishing. A quiet suburban town is plunged into immediate chaos and suspicion when 17 elementary school children from the same class mysteriously disappear from their beds at 2.17 AM, leaving no trace behind. Start this thing off by saying this is so football season started a couple of weeks ago, not to date the podcast. I must say this is the first movie that, because I watch on Mondays, this is the first movie that I didn't feel like I'd rather be watching Monday Night Football. So it was really good. It was, it kept me engaged. It was, the mystery was nice. And I must say that is a, not that the movies we previewed were bad, but I just really like football.
+Jordan: And it's like, not for you.
+Darius: Yeah, I got, the game was good and I'm like, I don't even care because this movie is, I'm locked in on this movie. So.
+Jordan: What you got for football season? Yeah, for football season, I usually watch them either start Saturday during the day or I do Saturday, Sunday night, like after the last game or Monday after the last game for the most part. Yes. What I want to say first of all, Julia Garner is having a ******* year. She so she played the the main character. She was also in. Fantastic Four, she was a silver surfer. I think she was in another movie this year called, was it the Wolfman? I think I want to say it was.
+Darius: I was going to pretend like that one didn't happen.
+Jordan: Oh, well, she wasn't killing it though. She was great.
+Darius: You know, I get it though. When you get your break, you just got to grab all of the road. You got to grab it all.
+Jordan: Yeah, you just got to get it how you live.
+Darius: You know, ask Daniel Kalua tomorrow, the deals might dry up. So ****. Yeah, man. You got to scoop him. You got to scoop him. But no, other than Wolfman, which was not good. She's been on. I've liked her since. So she had a role in the Americans. I first I was introduced to her, the Americans, and then Ozark. I've heard Ozark.
+Jordan: Yeah.
+Darius: So, yeah, shout out to Julia Gardner. You're having a year. I had one of my notes here that I deleted from my rundown was Julia Gardner. Woo. So Julia Gardner.
+Jordan: Yeah, she's great.
+Darius: Did no one have guns in this movie except for the criminal? What is that? What city in America is this gunless?
+Jordan: Would have been so quick if they used their guns. By the way, it's a small town, so I'm assuming they're Second Amendment people. That's just the vibe I got watching the movie. So I thought that was a little bit of a plot hole.
+Darius: Yeah, so I mean I've said this before on the pot. I don't demand movies be realistic. I demand they stay true to the world that was written. So if in this world gun ownership was not mass proliferated like it is in the real world, then it makes, I won't call it a plot hole. It just was given the modern version of where guns are in America. It's just bizarre to see that nobody is armed. Like nobody. You didn't see a gun until the end when they were in the bad guy's house. Correct. I won't spoil it, but the bad person's house. I just was like, where are the guns? Yeah. It's kind of like those 90s movies that wouldn't make sense if everyone had cell phones. Like, it's just like, all right, this movie would have been a few seconds.
+Jordan: Like Scream wouldn't have worked. I know what you did last summer wouldn't have worked.
+Darius: All the Ferris Buellers, the Home Alone, he'd have just texted his mom like, hey, you missed something.
+Jordan: Hey, someone's trying to break in the house.
+Darius: You know, so.
+Jordan: Yeah.
+Darius: What you got for Ag1?
+Jordan: I really liked that they had a kid do the narration for this movie. I don't know why, but it just really worked. It's funny as when I first started watching the movie and the screen was all black, like I thought my, the feet was ****** **. Like, I was like, what the **** going on?
+Darius: No, I make sure they're either MP4 or MKV and I've definitely checked them because I've gotten them where the sound is not old coded right and all kinds of ****. But I check them.
+Jordan: Yeah, I like that. was I thought that was a really nice touch. What else? The camera work in this movie was really, really good. I like the way that it was like all these like long shots. And for the first like almost 20 minutes of the movie, it feels like everything is shot like they're being chased. You almost never see anybody's face like straight on. I thought that was really dope storytelling, considering just kind of the confusion that was going on in the town.
+Darius: Yeah. I like the storytelling in general.
+Jordan: Yeah, me too.
+Darius: I love the different characters and I get into that in act two, but yeah, I agree. The storytelling is great. They do a good job of building suspense. Yes. They don't fall into common horror movie tropes. True. They did a really good job with grief, like having the dad sleep in the child's bed. The kid's bed. You know, having the difference in how the parents are grieving. oftentimes when there's a child death, like one parent is, go, go, go, go, go. And one parent just can't get out of bed.
+Jordan: Wallowing. And yeah.
+Darius: There's no right or wrong. They're just doing it differently. And that could also be a source of tension within the marriage. And you could see that on display. Right.
+Jordan: Yeah. A lot of times when a child is not a lot of times, but there's a It's a big number of times where if a couple lose a child, that the couple more often than not gets divorced.
+Darius: I mean, it's a nuclear bomb in your relationship, like, right? Yeah. I, you know, it's, you know.
+Jordan: It's literally the worst thing that could ever happen, you know, to to a couple.
+Darius: It breaks the biological chain because parents are not correct their children. And so. It breaks people. Like, I don't know why. Yeah, I like that. So.
+Jordan: No, I mean, it's really what happens. I mean, there's no other way to put it, honestly. I'm surprised they just reopened school with. Yeah, like a month later.
+Darius: Yeah. So I did. I read a book about the Columbine shooting and even, you know, I guess I mean, that's just I think they lost more than 17 kids that day, too. But they were they they reopened that next fall.
+Jordan: Yeah.
+Darius: And I don't know, this is way off topic, but funny anecdote, the principal of that school made a pledge to all the students that like he would see all of them graduate. And he knew, you know, he was traumatized too. And his wife, he just, he would, you know, he told his wife like, look, I made a pledge. And the freshmen who were there on the day of the shooting, I need to see them walk across the stage. But if we can get through that, I'll quit Columbine and we can, you know, start over, start over. And they ended up getting divorced. She didn't make it. But I just thought, I've always, I just remember reading that passage and going, I get it. I get, I get her being like, I need to move. I need to **** ** out of here. I, you know, and him being like, I made a promise to those students, you know, and I told them, The first day of school, back after the shooting, that fall, that I will walk all of them across the stage.
+Jordan: The stage.
+Darius: He did, he made, he gets a promise.
+Jordan: That's very honorable.
+Darius: He gets a promise. He did. He left.
+Jordan: It's interesting you bring that up. It's interesting you bring that up because I was on TikTok the other day and I don't remember exactly what, I think it was in relation to the person that got assassinated or killed. And someone was saying like, you know, talking about the whitewashing of certain history, parts of history, and they were saying that the, Columbine thing was not just, it wasn't just kids who got bullied who just, went berserk. It was white, they were white nationalists who had. problematic views who went just went and, they were obstacized because of their beliefs. They weren't just obstacized because they were like weird kids.
+Darius: Chris Rock had been in the 90s where he was like.
+Jordan: I'm scared of young white boys.
+Darius: Nah, he said, he said, I saw the yearbook. There was 17 of them. He's like, I didn't have 17 friends in high school. I don't have 17 friends now.
+Jordan: What you mean lonely? I count 17 of y'all.
+Darius: Yeah, I remember that. There's 17 people in that group. What are you talking about?
+Jordan: Yeah.
+Darius: That is what's funny. What were you saying?
+Jordan: So somebody talked about that, how they actually were white nationalists who were ostracized because of those obviously problematic beliefs. And in the college school, in the comments, and somebody in the comments, they were like, I actually went to Columbine and I was at the school the day I'm a survivor of the day it happened. And yes, they were white nationalists. So I thought it was crazy that we think about it like it was like 50 years ago. We act like it was like 50 years ago. And that person is probably in their early forties with kids. And it's just crazy to see that not much has changed, unfortunately.
+Darius: No. Yeah, I think there's a whole I mean, they keep I think they keep like some contact, the Columbine kids that survived. But, you know, the principal has since remarried and moved and the parents of one of the kids completely fell off the grid and the other parents, they're kind of still involved. But, we like the tapes, the basement tapes, I think they were called, they were eventually destroyed and you'll never know, they made several tapes. Detail of what they were going to do and they'll never mean they were destroyed and this is 1990 whatever so it's not like there's.
+Jordan: Like 97 I think something.
+Darius: Like that like there's external hard drives you can recover these were actual physical tapes and once they're destroyed.
+Jordan: Right they did you just burn them and that's it right?
+Darius: So anyways we're way off topic anything else for act one?
+Jordan: I thought the running style of the kids was actually a really nice touch yeah because it looks like they're just playing instead of them being in a trance or I mean, they obviously were in a trance, but they didn't look like they were in a trance. It didn't look like they were on some like serial killer ****. I did feel like almost showed.
+Darius: Go ahead. Sorry.
+Jordan: It almost showed like they were just off to go be kids. It looked like they were off to go be kids and just play, do whatever kids do to. And then they're running into, you know, a trap they had no idea was waiting for them. So I like the not liked, but I appreciated the allegory of, you know, the metaphor of what the movie is trying to say.
+Darius: I will say that it felt a little plot hole movie trophy to me in the sense that you ever watch those movies that only make sense if the characters never talk to each other? And I'm just like, no one, 17 kids disappeared. And it took until this movie happened for him to be like, let's map where they were running to, like, oh God, they're all running in the same pattern. And it's like, that's not something that they like 17 parents didn't go together and go, does anyone else have a written camera? Did you see this? What happened? It was all at the same time. Let's put, let's break out the map.
+Jordan: Let's start and see where we can all converge.
+Darius: Yeah, like it just felt real sloppy.
+Jordan: I'm with you on that. I also thought it was weird that only one parent like tried to find the kids. Like I'm not saying the other parents didn't try, but maybe it was off screen. But when he ran into the lady, opened the door and the lady opened the door and was like, hey, can I use look at your footage? She's like, no, I'm like, dude, you're on the same mission. Why would you not help?
+Darius: It just felt like everyone was kind of underplaying how weird it was that 17 kids disappeared at the same time. This isn't a normal Missing child gets found in a river, which is bad enough. But like, this isn't, this isn't an episode of Forensic Files. This is some supernatural ****.
+Jordan: Yeah. I thought that was weird. I also thought it was weird to me that they, I mean, the movie, that's the whole point of the movie. One of the big points of the movie was they all tried to like blame like the teacher and it's like, okay, one kid is safe. Where are his parents? Like, y'all didn't talk to his parents. Like, that's the, to me, that's the 1st place I'm going.
+Darius: Right. Again, a lot of decisions were made to move the plot along, not in the not in the decision that an actual parent would make.
+Jordan: Correct. Yes.
+Darius: Only one of them is yelling at the little is it Vigil or Virgil? I'd never know. Vigil. Vigil. And yeah. Again, I get that he's the main character in the movie, but it's it was just strange to me how nonchalant everyone was about this. Like she talks to the principal and she's like, well, you want to talk to the kid? He's like, oh, I got my lunch. Once I finish this sandwich. ****. You just can't go back to teach an English class. These kids are missing. No one knows. There's no evidence, nothing.
+Jordan: Yeah, also like, I'm even like, think about those kids had other classes, I'm sure, right? Like, so the other teachers weren't affected, the other students weren't affected. Like it just, I don't know it didn't make it didn't that something didn't make sense to me about this movie. Well, one of the things didn't make sense to me about this movie.
+Darius: Yeah, real trophy. You got anything else? Yeah.
+Jordan: Oh, so I go ahead. Yeah. So I did go back and watch like the first half over again. I just kind of see what I missed. And if you go back in the shot where the scene where they're interviewing, I think his name was Alex, the one kid that's left. And his dad is to his right on the on the couch in school. And to the left, there's another person, but they never show the face. But then they show a shot from the back of their head because they're showing the police officers. And you can see the orange hair of who we later find out who is, you know, they were right there in front of everybody in plain sight the entire time.
+Darius: Yeah. Also, let me just say any public school teacher, principal, whatever, If some auntie shows up and says, oh, the parents can't come, they're under the weather for weeks at a time. That's not. Yeah, that's not how that goes.
+Jordan: I'm checking the basement.
+Darius: I remember one time I had to pick up my niece from her elementary school and my sister didn't like make a phone call or something. Man, you'd have thought I was *******. Ted Bundy trying to walk up in that ***** and with good reason. But they was not letting me bring my niece. She was not leaving without some sort of parental contact, context.
+Jordan: No, absolutely.
+Darius: You can't just be like, oh no, his mom told me it's cool. That's how it works.
+Jordan: Yeah, like I remember I was in like third or fourth grade. It was me and my brother and sister. We were all in school together and we like missed the bus. So we're like walking to school and our friend's mom stops and gives us a ride. She just dropped my friend off to school. So my friend was white. So we put the school and it's a white lady in the van and three little black kids get out. And so the next thing you know, the what do they call it? The carpool, like monitors, whatever. They're like, that's weird. So they like bring us into the person's office and like, hey, are y'all okay? Like, how do you know that woman? Like, what's going on? This isn't safe. And they call my parents and like, let them know like, hey, we have your kids here, but this happened today.
+Darius: Yeah, I mean, yeah, the school takes responsibility for the children in their care and they don't take that responsibility lightly, nor should they.
+Jordan: Nor should they, yes.
+Darius: Act 2, the weaponized search. With authorities stalled, the teacher and a distraught parent launched their own investigation because of course, forcing a group of fractured, self-destructive townspeople to confront their own secrets as they hunt for the sole remaining child and the truth. And as I read that, blurb, like the teacher and the distraught parent and the authorities, something like this, the FBI would be involved. It wouldn't just be the one local sheriff.
+Jordan: One cop, a beat cop.
+Darius: Like a couple of detectives. And the sheriff like, oh man, in between DUI stops, just like checking on these missing kids. No, I will say that I do love stories that show the different scenes from different perspectives.
+Jordan: Me too.
+Darius: And so like you would go like you would you saw the the link at the bar from her perspective. Right. And then you later on, you see the cops perspective and you see why he fell for that because he was just having the worst day though he ate from hell. Ever. You know, a little police brutality sprinkled in. He had to do that. But, and so I just love that. Like one of my favorite examples of it is the TV show on Showtime called The Affair It's Over Now. And they would do like, episode would be like first half from the husband's perspective, second-half from the wife's perspective. And like first half from the male part of the affairs perspective and the female. And then they would do like same scenes through different perspectives. And like when it was the wife, the husband would just say meaner things. And when it was a husband, it just, it was cool. So yeah, this one didn't do too much flipping of the scenes based on who was it, but it was like a different angle and it gave you more perspective and more context to the scene. Cause I didn't even know they were both alcoholics until I saw his version of it and saw his wife was talking to him about, you know, you ain't supposed to be on that bottle. So what you got for act two, man?
+Jordan: Yes, I was going to ask you, I got a few questions for this act, but so the first one I'll ask you is, so do you think Josh Roland's character vandalized her car just because, or do you think he did that as a way to like, almost like mark the car so he could follow her?
+Darius: I think in a small town, it'd be pretty easy to follow her and figure out which cars are to get a license plate. I just think he was in deep grief and delusional and just ****. I don't think there's any rhyme or reason for it. I just think he was experiencing the pain that no one can possibly relate to. Right. And he just his brain just told him that made sense. But yeah, you know, yeah, to answer your question, I don't think it was a sort of You could do that, especially in a small town. You could do that with license plates. it's not that hard. So there's probably 2 gas stations in the whole ******* city. So.
+Jordan: Right. So, yeah, speaking to your point about the multiple perspective storylines, I thought that was really dope. It reminded me almost like Game of the Game of Thrones books where these chapters are different POV, different characters POV. And I also always like movies that have like a movie within a movie. Almost like that one scene in Goodfellas where he's it's the whole day where he's just trying to go and like get the coke and the helicopters over his head the whole time, like that kind of ****. And I was really want to like wish this was a book. I think it really would be a really cool idea for a book as well, which is ironic because most books movies come from books, but it was so well written. I do just want to make sure that we give we shout that out as well.
+Darius: It was it was really good writing and yeah, nothing. It didn't feel cheap like you didn't see. The characters other than the parents that were off screen and not doing anything, the characters all made decisions that made sense for themselves within the context of their story. And so I thought that was dope as well.
+Jordan: Yeah, yeah, that's that's a good way to put it. Which POV did you enjoy the most?
+Darius: The cop. The cop. From. Started the day. You know, he's he's I think he he's obviously going through some sort of alcohol withdrawal. His wife, his old lady leaves that he catches the kid mid burglary, runs him down, does a little police brutality, tells him, all right, we'll call it even. I caught you breaking into a house. I punch you in the face. No charges, no harm, no foul.
+Jordan: Yeah.
+Darius: And then. Goza tells his boss right away, we see some police corruption where his boss is like, well, let's just hope it pulls over.
+Jordan: Let's just hope it doesn't. Yeah.
+Darius: It's so normalized. Anyways, we... And then he goes and he gets, the infamous hay tax, which is undefeated. he's like, look, hay is enough. If she's into you, hay is enough.
+Jordan: So he's down in the dumps. He got pricked by a needle. Hopefully he was hoping he didn't get infected with anything, you know?
+Darius: It's not quite how AIDS and HIV work, but I understand why no one wants to get poked with dirty needles. Correct. Yeah. He's asking the guy, when's your last tetanus shot? Like that guy goes to the doctor.
+Jordan: Right.
+Darius: Like the homeless drug addict is like getting his regular physicals. Okay.
+Jordan: Yeah, I don't think the crackhead camping in the woods is going to be regularly visiting his PCP.
+Darius: Right, break. Do you have AIDS? Like, you know.
+Jordan: Like, that **** was hilarious. He's like, hepatitis. Anything.
+Darius: Yeah, right. But what else you got for act two?
+Jordan: Yeah, actually, I was going to say some of my favorite season movies were the ones with the cop and the junkie. Yeah, it was just so funny. Like, it was. It was like some mostly 11 in very heavy movie.
+Darius: So I was so much game recognized Gabe because. he gets stuck and then he punches the kid, which man, nice shot because he knocked him smooth out.
+Jordan: He knocked him smooth the **** out. Yeah.
+Darius: Harder than it looks. And he's just like, all right, man, I caught you breaking into someone's house. We even. Yeah. Like that's a felony too. You know, true. You know, bad police work, but I get why he would, I get why both characters would be like, Yeah. Let's just agree to agree to never talk to each other again.
+Jordan: Yeah, just never just call a truce.
+Darius: Which is impossible in a town with 15 people, but 50 people.
+Jordan: Yeah, right. And I like that they showed like you kind of was that the drug guy was kind of like the glue to a lot of the story because he was always outside the gas station when she was going in to buy the outside the liquor store where she was going to get liquor. And then, you know, he was in the woods and he saw, you know, who it was. And then, you know, everything with the cop as well. And then finding, well, that's actually finding solving the mystery, so to speak. And I love he just everything he did was completely by accident. Yeah. Him just being high, almost drunk and homeless and stupid. Yeah. Dude, my favorite thing is he calls.
+Darius: He's like, I know where the kids are. Can you send me 50 grand? Like, that's how that works.
+Jordan: She's like, can you meet me somewhere? I have a phobia.
+Darius: Yeah. Okay, dude. Again, everyone was bizarrely cavalier about the fact that 17 children disappeared in a thinner. Right. Like, dude, there would be a dedicated phone number for that. And as soon as he called in and saying, I have a lead on it, there would have been police cars on his location. Correct. You don't get to just be like, meet me at the store.
+Jordan: Yeah, let's meet in the Walgreens parking lot. You with the duffel bag. I'll send you the address.
+Darius: Yeah, that's not. You're not. This isn't. That's not how that goes. So yeah, but before you had any idea what was going on.
+Jordan: Going on in terms of the people being used as pawns, basically, or.
+Darius: It felt like disparate parts. I didn't like, I honestly, it just felt like no, I felt like it wasn't even about the children until the cop sees them or to the junkie breaks into the house and sees, you know, what's going on. It just felt like a random story about people in a small town until they, I was just, I was worried that they, that it was never going to get around to being a movie, you know?
+Jordan: Got you, got you. Yeah, I mean, I think. I think I probably figured they had to probably have been in that house because where else would they be? Also, talk about ****** police work. There was like 5 old newspapers in the driveway. The car had not moved an inch in a month and no one noticed or said anything. There's a child who's just getting himself to and from school every day, who usually is carpooled or driven.
+Darius: No one seen a parent. Some crazy aunt is like, oh, don't worry about it. It takes the principle to bring them by, again, does anyone care that the children are missing?
+Jordan: No, seriously, it's like no one gave a ****. It's like, it's sad, but oh well. I guess it's like that in society now too, but.
+Darius: Nah, if 17 children disappeared into thin air, there would be a nationwide 24/7 news cycle to try to find those children.
+Jordan: Well, I mean, the movie is a metaphor for school shootings, and in that sense, people don't care because nothing's changed.
+Darius: Fair. I still think they would, it was, they, they, if that's what they were going for, they were a little heavy-handed. People care more than that.
+Jordan: So I hope so. Yeah, I don't know when I started to figure it out, to be honest with you, because it was just, because like even like the, okay, so we'll just.
+Darius: Act 3, the reckoning. The separate paths of the desperate searchers suddenly converge on a single house where an unsettling force is finally revealed, forcing them into a horrific confrontation to break a devastating cycle and save the missing children. All right, this is where it gets a little stupid. I was like, yeah, because it just didn't make sense. I was just like, the cop gets a lead on the missing kids, doesn't call for backup, shows up alone to a house where he thinks 17 children are missing.
+Jordan: Just stupid.
+Darius: It just got really stupid here. I have in my notes here, they didn't land this plane.
+Jordan: They did not.
+Darius: They did not land the plane. I was really mad because it started great. It had me in.
+Jordan: Yeah.
+Darius: Just like. We get an endless chase scene, which I've said before, I ******* hate that ****. I just like, let's just run for 10 minutes and scream. No plot is moved. It's just really bad act 3.
+Jordan: They fumbled the ending really, really badly, I think.
+Darius: Also, we'll say that.
+Jordan: Yeah, yes. So the boogeyman, killer, whatever, kidnapper is.
+Darius: Still don't know her motivation.
+Jordan: Right, I suppose, yeah, the one kid's crazy aunt, she possesses people with a a rose stem and she wraps their hair around it, cuts herself, breaks it in half and they do what she wants or they kill people. And they run like this, like they're doing at the airplane.
+Darius: And they're invincible unless they're shot or hit by a car.
+Jordan: Right.
+Darius: But they don't, they're impervious to stab wounds and it's just nothing.
+Jordan: She shaved, remember she peeled the dude's face with the peeler? Yeah. Just like nothing happened.
+Darius: Oh, like the guy, the principal is in the store. and he's just like running into brick walls and yeah he's a ******* zombie and again this is where it got really stupid I just was like all right man.
+Jordan: It did get really stupid they did not.
+Darius: Land this point it just.
+Jordan: Didn't make sense because it's like one why is she doing this are they like her life force she needs to feed off souls I guess okay but why how'd she get like this she also she's like the the kids aunt great aunt so was her mom like that too like it?
+Darius: The who, what, why, where, and how.
+Jordan: When, where, and how?
+Darius: We got a who, we got a what, we got a when. We never got a why and a how.
+Jordan: Yeah.
+Darius: You got to answer those five questions to get them. If you in a thriller, you have to answer those five questions.
+Jordan: Yeah. If this move was a current event, they would have failed that assignment.
+Darius: Yeah. It's just we never got a why. We never got a how. She just kind of shows up. as an aunt that's sick and just starts kidnapping children telepathically and.
+Jordan: Telling people to poke themselves in the face with forks all right and.
+Darius: In the end it's just like an endless chase scene where there's like shooting and there's salt on the floor and he doesn't I was like all right this is stupid what times a game come on it's kind.
+Jordan: Of like you mean to tell me salt salt was the answer the whole time that okay yeah I don't.
+Darius: Really have anything man because all I got is this is stupid.
+Jordan: I was going to ask you, like, did you, because I was like, am I missing some symbolism here? Like, what am I missing? I don't. It just.
+Darius: Act one and two are great. They just, I don't know. Everything from the moment the cop shows up at that house and then drags a junkie in there is just stupid. Like, I don't really, I wish I had a more eloquent way to put it, but it was just stupid.
+Jordan: Yeah, it was stupid. They nailed the last like 30 seconds where they talk about how Some families were never the same and some kids were kind of able to speak again, like in terms of just the trauma of what happened. That was the only thing to me that landed. Well, I think a lot of scary movies do</t>
+  </si>
+  <si>
+    <t>Darius: I will never ever forgive anybody for making Jack Harlow a thing.
+Jordan: Hey everybody, welcome to the Out the Trunk Pod with Jordan and Darius. My name is Jordan. That's Jordan B. Riding on all socials.
+Darius: And I'm Darius. That's Deez I love you area on all socials.
+Jordan: And this is our movie review segment. Today we're going to be reviewing White Men Can't Jump. It's movie, the 90s version, the original version. Sans Jack Harlow. Rico like Suave, I'm a GK. Throw up the AM.
+Darius: Oh my God, he was so bad.
+Jordan: No, we really let him have like a career for a minute. That **** was crazy. Starring Wesley Snipes, Woody Harrelson, Rosie Perez, and Tyra Pharrell. This movie is about two mismatched basketball hustlers in LA, one black and one white, who form a shaky partnership to hustle players on the street courts. Their constant bickering and competing personal debts threaten their ability to win big and achieve their goals for their partners. So I'm going to tell us to you to open the back one.
+Darius: Act one, we're going to call the initial rivalry. Billy, a white hustler in debt, uses assumptions about his game to win money. The assumption means white boys can't jump. He crossed paths with Sydney, a talented player, leading to a tense argumentative confrontation on the court. Shout out Floyd Henderson and Kadeem Harrison for the cameo appearances. We've had El, the dude from Comic View who used to host on the side, he was a guy in the store. So it's always funny to go back and watch 90s Blackshade specifically and see like the small roles people who ended up having bigger roles later on had. So also these are some terrible basketball scenes. The magic of editing was not evolved as it is now. So what you got for act one?
+Jordan: Yeah, I was going to say, I was thinking the same thing. literally pretty much every who was like somewhat popping in the 90s was in this movie at some point. Like, even, do you know the guy who hosts Gilbert Arenas' podcast, Josiah Johnson? He does like the meme and **** on the sports memes on like NBA and ****. No, that's his dad though. That's his dad though. Okay, I got it. The guy who does, who says, I'm gonna go to my car, get my other gun, come back and shoot everybody. Yeah, that's his dad. How did I know that? And his dad actually hooped for real. He played in the NBA for like 10 years.
+Darius: Okay, all right.
+Jordan: He was a bucket. He put up like 20 bucks a night damn near.
+Darius: Ronaldo Ray was the guy I was talking about.
+Jordan: Oh, okay.
+Darius: Yeah, he used to, if you ever watched Comic Union for the 90s, he was like in the guy, like in the kitchen or whatever.
+Jordan: Gotcha, gotcha, okay.
+Darius: Black famous comedian from the 90s. I don't know if he's still with this or not, but if he is an RIP, anyways.
+Jordan: I also really **** with like the scenery of the movie. Like I love that the vocal movie takes place at Venice Beach, which is like a famous California location. They shot a lot of movies there. I thought Kobe used to go out there and hoop all the time back when he was young in LA, when he first got to LA. So I thought that was dope that they kind of kept it very authentic to Los Angeles without just showing all, showing like the Staples Center and the Hollywood.
+Darius: Sign and **** like that, No, it was clearly shot on location. But it does, it is interesting though, because these are, these characters are clearly poor. Right now, Venus Beach is some of the most expensive property in like all of LA.
+Jordan: Crazy gentrification.
+Darius: These are multi-million dollar pieces of land. And these characters, which brings me to my question. Why don't these people just get jobs? Like this can't be worse than working a job. It's like I'm gonna be worse than working a job.
+Jordan: Hoop every day in the California sun.
+Darius: Playing 2 on 2 for like 20 bucks. The first bet was $62. Like.
+Jordan: Yeah, $62. No, I'm **** that. Listen, welcome to John. Listen, welcome to Good Burger. Can I take you home to Good Burger? Can I take your order, please?
+Darius: This cannot be worse than just working a job. Waking up every day having to hustle. $20 to get McDonald's food. It is like, dude.
+Jordan: You're like hustling like the working homeless. Like, it's just...
+Darius: It's like, it can't be worse than just getting a job.
+Jordan: No, I agree. I definitely thought about that too. Another thing that seemed that like was talking about crazy inflation, like when she's like, oh, I need 30 bucks for groceries. What? If you went to the grocery right now, they get you 4 bags of chips.
+Darius: Man, I made a roast a couple Sundays ago and I got a chuck roast. It was like a 2 1/2 pound chuck roast. And for the uninitiated, chuck is a cheap cut of me. That's why you make it for roast because you have to braise it for hours and hours on end. That ************ was like 36 bucks for a roast. Like literally, this is the throwaway piece of the cow. That's why you have to braise it for four hours because it's tough. I never, I mean, a roast of that big used to be about 18 bucks. I was just completely blown away that a roast was 30 something dollars. But that's it to say she would not have been able to buy one roast.
+Jordan: No, I remember from my party, I bought 3 or 4 12 packs and like come back chips, maybe some sodas, whatever. It was like 80 bucks.
+Darius: Dude, I haven't bought soda in a very long time, but I remember when 412 packs was $10, you get 4 for 10 bucks. Yeah, man. It ain't nothing to run it up 80 at the grocery store. You can run it up.
+Jordan: No, it's nothing.
+Darius: And you ain't even bought snacks. You ain't bought meat. Like you just.
+Jordan: No.
+Darius: You just really bought, like you said, bought some snacks and ****. Which is funny because that's how wild inflation was because before I used to run to the grocery store when I can't tell that story. But a couple of years ago, it was way cheaper to go to the grocery store, for lack of a better word.
+Jordan: What else you got? Yeah, man. So the first, not first scene, but the first like basketball sequence where Billy meets Sydney and he kind of rolls towards the end of the game. He's been hustled. It's just crazy because like if Sidney was a hustler and you couldn't recognize that he was also a hustler because his hustle job like wasn't that good. Like he was sitting there all day.
+Darius: Yeah.
+Jordan: Watching y'all hoop in a bad. Oh, wait, white boy.
+Darius: Oh, yeah. Is this how you do it? What's it?
+Jordan: I never make I never make two in a row.
+Darius: Well, so there's anytime you watch a 90s movie, there's a suspension of belief that goes into it because People were just like, it just, I don't know how to explain it, but you just have to understand that this was believable at the time. Right, Like the idea that white boys could hoop at all outside of Larry Bird was like unfathomable.
+Jordan: Insane, yeah.
+Darius: So it's not at all, for them to be incredulous in 1992 is not that.
+Jordan: Yeah, and it's actually funny because like it's to that point there's legendary stories where like literally Larry Bird would be mad if you put a white guy on him. He was like, that's really respectful. Like, put a on him. He didn't say that.
+Darius: But like, that's my favorite Larry Bird story is he took offense when they put the white boy on him. So that, like the whole theme of the movie was playing off of that. Like this white can hoop, but this is rare this is extraordinary phenomenon so you got anything else track one.
+Jordan: Um yeah what the happened to basketball courts like they used to be really easy to find yeah and I feel like they're like nowhere right now like like near my in my neighborhood there's a h a h a court but they took all the rims off because of covid yeah and they just never put them back and like I don't know where people supposed to go to hoop anymore well so that.
+Darius: It's like a growing trend of like the privatization of public spaces. Now, when people want to play basketball, they have to have a lifetime membership. And so right, which sort of sort of takes away the that's the reason why the NBA just feels like it's a suburbanite sport. Yes, because it is, you know, So people don't hoop outside no more. it's about the controlled environment. You don't want the wind to pick up your ball. You don't want the double rims. You know, the hard, the hardwood, the hard, the concrete is harder on your knees and joints. And so, yeah, all the hoopers have went inside. It's all controlled environment. No one just goes and finds a run anymore. We've just like, you know, even parks nowadays are like carting at the door, you know, and like you gotta have a pass and like, there's not a lot of public space for people to just exist without spending money anymore. So, that's like we have one in my apartment complex, but you have to be a resident, but it's free if you're a resident. And, I had to catch myself one day. It was like a Sunday during the summer. And I had the patio door open and the kids were out there and they were just being kids, making noise and stuff. And I was cranky about it. And I just had to stop myself. Like, look, man, these kids outside being kids, what kind of miserable. I was like, you're being a miserable old *** man, being upset that you hear kids having fun outside, you know? And so like, you don't hear it very often. So it was just, that's how rare it is now that it ****** with me a little bit, but I had to check myself that, you know, so. To answer the question, that's where they all went. They went inside and now that they're bouncing the door charging you for a membership, so.
+Jordan: Right. I think that's all I got for act one. You got anything for act one?
+Darius: No, we can move on to act two, the grind for cash. The two players reluctantly decide to team up to maximize their earnings traveling across LA course to exploit parks. Billy's gambling addiction and Sydney's desire to move her family, his family, create mounting pressure on their scheme. a big context there. Billy shows up, hustle Sydney. Sydney obviously catches the hustle at the end, pulls up on Billy, like, let's, you know, let's run this, let's run this game. I won't say it too, man, but that's totally different context in 2025. So he's like, let's, you're the white guy, we can hustle this together. I just wanted to say off the top. There's so many scenes in here that in my 2020 eyes just seem excessively violent before I remember that the 90s was excessively violent. Like he's at our house, conversation, she just pulls a gun on him.
+Jordan: Yeah, like it's just like.
+Darius: Just pulls a gun on him and he's just like, hey, chill.
+Jordan: Yeah.
+Darius: He's used to this. And the first guy they hustle, he just starts swinging a blade at the.
+Jordan: Yeah.
+Darius: Like the number of just like latent, the amount of latent violence that just existed in the 90s, especially in places like LA. Like this was not an exaggeration. This was. Yeah, no, it wasn't like. Clearly her husband, boyfriend, whatever knew this person. They're casually having a conversation. Is she just ups a gun on him?
+Jordan: Wait, what? the ****?
+Darius: Okay. All right, fair enough.
+Jordan: And if he had hit you, self-defense.
+Darius: Yeah, I mean, the 90s was an extremely violent time. It was a wild time. Crown has definitely gone up since COVID, but it is like you cannot even, it's hard to even fathom how bad it was in the 90s.
+Jordan: It was about as close as you could get to the Wild Wild West, like since the Wild Wild West.
+Darius: Interpersonal disputes were just handled with gunfire. Like it was like regularly and maybe the cops investigated it, maybe they didn't. I don't know, like, depending on what. But it was not at all uncommon to just like, oh, you lost the basketball game. I'm just going to go get my gun and shoot the ***** up. Like, no.
+Jordan: Yeah. I remember Shannon Sharp told a story where he was in college and they used to hoop and somebody got into a fight and I think somebody maybe said some **** about somebody that's girl or, you know, whatever. And somebody He was like, I could tell she was about to get bad. He's like, I left. Dude, buddy left, went to the car, came back. Two people died. He in jail for life.
+Darius: Like, yeah, that's just, that's just, that was just the 90s. Like, yeah, people, people would just be chalked up outside. You're like, on your walk to work, you would just see like white sheets over chalked up bodies. So, you know, Yeah. Also, 90s, people were very poor. These people were living in motels, like one room, studio, motels, jumper. Well, Sydney had a crib, but like Billy, he had a crib.
+Jordan: That shower looked like a walking, a closet.
+Darius: Yeah, man. Like these people were in them trenches.
+Jordan: Yeah.
+Darius: So I just, the amount of poverty and the amount of violence that was just like a character in the movie without whatever mentioned, it just, it just was everywhere. It just was, it was like air. It was just, it existed in the movie without everyone, no one mentioning it because it's all they do. So right. What you got for act two, man.
+Jordan: Yeah, speaking of working, yeah, I'm like, so you mean to tell me you're doing like off book construction jobs and you're hooping every day and you were married with a child and you want your wife to not work Cause y'all doing so well financially.
+Darius: Get the **** on. Yeah.
+Jordan: Like the ego of some people, please. Like, let that woman work.
+Darius: You know, and also like, man, you and the projects, man, you can get with somebody's teenager to babysit your kid for a little nothing. This ain't the 2025 daycare. It ain't even like that.
+Jordan: The $2 a month and **** whatever.
+Darius: No, I mean, half the paint got led in it anyway. So you don't even need to do none of this. No, man, it was. It was weird, man. And it's like, dude, even they had teamed up hustle was for like a couple 100 bucks. And it's like, how many hoops can you even run this on? And like, what's the plan? It's just, I don't know, man.
+Jordan: They were hooping as if, remember in good times, they're like, they'd be like to rent 75 bucks a month. Okay. Like if you hustling and hooping, you're getting 100 bucks a day, a couple 100 bucks a day. Okay. That makes sense.
+Darius: Yeah.
+Jordan: Your bills are hundreds of thousands or and or thousands of dollars. There's no way you're paying them off shooting hoops every day. Like there's just no way.
+Darius: And Billy was down like 7 grand, which in 90s money.
+Jordan: Yeah, it's like 20 grand today.
+Darius: What was he? He was planning on getting the street hustling basketball players.
+Jordan: For 60 bucks a game.
+Darius: I do want to say, though, this is something that someone pointed out to me, and I can't unsee it now. It's like a lot of inseldom is watching movies like this and thinking like that back in the day, you could be dirt **** bag Rosie Perez. Like, please, man. Why would she be with this guy?
+Jordan: Even Tara Farrell, she was ******* gorgeous.
+Darius: Yeah, she was. Both of these dudes, well, assuming they're characters, you know, obviously these are good looking men in real life, but their characters were quite downtrodden. Way, way out of their league. These women would have had way better options than two big basketball hustlers.
+Jordan: Yeah, even the girl, the girl that the boy Yeah, the women were. She's not dating. No, the woman looks like that. It's not dating a dude who has to hoop for bills.
+Darius: It's not just sitting outside all day watching you play pickup basketball. No, with like, what are they? We'll get. Does anyone have jobs? Yeah, I call these grown men are just hooping in the afternoon.
+Jordan: Yeah, that **** was crazy.
+Darius: What else you got Frank to, man?
+Jordan: Okay, so then we got the scene where They go to the park and they lose. And then Rosie has to tell Billy that, no, you got played. He was hustling. He was working you. They go over to the house and they kind of like chill out a little, whatever. I guess the wife decided they were going to run the tournament together to kind of get the money back. Were you surprised when the way the wife handled it? Because like the first time I saw them, God always thought like, oh, she was going to be like, you're wrong. Give them their money back. She's like, **** you. We got bills.
+Darius: She won a lot of them projects, man.
+Jordan: Yeah.
+Darius: No, I wasn't surprised. I. Maybe it's me getting soft about age. I was disappointed in Sydney, though. I had seen this movie before, but it's been a while. No, it was a little. I just like, man, there was a man like. Yeah, like, yeah, that's like, damn, is there no honor amongst these thieves? Yes. But, you know, but like, what's the again, though, if you just hustle everybody Sooner or later, people, what is the end game?
+Jordan: Someone's going to want to get back at you.
+Darius: Yeah, because you're not winning these straight. This is.
+Jordan: No.
+Darius: It's one thing to lose your money straight. It's another thing to get cheated. I mean, he threw the game. Like, you know, he did not. as well as he's used to playing because he had an agreement outside of the stated terms. And that's not an honorable, like even amongst thieves, that's dishonorable.
+Jordan: So yeah, I think the violence was downplayed actually a lot in this movie because if you were hustling people who were doing this for a living, I think somebody would have shot you or something.
+Darius: I mean, especially in the 90s.
+Jordan: Yeah.
+Darius: So yeah, these, well, they did have the hitman running after Billy. Right. I mean, I get with that why they kept him alive, though, because dead men don't pay any bills. Dead men don't pay no bills, yeah. Right, so, but it was weird that, like, you're right, though. In a way, it was violent, but it wasn't violent enough, considering how much scamming they did.
+Jordan: How desperate they everybody was. Yeah, it wouldn't make sense, honestly.
+Darius: Everyone was in them trenches, man. You got anything else right too?
+Jordan: Yeah, so there's the scene where He just said, oh, you got a fine lady. I don't think he meant fine attractive. I think he just meant fine nice or quality. And Billy kind of got into this argument with him. And I wish they had delved more into a little bit of the racial politics of that interaction in the movie, where it's kind of like, you can hoop. You can **** a black girl. You can hoop with a and get money with him. But you don't want me to like. It just kind of, it's almost like the slave slave **** where it's like can't be in the house type **** a little bit. And I kind of wish they had like delve a little bit more into that in the movie.
+Darius: I could see that. I don't think you're ever going to get that out of this kind of movie.
+Jordan: Well, no, for sure, for sure. But I think it would be interesting.
+Darius: I mean, Billy was quite clearly a racist. But you know, he's I agree. I don't really have anything else to add to that, but I would agree.
+Jordan: Remember they were playing music and he just was like, don't play that *****. She didn't hear like he said ***** but we know what he meant.
+Darius: He said that because Sydney was in the car.
+Jordan: Right.
+Darius: So yeah, I agree. Billy was definitely racist in the way that, you know, like he, you know, he doesn't, he's not like joining the clan, but he just clearly thinks that there's a social hierarchy that must be maintained at all times.
+Jordan: Correct.
+Darius: Anything else for active?
+Jordan: Yeah, the gambling addiction aspect or portion of the movie, I mean, they touched on it in various spots and conversation with him and Gloria, but I wish they had, I kind of wanted to, would have wanted to know from a storytelling aspect, like where it started or, was the hooping just a manifestation of that or did the gambling contribute to him like playing basketball, if that makes sense. I kind of which one came first or which one fed which.
+Darius: We played in Louisiana. He said pick up for a college team.
+Jordan: College.
+Darius: I think I don't know if he had a gambling addiction as much as he just had terrible money management skills. And I don't think he saw it as gambling as much as he was. Right.
+Jordan: He puts out a certain thing at the time.
+Darius: And he just, I mean, he, I have in my notes here for act three. I'll just start it here. Like he was just a loser, man. He was just a gigantic loser. We get into act three a little bit like he just, you finally break through, you get your big break, you're up five bands, you split it and you get goaded into a dunk contest.
+Jordan: That he didn't even want to do with you.
+Darius: He didn't even, he felt bad, but again, he's amongst the things like.
+Jordan: You know, a sucker's born every minute. What's the quote from Rounders? It's immoral to let a sucker keep his money.
+Darius: Right. Clay Davis, Clay Travis, you know, Clay Davis from The Wire. I'll take any motherfucker's money if he's giving it away. You know, Just a quick just get to act three. High stakes and hard lessons. After a dramatic double cross, the two rivals must reluctantly reunite for a high stakes local tournament with the big cash prize. Their victory is immediately complicated by a new risky personal ranger between them. The way they're referencing is they win the tournament of 5000, which is a lot of money.
+Jordan: Hell yeah.
+Darius: And so especially for them, especially for the 90s. And he just blows it all in some stupid *** ego driven. Can you dunk? That's what I was just like, Billy, man, come on, dude. Like, yeah, you're on the way home with the money.
+Jordan: Just go home.
+Darius: Just go home.
+Jordan: Do you know how many problems people would solve?
+Darius: By if they just went home.
+Jordan: Eat the pizza, eat the pizza, drink the wine.
+Darius: Drink the wine, **** you, live to see another day. And live to see another day, man. Like, what are you doing? Yeah. And so I just, Billy, man. I think to speak to the gambling edition, I just think everything in this culture was just a wager. Like, so he goes to the park, the guys somehow the security guard controlled Jeopardy booking, but that's movie magic.
+Jordan: By the way, you make, you work security for a big LA production and you live in the, I don't know. what they pay, but I assume, I would think they pay it.
+Darius: Well, that's not the unbelievable part. It's totally believable for me that like some guy who works the door would not be making a ton of money. What's unbelievable is you have to kind of pull to cast Jeopardy. You know, like, oh yeah, let me talk to the guy.
+Jordan: Yeah, let me get you on with Mr. Jerbek and the.
+Darius: Next scene she's in. But I speak to the gambling culture, like even that was transactional. He's like, I'll do it if you hit a hook shot and if you lose, you lose your car. And it's just like, No, there are no favors. There's no nothing. Everything is a wager. So yeah, so I don't think he had a gambling addiction as much as he was just a product of a culture where everything was a wager.
+Jordan: That's fair. That's true.
+Darius: Billy was a loser. Sydney's double cross made me sad. What else you got for act three?
+Jordan: Yeah, the Gloria thing where like she leaves, then she goes back, then she leaves again. It was it just for him was okay. Well, You knew who he is. You knew what he was.
+Darius: Yeah.
+Jordan: He was going to blow the money. If not now, whenever next time he got some money, that was going to get blown.
+Darius: Yeah. Well, so there does become a point. I always say that like.
+Jordan: No, for sure.
+Darius: Everyone, most people are poor money managers just because the concept of managing money is relatively recent on the evolutionary scale. It's just a matter of do you start to make enough to where you can outrun your poor money management? It just doesn't matter anymore, right? So Billy might, I mean, once she had the jeopardy money and, you know, he gets some sort of stability, he might've turned it around because he wasn't, he was a loser in the sense that he just, he couldn't know a bad decision from a good decision. But you can out, it's not true that everyone's money problems are static at every level of income because, you know, I always say most people are bad with money. It's just that some people make a lot more to where their mistakes aren't. They don't matter. Right. Ordering DoorDash is objectively, waste of money, waste, wasteful and inexpensive, but it doesn't matter if you can afford it. You know, like, right, But if you are on SNAP, like I always say, like there was actually you can't order hot food with SNAP, but I am pro Snap, fully funded, all of that. But like, I'm not going to sit up here and lie. Like if, for some reason you're on Snap and you use it for DoorDash, that is a, that is an inefficient use of what are your limited resources. Like I'm not going to, you know, like you're not going.
+Jordan: To do so, but yeah, you've blown an extra 20 bucks on that food.
+Darius: Yeah, I mean, well, here's the reason. They should be able to do so not because it's like the right thing to do, but because creating the bureaucracy and administrative burden that would go into creating all these different categories of food that are eligible for the peasants. The amount of money you save wouldn't even be worth how much it would cost to build that infrastructure. So it's just like, sure, I understand why it's people find it off putting and distasteful for someone to buy like lobster tails with food stamps would snap. But like preventing it would It's such a waste of money. It's just such a waste of money. So like most people with limited resources for food are not going to go buy lobster tail. And it's like the money is the money is the money. You don't get more if you buy lobster tails. So we just, it's just easier to just, look, if you want to blow it on 4 lobster tails and that's what you're going to eat all week, it's not worth us trying to prevent it. You know, like, I don't understand why someone would find that off putting. So I get it. but the argument, I hate when people make the argument that like, why do you care? It's no big deal. It's like, okay, I understand why someone would care. But the real argument you make is that it just would be too burdensome on the administrative system to create, oh, now you got this grocery clerk going, oh, nope, this doesn't qualify. Oh, no, it's just too much work. Just let people do it.
+Jordan: It's just harder on everybody. And honestly, the truth is that as someone who worked in a grocery store, like it does a lot of the. administrative and political things that take place they really fall the back a lot of customer service people honestly like car parts price car parts goes up price of insurance goes up some customer service got rep is getting yelled at over **** that they have no control over you know what I mean?
+Darius: So you got some teenager working part-time for 12 bucks an hour getting screamed at because he says oh you can't get crab legs with this and it's like right and then what that person puts back the crab legs and it's just like Okay. Like what is why? Now everybody's day's ruined. It's like, for what? And for who? To save $1,000,000 a year on the federal budget, which is a rounding era. Like this is a waste of our time. So honestly, you wouldn't even save it because you'd have to pay someone to build all this infrastructure out. So I don't even know how we got here. But what's up with that three, man? What you got for that three?
+Jordan: I did like that how, because Sydney looked out for Billy with the the Jeopardy hook up.
+Darius: Yeah.
+Jordan: That when he got robbed, he was able to help him flip the robbery or not flip the right, but make some money back to kind of sustain himself financially, even though they lost everything.
+Darius: Yeah, he returned the favor, cost him his girlfriend. But, you know, he made a friend in Sydney. It was cool to see the movie ending, you know, with them as friends. But So let me ask you this. Was Gloria right to leave?
+Jordan: I think she was right to leave him. I think she was right to leave him because of his money management issues. I think she was wrong to leave him for that particular incident in terms of his money management issues, if that makes sense. Like he's helped out a friend. They say they're pretty confident. You've seen them hoop. You know, I think also, as a matter of fact, we wouldn't bring stuff except I forgot. I didn't get why Sydney didn't just tell Gloria what happened. Yo, we got robbed. We lost everything. They took our five and five grand. I think she probably would have been understanding and she probably would have been like, okay, cool.
+Darius: One, he's a man with pride. Two. True. Two. Billy bit his head off ******* an hour ago for calling her cute. So true.
+Jordan: Yeah.
+Darius: Yeah.
+Jordan: So yeah, I don't think she was wrong for leaving. I just think it was inconvenient when she chose to leave him. Yeah, because he actually was doing the right thing. But I think, you know, when you're at your what's end, you know, in your last straw, your last straw, it just is what it is. Nothing. There's nothing more to say that can be done there. I just was confused at the fact that at the fact that Billy didn't realize that it was over over when she when she walked away.
+Darius: You know, she She come back before every time, and he's done way worse. So yeah, we're having some internet issues. So let's land this plane. I do agree. Gloria should have left him. Sometimes you're just done. And yeah, you can't. She's just done. That was her. She came back to him that last time. He sings that terrible song at Jeopardy, takes that moment from her. But nonetheless, it's the 90s. And you do all that just to go gambles again. All right, man.
+Jordan: So what do you rate it, man? It's a fun 90s movie. Love the actually forgot. I love the soundtrack. I miss the 90s in terms of like the fashion and ****. This movie did a great job of showing that. I'm going to give it a 3 1/2 stars.
+Darius: I'm going to go four stars. Easy watch. Love the 90s?
+Jordan: Yeah.
+Darius: I miss movies like this. It was good, 90s, under 2 hours, pretty linear plot.
+Jordan: Yeah.
+Darius: And we just got to watch two dudes have some hijinks. So, all right. Thanks for listening. My name is Darius. That's Deez All up in your area on all socials.
+Jordan: And I'm Jordan. That's Jordan to be writing on all socials.
+Darius: Please rate, like, subscribe. We are out the trunk pod on all socials. That is out the trunk pod on all socials.
+Jordan: And for any ongoing movie recommendations, feel free to reach out to us via e-mail at outthetru</t>
+  </si>
+  <si>
+    <t>Darius: What do you want to watch next week, man?
+Jordan: Let's see. We're doing a lot of slashes lately. You want to do a drama?
+Darius: Yeah, sure.
+Jordan: Okay, let's do. Have you seen The Judge, Robert Downey Jr.?
+Darius: Yeah, I saw that in theaters when it came up. We can, I can go.
+Jordan: Hey everybody, welcome to Out the Trunk Pod with Jordan Darius. My name is Jordan. That's Jordan to be writing on all socials.
+Darius: And I'm Darius, that's Steve's I love you area on all socials.
+Jordan: And this is our movie review segment. For this episode, we're going to be reviewing your next little slasher film for Halloween. Happy Halloween, everybody.
+Darius: Happy Halloween, everybody.
+Jordan: Y'all be safe and **** out there. Be safe.
+Darius: Ladies wear the costumes with the *** out. You're not too grown. Let's do it.
+Jordan: Yes. Shout out to all the Velmas out there. Y'all the real VPs.
+Darius: ***** out. That's the whole point of why we are outside on Halloween.
+Jordan: This is literally the point of Halloween.
+Darius: Costumes with your *** out, please.
+Jordan: Yes. This movie came out, speaking of ***** out, because there's a lot of that in this movie. This movie came out in 2011, starring Sharni Vincent, Nicholas Tucci, Wendy Glenn, A.J. Bowen, Joe Swanberg, Margaret Levy, and sorry, Amy Simowitz, T.I. West, Rob Moran, and Barbara Crampton. It's okay if you've never heard.
+Darius: Of any of these people. I was going to say, be inspired.
+Jordan: If you've never, like, don't be like, who are these? As you were reading them, I was like, no one knows who these people are. Yeah, it's just a bunch of white people in this movie. So this movie is about where a film reunion at a remote mansion is violently interrupted by mass killers. As the family is systematically attacked, one young guest reveals an unexpected and extraordinary set of survival skills, turning the home invasion scenario into a desperate fight for her life. So I'll toss it to you for act one.
+Darius: Act one, a tense reunion. A wealthy, dysfunctional family gathers at their remote vacation home in rural Missouri for a celebratory weekend. Long simmering family tensions and arguments quickly surface at the dinner table, setting an uncomfortable mood just before their evening is violently shattered by an unexpected external threat. We started the movie with what might be the most pointless sex scene in cinema history.
+Jordan: I had no point in serving no purpose.
+Darius: I've never seen a sex scene serve less purpose. I tried to think of 1 and I was like, no, this is the most pointless sex scene.
+Jordan: Literally. They could have been ******* reading a book together and it would have been just as effective of an opening.
+Darius: That whole scene meant nothing. And then they just threw a sex scene in there. And it just was like, I've never, again, I thought long and hard. I cannot think of a more pointless sex scene.
+Jordan: I feel like they just wanted to show ******* in this movie. I think that's.
+Darius: Right, correct. It was just the last 30 seconds randomly.
+Jordan: It was super like loveless. Like it was just.
+Darius: It was. Well, to be honest, it's like a cult classic. Apparently.
+Jordan: Yeah, it is. Yes, I Google that. I found that out too. Yeah.
+Darius: But no, that's my first observation is. Giving it gold medal Olympic Award for the most pointless sex scene in all of movies.
+Jordan: Correct.
+Darius: What you got for act one?
+Jordan: I agree. What do I have for act one? It's funny to me that so this movie obviously is just this. It's supposed to be like a rich family, but the movie is so low budget that they couldn't afford to make the family look rich.
+Darius: The house was nice, but you could tell it wasn't filmed in the house from the outside. Right, exactly. They just went and got random drone footage of rich people's houses.
+Jordan: They just like shot from outside. It was like, okay, cool.
+Darius: Let's go into set now. The budget was $1 million.
+Jordan: Yeah, I saw that. Yep. And it made like 65 million, I think.
+Darius: Yeah, I mean, it came up. I went and saw it in the theaters. So, but the budget was literally one single $1,000,000.
+Jordan: Yes. And it was literally all on the stunts and special effects.
+Darius: Yeah.
+Jordan: Because, because the acting they got for free. Oh, okay. That's my question. And you get, and you get what you pay for.
+Darius: There's a reason why you ain't seen none of these anything else?
+Jordan: Correct.
+Darius: Yes. The argument, the argument was like, oh my God, no. Are you sleeping with her?
+Jordan: No. It's just stupid. Like, like even like, there's like the scene where the sun Scares the dad by accident. And I was like, is he just creepy or is he a bad actor? I couldn't tell. I still don't know. I watched the movie twice. I still don't know.
+Darius: That's a point of contention was the acting bad or was the ad back or was the acting bad or wasn't bad acting part of the bit part of the it's almost like Napoleon Dynamite where he the bad acting was part of the joke. I can't tell, which leads me to believe that the joke didn't land.
+Jordan: Yeah, I think, yeah, because I was like, are they supposed to be showing like that they're ****** at being villains or are they just ****** actors? Because like the one son, he's supposed to be like a non-assuming guy, but he has this like creepy smile, random moments in the, like it's just, he's like, hey dad.
+Darius: Like what? First, there's like the most unsexy come on ever when the older brother with his wife in the bathroom.
+Jordan: And she's like brushing her teeth and he just starts taking her bra off.
+Darius: Like with the coldest hands. Like I could feel how cold his hands were from ******* my couch. Like dude, you gotta be a little bit, first of all, y'all just got like.
+Jordan: I just drove however many hours from whatever city you live in.
+Darius: You meet your granny's in the next room. Like, you know, listen, ***** strikes are ***** strikes. So I'm not here to cast judgment, but a little bit more finesse.
+Jordan: Correct.
+Darius: And he walks away and he's like, God, you like it? So all right.
+Jordan: So you don't *** ****. You need a pill. I don't know. Okay.
+Darius: So he just let. So okay. They were looking, what did, why did he send old girl? Long story, they sent his girlfriend who he barely knows to the neighbor's house in the middle of nowhere by herself.
+Jordan: That was crazy.
+Darius: You know, don't send your girl in the middle of the woods alone. Don't do that. I think we need to announce that, but don't do that.
+Jordan: Yes. A lot of this movie goes back to something we talked about earlier where certain movies only work if the characters are all really stupid.
+Darius: Yes.
+Jordan: In this movie is a testament to that. I did like the misdirection, I will say, because when I first the first opening scene where they killed whoever the bad guy is, as we know him at that point is they kill the student with the old professor or whatever. And I thought it was like one of those like, you know, in horror movies, there's like certain rules and **** like that. Like I thought it was like the I'm going to punish like the horror type thing, you know, like some religious **** or something. And then when the son drives in with the girlfriend, the British or Australian girl, and she's like, your dad's rich, like, whatever. And he's like, I hope you don't have a problem with fascists. Then I thought it was going to be like an eat the rich slasher.
+Darius: Yeah. One lazy exposition. How would she just like?
+Jordan: You just you Googled it your dad.
+Darius: She's basically in the audience and she's asking questions we would ask. And I know I said in a previous preview that you're supposed to use the B plot to sort of explain things to people. It's not supposed to be that heavy-handed. It's like, that's the art of writing. You're supposed to, you know, the subtlety of it. Yeah, so. Yeah, I mean, what you got fragged? What?
+Jordan: I think that the movie didn't. I knew earlier that the people were stupid when there was just a mom and dad in the house and someone's upstairs and you hear that you see the chandelier like rattle or whatever. She's like, honey, there's someone in the house. And he's like, okay, well, you just go outside and I'll go just by myself. Horrible 101. You never, ever, ever split up.
+Darius: No, I mean, in any sort of survival situation, splitting up is just, it's rarely worth it unless one person is injured and you need to go for help. But like, there's power in numbers and it's just hard to kill two people versus one. And Especially too, as we get late, my observation in act 2, once the chaos breaks out, is just the one I have for all of these horror movies. So I'll just save that one.
+Jordan: Yeah.
+Darius: We got anything else for act one?
+Jordan: Yeah, that's really ****. I mean, act one is pretty, yeah, act one is pretty nondescript. It's really act two and three where the movie kind of hits some sort of stride.
+Darius: My favorite part of scary movies actually is before the **** breaks loose. So I always enjoy act one. the scene setting, like when I watch The Strangers, I like it. I just like to see, that's honestly, I've watched this movie a lot, but I almost always stop around Act 2 because it's just like, all right, this is just, you know, whatever scary movie it was. But Act 2, Chaos and Counterattack. As mass assailants besiege the isolated house, the terrified family scrambles to find a way to survive. Amidst the carnage, one unlikely guest with a surprising background takes charge, revealing A remarkable resourcefulness and shifting the balance of power in this desperate confrontation. As I said earlier, this is all these movies are premised on no one having guns in America. Correct.
+Jordan: So you have a cabin in the woods with ****** cell service and you didn't think to bring it in a gun?
+Darius: In Missouri. they're in Missouri.
+Jordan: I didn't even realize that.
+Darius: It's yeah, like the bad guys don't have guns, which would have made their jobs a million times easier. They got bow and arrows.
+Jordan: They're using crossbows and axes and hatchets.
+Darius: For no reason other than to keep the plot going.
+Jordan: This movie should have been set in like 1850. That would have that would have made that would have made it make much more sense.
+Darius: Why doesn't anyone ever have guns in these movies? Like it's just. Especially because in spoiler alert, you're watching. So it was one thing in like the strangers because there was almost like a, it was almost a ritualistic killing. Right. It was like almost like a almost sexual. Some of these movies like this, the stabbing and the hunt and the chase was part of it. This is the contract killing. Why are you doing a contract killing the hard way?
+Jordan: By the way, we learned later on in the movie that the guys that they hired to kill people were in the military. What the **** are you doing with the crossbow?
+Darius: No, it just doesn't make sense. Like you said, this is some Game of Thrones weaponry. And again, if you're a part of some ritual like other movies have or some supernatural thing, all right, cool.
+Jordan: Yeah. Like, have you ever seen like The Invitation?
+Darius: No, I have not. No.
+Jordan: Really good one.
+Darius: But like it's like you're doing a home evasion with crossbows in the year 2011. All right. Also, when people are shooting things through the window, you should get away from the window.
+Jordan: Duck. And also don't turn your back on the window.
+Darius: No, I stalled the first guy out who got shot in the shoulder because that was chaos.
+Jordan: He was grabbing his mom. Yeah.
+Darius: That was chaos. But like it kept walking towards window.
+Jordan: They just and they just by the way, they just kept standing up. I was like, what do you, honestly, that kitchen, the dining room murder scene, after the first guy got killed, I just laughed the entire time because it just was so screaming.
+Darius: The screaming. Oh my God. The bad acting screaming. Like she's just. Correct. She's just like doing nothing.
+Jordan: By the way, no tears were falling from her eyes, by the way.
+Darius: It just, and they like, dude, turn her mic down. She's, I can't hear anything else. Please.
+Jordan: Yeah. that that scene was pretty funny I will say I did like the dinner scene before that happened like the argument before that because that brother was a ******* ******** like yeah if anyone in the movie deserved what happened to him he kind of deserved it he was he was a ***** ** **** and you could tell he gave his siblings hell throughout their whole lives but yeah I'll be honest with you even though that since this weekend in misdirection I thought the girlfriend was the internet first the British girl the Australian girl She was just way too calm. And how do you know how to do all this ****? Like, I was like, something's weird about you.
+Darius: Know, I think, yeah, I didn't think she was in it. I definitely thought one of the brothers were. And the one it ended up being, you know, we'll tell you an act three could not have been the. I mean, that might be the.
+Jordan: He was so obvious.
+Darius: Yes. And his girlfriend was just like, literally just like a bad guy.
+Jordan: Yeah, by the way, that's right. That's I thought about it too. Cause like, When they met his mom outside, like she's like smoking a cigarette. She didn't say hello. She didn't shake her hand. Like it was just really weird. And also like he just was, he didn't like his siblings were dying all around him and he never cried once. Like that was weird.
+Darius: Also, man, all these new partners, girlfriends, whatever, boyfriends, meeting like in the middle of nowhere. Like can we like meet at an Applebee's? Can I meet your parents at an Applebee's first? Why I gotta spend a week in the middle of the ******* woods with them for the first time I'm eating them.
+Jordan: No, never, ever, ever.
+Darius: Can we pop into a Chili's and get some chicken crispers? And first, you know, let's do a cabinet in the woods once we know each other.
+Jordan: Right. Yeah, you say that for like holidays and ****. You're supposed to just go and, you know, have a happy hour.
+Darius: Then proceeds so they get Arrows are flying, chaos is the best. They get to the foyer.
+Jordan: Oh, yes, this is my favorite part.
+Darius: And they're like, we need to run out.
+Jordan: It was so dumb.
+Darius: And they're like, you ran track. And they proceed to concoct the dumbest thing I've ever seen in my life.
+Jordan: Yes. So for the viewers, there's a big double door to open the door into the massive mansion that they live in. So the dad and one of the sons opens the door and she's supposed to sprint out to run for help.
+Darius: His youngest daughter, their youngest sister, that's who they sent out into the murderous woods.
+Jordan: Yes, right. And she's supposed to, Jesse Owens her way to safety.
+Darius: And she literally, in a very cinematic way, starts sprinting in a straight line.
+Jordan: Barefoot.
+Darius: Barefoot out into the woods. I don't know where plan was.
+Jordan: Plan was.
+Darius: Why they're bringing so much attention. Wouldn't you want to sneak? And then she runs right to her death. Apparently there's a trip wire.
+Jordan: Yeah. And Danner decapitated her. That didn't make sense either because she wasn't running fast enough to even.
+Darius: You can't generate that much force. No, I thought when I first saw.
+Jordan: It, I thought she got, I thought they shot a gun and it like grazed her throat.
+Darius: She almost decapitated herself by running 10 mph into a string.
+Jordan: Yes.
+Darius: I mean, it wouldn't feel good. It hurt. You probably break some skin, but you would not instantly die. And she just runs and they open the doors and she just and that was it.
+Jordan: By the way, if the gunman or assailant is outside with the crossbow in front of the house, you think her jogging out was going to shock him? He has a weapon. She doesn't. Why would he be afraid?
+Darius: Why are you? Why is one person doing? Why does anyone have to stay in this house? I don't like I'm confused by all of this. Like why don't y'all just leave together for help? Like there's nothing No one had cars. There's no cars outside that we can get to.
+Jordan: Yeah, where did y'all park? They're like, yeah, we can't get to the cars.
+Darius: The cars just disappeared. Like everyone forgot they drove.
+Jordan: Yeah, by the way, so my strategy would be we're either all living together or we're all staying in the house. And if you're all staying in the house, you need to all sit in the foyer where there's no windows and just ******* huddle up and just make some **** shake.
+Darius: Grab some knives, boil some water, grab, there's a bat somewhere in here, some wood. No survival skills. No one, well, old girl went and got some weapons, but.
+Jordan: Yeah, we're not, no one's going to any room alone. We're all going all together everywhere.
+Darius: Mom has a panic attack. They send her upstairs alone and lay her and lay her in bed by herself.
+Jordan: To do what?
+Darius: I don't know.
+Jordan: Right. After her daughter just got her head blown off.
+Darius: And so they're like, here's the value, take a nap. And we're gonna, we're gonna go downstairs and watch a movie, I guess. I don't.
+Jordan: Right. She couldn't sleep next to y'all where she would be safe.
+Darius: I just sit there, I'm home alone and like, I will be right back, you know, sleeping off.
+Jordan: Just take a nap, sleep off for the death of your child. What?
+Darius: Oh, obviously mom dies because of course bad guy shows up, butchers her.
+Jordan: He's under the bed. Yep.
+Darius: Dad sees her freaks out. That's when we find out. That's what old girl just starts putting belt to *** like she was. Yeah, she stabbed one guy in the hand. She went and got knives.
+Jordan: Yeah, she turned into Colombiana.
+Darius: Never was explained. Well, I guess she kind of when she was making the knife, the nail death trap, she kind.
+Jordan: Of said she grew up in a survivalist compound. And I don't know. I guess that's supposed to be a sufficient answer. I don't believe that, but.
+Darius: And so she. I don't know. So the dad dies when the daughter and the son, like, what was the dad doing? He was like walking around by himself.
+Jordan: He was. I don't know what he was doing. He basically figured out that it was an inside job or not inside job, but that the person in the house.
+Darius: Yeah.
+Jordan: Yeah. They've been to whoever had been squatting there. was obviously planning this the whole time. And he's about to tell them, and then dude comes behind him and slits his throat.
+Darius: And then we get the bad acting where, well, I guess that's getting attacked. Are you gonna get there?
+Jordan: Yeah, **** it. Yeah. I'm still tripping off. She thought she was gonna outrun a crossbow. But yeah, let's go.
+Darius: She thought she was gonna outrun a crossbow by making a big production of running out by herself to where I don't know. Everyone forgot they had cars.
+Jordan: Right.
+Darius: I really just, again, like you said, the plot is premised on everyone being the dumbest ************* you've ever met. And so the plot continues. Act 3, the final stand, the dwindling number of survivors engages in a brutal drawn out battle for survival. That's A poorly read sentence. I guess the relentless intruders, booby traps and close quarters combat turn the house into a deadly gauntlet as the heroine fights to make it to mourning alive. What are the odds you playing all this and your brother's girlfriend happens to be female John Wick? Right. Yeah.
+Jordan: What are the chances of that?
+Darius: Because like, yeah, he's, we, I mean, spoiler, we find out that her boyfriend or whatever was in on it at the end.
+Jordan: Yeah, two of the sons are in on it.
+Darius: But like, they had just met. So it's entirely possible he didn't know that she was just damn skilled. Like, why would you ever bring that up? You know? Yeah. And so this ****** luck, you know, the girl your brother's ******* just happens to be a *******.
+Jordan: Yeah.
+Darius: What's the old girl from? What's the Avenger girl? Scarlett? Scarlett.
+Jordan: Black Widow.
+Darius: Black Widow. Yeah. She just without guns because apparently it's 1776.
+Jordan: Right.
+Darius: What you got for Act 3?
+Jordan: Yeah. So I think for me that act three was what I thought most back through was. I feel like their inheritance wasn't enough of motivation for them to do all of that. Like, I get hating your brother. He was * ****. But like, your parents were nice to you.
+Darius: Die already. This is hard.
+Jordan: Just just die. Like, like it took eight screwdrivers to the chest to kill your brother. Really.
+Darius: Well, that's one thing that movies get wrong is just how hard it is to stab someone to death. That that was true. Like, it's actually. It's incredibly difficult to stab someone to death.
+Jordan: Yeah.
+Darius: So how many people have the stab? Well, I mean, just in general, like two things movies get weird is like non-fatal gunshot wounds are way more dangerous than movies that let you believe. And stabbing, stabbing in like in movies when you like strangle someone with the pillow, it's basically possible. But yeah, so he's just like stabbing his brother And his brother is isn't dying yet. And he just like throws a temper tantrum like the sword die.
+Jordan: I just didn't get it because like for one of the movie didn't do a great job of showing how much money the parents had, mostly because the budget was so low, I guess. But also like your parents weren't old. So the fact you even think about your inheritance was kind of weird to me. And like, why why kill your sisters too? Like they just It wasn't enough of an explanation for me.
+Darius: My understanding is...
+Jordan: The young kids seem like a ****** ** but.
+Darius: They wanted to seem like a random home massacre because anything else they would look at the people inheriting all that money as to why, you know, these relatively you know, good shape, not old, but not elder. Like it's not, they were like, what, early 60s? Like they have, they look like they could live a long life after that. Just, you know, got, just died. So.
+Jordan: Yeah.
+Darius: And that's why he brought her along so she can be the non-interested party that witnessed it. Like she's not, if the only survivors are people that stand to gain a bunch of money, you know, but they would have kept her alive if she was you know was willing to you know not yeah to John Wick so what you got fract three man.
+Jordan: Um oh so I had to wait until we talked about the spoiler of the twist here but um so when the son was behind the dad in fact one when he was in the house do you think that was when he was supposed to kill him but he just chickened out?
+Darius: Yeah I think so um yeah I think so because The son that left, we're talking about the dude who left, but the Australian girl's boyfriend, right? Yeah. He calls his brother and giant female John Wick picks up the phone and she doesn't say anything. And he's just like, I'm sorry, I checked it out. I left. I couldn't go through with it. So I think, yeah, that was all part of the plan. Though I hesitate to give this writer much credit. You know, as far as like, yeah, next level plot devices and writing. but yeah to answer your question I believe so.
+Jordan: Yeah when did you not say when did you know because I feel like we all kind of learned it around the same time but like did you thinking back and looking back on that were there did you see anything that you missed in terms of like clues about who was involved?
+Darius: It's hard to tell the clues from God awful acting so that is true that is true I thought it was very obvious because I've seen it it's very obvious who the killers were But only because no one, I mean, this was some bad acting, man. Like they were.
+Jordan: Yo, dog, it was horrible.
+Darius: They might as well have been holding the pieces of paper with their lines on it, like on the set.
+Jordan: Yeah. They should have just had the prop guy with the cue cards like that.
+Darius: I've seen better acting at like high school plays.
+Jordan: No, really.
+Darius: They were horrible.
+Jordan: Every last one of them.
+Darius: But in a weird way, I enjoyed this movie. I'll be honest.
+Jordan: Yeah, it actually is pretty fun.
+Darius: I got a good serious laugh out loud when the girl, the killer girl and the killer dude were laying next to his mom's dead body.
+Jordan: Yeah.
+Darius: Like, you'd never want to do anything exciting. And he's like, really?
+Jordan: No, seriously. Yeah. Like, I actually was crazy.
+Darius: I actually, he was.
+Jordan: A villain and I did hate him, but I was like, yeah, you got to, you tripping on that one. He just killed his whole family.
+Darius: Like, never do anything exciting. He's like, I'm just murdering my whole house here. Like, what are you talking about? Right. Exciting enough for you?
+Jordan: On the first link, by the way.
+Darius: Yeah. You know, I'm gonna make you rich and I'm killing everybody in front of you, but you know.
+Jordan: Yeah.
+Darius: Looking in front of my dead mom's corpse is a bridge too far. That is where I draw the line.
+Jordan: Yeah, that's it. That's my, yeah, that was crazy. I was like, is she serious right now? Where the **** did he meet her?
+Darius: What a stupid movie.
+Jordan: It is so dumb. But most Halloween movies are dumb.
+Darius: I enjoy it though. I enjoy it though.
+Jordan: It is fun. It's fun though. It's fun. That's kind of, yeah, it's good fun.
+Darius: Do you have anything else for actor?
+Jordan: Yeah. So the clues that I caught looking back and I just like reflecting was when the younger brother, everybody's freaking out in the foyer and they couldn't didn't get self-service. And he's like, they jammed it. They probably jammed it. You can buy my life for 30 bucks.
+Darius: And his brother, which I wrote his back, is like, you ******* nerd.
+Jordan: ******* low life. You low life.
+Darius: That was funny. I laughed.
+Jordan: Yeah, that was that was a kind of a dead giveaway right there.
+Darius: Almost two of those. But it's funny because it is. It is sort of realistic in that situation. The older brother would be like, why do you know that, you ******* low life?
+Jordan: No, seriously, yeah.
+Darius: Because I can see in that situation, you just be like, wait, what the ****?
+Jordan: No, because what the **** do you mean? Yeah, I think another thing I did like though was that they killed, not like, but it was smart of them to kill the neighbors first because that would have been the first line of defense in terms of you're going to go there for help.
+Darius: And it makes it feel a lot more random than just.
+Jordan: It makes it random. So it looks like you're just killing rich people.
+Darius: That makes sense. That was all I had. You have anything else?
+Jordan: Yeah, that's pretty much all I got for this one.
+Darius: What do you rate it?
+Jordan: In terms of I'm going to give this one 2 1/2 stars, which is like 5 stars considering how ****** the actors are in this movie.
+Darius: I'm going for it, man. I love this movie. It's stupid as hell. The acting is terrible. I've probably seen it 12 times.
+Jordan: Yeah.
+Darius: It's just.
+Jordan: Yeah, I might watch it again this week. It actually is kind of fun.
+Darius: It's I love a good stupid slasher and the first I love this setup, the bad acting. And yeah, for a four. I'm grading it on a curve because it's a Halloween movie. But no, this is not this is not great cinema, but it doesn't always have to be that way. So I'm giving it a four.
+Jordan: That is true. Yeah. I just had to. We just can't undersell to the audience, guys, how bad these actors are in this movie.
+Darius: There's a reason it was. The movie is 15 years old. You haven't seen any of these people ever since.
+Jordan: Yeah, we actually should not have even mentioned their names in this episode.
+Darius: Because I don't remember their characters names.
+Jordan: I don't either. Not at all.
+Darius: Right. Thanks for listening. My name is Darius. That's these all up in the area on all socials.
+Jordan: And I'm Jordan. That's Jordan to be riding on all socials.
+Darius: Please rate, like, subscribe. We are at Out the Trunk Pod on all socials. That is Out the Trunk Pod on all socials.
+Jordan: And for anyone going to move recommendations, reach out to us via e-mail at outthetrunkpod@gmail.com. That's outthetrunkpod@gmail.com. Thanks again for watching, guys. That's a wrap. Happy Halloween. We'll be back next week reviewing The Judge. Y'all take care.
+Darius: What do you want to watch next week, man?
+Jordan: Let's see. We're doing a lot of slashes lately. You want to do a drama?
+Darius: Yeah, sure.
+Jordan: Okay, let's do. Have you seen The Judge, Robert Downey Jr.?
+Darius: Yeah, I saw that in theaters when it came up. We can, I can go.
+Jordan: Hey everybody, welcome to Out the Trunk Pod with Jordan Darius. My name is Jordan. That's Jordan to be writing on all socials.
+Darius: And I'm Darius, that's Steve's I love you area on all socials.
+Jordan: And this is our movie review segment. For this episode, we're going to be reviewing your next little slasher film for Halloween. Happy Halloween, everybody.
+Darius: Happy Halloween, everybody.
+Jordan: Y'all be safe and **** out there. Be safe.
+Darius: Ladies wear the costumes with the *** out. You're not too grown. Let's do it.
+Jordan: Yes. Shout out to all the Velmas out there. Y'all the real VPs.
+Darius: ***** out. That's the whole point of why we are outside on Halloween.
+Jordan: This is literally the point of</t>
   </si>
 </sst>
 </file>
@@ -1773,4 +7374,312 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="149.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>86</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>95</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E65165-62A4-4188-BB7C-56029849ADF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11AB435-A7A4-42DF-BD98-EE62D6A119C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,24 +17,18 @@
     <sheet name="Transcripts" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Movie Ratings'!$A$1:$F$37</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="147">
   <si>
     <t>12 Angry Men</t>
   </si>
   <si>
-    <t>Did the prosecution actually prove the case?</t>
-  </si>
-  <si>
-    <t>Justice; civic duty; bias; memory; reasonable doubt</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=WjvBorOaAQc</t>
   </si>
   <si>
@@ -44,315 +38,105 @@
     <t>Arrival</t>
   </si>
   <si>
-    <t>If you could press a button and see the rest of your life, would you want to know?</t>
-  </si>
-  <si>
-    <t>Fate; language; love; grief; randomness; choice</t>
-  </si>
-  <si>
     <t>Baby Driver</t>
   </si>
   <si>
-    <t>What song did this movie remind you of?</t>
-  </si>
-  <si>
-    <t>Music; crime; technology aging</t>
-  </si>
-  <si>
     <t>Backrooms</t>
   </si>
   <si>
-    <t>Why did this movie become popular when the hosts found almost no story, character development, or payoff?</t>
-  </si>
-  <si>
-    <t>Isolation; loneliness; mental health; liminal spaces; identity; meaning-making; storytelling versus concept</t>
-  </si>
-  <si>
     <t>B.A.P.S.</t>
   </si>
   <si>
-    <t>What hybrid business would we open with our podcast studio?</t>
-  </si>
-  <si>
-    <t>90s comedy; class; fish-out-of-water; friendship; hood classics</t>
-  </si>
-  <si>
     <t>The Best Man</t>
   </si>
   <si>
-    <t>Does a secret like that ever truly stay buried?</t>
-  </si>
-  <si>
-    <t>Friendship; loyalty; betrayal</t>
-  </si>
-  <si>
     <t>Boomerang</t>
   </si>
   <si>
-    <t>Is this movie good?</t>
-  </si>
-  <si>
-    <t>Dating; ego; image</t>
-  </si>
-  <si>
     <t>Brown Sugar</t>
   </si>
   <si>
-    <t>When did you fall in love with hip-hop?</t>
-  </si>
-  <si>
-    <t>Hip-hop; friendship; love</t>
-  </si>
-  <si>
     <t>Children of Men</t>
   </si>
   <si>
-    <t>Do you have a go bag?</t>
-  </si>
-  <si>
-    <t>Collapse; infrastructure; survival</t>
-  </si>
-  <si>
     <t>The Dark Knight</t>
   </si>
   <si>
-    <t>Was Gotham better off preserving Harvey Dent's heroic image, even if it required lying to the public?</t>
-  </si>
-  <si>
-    <t>Order vs. chaos; burden of heroism; moral compromise; public faith and symbolism; law versus vigilantism; fragility of civilization; sacrifice</t>
-  </si>
-  <si>
     <t>Friday</t>
   </si>
   <si>
-    <t>Is Pineapple Express the white Friday?</t>
-  </si>
-  <si>
-    <t>Neighborhood; comedy; friendship</t>
-  </si>
-  <si>
     <t>Game Night</t>
   </si>
   <si>
-    <t>If you had a house in the suburbs, would you host?</t>
-  </si>
-  <si>
-    <t>Hosting; games; suburbs</t>
-  </si>
-  <si>
     <t>Good Boys</t>
   </si>
   <si>
-    <t>Are you still cool with anyone from grade school?</t>
-  </si>
-  <si>
-    <t>Childhood; friendship; growing up</t>
-  </si>
-  <si>
     <t>The Judge</t>
   </si>
   <si>
-    <t>Was the bathroom scene the most powerful scene?</t>
-  </si>
-  <si>
-    <t>Family; fathers; courtrooms</t>
-  </si>
-  <si>
     <t>Juror No. 2</t>
   </si>
   <si>
-    <t>What does justice require when protecting yourself could condemn someone else?</t>
-  </si>
-  <si>
-    <t>Justice; conscience; self-preservation</t>
-  </si>
-  <si>
     <t>Love &amp; Basketball</t>
   </si>
   <si>
-    <t>Was Monica wrong for leaving because of curfew?</t>
-  </si>
-  <si>
-    <t>Love; ambition; family; sports</t>
-  </si>
-  <si>
     <t>Love Jones</t>
   </si>
   <si>
-    <t>Was Darius who Nina wanted, or who was there when she was tired?</t>
-  </si>
-  <si>
-    <t>Romance; art; timing</t>
-  </si>
-  <si>
     <t>Mrs. Doubtfire</t>
   </si>
   <si>
-    <t>Did this movie age well?</t>
-  </si>
-  <si>
-    <t>Divorce; parenting; nostalgia</t>
-  </si>
-  <si>
     <t>Nick &amp; Norah's Infinite Playlist</t>
   </si>
   <si>
-    <t>What five acts would you do anything to see live?</t>
-  </si>
-  <si>
-    <t>Music; NYC; dating</t>
-  </si>
-  <si>
     <t>Obsession</t>
   </si>
   <si>
-    <t>Does unrequited love count as real love if it is never returned?</t>
-  </si>
-  <si>
-    <t>Be careful what you wish for; agency and coercion; unrequited love; attachment; youthful insecurity; control versus genuine affection</t>
-  </si>
-  <si>
     <t>The Odyssey</t>
   </si>
   <si>
-    <t>Is this Matt Damon's best role?</t>
-  </si>
-  <si>
-    <t>Journey; mythology; war; homecoming</t>
-  </si>
-  <si>
     <t>The Prestige</t>
   </si>
   <si>
-    <t>Did Borden tie the wrong knot, and did Borden truly know which knot was tied?</t>
-  </si>
-  <si>
-    <t>Obsession; sacrifice; rivalry; identity; showmanship versus craft; passion; deception; divided lives; the cost of applause</t>
-  </si>
-  <si>
     <t>Reservoir Dogs</t>
   </si>
   <si>
-    <t>Is Reservoir Dogs actually a great movie, or has its reputation been elevated because Tarantino later became one of the most acclaimed directors of all time?</t>
-  </si>
-  <si>
-    <t>Trust vs. self-preservation; loyalty and betrayal; the psychology of lying; reputation versus reality; criminal organizations; group dynamics under pressure; the costs of paranoia</t>
-  </si>
-  <si>
     <t>The Sandlot</t>
   </si>
   <si>
-    <t>Are you still friends with anyone from your childhood neighborhood?</t>
-  </si>
-  <si>
-    <t>Childhood; friendship; nostalgia</t>
-  </si>
-  <si>
     <t>Sleepy Hollow</t>
   </si>
   <si>
-    <t>Would you rather be the writer or director?</t>
-  </si>
-  <si>
-    <t>Mystery; supernatural; worldbuilding</t>
-  </si>
-  <si>
     <t>State Property</t>
   </si>
   <si>
-    <t>Was this the OG Tubi movie?</t>
-  </si>
-  <si>
-    <t>Nostalgia; crime; rap culture</t>
-  </si>
-  <si>
     <t>Still Alice</t>
   </si>
   <si>
-    <t>Would you use genetic testing to edit chronic illness out?</t>
-  </si>
-  <si>
-    <t>Memory; identity; illness</t>
-  </si>
-  <si>
     <t>Stranger Than Fiction</t>
   </si>
   <si>
-    <t>If a voice narrated your life, what genre would it be?</t>
-  </si>
-  <si>
-    <t>Routine; mortality; originality</t>
-  </si>
-  <si>
     <t>Take Me Home Tonight</t>
   </si>
   <si>
-    <t>What was your favorite Grand Theft Auto?</t>
-  </si>
-  <si>
-    <t>Adulthood; nostalgia; pressure</t>
-  </si>
-  <si>
     <t>The Drama</t>
   </si>
   <si>
-    <t>Is Emma's revelation alone enough to call off the wedding, or is the larger issue everything else surrounding her character?</t>
-  </si>
-  <si>
-    <t>Forgiveness; trust; hidden identity; mental health; love versus judgment; emotional immaturity; second chances; relationship pressure</t>
-  </si>
-  <si>
     <t>The Photograph</t>
   </si>
   <si>
-    <t>Should Michael have pursued a serious relationship with Mae while actively preparing to take a job in another country?</t>
-  </si>
-  <si>
-    <t>Family legacy; motherhood; generational trauma; ambition versus relationships; memory and grief; love across generations; identity and self-discovery</t>
-  </si>
-  <si>
     <t>This Christmas</t>
   </si>
   <si>
-    <t>Does your family do a big Christmas?</t>
-  </si>
-  <si>
-    <t>Family; holidays; secrets</t>
-  </si>
-  <si>
     <t>Weapons</t>
   </si>
   <si>
-    <t>Why did no one have guns?</t>
-  </si>
-  <si>
-    <t>Grief; suspense; endings</t>
-  </si>
-  <si>
     <t>White Men Can't Jump</t>
   </si>
   <si>
-    <t>Was Gloria right to leave?</t>
-  </si>
-  <si>
-    <t>Money; relationships; basketball</t>
-  </si>
-  <si>
     <t>You're Next</t>
   </si>
   <si>
-    <t>Why is everyone doing a contract killing the hard way?</t>
-  </si>
-  <si>
-    <t>Horror logic; survival; Halloween</t>
-  </si>
-  <si>
-    <t>How did this win Best Picture?</t>
-  </si>
-  <si>
-    <t>Aging; suburbia; discomfort; midlife crisis; adult rewatch</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=uVc5pvyebG8</t>
   </si>
   <si>
@@ -459,12 +243,6 @@
   </si>
   <si>
     <t>darius_rating</t>
-  </si>
-  <si>
-    <t>best_question</t>
-  </si>
-  <si>
-    <t>major_themes</t>
   </si>
   <si>
     <t>youtube_link</t>
@@ -6069,6 +5847,1069 @@
 Darius: ***** out. That's the whole point of why we are outside on Halloween.
 Jordan: This is literally the point of</t>
   </si>
+  <si>
+    <t>Show Notes &amp; Highlights</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Small Talk, WOOM, Sports section, and MY NOTES included Most elitist opinion, Aging, Does rewatchability matter, Pool Season, date contact, Rock Bottom, and similar prompts.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Courtroom drama about twelve jurors debating whether the state proved a murder case beyond a reasonable doubt.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act I: The Lone Voice — one juror forces the room to actually deliberate.&lt;/li&gt;
+    &lt;li&gt;Act II: Shifting the Tide — witness testimony, memory, bias, and burden of proof are challenged.&lt;/li&gt;
+    &lt;li&gt;Act III: The Final Verdict — the remaining holdouts confront their own reasoning.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Did the prosecution actually prove the case?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; It is not the defense’s job to prove innocence; it is the prosecution’s job to prove guilt.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Beyond a reasonable doubt should be a high burden before the state takes freedom.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Justice&lt;/li&gt;
+      &lt;li&gt;civic duty&lt;/li&gt;
+      &lt;li&gt;bias&lt;/li&gt;
+      &lt;li&gt;memory&lt;/li&gt;
+      &lt;li&gt;reasonable doubt&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Suburban midlife crisis drama about Lester Burnham rejecting his numb routine while the neighborhood’s secrets unravel.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act I: The Wake-Up Call — Lester’s routine breaks.&lt;/li&gt;
+    &lt;li&gt;Act II: Breaking the Mold — Lester rebels while the family fractures.&lt;/li&gt;
+    &lt;li&gt;Act III: The Beautiful End — the movie reaches its uncomfortable conclusion.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; How did this win Best Picture?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; It was not attraction; it was what youth represented.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Add this to the list of 90s movies about bored suburbanites who were too comfortable.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Aging&lt;/li&gt;
+      &lt;li&gt;suburbia&lt;/li&gt;
+      &lt;li&gt;discomfort&lt;/li&gt;
+      &lt;li&gt;midlife crisis&lt;/li&gt;
+      &lt;li&gt;adult rewatch&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;No original rundown captured in this import package.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Science-fiction drama centered on language, time perception, grief, love, and whether knowing the future changes how life should be lived.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Episode discussion focused less on act structure and more on fate, randomness, love, and accepting life with knowledge of pain.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; If you could press a button and see the rest of your life, would you want to know?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Choose love over fear; the ending is about accepting joy even knowing grief is coming.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The filler episodes of life are what make life feel alive.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Fate&lt;/li&gt;
+      &lt;li&gt;language&lt;/li&gt;
+      &lt;li&gt;love&lt;/li&gt;
+      &lt;li&gt;grief&lt;/li&gt;
+      &lt;li&gt;randomness&lt;/li&gt;
+      &lt;li&gt;choice&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+  &lt;p&gt;&lt;strong&gt;Archive Note:&lt;/strong&gt; A-tier philosophical episode.&lt;/p&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Style-driven getaway driver movie scored by music.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; What song did this movie remind you of?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The musical detail makes it theater-friendly.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; This is basically a two-hour music video.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Music&lt;/li&gt;
+      &lt;li&gt;crime&lt;/li&gt;
+      &lt;li&gt;technology aging&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: No Clipping Reality | Act 2: Endless Yellow | Act 3: Escape the Liminal&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;A man becomes trapped in the mysterious Backrooms, an endless maze of yellow hallways, while a strange scientific experiment and personal psychological struggles unfold around him.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 introduces the maze and confused premise. Act 2 follows prolonged wandering through the Backrooms while the hosts question the film’s purpose. Act 3 attempts to connect the maze to psychology and identity, but leaves most questions unanswered.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Why did this movie become popular when the hosts found almost no story, character development, or payoff?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The film feels like a maze without a destination. Every time a theme appears, the movie abandons it before developing a meaningful journey.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The Backrooms works better as a short-form internet concept than a feature-length film. Stretching a YouTube idea into two hours exposed the lack of story.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Is the movie a deep metaphor about the human mind, or simply an incoherent story that audiences are overanalyzing?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Isolation&lt;/li&gt;
+      &lt;li&gt;loneliness&lt;/li&gt;
+      &lt;li&gt;mental health&lt;/li&gt;
+      &lt;li&gt;liminal spaces&lt;/li&gt;
+      &lt;li&gt;identity&lt;/li&gt;
+      &lt;li&gt;meaning-making&lt;/li&gt;
+      &lt;li&gt;storytelling versus concept&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;WOOM included chasing your dreams in 2026, Yung Miami/India Arie, Smartest Person in the Room, NBA Free Agency, Gold Medal Theory, and Top 3 TV episodes.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Cult comedy about Nisi and Mickey heading to Los Angeles, landing in a Beverly Hills mansion, and winning over a wealthy older man while chasing their business dream.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act I: From Georgia to Beverly Hills — diner, club, video audition, and the $10,000 scheme.&lt;/li&gt;
+    &lt;li&gt;Act II: The Makeover of a Mansion — Nisi and Mickey transform the mansion’s vibe.&lt;/li&gt;
+    &lt;li&gt;Act III: The Real Princesses — the scheme unravels and loyalty wins out.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; What hybrid business would we open with our podcast studio?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; This is basically Spendat: The Movie.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Raleigh needs an actual greasy-spoon breakfast diner, not brunch.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;90s comedy&lt;/li&gt;
+      &lt;li&gt;class&lt;/li&gt;
+      &lt;li&gt;fish-out-of-water&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+      &lt;li&gt;hood classics&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Wedding ensemble drama where Harper’s novel threatens friendships.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Does a secret like that ever truly stay buried?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Harper is the protagonist but also basically the villain.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Fiction inspired by true events needs plausible deniability.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Friendship&lt;/li&gt;
+      &lt;li&gt;loyalty&lt;/li&gt;
+      &lt;li&gt;betrayal&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Marcus Graham meets his match and reassesses ego, dating, and control.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is this movie good?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Eddie Murphy is a strong dramatic actor among comedians.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Halle Berry as the everyday woman is ridiculous.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Dating&lt;/li&gt;
+      &lt;li&gt;ego&lt;/li&gt;
+      &lt;li&gt;image&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Hip-hop friendship romance about Dre and Sidney realizing the metaphor was love.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; When did you fall in love with hip-hop?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie is the article voiceover using hip-hop as a love metaphor.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Before rap became about getting a bag, there was more collaboration.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Hip-hop&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+      &lt;li&gt;love&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Dystopian escort story built around fertility collapse, government breakdown, and survival.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Do you have a go bag?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The future looking old shows social collapse creatively.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Post-apocalyptic movies are inherently conservative.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Collapse&lt;/li&gt;
+      &lt;li&gt;infrastructure&lt;/li&gt;
+      &lt;li&gt;survival&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The Shadows Over Gotham | Act 2: The Escalation of Chaos | Act 3: The Soul of Gotham&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Batman, Jim Gordon, and Harvey Dent attempt to eliminate organized crime in Gotham while the Joker unleashes escalating chaos, forcing every major character to confront difficult moral choices.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: Joker’s bank heist establishes his intelligence, unpredictability, and agenda while Batman, Gordon, and Dent begin their alliance.&lt;/li&gt;
+    &lt;li&gt;Act 2: Joker’s attacks escalate as the hosts discuss Batman’s no-kill rule, Joker’s philosophy, and Nolan’s storytelling.&lt;/li&gt;
+    &lt;li&gt;Act 3: Harvey Dent becomes Two-Face, Batman accepts blame to preserve hope, and the hosts examine the film’s legacy.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was Gotham better off preserving Harvey Dent’s heroic image, even if it required lying to the public?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie transcends the genre because nearly every major character faces a difficult moral choice with real consequences.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The film succeeds because the good guys actually lose. Actions have consequences, victories are costly, and the stakes feel permanent.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Was Batman right to refuse to kill the Joker despite the destruction and lives lost?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Order vs. chaos&lt;/li&gt;
+      &lt;li&gt;burden of heroism&lt;/li&gt;
+      &lt;li&gt;moral compromise&lt;/li&gt;
+      &lt;li&gt;public faith and symbolism&lt;/li&gt;
+      &lt;li&gt;law versus vigilantism&lt;/li&gt;
+      &lt;li&gt;fragility of civilization&lt;/li&gt;
+      &lt;li&gt;sacrifice&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Neighborhood comedy about Craig, Smokey, Deebo, and one long Friday.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is Pineapple Express the white Friday?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Pineapple Express is the white Friday.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Getting fired on your day off is egregious.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Neighborhood&lt;/li&gt;
+      &lt;li&gt;comedy&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Game-night comedy where a murder mystery becomes a real kidnapping case.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; If you had a house in the suburbs, would you host?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Bring back cool credits in movies.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Jesse Plemons is the saving grace.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Hosting&lt;/li&gt;
+      &lt;li&gt;games&lt;/li&gt;
+      &lt;li&gt;suburbs&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Sixth-grade coming-of-age comedy about friendship and getting older.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Are you still cool with anyone from grade school?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie illustrates how stupid kids are.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The Black kid gets something to do beyond being Black.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Childhood&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+      &lt;li&gt;growing up&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Legal/family drama about a lawyer defending his estranged judge father.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was the bathroom scene the most powerful scene?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Opening relics show each family member’s role.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Robert Downey Jr. is elite; Marvel took serious roles from us.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Family&lt;/li&gt;
+      &lt;li&gt;fathers&lt;/li&gt;
+      &lt;li&gt;courtrooms&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Moral-dilemma courtroom premise; movie section in rundown was mostly blank.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; What does justice require when protecting yourself could condemn someone else?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Needs transcript pass.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Needs transcript pass.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Justice&lt;/li&gt;
+      &lt;li&gt;conscience&lt;/li&gt;
+      &lt;li&gt;self-preservation&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Sports romance about Monica and Quincy balancing love, family, and ambition.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was Monica wrong for leaving because of curfew?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie aged well and has strong family/feminist messaging.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; “Let’s play for your heart” is corny.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Love&lt;/li&gt;
+      &lt;li&gt;ambition&lt;/li&gt;
+      &lt;li&gt;family&lt;/li&gt;
+      &lt;li&gt;sports&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Romantic drama about poetry, timing, vulnerability, and whether love is real or just a thing.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was Darius who Nina wanted, or who was there when she was tired?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Nina loved how Darius made her feel more than she loved him.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Everyone is pretending to like jazz.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Romance&lt;/li&gt;
+      &lt;li&gt;art&lt;/li&gt;
+      &lt;li&gt;timing&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Family comedy revisited through an adult lens around divorce, parenting, and responsibility.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Did this movie age well?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Robin Williams at peak powers makes this a five-star classic.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; As an adult, Daniel looks like a man-child Miranda had to parent with.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Divorce&lt;/li&gt;
+      &lt;li&gt;parenting&lt;/li&gt;
+      &lt;li&gt;nostalgia&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Teen New York rom-com centered on music, technology, and one-night adventure.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; What five acts would you do anything to see live?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; After a breakup, delete everything or at least hide it.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The movie is a dated technology museum: iPod, burned CDs, flip phones.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Music&lt;/li&gt;
+      &lt;li&gt;NYC&lt;/li&gt;
+      &lt;li&gt;dating&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The One Wish Willow | Act 2: Love Turned Unhinged | Act 3: The Price of Control&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; A shy record-store employee uses a supernatural charm to make childhood friend Nikki love him above everything else, turning unrequited longing into violent possession.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1 establishes Bear’s wish, Nikki’s lack of romantic interest, and Ian’s concealed history with her. Act 2 tracks the wish escalating through isolation, control, and violence. Act 3 confronts Bear’s responsibility, Nikki’s attempts to resist, and the deadly consequences of forced devotion.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Does unrequited love count as real love if it is never returned?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Nikki’s performance remains magnetic while small visual details suggest the real Nikki is fighting the wish throughout the movie.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Bear’s longing is relatable, but getting exactly what he wished for exposes the danger of confusing control with love.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Is Bear the villain, an immature young man trapped by an impulsive wish, or both?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Be careful what you wish for&lt;/li&gt;
+      &lt;li&gt;agency and coercion&lt;/li&gt;
+      &lt;li&gt;unrequited love&lt;/li&gt;
+      &lt;li&gt;attachment&lt;/li&gt;
+      &lt;li&gt;youthful insecurity&lt;/li&gt;
+      &lt;li&gt;control versus genuine affection&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Christopher Nolan epic about Odysseus returning home after the Trojan War.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is this Matt Damon’s best role?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The Calypso “let go” idea works: surrender is not giving up.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The Cyclops sequence is the ultimate rewatch scene and proves what practical effects can do.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Journey&lt;/li&gt;
+      &lt;li&gt;mythology&lt;/li&gt;
+      &lt;li&gt;war&lt;/li&gt;
+      &lt;li&gt;homecoming&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The Rivalry Begins | Act 2: The Illusion of Sacrifice | Act 3: The Ultimate Trick&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Two rival magicians in Victorian London become consumed by obsession after a fatal stage accident, sacrificing relationships, identities, and lives to create the ultimate illusion.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: A tragic water-tank accident divides the magicians and begins a destructive cycle of rivalry and sabotage.&lt;/li&gt;
+    &lt;li&gt;Act 2: A teleportation illusion intensifies the feud, leading Angier toward Tesla while Borden’s devotion to craft strains every relationship.&lt;/li&gt;
+    &lt;li&gt;Act 3: The secrets behind both illusions are revealed, exposing the human cost of obsession, sacrifice, and living a double life.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Did Borden tie the wrong knot, and did Borden truly know which knot was tied?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The screenplay’s symbolism, paired birds, foreshadowing, blocking, and mirrored rivalries make every scene necessary and reward immediate rewatching.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The twist holds up because the movie stays faithful to its clues; the twin performance, missing fingers, and divided relationships all remain consistent.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Is Angier the villain, or is Angier’s escalating cruelty understandable after watching a spouse die during Borden’s trick?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Obsession&lt;/li&gt;
+      &lt;li&gt;sacrifice&lt;/li&gt;
+      &lt;li&gt;rivalry&lt;/li&gt;
+      &lt;li&gt;identity&lt;/li&gt;
+      &lt;li&gt;showmanship versus craft&lt;/li&gt;
+      &lt;li&gt;passion&lt;/li&gt;
+      &lt;li&gt;deception&lt;/li&gt;
+      &lt;li&gt;divided lives&lt;/li&gt;
+      &lt;li&gt;the cost of applause&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: A Job Before the Fall&lt;/li&gt;
+    &lt;li&gt;Act 2: Paranoia in the Warehouse&lt;/li&gt;
+    &lt;li&gt;Act 3: Trust Runs Out&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;After a diamond heist collapses into chaos, a crew of criminals regroups in a warehouse and begins searching for the rat among them. As suspicion grows, relationships fracture and the aftermath becomes more important than the robbery itself.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: Discussion of the crew&amp;#39;s structure, robbery planning, trust, conspiracy theories, and Tarantino&amp;#39;s early career.&lt;/li&gt;
+    &lt;li&gt;Act 2: Analysis of Mr. Blonde, the undercover storyline, the famous tipping scene, and the film&amp;#39;s cultural reputation.&lt;/li&gt;
+    &lt;li&gt;Act 3: Debate over whether the movie is genuinely great or simply pretentious, plus discussion of alternative endings and Tarantino&amp;#39;s evolution as a filmmaker.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is Reservoir Dogs actually a great movie, or has its reputation been elevated because Tarantino later became one of the most acclaimed directors of all time?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie feels more culturally important than it feels enjoyable today. Its influence on later filmmakers is undeniable, but many of its characters and story elements feel underdeveloped on rewatch.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Reservoir Dogs may be the victim of retrospective praise. People love Pulp Fiction so much that they project some of that greatness backward onto Tarantino&amp;#39;s debut feature.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Is it better to commit a robbery with close friends or complete strangers, and does Reservoir Dogs prove that both approaches are doomed to fail?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Trust vs. self-preservation&lt;/li&gt;
+      &lt;li&gt;Loyalty and betrayal&lt;/li&gt;
+      &lt;li&gt;The psychology of lying&lt;/li&gt;
+      &lt;li&gt;Reputation versus reality&lt;/li&gt;
+      &lt;li&gt;Criminal organizations&lt;/li&gt;
+      &lt;li&gt;Group dynamics under pressure&lt;/li&gt;
+      &lt;li&gt;The costs of paranoia&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Coming-of-age baseball classic about childhood, summer, and neighborhood friendship.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Are you still friends with anyone from your childhood neighborhood?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Heroes get remembered and legends never die.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Adults should get one summer off every decade.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Childhood&lt;/li&gt;
+      &lt;li&gt;friendship&lt;/li&gt;
+      &lt;li&gt;nostalgia&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Gothic mystery/horror built on supernatural skepticism and Tim Burton atmosphere.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Would you rather be the writer or director?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Johnny Depp and Tim Burton are an underrated actor-director collaboration.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The B-plot is usually the vegetables you sneak into the story.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Mystery&lt;/li&gt;
+      &lt;li&gt;supernatural&lt;/li&gt;
+      &lt;li&gt;worldbuilding&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Roc-A-Fella cult crime movie about ABM taking over North Philly.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was this the OG Tubi movie?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; This is five-star classic Black cinema, warts and all.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; If you remove the good parts of Goodfellas, what remains is State Property.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Nostalgia&lt;/li&gt;
+      &lt;li&gt;crime&lt;/li&gt;
+      &lt;li&gt;rap culture&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Drama about early-onset Alzheimer’s, identity, memory, and family care.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Would you use genetic testing to edit chronic illness out?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The “most disappointing” child saw Alice the clearest.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Alice likely masked the disease longer because intelligence let her compensate.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Memory&lt;/li&gt;
+      &lt;li&gt;identity&lt;/li&gt;
+      &lt;li&gt;illness&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Original fantasy/drama about a man hearing the narrator of his life.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; If a voice narrated your life, what genre would it be?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Autopilot can make you feel like a side character in your own life.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Shout out to original movies.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Routine&lt;/li&gt;
+      &lt;li&gt;mortality&lt;/li&gt;
+      &lt;li&gt;originality&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; 80s party comedy about career pressure, lying, and adulthood.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; What was your favorite Grand Theft Auto?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; It is fun practice to extract conversation from a mediocre movie.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; White Friday minus compelling characters and being funny.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Adulthood&lt;/li&gt;
+      &lt;li&gt;nostalgia&lt;/li&gt;
+      &lt;li&gt;pressure&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: The Perfect Week Begins | Act 2: Truth Enters The Room | Act 3: Wedding Day Reckoning&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;Days before their wedding, Emma and Charlie’s seemingly perfect relationship is shattered by a shocking confession from Emma’s past, forcing everyone around them to confront trust, forgiveness, and identity.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 establishes their romance and wedding preparations. Act 2 detonates the story with Emma’s revelation that she once planned a school shooting. Act 3 follows the emotional fallout, wedding chaos, and ambiguous reconciliation.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Is Emma’s revelation alone enough to call off the wedding, or is the larger issue everything else surrounding her character?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The film feels like a 100-minute panic attack, using anxiety, awkwardness, and emotional tension to place viewers directly in Charlie’s perspective.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The biggest red flag was not the confession itself, but Emma reaching adulthood with virtually no close friendships or meaningful relationships.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Do Emma and Charlie survive as a couple after the ending, or was the damage too large to overcome?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Forgiveness&lt;/li&gt;
+      &lt;li&gt;trust&lt;/li&gt;
+      &lt;li&gt;hidden identity&lt;/li&gt;
+      &lt;li&gt;mental health&lt;/li&gt;
+      &lt;li&gt;love versus judgment&lt;/li&gt;
+      &lt;li&gt;emotional immaturity&lt;/li&gt;
+      &lt;li&gt;second chances&lt;/li&gt;
+      &lt;li&gt;relationship pressure&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The Photo That Opens The Door&lt;/li&gt;
+    &lt;li&gt;Act 2: Parallel Lives, Parallel Problems&lt;/li&gt;
+    &lt;li&gt;Act 3: Choosing What To Carry Forward&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt;&lt;/p&gt;
+  &lt;p&gt;After her mother&amp;#39;s death, Mae discovers a photograph and a series of unanswered questions about her family&amp;#39;s history. Her search for answers brings her together with journalist Michael Block, sparking a romance while two generations of love stories unfold in parallel.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act 1: The hosts discuss Issa Rae&amp;#39;s performance, the film&amp;#39;s premise, and the lack of chemistry between the leads.&lt;/li&gt;
+    &lt;li&gt;Act 2: Focus shifts to the dual timelines, comparisons to Love Jones, the soundtrack, and the film&amp;#39;s incomplete character arcs.&lt;/li&gt;
+    &lt;li&gt;Act 3: Discussion centers on letters, family secrets, inherited memories, and why the film never fully delivers on its emotional potential.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Should Michael have pursued a serious relationship with Mae while actively preparing to take a job in another country?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie contains the ingredients for a meaningful story about Black motherhood, ambition, generational wounds, and family legacy, but never fully commits to developing any of those ideas.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; The film feels like two separate movies stitched together. The flashbacks and present-day romance rarely connect in a meaningful way, leaving both storylines underdeveloped.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; Was this a genuine romance, or was it simply a less compelling attempt to recreate the magic of Love Jones for a newer generation?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Family legacy&lt;/li&gt;
+      &lt;li&gt;Motherhood&lt;/li&gt;
+      &lt;li&gt;Generational trauma&lt;/li&gt;
+      &lt;li&gt;Ambition versus relationships&lt;/li&gt;
+      &lt;li&gt;Memory and grief&lt;/li&gt;
+      &lt;li&gt;Love across generations&lt;/li&gt;
+      &lt;li&gt;Identity and self-discovery&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Holiday family drama about secrets, siblings, debt, relationships, and reunion.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Does your family do a big Christmas?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Black parent logic: you cannot sing, but you can ride a motorcycle.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Christmas family movies all have the same plot, but it works.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Family&lt;/li&gt;
+      &lt;li&gt;holidays&lt;/li&gt;
+      &lt;li&gt;secrets&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Horror mystery about a town after almost an entire class disappears.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Why did no one have guns?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Camera work and child narration build confusion and suspense.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Act one and two are great; the ending falls apart.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Grief&lt;/li&gt;
+      &lt;li&gt;suspense&lt;/li&gt;
+      &lt;li&gt;endings&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Sports comedy about hustling, partnership, money, and relationships in 90s LA.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Was Gloria right to leave?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; Gloria was right to leave because of repeated money-management issues.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Why don’t these people just get jobs?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Money&lt;/li&gt;
+      &lt;li&gt;relationships&lt;/li&gt;
+      &lt;li&gt;basketball&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Run down and/or transcript notes preserved in original archive; this page keeps the same original-section layout for OneNote import.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Summary:&lt;/strong&gt; Home-invasion slasher discussed as dumb, fun, and Halloween-curve entertainment.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;ul&gt;
+    &lt;li&gt;Act / Segment Breakdown: use original rundown act notes in OneNote as needed; this import preserves the BEFORE/AFTER page structure.&lt;/li&gt;
+  &lt;/ul&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Why is everyone doing a contract killing the hard way?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; This movie only works if everyone is stupid.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; I love a good stupid slasher; grading it on a Halloween curve.&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Horror logic&lt;/li&gt;
+      &lt;li&gt;survival&lt;/li&gt;
+      &lt;li&gt;Halloween&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
 </sst>
 </file>
 
@@ -6081,12 +6922,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Aptos"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -6114,6 +6949,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -6140,32 +6980,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -6173,6 +7003,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6513,863 +7346,751 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" style="12" customWidth="1"/>
-    <col min="5" max="5" width="72" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="72" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="8" customWidth="1"/>
+    <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="6" max="6" width="53.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>145</v>
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>147</v>
+        <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>1957</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="7">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="7">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="6" t="s">
+    </row>
+    <row r="3" spans="1:6" ht="364.5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="B3" s="4">
+        <v>1999</v>
+      </c>
+      <c r="C3" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="4">
+        <v>2016</v>
+      </c>
+      <c r="C4" s="8">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8">
+        <v>4</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F4" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="5" spans="1:6" ht="378" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B5" s="4">
+        <v>2017</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D5" s="8">
+        <v>3</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>1997</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="E7" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4">
         <v>1999</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C8" s="8">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4">
+        <v>1992</v>
+      </c>
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>2</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C10" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D10" s="8">
+        <v>4</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4">
+        <v>2006</v>
+      </c>
+      <c r="C11" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="8">
+        <v>3</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>2008</v>
+      </c>
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>5</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="391.5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1995</v>
+      </c>
+      <c r="C13" s="8">
         <v>3.5</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D13" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="405" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>2018</v>
+      </c>
+      <c r="C14" s="8">
+        <v>2</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>2019</v>
+      </c>
+      <c r="C15" s="8">
+        <v>3</v>
+      </c>
+      <c r="D15" s="8">
+        <v>3</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="F15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>2014</v>
+      </c>
+      <c r="C16" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D16" s="8">
+        <v>3</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="405" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>2024</v>
+      </c>
+      <c r="C17" s="8"/>
+      <c r="E17" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2000</v>
+      </c>
+      <c r="C18" s="8">
+        <v>5</v>
+      </c>
+      <c r="D18" s="8">
+        <v>3</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>1997</v>
+      </c>
+      <c r="C19" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D19" s="8">
+        <v>4</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>1993</v>
+      </c>
+      <c r="C20" s="8">
+        <v>5</v>
+      </c>
+      <c r="D20" s="8">
+        <v>5</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
+        <v>2008</v>
+      </c>
+      <c r="C21" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D21" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="F21" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C22" s="8">
+        <v>4</v>
+      </c>
+      <c r="D22" s="8">
+        <v>4</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C23" s="8">
+        <v>5</v>
+      </c>
+      <c r="D23" s="8">
+        <v>5</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4">
+        <v>2006</v>
+      </c>
+      <c r="C24" s="8">
+        <v>5</v>
+      </c>
+      <c r="D24" s="8">
+        <v>5</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="F24" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1992</v>
+      </c>
+      <c r="C25" s="8">
         <v>2.5</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" t="s">
-        <v>109</v>
+      <c r="D25" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="26" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1993</v>
+      </c>
+      <c r="C26" s="8">
         <v>5</v>
       </c>
-      <c r="B4" s="5">
-        <v>2016</v>
-      </c>
-      <c r="C4" s="12">
+      <c r="D26" s="8">
         <v>5</v>
       </c>
-      <c r="D4" s="12">
+      <c r="E26" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4">
+        <v>1999</v>
+      </c>
+      <c r="C27" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4">
+        <v>2002</v>
+      </c>
+      <c r="C28" s="8">
+        <v>5</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4">
+        <v>2014</v>
+      </c>
+      <c r="C29" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="D29" s="8">
+        <v>5</v>
+      </c>
+      <c r="E29" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4">
+        <v>2006</v>
+      </c>
+      <c r="C30" s="8">
+        <v>3</v>
+      </c>
+      <c r="D30" s="8">
+        <v>2</v>
+      </c>
+      <c r="E30" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>2011</v>
+      </c>
+      <c r="C31" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D31" s="8">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F31" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4">
+        <v>2026</v>
+      </c>
+      <c r="C32" s="8">
         <v>4</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G4" t="s">
-        <v>110</v>
+      <c r="D32" s="8">
+        <v>4</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" t="s">
+        <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="5">
-        <v>2017</v>
-      </c>
-      <c r="C5" s="12">
+    <row r="33" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4">
+        <v>2020</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2</v>
+      </c>
+      <c r="D33" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4">
+        <v>2007</v>
+      </c>
+      <c r="C34" s="8">
+        <v>3</v>
+      </c>
+      <c r="D34" s="8">
         <v>3.5</v>
       </c>
-      <c r="D5" s="12">
+      <c r="E34" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4">
+        <v>2025</v>
+      </c>
+      <c r="C35" s="8">
         <v>3</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>111</v>
+      <c r="D35" s="8">
+        <v>3</v>
+      </c>
+      <c r="E35" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="F35" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C6" s="12">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>112</v>
+    <row r="36" spans="1:6" ht="405" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4">
+        <v>1992</v>
+      </c>
+      <c r="C36" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="D36" s="8">
+        <v>4</v>
+      </c>
+      <c r="E36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="F36" t="s">
+        <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1997</v>
-      </c>
-      <c r="C7" s="12"/>
-      <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1999</v>
-      </c>
-      <c r="C8" s="12">
+    <row r="37" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4">
+        <v>2011</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="D37" s="8">
         <v>4</v>
       </c>
-      <c r="D8" s="12">
-        <v>4</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1992</v>
-      </c>
-      <c r="C9" s="12">
-        <v>3</v>
-      </c>
-      <c r="D9" s="12">
-        <v>2</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="5">
-        <v>2002</v>
-      </c>
-      <c r="C10" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="D10" s="12">
-        <v>4</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="5">
-        <v>2006</v>
-      </c>
-      <c r="C11" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="D11" s="12">
-        <v>3</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="5">
-        <v>2008</v>
-      </c>
-      <c r="C12" s="12">
-        <v>5</v>
-      </c>
-      <c r="D12" s="12">
-        <v>5</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="5">
-        <v>1995</v>
-      </c>
-      <c r="C13" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D13" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="5">
-        <v>2018</v>
-      </c>
-      <c r="C14" s="12">
-        <v>2</v>
-      </c>
-      <c r="D14" s="12">
-        <v>2</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="5">
-        <v>2019</v>
-      </c>
-      <c r="C15" s="12">
-        <v>3</v>
-      </c>
-      <c r="D15" s="12">
-        <v>3</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" s="5">
-        <v>2014</v>
-      </c>
-      <c r="C16" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D16" s="12">
-        <v>3</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="5">
-        <v>2024</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="E17" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="5">
-        <v>2000</v>
-      </c>
-      <c r="C18" s="12">
-        <v>5</v>
-      </c>
-      <c r="D18" s="12">
-        <v>3</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G18" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1997</v>
-      </c>
-      <c r="C19" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D19" s="12">
-        <v>4</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>53</v>
-      </c>
-      <c r="B20" s="5">
-        <v>1993</v>
-      </c>
-      <c r="C20" s="12">
-        <v>5</v>
-      </c>
-      <c r="D20" s="12">
-        <v>5</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B21" s="5">
-        <v>2008</v>
-      </c>
-      <c r="C21" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D21" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C22" s="12">
-        <v>4</v>
-      </c>
-      <c r="D22" s="12">
-        <v>4</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C23" s="12">
-        <v>5</v>
-      </c>
-      <c r="D23" s="12">
-        <v>5</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="5">
-        <v>2006</v>
-      </c>
-      <c r="C24" s="12">
-        <v>5</v>
-      </c>
-      <c r="D24" s="12">
-        <v>5</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="E37" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="F37" t="s">
         <v>68</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1992</v>
-      </c>
-      <c r="C25" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="D25" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="5">
-        <v>1993</v>
-      </c>
-      <c r="C26" s="12">
-        <v>5</v>
-      </c>
-      <c r="D26" s="12">
-        <v>5</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="G26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="5">
-        <v>1999</v>
-      </c>
-      <c r="C27" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D27" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>77</v>
-      </c>
-      <c r="B28" s="5">
-        <v>2002</v>
-      </c>
-      <c r="C28" s="12">
-        <v>5</v>
-      </c>
-      <c r="D28" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>80</v>
-      </c>
-      <c r="B29" s="5">
-        <v>2014</v>
-      </c>
-      <c r="C29" s="12">
-        <v>4.5</v>
-      </c>
-      <c r="D29" s="12">
-        <v>5</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="5">
-        <v>2006</v>
-      </c>
-      <c r="C30" s="12">
-        <v>3</v>
-      </c>
-      <c r="D30" s="12">
-        <v>2</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="G30" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>86</v>
-      </c>
-      <c r="B31" s="5">
-        <v>2011</v>
-      </c>
-      <c r="C31" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="D31" s="12">
-        <v>1</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="G31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>89</v>
-      </c>
-      <c r="B32" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C32" s="12">
-        <v>4</v>
-      </c>
-      <c r="D32" s="12">
-        <v>4</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" s="5">
-        <v>2020</v>
-      </c>
-      <c r="C33" s="12">
-        <v>2</v>
-      </c>
-      <c r="D33" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="G33" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>95</v>
-      </c>
-      <c r="B34" s="5">
-        <v>2007</v>
-      </c>
-      <c r="C34" s="12">
-        <v>3</v>
-      </c>
-      <c r="D34" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="G34" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="5">
-        <v>2025</v>
-      </c>
-      <c r="C35" s="12">
-        <v>3</v>
-      </c>
-      <c r="D35" s="12">
-        <v>3</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="G35" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="5">
-        <v>1992</v>
-      </c>
-      <c r="C36" s="12">
-        <v>3.5</v>
-      </c>
-      <c r="D36" s="12">
-        <v>4</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G36" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>104</v>
-      </c>
-      <c r="B37" s="5">
-        <v>2011</v>
-      </c>
-      <c r="C37" s="12">
-        <v>2.5</v>
-      </c>
-      <c r="D37" s="12">
-        <v>4</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="G37" t="s">
-        <v>140</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{8E5B87CC-F717-4172-93E2-C446A611ADD5}"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{8E5B87CC-F717-4172-93E2-C446A611ADD5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7386,11 +8107,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>141</v>
+      <c r="A1" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>148</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
@@ -7398,284 +8119,284 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>150</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>154</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>162</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>163</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>164</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>166</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>170</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>176</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>178</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>180</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>98</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>101</v>
+        <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>183</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/Movie Archive Inputs.xlsx
+++ b/Movie Archive Inputs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Creative\Podcasts\Website\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11AB435-A7A4-42DF-BD98-EE62D6A119C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD4D2A1-218C-4982-BCEA-37AB0A8980C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Movie Ratings" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="150">
   <si>
     <t>12 Angry Men</t>
   </si>
@@ -6909,6 +6909,190 @@
     &lt;/ul&gt;
   &lt;/div&gt;
 &lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Hustlers</t>
+  </si>
+  <si>
+    <t>&lt;section class="show-notes-highlights"&gt;
+  &lt;h2&gt;Show Notes &amp;amp; Highlights&lt;/h2&gt;
+  &lt;h3&gt;Episode Rundown&lt;/h3&gt;
+  &lt;h3&gt;Front Half / Episode Segments&lt;/h3&gt;
+  &lt;p&gt;Act 1: The Education | Act 2: The Recession Pivot | Act 3: The Cost of the Game&lt;/p&gt;
+  &lt;h3&gt;Movie / Episode Basics&lt;/h3&gt;
+  &lt;p&gt;A young stripper learns the business from Ramona before the 2008 financial crisis forces a group of dancers into an increasingly dangerous criminal scheme targeting wealthy clients.&lt;/p&gt;
+  &lt;h3&gt;Act / Segment Breakdown&lt;/h3&gt;
+  &lt;p&gt;Act 1 covers mentorship, strip-club culture, and power dynamics. Act 2 explores the economic fallout of 2008 and the women’s scam operation. Act 3 focuses on accountability, loyalty, criminal consequences, and moral ambiguity.&lt;/p&gt;
+  &lt;h3&gt;Episode Highlights&lt;/h3&gt;
+  &lt;p&gt;&lt;strong&gt;Best Question:&lt;/strong&gt; Did the women genuinely believe they were helping themselves survive, or were they simply rationalizing serious crimes?&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Jordan Insight:&lt;/strong&gt; The movie succeeds because everyone is morally compromised. The women, the customers, and the clubs all operate in shades of gray rather than simple heroes and villains.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Darius Insight:&lt;/strong&gt; Hustlers is one of the better films about the 2008 financial crisis because it captures how quickly economic desperation can push ordinary people toward extreme choices.&lt;/p&gt;
+  &lt;p&gt;&lt;strong&gt;Best Debate:&lt;/strong&gt; If the genders were reversed, would audiences have celebrated the story the same way?&lt;/p&gt;
+  &lt;div class="major-themes"&gt;
+    &lt;h3&gt;Major Themes&lt;/h3&gt;
+    &lt;ul&gt;
+      &lt;li&gt;Economic survival&lt;/li&gt;
+      &lt;li&gt;exploitation&lt;/li&gt;
+      &lt;li&gt;mentorship&lt;/li&gt;
+      &lt;li&gt;loyalty&lt;/li&gt;
+      &lt;li&gt;financial desperation&lt;/li&gt;
+      &lt;li&gt;gender dynamics&lt;/li&gt;
+      &lt;li&gt;accountability&lt;/li&gt;
+      &lt;li&gt;crime and rationalization&lt;/li&gt;
+    &lt;/ul&gt;
+  &lt;/div&gt;
+&lt;/section&gt;</t>
+  </si>
+  <si>
+    <t>Jordan: Welcome to the Out the Trunk pod with Jordan and Darius. My name is Jordan. That's Jordan to be writing on all socials.
+Darius: And I'm Darius. That's these all up in area on all socials. And today we're.
+Jordan: Going to be talking about the movie Hustlers, what worked, what didn't, and whether the movie's big swings paid off. Let's get into it.
+Darius: Act 1, the education. Destiny enters a high pressure club world, learns from Ramona's confidence and strategy, and begins to understand the power dynamics behind performance, money, and survival. Off the rip, I feel like I'm an alien from a different planet because I do not enjoy strip clubs at all. And I get that that makes me alien to most men. But every time I go, I'm like, I just would rather be somewhere else right now. Like, I don't enjoy this. You know, I understand that makes me weird, but they're not for me. So a little fun fact about Darius.
+Jordan: Yeah, I've been a few times. It's cool. It's not my, not really my like regular type thing. We do know people who it is the regular thing. Yeah, I mean, it's all right. It's, you know, it's cool when you're with friends and they want to go. It's better to go with like your women friends. It's more enjoyable for everyone. From what I hear.
+Darius: I remember one of my favorite tweets was the guy who was like, dudes going to strip clubs. It's got to be so odd. It's like, hey, you guys want to go get some ****** together? Sure. What else we do it like? and I felt so seen because I was like, I thought I was the only one who thought that I'm just not into this.
+Jordan: No, it actually is nuts. It's like, because at no point in life would you be like, hey, you want to sit with me while I can dry up?
+Darius: Yeah, it's just, I'm not sure why this isn't as taboo. I mean, it's not taboo at all as ****. In some cities, it's like a restaurant with strippers in it.
+Jordan: I'm about to say, yeah, Atlanta and like New Orleans.
+Darius: Not for me. I've been to strip clubs all over the country. Mostly not at my idea. You know, bachelor parties, fellas want to go. I'm not a party hooper.
+Jordan: Yeah.
+Darius: So like, if the group's going, I'm not going to be like, this is a moral outbreak, you know, I just whatever. But yeah, yeah.
+Jordan: You know, Vegas Friendsgivings, Atlanta, you know, the whole thing.
+Darius: Oh, yeah. Y'all did DoorDash strippers after Thanksgiving dinner. I forgot about that. That was one of our best episodes.
+Jordan: It really was. I didn't. I didn't order them. I was just there. And while they were arrived at the location for the listeners.
+Darius: You know, it doesn't. It doesn't matter. You were there when the strippers were called up on the app. Yeah, that's and dropped off via in somebody's Honda Sonata. And yeah, the rest was history.
+Jordan: The rest is history. And in. My first note is JLo is fine as ****. That is a central plot point. That is a central plot point of the movie, literally, because she is a stripper. Also, she's an amazing actress. And I know we like to she's fun to like make fun of on social media and stuff like that. But she's really super talented. And I'd love to see her more movies and especially like more villain roles because she was phenomenal in this movie.
+Darius: Yeah, you she does. The IMDB is bloated because she does a lot of Netflix. Blop the slop.
+Jordan: Yeah.
+Darius: Like, you know, oh, someone kidnapped my kid. I'm going to go, you know, like she has a lot of slop on the Netflix and the.
+Jordan: Yeah, she does.
+Darius: But when she locks in and they give her a good script, she's up there.
+Jordan: You know, it's not too many that can **** with her.
+Darius: No, it's. Yeah. Yeah. Well, that's English. What else you got for act one?
+Jordan: I like how they broke down. like the psychology of the guys, like the profiles of what they look for when they're looking for a mark. They're like, look at his shoes, look at his watch, look at the permanent things, not the suits, because you can wear a nice suit for one day. That doesn't give away your lifestyle. Like how they broke down like, oh, this is the low level guy on Wall Street. This is the hedge fund exec. This is the whatever the term is. I don't know. I'm not bigging this to Wall Street. I mean, stocks, but the mid-level guys. I thought that was really cool how they kind of broke that down and showed the profiles. Also, it was insane even showing like their houses, like they all had crazy cribs, but there was still a vast difference in their classes.
+Darius: Yeah, it's like, especially when it comes to formal wear, the suits are dead. I mean, the shoes are a dead giveaway because everybody got two or three nice suits and you got to wear shoes every day. And so if your money is funny, you're not replenishing them. And they get beat or they're cheap to begin with. And it's just right. Yeah. The shoes are always you see a lot of, you know, nice to very nice suits and the shoes are busted and it's like, okay, you bought that one suit, you take care. And there's no shade. I own two suits. So granted, I don't really I don't wear that only use for them, but it's not like I have a closet full of suits either. And I have one pair of black dress shoes and one pair of brown dress shoes, and they're cheap. So I speak from experience.
+Jordan: So you know the mark in the club.
+Darius: No, no, I would never fall for any of these tricks.
+Jordan: I think, you know, that too.
+Darius: It's a lot. The the male ego is crazy because you see you get this a lot like dudes will touch down in Vegas and get drugged and robbed. And the story will be like, I walked in the club and these two women were interested in me and they asked me back to their room. And I'm like, have you ever had that kind of motion in your life?
+Jordan: Like outside of the movies, In Little.
+Darius: Rock, Arkansas, you've never had that kind of motion, but you touched down in Las Vegas and now you just can't keep them on for you.
+Jordan: Right.
+Darius: It never occurred to you that this is odd.
+Jordan: Yeah, and it's like, I mean, granted, it's different in the movies versus real life, but like in the movie, they weren't really hammered by the time girls got to them. So it really doesn't make any sense why you would fall for that.
+Darius: I've had it. I've just tried on me in Vegas. It's real. It's not like it happens just like that. Like you'll be sitting at a bar having your drink and a woman that two, like one woman, sometimes two that are just, it's just way too good to be true. Will come up to you and be like, Oh, when did you fly in? What do you do for a living? You're so funny. And they're just laughing at everything you say. And you're just like, I'm not that smooth.
+Jordan: Yeah, no. And I can't. And I don't want to afford you, even if I could.
+Darius: So there's like, you're a solid nine. I've never had one nine come up to me and be this friendly. Now, two in Vegas, like, come on, right?
+Jordan: Yeah.
+Darius: If it happens just like that, it was not a realistic.
+Jordan: Yeah, that's the crazy part to me. It's like, I don't know how they don't know. Like, it's like so obvious.
+Darius: And any time you see a picture of a dude after the fact, you like my guy.
+Jordan: Yeah, it's like when the cops read the articles and they were like, what a ****.
+Darius: It's like, dude, you know, fellas, be cognizant of the kind of emotion you have in your day-to-day. And then when you go to these cities, LA, Miami, Vegas, I have to say crazy nights can't happen because I've definitely, while traveling, the stars aligned and it was a good time. But you know, keep your wits about you. Don't get too overly drunk. If it's too good to be true.
+Jordan: It is.
+Darius: It probably is, man. You got to know.
+Jordan: You got to know.
+Darius: Now it's entirely possible.
+Jordan: Know what you look like?
+Darius: It's entirely possible to be out, you and the fellas at a club in Vegas and run into a bachelorette party. And they're good looking, but regular good looking.
+Jordan: Yeah, that makes sense.
+Darius: And you know, one of the bridesmaids is just in a great vacation mood. That's fine. But like a solid nine and her girlfriend come up is like, hey, you want to go have a threesome? It's like, you're going to wake.
+Jordan: Up with all your **** gone and you're not going to remember the last week of your life.
+Darius: At least put your wallet in the safe so you can get yourself something to eat the next day. They will take your socks if it's available.
+Jordan: And then you got to explain that to your bank and your wife or girlfriend, whoever you have, it's just, and then you, and then they're like, really, that's what happened to you? Like, and you didn't see that coming.
+Darius: It's just, it's not to say good nights can't happen on the road, because it does, especially in party cities where you're not the only person on vacation. You want to resort in Cancun, everyone's there's everyone there is Ain't got to worry about work, ain't got to worry about their kids, ain't got to worry about whatever. A good time, hair down. But just be aware of where you rank, what kind of emotion you normally have, and weigh that against your current circumstances and ask yourself, does this make sense? You know.
+Jordan: Yeah. In the words of Boss Mandilo, it's a motion party. You cannot get in.
+Darius: Exactly, Ben. It's just, you know. But it does happen exactly like the movies. So let me ask you this. So they set up almost like a mentorship program between, I'm really bad at character names, but J-Lo's character and Constant Wu's character. And in a cutthroat business, like a strip club, where the money is finite, like you're working for, the money is not pooled, you know, can mentorship really exist in a business that's cutthroat where everyone's working for the same $100 that's available by the men on the floor.
+Jordan: Yeah, I don't. I'm sure I'm sure it happens. Like, I know it happens. But from an institutional standpoint, I don't believe so. Like, you know, you think about it. And also, Jayla's character is an older character in the like she's older, like the older lady in the strip club is not trying to help the young new girl. And like, that's just not plausible. Like, this is how they pay the bills, you know what I'm saying?
+Darius: Like, that's just literally age out. So.
+Jordan: Yeah, like, like Brett Ford wasn't trying to help Aaron Rodgers for a reason. You know what I'm saying?
+Darius: Like, I was actually going to bring up that example is like human beings are naturally cooperative because you'll see you'll see videos of Miles Garrett and Will Anderson and a couple of people working out and like. Miles Garrett has. Why would he help Will Anderson get better? Right. But that's just how people are, even though they're competing for the same trophy. It's just. We're just naturally a cooperative species. So I think even though it makes no actual sense, it's possible you see it happen. And that was my example of it happening was like sports where people, competitors in the off season will work out together and make each other better, which doesn't actually make any sense beyond our natural ability to cooperate and, you know, pool our resources. So.
+Jordan: Yeah, that's a good point. Yeah, like I mean, trying to think like I remember Ironically, that was it at a strip club one night with when it was others when we all went, we're all there, whatever. And the one girl was done working. And then the next girl was about to come out to work. And she was like, oh, that's my best friend. Like, make sure to give her a good tip. Like, you know, so there is some camaraderie there. But I had a friend, a childhood friend who was a dancer. And she would tell me like some of the **** that went on between the girls and I can't go to this club because this girl's boyfriend doesn't like me and he runs the door and, **** like that. So there is a very competitive, element to that field.
+Darius: I have a friend of mine who used to bounce at a strip club, and he said he broke up fights at least every other night between the strippers.
+Jordan: Yeah, makes sense.
+Darius: He was like, most of my bouncing was. because now that was my client or I saw him last week or you owe me 10% of da da da da da because my stage time was cut or.
+Jordan: Just tipping out and all that stuff.
+Darius: Tipping to the DJ for more another song and just it can be ruthless. Yeah, because the men there they're not most of them aren't throwing all of their money and so you have to right you're fighting for someone else's discretionary income um correct of which you know it's a limited resource so yeah you got anything else for act one?
+Jordan: Um this movie is loaded I hadn't seen this movie play since it came out and I forgot how many just how many people were in this movie they had everybody in here.
+Darius: And honestly what did this release 2018?
+Jordan: I think so. Maybe 16?
+Darius: I mean, this is probably Lizzo before the fame, right?
+Jordan: I think like right before or at the peak, 2019.
+Darius: So we probably did.
+Jordan: So she was kind of popping back.
+Darius: Yeah, but like Cardi B just had that.
+Jordan: She had just popped.
+Darius: Yeah. It's a lot of people that this budget probably couldn't afford anymore. But it was it's cool. They all had little cameos and they all did. what they could with the time they had. And I enjoyed it, you know?
+Jordan: Me too. Me too. Did you have a favorite performance in the movie? Aside from J.Lo and constants, I guess I should say.
+Darius: The reporter, Kate Winslet, I think it was.
+Jordan: Julia Styles.
+Darius: Julia Styles Save the Last Dance. Yeah, I just thought I get to it later that I think that's kind of like a movie trope, but just the way she would react to the subject in the questioning, I thought if someone who listens to a lot of interview pods and watches a lot of journalism at work, I just thought she caught the nuances of that really, really well. There's an art to interviewing someone, when to interject, when to let them speak, when to, it's, you don't know what good interviewing is until you hear bad interviews.
+Jordan: See a bad interviewer?
+Darius: Like the super popular Joe Budden's pod, I think they are terrible interviewers. I never hear what the subject has to say. Yeah, they'll have a guest on and I'm like, can y'all let him answer the damn question? Why is he even here then? Like you just like, it's like. Right. And so she she got getting in and out of your cuts, asking the question and getting out of the way, not clearing your throat too much. I thought that she was really great as she did. She did a good job of acting like a great interviewer, so.
+Jordan: Yeah, that's true.
+Darius: Straving the last dance. What else you got for act one?
+Jordan: That's all I got for act one.
+Darius: Heading into act 2, the recession pivot, millennial shudder right there. Economic pressure changes the rules, forcing the women to reassess work, friendship, and risk as they look for stability in an unforgiving post-crash landscape. I have a particular affinity for movies about the financial crash, crash of 08 because that was when I entered the workforce for real. And, you know, for the kids, if you weren't around for that, it was it's impossible to explain to you how I knew people with like master degrees who were taking jobs at McDonald's because that was the job. That was all they could do. You know, it was it's it is Yeah, it was it was an era defining time. So where were you in a way? Were you still in school or what was going on in a way?
+Jordan: Yeah, I was in high school. I was a sophomore.
+Darius: All right, fair enough.
+Jordan: Yeah, I was. I luckily I was not. They didn't need me.
+Darius: Fair enough. Yeah, I it's. It's just, you know, it is a special place in my upbringing. So yeah, that's part of why I like this movie is because it captures the overnight change well like she comes back to the club and like it was empty it was empty and the things she had to do for the things she thought she'd never had to do for money like she has to do and you know obviously it's way different into the spectrum but like you know people with master's degrees never thought they'd have to apply at Wendy's and they had to because that's right he was and so yeah that kind of resonated with me in a way what you got for act two?
+Jordan: They did do a great job of showing what it's like trying to look for a job in a really ****** economy. And it's kind of interesting because I was thinking about this over the last few weeks and the conversation I had with my dad, maybe like close to a year ago. And I was trying to explain to him kind of what it's like now, you know, for like younger people. And I was like, I was like, we're the most educated underachievers of all time. like the job market, the way the job market is and competitiveness of it, the lack of, I won't say livable wages, but just, it's just really hard to get a comfortable job in a position that would really let you have the life that you want to have based on what we were told when we went to high school and went to college, and kind of the movie did a great job of showcasing that because, she did try to do the right thing she got an honest job you know she got a GED she was trying to go to school market went to hell and she can't even sell do retail and it's like I worked at a bar if I can that's talking to people all day like how can I not you know do retail and it's just like it feels like the days of like taking a shot on a candidate for like a job is kind of over and the job that scene did a great job of of showing that yeah that's what.
+Darius: People made the, I saw this point made on Twitter is like, what's with these jobs with these three, four, five rounds of interviews? And someone responded with, that's because they're all looking for a unicorn candidate instead of just like picking somebody and teaching them a job. And yeah, just like.
+Jordan: They don't want to train anymore.
+Darius: They don't want to train anymore. They want people who already know what they're already know the job. Not only that, but they just like, you know, I once had a mentor earlier in my career, he sat me down and he was like, one day you're going to have a team and on that team is going to be 10 people and you're going to have two to three superstar high productive employees. And you're going to have two to three. He's like, you're going to have two highly productive employees and you're going to have two pieces of ****. And you're going to have six people who just want to clock in, do their job and go home. Right. You nurture the people who want to be productive and get advanced and you help them nurture their career and you cycle out the pieces of **** to, you know, get them out of there. You leave the six people who just want to work and go home alone. Like, you know, like, and so it's almost like nobody wants employees that just want to work and go home. Everyone wants 10 superstars on a team and that's just not right. If it wasn't, if everyone was a superstar, I wouldn't be valuable. I always, that always resonated with me. And it's dated advice now because everyone wants 10 superstars, but he just was like, correct. Out of the 10 people, two are gonna be superstars, highly productive. You take care of them, you get them what they need. You help them develop their careers. So on and so forth. They get a little extra rope, so on and so forth. They get more privileges. But to cycle them out, leave the six that just wanna clock in, do their job, perform well. You know, get a meet expectations on their thing and go home with their families. And there's nothing wrong with that. And so we've lost that assets in work.
+Jordan: That's a great way to put it, because it feels like jobs view them as the pieces of ****. Like, you know, like I was talking about that with some friends of mine were telling me like they were looking for a job and they were saying like, let's say that their name was Jane Doe and they were like 5-2, for example. And they were saying like, I could look for a job for a girl named Jane and I wouldn't I wouldn't get it and it's like I could look for a job for a girl named Jane Doe and I wouldn't get a call back and it could be a job for a Jane Doe who's 5-2 and I still wouldn't get a call like you know what I mean and it's like because the ATS systems and the AI and the all the SEO and all that stuff it's more of a word problem than a resume you know what I'm saying it's It's more of an audition than an interview.
+Darius: It's funny because it's like you wouldn't ever actually want to do this because this is a free country. But I think a lot of industries would be better off with just auto sorting. Like this is we got 1000 college graduates this year. You get 10, you get 10, you know, like because and like almost like an NBA draft, but you know, that would never work. And you know, because there's a bunch of like civil rights issues that go with that.
+Jordan: And too many variables.
+Darius: But it's almost, it's the same as like the Netflix thing where if you have 1000 movies to watch, you're never going to pick one. If you're sitting there with 8 million applications, I want Jane Doe 52. Here's Jane Doe 51, she's out of here. Here's Doe Jane 56, she's out here. It's just like, you need to just make a decision. Stop waiting for the unicorn because unicorns by definition are exceedingly rare.
+Jordan: Correct.
+Darius: Yeah, I'm with you. It's it's.
+Jordan: And that unicorn would be over. But yeah, that's true. Yeah.
+Darius: And how long are you going to keep the unicorn, you know?
+Jordan: So that too. Yeah, it's very odd. And I feel like the the they run off good people because of the obsession with like metrics and the obsession with hyper productivity now, you know what I mean? It's like they'll, they'll say like, I don't want you to be a machine, but like actually work faster and harder and make less mistakes. Machines do that, you know what I mean?
+Darius: The, the, sorry, I lost my notes for, yeah, the, you're in a economy this, as it becomes more specialized, you're sort of losing the person who, like I said, just wants to work and go home. And so, or just like the general worker, like everyone wants, I have, I'm hiring for this position and this person needs to do this task. So I want someone who's done it for 10 years already. And it's like, it's a super specific task that you would only ever do on this team. It's like, have you considered just hiring someone with good traits and good experience and teaching them it?
+Jordan: Yeah, it feels like that's what companies used to do. Entry level like those entry level jobs don't exist basically like there if you go if you go to LinkedIn and you go to any entry level job you're gonna see they're required three to. Five years of experience. And it's like she said in the movie, she's like, if I don't have experience, how do I get experience? It's like, that's what it's like. I don't, it's bad.
+Darius: Well, you know, we're always chasing the ghost of 08. What else you got for act two?
+Jordan: Right. Okay, so they kind of, they're down bad. I don't know why that was funny to me. Whether they're down bad.
+Darius: Yeah. It's like selling *** didn't work.
+Jordan: So start scamming. They walk so Karisha could run. Pretty much.
+Darius: That's what I thought about that song too. She's definitely a child of this movie. So yes.
+Jordan: Yeah. So they kind of built this scheme to pick guys up at bars. drug them and then bring them to the strip club. They're not knowing if they worked there, I guess, as like ringers pretty much. Although I will say that the scene of them like cooking the **** was kind of crazy because how do you learn how to do that? And then also, if you're going to do that, why not just sell drugs? I don't know.
+Darius: You learn how to do that working in a strip club, which I'm sure it just like has drugs flowing in and out of it constantly. Well, Why not sell drugs? Honestly, I think a lot of them didn't see themselves as criminals. Yeah, like they thought that they were just like ripping off rich people.
+Jordan: Yeah, I think they thought they were Robin Hood.
+Darius: Yeah, that's not what my one of my questions is was what they did immoral. But clearly we both agree that drugging and bankrupting people who it's like, do they think that they were like, The CEO was in there. Like you're doing like mid managers like this. Like these are people with just like regular jobs within the organization of the bank. Like they're well paid, but they're not running a business.
+Jordan: The guys who are wealthy enough or have as much wealth as the girls thought they had, game would just hire hookers, I feel like. So.
+Darius: And it's just, yeah. The older me definitely views them a bit more critically than 2019 me did because yeah, they really like that guy's call. He's like, do I can't pay my mortgage?
+Jordan: I can't pay him work, dude. And they were maxing out everybody's cars.
+Darius: Yes. And company cars. People lost their jobs like your company credit card. Yeah. What are you going to tell them? Oh, I went to a strip club and they got robbed that you think your boss is going to hear that **** or believe you? It's just, you know, and I'm like, these aren't people who were tricking on you and got overboard. These are people you get robbed.
+Jordan: It's a totally different thing. Yeah, and I remember Cardi B, was stripping. She said she used to drug and rob guys. She said she used to do that **** to guys. And I remember people were like, yeah, well, they were going to abuse her anyway.
+Darius: And it's like, no, that's not how it works.
+Jordan: I don't know if that's how that works. Number one, #2, if you went to that guy's house and there was an agreement of services that were possibly going to be rendered, that's not.
+Darius: The same thing, She was dead wrong for trying to, I mean, just speaking of it so matter of factly, like just drugging people. Don't do that. Bad, bad Cardi. No, I don't think that they didn't want to do drugs. They didn't want to sell drugs because what they thought they were doing was like, you said, some sort of Robin Hood, some sort of benevolent activity when really what they were doing was, I mean, like multiple felonies. I'm surprised. In fact, they only went down for financial crimes. It's kind of wild because they were assaulting people.
+Jordan: Honestly, they got off really, really light. I don't know if it's because of the, they were women or if it's because of women.
+Darius: No, it's because they were women.
+Jordan: The time they were in or whatever. I don't know, maybe laws weren't strange, laws weren't stringent in 13, 2013. I don't know.
+Darius: Even the reception of this movie where it was, it was almost like joyous. I promise you a movie about a bunch of men drugging women would not be received as well.
+Jordan: Yes, absolutely right. Yes. Like imagine that scene where they throw the naked guy on the ground outside the hospital. Let's just swap all those roles.
+Darius: Yeah, I just.
+Jordan: What would we call that movie?
+Darius: I remember the energy around this movie. And it was it was very much not very much not. It was not it wasn't there was not a critical no analysis of the behavior. I'll put it that way.
+Jordan: Yeah. They treated it, what it was? It was almost treated like it was like John Q for moms.
+Darius: Yeah.
+Jordan: Like, the kid needed a new heart, so we had to rob the hospital.
+Darius: Yeah. That is interesting that I didn't think about it when I was watching this, but the reception of this movie was definitely not viewed through, we'll just call it like a Me Too lens, like it would have been if the gender roles were reversed.
+Jordan: Yes. Very true.
+Darius: What else you got for act 2?
+Jordan: Okay, so where do you think they went and left? I mean, obviously working with the cokehead chick was crazy, but do you think it was more so them leaving the club and trying to go independent, so to speak, with their little ring?
+Darius: I think like most people who commit financial crimes, They just, they went to the, where did they go left? I think they went left. I don't think there was ever a way to, sooner or later, they're gonna get caught. Someone's going to not care about being embarrassed to admit what happened to them. And they're gonna, you know, like I want, like, okay, I'll just, okay, I was, fell too hard for some women who were probably too hot for me, but they robbed me and I want justice for that. And that person's gonna have all the evidence and you're gonna go down. And they had, like I'm sure they started with, 100 bucks. But then when you're maxing out thousands of dollars, sooner or later, you're going to reach a point where someone just does not care to be embarrassed. They want revenge or justice or whatever you call it. So where they went left was going to the well one too many times. But I think that almost always happens with financial crimes. Ponzi schemes don't start as people trying to defraud people. They start with I promised this return and I can't get it, but I can go get a new investor and pay this person back. But by the time I flip the third one, I can pay everybody back.
+Jordan: I got to get another one.
+Darius: And then it works. Then you go and do it, usually you try to do it again. And then, you know, it eventually, and you keep, and it just, it never feels, you know, it's like addiction. People don't, I mean, outside of Mel on Snowfall, people don't become Rockheads overnight. It's always, you know, you go to the well, First it starts as a social thing and then it's a stressful thing. And then it's that. No one starts. She again, except for her. No one becomes a crackhead overnight. You know, it's a gradual thing. It's a party thing. Yeah. We're in the back room at a club and okay, I'm going to, you know, and then it's now you're now you're, you know, selling your microwave. Yeah. So it's It happens gradually then all at once is what they say.
+Jordan: Yeah. Do you think, I mean, Jayla's scared to kind of mention it a little bit, you know, well, she more so mentioned it in the long terms of the guys that wanted to get caught for like cheating or whatever. But do you think they factored into the, they took into account the fact that like men are less likely to report crimes against them?
+Darius: Yeah, for sure.
+Jordan: Things of that nature.
+Darius: The skeleton key of the whole thing was that they were women.
+Jordan: Yeah.
+Darius: You know, I the Weaponizing the power of male *****. Right. You know, I, it's like I've seen men willing to walk across hot coals barefoot to get, you know, to *** ****. It's so, and so that, and you know, they're pretty women, so they're harmless. And then the cops, how long did the cops hang up on people calling to try to report them? Right. it's just the entire premise of this was them believing that no one would take male victims seriously. Yeah. Yes.
+Jordan: Do you? Okay, so it might be for actor. I don't know. So there's a portion of interview where she, you can almost hear Constance Wu's character like bargaining almost like an addict where she's like, no, you have to understand like, We didn't think we were doing anything wrong. We're like, you have to understand these were guys who, would have, co</t>
   </si>
 </sst>
 </file>
@@ -7346,7 +7530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8087,6 +8271,23 @@
         <v>68</v>
       </c>
     </row>
+    <row r="38" spans="1:6" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="4">
+        <v>2019</v>
+      </c>
+      <c r="C38" s="7">
+        <v>4</v>
+      </c>
+      <c r="D38" s="8">
+        <v>3.5</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>148</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F37" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <hyperlinks>
@@ -8099,7 +8300,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5993E05E-2F2C-4E78-8DF8-86474A36DE5C}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.140625" bestFit="1" customWidth="1"/>
@@ -8399,6 +8600,14 @@
         <v>109</v>
       </c>
     </row>
+    <row r="38" spans="1:2" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>147</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
